--- a/Excel/11_Wastewater_WIP_v02.xlsx
+++ b/Excel/11_Wastewater_WIP_v02.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\htdocs\zneagcrc\GAF-VEERG-Functions\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27623E65-2795-4A97-A8CB-2B068FC593E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F84FDF4-8C41-443A-B5C4-709AB3E97C0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1020" yWindow="0" windowWidth="34605" windowHeight="18645" activeTab="2" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
+    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="12645" activeTab="2" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
   </bookViews>
   <sheets>
     <sheet name="Home" sheetId="71" r:id="rId1"/>
@@ -5302,16 +5302,16 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{86752300-1056-4C92-8247-C96E2D7BEDD4}" name="Table_SourceData_MCF_Wastewater" displayName="Table_SourceData_MCF_Wastewater" ref="D9:E14" totalsRowShown="0" dataDxfId="22" dataCellStyle="Content normal">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{86752300-1056-4C92-8247-C96E2D7BEDD4}" name="Table_SourceData_MCF_Wastewater" displayName="Table_SourceData_MCF_Wastewater" ref="D9:E14" totalsRowShown="0" dataDxfId="58" dataCellStyle="Content normal">
   <autoFilter ref="D9:E14" xr:uid="{86752300-1056-4C92-8247-C96E2D7BEDD4}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{60322701-4B4B-459F-8E0D-E1FDA0005D7E}" name="Facility type t" dataDxfId="21" dataCellStyle="Content normal">
+    <tableColumn id="1" xr3:uid="{60322701-4B4B-459F-8E0D-E1FDA0005D7E}" name="Facility type t" dataDxfId="57" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Wastewater_SourceData.Waste_MethaneCorrectionFactorWastewater_Data(), Table_SourceData_MCF_Wastewater[[#Headers],[Facility type t]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{DD81C2AC-C02C-4272-B2E3-0B8EF13E42DC}" name="CFww,t" dataDxfId="20" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{DD81C2AC-C02C-4272-B2E3-0B8EF13E42DC}" name="CFww,t" dataDxfId="56" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Wastewater_SourceData.Waste_MethaneCorrectionFactorWastewater_Data(), Table_SourceData_MCF_Wastewater[[#Headers],[Facility type t]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5391,7 +5391,7 @@
     <tableColumn id="1" xr3:uid="{AC686EA2-8D9A-4D6D-A8A8-062FB3B515CC}" name="Is in leaching zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWET_Data(),Table_SourceData_FracWET[[#Headers],[Is in leaching zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{1FCEBDA5-65F4-46B1-B370-C11FB49932FA}" name="FracWET" dataDxfId="42">
+    <tableColumn id="2" xr3:uid="{1FCEBDA5-65F4-46B1-B370-C11FB49932FA}" name="FracWET" dataDxfId="36">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWET_Data(),Table_SourceData_FracWET[[#Headers],[Is in leaching zone]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5439,7 +5439,7 @@
     <tableColumn id="1" xr3:uid="{F2C9E476-6A55-47D9-B3E7-C67EA63535FA}" name="Irrigation type i">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{88DAA629-0590-41E1-A2CC-610CF9FDB97C}" name="FracWET" dataDxfId="41" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{88DAA629-0590-41E1-A2CC-610CF9FDB97C}" name="FracWET" dataDxfId="35" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5457,7 +5457,7 @@
     <tableColumn id="1" xr3:uid="{AF9CBDC1-27EF-4EED-B8DF-92F594F394C9}" name="Climate zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data(), Table_SourceData_EFPastureRangeAndPaddock[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{F1AF672B-1B1A-422D-A6B3-621D6214B60E}" name="EFPRP" dataDxfId="40" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{F1AF672B-1B1A-422D-A6B3-621D6214B60E}" name="EFPRP" dataDxfId="34" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data(), Table_SourceData_EFPastureRangeAndPaddock[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5475,7 +5475,7 @@
     <tableColumn id="1" xr3:uid="{F56D4BDC-1A8D-48FE-B31E-DE67F81E1C52}" name="Month">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{84A8C1F6-0D04-4FAE-AC8C-5DCE94CD2667}" name="Season" dataDxfId="39" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{84A8C1F6-0D04-4FAE-AC8C-5DCE94CD2667}" name="Season" dataDxfId="33" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5507,49 +5507,49 @@
     <tableColumn id="1" xr3:uid="{F0787CE1-8BC3-48A0-BD72-4D31FF2981AB}" name="Temperature zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{236F7AC5-AA7A-4B5B-A91D-B3234A850B1F}" name="MAT (ºC)" dataDxfId="38" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{236F7AC5-AA7A-4B5B-A91D-B3234A850B1F}" name="MAT (ºC)" dataDxfId="32" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{C188DBCE-83A9-4948-B739-6D8CFA8FB1F1}" name="Anaerobic lagoon" dataDxfId="37" dataCellStyle="Content normal">
+    <tableColumn id="3" xr3:uid="{C188DBCE-83A9-4948-B739-6D8CFA8FB1F1}" name="Anaerobic lagoon" dataDxfId="31" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{7F0A7CCE-9091-445B-A615-A547A51F5200}" name="Digester / covered lagoons" dataDxfId="36" dataCellStyle="Content normal">
+    <tableColumn id="4" xr3:uid="{7F0A7CCE-9091-445B-A615-A547A51F5200}" name="Digester / covered lagoons" dataDxfId="30" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{F45FD72F-73B7-4580-B927-C93DC98F52E5}" name="Liquid systems" dataDxfId="35" dataCellStyle="Content normal">
+    <tableColumn id="5" xr3:uid="{F45FD72F-73B7-4580-B927-C93DC98F52E5}" name="Liquid systems" dataDxfId="29" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{C72DB022-C4D0-41C7-A672-C4F576EDC815}" name="Daily spread" dataDxfId="34" dataCellStyle="Content normal">
+    <tableColumn id="6" xr3:uid="{C72DB022-C4D0-41C7-A672-C4F576EDC815}" name="Daily spread" dataDxfId="28" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{98BE1154-A30B-4B37-8D42-1FCB8196ADFF}" name="Composting (passive windrow)" dataDxfId="33" dataCellStyle="Content normal">
+    <tableColumn id="7" xr3:uid="{98BE1154-A30B-4B37-8D42-1FCB8196ADFF}" name="Composting (passive windrow)" dataDxfId="27" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{FE6F67A9-BD27-47E8-B501-A2D2DDFAFD2B}" name="Solid storage" dataDxfId="32" dataCellStyle="Content normal">
+    <tableColumn id="8" xr3:uid="{FE6F67A9-BD27-47E8-B501-A2D2DDFAFD2B}" name="Solid storage" dataDxfId="26" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{1612D188-6F19-4A62-9F7B-984763732FCD}" name="Pit storage" dataDxfId="31" dataCellStyle="Content normal">
+    <tableColumn id="9" xr3:uid="{1612D188-6F19-4A62-9F7B-984763732FCD}" name="Pit storage" dataDxfId="25" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{F2B629FE-D9AC-43BB-8712-0244FAFED160}" name="Deep litter" dataDxfId="30" dataCellStyle="Content normal">
+    <tableColumn id="10" xr3:uid="{F2B629FE-D9AC-43BB-8712-0244FAFED160}" name="Deep litter" dataDxfId="24" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{AEB1AAB3-C1F7-4609-811C-C8F71F27BEA7}" name="Poultry manure with bedding" dataDxfId="29" dataCellStyle="Content normal">
+    <tableColumn id="11" xr3:uid="{AEB1AAB3-C1F7-4609-811C-C8F71F27BEA7}" name="Poultry manure with bedding" dataDxfId="23" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{30CD3C79-0D8E-4E7F-87FD-8F4EA6115707}" name="Poultry manure without bedding" dataDxfId="28" dataCellStyle="Content normal">
+    <tableColumn id="12" xr3:uid="{30CD3C79-0D8E-4E7F-87FD-8F4EA6115707}" name="Poultry manure without bedding" dataDxfId="22" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{B6966C78-6D1B-4D36-AF62-930896F91722}" name="Direct processing" dataDxfId="27" dataCellStyle="Content normal">
+    <tableColumn id="13" xr3:uid="{B6966C78-6D1B-4D36-AF62-930896F91722}" name="Direct processing" dataDxfId="21" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{319A832A-BD0E-4DCC-BA3B-3FE865BD158B}" name="Direct application" dataDxfId="26" dataCellStyle="Content normal">
+    <tableColumn id="14" xr3:uid="{319A832A-BD0E-4DCC-BA3B-3FE865BD158B}" name="Direct application" dataDxfId="20" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{1A0A5924-316D-4A5B-BC7C-60065B83EB70}" name="Pasture range and paddock" dataDxfId="25" dataCellStyle="Content normal">
+    <tableColumn id="15" xr3:uid="{1A0A5924-316D-4A5B-BC7C-60065B83EB70}" name="Pasture range and paddock" dataDxfId="19" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{41772124-674F-460B-8395-C3AE2FD9C178}" name="MAT raw" dataDxfId="24" dataCellStyle="Content normal">
+    <tableColumn id="16" xr3:uid="{41772124-674F-460B-8395-C3AE2FD9C178}" name="MAT raw" dataDxfId="18" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5567,7 +5567,7 @@
     <tableColumn id="1" xr3:uid="{9399ABC9-646D-4864-8875-225CB798A120}" name="Climate Zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data(), Table_SourceData_Common_EFOrganicFertCropResidues[[#Headers],[Climate Zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{828CCD4A-4F4D-4667-8FE5-C00753040270}" name="EFNi &amp; EFN2Oi" dataDxfId="23" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{828CCD4A-4F4D-4667-8FE5-C00753040270}" name="EFNi &amp; EFN2Oi" dataDxfId="17" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data(), Table_SourceData_Common_EFOrganicFertCropResidues[[#Headers],[Climate Zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5576,16 +5576,16 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{CAC655BD-F756-4971-8D46-22867B90DE87}" name="Table_SourceData_MCF_Sludge" displayName="Table_SourceData_MCF_Sludge" ref="D21:E26" totalsRowShown="0" dataDxfId="19" dataCellStyle="Content normal">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{CAC655BD-F756-4971-8D46-22867B90DE87}" name="Table_SourceData_MCF_Sludge" displayName="Table_SourceData_MCF_Sludge" ref="D21:E26" totalsRowShown="0" dataDxfId="55" dataCellStyle="Content normal">
   <autoFilter ref="D21:E26" xr:uid="{CAC655BD-F756-4971-8D46-22867B90DE87}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{D1DF76B8-1010-4952-AD56-4DF4622F5028}" name="Facility type t" dataDxfId="18" dataCellStyle="Content normal">
+    <tableColumn id="1" xr3:uid="{D1DF76B8-1010-4952-AD56-4DF4622F5028}" name="Facility type t" dataDxfId="54" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Wastewater_SourceData.Waste_MethaneCorrectionFactorSludge_Data(), Table_SourceData_MCF_Sludge[[#Headers],[Facility type t]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{D0EA373F-22E1-4557-BE26-A505C4693CDC}" name="CFsludge,t" dataDxfId="17" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{D0EA373F-22E1-4557-BE26-A505C4693CDC}" name="CFsludge,t" dataDxfId="53" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Wastewater_SourceData.Waste_MethaneCorrectionFactorSludge_Data(), Table_SourceData_MCF_Sludge[[#Headers],[Facility type t]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5701,49 +5701,49 @@
     <tableColumn id="1" xr3:uid="{6ED0CF1D-7CD9-4066-8EE4-25FE923E5D3B}" name="Climate zone" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{CF963462-2F2C-4BF6-A892-086541529F20}" name="MAT" totalsRowDxfId="58" totalsRowCellStyle="Content bold">
+    <tableColumn id="2" xr3:uid="{CF963462-2F2C-4BF6-A892-086541529F20}" name="MAT" totalsRowDxfId="52" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{1B3F3876-9D6F-447A-A423-66E21AC0558A}" name="MAP" totalsRowDxfId="57" totalsRowCellStyle="Content bold">
+    <tableColumn id="3" xr3:uid="{1B3F3876-9D6F-447A-A423-66E21AC0558A}" name="MAP" totalsRowDxfId="51" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{A4802F3E-DC20-40F1-AC5A-D182C68519BB}" name="Frost days per year" totalsRowDxfId="56" totalsRowCellStyle="Content bold">
+    <tableColumn id="4" xr3:uid="{A4802F3E-DC20-40F1-AC5A-D182C68519BB}" name="Frost days per year" totalsRowDxfId="50" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{1F7F9556-3126-439E-875C-D76E463F8036}" name="Elevation" totalsRowDxfId="55" totalsRowCellStyle="Content bold">
+    <tableColumn id="5" xr3:uid="{1F7F9556-3126-439E-875C-D76E463F8036}" name="Elevation" totalsRowDxfId="49" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{DBB23AF3-C817-42CE-BE89-ADDA8D904773}" name="MAP:PET" totalsRowDxfId="54" totalsRowCellStyle="Content bold">
+    <tableColumn id="6" xr3:uid="{DBB23AF3-C817-42CE-BE89-ADDA8D904773}" name="MAP:PET" totalsRowDxfId="48" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{60216B5C-783A-4916-AACF-4280FF3BECAD}" name="Min temp" totalsRowDxfId="53" totalsRowCellStyle="Content bold">
+    <tableColumn id="7" xr3:uid="{60216B5C-783A-4916-AACF-4280FF3BECAD}" name="Min temp" totalsRowDxfId="47" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{1FE05885-DAC3-47B8-BEB3-6920E3033122}" name="Max temp" totalsRowDxfId="52" totalsRowCellStyle="Content bold">
+    <tableColumn id="8" xr3:uid="{1FE05885-DAC3-47B8-BEB3-6920E3033122}" name="Max temp" totalsRowDxfId="46" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{2B644226-778B-401E-99C4-CEB1DE3EDAE1}" name="Min rainfall" totalsRowDxfId="51" totalsRowCellStyle="Content bold">
+    <tableColumn id="9" xr3:uid="{2B644226-778B-401E-99C4-CEB1DE3EDAE1}" name="Min rainfall" totalsRowDxfId="45" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{B73B8CF5-08DF-4843-B82E-B9FB1813470C}" name="Max rainfall" totalsRowDxfId="50" totalsRowCellStyle="Content bold">
+    <tableColumn id="10" xr3:uid="{B73B8CF5-08DF-4843-B82E-B9FB1813470C}" name="Max rainfall" totalsRowDxfId="44" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{2516891E-4C4A-426D-8B84-5149409BFCBC}" name="Min frost days" totalsRowDxfId="49" totalsRowCellStyle="Content bold">
+    <tableColumn id="11" xr3:uid="{2516891E-4C4A-426D-8B84-5149409BFCBC}" name="Min frost days" totalsRowDxfId="43" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{189C1E5A-6304-4676-A9EB-8B293F4544B2}" name="Max frost days" totalsRowDxfId="48" totalsRowCellStyle="Content bold">
+    <tableColumn id="15" xr3:uid="{189C1E5A-6304-4676-A9EB-8B293F4544B2}" name="Max frost days" totalsRowDxfId="42" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{14B9E9DB-0BCC-48C2-8CCA-57C75DB45D61}" name="Min elevation" totalsRowDxfId="47" totalsRowCellStyle="Content bold">
+    <tableColumn id="12" xr3:uid="{14B9E9DB-0BCC-48C2-8CCA-57C75DB45D61}" name="Min elevation" totalsRowDxfId="41" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{67D82299-FF27-4038-A32D-781A02A531ED}" name="Max elevation" totalsRowDxfId="46" totalsRowCellStyle="Content bold">
+    <tableColumn id="16" xr3:uid="{67D82299-FF27-4038-A32D-781A02A531ED}" name="Max elevation" totalsRowDxfId="40" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{FB2C0315-064C-437A-86D7-3E8FA9F4822B}" name="Min MAP:PET" totalsRowDxfId="45" totalsRowCellStyle="Content bold">
+    <tableColumn id="13" xr3:uid="{FB2C0315-064C-437A-86D7-3E8FA9F4822B}" name="Min MAP:PET" totalsRowDxfId="39" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{378C37E5-D887-4B5C-9001-232EF0A792B4}" name="Max MAP:PET" totalsRowDxfId="44" totalsRowCellStyle="Content bold">
+    <tableColumn id="17" xr3:uid="{378C37E5-D887-4B5C-9001-232EF0A792B4}" name="Max MAP:PET" totalsRowDxfId="38" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5761,7 +5761,7 @@
     <tableColumn id="1" xr3:uid="{44AAB7B6-31A0-4522-84AE-3428F2D4D02F}" name="Climate zone" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{8619F0C7-D005-4F89-B453-E75937AA076E}" name="Wet or Dry Zone" totalsRowDxfId="43" totalsRowCellStyle="Content bold">
+    <tableColumn id="2" xr3:uid="{8619F0C7-D005-4F89-B453-E75937AA076E}" name="Wet or Dry Zone" totalsRowDxfId="37" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -6413,7 +6413,7 @@
         <v>124</v>
       </c>
       <c r="E9" s="52">
-        <f>'11.1.1-2 Wastewater CH4'!E30</f>
+        <f>VEERG_11_1_1_1__1_MethaneEmissionsFromWastewaterTreatment_Result_Method1</f>
         <v>4.7159433000000001E-2</v>
       </c>
       <c r="F9" s="52">
@@ -6445,7 +6445,7 @@
         <v>125</v>
       </c>
       <c r="E10" s="75">
-        <f>'11.1.3-4 Wastewater N2O'!E17</f>
+        <f>VEERG_11_1_3_1__1_NitrousOxideEmissionsFromFlaredBiogas_Result_Method1</f>
         <v>4.26764E-7</v>
       </c>
       <c r="F10" s="75">
@@ -8068,7 +8068,7 @@
         <v>Input</v>
       </c>
       <c r="J14" s="48">
-        <f>'Input - Wastewater'!F8</f>
+        <f>X_Cell_Wastewater_QuantityInM3</f>
         <v>1000</v>
       </c>
     </row>
@@ -8092,7 +8092,7 @@
         <v>Input</v>
       </c>
       <c r="J15" s="48">
-        <f>'Input - Wastewater'!F14</f>
+        <f>X_Cell_Wastewater_InletCOD</f>
         <v>0.9</v>
       </c>
     </row>
@@ -8116,7 +8116,7 @@
         <v>Input</v>
       </c>
       <c r="J16" s="48">
-        <f>'Input - Wastewater'!F15</f>
+        <f>X_Cell_Wastewater_FractionCODRemovedAsSludge</f>
         <v>0.5</v>
       </c>
     </row>
@@ -8136,7 +8136,7 @@
         <v>Input</v>
       </c>
       <c r="J17" s="48">
-        <f>'Input - Wastewater'!F17</f>
+        <f>X_Cell_Wastewater_OutletCOD</f>
         <v>0.1</v>
       </c>
     </row>
@@ -8196,7 +8196,7 @@
         <v>Input</v>
       </c>
       <c r="J20" s="48">
-        <f>'Input - Wastewater'!F16</f>
+        <f>X_Cell_Wastewater_FractionCODRemovedAndTransferred</f>
         <v>0.2</v>
       </c>
     </row>
@@ -8258,7 +8258,7 @@
         <v>Input</v>
       </c>
       <c r="J23" s="48">
-        <f>'Input - Wastewater'!F24</f>
+        <f>X_Cell_Wastewater_SludgeMethaneCapturedForCombustion</f>
         <v>100</v>
       </c>
     </row>
@@ -8278,7 +8278,7 @@
         <v>Input</v>
       </c>
       <c r="J24" s="48">
-        <f>'Input - Wastewater'!F25</f>
+        <f>X_Cell_Wastewater_SludgeMethaneFlared</f>
         <v>100</v>
       </c>
     </row>
@@ -8298,7 +8298,7 @@
         <v>Input</v>
       </c>
       <c r="J25" s="48">
-        <f>'Input - Wastewater'!F26</f>
+        <f>X_Cell_Wastewater_SludgeMethaneTransferred</f>
         <v>100</v>
       </c>
     </row>
@@ -8358,7 +8358,7 @@
         <v>Input</v>
       </c>
       <c r="J28" s="48" t="str">
-        <f>'Input - Wastewater'!$F$7</f>
+        <f>X_Cell_Wastewater_TreatmentFacilityType</f>
         <v>Unmanaged aerobic treatment</v>
       </c>
     </row>
@@ -8815,7 +8815,7 @@
         <v>Input</v>
       </c>
       <c r="I13" s="48">
-        <f>'Input - Wastewater'!F25</f>
+        <f>X_Cell_Wastewater_SludgeMethaneFlared</f>
         <v>100</v>
       </c>
     </row>
@@ -13758,6 +13758,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="09eef6d6-daa8-4301-8f9f-b1ec38079286" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7291119c-fce9-4911-96ae-b800be5dccd8">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100ACB660BB23738846A00119B5826AC974" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3e3613359d4ae7f6bda6c57be713f101">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="7291119c-fce9-4911-96ae-b800be5dccd8" xmlns:ns3="09eef6d6-daa8-4301-8f9f-b1ec38079286" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="87491bfad7f11426ad96486e70428b3e" ns2:_="" ns3:_="">
     <xsd:import namespace="7291119c-fce9-4911-96ae-b800be5dccd8"/>
@@ -13952,31 +13972,30 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="09eef6d6-daa8-4301-8f9f-b1ec38079286" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7291119c-fce9-4911-96ae-b800be5dccd8">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
 <AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgAvAC8AIAAtAC0ALQAgAFcAbwByAGsAYgBvAG8AawAgAG0AbwBkAHUAbABlACAALQAtAC0AXABuAC8ALwAgAEEAIABmAGkAbABlACAAbwBmACAAbgBhAG0AZQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAG8AZgAgAHQAaABlACAAZgBvAHIAbQA6AFwAbgAvAC8AIAAgACAAIABuAGEAbQBlACAAPQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AOwBcAG4AXABuACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhACIALAAiAHQAZQB4AHQAIgA6ACIALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgBTAG8AdQByAGMAZQAgAGQAYQB0AGEAIAB0AGgAYQB0ACAAaQBzACAAYwBvAG0AbQBvAG4AIABhAGMAcgBvAHMAcwAgAGEAbABsACAAZQBuAHQAZQByAHAAcgBpAHMAZQAgAHQAeQBwAGUAcwBcAG4ARQB4AGMAZQBsACAAbQBvAGQAdQBsAGUAIABuAGEAbQBlADoAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFMAbwB1AHIAYwBlADoAIABOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQBcAG4ATgBJAFIAXwAyADAAMgAzAF8AVgBvAGwAMQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXABuAHAAIAA9ACAAZABlAG4AcwBpAHQAeQAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAIAAoADAALgA2ADcAOAA0ACAAawBnAC8AbQAzACkAXABuAFQAYQBrAGUAbgAgAGYAcgBvAG0AIAB0AGgAZQAgAE4AYQB0AGkAbwBuAGEAbAAgAEcAcgBlAGUAbgBoAG8AdQBzAGUAIABhAG4AZAAgAEUAbgBlAHIAZwB5ACAAUgBlAHAAbwByAHQAaQBuAGcAIABcAG4AKABNAGUAYQBzAHUAcgBlAG0AZQBuAHQAKQAgAEQAZQB0AGUAcgBtAGkAbgBhAHQAaQBvAG4AIAAyADAAMAA4AFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHAAIAA9ACAAZABlAG4AcwBpAHQAeQAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcALwBtADMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgADIAMAAyADMAIABWAG8AbAB1AG0AZQAgADEAOgAgAEUAcQB1AGEAdABpAG8AbgBzACAAMwAuAEIALgAxAGEAXwAyACwAIAAzAC4AQgAuADEAYwBfADIALAAgADMALgBCAC4AMwBfADEALAAgADMALgBCAC4ANABnAF8AMgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAMAAuADYANwA4ADQAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAFwAbgBDAGcAIAA9ACAANAA0AC8AMgA4ACAAZgBhAGMAdABvAHIAIAB0AG8AIABjAG8AbgB2AGUAcgB0ACAAZQBsAGUAbQBlAG4AdABhAGwAIABtAGEAcwBzACAAbwBmACAATgAyAE8AIAB0AG8AIABtAG8AbABlAGMAdQBsAGEAcgAgAG0AYQBzAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABOADIATwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBDAGcATgAyAE8AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAYQBjAHQAbwByAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgADIAMAAyADMAIABWAG8AbAB1AG0AZQAgADEAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgANAA0AC8AMgA4ACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAFwAbgBGAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABnAGEAcwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgBhAGMAdABvAHIAIAB0AG8AIABjAG8AbgB2AGUAcgB0ACAAZQBsAGUAbQBlAG4AdABhAGwAIABtAGEAcwBzACAAbwBmACAAZwBhAHMAIAB0AG8AIABtAG8AbABlAGMAdQBsAGEAcgAgAG0AYQBzAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBDAGcAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgBhAGMAdABvAHIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFgAWABYAFgAWABYAFgAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADgALAAgADQALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAYQBzAFwAIgAsACAAXAAiAEMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBcACIALAAgAFwAIgBDAG8AbgB2AGUAcgBzAGkAbwBuACAAZgBhAGMAdABvAHIAIAAxAFwAIgAsACAAXAAiAEMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgADIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyAFwAIgAsACAAXAAiADQANAAvADEAMgBcACIALAAgADQANAAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMASAA0AFwAIgAsACAAXAAiADEANgAvADEAMgBcACIALAAgADEANgAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AMgBPAFwAIgAsACAAXAAiADQANAAvADIAOABcACIALAAgADQANAAsACAAMgA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB4AFwAIgAsACAAXAAiADQANgAvADEANABcACIALAAgADQANgAsACAAMQA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwBcACIALAAgAFwAIgAyADgALwAxADIAXAAiACwAIAAyADgALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAE8AMgAgAEwAaQBtAGUAXAAiACwAIABcACIANAA0AC8AMQAyAFwAIgAsACAANAA0ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBNAFYATwBDAFwAIgAsACAAXAAiADEANAAvADEAMgBcACIALAAgADEANAAsACAAMQAyAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABOADIATwBcAG4ARwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAGcAcgBlAGUAbgBoAG8AdQBzAGUAIABnAGEAcwBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABnAHIAZQBlAG4AaABvAHUAcwBlACAAZwBhAHMAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARwBXAFAATgAyAE8AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgBhAGMAdABvAHIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFgAWABYAFgAWABYAFgAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADgALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAYQBzAFwAIgAsACAAXAAiAEMATwAyAC0AZQAgAGYAYQBjAHQAbwByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAE8AMgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBIADQAXAAiACwAIAAyADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgAyAE8AXAAiACwAIAAyADYANQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAEYANABcACIALAAgADYANgAzADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwAyAEYANgBcACIALAAgADEAMgAyADAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAEYANgBcACIALAAgADIAMgA4ADAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAEYAMwBcACIALAAgADEANwAyADAAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAcwB0AGEAdABlAHMAIABhAG4AZAAgAHQAZQByAHIAaQB0AG8AcgBpAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA5ACwAIAAzACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHQAYQB0AGUALwBUAGUAcgByAGkAdABvAHIAeQBcACIALAAgAFwAIgBDAG8AbQBtAG8AbgAgAE4AYQBtAGUAXAAiACwAIABcACIAQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AZQB3ACAAUwBvAHUAdABoACAAVwBhAGwAZQBzAFwAIgAsACAAXAAiAE4AZQB3ACAAUwBvAHUAdABoACAAVwBhAGwAZQBzAFwAIgAsACAAXAAiAE4AUwBXAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAQwBhAHAAaQB0AGEAbAAgAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAEEAQwBUAFwAIgAsACAAXAAiAEEAQwBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAGkAYwB0AG8AcgBpAGEAXAAiACwAIABcACIAVgBpAGMAdABvAHIAaQBhAFwAIgAsACAAXAAiAFYASQBDAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBRAHUAZQBlAG4AcwBsAGEAbgBkAFwAIgAsACAAXAAiAFEAdQBlAGUAbgBzAGwAYQBuAGQAXAAiACwAIABcACIAUQBMAEQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAbwB1AHQAaAAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFMAbwB1AHQAaAAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFMAQQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQBcACIALAAgAFwAIgBXAEEAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAYQBzAG0AYQBuAGkAYQBcACIALAAgAFwAIgBUAGEAcwBtAGEAbgBpAGEAXAAiACwAIABcACIAVABBAFMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwByAHQAaABlAHIAbgAgAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAE4AbwByAHQAaABlAHIAbgAgAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAE4AVABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQBCAFMAIABTAHQAYQB0AGkAcwB0AGMAYQBsACAAQQByAGUAYQBzACAATABlAHYAZQBsACAANAAgAC0AIABXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAEIAdQByAGUAYQB1ACAAbwBmACAAUwB0AGEAdABpAHMAdABpAGMAcwAgACgAQQBCAFMAKQAgAC0AIABTAHQAYQB0AGkAcwB0AGkAYwBhAGwAIABBAHIAZQBhAHMAIABMAGUAdgBlAGwAIAAyACAALQAgADIAMAAyADEAIAAtACAAUwBoAGEAcABlAGYAaQBsAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADEALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAQQAgADQAIABOAGEAbQBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBCAHUAbgBiAHUAcgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAGEAbgBkAHUAcgBhAGgAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABJAG4AbgBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABOAG8AcgB0AGgAIABFAGEAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAATgBvAHIAdABoACAAVwBlAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAFMAbwB1AHQAaAAgAEUAYQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABTAG8AdQB0AGgAIABXAGUAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAAVwBoAGUAYQB0ACAAQgBlAGwAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhACAALQAgAE8AdQB0AGIAYQBjAGsAIAAoAE4AbwByAHQAaAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAATwB1AHQAYgBhAGMAawAgACgAUwBvAHUAdABoACkAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAdwBlAHQAIABhAG4AZAAgAGQAcgB5ACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAyADoAIABUAHIAYQBuAHMAbABhAHQAaQBuAGcAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBzACAAdABvACAAdwBlAHQAIABhAG4AZAAgAGQAcgB5ACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAdwBhAHIAbQAgAC8AIABjAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAvACAAZAByAHkAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAIABhAG4AZAAgAGgAaQBnAGgAIAB0AGUAbQBwACAAYwBsAGEAcwBzAGUAcwAgAHQAbwAgAGEAYwBjAG8AbQBtAG8AZABhAHQAZQAgAGMAbABpAG0AYQB0AGUAIABzAGMAZQBuAGEAcgBpAG8AcwAgAGUAeABjAGwAdQBkAGUAZAAgAGIAeQAgAFYARQBFAFIARwAgAGMAcgBpAHQAZQByAGkAYQAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAGkAeABlAGQAIAB0AHkAcABvACAALQAgAEMAaABhAG4AZwBlAGQAIABcAHUAMAAwADIANwBGAHIAeQBcAHUAMAAwADIANwAgAHQAbwAgAFwAdQAwADAAMgA3AEQAcgB5AFwAdQAwADAAMgA3AC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADUALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAFcAZQB0ACAAbwByACAARAByAHkAIABaAG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABtAG8AbgB0AGEAbgBlAFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAHcAZQB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABkAHIAeQBcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdABcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAtACAAaABpAGcAaAAgAHQAZQBtAHAAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAaABpAGcAaAAgAHQAZQBtAHAAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA1ACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAB3AGEAcgBtACAALwAgAGMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC8AIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdAAgAGEAbgBkACAAaABpAGcAaAAgAHQAZQBtAHAAIABjAGwAYQBzAHMAZQBzACAAdABvACAAYQBjAGMAbwBtAG0AbwBkAGEAdABlACAAYwBsAGkAbQBhAHQAZQAgAHMAYwBlAG4AYQByAGkAbwBzACAAZQB4AGMAbAB1AGQAZQBkACAAYgB5ACAAVgBFAEUAUgBHACAAYwByAGkAdABlAHIAaQBhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAaQB4AGUAZAAgAHQAeQBwAG8AIABpAG4AIABNAEEAVAAgAHYAYQBsAHUAZQAgAGYAbwByACAAdwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAYwBoAGEAbgBnAGUAZAAgADEAMAAgAHQAbwAgADEAMQAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIABtAGkAbgAgAGEAbgBkACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAZgBvAHIAIABNAEEAVAAsACAATQBBAFAALAAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAIABwAGUAcgAgAHkAZQBhAHIALAAgAGUAbABlAHYAYQB0AGkAbwBuACwAIABNAEEAUAA6AFAARQBUACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlAHMAIABmAHIAbwBtACAAcgBlAGEAbAAgAGMAbABpAG0AYQB0AGUAIABkAGEAdABhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAQQBGACAAYQBjAGMAZQBwAHQAcwAgAHIAYQBpAG4AZgBhAGwAbAAgAGEAcwAgAGEAIABwAHIAbwB4AHkAIABmAG8AcgAgAHAAcgBlAGMAaQBwAGkAdABhAHQAaQBvAG4ALgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOQAsACAAMQA2ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAGwAaQBtAGEAdABlACAAWgBvAG4AZQBcACIALAAgAFwAIgBNAEEAVABcACIALAAgAFwAIgBNAEEAUABcACIALAAgAFwAIgBGAHIAbwBzAHQAIABkAGEAeQBzACAAcABlAHIAIAB5AGUAYQByAFwAIgAsACAAXAAiAEUAbABlAHYAYQB0AGkAbwBuAFwAIgAsACAAXAAiAE0AQQBQADoAUABFAFQAXAAiACwAIABcACIATQBpAG4AIAB0AGUAbQBwAFwAIgAsACAAXAAiAE0AYQB4ACAAdABlAG0AcABcACIALAAgAFwAIgBNAGkAbgAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBNAGEAeAAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBNAGkAbgAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAXAAiACwAIABcACIATQBhAHgAIABmAHIAbwBzAHQAIABkAGEAeQBzAFwAIgAsACAAXAAiAE0AaQBuACAAZQBsAGUAdgBhAHQAaQBvAG4AXAAiACwAIABcACIATQBhAHgAIABlAGwAZQB2AGEAdABpAG8AbgBcACIALAAgAFwAIgBNAGkAbgAgAE0AQQBQADoAUABFAFQAXAAiACwAIABcACIATQBpAG4AIABNAEEAUAA6AFAARQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABtAG8AbgB0AGEAbgBlAFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQA4ACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAwADAAIABtAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAMQA4AC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAANwAsACAAMQAwADAAMAAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAHcAZQB0AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQA4ACAAQwBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADIAMAAwADAAIABtAG0AXAAiACwAIABcACIAZCIgADcAXAAiACwAIABcACIAZCIgADEAMAAwADAAIABtAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAMQA4AC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAyADAAMAAwAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQAuADkAOQA5ACwAIAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAOAAgAEMAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADAAMAAwACAAbQBtACAALQAgAGQiIAAyADAAMAAwACAAbQBtAFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgADEAOAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAAMQAwADAAMAAuADAAMAAxACwAIAAyADAAMAAwACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQAuADkAOQA5ACwAIAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAGQAcgB5AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQA4ACAAQwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAwADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAXAAiACwAIAAxADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgADEALgAwADAAMQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAGQiIAAxAFwAIgAsACAAMQAwAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAgAC0AOQA5ADkAOQA5ADkALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMAAgAEMAIAAtACAAZCIgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxAFwAIgAsACAALQA5ADkAOQA5ADkAOQAsACAAMQAwACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAxAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMAAgAEMAIAAtACAAZCIgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAZCIgADEAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAMQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBBAHAAcABlAG4AZABpAGMAZQBzAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdABlADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AQQBUACAAPQAgAG0AZQBhAG4AIABhAG4AbgB1AGEAbAAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBBAFAAIAA9ACAAbQBlAGEAbgAgAGEAbgBuAHUAYQBsACAAcAByAGUAYwBpAHAAaQB0AGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABFAFQAIAA9ACAAcABvAHQAZQBuAHQAaQBhAGwAIABlAHYAYQBwAG8AdAByAGEAbgBzAHAAaQByAGEAdABpAG8AbgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABBAGQAZABlAGQAIABlAHgAdAByAGEAIABNAEEAVAAgAG0AaQBuACAAYQBuAGQAIABNAEEAVAAgAG0AYQB4ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGMAYQBsAGMAdQBsAGEAdABlACAAegBvAG4AZQAgAGYAcgBvAG0AIAByAGUAYQBsACAAdABlAG0AcABlAHIAYQB0AHUAcgBlACAAZABhAHQAYQAuAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANAAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AHUAcgBlACAAWgBvAG4AZQBcACIALAAgAFwAIgBNAGUAZABpAGEAbgAgAEEAbgBuAHUAYQBsACAAVABlAG0AcABlAHIAYQB0AHUAcgBlACAAKABNAEEAVAApAFwAIgAsACAAXAAiAE0AaQBuACAATQBBAFQAXAAiACwAIABcACIATQBhAHgAIABNAEEAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgAFwAIgBlIiAAMgA2ACAAQwBcACIALAAgADIANgAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIABcACIAMQA1ACAALQAgADIANQAgAEMAXAAiACwAIAAxADUALAAgADIANQAuADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIABcACIAZCIgADEANAAgAEMAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADQALgA5ADkAOQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAAQQBkAGQAZQBkACAAZQB4AHQAcgBhACAAUgBhAGkAbgBmAGEAbABsACAAbQBpAG4AIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAG0AYQB4ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGMAYQBsAGMAdQBsAGEAdABlACAAegBvAG4AZQAgAGYAcgBvAG0AIAByAGUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAZABhAHQAYQAuAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBhAGkAbgBmAGEAbABsACAAWgBvAG4AZQBcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABtAGkAbgBcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABtAGEAeABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbAAgAFwAdQAwADAAMwBlACAANgAwADAAbQBtAFwAIgAsACAANgAwADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATABvAHcAIAByAGEAaQBuAGYAYQBsAGwAXAAiACwAIABcACIAQQBuAG4AdQBhAGwAIAByAGEAaQBuAGYAYQBsAGwAIABkIiAANgAwADAAbQBtAFwAIgAsACAALQA5ADkAOQA5ADkAOQAsACAANgAwADAAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABaAG8AbgBlAFwAIgAsACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAGMAcgBpAHQAZQByAGkAYQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATABlAGEAYwBoAGkAbgBnACAAbwBjAGMAdQByAHMAXAAiACwAIABcACIAowMoADXYX9w12E7cNdhW3DXYW9wpAFwAdQAwADAAMwBlAKMDKAA12DjcNdhH3DAAKQArADXYYNw12FzcNdhW3DXYWdwgADXYZNw12E7cNdhh3DXYUtw12F/cIAAOITXYXNw12FncNdhR3DXYVtw12FvcNdhU3CAANdhQ3DXYTtw12F3cNdhO3DXYUNw12FbcNdhh3DXYZtxcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATABlAGEAYwBoAGkAbgBnACAAZABvAGUAcwAgAG4AbwB0ACAAbwBjAGMAdQByAFwAIgAsACAAXAAiAKMDKAA12F/cNdhO3DXYVtw12FvcKQBkIqMDKAA12DjcNdhH3DAAKQArADXYYNw12FzcNdhW3DXYWdwgADXYZNw12E7cNdhh3DXYUtw12F/cIAAOITXYXNw12FncNdhR3DXYVtw12FvcNdhU3CAANdhQ3DXYTtw12F3cNdhO3DXYUNw12FbcNdhh3DXYZtxcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXABuADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAbgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAEQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcwAgAGkAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAXAAiACwAXAAiAEYAcgBhAGMAVwBFAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFkAZQBzACAALQAgAGkAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwAgAC0AIABuAG8AdAAgAGkAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAXAAiACwAIAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoACgAXAAiAFwAIgApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAGQAYQB0AGEAIABzAGMAbwByAGUAcwAgAGYAbwByACAAcwBjAG8AcABlACAAMwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABYAFgAWABYAFgAWABYAFgAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABhAHQAYQAgAHMAbwB1AHIAYwBlAFwAIgAsACAAXAAiAEQAYQB0AGEAIABzAGMAbwByAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAbgB0AGUAcgBuAGEAdABpAG8AbgBhAGwAIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAcwBjAG8AcABlACAAMwAgAGQAYQB0AGEAYgBhAHMAZQBcACIALAAgADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB0AGEAdABlACAAbwByACAAcgBlAGcAaQBvAG4AYQBsACAAcwBjAG8AcABlACAAMwAgAGQAYQB0AGEAYgBhAHMAZQBcACIALAAgADMAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBtAGkAcwBzAGkAbwBuAHMAIABpAG4AdABlAG4AcwBpAHQAeQAgAGMAYQBsAGMAdQBsAGEAdABlAGQAIABmAHIAbwBtACAAYQBwAHAAcgBvAHYAZQBkACAAbQBlAHQAaABvAGQAXAAiACwAIAA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAZQByAGkAZgBpAGUAZAAgAGMAcgBlAGQAZQBuAHQAaQBhAGwAIABtAGEAdABjAGgAaQBuAGcAIABJAFMATwAxADQAMAA2ADcAXAAiACwAIAA1AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXABuADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAbgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgARABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAVgBvAGwAdQBtAGUAIAAxADoAIABMAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmACAAKAAzAC4ARAAuAGIALgAyACkAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAcgBhAGMATABFAEEAQwBIAFwAIgAsADAALgAyADQAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoACgAXAAiAFwAIgApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABuAGkAdAByAG8AZwBlAG4AIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABuAGkAdAByAG8AZwBlAG4AIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABrAGcAIABOADIATwAtAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgAFYAbwBsAHUAbQBlACAAMQA6ACAARQBxAHUAYQB0AGkAbwBuACAAMwAuAEQALgBCAF8AMQAwAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARgBsAGUAYQBjAGgAXAAiACwAMAAuADAAMQAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoACgAXAAiAFwAIgApACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXABuAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADEAXABuAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAZgBvAHIAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AIAAoAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AKQAgACgARQBGAE4AMgBPACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAGYAbwByACAAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAGsAZwAgAE4AMgBPAC0ATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADIALgAyAC4AMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQA1ACwAIAA1ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABqAFwAIgAsAFwAIgBFAEYATgAyAE8AXAAiACwAIABcACIAUAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAbwBuAGwAeQBcACIALAAgAFwAIgBJAHIAcgBpAGcAYQB0AGkAbwBuACAAbQBlAHQAaABvAGQAXAAiACwAIABcACIAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsADAALgAwADAANQA5ACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwAFwAIgAsADAALgAwADAANwAsACAAXAAiAEMAcgBvAHAAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsADAALgAwADAAMQA4ACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEwAbwB3ACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQBcACIALAAwAC4AMAAwADEAOAAsACAAXAAiAFAAYQBzAHQAdQByAGUAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcAAgACgAbABvAHcAIAByAGEAaQBuAGYAYQBsAGwAKQBcACIALAAwAC4AMAAwADIAOQAsACAAXAAiAEMAcgBvAHAAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAGMAcgBvAHAAIAAoAGgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAKQBcACIALAAwAC4AMAAwADgALAAgAFwAIgBDAHIAbwBwAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIASABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB1AGcAYQByAFwAIgAsADAALgAwADEAOQA5ACwAIABcACIAUwB1AGcAYQByAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AdAB0AG8AbgBcACIALAAwAC4AMAAwADUAMwAsACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAG8AcgB0AGkAYwB1AGwAdAB1AHIAYQBsACAAYwByAG8AcABzAFwAIgAsADAALgAwADAANgA0ACwAIABcACIASABvAHIAdABpAGMAdQBsAHQAdQByAGEAbAAgAGMAcgBvAHAAcwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBpAGMAZQAgACgAYwBvAG4AdABpAG4AdQBvAHUAcwAgAGYAbABvAG8AZABpAG4AZwApAFwAIgAsADAALgAwADAAMwAsACAAXAAiAFIAaQBjAGUAXAAiACwAIABcACIAQwBvAG4AdABpAG4AdQBvAHUAcwAgAGYAbABvAG8AZABpAG4AZwBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBpAGMAZQAgACgAcwBpAG4AZwBsAGUAIABhAG4AZAAgAG0AdQBsAHQAaQBwAGwAZQAgAGQAcgBhAGkAbgBhAGcAZQAsACAAbwByACAAYQBsAHQAZQByAG4AYQB0AGUAIAB3AGUAdAB0AGkAbgBnACAAYQBuAGQAIABkAHIAeQBpAG4AZwApAFwAIgAsADAALgAwADAANQAsACAAXAAiAFIAaQBjAGUAXAAiACwAIABcACIAUwBpAG4AZwBsAGUAIABhAG4AZAAgAG0AdQBsAHQAaQBwAGwAZQAgAGQAcgBhAGkAbgBhAGcAZQAsACAAbwByACAAYQBsAHQAZQByAG4AYQB0AGUAIAB3AGUAdAB0AGkAbgBnACAAYQBuAGQAIABkAHIAeQBpAG4AZwBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBxAHUAYQBjAHUAbAB0AHUAcgBlAFwAIgAsADAALgAwADAAMgA2ACwAIABcACIAQQBxAHUAYQBjAHUAbAB0AHUAcgBlAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAG8AcgBlAHMAdAByAHkAXAAiACwAMAAuADAAMAAxADgALAAgAFwAIgBGAG8AcgBlAHMAdAByAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA1ACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGUAbQBvAHYAZQBkACAAZAB1AHAAbABpAGMAYQB0AGUAIABcAHUAMAAwADIANwBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAB1ADAAMAAyADcAIAByAG8AdwAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGUAbQBvAHYAZQBkACAAYQBzAHQAZQByAGkAcwBrAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAFwAdQAwADAAMgA3AHAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAG8AbgBsAHkAXAB1ADAAMAAyADcALAAgAFwAdQAwADAAMgA3AHIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAXAB1ADAAMAAyADcAIABhAG4AZAAgAFwAdQAwADAAMgA3AGkAcgByAGkAZwBhAHQAaQBvAG4AIABtAGUAdABoAG8AZABcAHUAMAAwADIANwAgAGMAbwBsAHUAbQBuAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAdQBwAGwAaQBjAGEAdABlAGQAIABcAHUAMAAwADIANwBuAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQBcAHUAMAAwADIANwAgAHIAbwB3ACAAdwBpAHQAaAAgAHMAYQBtAGUAIABFAEYAIABmAG8AcgAgAGwAbwB3ACAAYQBuAGQAIABoAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAFwAbgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABDAGgAYQBwAHQAZQByACAAMQAsACAAcwBlAGMAdABpAG8AbgAgADEALgA4AC4AMgAgAEwAZQBhAGMAaABpAG4AZwAsACAAYwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBzAFwAbgBJAFAAQwBDADoAIABOADIATwAgAEUATQBJAFMAUwBJAE8ATgBTACAARgBSAE8ATQAgAE0AQQBOAEEARwBFAEQAIABTAE8ASQBMAFMALAAgAEEATgBEACAAQwBPADIAIABFAE0ASQBTAFMASQBPAE4AUwAgAEYAUgBPAE0AIABMAEkATQBFACAAQQBOAEQAIABVAFIARQBBACAAQQBQAFAATABJAEMAQQBUAEkATwBOAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwBXAEUAVAAgAGYAbwByACAAaQByAHIAaQBnAGEAdABpAG8AbgAgAHQAeQBwAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAEMAaABhAHAAdABlAHIAIAAxACwAIABzAGUAYwB0AGkAbwBuACAAMQAuADgALgAyACAATABlAGEAYwBoAGkAbgBnACwAIABjAGwAaQBtAGEAdABlACAAYQBuAGQAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBJAFAAQwBDACAAMgAwADEAOQAgAFIAZQBmAGkAbgBlAG0AZQBuAHQAIABWAG8AbAB1AG0AZQAgADQAOgAgAEMAaABhAHAAdABlAHIAIAAxADEAOgAgAE4AMgBPACAARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAATQBhAG4AYQBnAGUAZAAgAFMAbwBpAGwAcwAsACAAYQBuAGQAIABDAE8AMgAgAEUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAEwAaQBtAGUAIABhAG4AZAAgAFUAcgBlAGEAIABBAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGkAbwBuACAAdAB5AHAAZQAgAGkAcgBcACIALABcACIARgByAGEAYwBXAEUAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAByAGkAcAAgAGkAcgByAGkAZwBhAHQAaQBvAG4AXAAiACwAIAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAcAByAGkAbgBrAGwAZQByACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB1AHIAZgBhAGMAZQAgAGkAcgByAGkAZwBhAHQAaQBvAG4AXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AdABoAGUAcgAgAGkAcgByAGkAZwBhAHQAaQBvAG4AXAAiACwAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAARgBSAE8ATQAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAAVABhAGIAbABlACAAYwByAGUAYQB0AGUAZAAgAGIAYQBzAGUAZAAgAG8AbgAgAFYARQBFAFIARwAgAHQAZQB4AHQAIABcAHUAMAAwADIANwBBAHIAZQBhAHMAIABhAHIAZQAgAHMAdQBiAGoAZQBjAHQAIAB0AG8AIABsAGUAYQBjAGgAaQBuAGcAIAAoAGkALgBlAC4ALAAgAGkAbgAgAHQAaABlACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQApACAAdwBoAGUAbgAuAC4ALgAgAHQAaABlACAAbABhAG4AZAAgAGkAcwAgAGkAcgByAGkAZwBhAHQAZQBkACAAKABlAHgAYwBlAHAAdAAgAGQAcgBpAHAAIABpAHIAcgBpAGcAYQB0AGkAbwBuACkALgBcAHUAMAAwADIANwBcACIAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAFwAbgBUAGEAYgBsAGUAIABBAC4AMgAuADIALgAyADoAIABFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAdQByAGkAbgBlACAAYQBuAGQAIABkAHUAbgBnACAAZABlAHAAbwBzAGkAdABlAGQAIABvAG4AIABwAGEAcwB0AHUAcgBlACwAIAByAGEAbgBnAGUAIABvAHIAIABwAGEAZABkAG8AYwBrACAAKABrAGcAIABOADIATwAtAE4ALwBrAGcAIABOACkAIAAoAEUARgBQAFIAUAApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAdQByAGkAbgBlACAAYQBuAGQAIABkAHUAbgBnACAAZABlAHAAbwBzAGkAdABlAGQAIABvAG4AIABwAGEAcwB0AHUAcgBlACwAIAByAGEAbgBnAGUAIABvAHIAIABwAGEAZABkAG8AYwBrAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AMgBPACAALQAgAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADIALgAyAC4AMgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAEUARgBQAFIAUABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAAyAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABDAGgAYQBuAGcAZQBkACAAXAB1ADAAMAAyADcARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBzAFwAdQAwADAAMgA3ACAAdABvACAAcwBpAG4AZwB1AGwAYQByACAAXAB1ADAAMAAyADcARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcAHUAMAAwADIANwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAG8AbgB0AGgAcwAgAHQAbwAgAFMAZQBhAHMAbwBuAHMAIABNAGEAcABwAGkAbgBnAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBvAG4AdABoAFwAIgAsACAAXAAiAFMAZQBhAHMAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAGEAbgB1AGEAcgB5AFwAIgAsACAAXAAiAFMAdQBtAG0AZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAGUAYgByAHUAYQByAHkAXAAiACwAIABcACIAUwB1AG0AbQBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQByAGMAaABcACIALAAgAFwAIgBBAHUAdAB1AG0AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBwAHIAaQBsAFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAGEAeQBcACIALAAgAFwAIgBBAHUAdAB1AG0AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASgB1AG4AZQBcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASgB1AGwAeQBcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQB1AGcAdQBzAHQAXAAiACwAIABcACIAVwBpAG4AdABlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAZQBwAHQAZQBtAGIAZQByAFwAIgAsACAAXAAiAFMAcAByAGkAbgBnAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBPAGMAdABvAGIAZQByAFwAIgAsACAAXAAiAFMAcAByAGkAbgBnAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdgBlAG0AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAZQBjAGUAbQBiAGUAcgBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBhAG4AdQByAGUAIABNAGEAbgBhAGcAZQBtAGUAbgB0ACAAEyAgAE0AZQB0AGgAYQBuAGUAIABjAG8AbgB2AGUAcgBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABwAGUAcgAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAIAAoAGYAcgBhAGMAdABpAG8AbgApACAAKABNAEMARgBpAG0AKQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAxAC4AOAAuADEAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIAMgAsACAAMQA2ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAE0AQQBUACAAKAC6AEMAKQBcACIALAAgAFwAIgBVAG4AYwBvAHYAZQByAGUAZAAgAGEAbgBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuAFwAIgAsACAAXAAiAEMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBcACIALAAgAFwAIgBMAGkAcQB1AGkAZAAgAFMAbAB1AHIAcgB5ACAAKAB3AGkAdABoAG8AdQB0ACAAbgBhAHQAdQByAGEAbAAgAGMAcgB1AHMAdAApAFwAIgAsACAAXAAiAEQAYQBpAGwAeQAgAHMAcAByAGUAYQBkACAAKABiACkAXAAiACwAIABcACIAQwBvAG0AcABvAHMAdABpAG4AZwAgACgAcABhAHMAcwBpAHYAZQAgAHcAaQBuAGQAcgBvAHcAKQBcACIALAAgAFwAIgBTAG8AbABpAGQAIABTAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAFAAaQB0ACAAUwB0AG8AcgBhAGcAZQAgAFwAdQAwADAAMwBjADEAIABtAG8AbgB0AGgAXAAiACwAIABcACIARABlAGUAcAAgAEwAaQB0AHQAZQByAFwAIgAsACAAXAAiAFAAbwB1AGwAdAByAHkAIABNAGEAbgB1AHIAZQAgACgAdwBpAHQAaAAvAHcAaQB0AGgAbwB1AHQAIABsAGkAdAB0AGUAcgApAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAcAByAG8AYwBlAHMAcwBpAG4AZwAgAGkAbgB0AG8AIABwAGUAbABsAGUAdABpAHoAZQBkACAAZgBlAHIAdABpAGwAaQBzAGUAcgBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgAgAHQAbwAgAHMAbwBpAGwAXAAiACwAIABcACIAUABhAHMAdAB1AHIAZQAsACAAUgBhAG4AZwBlACAAYQBuAGQAIABQAGEAZABkAG8AYwBrACAAKABjACkAKABkACkAXAAiACwAIABcACIATQBBAFQAIAByAGEAdwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgAFwAIgBkIjEAMABcACIALAAgADAALgA2ADYALAAgADAALgAxACwAIAAwAC4AMQAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIAAxADEALAAgADAALgA2ADgALAAgADAALgAxACwAIAAwAC4AMQAxACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgADEAMgAsACAAMAAuADcALAAgADAALgAxACwAIAAwAC4AMQAzACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgADEAMwAsACAAMAAuADcAMQAsACAAMAAuADEALAAgADAALgAxADQALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQA0ACwAIAAwAC4ANwAzACwAIAAwAC4AMQAsACAAMAAuADEANQAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA1ACwAIAAwAC4ANwA0ACwAIAAwAC4AMQAsACAAMAAuADEANwAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEANQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEANgAsACAAMAAuADcANQAsACAAMAAuADEALAAgADAALgAxADgALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADcALAAgADAALgA3ADYALAAgADAALgAxACwAIAAwAC4AMgAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEANwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEAOAAsACAAMAAuADcANwAsACAAMAAuADEALAAgADAALgAyADIALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADkALAAgADAALgA3ADcALAAgADAALgAxACwAIAAwAC4AMgA0ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgAwACwAIAAwAC4ANwA4ACwAIAAwAC4AMQAsACAAMAAuADIANgAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIAMQAsACAAMAAuADcAOAAsACAAMAAuADEALAAgADAALgAyADkALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADIALAAgADAALgA3ADgALAAgADAALgAxACwAIAAwAC4AMwAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgAzACwAIAAwAC4ANwA5ACwAIAAwAC4AMQAsACAAMAAuADMANAAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIANAAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgAzADcALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADUALAAgADAALgA3ADkALAAgADAALgAxACwAIAAwAC4ANAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AXAAiACwAIAAyADYALAAgADAALgA3ADkALAAgADAALgAxACwAIAAwAC4ANAA0ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AXAAiACwAIAAyADcALAAgADAALgA4ACwAIAAwAC4AMQAsACAAMAAuADQAOAAsACAAMAAuADAAMQAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIANwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtAFwAIgAsACAAXAAiAGUiMgA4AFwAIgAsACAAMAAuADgALAAgADAALgAxACwAIAAwAC4ANQAsACAAMAAuADAAMQAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBBAG4AYQBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuAFwAIgAsACAAXAAiAEQAaQBnAGUAcwB0AGUAcgAgAC8AIABjAG8AdgBlAHIAZQBkACAAbABhAGcAbwBvAG4AcwBcACIALAAgAFwAIgBMAGkAcQB1AGkAZAAgAHMAeQBzAHQAZQBtAHMAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAXAAiACwAIABcACIAQwBvAG0AcABvAHMAdABpAG4AZwAgACgAcABhAHMAcwBpAHYAZQAgAHcAaQBuAGQAcgBvAHcAKQBcACIALAAgAFwAIgBTAG8AbABpAGQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAFAAaQB0ACAAcwB0AG8AcgBhAGcAZQBcACIALAAgAFwAIgBEAGUAZQBwACAAbABpAHQAdABlAHIAXAAiACwAIABcACIAUABvAHUAbAB0AHIAeQAgAG0AYQBuAHUAcgBlACAAdwBpAHQAaAAgAGIAZQBkAGQAaQBuAGcAXAAiACwAIABcACIAUABvAHUAbAB0AHIAeQAgAG0AYQBuAHUAcgBlACAAdwBpAHQAaABvAHUAdAAgAGIAZQBkAGQAaQBuAGcAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABwAHIAbwBjAGUAcwBzAGkAbgBnAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuAFwAIgAsACAAXAAiAFAAYQBzAHQAdQByAGUAIAByAGEAbgBnAGUAIABhAG4AZAAgAHAAYQBkAGQAbwBjAGsAXAAiACwAIABcACIATQBBAFQAIAByAGEAdwBcACIAIABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAOgAgAEEAZABkAGUAZAAgAHIAbwB3ACAAbwBmACAATgBJAFIAIABNAE0AQQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgAgAEQAdQBwAGwAaQBjAGEAdABlAGQAIABcAHUAMAAwADIANwBQAG8AdQBsAHQAcgB5ACAAdwBpAHQAaAAgAGEAbgBkACAAdwBpAHQAaABvAHUAdAAgAGwAaQB0AHQAZQByAFwAdQAwADAAMgA3ACAAYwBvAGwAdQBtAG4AIAB3AGkAdABoACAAcwBlAHAAYQByAGEAdABlACAATgBJAFIAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AIABBAGQAZABlAGQAIABcAHUAMAAwADIANwBNAEEAVAAgAHIAYQB3AFwAdQAwADAAMgA3ACAAYwBvAGwAdQBtAG4AIAB0AG8AIABhAGwAbABvAHcAIABsAG8AbwBrAHUAcAAgAG8AZgAgAG4AdQBtAGIAZQByAHMALgBcACIAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAbgBkACAAYwByAG8AcAAgAHIAZQBzAGkAZAB1AGUAcwAgAHIAZQB0AHUAcgBuAGUAZAAgAHQAbwAgAHQAaABlACAAcwBvAGkAbABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBGAE4AaQAgAFwAdQAwADAAMgA2ACAARQBGAE4AMgBPAGkAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABOADIATwAgAC0AIABOACAALwAgAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADIALgAxAC4ANABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgAFwAIgBFAEYATgBpACAAXAB1ADAAMAAyADYAIABFAEYATgAyAE8AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIAAwAC4AMAAwADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAANQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIAXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBcAG4AQwBvAG4AdgBlAHIAdAAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcAG4ARQBOADIATwAgAEMATwAyAGUAXABuAHQAIABDAE8AMgBlAFwAbgBFAE4AMgBPADoAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAAoAHQAIABOADIATwApAFwAbgBHAFcAUABOADIATwA6ACAAZwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIAAoAHQAIABDAE8AMgAtAGUAIAAvACAAdAAgAE4AMgBPACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABFAF8ATgAyAE8ALAAgAEcAVwBQAF8ATgAyAE8ALABcAG4AIAAgACAAIABFAF8ATgAyAE8AIAAqACAARwBXAFAAXwBOADIATwBcAG4AIAAgACkAXABuADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAbwBuAHYAZQByAHQAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAB0AG8AIABjAGEAcgBiAG8AbgAgAGQAaQBvAHgAaQBkAGUAIABlAHEAdQBpAHYAYQBsAGUAbgB0ACAAZQBtAGkAcwBzAGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBOADIATwAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAE8AMgBlAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMATwAyAF8AZQAgAD0AIABFAF8AewBOADIATwB9ACAAXABcAHQAaQBtAGUAcwAgAEcAVwBQAF8AewBOADIATwB9AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUATgAyAE8AXAAiACwAXAAiAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAE4AMgBPACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAVwBQAE4AMgBPAFwAIgAsAFwAIgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAATgAyAE8AKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBcAG4AQwBvAG4AdgBlAHIAdAAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcAG4ARQBDAEgANAAgAEMATwAyAGUAXABuAHQAIABDAE8AMgBlAFwAbgBFAEMASAA0ADoAIABtAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAAoAHQAIABDAEgANAApAFwAbgBHAFcAUABDAEgANAA6ACAAZwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAG0AZQB0AGgAYQBuAGUAIAAoAHQAIABDAE8AMgAtAGUAIAAvACAAdAAgAEMASAA0ACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABFAF8AQwBIADQALAAgAEcAVwBQAF8AQwBIADQALABcAG4AIAAgACAAIABFAF8AQwBIADQAIAAqACAARwBXAFAAXwBDAEgANABcAG4AIAAgACkAXABuADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAbwBuAHYAZQByAHQAIABtAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAB0AG8AIABjAGEAcgBiAG8AbgAgAGQAaQBvAHgAaQBkAGUAIABlAHEAdQBpAHYAYQBsAGUAbgB0ACAAZQBtAGkAcwBzAGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBDAEgANAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAE8AMgBlAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMATwAyAF8AZQAgAD0AIABFAF8AewBDAEgANAB9ACAAXABcAHQAaQBtAGUAcwAgAEcAVwBQAF8AewBDAEgANAB9AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUAQwBIADQAXAAiACwAXAAiAE0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAEMASAA0ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAVwBQAEMASAA0AFwAIgAsAFwAIgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbQBlAHQAaABhAG4AZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAAQwBIADQAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIAVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAUgBvAHcAUwB0AGEAcgB0AE4AdQBtAGIAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwALABSAG8AdwBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAYQBuAGQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAUgBPAFcAKABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAApACAAKwAgAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkAIAAtACAAMQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABUAGEAYgBsAGUASABlAGEAZABlAHIAQwBlAGwAbAAsAFwAbgAgACAAQwBPAEwAVQBNAE4AKABUAGEAYgBsAGUASABlAGEAZABlAHIAQwBlAGwAbAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBBAHIAcgBhAHkASQBuAFQAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgAEEAcgByAGEAeQBEAGEAdABhACwAIABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQAsACAAWwBDAG8AbAB1AG0AbgBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAQQBuAGQAQQByAHIAYQB5AF0ALABcAG4AIABJAEYARQBSAFIATwBSACgAXABuACAAIAAgACAAIABJAE4ARABFAFgAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAVQBOAEkAUQBVAEUAKABBAHIAcgBhAHkARABhAHQAYQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBPAFcAKAApAC0AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAUgBvAHcAUwB0AGEAcgB0AE4AdQBtAGIAZQByACgAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwALAAgAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEMATwBMAFUATQBOACgAKQAtAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAEMAbwBsAHUAbQBuAFMAdABhAHIAdABOAHUAbQBiAGUAcgAoAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACkAIAArAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAEMAbwBsAHUAbQBuAHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBBAG4AZABBAHIAcgBhAHkAKQAsACAAMQAsACAAQwBvAGwAdQBtAG4AcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAEEAbgBkAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACAAIAAgACAAKQAsACAAXAAiAFwAIgBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFwAIgBcACIAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEkARgAoAEkAUwBOAFUATQBCAEUAUgAoAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFwAIgBcACIAKQBcAG4AIAAgACAAIAApACwAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApACwAIAAwACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBUAHcAbwBDAG8AbAB1AG0AbgBzAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlADEALAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADIALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAWwBWAGEAbAB1AGUASQBGAEYAYQBsAHMAZQBdACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoADEALAAgACgATABvAG8AawB1AHAAQQByAHIAYQB5ADEAPQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQApACoAKABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABWAGEAbAB1AGUASQBGAEYAYQBsAHMAZQApACwAIABcACIAXAAiACwAIABWAGEAbAB1AGUASQBGAEYAYQBsAHMAZQApACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBPAG4AZQBDAG8AbAB1AG0AbgBBAG4AZABIAGUAYQBkAGUAcgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACwAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMgAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADEALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFsAVgBhAGwAdQBlAEkAZgBGAGEAbABzAGUAXQAsAFwAbgAgACAAIAAgAEkARgBFAFIAUgBPAFIAKABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADEALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACkAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAFYAYQBsAHUAZQBJAGYARgBhAGwAcwBlACkALAAgAFwAIgBcACIALAAgAFYAYQBsAHUAZQBJAGYARgBhAGwAcwBlACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAcABsAGkAdABTAHQAcgBpAG4AZwBJAG4AdABvAEEAcgByAGEAeQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEMAZQBsAGwALAAgAEQAZQBsAGkAbQBpAHQAZQByACwAIABbAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAxAF0ALAAgAFsAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADIAXQAsAFwAbgAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAWABNAEwAKABcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBcAHUAMAAwADMAYwB0AFwAdQAwADAAMwBlAFwAdQAwADAAMwBjAHMAXAB1ADAAMAAzAGUAXAAiACAAXAB1ADAAMAAyADYAXABuACAAIAAgACAAIAAgACAAIABTAFUAQgBTAFQASQBUAFUAVABFACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFMAVQBCAFMAVABJAFQAVQBUAEUAKABTAFUAQgBTAFQASQBUAFUAVABFACgAQwBlAGwAbAAsAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAxACwAXAAiAFwAIgApACwAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADIALABcACIAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAARABlAGwAaQBtAGkAdABlAHIALABcACIAXAB1ADAAMAAzAGMALwBzAFwAdQAwADAAMwBlAFwAdQAwADAAMwBjAHMAXAB1ADAAMAAzAGUAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAKQAgAFwAdQAwADAAMgA2AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFwAdQAwADAAMwBjAC8AcwBcAHUAMAAwADMAZQBcAHUAMAAwADMAYwAvAHQAXAB1ADAAMAAzAGUAXAAiACwAXABuACAAIAAgACAAIAAgACAAIABcACIALwAvAHMAXAAiAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABDAGwAaQBtAGEAdABlAFoAbwBuAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABhAHYAZwBUAGUAbQBwACwAYQB2AGcAUgBhAGkAbgAsAGYAcgBvAHMAdABEAGEAeQBzACwAZQBsAGUAdgAsAG0AYQBwAF8AcABlAHQALABcAG4AIAAgACAAIABtAGkAbgBUAGUAbQBwAEEAcgByAGEAeQAsAG0AYQB4AFQAZQBtAHAAQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4AUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQAsAG0AYQB4AFIAYQBpAG4AZgBhAGwAbABBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBGAHIAbwBzAHQAQQByAHIAYQB5ACwAbQBhAHgARgByAG8AcwB0AEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAEUAbABlAHYAYQB0AGkAbwBuAEEAcgByAGEAeQAsAG0AYQB4AEUAbABlAHYAYQB0AGkAbwBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAFAARQBUAEEAcgByAGEAeQAsAG0AYQB4AFAARQBUAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAGMAbABpAG0AYQB0AGUAWgBvAG4AZQBBAHIAcgBhAHkALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAbQBhAHMAawAsAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBUAGUAbQBwAEEAcgByAGEAeQApAFwAdQAwADAAMwBjAD0AYQB2AGcAVABlAG0AcAApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AFQAZQBtAHAAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBhAHYAZwBUAGUAbQBwACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4AUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQApAFwAdQAwADAAMwBjAD0AYQB2AGcAUgBhAGkAbgApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AFIAYQBpAG4AZgBhAGwAbABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGEAdgBnAFIAYQBpAG4AKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBGAHIAbwBzAHQAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBmAHIAbwBzAHQARABhAHkAcwApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AEYAcgBvAHMAdABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGYAcgBvAHMAdABEAGEAeQBzACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4ARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBlAGwAZQB2ACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBlAGwAZQB2ACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4AUABFAFQAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBtAGEAcABfAHAAZQB0ACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgAUABFAFQAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBtAGEAcABfAHAAZQB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAFQAQQBLAEUAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAKABjAGwAaQBtAGEAdABlAFoAbwBuAGUAQQByAHIAYQB5ACwAbQBhAHMAawAsACAAXAAiAE4AbwAgAG0AYQB0AGMAaABcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAASQB0AGUAbQBGAHIAbwBtAE0AaQBuAE0AYQB4AFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABNAGkAbgBBAHIAcgBhAHkALAAgAE0AYQB4AEEAcgByAGEAeQAsACAASQB0AGUAbQBBAHIAcgBhAHkALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAbQBhAHMAawAsAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABNAGkAbgBBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAE0AYQB4AEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0ATABvAG8AawB1AHAAVgBhAGwAdQBlACkALABcAG4AIAAgACAAIAAgACAAIAAgAEYASQBMAFQARQBSACgASQB0AGUAbQBBAHIAcgBhAHkALAAgAG0AYQBzAGsALAAgAFwAIgBOAG8AIABtAGEAdABjAGgAXAAiACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBTAHUAbQBRAHUAYQBuAHQAaQB0AHkARgByAG8AbQBDAHIAaQB0AGUAcgBpAGEAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAEMAcgBpAHQAZQByAGkAYQAxACwAIABDAHIAaQB0AGUAcgBpAGEAMQBUAHkAcABlAEEAcgByAGEAeQAsACAAUQB1AGEAbgB0AGkAdAB5ACwAIABbAE0AdQBsAHQAaQBwAGwAaQBlAHIAXQAsACAAWwBDAHIAaQB0AGUAcgBpAGEAMgBdACwAWwBDAHIAaQB0AGUAcgBpAGEAMgBBAHIAcgBhAHkAXQAsAFwAbgAgACAATABFAFQAKABcAG4AIAAgACAAIABtAHUAbAB0AGkAcABsAGkAZQByACwAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAE0AdQBsAHQAaQBwAGwAaQBlAHIAKQAsADEALABNAHUAbAB0AGkAcABsAGkAZQByACkALABcAG4AIAAgACAAIABxAHUAYQBuAHQAaQB0AHkALAAgAFEAdQBhAG4AdABpAHQAeQAqAE0AdQBsAHQAaQBwAGwAaQBlAHIALABcAG4AIAAgACAAIABjAHIAaQB0AGUAcgBpAGEAMQAsAC0ALQAoAEMAcgBpAHQAZQByAGkAYQAxAFQAeQBwAGUAQQByAHIAYQB5AD0AQwByAGkAdABlAHIAaQBhADEAKQAsAFwAbgAgACAAIAAgAGMAcgBpAHQAZQByAGkAYQAyACwASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABDAHIAaQB0AGUAcgBpAGEAMgApACwAMQAsAC0ALQAoAEMAcgBpAHQAZQByAGkAYQAyAEEAcgByAGEAeQA9AEMAcgBpAHQAZQByAGkAYQAyACkAKQAsAFwAbgAgACAAIAAgAFMAVQBNAFAAUgBPAEQAVQBDAFQAKABjAHIAaQB0AGUAcgBpAGEAMQAqAGMAcgBpAHQAZQByAGkAYQAyACoAcQB1AGEAbgB0AGkAdAB5ACkAXABuACAAIAApAFwAbgApADsAXABuAFwAbgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAHMAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBTAHQAYQByAHQALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBFAG4AZAAsAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAUwAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgACAAIAAgACAARQAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAXABuACAAIAAgACAAIAAgACAAIABtACwATQBPAE4AVABIACgAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAApACwAXABuACAAIAAgACAAIAAgACAAIABkACwARABBAFkAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAFAAZQByAGkAbwBkAEUAbgBkACwATABBAE0AQgBEAEEAKABzAHQALABFAEQAQQBUAEUAKABzAHQALAAxADIAKQAtADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAQQAsAFMALQAzADYANQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBhACwAWQBFAEEAUgAoAEEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBiACwAWQBFAEEAUgAoAEUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZgBpAHIAcwB0AFkAZQBhAHIALAB5AGEAKwAoAFAAZQByAGkAbwBkAEUAbgBkACgARABBAFQARQAoAHkAYQAsAG0ALABkACkAKQBcAHUAMAAwADMAYwAgAFMAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAbABhAHMAdABZAGUAYQByACwAeQBiAC0AKABEAEEAVABFACgAeQBiACwAbQAsAGQAKQBcAHUAMAAwADMAZQAgAEUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAATQBBAFgAKAAwACwAbABhAHMAdABZAGUAYQByAC0AZgBpAHIAcwB0AFkAZQBhAHIAKwAxACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAFAAZQByAGkAbwBkAHMAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBTAHQAYQByAHQALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBFAG4AZAAsAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAUwAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgACAAIAAgACAARQAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAXABuACAAIAAgACAAIAAgACAAIABtACwATQBPAE4AVABIACgAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAApACwAXABuACAAIAAgACAAIAAgACAAIABkACwARABBAFkAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALAAgAC8AKgBoAGUAbABwAGUAcgA6ACAAZQBuAGQAIABkAGEAdABlACAAZgBvAHIAIABhACAAcgBlAHAAbwByAHQAaQBuAGcAIABwAGUAcgBpAG8AZAAgAHMAdABhAHIAdABpAG4AZwAgAGEAdAAgAGEAIABnAGkAdgBlAG4AIABkAGEAdABlACoALwBcAG4AIAAgACAAIAAgACAAIAAgAFAAZQByAGkAbwBkAEUAbgBkACwATABBAE0AQgBEAEEAKABzAHQALABFAEQAQQBUAEUAKABzAHQALAAxADIAKQAtADEAKQAsACAALwAqAG8AbgBsAHkAIABuAGUAZQBkACAAdABvACAAbABvAG8AawAgAGIAYQBjAGsAIAAzADYANQAgAGQAYQB5AHMAKABtAGEAeAAgAG8AdgBlAHIAbABhAHAAIAB3AGkAbgBkAG8AdwApACoALwBcAG4AIAAgACAAIAAgACAAIAAgAEEALABTAC0AMwA2ADUALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYQAsAFkARQBBAFIAKABBACkALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYgAsAFkARQBBAFIAKABFACkALAAgAC8AKgBpAGYAIAB0AGgAZQAgAGEAbgBjAGgAbwByACAAZgBvAHIAIAB5AGEAIABlAG4AZABzACAAYgBlAGYAbwByAGUAIABTACwAaQB0ACAAYwBhAG4AXAB1ADAAMAAyADcAdAAgAG8AdgBlAHIAbABhAHAAOwAgAG0AbwB2AGUAIAB0AG8AIABuAGUAeAB0ACAAeQBlAGEAcgAqAC8AXABuACAAIAAgACAAIAAgACAAIABmAGkAcgBzAHQAWQBlAGEAcgAsAHkAYQArACgAUABlAHIAaQBvAGQARQBuAGQAKABEAEEAVABFACgAeQBhACwAbQAsAGQAKQApAFwAdQAwADAAMwBjAFMAKQAsACAALwAqAGkAZgAgAHQAaABlACAAYQBuAGMAaABvAHIAIABmAG8AcgAgAHkAYgAgAHMAdABhAHIAdABzACAAYQBmAHQAZQByACAARQAsAGkAdAAgAGMAYQBuAFwAdQAwADAAMgA3AHQAIABvAHYAZQByAGwAYQBwADsAIABtAG8AdgBlACAAdABvACAAcAByAGUAdgBpAG8AdQBzACAAeQBlAGEAcgAqAC8AXABuACAAIAAgACAAIAAgACAAIABsAGEAcwB0AFkAZQBhAHIALAB5AGIALQAoAEQAQQBUAEUAKAB5AGIALABtACwAZAApAFwAdQAwADAAMwBlAEUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAbgAsAE0AQQBYACgAMAAsAGwAYQBzAHQAWQBlAGEAcgAtAGYAaQByAHMAdABZAGUAYQByACsAMQApACwAXABuACAAIAAgACAAIAAgACAAIAB5AHIAcwAsAFMARQBRAFUARQBOAEMARQAoAG4ALAAxACwAZgBpAHIAcwB0AFkAZQBhAHIALAAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAHMAdABhAHIAdABzACwARABBAFQARQAoAHkAcgBzACwAbQAsAGQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZQBuAGQAcwAsAE0AQQBQACgAcwB0AGEAcgB0AHMALABQAGUAcgBpAG8AZABFAG4AZAApACwAXABuACAAIAAgACAAIAAgACAAIAB0AGEAZwAsAEkARgAoAHMAdABhAHIAdABzAD0AUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAIgAgACgAVABoAGkAcwAgAHIAZQBwAG8AcgB0AGkAbgBnACAAYwB5AGMAbABlACkAXAAiACwAXAAiAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABzAHQAYQByAHQAcwBUAGUAeAB0ACwAVABFAFgAVAAoAHMAdABhAHIAdABzACwAXAAiAGQAZAAgAG0AbQBtACAAeQB5AHkAeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZQBuAGQAcwBUAGUAeAB0ACwAVABFAFgAVAAoAGUAbgBkAHMALABcACIAZABkACAAbQBtAG0AIAB5AHkAeQB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABuAD0AMAAsAFwAIgBcACIALABIAFMAVABBAEMASwAoAHMAdABhAHIAdABzAFQAZQB4AHQAIABcAHUAMAAwADIANgAgAFwAIgAgAHQAbwAgAFwAIgAgAFwAdQAwADAAMgA2ACAAZQBuAGQAcwBUAGUAeAB0ACAAXAB1ADAAMAAyADYAIAB0AGEAZwApACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkARgB1AG4AYwB0AGkAbwBuAE4AYQBtAGUAXABuAD0ATABBAE0AQgBEAEEAKABGAHUAbgBjAHQAaQBvAG4ALAAgAFQARQBYAFQAQgBFAEYATwBSAEUAKABGAE8AUgBNAFUATABBAFQARQBYAFQAKABGAHUAbgBjAHQAaQBvAG4AKQAsACAAXAAiACgAXAAiACkAKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAE4AMgBPAEUARgBGAHIAbwBtAFAAcgBvAGQASQByAHIAaQBnAGEAdABpAG8AbgBSAGEAaQBuAGYAYQBsAGwAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAIABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACwAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AQQByAHIAYQB5ACwAIABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkAEEAcgByAGEAeQAsACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAQQByAHIAYQB5ACwAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQALAAgAEkARgAoAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAPQBcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEEAbgB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQAsACAASQBGACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAAgAD0AIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAIABcACIAQQBuAHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKAAxACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEEAcgByAGEAeQA9AFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AKQAqAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAoAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAQQByAHIAYQB5AD0ASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAApACoAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACgAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAQQByAHIAYQB5AD0AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEcAZQB0AEYAcgBhAGMAVwBFAFQAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ALABcAG4AIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQALAAgAFwAbgAgACAAIAAgACAAIAAgACAAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUALABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBMAG8AbwBrAHUAcAAsAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQALAAgAFwAbgAgACAAIAAgACAAIAAgACAAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ATABvAG8AawB1AHAALABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBGAHIAYQBjAFcARQBUACAAKwAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVABcAHUAMAAwADMAZQAwACwAIAAxACwAIAAwACkAXABuACAAIAAgACAAKQApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEMAbwBuAHYAZQByAHQAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAVABvAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUALABcAG4AIAAgACAAIABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBBAHIAcgBhAHkALAAgAFMAdABhAHQAZQBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUALAAgAFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAEEAcgByAGEAeQAsACAAUwB0AGEAdABlAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwBvAHUAcgBjAGUASAB5AHAAZQByAGwAaQBuAGsAXABuAD0ATABBAE0AQgBEAEEAKABUAGEAcgBnAGUAdABDAGUAbABsACwAXABuACAAIABMAEUAVAAoAFwAbgAgACAAIAAgAHMAaAAsACAAVABFAFgAVABBAEYAVABFAFIAKABDAEUATABMACgAXAAiAGYAaQBsAGUAbgBhAG0AZQBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsACAAXAAiAF0AXAAiACkALABcAG4AIAAgACAAIABhAGQAZAByACwAIABDAEUATABMACgAXAAiAGEAZABkAHIAZQBzAHMAXAAiACwAIABUAGEAcgBnAGUAdABDAGUAbABsACkALABcAG4AIAAgACAAIABcACIAIwBcAHUAMAAwADIANwBcACIAIABcAHUAMAAwADIANgAgAHMAaAAgAFwAdQAwADAAMgA2ACAAXAAiAFwAdQAwADAAMgA3ACEAXAAiACAAXAB1ADAAMAAyADYAIABhAGQAZAByAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAbwB1AHIAYwBlAEgAeQBwAGUAcgBsAGkAbgBrAEQAaQBmAGYAZQByAGUAbgB0AFMAaABlAGUAdABcAG4APQBMAEEATQBCAEQAQQAoAFQAYQByAGcAZQB0AEMAZQBsAGwALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAcwBoACwAIABUAEUAWABUAEEARgBUAEUAUgAoAEMARQBMAEwAKABcACIAZgBpAGwAZQBuAGEAbQBlAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAIABcACIAXQBcACIAKQAsAFwAbgAgACAAIAAgAGEAZABkAHIALAAgAEMARQBMAEwAKABcACIAYQBkAGQAcgBlAHMAcwBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsAFwAbgAgACAAIAAgAFwAIgAjAFwAIgAgAFwAdQAwADAAMgA2ACAAYQBkAGQAcgBcAG4AIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgBnAHUAbQBlAG4AdABzAF8AMQBfADIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALABcAG4AIAAgACAAIABDAEgATwBPAFMARQBDAE8ATABTACgAQQByAGcAdQBtAGUAbgB0AHMAQQByAHIAYQB5ACwAIAAxACwAIAAyACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgBnAHUAbQBlAG4AdABzAF8AMwBfADQAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALABcAG4AIAAgACAAIABDAEgATwBPAFMARQBDAE8ATABTACgAQQByAGcAdQBtAGUAbgB0AHMAQQByAHIAYQB5ACwAIAAzACwAIAA0ACkAXABuACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8ARwBlAHQATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUALAAgAE0ATQBTACwAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUAQQByAHIAYQB5ACwAIABNAE0AUwBBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKABcAG4AIAAgACAAIAAgACAAIAAgAE0ARQBEAEkAQQBOACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAE0ASQBOACgAVABlAG0AcABlAHIAYQB0AHUAcgBlAEEAcgByAGEAeQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATQBBAFgAKABUAGUAbQBwAGUAcgBhAHQAdQByAGUAQQByAHIAYQB5ACkAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUAQQByAHIAYQB5ACwAXABuACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATQBNAFMALAAgAE0ATQBTAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBSAGUAcwB1AGwAdABzAEkAdABlAG0ARgByAG8AbQBFAHEAdQBhAHQAaQBvAG4AVABpAHQAbABlAEEAbgBkAFMAbwB1AHIAYwBlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAVABpAHQAbABlAEMAZQBsAGwALAAgAFMAbwB1AHIAYwBlAEMAZQBsAGwALABcAG4AIAAgACAAIABTAFUAQgBTAFQASQBUAFUAVABFACgATABFAEYAVAAoAFMAbwB1AHIAYwBlAEMAZQBsAGwALAAgAEYASQBOAEQAKABcACIALABcACIALAAgAFMAbwB1AHIAYwBlAEMAZQBsAGwAKQAgAC0AMQApACwAIABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAXAAiACwAIABcACIAXAAiACkAIABcAHUAMAAwADIANgAgAFwAIgAgAFwAIgAgAFwAdQAwADAAMgA2ACAAVABpAHQAbABlAEMAZQBsAGwAXABuACkAOwAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuADEAMQAuADEAOgAgAFcAYQBzAHQAZQB3AGEAdABlAHIAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuADEAMQAuADEALgAxAC4AMQAgAE0AZQB0AGgAbwBkACAAMQAgAC0AIABNAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAbwBuAHMAaQB0AGUAIABXAGEAcwB0AGUAdwBhAHQAZQByACAATQBhAG4AYQBnAGUAbQBlAG4AdABcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADEAMQBfADEAXwAxAF8AMQBfAF8AMQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBXAGEAcwB0AGUAdwBhAHQAZQByAFQAcgBlAGEAdABtAGUAbgB0AFwAbgBNAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAdwBhAHMAdABlAHcAYQB0AGUAcgAgAHQAcgBlAGEAdABtAGUAbgB0AFwAbgBFAF8AQwBIADQAXABuAHQAIABDAEgANABcAG4ARQBfAHsAQwBIADQAfQA9AFwAXABmAHIAYQBjAHsAMQB9AHsAMQAwADAAMAB9AFwAXAB0AGkAbQBlAHMAXABcAGwAZQBmAHQAWwBcAFwAbABlAGYAdAAoAFcAXwB0AFwAXAB0AGkAbQBlAHMAXABcAGwAZQBmAHQAKABDAE8ARABfAHsAaQBuAH0AXABcAHQAaQBtAGUAcwAoADEALQBGAF8AewBzAGwAdQBkAGcAZQB9ACkALQBDAE8ARABfAHsAbwB1AHQAfQBcAFwAcgBpAGcAaAB0ACkAXABcAHQAaQBtAGUAcwAgAEMARgBfAHsAdwB3ACwAdAB9AFwAXAB0AGkAbQBlAHMAIABFAEYAXwB7AHcAdwB9AFwAXAByAGkAZwBoAHQAKQArAFwAXABsAGUAZgB0ACgAVwBfAHQAXABcAHQAaQBtAGUAcwBcAFwAbABlAGYAdAAoAEMATwBEAF8AewBpAG4AfQBcAFwAdABpAG0AZQBzACgARgBfAHsAcwBsAHUAZABnAGUAfQAtAEYAXwB7AHIAZQBtAG8AdgBlAGQAfQApAFwAXAByAGkAZwBoAHQAKQBcAFwAdABpAG0AZQBzACAAQwBGAF8AewBzAGwAdQBkAGcAZQAsAHQAfQBcAFwAdABpAG0AZQBzACAARQBGAF8AewBzAGwAdQBkAGcAZQB9AFwAXAByAGkAZwBoAHQAKQAtAFwAXABsAGUAZgB0ACgANgAuADcAOAA0AFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0ANAB9AFwAXAB0AGkAbQBlAHMAKABRAF8AewBjAGEAcAB9ACsAUQBfAHsAZgBsAGEAcgBlAGQAfQArAFEAXwB7AG8AdQB0AH0AKQBcAFwAcgBpAGcAaAB0ACkAKwBcAFwAbABlAGYAdAAoAFEAXwB7AGYAbABhAHIAZQBkAH0AXABcAHQAaQBtAGUAcwAgAEUAQwBfAHsAZgBsAGEAcgBlAGQAfQBcAFwAdABpAG0AZQBzACAARQBGAF8AewBmAGwAYQByAGUAZAAsAEMASAA0AH0AXABcAHIAaQBnAGgAdAApAFwAXAByAGkAZwBoAHQAXQBcAG4AVwBfAHQAIAA9ACAAcQB1AGEAbgB0AGkAdAB5ACAAbwBmACAAdwBhAHMAdABlAHcAYQB0AGUAcgAgAHQAcgBlAGEAdABlAGQAIABhAHQAIABmAGEAYwBpAGwAaQB0AHkAIAB0AHkAcABlACAAdAAgACgAbQAzACkAXABuAEMATwBEAF8AaQBuACAAPQAgAGEAdgBlAHIAYQBnAGUAIABpAG4AbABlAHQAIABDAGgAZQBtAGkAYwBhAGwAIABPAHgAeQBnAGUAbgAgAEQAZQBtAGEAbgBkACAAYwBvAG4AYwBlAG4AdAByAGEAdABpAG8AbgAgAG8AZgAgAHcAYQBzAHQAZQB3AGEAdABlAHIAIAAoAGsAZwAgAEMATwBEAC8AbQAzACkAXABuAEYAXwBzAGwAdQBkAGcAZQAgAD0AIABmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABDAE8ARAAgAHIAZQBtAG8AdgBlAGQAIABmAHIAbwBtACAAdwBhAHMAdABlAHcAYQB0AGUAcgAgAGEAcwAgAHMAbAB1AGQAZwBlAFwAbgBDAE8ARABfAG8AdQB0ACAAPQAgAGEAdgBlAHIAYQBnAGUAIABvAHUAdABsAGUAdAAgAEMATwBEACAAYwBvAG4AYwBlAG4AdAByAGEAdABpAG8AbgAgAG8AZgAgAHcAYQBzAHQAZQB3AGEAdABlAHIAIAAoAGsAZwAgAEMATwBEAC8AbQAzACkAXABuAEMARgBfAHcAdwBfAHQAIAA9ACAAbQBlAHQAaABhAG4AZQAgAGMAbwByAHIAZQBjAHQAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAZgBhAGMAaQBsAGkAdAB5ACAAdAB5AHAAZQAgAHQAIAB1AHMAZQBkACAAdABvACAAdAByAGUAYQB0ACAAdwBhAHMAdABlAHcAYQB0AGUAcgBcAG4ARQBGAF8AdwB3ACAAPQAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAdwBhAHMAdABlAHcAYQB0AGUAcgAgACgAawBnACAAQwBPADIAZQAvAGsAZwAgAEMATwBEACkAXABuAEYAXwByAGUAbQBvAHYAZQBkACAAPQAgAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAEMATwBEACAAcgBlAG0AbwB2AGUAZAAgAGYAcgBvAG0AIAB0AGgAZQAgAHcAYQBzAHQAZQB3AGEAdABlAHIAIAB0AHIAZQBhAHQAbQBlAG4AdAAgAGYAYQBjAGkAbABpAHQAeQAgAGEAbgBkACAAdAByAGEAbgBzAGYAZQByAHIAZQBkACAAZQBsAHMAZQB3AGgAZQByAGUAXABuAEMARgBfAHMAbAB1AGQAZwBlAF8AdAAgAD0AIABtAGUAdABoAGEAbgBlACAAYwBvAHIAcgBlAGMAdABpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABmAGEAYwBpAGwAaQB0AHkAIAB0AHkAcABlACAAdAAgAHUAcwBlAGQAIAB0AG8AIAB0AHIAZQBhAHQAIABzAGwAdQBkAGcAZQBcAG4ARQBGAF8AcwBsAHUAZABnAGUAIAA9ACAAbQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABzAGwAdQBkAGcAZQAgACgAawBnACAAQwBPADIAZQAvAGsAZwAgAEMATwBEACkAXABuAFEAXwBjAGEAcAAgAD0AIABxAHUAYQBuAHQAaQB0AHkAIABvAGYAIABtAGUAdABoAGEAbgBlACAAaQBuACAAcwBsAHUAZABnAGUAIABiAGkAbwBnAGEAcwAgAGMAYQBwAHQAdQByAGUAZAAgAGYAbwByACAAYwBvAG0AYgB1AHMAdABpAG8AbgAgACgAbQAzACAAQwBIADQAKQBcAG4AUQBfAGYAbABhAHIAZQBkACAAPQAgAHEAdQBhAG4AdABpAHQAeQAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAIABpAG4AIABzAGwAdQBkAGcAZQAgAGIAaQBvAGcAYQBzACAAZgBsAGEAcgBlAGQAIAAoAG0AMwAgAEMASAA0ACkAXABuAFEAXwBvAHUAdAAgAD0AIABxAHUAYQBuAHQAaQB0AHkAIABvAGYAIABtAGUAdABoAGEAbgBlACAAaQBuACAAcwBsAHUAZABnAGUAIABiAGkAbwBnAGEAcwAgAHQAcgBhAG4AcwBmAGUAcgByAGUAZAAgAG8AdQB0ACAAbwBmACAAdABoAGUAIAB0AHIAZQBhAHQAbQBlAG4AdAAgAGYAYQBjAGkAbABpAHQAeQAgACgAbQAzACAAQwBIADQAKQBcAG4ARQBDAF8AZgBsAGEAcgBlAGQAIAA9ACAAZQBuAGUAcgBnAHkAIABjAG8AbgB0AGUAbgB0ACAAZgBhAGMAdABvAHIAIABvAGYAIABtAGUAdABoAGEAbgBlACAAaQBuACAAcwBsAHUAZABnAGUAIABiAGkAbwBnAGEAcwAgAGYAbABhAHIAZQBkACAAKABHAEoALwBtADMAKQBcAG4ARQBGAF8AZgBsAGEAcgBlAGQAXwBDAEgANAAgAD0AIABtAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHMAbAB1AGQAZwBlACAAYgBpAG8AZwBhAHMAIABmAGwAYQByAGUAZAAgACgAawBnACAAQwBPADIAZQAvAEcASgApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADEAMQBfADEAXwAxAF8AMQBfAF8AMQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBXAGEAcwB0AGUAdwBhAHQAZQByAFQAcgBlAGEAdABtAGUAbgB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFcAXwB0ACwAIABDAE8ARABfAGkAbgAsACAARgBfAHMAbAB1AGQAZwBlACwAIABDAE8ARABfAG8AdQB0ACwAIABDAEYAXwB3AHcAXwB0ACwAIABFAEYAXwB3AHcALAAgAEYAXwByAGUAbQBvAHYAZQBkACwAIABDAEYAXwBzAGwAdQBkAGcAZQBfAHQALAAgAEUARgBfAHMAbAB1AGQAZwBlACwAIABRAF8AYwBhAHAALAAgAFEAXwBmAGwAYQByAGUAZAAsACAAUQBfAG8AdQB0ACwAIABFAEMAXwBmAGwAYQByAGUAZAAsACAARQBGAF8AZgBsAGEAcgBlAGQAQwBIADQALABcAG4AIAAgACAAIAAoADEALwAxADAAMAAwACkAIAAqACAAKAAoAFcAXwB0ACAAKgAgACgAQwBPAEQAXwBpAG4AIAAqACAAKAAxACAALQAgAEYAXwBzAGwAdQBkAGcAZQApACAALQAgAEMATwBEAF8AbwB1AHQAKQAgACoAIABDAEYAXwB3AHcAXwB0ACAAKgAgAEUARgBfAHcAdwApACAAKwAgACgAVwBfAHQAIAAqACAAKABDAE8ARABfAGkAbgAgACoAIAAoAEYAXwBzAGwAdQBkAGcAZQAgAC0AIABGAF8AcgBlAG0AbwB2AGUAZAApACkAIAAqACAAQwBGAF8AcwBsAHUAZABnAGUAXwB0ACAAKgAgAEUARgBfAHMAbAB1AGQAZwBlACkAIAAtACAAKAA2AC4ANwA4ADQAIAAqACAAMQAwAF4ALQA0ACAAKgAgACgAUQBfAGMAYQBwACAAKwAgAFEAXwBmAGwAYQByAGUAZAAgACsAIABRAF8AbwB1AHQAKQApACAAKwAgACgAUQBfAGYAbABhAHIAZQBkACAAKgAgACgARQBDAF8AZgBsAGEAcgBlAGQAIAAqACAARQBGAF8AZgBsAGEAcgBlAGQAQwBIADQAKQApACkAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADEAXwAxAF8AMQBfADEAXwBfADEAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AVwBhAHMAdABlAHcAYQB0AGUAcgBUAHIAZQBhAHQAbQBlAG4AdABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAHcAYQBzAHQAZQB3AGEAdABlAHIAIAB0AHIAZQBhAHQAbQBlAG4AdABcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQAxAF8AMQBfADEAXwAxAF8AXwAxAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFcAYQBzAHQAZQB3AGEAdABlAHIAVAByAGUAYQB0AG0AZQBuAHQAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwBDAEgANABcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQAxAF8AMQBfADEAXwAxAF8AXwAxAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFcAYQBzAHQAZQB3AGEAdABlAHIAVAByAGUAYQB0AG0AZQBuAHQAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgB0ACAAQwBIADQAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEAMQBfADEAXwAxAF8AMQBfAF8AMQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBXAGEAcwB0AGUAdwBhAHQAZQByAFQAcgBlAGEAdABtAGUAbgB0AF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADEAMQAuADEALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAxACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEAMQBfADEAXwAxAF8AMQBfAF8AMQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBXAGEAcwB0AGUAdwBhAHQAZQByAFQAcgBlAGEAdABtAGUAbgB0AF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEcAcgBlAGUAbgBoAG8AdQBzAGUAIABhAG4AZAAgAEUAbgBlAHIAZwB5ACAAUgBlAHAAbwByAHQAaQBuAGcAIABNAGUAYQBzAHUAcgBlAG0AZQBuAHQAIABEAGUAdABlAHIAbQBpAG4AYQB0AGkAbwBuACAAMgAwADAAOABcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQAxAF8AMQBfADEAXwAxAF8AXwAxAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFcAYQBzAHQAZQB3AGEAdABlAHIAVAByAGUAYQB0AG0AZQBuAHQAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAF8AewBDAEgANAB9AD0AXABcAGYAcgBhAGMAewAxAH0AewAxADAAMAAwAH0AXABcAHQAaQBtAGUAcwBcAFwAbABlAGYAdAB7AFwAXABsAGUAZgB0AHsAVwBfAHQAXABcAHQAaQBtAGUAcwBcAFwAbABlAGYAdABbAEMATwBEAF8AewBpAG4AfQBcAFwAdABpAG0AZQBzACgAMQAtAEYAXwB7AHMAbAB1AGQAZwBlAH0AKQAtAEMATwBEAF8AewBvAHUAdAB9AFwAXAByAGkAZwBoAHQAXQBcAFwAdABpAG0AZQBzACAAQwBGAF8AewB3AHcALAB0AH0AXABcAHQAaQBtAGUAcwAgAEUARgBfAHsAdwB3AH0AXABcAHIAaQBnAGgAdAB9ACsAXABcAGwAZQBmAHQAewBXAF8AdABcAFwAdABpAG0AZQBzAFwAXABsAGUAZgB0AFsAQwBPAEQAXwB7AGkAbgB9AFwAXAB0AGkAbQBlAHMAKABGAF8AewBzAGwAdQBkAGcAZQB9AC0ARgBfAHsAcgBlAG0AbwB2AGUAZAB9ACkAXABcAHIAaQBnAGgAdABdAFwAXAB0AGkAbQBlAHMAIABDAEYAXwB7AHMAbAB1AGQAZwBlACwAdAB9AFwAXAB0AGkAbQBlAHMAIABFAEYAXwB7AHMAbAB1AGQAZwBlAH0AXABcAHIAaQBnAGgAdAB9AC0AXABcAGwAZQBmAHQAewA2AC4ANwA4ADQAXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQA0AH0AXABcAHQAaQBtAGUAcwAgAFwAXABsAGUAZgB0AFsAIABRAF8AewBjAGEAcAB9ACsAUQBfAHsAZgBsAGEAcgBlAGQAfQArAFEAXwB7AG8AdQB0AH0AXABcAHIAaQBnAGgAdABdAFwAXAByAGkAZwBoAHQAfQArAFwAXABsAGUAZgB0AHsAUQBfAHsAZgBsAGEAcgBlAGQAfQBcAFwAdABpAG0AZQBzACAAXABcAGwAZQBmAHQAWwAgAEUAQwBfAHsAZgBsAGEAcgBlAGQAfQBcAFwAdABpAG0AZQBzACAARQBGAF8AewBmAGwAYQByAGUAZAAsAEMASAA0AH0AXABcAHIAaQBnAGgAdABdAFwAXAByAGkAZwBoAHQAfQBcAFwAcgBpAGcAaAB0AH0AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEAMQBfADEAXwAxAF8AMQBfAF8AMQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBXAGEAcwB0AGUAdwBhAHQAZQByAFQAcgBlAGEAdABtAGUAbgB0AF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADUALAAgADQALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBfAHQAXAAiACwAIABcACIAcQB1AGEAbgB0AGkAdAB5ACAAbwBmACAAdwBhAHMAdABlAHcAYQB0AGUAcgAgAHQAcgBlAGEAdABlAGQAIABhAHQAIABmAGEAYwBpAGwAaQB0AHkAIAB0AHkAcABlACAAdABcACIALAAgAFwAIgBtADMAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAE8ARABfAGkAbgBcACIALAAgAFwAIgBhAHYAZQByAGEAZwBlACAAaQBuAGwAZQB0ACAAQwBoAGUAbQBpAGMAYQBsACAATwB4AHkAZwBlAG4AIABEAGUAbQBhAG4AZAAgAGMAbwBuAGMAZQBuAHQAcgBhAHQAaQBvAG4AIABvAGYAIAB3AGEAcwB0AGUAdwBhAHQAZQByAFwAIgAsACAAXAAiAGsAZwAgAEMATwBEAC8AbQAzAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBfAHMAbAB1AGQAZwBlAFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAEMATwBEACAAcgBlAG0AbwB2AGUAZAAgAGYAcgBvAG0AIAB3AGEAcwB0AGUAdwBhAHQAZQByACAAYQBzACAAcwBsAHUAZABnAGUAXAAiACwAIABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPAEQAXwBvAHUAdABcACIALAAgAFwAIgBhAHYAZQByAGEAZwBlACAAbwB1AHQAbABlAHQAIABDAE8ARAAgAGMAbwBuAGMAZQBuAHQAcgBhAHQAaQBvAG4AIABvAGYAIAB3AGEAcwB0AGUAdwBhAHQAZQByAFwAIgAsACAAXAAiAGsAZwAgAEMATwBEAC8AbQAzAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBGAF8AdwB3AF8AdABcACIALAAgAFwAIgBtAGUAdABoAGEAbgBlACAAYwBvAHIAcgBlAGMAdABpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABmAGEAYwBpAGwAaQB0AHkAIAB0AHkAcABlACAAdAAgAHUAcwBlAGQAIAB0AG8AIAB0AHIAZQBhAHQAIAB3AGEAcwB0AGUAdwBhAHQAZQByAFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARgBfAHcAdwBcACIALAAgAFwAIgBtAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHcAYQBzAHQAZQB3AGEAdABlAHIAXAAiACwAIABcACIAawBnACAAQwBIADQALwBrAGcAIABDAE8ARABcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAXwByAGUAbQBvAHYAZQBkAFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAEMATwBEACAAcgBlAG0AbwB2AGUAZAAgAGYAcgBvAG0AIAB0AGgAZQAgAHcAYQBzAHQAZQB3AGEAdABlAHIAIAB0AHIAZQBhAHQAbQBlAG4AdAAgAGYAYQBjAGkAbABpAHQAeQAgAGEAbgBkACAAdAByAGEAbgBzAGYAZQByAHIAZQBkACAAZQBsAHMAZQB3AGgAZQByAGUAXAAiACwAIABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBGAF8AcwBsAHUAZABnAGUAXwB0AFwAIgAsACAAXAAiAG0AZQB0AGgAYQBuAGUAIABjAG8AcgByAGUAYwB0AGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAGYAYQBjAGkAbABpAHQAeQAgAHQAeQBwAGUAIAB0ACAAdQBzAGUAZAAgAHQAbwAgAHQAcgBlAGEAdAAgAHMAbAB1AGQAZwBlAFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARgBfAHMAbAB1AGQAZwBlAFwAIgAsACAAXAAiAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAcwBsAHUAZABnAGUAXAAiACwAIABcACIAawBnACAAQwBIADQALwBrAGcAIABDAE8ARABcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEAXwBjAGEAcABcACIALAAgAFwAIgBxAHUAYQBuAHQAaQB0AHkAIABvAGYAIABtAGUAdABoAGEAbgBlACAAaQBuACAAcwBsAHUAZABnAGUAIABiAGkAbwBnAGEAcwAgAGMAYQBwAHQAdQByAGUAZAAgAGYAbwByACAAYwBvAG0AYgB1AHMAdABpAG8AbgBcACIALAAgAFwAIgBtADMAIABDAEgANABcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEAXwBmAGwAYQByAGUAZABcACIALAAgAFwAIgBxAHUAYQBuAHQAaQB0AHkAIABvAGYAIABtAGUAdABoAGEAbgBlACAAaQBuACAAcwBsAHUAZABnAGUAIABiAGkAbwBnAGEAcwAgAGYAbABhAHIAZQBkACAAYgB5ACAAdABoAGUAIAB0AHIAZQBhAHQAbQBlAG4AdAAgAGYAYQBjAGkAbABpAHQAeQBcACIALAAgAFwAIgBtADMAIABDAEgANABcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEAXwBvAHUAdABcACIALAAgAFwAIgBxAHUAYQBuAHQAaQB0AHkAIABvAGYAIABtAGUAdABoAGEAbgBlACAAaQBuACAAcwBsAHUAZABnAGUAIABiAGkAbwBnAGEAcwAgAHQAcgBhAG4AcwBmAGUAcgByAGUAZAAgAG8AdQB0ACAAbwBmACAAdABoAGUAIAB0AHIAZQBhAHQAbQBlAG4AdAAgAGYAYQBjAGkAbABpAHQAeQBcACIALAAgAFwAIgBtADMAIABDAEgANABcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUAQwBfAGYAbABhAHIAZQBkAFwAIgAsACAAXAAiAGUAbgBlAHIAZwB5ACAAYwBvAG4AdABlAG4AdAAgAGYAYQBjAHQAbwByACAAbwBmACAAbQBlAHQAaABhAG4AZQAgAGkAbgAgAHMAbAB1AGQAZwBlACAAYgBpAG8AZwBhAHMAIABmAGwAYQByAGUAZABcACIALAAgAFwAIgBHAEoALwBtADMAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAEYAXwBmAGwAYQByAGUAZABDAEgANABcACIALAAgAFwAIgBtAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHMAbAB1AGQAZwBlACAAYgBpAG8AZwBhAHMAIABmAGwAYQByAGUAZABcACIALAAgAFwAIgBrAGcAIABDAEgANAAvAEcASgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAHQAXAAiACwAIABcACIAdAByAGUAYQB0AG0AZQBuAHQAIABmAGEAYwBpAGwAaQB0AHkAIAB0AHkAcABlAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgBWAEUARQBSAEcAXwAxADEAXwAxAF8AMQBfADEAXwBfADEAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AVwBhAHMAdABlAHcAYQB0AGUAcgBUAHIAZQBhAHQAbQBlAG4AdABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ATgAgAFMATwBVAFIAQwBFADoAIABDAGgAYQBuAGcAZQBkACAAdQBuAGkAdABzACAAbwBmACAARQBGAF8AdwB3ACwAIABFAEYAXwBTAGwAdQBkAGcAZQAgAGEAbgBkACAARQBGAF8AZgBsAGEAcgBlAGQAIABmAHIAbwBtACAAQwBPADIAZQAgAHQAbwAgAEMASAA0ACAAdABvACAAbQBhAHQAYwBoACAAZABhAHQAYQAgAGkAbgAgAFQAYQBiAGwAZQAgAFwAIgApADsAIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAGEAcwB0AGUAdwBhAHQAZQByAF8AUwBvAHUAcgBjAGUARABhAHQAYQAiACwAIgB0AGUAeAB0ACIAOgAiAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AVABhAGIAbABlACAAQQAuADQALgAxAC4AMwA6ACAATQBlAHQAaABhAG4AZQAgAGMAbwByAHIAZQBjAHQAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAdAByAGUAYQB0AG0AZQBuAHQAIABmAGEAYwBpAGwAaQB0AHkAIAB0AHkAcABlACAAdAAgAHUAcwBlAGQAIAB0AG8AIAB0AHIAZQBhAHQAIAB3AGEAcwB0AGUAdwBhAHQAZQByACAAKABmAHIAYQBjAHQAaQBvAG4AKQAgACgAQwBGAHcAdwAsAHQAKQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBDAG8AcgByAGUAYwB0AGkAbwBuAEYAYQBjAHQAbwByAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBUAGkAdABsAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBNAGUAdABoAGEAbgBlACAAYwBvAHIAcgBlAGMAdABpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB0AHIAZQBhAHQAbQBlAG4AdAAgAGYAYQBjAGkAbABpAHQAeQAgAHQAeQBwAGUAIAB0ACAAdQBzAGUAZAAgAHQAbwAgAHQAcgBlAGEAdAAgAHcAYQBzAHQAZQB3AGEAdABlAHIAXAAiACkAKQA7AFwAbgBcAG4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBDAG8AcgByAGUAYwB0AGkAbwBuAEYAYQBjAHQAbwByAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBWAGEAcgBpAGEAYgBsAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBDAEYAdwB3ACwAdABcACIAKQApADsAXABuAFwAbgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEMAbwByAHIAZQBjAHQAaQBvAG4ARgBhAGMAdABvAHIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFUAbgBpAHQAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACkAKQA7AFwAbgBcAG4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBDAG8AcgByAGUAYwB0AGkAbwBuAEYAYQBjAHQAbwByAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBTAG8AdQByAGMAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgA0AC4AMQAuADMAXAAiACkAKQA7AFwAbgBcAG4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBDAG8AcgByAGUAYwB0AGkAbwBuAEYAYQBjAHQAbwByAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBEAGEAdABhAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADIALABcAG4AIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIABcACIARgBhAGMAaQBsAGkAdAB5ACAAdAB5AHAAZQAgAHQAXAAiACwAIABcACIAQwBGAHcAdwAsAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIATQBhAG4AYQBnAGUAZAAgAGEAZQByAG8AYgBpAGMAIAB0AHIAZQBhAHQAbQBlAG4AdABcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBVAG4AbQBhAG4AYQBnAGUAZAAgAGEAZQByAG8AYgBpAGMAIAB0AHIAZQBhAHQAbQBlAG4AdABcACIALAAgADAALgAzADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQQBuAGEAZQByAG8AYgBpAGMAIABkAGkAZwBlAHMAdABvAHIALwByAGUAYQBjAHQAbwByAFwAIgAsACAAMAAuADgAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBTAGgAYQBsAGwAbwB3ACAAYQBuAGEAZQByAG8AYgBpAGMAIABsAGEAZwBvAG8AbgAgACgAZCIgADIAIABtACkAXAAiACwAIAAwAC4AMgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEQAZQBlAHAAIABhAG4AYQBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuACAAKABcAHUAMAAwADMAZQAgADIAbQApAFwAIgAsACAAMAAuADgAXABuACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AKQApACkAOwBcAG4AXABuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUAQwBvAHIAcgBlAGMAdABpAG8AbgBGAGEAYwB0AG8AcgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBcACIAKQApADsAXABuAFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgBUAGEAYgBsAGUAIABBAC4ANAAuADEALgA0ADoAIABNAGUAdABoAGEAbgBlACAAYwBvAHIAcgBlAGMAdABpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB0AHIAZQBhAHQAbQBlAG4AdAAgAGYAYQBjAGkAbABpAHQAeQAgAHQAeQBwAGUAIAB0ACAAdQBzAGUAZAAgAHQAbwAgAHQAcgBlAGEAdAAgAHMAbAB1AGQAZwBlACAAKABmAHIAYQBjAHQAaQBvAG4AKQAgACgAQwBGAHMAbAB1AGQAZwBlACwAdAApAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEMAbwByAHIAZQBjAHQAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAXwBUAGkAdABsAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBNAGUAdABoAGEAbgBlACAAYwBvAHIAcgBlAGMAdABpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB0AHIAZQBhAHQAbQBlAG4AdAAgAGYAYQBjAGkAbABpAHQAeQAgAHQAeQBwAGUAIAB0ACAAdQBzAGUAZAAgAHQAbwAgAHQAcgBlAGEAdAAgAHMAbAB1AGQAZwBlAFwAIgApACkAOwBcAG4AXABuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUAQwBvAHIAcgBlAGMAdABpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBfAFYAYQByAGkAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEMARgBzAGwAdQBkAGcAZQAsAHQAXAAiACkAKQA7AFwAbgBcAG4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBDAG8AcgByAGUAYwB0AGkAbwBuAEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAF8AVQBuAGkAdABcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIAKQApADsAXABuAFwAbgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEMAbwByAHIAZQBjAHQAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAXwBTAG8AdQByAGMAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgA0AC4AMQAuADQAXAAiACkAKQA7AFwAbgBcAG4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBDAG8AcgByAGUAYwB0AGkAbwBuAEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAF8ARABhAHQAYQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAAyACwAXABuACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEYAYQBjAGkAbABpAHQAeQAgAHQAeQBwAGUAIAB0AFwAIgAsACAAXAAiAEMARgBzAGwAdQBkAGcAZQAsAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIATQBhAG4AYQBnAGUAZAAgAGEAZQByAG8AYgBpAGMAIAB0AHIAZQBhAHQAbQBlAG4AdABcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBVAG4AbQBhAG4AYQBnAGUAZAAgAGEAZQByAG8AYgBpAGMAIAB0AHIAZQBhAHQAbQBlAG4AdABcACIALAAgADAALgAzADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQQBuAGEAZQByAG8AYgBpAGMAIABkAGkAZwBlAHMAdABvAHIALwByAGUAYQBjAHQAbwByAFwAIgAsACAAMAAuADgAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBTAGgAYQBsAGwAbwB3ACAAYQBuAGEAZQByAG8AYgBpAGMAIABsAGEAZwBvAG8AbgAgACgAZCIgADIAIABtACkAXAAiACwAIAAwAC4AMgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEQAZQBlAHAAIABhAG4AYQBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuACAAKABcAHUAMAAwADMAZQAgADIAbQApAFwAIgAsACAAMAAuADgAXABuACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AKQApACkAOwBcAG4AXABuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUAQwBvAHIAcgBlAGMAdABpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AVABpAHQAbABlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIATQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB3AGEAcwB0AGUAdwBhAHQAZQByAFwAIgApACkAOwBcAG4AXABuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBWAGEAcgBpAGEAYgBsAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBFAEYAdwB3AFwAIgApACkAOwBcAG4AXABuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBVAG4AaQB0AFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAawBnACAAQwBIADQAIAAvACAAawBnACAAQwBPAEQAXAAiACkAKQA7AFwAbgBcAG4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAMQAxAC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAcwBcACIAKQApADsAXABuAFwAbgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBXAGEAcwB0AGUAdwBhAHQAZQByAF8ARABhAHQAYQBcAG4APQBMAEEATQBCAEQAQQAoACAAMAAuADIANQApADsAXABuAFwAbgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAF8AVABpAHQAbABlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIATQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABzAGwAdQBkAGcAZQBcACIAKQApADsAXABuAFwAbgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBfAFYAYQByAGkAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEUARgBzAGwAdQBkAGcAZQBcACIAKQApADsAXABuAFwAbgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBfAFUAbgBpAHQAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBrAGcAIABDAEgANAAgAC8AIABrAGcAIABDAE8ARABcACIAKQApADsAXABuAFwAbgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBfAFMAbwB1AHIAYwBlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAMQAxAC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAcwBcACIAKQApADsAXABuAFwAbgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBfAEQAYQB0AGEAXABuAD0ATABBAE0AQgBEAEEAKAAwAC4AMgA1ACkAOwBcAG4AXABuAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4AVwBhAHMAdABlAF8ARQBuAGUAcgBnAHkAQwBvAG4AdABlAG4AdABGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBCAGkAbwBnAGEAcwBGAGwAYQByAGUAZABfAFQAaQB0AGwAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEUAbgBlAHIAZwB5ACAAYwBvAG4AdABlAG4AdAAgAGYAYQBjAHQAbwByACAAbwBmACAAcwBsAHUAZABnAGUAIABiAGkAbwBnAGEAcwAgAGYAbABhAHIAZQBkAFwAIgApACkAOwBcAG4AXABuAFcAYQBzAHQAZQBfAEUAbgBlAHIAZwB5AEMAbwBuAHQAZQBuAHQARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAQgBpAG8AZwBhAHMARgBsAGEAcgBlAGQAXwBWAGEAcgBpAGEAYgBsAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBFAEMAZgBsAGEAcgBlAGQAXAAiACkAKQA7AFwAbgBcAG4AVwBhAHMAdABlAF8ARQBuAGUAcgBnAHkAQwBvAG4AdABlAG4AdABGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBCAGkAbwBnAGEAcwBGAGwAYQByAGUAZABfAFUAbgBpAHQAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBHAEoAIAAvACAAbQAzAFwAIgApACkAOwBcAG4AXABuAFcAYQBzAHQAZQBfAEUAbgBlAHIAZwB5AEMAbwBuAHQAZQBuAHQARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAQgBpAG8AZwBhAHMARgBsAGEAcgBlAGQAXwBTAG8AdQByAGMAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADEAMQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0AHMAXAAiACkAKQA7AFwAbgBcAG4AVwBhAHMAdABlAF8ARQBuAGUAcgBnAHkAQwBvAG4AdABlAG4AdABGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBCAGkAbwBnAGEAcwBGAGwAYQByAGUAZABfAEQAYQB0AGEAXABuAD0ATABBAE0AQgBEAEEAKAAwAC4AMAAzADcANwApADsAXABuAFwAbgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAEIAaQBvAGcAYQBzAEYAbABhAHIAZQBkAF8AVABpAHQAbABlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIATQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABzAGwAdQBkAGcAZQAgAGIAaQBvAGcAYQBzACAAZgBsAGEAcgBlAGQAXAAiACkAKQA7AFwAbgBcAG4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAQgBpAG8AZwBhAHMARgBsAGEAcgBlAGQAXwBWAGEAcgBpAGEAYgBsAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBFAEYAZgBsAGEAcgBlAGQALABDAEgANABcACIAKQApADsAXABuAFwAbgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBCAGkAbwBnAGEAcwBGAGwAYQByAGUAZABfAFUAbgBpAHQAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBrAGcAIABDAEgANAAgAC8AIABHAEoAXAAiACkAKQA7AFwAbgBcAG4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAQgBpAG8AZwBhAHMARgBsAGEAcgBlAGQAXwBTAG8AdQByAGMAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADEAMQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0AHMAXAAiACkAKQA7AFwAbgBcAG4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAQgBpAG8AZwBhAHMARgBsAGEAcgBlAGQAXwBEAGEAdABhAFwAbgA9AEwAQQBNAEIARABBACgAMAAuADIAMgA4ADkAKQA7AFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgBXAGEAcwB0AGUAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAQgBpAG8AZwBhAHMARgBsAGEAcgBlAGQAXwBUAGkAdABsAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHMAbAB1AGQAZwBlACAAYgBpAG8AZwBhAHMAIABmAGwAYQByAGUAZABcACIAKQApADsAXABuAFwAbgBXAGEAcwB0AGUAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAQgBpAG8AZwBhAHMARgBsAGEAcgBlAGQAXwBWAGEAcgBpAGEAYgBsAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBFAEYAZgBsAGEAcgBlAGQALABOADIATwBcACIAKQApADsAXABuAFwAbgBXAGEAcwB0AGUAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAQgBpAG8AZwBhAHMARgBsAGEAcgBlAGQAXwBVAG4AaQB0AFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAawBnACAATgAyAE8AIAAvACAARwBKAFwAIgApACkAOwBcAG4AXABuAFcAYQBzAHQAZQBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBCAGkAbwBnAGEAcwBGAGwAYQByAGUAZABfAFMAbwB1AHIAYwBlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAMQAxAC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAcwBcACIAKQApADsAXABuAFwAbgBXAGEAcwB0AGUAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAQgBpAG8AZwBhAHMARgBsAGEAcgBlAGQAXwBEAGEAdABhAFwAbgA9AEwAQQBNAEIARABBACgAMQAuADEAMwAyAGUALQA0ACkAOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAGEAcwB0AGUAdwBhAHQAZQByAF8ATgAyAE8AXwBFAHEAdQBhAHQAaQBvAG4AcwAiACwAIgB0AGUAeAB0ACIAOgAiAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AMQAxAC4AMQA6ACAAVwBhAHMAdABlAHcAYQB0AGUAcgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AMQAxAC4AMQAuADMALgAxACAATQBlAHQAaABvAGQAIAAxACAALQAgAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABvAG4AcwBpAHQAZQAgAFcAYQBzAHQAZQB3AGEAdABlAHIAIABNAGEAbgBhAGcAZQBtAGUAbgB0AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8AMQAxAF8AMQBfADMAXwAxAF8AXwAxAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBGAGwAYQByAGUAZABCAGkAbwBnAGEAcwBcAG4ATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAGYAbABhAHIAZQBkACAAYgBpAG8AZwBhAHMAXABuAEUAXwBOADIATwBcAG4AdAAgAE4AMgBPAFwAbgBFAF8AewBOADIATwB9AD0AXABcAGYAcgBhAGMAewBRAF8AewBmAGwAYQByAGUAZAB9AH0AewAxADAAMAAwAH0AXABcAHQAaQBtAGUAcwAgAEUARgBfAHsAZgBsAGEAcgBlAGQALABOADIATwB9AFwAbgBRAF8AZgBsAGEAcgBlAGQAIAA9ACAAdgBvAGwAdQBtAGUAIABvAGYAIABiAGkAbwBnAGEAcwAgAGYAbABhAHIAZQBkACAAKABtADMAIABvAHIAIABHAEoAKQBcAG4ARQBGAF8AZgBsAGEAcgBlAGQAXwBOADIATwAgAD0AIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAGYAbABhAHIAZQBkACAAYgBpAG8AZwBhAHMAIAAoAGsAZwAgAE4AMgBPAC8ARwBKACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8AMQAxAF8AMQBfADMAXwAxAF8AXwAxAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBGAGwAYQByAGUAZABCAGkAbwBnAGEAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABRAF8AZgBsAGEAcgBlAGQALAAgAEUAQwBfAGYAbABhAHIAZQBkACwAIABFAEYAXwBmAGwAYQByAGUAZABOADIATwAsAFwAbgAgACAAIAAgACgAUQBfAGYAbABhAHIAZQBkACAALwAgADEAMAAwADAAKQAgACoAIAAoAEUAQwBfAGYAbABhAHIAZQBkACAAKgAgAEUARgBfAGYAbABhAHIAZQBkAE4AMgBPACkAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADEAXwAxAF8AMwBfADEAXwBfADEAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEYAbABhAHIAZQBkAEIAaQBvAGcAYQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAZgBsAGEAcgBlAGQAIABiAGkAbwBnAGEAcwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQAxAF8AMQBfADMAXwAxAF8AXwAxAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBGAGwAYQByAGUAZABCAGkAbwBnAGEAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBfAE4AMgBPAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADEAXwAxAF8AMwBfADEAXwBfADEAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEYAbABhAHIAZQBkAEIAaQBvAGcAYQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAE4AMgBPAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADEAXwAxAF8AMwBfADEAXwBfADEAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEYAbABhAHIAZQBkAEIAaQBvAGcAYQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADEAMQAuADEALgAzAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAxACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEAMQBfADEAXwAzAF8AMQBfAF8AMQBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ARgBsAGEAcgBlAGQAQgBpAG8AZwBhAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEAMQBfADEAXwAzAF8AMQBfAF8AMQBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ARgBsAGEAcgBlAGQAQgBpAG8AZwBhAHMAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAF8AewBOADIATwB9AD0AXABcAGYAcgBhAGMAewBRAF8AewBmAGwAYQByAGUAZAB9AH0AewAxADAAMAAwAH0AXABcAHQAaQBtAGUAcwAgAFwAXABsAGUAZgB0AFsARQBDAF8AewBmAGwAYQByAGUAZAB9ACAAXABcAHQAaQBtAGUAcwAgAEUARgBfAHsAZgBsAGEAcgBlAGQALABOADIATwB9AFwAXAByAGkAZwBoAHQAXQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQAxAF8AMQBfADMAXwAxAF8AXwAxAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBGAGwAYQByAGUAZABCAGkAbwBnAGEAcwBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAANAAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBRAF8AZgBsAGEAcgBlAGQAXAAiACwAIABcACIAdgBvAGwAdQBtAGUAIABvAGYAIABiAGkAbwBnAGEAcwAgAGYAbABhAHIAZQBkAFwAIgAsACAAXAAiAG0AMwBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUAQwBfAGYAbABhAHIAZQBkAFwAIgAsACAAXAAiAGUAbgBlAHIAZwB5ACAAYwBvAG4AdABlAG4AdAAgAGYAYQBjAHQAbwByACAAbwBmACAAcwBsAHUAZABnAGUAIABiAGkAbwBnAGEAcwAgAGYAbABhAHIAZQBkAFwAIgAsACAAXAAiAEcASgAvAG0AMwBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARgBfAGYAbABhAHIAZQBkAE4AMgBPAFwAIgAsACAAXAAiAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAZgBsAGEAcgBlAGQAIABiAGkAbwBnAGEAcwBcACIALAAgAFwAIgBrAGcAIABOADIATwAvAEcASgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuACIAfQBdACwAIgBwAHIAbwBqAGUAYwB0AE4AYQBtAGUAcwAiADoAWwAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBBAHAAcABlAG4AZABpAGMAZQBzACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAFIAbwB3AFMAdABhAHIAdABOAHUAbQBiAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAEMAbwBsAHUAbQBuAFMAdABhAHIAdABOAHUAbQBiAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgByAGEAeQBJAG4AVABhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAFQAdwBvAEMAbwBsAHUAbQBuAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATwBuAGUAQwBvAGwAdQBtAG4AQQBuAGQASABlAGEAZABlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AUwBwAGwAaQB0AFMAdAByAGkAbgBnAEkAbgB0AG8AQQByAHIAYQB5ACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEMAbABpAG0AYQB0AGUAWgBvAG4AZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABJAHQAZQBtAEYAcgBvAG0ATQBpAG4ATQBhAHgAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AUwB1AG0AUQB1AGEAbgB0AGkAdAB5AEYAcgBvAG0AQwByAGkAdABlAHIAaQBhACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBzACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAFAAZQByAGkAbwBkAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBGAHUAbgBjAHQAaQBvAG4ATgBhAG0AZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABOADIATwBFAEYARgByAG8AbQBQAHIAbwBkAEkAcgByAGkAZwBhAHQAaQBvAG4AUgBhAGkAbgBmAGEAbABsACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ARwBlAHQARgByAGEAYwBXAEUAVAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBDAG8AbgB2AGUAcgB0AFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAFQAbwBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQAxAF8AMQBfADEAXwAxAF8AXwAxAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFcAYQBzAHQAZQB3AGEAdABlAHIAVAByAGUAYQB0AG0AZQBuAHQAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEAMQBfADEAXwAxAF8AMQBfAF8AMQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBXAGEAcwB0AGUAdwBhAHQAZQByAFQAcgBlAGEAdABtAGUAbgB0AF8AVABpAHQAbABlACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADEAXwAxAF8AMQBfADEAXwBfADEAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AVwBhAHMAdABlAHcAYQB0AGUAcgBUAHIAZQBhAHQAbQBlAG4AdABfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQAxAF8AMQBfADEAXwAxAF8AXwAxAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFcAYQBzAHQAZQB3AGEAdABlAHIAVAByAGUAYQB0AG0AZQBuAHQAXwBVAG4AaQB0ACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADEAXwAxAF8AMQBfADEAXwBfADEAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AVwBhAHMAdABlAHcAYQB0AGUAcgBUAHIAZQBhAHQAbQBlAG4AdABfAFMAbwB1AHIAYwBlACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADEAXwAxAF8AMQBfADEAXwBfADEAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AVwBhAHMAdABlAHcAYQB0AGUAcgBUAHIAZQBhAHQAbQBlAG4AdABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADEAXwAxAF8AMQBfADEAXwBfADEAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AVwBhAHMAdABlAHcAYQB0AGUAcgBUAHIAZQBhAHQAbQBlAG4AdABfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEAMQBfADEAXwAxAF8AMQBfAF8AMQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBXAGEAcwB0AGUAdwBhAHQAZQByAFQAcgBlAGEAdABtAGUAbgB0AF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEAMQBfADEAXwAxAF8AMQBfAF8AMQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBXAGEAcwB0AGUAdwBhAHQAZQByAFQAcgBlAGEAdABtAGUAbgB0AF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEMAbwByAHIAZQBjAHQAaQBvAG4ARgBhAGMAdABvAHIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFQAaQB0AGwAZQAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUAQwBvAHIAcgBlAGMAdABpAG8AbgBGAGEAYwB0AG8AcgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBDAG8AcgByAGUAYwB0AGkAbwBuAEYAYQBjAHQAbwByAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBVAG4AaQB0ACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBDAG8AcgByAGUAYwB0AGkAbwBuAEYAYQBjAHQAbwByAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBTAG8AdQByAGMAZQAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUAQwBvAHIAcgBlAGMAdABpAG8AbgBGAGEAYwB0AG8AcgBXAGEAcwB0AGUAdwBhAHQAZQByAF8ARABhAHQAYQAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUAQwBvAHIAcgBlAGMAdABpAG8AbgBGAGEAYwB0AG8AcgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEMAbwByAHIAZQBjAHQAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAXwBUAGkAdABsAGUAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEMAbwByAHIAZQBjAHQAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEMAbwByAHIAZQBjAHQAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAXwBVAG4AaQB0ACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBDAG8AcgByAGUAYwB0AGkAbwBuAEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAF8AUwBvAHUAcgBjAGUAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEMAbwByAHIAZQBjAHQAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAXwBEAGEAdABhACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBDAG8AcgByAGUAYwB0AGkAbwBuAEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AVABpAHQAbABlACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBVAG4AaQB0ACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAEQAYQB0AGEAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBfAFQAaQB0AGwAZQAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAXwBVAG4AaQB0ACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAXwBTAG8AdQByAGMAZQAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAF8ARABhAHQAYQAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFcAYQBzAHQAZQBfAEUAbgBlAHIAZwB5AEMAbwBuAHQAZQBuAHQARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAQgBpAG8AZwBhAHMARgBsAGEAcgBlAGQAXwBUAGkAdABsAGUAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBXAGEAcwB0AGUAXwBFAG4AZQByAGcAeQBDAG8AbgB0AGUAbgB0AEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAEIAaQBvAGcAYQBzAEYAbABhAHIAZQBkAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AVwBhAHMAdABlAF8ARQBuAGUAcgBnAHkAQwBvAG4AdABlAG4AdABGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBCAGkAbwBnAGEAcwBGAGwAYQByAGUAZABfAFUAbgBpAHQAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBXAGEAcwB0AGUAXwBFAG4AZQByAGcAeQBDAG8AbgB0AGUAbgB0AEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAEIAaQBvAGcAYQBzAEYAbABhAHIAZQBkAF8AUwBvAHUAcgBjAGUAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBXAGEAcwB0AGUAXwBFAG4AZQByAGcAeQBDAG8AbgB0AGUAbgB0AEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAEIAaQBvAGcAYQBzAEYAbABhAHIAZQBkAF8ARABhAHQAYQAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAEIAaQBvAGcAYQBzAEYAbABhAHIAZQBkAF8AVABpAHQAbABlACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAQgBpAG8AZwBhAHMARgBsAGEAcgBlAGQAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBCAGkAbwBnAGEAcwBGAGwAYQByAGUAZABfAFUAbgBpAHQAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBCAGkAbwBnAGEAcwBGAGwAYQByAGUAZABfAFMAbwB1AHIAYwBlACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAQgBpAG8AZwBhAHMARgBsAGEAcgBlAGQAXwBEAGEAdABhACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AVwBhAHMAdABlAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAEIAaQBvAGcAYQBzAEYAbABhAHIAZQBkAF8AVABpAHQAbABlACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AVwBhAHMAdABlAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAEIAaQBvAGcAYQBzAEYAbABhAHIAZQBkAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AVwBhAHMAdABlAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAEIAaQBvAGcAYQBzAEYAbABhAHIAZQBkAF8AVQBuAGkAdAAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFcAYQBzAHQAZQBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBCAGkAbwBnAGEAcwBGAGwAYQByAGUAZABfAFMAbwB1AHIAYwBlACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AVwBhAHMAdABlAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAEIAaQBvAGcAYQBzAEYAbABhAHIAZQBkAF8ARABhAHQAYQAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8ATgAyAE8AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEAMQBfADEAXwAzAF8AMQBfAF8AMQBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ARgBsAGEAcgBlAGQAQgBpAG8AZwBhAHMAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAE4AMgBPAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADEAXwAxAF8AMwBfADEAXwBfADEAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEYAbABhAHIAZQBkAEIAaQBvAGcAYQBzAF8AVABpAHQAbABlACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBOADIATwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQAxAF8AMQBfADMAXwAxAF8AXwAxAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBGAGwAYQByAGUAZABCAGkAbwBnAGEAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8ATgAyAE8AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEAMQBfADEAXwAzAF8AMQBfAF8AMQBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ARgBsAGEAcgBlAGQAQgBpAG8AZwBhAHMAXwBVAG4AaQB0ACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBOADIATwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQAxAF8AMQBfADMAXwAxAF8AXwAxAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBGAGwAYQByAGUAZABCAGkAbwBnAGEAcwBfAFMAbwB1AHIAYwBlACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBOADIATwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQAxAF8AMQBfADMAXwAxAF8AXwAxAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBGAGwAYQByAGUAZABCAGkAbwBnAGEAcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBOADIATwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQAxAF8AMQBfADMAXwAxAF8AXwAxAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBGAGwAYQByAGUAZABCAGkAbwBnAGEAcwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAE4AMgBPAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADEAXwAxAF8AMwBfADEAXwBfADEAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEYAbABhAHIAZQBkAEIAaQBvAGcAYQBzAF8AQQByAGcAdQBtAGUAbgB0AHMAIgBdACwAIgBsAG8AYwBhAGwAZQAiADoAewAiAGwAaQBzAHQAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgByAG8AdwBTAGUAcABhAHIAYQB0AG8AcgAiADoAIgA7ACIALAAiAGMAbwBsAHUAbQBuAFMAZQBwAGEAcgBhAHQAbwByACIAOgAiACwAIgAsACIAdABoAG8AdQBzAGEAbgBkAHMAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgB0AGgAbwB1AHMAYQBuAGQAcwBQAG8AcwBpAHQAaQBvAG4AcwAiADoAWwAzAF0ALAAiAGQAZQBjAGkAbQBhAGwAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALgAiACwAIgBkAGEAdABlAE8AcgBkAGUAcgAiADoAIgBEAE0AWQAiACwAIgBjAHUAcgByAGUAbgBjAHkAUwB5AG0AYgBvAGwAIgA6ACIAJAAiACwAIgBpAHMAQwB1AHIAcgBlAG4AYwB5AFMAeQBtAGIAbwBsAEwAZQBhAGQAIgA6AHQAcgB1AGUALAAiAGkAcwBDAHUAcgByAGUAbgBjAHkAUwBlAHAAQgB5AFMAcABhAGMAZQAiADoAZgBhAGwAcwBlACwAIgByAG8AdwBMAGUAdAB0AGUAcgAiADoAIgBSACIALAAiAGMAbwBsAHUAbQBuAEwAZQB0AHQAZQByACIAOgAiAEMAIgAsACIAcgBjAEwAZQBmAHQAQgByAGEAYwBrAGUAdAAiADoAIgBbACIALAAiAHIAYwBSAGkAZwBoAHQAQgByAGEAYwBrAGUAdAAiADoAIgBdACIALAAiAHMAdABhAHQAZQBtAGUAbgB0AFMAZQBwAGEAcgBhAHQAbwByACIAOgAiADsAIgAsACIAbABvAGMAYQBsAGUATgBhAG0AZQAiADoAIgBlAG4ALQB1AHMAIgB9AH0A</AFEJSONBlob>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD460F9D-420A-4723-B323-396E4D19EC9B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="09eef6d6-daa8-4301-8f9f-b1ec38079286"/>
+    <ds:schemaRef ds:uri="7291119c-fce9-4911-96ae-b800be5dccd8"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9A9CF321-0D35-4044-BC72-33748FE2B865}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{809E3D44-A88D-4EBF-A307-6B8CE77A3361}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -13995,25 +14014,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9A9CF321-0D35-4044-BC72-33748FE2B865}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD460F9D-420A-4723-B323-396E4D19EC9B}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="09eef6d6-daa8-4301-8f9f-b1ec38079286"/>
-    <ds:schemaRef ds:uri="7291119c-fce9-4911-96ae-b800be5dccd8"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6BE249C-20B1-4A62-BBCD-F2A46D88BCAB}">
   <ds:schemaRefs>

--- a/Excel/11_Wastewater_WIP_v02.xlsx
+++ b/Excel/11_Wastewater_WIP_v02.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\htdocs\zneagcrc\GAF-VEERG-Functions\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F84FDF4-8C41-443A-B5C4-709AB3E97C0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB2C339C-F995-4455-B4BE-0A75E09419A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="12645" activeTab="2" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
+    <workbookView xWindow="1350" yWindow="360" windowWidth="36255" windowHeight="19140" activeTab="2" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
   </bookViews>
   <sheets>
     <sheet name="Home" sheetId="71" r:id="rId1"/>
@@ -178,6 +178,7 @@
     <definedName name="Common_SourceData.Common_SourceData_WetAndDryZones_Unit">_xlfn.LAMBDA("")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_WetAndDryZones_Variable">_xlfn.LAMBDA("")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_WetAndDryZones_Variation">_xlfn.LAMBDA(_xlfn.MAKEARRAY(3, 1, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"VARIATION OF SOURCE DATA:";"Added warm / cool temperate moist / dry - low frost and high temp classes to accommodate climate scenarios excluded by VEERG criteria.";"Fixed typo - Changed 'Fry' to 'Dry'."}, _xlpm.r, _xlpm.c))))</definedName>
+    <definedName name="Common_SourceData_DensityOfMethane_Data">'Constants - Common'!$D$175</definedName>
     <definedName name="CommonCropping_SourceData.CommonCropping_SourceData_FracGASFfInorganicFertiliser_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(6, 3, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Fertiliser type f","FracGASFf","Basis";"Urea-based fertilisers",0.15,"Urea";"Ammonium-based fertilisers",0.08,"Ammonium";"Nitrate-based fertilisers",0.01,"Nitrate";"Ammonium-nitrate based fertilisers",0.05,"Ammonium-nitrate";"Other fertilisers",0.11,"Other"}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="CommonCropping_SourceData.CommonCropping_SourceData_FracGASFfInorganicFertiliser_NIRReference">_xlfn.LAMBDA("IPCC 2019 Refinement Volume 4 Table 11.3 [1, p. 11]")</definedName>
     <definedName name="CommonCropping_SourceData.CommonCropping_SourceData_FracGASFfInorganicFertiliser_Source">_xlfn.LAMBDA("VEERG 2026:Table 12.2.2.9")</definedName>
@@ -13758,6 +13759,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="09eef6d6-daa8-4301-8f9f-b1ec38079286" xsi:nil="true"/>
@@ -13768,16 +13778,11 @@
 </p:properties>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgAvAC8AIAAtAC0ALQAgAFcAbwByAGsAYgBvAG8AawAgAG0AbwBkAHUAbABlACAALQAtAC0AXABuAC8ALwAgAEEAIABmAGkAbABlACAAbwBmACAAbgBhAG0AZQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAG8AZgAgAHQAaABlACAAZgBvAHIAbQA6AFwAbgAvAC8AIAAgACAAIABuAGEAbQBlACAAPQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AOwBcAG4AXABuACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhACIALAAiAHQAZQB4AHQAIgA6ACIALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgBTAG8AdQByAGMAZQAgAGQAYQB0AGEAIAB0AGgAYQB0ACAAaQBzACAAYwBvAG0AbQBvAG4AIABhAGMAcgBvAHMAcwAgAGEAbABsACAAZQBuAHQAZQByAHAAcgBpAHMAZQAgAHQAeQBwAGUAcwBcAG4ARQB4AGMAZQBsACAAbQBvAGQAdQBsAGUAIABuAGEAbQBlADoAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFMAbwB1AHIAYwBlADoAIABOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQBcAG4ATgBJAFIAXwAyADAAMgAzAF8AVgBvAGwAMQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXABuAHAAIAA9ACAAZABlAG4AcwBpAHQAeQAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAIAAoADAALgA2ADcAOAA0ACAAawBnAC8AbQAzACkAXABuAFQAYQBrAGUAbgAgAGYAcgBvAG0AIAB0AGgAZQAgAE4AYQB0AGkAbwBuAGEAbAAgAEcAcgBlAGUAbgBoAG8AdQBzAGUAIABhAG4AZAAgAEUAbgBlAHIAZwB5ACAAUgBlAHAAbwByAHQAaQBuAGcAIABcAG4AKABNAGUAYQBzAHUAcgBlAG0AZQBuAHQAKQAgAEQAZQB0AGUAcgBtAGkAbgBhAHQAaQBvAG4AIAAyADAAMAA4AFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHAAIAA9ACAAZABlAG4AcwBpAHQAeQAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcALwBtADMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgADIAMAAyADMAIABWAG8AbAB1AG0AZQAgADEAOgAgAEUAcQB1AGEAdABpAG8AbgBzACAAMwAuAEIALgAxAGEAXwAyACwAIAAzAC4AQgAuADEAYwBfADIALAAgADMALgBCAC4AMwBfADEALAAgADMALgBCAC4ANABnAF8AMgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAMAAuADYANwA4ADQAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAFwAbgBDAGcAIAA9ACAANAA0AC8AMgA4ACAAZgBhAGMAdABvAHIAIAB0AG8AIABjAG8AbgB2AGUAcgB0ACAAZQBsAGUAbQBlAG4AdABhAGwAIABtAGEAcwBzACAAbwBmACAATgAyAE8AIAB0AG8AIABtAG8AbABlAGMAdQBsAGEAcgAgAG0AYQBzAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABOADIATwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBDAGcATgAyAE8AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAYQBjAHQAbwByAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgADIAMAAyADMAIABWAG8AbAB1AG0AZQAgADEAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgANAA0AC8AMgA4ACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAFwAbgBGAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABnAGEAcwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgBhAGMAdABvAHIAIAB0AG8AIABjAG8AbgB2AGUAcgB0ACAAZQBsAGUAbQBlAG4AdABhAGwAIABtAGEAcwBzACAAbwBmACAAZwBhAHMAIAB0AG8AIABtAG8AbABlAGMAdQBsAGEAcgAgAG0AYQBzAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBDAGcAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgBhAGMAdABvAHIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFgAWABYAFgAWABYAFgAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADgALAAgADQALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAYQBzAFwAIgAsACAAXAAiAEMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBcACIALAAgAFwAIgBDAG8AbgB2AGUAcgBzAGkAbwBuACAAZgBhAGMAdABvAHIAIAAxAFwAIgAsACAAXAAiAEMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgADIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyAFwAIgAsACAAXAAiADQANAAvADEAMgBcACIALAAgADQANAAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMASAA0AFwAIgAsACAAXAAiADEANgAvADEAMgBcACIALAAgADEANgAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AMgBPAFwAIgAsACAAXAAiADQANAAvADIAOABcACIALAAgADQANAAsACAAMgA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB4AFwAIgAsACAAXAAiADQANgAvADEANABcACIALAAgADQANgAsACAAMQA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwBcACIALAAgAFwAIgAyADgALwAxADIAXAAiACwAIAAyADgALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAE8AMgAgAEwAaQBtAGUAXAAiACwAIABcACIANAA0AC8AMQAyAFwAIgAsACAANAA0ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBNAFYATwBDAFwAIgAsACAAXAAiADEANAAvADEAMgBcACIALAAgADEANAAsACAAMQAyAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABOADIATwBcAG4ARwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAGcAcgBlAGUAbgBoAG8AdQBzAGUAIABnAGEAcwBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABnAHIAZQBlAG4AaABvAHUAcwBlACAAZwBhAHMAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARwBXAFAATgAyAE8AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgBhAGMAdABvAHIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFgAWABYAFgAWABYAFgAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADgALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAYQBzAFwAIgAsACAAXAAiAEMATwAyAC0AZQAgAGYAYQBjAHQAbwByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAE8AMgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBIADQAXAAiACwAIAAyADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgAyAE8AXAAiACwAIAAyADYANQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAEYANABcACIALAAgADYANgAzADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwAyAEYANgBcACIALAAgADEAMgAyADAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAEYANgBcACIALAAgADIAMgA4ADAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAEYAMwBcACIALAAgADEANwAyADAAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAcwB0AGEAdABlAHMAIABhAG4AZAAgAHQAZQByAHIAaQB0AG8AcgBpAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA5ACwAIAAzACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHQAYQB0AGUALwBUAGUAcgByAGkAdABvAHIAeQBcACIALAAgAFwAIgBDAG8AbQBtAG8AbgAgAE4AYQBtAGUAXAAiACwAIABcACIAQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AZQB3ACAAUwBvAHUAdABoACAAVwBhAGwAZQBzAFwAIgAsACAAXAAiAE4AZQB3ACAAUwBvAHUAdABoACAAVwBhAGwAZQBzAFwAIgAsACAAXAAiAE4AUwBXAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAQwBhAHAAaQB0AGEAbAAgAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAEEAQwBUAFwAIgAsACAAXAAiAEEAQwBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAGkAYwB0AG8AcgBpAGEAXAAiACwAIABcACIAVgBpAGMAdABvAHIAaQBhAFwAIgAsACAAXAAiAFYASQBDAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBRAHUAZQBlAG4AcwBsAGEAbgBkAFwAIgAsACAAXAAiAFEAdQBlAGUAbgBzAGwAYQBuAGQAXAAiACwAIABcACIAUQBMAEQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAbwB1AHQAaAAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFMAbwB1AHQAaAAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFMAQQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQBcACIALAAgAFwAIgBXAEEAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAYQBzAG0AYQBuAGkAYQBcACIALAAgAFwAIgBUAGEAcwBtAGEAbgBpAGEAXAAiACwAIABcACIAVABBAFMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwByAHQAaABlAHIAbgAgAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAE4AbwByAHQAaABlAHIAbgAgAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAE4AVABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQBCAFMAIABTAHQAYQB0AGkAcwB0AGMAYQBsACAAQQByAGUAYQBzACAATABlAHYAZQBsACAANAAgAC0AIABXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAEIAdQByAGUAYQB1ACAAbwBmACAAUwB0AGEAdABpAHMAdABpAGMAcwAgACgAQQBCAFMAKQAgAC0AIABTAHQAYQB0AGkAcwB0AGkAYwBhAGwAIABBAHIAZQBhAHMAIABMAGUAdgBlAGwAIAAyACAALQAgADIAMAAyADEAIAAtACAAUwBoAGEAcABlAGYAaQBsAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADEALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAQQAgADQAIABOAGEAbQBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBCAHUAbgBiAHUAcgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAGEAbgBkAHUAcgBhAGgAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABJAG4AbgBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABOAG8AcgB0AGgAIABFAGEAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAATgBvAHIAdABoACAAVwBlAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAFMAbwB1AHQAaAAgAEUAYQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABTAG8AdQB0AGgAIABXAGUAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAAVwBoAGUAYQB0ACAAQgBlAGwAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhACAALQAgAE8AdQB0AGIAYQBjAGsAIAAoAE4AbwByAHQAaAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAATwB1AHQAYgBhAGMAawAgACgAUwBvAHUAdABoACkAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAdwBlAHQAIABhAG4AZAAgAGQAcgB5ACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAyADoAIABUAHIAYQBuAHMAbABhAHQAaQBuAGcAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBzACAAdABvACAAdwBlAHQAIABhAG4AZAAgAGQAcgB5ACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAdwBhAHIAbQAgAC8AIABjAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAvACAAZAByAHkAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAIABhAG4AZAAgAGgAaQBnAGgAIAB0AGUAbQBwACAAYwBsAGEAcwBzAGUAcwAgAHQAbwAgAGEAYwBjAG8AbQBtAG8AZABhAHQAZQAgAGMAbABpAG0AYQB0AGUAIABzAGMAZQBuAGEAcgBpAG8AcwAgAGUAeABjAGwAdQBkAGUAZAAgAGIAeQAgAFYARQBFAFIARwAgAGMAcgBpAHQAZQByAGkAYQAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAGkAeABlAGQAIAB0AHkAcABvACAALQAgAEMAaABhAG4AZwBlAGQAIABcAHUAMAAwADIANwBGAHIAeQBcAHUAMAAwADIANwAgAHQAbwAgAFwAdQAwADAAMgA3AEQAcgB5AFwAdQAwADAAMgA3AC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADUALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAFcAZQB0ACAAbwByACAARAByAHkAIABaAG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABtAG8AbgB0AGEAbgBlAFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAHcAZQB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABkAHIAeQBcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdABcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAtACAAaABpAGcAaAAgAHQAZQBtAHAAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAaABpAGcAaAAgAHQAZQBtAHAAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA1ACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAB3AGEAcgBtACAALwAgAGMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC8AIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdAAgAGEAbgBkACAAaABpAGcAaAAgAHQAZQBtAHAAIABjAGwAYQBzAHMAZQBzACAAdABvACAAYQBjAGMAbwBtAG0AbwBkAGEAdABlACAAYwBsAGkAbQBhAHQAZQAgAHMAYwBlAG4AYQByAGkAbwBzACAAZQB4AGMAbAB1AGQAZQBkACAAYgB5ACAAVgBFAEUAUgBHACAAYwByAGkAdABlAHIAaQBhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAaQB4AGUAZAAgAHQAeQBwAG8AIABpAG4AIABNAEEAVAAgAHYAYQBsAHUAZQAgAGYAbwByACAAdwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAYwBoAGEAbgBnAGUAZAAgADEAMAAgAHQAbwAgADEAMQAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIABtAGkAbgAgAGEAbgBkACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAZgBvAHIAIABNAEEAVAAsACAATQBBAFAALAAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAIABwAGUAcgAgAHkAZQBhAHIALAAgAGUAbABlAHYAYQB0AGkAbwBuACwAIABNAEEAUAA6AFAARQBUACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlAHMAIABmAHIAbwBtACAAcgBlAGEAbAAgAGMAbABpAG0AYQB0AGUAIABkAGEAdABhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAQQBGACAAYQBjAGMAZQBwAHQAcwAgAHIAYQBpAG4AZgBhAGwAbAAgAGEAcwAgAGEAIABwAHIAbwB4AHkAIABmAG8AcgAgAHAAcgBlAGMAaQBwAGkAdABhAHQAaQBvAG4ALgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOQAsACAAMQA2ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAGwAaQBtAGEAdABlACAAWgBvAG4AZQBcACIALAAgAFwAIgBNAEEAVABcACIALAAgAFwAIgBNAEEAUABcACIALAAgAFwAIgBGAHIAbwBzAHQAIABkAGEAeQBzACAAcABlAHIAIAB5AGUAYQByAFwAIgAsACAAXAAiAEUAbABlAHYAYQB0AGkAbwBuAFwAIgAsACAAXAAiAE0AQQBQADoAUABFAFQAXAAiACwAIABcACIATQBpAG4AIAB0AGUAbQBwAFwAIgAsACAAXAAiAE0AYQB4ACAAdABlAG0AcABcACIALAAgAFwAIgBNAGkAbgAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBNAGEAeAAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBNAGkAbgAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAXAAiACwAIABcACIATQBhAHgAIABmAHIAbwBzAHQAIABkAGEAeQBzAFwAIgAsACAAXAAiAE0AaQBuACAAZQBsAGUAdgBhAHQAaQBvAG4AXAAiACwAIABcACIATQBhAHgAIABlAGwAZQB2AGEAdABpAG8AbgBcACIALAAgAFwAIgBNAGkAbgAgAE0AQQBQADoAUABFAFQAXAAiACwAIABcACIATQBpAG4AIABNAEEAUAA6AFAARQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABtAG8AbgB0AGEAbgBlAFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQA4ACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAwADAAIABtAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAMQA4AC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAANwAsACAAMQAwADAAMAAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAHcAZQB0AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQA4ACAAQwBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADIAMAAwADAAIABtAG0AXAAiACwAIABcACIAZCIgADcAXAAiACwAIABcACIAZCIgADEAMAAwADAAIABtAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAMQA4AC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAyADAAMAAwAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQAuADkAOQA5ACwAIAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAOAAgAEMAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADAAMAAwACAAbQBtACAALQAgAGQiIAAyADAAMAAwACAAbQBtAFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgADEAOAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAAMQAwADAAMAAuADAAMAAxACwAIAAyADAAMAAwACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQAuADkAOQA5ACwAIAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAGQAcgB5AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQA4ACAAQwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAwADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAXAAiACwAIAAxADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgADEALgAwADAAMQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAGQiIAAxAFwAIgAsACAAMQAwAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAgAC0AOQA5ADkAOQA5ADkALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMAAgAEMAIAAtACAAZCIgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxAFwAIgAsACAALQA5ADkAOQA5ADkAOQAsACAAMQAwACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAxAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMAAgAEMAIAAtACAAZCIgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAZCIgADEAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAMQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBBAHAAcABlAG4AZABpAGMAZQBzAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdABlADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AQQBUACAAPQAgAG0AZQBhAG4AIABhAG4AbgB1AGEAbAAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBBAFAAIAA9ACAAbQBlAGEAbgAgAGEAbgBuAHUAYQBsACAAcAByAGUAYwBpAHAAaQB0AGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABFAFQAIAA9ACAAcABvAHQAZQBuAHQAaQBhAGwAIABlAHYAYQBwAG8AdAByAGEAbgBzAHAAaQByAGEAdABpAG8AbgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABBAGQAZABlAGQAIABlAHgAdAByAGEAIABNAEEAVAAgAG0AaQBuACAAYQBuAGQAIABNAEEAVAAgAG0AYQB4ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGMAYQBsAGMAdQBsAGEAdABlACAAegBvAG4AZQAgAGYAcgBvAG0AIAByAGUAYQBsACAAdABlAG0AcABlAHIAYQB0AHUAcgBlACAAZABhAHQAYQAuAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANAAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AHUAcgBlACAAWgBvAG4AZQBcACIALAAgAFwAIgBNAGUAZABpAGEAbgAgAEEAbgBuAHUAYQBsACAAVABlAG0AcABlAHIAYQB0AHUAcgBlACAAKABNAEEAVAApAFwAIgAsACAAXAAiAE0AaQBuACAATQBBAFQAXAAiACwAIABcACIATQBhAHgAIABNAEEAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgAFwAIgBlIiAAMgA2ACAAQwBcACIALAAgADIANgAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIABcACIAMQA1ACAALQAgADIANQAgAEMAXAAiACwAIAAxADUALAAgADIANQAuADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIABcACIAZCIgADEANAAgAEMAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADQALgA5ADkAOQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAAQQBkAGQAZQBkACAAZQB4AHQAcgBhACAAUgBhAGkAbgBmAGEAbABsACAAbQBpAG4AIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAG0AYQB4ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGMAYQBsAGMAdQBsAGEAdABlACAAegBvAG4AZQAgAGYAcgBvAG0AIAByAGUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAZABhAHQAYQAuAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBhAGkAbgBmAGEAbABsACAAWgBvAG4AZQBcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABtAGkAbgBcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABtAGEAeABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbAAgAFwAdQAwADAAMwBlACAANgAwADAAbQBtAFwAIgAsACAANgAwADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATABvAHcAIAByAGEAaQBuAGYAYQBsAGwAXAAiACwAIABcACIAQQBuAG4AdQBhAGwAIAByAGEAaQBuAGYAYQBsAGwAIABkIiAANgAwADAAbQBtAFwAIgAsACAALQA5ADkAOQA5ADkAOQAsACAANgAwADAAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABaAG8AbgBlAFwAIgAsACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAGMAcgBpAHQAZQByAGkAYQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATABlAGEAYwBoAGkAbgBnACAAbwBjAGMAdQByAHMAXAAiACwAIABcACIAowMoADXYX9w12E7cNdhW3DXYW9wpAFwAdQAwADAAMwBlAKMDKAA12DjcNdhH3DAAKQArADXYYNw12FzcNdhW3DXYWdwgADXYZNw12E7cNdhh3DXYUtw12F/cIAAOITXYXNw12FncNdhR3DXYVtw12FvcNdhU3CAANdhQ3DXYTtw12F3cNdhO3DXYUNw12FbcNdhh3DXYZtxcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATABlAGEAYwBoAGkAbgBnACAAZABvAGUAcwAgAG4AbwB0ACAAbwBjAGMAdQByAFwAIgAsACAAXAAiAKMDKAA12F/cNdhO3DXYVtw12FvcKQBkIqMDKAA12DjcNdhH3DAAKQArADXYYNw12FzcNdhW3DXYWdwgADXYZNw12E7cNdhh3DXYUtw12F/cIAAOITXYXNw12FncNdhR3DXYVtw12FvcNdhU3CAANdhQ3DXYTtw12F3cNdhO3DXYUNw12FbcNdhh3DXYZtxcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXABuADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAbgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAEQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcwAgAGkAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAXAAiACwAXAAiAEYAcgBhAGMAVwBFAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFkAZQBzACAALQAgAGkAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwAgAC0AIABuAG8AdAAgAGkAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAXAAiACwAIAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoACgAXAAiAFwAIgApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAGQAYQB0AGEAIABzAGMAbwByAGUAcwAgAGYAbwByACAAcwBjAG8AcABlACAAMwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABYAFgAWABYAFgAWABYAFgAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABhAHQAYQAgAHMAbwB1AHIAYwBlAFwAIgAsACAAXAAiAEQAYQB0AGEAIABzAGMAbwByAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAbgB0AGUAcgBuAGEAdABpAG8AbgBhAGwAIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAcwBjAG8AcABlACAAMwAgAGQAYQB0AGEAYgBhAHMAZQBcACIALAAgADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB0AGEAdABlACAAbwByACAAcgBlAGcAaQBvAG4AYQBsACAAcwBjAG8AcABlACAAMwAgAGQAYQB0AGEAYgBhAHMAZQBcACIALAAgADMAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBtAGkAcwBzAGkAbwBuAHMAIABpAG4AdABlAG4AcwBpAHQAeQAgAGMAYQBsAGMAdQBsAGEAdABlAGQAIABmAHIAbwBtACAAYQBwAHAAcgBvAHYAZQBkACAAbQBlAHQAaABvAGQAXAAiACwAIAA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAZQByAGkAZgBpAGUAZAAgAGMAcgBlAGQAZQBuAHQAaQBhAGwAIABtAGEAdABjAGgAaQBuAGcAIABJAFMATwAxADQAMAA2ADcAXAAiACwAIAA1AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXABuADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAbgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgARABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAVgBvAGwAdQBtAGUAIAAxADoAIABMAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmACAAKAAzAC4ARAAuAGIALgAyACkAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAcgBhAGMATABFAEEAQwBIAFwAIgAsADAALgAyADQAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoACgAXAAiAFwAIgApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABuAGkAdAByAG8AZwBlAG4AIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABuAGkAdAByAG8AZwBlAG4AIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABrAGcAIABOADIATwAtAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgAFYAbwBsAHUAbQBlACAAMQA6ACAARQBxAHUAYQB0AGkAbwBuACAAMwAuAEQALgBCAF8AMQAwAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARgBsAGUAYQBjAGgAXAAiACwAMAAuADAAMQAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoACgAXAAiAFwAIgApACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXABuAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADEAXABuAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAZgBvAHIAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AIAAoAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AKQAgACgARQBGAE4AMgBPACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAGYAbwByACAAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAGsAZwAgAE4AMgBPAC0ATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADIALgAyAC4AMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQA1ACwAIAA1ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABqAFwAIgAsAFwAIgBFAEYATgAyAE8AXAAiACwAIABcACIAUAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAbwBuAGwAeQBcACIALAAgAFwAIgBJAHIAcgBpAGcAYQB0AGkAbwBuACAAbQBlAHQAaABvAGQAXAAiACwAIABcACIAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsADAALgAwADAANQA5ACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwAFwAIgAsADAALgAwADAANwAsACAAXAAiAEMAcgBvAHAAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsADAALgAwADAAMQA4ACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEwAbwB3ACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQBcACIALAAwAC4AMAAwADEAOAAsACAAXAAiAFAAYQBzAHQAdQByAGUAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcAAgACgAbABvAHcAIAByAGEAaQBuAGYAYQBsAGwAKQBcACIALAAwAC4AMAAwADIAOQAsACAAXAAiAEMAcgBvAHAAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAGMAcgBvAHAAIAAoAGgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAKQBcACIALAAwAC4AMAAwADgALAAgAFwAIgBDAHIAbwBwAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIASABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB1AGcAYQByAFwAIgAsADAALgAwADEAOQA5ACwAIABcACIAUwB1AGcAYQByAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AdAB0AG8AbgBcACIALAAwAC4AMAAwADUAMwAsACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAG8AcgB0AGkAYwB1AGwAdAB1AHIAYQBsACAAYwByAG8AcABzAFwAIgAsADAALgAwADAANgA0ACwAIABcACIASABvAHIAdABpAGMAdQBsAHQAdQByAGEAbAAgAGMAcgBvAHAAcwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBpAGMAZQAgACgAYwBvAG4AdABpAG4AdQBvAHUAcwAgAGYAbABvAG8AZABpAG4AZwApAFwAIgAsADAALgAwADAAMwAsACAAXAAiAFIAaQBjAGUAXAAiACwAIABcACIAQwBvAG4AdABpAG4AdQBvAHUAcwAgAGYAbABvAG8AZABpAG4AZwBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBpAGMAZQAgACgAcwBpAG4AZwBsAGUAIABhAG4AZAAgAG0AdQBsAHQAaQBwAGwAZQAgAGQAcgBhAGkAbgBhAGcAZQAsACAAbwByACAAYQBsAHQAZQByAG4AYQB0AGUAIAB3AGUAdAB0AGkAbgBnACAAYQBuAGQAIABkAHIAeQBpAG4AZwApAFwAIgAsADAALgAwADAANQAsACAAXAAiAFIAaQBjAGUAXAAiACwAIABcACIAUwBpAG4AZwBsAGUAIABhAG4AZAAgAG0AdQBsAHQAaQBwAGwAZQAgAGQAcgBhAGkAbgBhAGcAZQAsACAAbwByACAAYQBsAHQAZQByAG4AYQB0AGUAIAB3AGUAdAB0AGkAbgBnACAAYQBuAGQAIABkAHIAeQBpAG4AZwBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBxAHUAYQBjAHUAbAB0AHUAcgBlAFwAIgAsADAALgAwADAAMgA2ACwAIABcACIAQQBxAHUAYQBjAHUAbAB0AHUAcgBlAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAG8AcgBlAHMAdAByAHkAXAAiACwAMAAuADAAMAAxADgALAAgAFwAIgBGAG8AcgBlAHMAdAByAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA1ACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGUAbQBvAHYAZQBkACAAZAB1AHAAbABpAGMAYQB0AGUAIABcAHUAMAAwADIANwBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAB1ADAAMAAyADcAIAByAG8AdwAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGUAbQBvAHYAZQBkACAAYQBzAHQAZQByAGkAcwBrAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAFwAdQAwADAAMgA3AHAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAG8AbgBsAHkAXAB1ADAAMAAyADcALAAgAFwAdQAwADAAMgA3AHIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAXAB1ADAAMAAyADcAIABhAG4AZAAgAFwAdQAwADAAMgA3AGkAcgByAGkAZwBhAHQAaQBvAG4AIABtAGUAdABoAG8AZABcAHUAMAAwADIANwAgAGMAbwBsAHUAbQBuAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAdQBwAGwAaQBjAGEAdABlAGQAIABcAHUAMAAwADIANwBuAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQBcAHUAMAAwADIANwAgAHIAbwB3ACAAdwBpAHQAaAAgAHMAYQBtAGUAIABFAEYAIABmAG8AcgAgAGwAbwB3ACAAYQBuAGQAIABoAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAFwAbgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABDAGgAYQBwAHQAZQByACAAMQAsACAAcwBlAGMAdABpAG8AbgAgADEALgA4AC4AMgAgAEwAZQBhAGMAaABpAG4AZwAsACAAYwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBzAFwAbgBJAFAAQwBDADoAIABOADIATwAgAEUATQBJAFMAUwBJAE8ATgBTACAARgBSAE8ATQAgAE0AQQBOAEEARwBFAEQAIABTAE8ASQBMAFMALAAgAEEATgBEACAAQwBPADIAIABFAE0ASQBTAFMASQBPAE4AUwAgAEYAUgBPAE0AIABMAEkATQBFACAAQQBOAEQAIABVAFIARQBBACAAQQBQAFAATABJAEMAQQBUAEkATwBOAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwBXAEUAVAAgAGYAbwByACAAaQByAHIAaQBnAGEAdABpAG8AbgAgAHQAeQBwAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAEMAaABhAHAAdABlAHIAIAAxACwAIABzAGUAYwB0AGkAbwBuACAAMQAuADgALgAyACAATABlAGEAYwBoAGkAbgBnACwAIABjAGwAaQBtAGEAdABlACAAYQBuAGQAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBJAFAAQwBDACAAMgAwADEAOQAgAFIAZQBmAGkAbgBlAG0AZQBuAHQAIABWAG8AbAB1AG0AZQAgADQAOgAgAEMAaABhAHAAdABlAHIAIAAxADEAOgAgAE4AMgBPACAARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAATQBhAG4AYQBnAGUAZAAgAFMAbwBpAGwAcwAsACAAYQBuAGQAIABDAE8AMgAgAEUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAEwAaQBtAGUAIABhAG4AZAAgAFUAcgBlAGEAIABBAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGkAbwBuACAAdAB5AHAAZQAgAGkAcgBcACIALABcACIARgByAGEAYwBXAEUAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAByAGkAcAAgAGkAcgByAGkAZwBhAHQAaQBvAG4AXAAiACwAIAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAcAByAGkAbgBrAGwAZQByACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB1AHIAZgBhAGMAZQAgAGkAcgByAGkAZwBhAHQAaQBvAG4AXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AdABoAGUAcgAgAGkAcgByAGkAZwBhAHQAaQBvAG4AXAAiACwAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAARgBSAE8ATQAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAAVABhAGIAbABlACAAYwByAGUAYQB0AGUAZAAgAGIAYQBzAGUAZAAgAG8AbgAgAFYARQBFAFIARwAgAHQAZQB4AHQAIABcAHUAMAAwADIANwBBAHIAZQBhAHMAIABhAHIAZQAgAHMAdQBiAGoAZQBjAHQAIAB0AG8AIABsAGUAYQBjAGgAaQBuAGcAIAAoAGkALgBlAC4ALAAgAGkAbgAgAHQAaABlACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQApACAAdwBoAGUAbgAuAC4ALgAgAHQAaABlACAAbABhAG4AZAAgAGkAcwAgAGkAcgByAGkAZwBhAHQAZQBkACAAKABlAHgAYwBlAHAAdAAgAGQAcgBpAHAAIABpAHIAcgBpAGcAYQB0AGkAbwBuACkALgBcAHUAMAAwADIANwBcACIAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAFwAbgBUAGEAYgBsAGUAIABBAC4AMgAuADIALgAyADoAIABFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAdQByAGkAbgBlACAAYQBuAGQAIABkAHUAbgBnACAAZABlAHAAbwBzAGkAdABlAGQAIABvAG4AIABwAGEAcwB0AHUAcgBlACwAIAByAGEAbgBnAGUAIABvAHIAIABwAGEAZABkAG8AYwBrACAAKABrAGcAIABOADIATwAtAE4ALwBrAGcAIABOACkAIAAoAEUARgBQAFIAUAApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAdQByAGkAbgBlACAAYQBuAGQAIABkAHUAbgBnACAAZABlAHAAbwBzAGkAdABlAGQAIABvAG4AIABwAGEAcwB0AHUAcgBlACwAIAByAGEAbgBnAGUAIABvAHIAIABwAGEAZABkAG8AYwBrAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AMgBPACAALQAgAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADIALgAyAC4AMgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAEUARgBQAFIAUABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAAyAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABDAGgAYQBuAGcAZQBkACAAXAB1ADAAMAAyADcARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBzAFwAdQAwADAAMgA3ACAAdABvACAAcwBpAG4AZwB1AGwAYQByACAAXAB1ADAAMAAyADcARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcAHUAMAAwADIANwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAG8AbgB0AGgAcwAgAHQAbwAgAFMAZQBhAHMAbwBuAHMAIABNAGEAcABwAGkAbgBnAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBvAG4AdABoAFwAIgAsACAAXAAiAFMAZQBhAHMAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAGEAbgB1AGEAcgB5AFwAIgAsACAAXAAiAFMAdQBtAG0AZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAGUAYgByAHUAYQByAHkAXAAiACwAIABcACIAUwB1AG0AbQBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQByAGMAaABcACIALAAgAFwAIgBBAHUAdAB1AG0AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBwAHIAaQBsAFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAGEAeQBcACIALAAgAFwAIgBBAHUAdAB1AG0AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASgB1AG4AZQBcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASgB1AGwAeQBcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQB1AGcAdQBzAHQAXAAiACwAIABcACIAVwBpAG4AdABlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAZQBwAHQAZQBtAGIAZQByAFwAIgAsACAAXAAiAFMAcAByAGkAbgBnAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBPAGMAdABvAGIAZQByAFwAIgAsACAAXAAiAFMAcAByAGkAbgBnAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdgBlAG0AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAZQBjAGUAbQBiAGUAcgBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBhAG4AdQByAGUAIABNAGEAbgBhAGcAZQBtAGUAbgB0ACAAEyAgAE0AZQB0AGgAYQBuAGUAIABjAG8AbgB2AGUAcgBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABwAGUAcgAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAIAAoAGYAcgBhAGMAdABpAG8AbgApACAAKABNAEMARgBpAG0AKQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAxAC4AOAAuADEAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIAMgAsACAAMQA2ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAE0AQQBUACAAKAC6AEMAKQBcACIALAAgAFwAIgBVAG4AYwBvAHYAZQByAGUAZAAgAGEAbgBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuAFwAIgAsACAAXAAiAEMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBcACIALAAgAFwAIgBMAGkAcQB1AGkAZAAgAFMAbAB1AHIAcgB5ACAAKAB3AGkAdABoAG8AdQB0ACAAbgBhAHQAdQByAGEAbAAgAGMAcgB1AHMAdAApAFwAIgAsACAAXAAiAEQAYQBpAGwAeQAgAHMAcAByAGUAYQBkACAAKABiACkAXAAiACwAIABcACIAQwBvAG0AcABvAHMAdABpAG4AZwAgACgAcABhAHMAcwBpAHYAZQAgAHcAaQBuAGQAcgBvAHcAKQBcACIALAAgAFwAIgBTAG8AbABpAGQAIABTAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAFAAaQB0ACAAUwB0AG8AcgBhAGcAZQAgAFwAdQAwADAAMwBjADEAIABtAG8AbgB0AGgAXAAiACwAIABcACIARABlAGUAcAAgAEwAaQB0AHQAZQByAFwAIgAsACAAXAAiAFAAbwB1AGwAdAByAHkAIABNAGEAbgB1AHIAZQAgACgAdwBpAHQAaAAvAHcAaQB0AGgAbwB1AHQAIABsAGkAdAB0AGUAcgApAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAcAByAG8AYwBlAHMAcwBpAG4AZwAgAGkAbgB0AG8AIABwAGUAbABsAGUAdABpAHoAZQBkACAAZgBlAHIAdABpAGwAaQBzAGUAcgBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgAgAHQAbwAgAHMAbwBpAGwAXAAiACwAIABcACIAUABhAHMAdAB1AHIAZQAsACAAUgBhAG4AZwBlACAAYQBuAGQAIABQAGEAZABkAG8AYwBrACAAKABjACkAKABkACkAXAAiACwAIABcACIATQBBAFQAIAByAGEAdwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgAFwAIgBkIjEAMABcACIALAAgADAALgA2ADYALAAgADAALgAxACwAIAAwAC4AMQAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIAAxADEALAAgADAALgA2ADgALAAgADAALgAxACwAIAAwAC4AMQAxACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgADEAMgAsACAAMAAuADcALAAgADAALgAxACwAIAAwAC4AMQAzACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgADEAMwAsACAAMAAuADcAMQAsACAAMAAuADEALAAgADAALgAxADQALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQA0ACwAIAAwAC4ANwAzACwAIAAwAC4AMQAsACAAMAAuADEANQAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA1ACwAIAAwAC4ANwA0ACwAIAAwAC4AMQAsACAAMAAuADEANwAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEANQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEANgAsACAAMAAuADcANQAsACAAMAAuADEALAAgADAALgAxADgALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADcALAAgADAALgA3ADYALAAgADAALgAxACwAIAAwAC4AMgAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEANwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEAOAAsACAAMAAuADcANwAsACAAMAAuADEALAAgADAALgAyADIALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADkALAAgADAALgA3ADcALAAgADAALgAxACwAIAAwAC4AMgA0ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgAwACwAIAAwAC4ANwA4ACwAIAAwAC4AMQAsACAAMAAuADIANgAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIAMQAsACAAMAAuADcAOAAsACAAMAAuADEALAAgADAALgAyADkALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADIALAAgADAALgA3ADgALAAgADAALgAxACwAIAAwAC4AMwAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgAzACwAIAAwAC4ANwA5ACwAIAAwAC4AMQAsACAAMAAuADMANAAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIANAAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgAzADcALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADUALAAgADAALgA3ADkALAAgADAALgAxACwAIAAwAC4ANAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AXAAiACwAIAAyADYALAAgADAALgA3ADkALAAgADAALgAxACwAIAAwAC4ANAA0ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AXAAiACwAIAAyADcALAAgADAALgA4ACwAIAAwAC4AMQAsACAAMAAuADQAOAAsACAAMAAuADAAMQAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIANwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtAFwAIgAsACAAXAAiAGUiMgA4AFwAIgAsACAAMAAuADgALAAgADAALgAxACwAIAAwAC4ANQAsACAAMAAuADAAMQAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBBAG4AYQBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuAFwAIgAsACAAXAAiAEQAaQBnAGUAcwB0AGUAcgAgAC8AIABjAG8AdgBlAHIAZQBkACAAbABhAGcAbwBvAG4AcwBcACIALAAgAFwAIgBMAGkAcQB1AGkAZAAgAHMAeQBzAHQAZQBtAHMAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAXAAiACwAIABcACIAQwBvAG0AcABvAHMAdABpAG4AZwAgACgAcABhAHMAcwBpAHYAZQAgAHcAaQBuAGQAcgBvAHcAKQBcACIALAAgAFwAIgBTAG8AbABpAGQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAFAAaQB0ACAAcwB0AG8AcgBhAGcAZQBcACIALAAgAFwAIgBEAGUAZQBwACAAbABpAHQAdABlAHIAXAAiACwAIABcACIAUABvAHUAbAB0AHIAeQAgAG0AYQBuAHUAcgBlACAAdwBpAHQAaAAgAGIAZQBkAGQAaQBuAGcAXAAiACwAIABcACIAUABvAHUAbAB0AHIAeQAgAG0AYQBuAHUAcgBlACAAdwBpAHQAaABvAHUAdAAgAGIAZQBkAGQAaQBuAGcAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABwAHIAbwBjAGUAcwBzAGkAbgBnAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuAFwAIgAsACAAXAAiAFAAYQBzAHQAdQByAGUAIAByAGEAbgBnAGUAIABhAG4AZAAgAHAAYQBkAGQAbwBjAGsAXAAiACwAIABcACIATQBBAFQAIAByAGEAdwBcACIAIABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAOgAgAEEAZABkAGUAZAAgAHIAbwB3ACAAbwBmACAATgBJAFIAIABNAE0AQQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgAgAEQAdQBwAGwAaQBjAGEAdABlAGQAIABcAHUAMAAwADIANwBQAG8AdQBsAHQAcgB5ACAAdwBpAHQAaAAgAGEAbgBkACAAdwBpAHQAaABvAHUAdAAgAGwAaQB0AHQAZQByAFwAdQAwADAAMgA3ACAAYwBvAGwAdQBtAG4AIAB3AGkAdABoACAAcwBlAHAAYQByAGEAdABlACAATgBJAFIAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AIABBAGQAZABlAGQAIABcAHUAMAAwADIANwBNAEEAVAAgAHIAYQB3AFwAdQAwADAAMgA3ACAAYwBvAGwAdQBtAG4AIAB0AG8AIABhAGwAbABvAHcAIABsAG8AbwBrAHUAcAAgAG8AZgAgAG4AdQBtAGIAZQByAHMALgBcACIAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAbgBkACAAYwByAG8AcAAgAHIAZQBzAGkAZAB1AGUAcwAgAHIAZQB0AHUAcgBuAGUAZAAgAHQAbwAgAHQAaABlACAAcwBvAGkAbABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBGAE4AaQAgAFwAdQAwADAAMgA2ACAARQBGAE4AMgBPAGkAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABOADIATwAgAC0AIABOACAALwAgAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADIALgAxAC4ANABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgAFwAIgBFAEYATgBpACAAXAB1ADAAMAAyADYAIABFAEYATgAyAE8AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIAAwAC4AMAAwADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAANQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIAXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBcAG4AQwBvAG4AdgBlAHIAdAAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcAG4ARQBOADIATwAgAEMATwAyAGUAXABuAHQAIABDAE8AMgBlAFwAbgBFAE4AMgBPADoAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAAoAHQAIABOADIATwApAFwAbgBHAFcAUABOADIATwA6ACAAZwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIAAoAHQAIABDAE8AMgAtAGUAIAAvACAAdAAgAE4AMgBPACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABFAF8ATgAyAE8ALAAgAEcAVwBQAF8ATgAyAE8ALABcAG4AIAAgACAAIABFAF8ATgAyAE8AIAAqACAARwBXAFAAXwBOADIATwBcAG4AIAAgACkAXABuADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAbwBuAHYAZQByAHQAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAB0AG8AIABjAGEAcgBiAG8AbgAgAGQAaQBvAHgAaQBkAGUAIABlAHEAdQBpAHYAYQBsAGUAbgB0ACAAZQBtAGkAcwBzAGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBOADIATwAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAE8AMgBlAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMATwAyAF8AZQAgAD0AIABFAF8AewBOADIATwB9ACAAXABcAHQAaQBtAGUAcwAgAEcAVwBQAF8AewBOADIATwB9AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUATgAyAE8AXAAiACwAXAAiAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAE4AMgBPACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAVwBQAE4AMgBPAFwAIgAsAFwAIgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAATgAyAE8AKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBcAG4AQwBvAG4AdgBlAHIAdAAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcAG4ARQBDAEgANAAgAEMATwAyAGUAXABuAHQAIABDAE8AMgBlAFwAbgBFAEMASAA0ADoAIABtAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAAoAHQAIABDAEgANAApAFwAbgBHAFcAUABDAEgANAA6ACAAZwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAG0AZQB0AGgAYQBuAGUAIAAoAHQAIABDAE8AMgAtAGUAIAAvACAAdAAgAEMASAA0ACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABFAF8AQwBIADQALAAgAEcAVwBQAF8AQwBIADQALABcAG4AIAAgACAAIABFAF8AQwBIADQAIAAqACAARwBXAFAAXwBDAEgANABcAG4AIAAgACkAXABuADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAbwBuAHYAZQByAHQAIABtAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAB0AG8AIABjAGEAcgBiAG8AbgAgAGQAaQBvAHgAaQBkAGUAIABlAHEAdQBpAHYAYQBsAGUAbgB0ACAAZQBtAGkAcwBzAGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBDAEgANAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAE8AMgBlAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMATwAyAF8AZQAgAD0AIABFAF8AewBDAEgANAB9ACAAXABcAHQAaQBtAGUAcwAgAEcAVwBQAF8AewBDAEgANAB9AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUAQwBIADQAXAAiACwAXAAiAE0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAEMASAA0ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAVwBQAEMASAA0AFwAIgAsAFwAIgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbQBlAHQAaABhAG4AZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAAQwBIADQAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIAVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAUgBvAHcAUwB0AGEAcgB0AE4AdQBtAGIAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwALABSAG8AdwBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAYQBuAGQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAUgBPAFcAKABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAApACAAKwAgAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkAIAAtACAAMQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABUAGEAYgBsAGUASABlAGEAZABlAHIAQwBlAGwAbAAsAFwAbgAgACAAQwBPAEwAVQBNAE4AKABUAGEAYgBsAGUASABlAGEAZABlAHIAQwBlAGwAbAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBBAHIAcgBhAHkASQBuAFQAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgAEEAcgByAGEAeQBEAGEAdABhACwAIABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQAsACAAWwBDAG8AbAB1AG0AbgBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAQQBuAGQAQQByAHIAYQB5AF0ALABcAG4AIABJAEYARQBSAFIATwBSACgAXABuACAAIAAgACAAIABJAE4ARABFAFgAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAVQBOAEkAUQBVAEUAKABBAHIAcgBhAHkARABhAHQAYQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBPAFcAKAApAC0AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAUgBvAHcAUwB0AGEAcgB0AE4AdQBtAGIAZQByACgAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwALAAgAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEMATwBMAFUATQBOACgAKQAtAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAEMAbwBsAHUAbQBuAFMAdABhAHIAdABOAHUAbQBiAGUAcgAoAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACkAIAArAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAEMAbwBsAHUAbQBuAHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBBAG4AZABBAHIAcgBhAHkAKQAsACAAMQAsACAAQwBvAGwAdQBtAG4AcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAEEAbgBkAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACAAIAAgACAAKQAsACAAXAAiAFwAIgBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFwAIgBcACIAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEkARgAoAEkAUwBOAFUATQBCAEUAUgAoAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFwAIgBcACIAKQBcAG4AIAAgACAAIAApACwAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApACwAIAAwACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBUAHcAbwBDAG8AbAB1AG0AbgBzAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlADEALAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADIALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAWwBWAGEAbAB1AGUASQBGAEYAYQBsAHMAZQBdACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoADEALAAgACgATABvAG8AawB1AHAAQQByAHIAYQB5ADEAPQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQApACoAKABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABWAGEAbAB1AGUASQBGAEYAYQBsAHMAZQApACwAIABcACIAXAAiACwAIABWAGEAbAB1AGUASQBGAEYAYQBsAHMAZQApACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBPAG4AZQBDAG8AbAB1AG0AbgBBAG4AZABIAGUAYQBkAGUAcgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACwAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMgAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADEALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFsAVgBhAGwAdQBlAEkAZgBGAGEAbABzAGUAXQAsAFwAbgAgACAAIAAgAEkARgBFAFIAUgBPAFIAKABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADEALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACkAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAFYAYQBsAHUAZQBJAGYARgBhAGwAcwBlACkALAAgAFwAIgBcACIALAAgAFYAYQBsAHUAZQBJAGYARgBhAGwAcwBlACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAcABsAGkAdABTAHQAcgBpAG4AZwBJAG4AdABvAEEAcgByAGEAeQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEMAZQBsAGwALAAgAEQAZQBsAGkAbQBpAHQAZQByACwAIABbAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAxAF0ALAAgAFsAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADIAXQAsAFwAbgAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAWABNAEwAKABcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBcAHUAMAAwADMAYwB0AFwAdQAwADAAMwBlAFwAdQAwADAAMwBjAHMAXAB1ADAAMAAzAGUAXAAiACAAXAB1ADAAMAAyADYAXABuACAAIAAgACAAIAAgACAAIABTAFUAQgBTAFQASQBUAFUAVABFACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFMAVQBCAFMAVABJAFQAVQBUAEUAKABTAFUAQgBTAFQASQBUAFUAVABFACgAQwBlAGwAbAAsAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAxACwAXAAiAFwAIgApACwAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADIALABcACIAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAARABlAGwAaQBtAGkAdABlAHIALABcACIAXAB1ADAAMAAzAGMALwBzAFwAdQAwADAAMwBlAFwAdQAwADAAMwBjAHMAXAB1ADAAMAAzAGUAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAKQAgAFwAdQAwADAAMgA2AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFwAdQAwADAAMwBjAC8AcwBcAHUAMAAwADMAZQBcAHUAMAAwADMAYwAvAHQAXAB1ADAAMAAzAGUAXAAiACwAXABuACAAIAAgACAAIAAgACAAIABcACIALwAvAHMAXAAiAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABDAGwAaQBtAGEAdABlAFoAbwBuAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABhAHYAZwBUAGUAbQBwACwAYQB2AGcAUgBhAGkAbgAsAGYAcgBvAHMAdABEAGEAeQBzACwAZQBsAGUAdgAsAG0AYQBwAF8AcABlAHQALABcAG4AIAAgACAAIABtAGkAbgBUAGUAbQBwAEEAcgByAGEAeQAsAG0AYQB4AFQAZQBtAHAAQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4AUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQAsAG0AYQB4AFIAYQBpAG4AZgBhAGwAbABBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBGAHIAbwBzAHQAQQByAHIAYQB5ACwAbQBhAHgARgByAG8AcwB0AEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAEUAbABlAHYAYQB0AGkAbwBuAEEAcgByAGEAeQAsAG0AYQB4AEUAbABlAHYAYQB0AGkAbwBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAFAARQBUAEEAcgByAGEAeQAsAG0AYQB4AFAARQBUAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAGMAbABpAG0AYQB0AGUAWgBvAG4AZQBBAHIAcgBhAHkALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAbQBhAHMAawAsAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBUAGUAbQBwAEEAcgByAGEAeQApAFwAdQAwADAAMwBjAD0AYQB2AGcAVABlAG0AcAApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AFQAZQBtAHAAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBhAHYAZwBUAGUAbQBwACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4AUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQApAFwAdQAwADAAMwBjAD0AYQB2AGcAUgBhAGkAbgApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AFIAYQBpAG4AZgBhAGwAbABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGEAdgBnAFIAYQBpAG4AKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBGAHIAbwBzAHQAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBmAHIAbwBzAHQARABhAHkAcwApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AEYAcgBvAHMAdABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGYAcgBvAHMAdABEAGEAeQBzACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4ARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBlAGwAZQB2ACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBlAGwAZQB2ACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4AUABFAFQAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBtAGEAcABfAHAAZQB0ACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgAUABFAFQAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBtAGEAcABfAHAAZQB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAFQAQQBLAEUAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAKABjAGwAaQBtAGEAdABlAFoAbwBuAGUAQQByAHIAYQB5ACwAbQBhAHMAawAsACAAXAAiAE4AbwAgAG0AYQB0AGMAaABcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAASQB0AGUAbQBGAHIAbwBtAE0AaQBuAE0AYQB4AFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABNAGkAbgBBAHIAcgBhAHkALAAgAE0AYQB4AEEAcgByAGEAeQAsACAASQB0AGUAbQBBAHIAcgBhAHkALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAbQBhAHMAawAsAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABNAGkAbgBBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAE0AYQB4AEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0ATABvAG8AawB1AHAAVgBhAGwAdQBlACkALABcAG4AIAAgACAAIAAgACAAIAAgAEYASQBMAFQARQBSACgASQB0AGUAbQBBAHIAcgBhAHkALAAgAG0AYQBzAGsALAAgAFwAIgBOAG8AIABtAGEAdABjAGgAXAAiACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBTAHUAbQBRAHUAYQBuAHQAaQB0AHkARgByAG8AbQBDAHIAaQB0AGUAcgBpAGEAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAEMAcgBpAHQAZQByAGkAYQAxACwAIABDAHIAaQB0AGUAcgBpAGEAMQBUAHkAcABlAEEAcgByAGEAeQAsACAAUQB1AGEAbgB0AGkAdAB5ACwAIABbAE0AdQBsAHQAaQBwAGwAaQBlAHIAXQAsACAAWwBDAHIAaQB0AGUAcgBpAGEAMgBdACwAWwBDAHIAaQB0AGUAcgBpAGEAMgBBAHIAcgBhAHkAXQAsAFwAbgAgACAATABFAFQAKABcAG4AIAAgACAAIABtAHUAbAB0AGkAcABsAGkAZQByACwAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAE0AdQBsAHQAaQBwAGwAaQBlAHIAKQAsADEALABNAHUAbAB0AGkAcABsAGkAZQByACkALABcAG4AIAAgACAAIABxAHUAYQBuAHQAaQB0AHkALAAgAFEAdQBhAG4AdABpAHQAeQAqAE0AdQBsAHQAaQBwAGwAaQBlAHIALABcAG4AIAAgACAAIABjAHIAaQB0AGUAcgBpAGEAMQAsAC0ALQAoAEMAcgBpAHQAZQByAGkAYQAxAFQAeQBwAGUAQQByAHIAYQB5AD0AQwByAGkAdABlAHIAaQBhADEAKQAsAFwAbgAgACAAIAAgAGMAcgBpAHQAZQByAGkAYQAyACwASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABDAHIAaQB0AGUAcgBpAGEAMgApACwAMQAsAC0ALQAoAEMAcgBpAHQAZQByAGkAYQAyAEEAcgByAGEAeQA9AEMAcgBpAHQAZQByAGkAYQAyACkAKQAsAFwAbgAgACAAIAAgAFMAVQBNAFAAUgBPAEQAVQBDAFQAKABjAHIAaQB0AGUAcgBpAGEAMQAqAGMAcgBpAHQAZQByAGkAYQAyACoAcQB1AGEAbgB0AGkAdAB5ACkAXABuACAAIAApAFwAbgApADsAXABuAFwAbgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAHMAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBTAHQAYQByAHQALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBFAG4AZAAsAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAUwAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgACAAIAAgACAARQAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAXABuACAAIAAgACAAIAAgACAAIABtACwATQBPAE4AVABIACgAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAApACwAXABuACAAIAAgACAAIAAgACAAIABkACwARABBAFkAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAFAAZQByAGkAbwBkAEUAbgBkACwATABBAE0AQgBEAEEAKABzAHQALABFAEQAQQBUAEUAKABzAHQALAAxADIAKQAtADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAQQAsAFMALQAzADYANQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBhACwAWQBFAEEAUgAoAEEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBiACwAWQBFAEEAUgAoAEUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZgBpAHIAcwB0AFkAZQBhAHIALAB5AGEAKwAoAFAAZQByAGkAbwBkAEUAbgBkACgARABBAFQARQAoAHkAYQAsAG0ALABkACkAKQBcAHUAMAAwADMAYwAgAFMAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAbABhAHMAdABZAGUAYQByACwAeQBiAC0AKABEAEEAVABFACgAeQBiACwAbQAsAGQAKQBcAHUAMAAwADMAZQAgAEUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAATQBBAFgAKAAwACwAbABhAHMAdABZAGUAYQByAC0AZgBpAHIAcwB0AFkAZQBhAHIAKwAxACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAFAAZQByAGkAbwBkAHMAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBTAHQAYQByAHQALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBFAG4AZAAsAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAUwAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgACAAIAAgACAARQAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAXABuACAAIAAgACAAIAAgACAAIABtACwATQBPAE4AVABIACgAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAApACwAXABuACAAIAAgACAAIAAgACAAIABkACwARABBAFkAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALAAgAC8AKgBoAGUAbABwAGUAcgA6ACAAZQBuAGQAIABkAGEAdABlACAAZgBvAHIAIABhACAAcgBlAHAAbwByAHQAaQBuAGcAIABwAGUAcgBpAG8AZAAgAHMAdABhAHIAdABpAG4AZwAgAGEAdAAgAGEAIABnAGkAdgBlAG4AIABkAGEAdABlACoALwBcAG4AIAAgACAAIAAgACAAIAAgAFAAZQByAGkAbwBkAEUAbgBkACwATABBAE0AQgBEAEEAKABzAHQALABFAEQAQQBUAEUAKABzAHQALAAxADIAKQAtADEAKQAsACAALwAqAG8AbgBsAHkAIABuAGUAZQBkACAAdABvACAAbABvAG8AawAgAGIAYQBjAGsAIAAzADYANQAgAGQAYQB5AHMAKABtAGEAeAAgAG8AdgBlAHIAbABhAHAAIAB3AGkAbgBkAG8AdwApACoALwBcAG4AIAAgACAAIAAgACAAIAAgAEEALABTAC0AMwA2ADUALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYQAsAFkARQBBAFIAKABBACkALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYgAsAFkARQBBAFIAKABFACkALAAgAC8AKgBpAGYAIAB0AGgAZQAgAGEAbgBjAGgAbwByACAAZgBvAHIAIAB5AGEAIABlAG4AZABzACAAYgBlAGYAbwByAGUAIABTACwAaQB0ACAAYwBhAG4AXAB1ADAAMAAyADcAdAAgAG8AdgBlAHIAbABhAHAAOwAgAG0AbwB2AGUAIAB0AG8AIABuAGUAeAB0ACAAeQBlAGEAcgAqAC8AXABuACAAIAAgACAAIAAgACAAIABmAGkAcgBzAHQAWQBlAGEAcgAsAHkAYQArACgAUABlAHIAaQBvAGQARQBuAGQAKABEAEEAVABFACgAeQBhACwAbQAsAGQAKQApAFwAdQAwADAAMwBjAFMAKQAsACAALwAqAGkAZgAgAHQAaABlACAAYQBuAGMAaABvAHIAIABmAG8AcgAgAHkAYgAgAHMAdABhAHIAdABzACAAYQBmAHQAZQByACAARQAsAGkAdAAgAGMAYQBuAFwAdQAwADAAMgA3AHQAIABvAHYAZQByAGwAYQBwADsAIABtAG8AdgBlACAAdABvACAAcAByAGUAdgBpAG8AdQBzACAAeQBlAGEAcgAqAC8AXABuACAAIAAgACAAIAAgACAAIABsAGEAcwB0AFkAZQBhAHIALAB5AGIALQAoAEQAQQBUAEUAKAB5AGIALABtACwAZAApAFwAdQAwADAAMwBlAEUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAbgAsAE0AQQBYACgAMAAsAGwAYQBzAHQAWQBlAGEAcgAtAGYAaQByAHMAdABZAGUAYQByACsAMQApACwAXABuACAAIAAgACAAIAAgACAAIAB5AHIAcwAsAFMARQBRAFUARQBOAEMARQAoAG4ALAAxACwAZgBpAHIAcwB0AFkAZQBhAHIALAAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAHMAdABhAHIAdABzACwARABBAFQARQAoAHkAcgBzACwAbQAsAGQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZQBuAGQAcwAsAE0AQQBQACgAcwB0AGEAcgB0AHMALABQAGUAcgBpAG8AZABFAG4AZAApACwAXABuACAAIAAgACAAIAAgACAAIAB0AGEAZwAsAEkARgAoAHMAdABhAHIAdABzAD0AUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAIgAgACgAVABoAGkAcwAgAHIAZQBwAG8AcgB0AGkAbgBnACAAYwB5AGMAbABlACkAXAAiACwAXAAiAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABzAHQAYQByAHQAcwBUAGUAeAB0ACwAVABFAFgAVAAoAHMAdABhAHIAdABzACwAXAAiAGQAZAAgAG0AbQBtACAAeQB5AHkAeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZQBuAGQAcwBUAGUAeAB0ACwAVABFAFgAVAAoAGUAbgBkAHMALABcACIAZABkACAAbQBtAG0AIAB5AHkAeQB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABuAD0AMAAsAFwAIgBcACIALABIAFMAVABBAEMASwAoAHMAdABhAHIAdABzAFQAZQB4AHQAIABcAHUAMAAwADIANgAgAFwAIgAgAHQAbwAgAFwAIgAgAFwAdQAwADAAMgA2ACAAZQBuAGQAcwBUAGUAeAB0ACAAXAB1ADAAMAAyADYAIAB0AGEAZwApACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkARgB1AG4AYwB0AGkAbwBuAE4AYQBtAGUAXABuAD0ATABBAE0AQgBEAEEAKABGAHUAbgBjAHQAaQBvAG4ALAAgAFQARQBYAFQAQgBFAEYATwBSAEUAKABGAE8AUgBNAFUATABBAFQARQBYAFQAKABGAHUAbgBjAHQAaQBvAG4AKQAsACAAXAAiACgAXAAiACkAKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAE4AMgBPAEUARgBGAHIAbwBtAFAAcgBvAGQASQByAHIAaQBnAGEAdABpAG8AbgBSAGEAaQBuAGYAYQBsAGwAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAIABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACwAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AQQByAHIAYQB5ACwAIABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkAEEAcgByAGEAeQAsACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAQQByAHIAYQB5ACwAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQALAAgAEkARgAoAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAPQBcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEEAbgB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQAsACAASQBGACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAAgAD0AIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAIABcACIAQQBuAHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKAAxACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEEAcgByAGEAeQA9AFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AKQAqAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAoAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAQQByAHIAYQB5AD0ASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAApACoAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACgAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAQQByAHIAYQB5AD0AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEcAZQB0AEYAcgBhAGMAVwBFAFQAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ALABcAG4AIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQALAAgAFwAbgAgACAAIAAgACAAIAAgACAAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUALABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBMAG8AbwBrAHUAcAAsAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQALAAgAFwAbgAgACAAIAAgACAAIAAgACAAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ATABvAG8AawB1AHAALABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBGAHIAYQBjAFcARQBUACAAKwAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVABcAHUAMAAwADMAZQAwACwAIAAxACwAIAAwACkAXABuACAAIAAgACAAKQApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEMAbwBuAHYAZQByAHQAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAVABvAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUALABcAG4AIAAgACAAIABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBBAHIAcgBhAHkALAAgAFMAdABhAHQAZQBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUALAAgAFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAEEAcgByAGEAeQAsACAAUwB0AGEAdABlAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwBvAHUAcgBjAGUASAB5AHAAZQByAGwAaQBuAGsAXABuAD0ATABBAE0AQgBEAEEAKABUAGEAcgBnAGUAdABDAGUAbABsACwAXABuACAAIABMAEUAVAAoAFwAbgAgACAAIAAgAHMAaAAsACAAVABFAFgAVABBAEYAVABFAFIAKABDAEUATABMACgAXAAiAGYAaQBsAGUAbgBhAG0AZQBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsACAAXAAiAF0AXAAiACkALABcAG4AIAAgACAAIABhAGQAZAByACwAIABDAEUATABMACgAXAAiAGEAZABkAHIAZQBzAHMAXAAiACwAIABUAGEAcgBnAGUAdABDAGUAbABsACkALABcAG4AIAAgACAAIABcACIAIwBcAHUAMAAwADIANwBcACIAIABcAHUAMAAwADIANgAgAHMAaAAgAFwAdQAwADAAMgA2ACAAXAAiAFwAdQAwADAAMgA3ACEAXAAiACAAXAB1ADAAMAAyADYAIABhAGQAZAByAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAbwB1AHIAYwBlAEgAeQBwAGUAcgBsAGkAbgBrAEQAaQBmAGYAZQByAGUAbgB0AFMAaABlAGUAdABcAG4APQBMAEEATQBCAEQAQQAoAFQAYQByAGcAZQB0AEMAZQBsAGwALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAcwBoACwAIABUAEUAWABUAEEARgBUAEUAUgAoAEMARQBMAEwAKABcACIAZgBpAGwAZQBuAGEAbQBlAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAIABcACIAXQBcACIAKQAsAFwAbgAgACAAIAAgAGEAZABkAHIALAAgAEMARQBMAEwAKABcACIAYQBkAGQAcgBlAHMAcwBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsAFwAbgAgACAAIAAgAFwAIgAjAFwAIgAgAFwAdQAwADAAMgA2ACAAYQBkAGQAcgBcAG4AIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgBnAHUAbQBlAG4AdABzAF8AMQBfADIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALABcAG4AIAAgACAAIABDAEgATwBPAFMARQBDAE8ATABTACgAQQByAGcAdQBtAGUAbgB0AHMAQQByAHIAYQB5ACwAIAAxACwAIAAyACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgBnAHUAbQBlAG4AdABzAF8AMwBfADQAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALABcAG4AIAAgACAAIABDAEgATwBPAFMARQBDAE8ATABTACgAQQByAGcAdQBtAGUAbgB0AHMAQQByAHIAYQB5ACwAIAAzACwAIAA0ACkAXABuACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8ARwBlAHQATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUALAAgAE0ATQBTACwAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUAQQByAHIAYQB5ACwAIABNAE0AUwBBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKABcAG4AIAAgACAAIAAgACAAIAAgAE0ARQBEAEkAQQBOACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAE0ASQBOACgAVABlAG0AcABlAHIAYQB0AHUAcgBlAEEAcgByAGEAeQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATQBBAFgAKABUAGUAbQBwAGUAcgBhAHQAdQByAGUAQQByAHIAYQB5ACkAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUAQQByAHIAYQB5ACwAXABuACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATQBNAFMALAAgAE0ATQBTAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBSAGUAcwB1AGwAdABzAEkAdABlAG0ARgByAG8AbQBFAHEAdQBhAHQAaQBvAG4AVABpAHQAbABlAEEAbgBkAFMAbwB1AHIAYwBlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAVABpAHQAbABlAEMAZQBsAGwALAAgAFMAbwB1AHIAYwBlAEMAZQBsAGwALABcAG4AIAAgACAAIABTAFUAQgBTAFQASQBUAFUAVABFACgATABFAEYAVAAoAFMAbwB1AHIAYwBlAEMAZQBsAGwALAAgAEYASQBOAEQAKABcACIALABcACIALAAgAFMAbwB1AHIAYwBlAEMAZQBsAGwAKQAgAC0AMQApACwAIABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAXAAiACwAIABcACIAXAAiACkAIABcAHUAMAAwADIANgAgAFwAIgAgAFwAIgAgAFwAdQAwADAAMgA2ACAAVABpAHQAbABlAEMAZQBsAGwAXABuACkAOwAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuADEAMQAuADEAOgAgAFcAYQBzAHQAZQB3AGEAdABlAHIAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuADEAMQAuADEALgAxAC4AMQAgAE0AZQB0AGgAbwBkACAAMQAgAC0AIABNAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAbwBuAHMAaQB0AGUAIABXAGEAcwB0AGUAdwBhAHQAZQByACAATQBhAG4AYQBnAGUAbQBlAG4AdABcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADEAMQBfADEAXwAxAF8AMQBfAF8AMQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBXAGEAcwB0AGUAdwBhAHQAZQByAFQAcgBlAGEAdABtAGUAbgB0AFwAbgBNAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAdwBhAHMAdABlAHcAYQB0AGUAcgAgAHQAcgBlAGEAdABtAGUAbgB0AFwAbgBFAF8AQwBIADQAXABuAHQAIABDAEgANABcAG4ARQBfAHsAQwBIADQAfQA9AFwAXABmAHIAYQBjAHsAMQB9AHsAMQAwADAAMAB9AFwAXAB0AGkAbQBlAHMAXABcAGwAZQBmAHQAWwBcAFwAbABlAGYAdAAoAFcAXwB0AFwAXAB0AGkAbQBlAHMAXABcAGwAZQBmAHQAKABDAE8ARABfAHsAaQBuAH0AXABcAHQAaQBtAGUAcwAoADEALQBGAF8AewBzAGwAdQBkAGcAZQB9ACkALQBDAE8ARABfAHsAbwB1AHQAfQBcAFwAcgBpAGcAaAB0ACkAXABcAHQAaQBtAGUAcwAgAEMARgBfAHsAdwB3ACwAdAB9AFwAXAB0AGkAbQBlAHMAIABFAEYAXwB7AHcAdwB9AFwAXAByAGkAZwBoAHQAKQArAFwAXABsAGUAZgB0ACgAVwBfAHQAXABcAHQAaQBtAGUAcwBcAFwAbABlAGYAdAAoAEMATwBEAF8AewBpAG4AfQBcAFwAdABpAG0AZQBzACgARgBfAHsAcwBsAHUAZABnAGUAfQAtAEYAXwB7AHIAZQBtAG8AdgBlAGQAfQApAFwAXAByAGkAZwBoAHQAKQBcAFwAdABpAG0AZQBzACAAQwBGAF8AewBzAGwAdQBkAGcAZQAsAHQAfQBcAFwAdABpAG0AZQBzACAARQBGAF8AewBzAGwAdQBkAGcAZQB9AFwAXAByAGkAZwBoAHQAKQAtAFwAXABsAGUAZgB0ACgANgAuADcAOAA0AFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0ANAB9AFwAXAB0AGkAbQBlAHMAKABRAF8AewBjAGEAcAB9ACsAUQBfAHsAZgBsAGEAcgBlAGQAfQArAFEAXwB7AG8AdQB0AH0AKQBcAFwAcgBpAGcAaAB0ACkAKwBcAFwAbABlAGYAdAAoAFEAXwB7AGYAbABhAHIAZQBkAH0AXABcAHQAaQBtAGUAcwAgAEUAQwBfAHsAZgBsAGEAcgBlAGQAfQBcAFwAdABpAG0AZQBzACAARQBGAF8AewBmAGwAYQByAGUAZAAsAEMASAA0AH0AXABcAHIAaQBnAGgAdAApAFwAXAByAGkAZwBoAHQAXQBcAG4AVwBfAHQAIAA9ACAAcQB1AGEAbgB0AGkAdAB5ACAAbwBmACAAdwBhAHMAdABlAHcAYQB0AGUAcgAgAHQAcgBlAGEAdABlAGQAIABhAHQAIABmAGEAYwBpAGwAaQB0AHkAIAB0AHkAcABlACAAdAAgACgAbQAzACkAXABuAEMATwBEAF8AaQBuACAAPQAgAGEAdgBlAHIAYQBnAGUAIABpAG4AbABlAHQAIABDAGgAZQBtAGkAYwBhAGwAIABPAHgAeQBnAGUAbgAgAEQAZQBtAGEAbgBkACAAYwBvAG4AYwBlAG4AdAByAGEAdABpAG8AbgAgAG8AZgAgAHcAYQBzAHQAZQB3AGEAdABlAHIAIAAoAGsAZwAgAEMATwBEAC8AbQAzACkAXABuAEYAXwBzAGwAdQBkAGcAZQAgAD0AIABmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABDAE8ARAAgAHIAZQBtAG8AdgBlAGQAIABmAHIAbwBtACAAdwBhAHMAdABlAHcAYQB0AGUAcgAgAGEAcwAgAHMAbAB1AGQAZwBlAFwAbgBDAE8ARABfAG8AdQB0ACAAPQAgAGEAdgBlAHIAYQBnAGUAIABvAHUAdABsAGUAdAAgAEMATwBEACAAYwBvAG4AYwBlAG4AdAByAGEAdABpAG8AbgAgAG8AZgAgAHcAYQBzAHQAZQB3AGEAdABlAHIAIAAoAGsAZwAgAEMATwBEAC8AbQAzACkAXABuAEMARgBfAHcAdwBfAHQAIAA9ACAAbQBlAHQAaABhAG4AZQAgAGMAbwByAHIAZQBjAHQAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAZgBhAGMAaQBsAGkAdAB5ACAAdAB5AHAAZQAgAHQAIAB1AHMAZQBkACAAdABvACAAdAByAGUAYQB0ACAAdwBhAHMAdABlAHcAYQB0AGUAcgBcAG4ARQBGAF8AdwB3ACAAPQAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAdwBhAHMAdABlAHcAYQB0AGUAcgAgACgAawBnACAAQwBPADIAZQAvAGsAZwAgAEMATwBEACkAXABuAEYAXwByAGUAbQBvAHYAZQBkACAAPQAgAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAEMATwBEACAAcgBlAG0AbwB2AGUAZAAgAGYAcgBvAG0AIAB0AGgAZQAgAHcAYQBzAHQAZQB3AGEAdABlAHIAIAB0AHIAZQBhAHQAbQBlAG4AdAAgAGYAYQBjAGkAbABpAHQAeQAgAGEAbgBkACAAdAByAGEAbgBzAGYAZQByAHIAZQBkACAAZQBsAHMAZQB3AGgAZQByAGUAXABuAEMARgBfAHMAbAB1AGQAZwBlAF8AdAAgAD0AIABtAGUAdABoAGEAbgBlACAAYwBvAHIAcgBlAGMAdABpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABmAGEAYwBpAGwAaQB0AHkAIAB0AHkAcABlACAAdAAgAHUAcwBlAGQAIAB0AG8AIAB0AHIAZQBhAHQAIABzAGwAdQBkAGcAZQBcAG4ARQBGAF8AcwBsAHUAZABnAGUAIAA9ACAAbQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABzAGwAdQBkAGcAZQAgACgAawBnACAAQwBPADIAZQAvAGsAZwAgAEMATwBEACkAXABuAFEAXwBjAGEAcAAgAD0AIABxAHUAYQBuAHQAaQB0AHkAIABvAGYAIABtAGUAdABoAGEAbgBlACAAaQBuACAAcwBsAHUAZABnAGUAIABiAGkAbwBnAGEAcwAgAGMAYQBwAHQAdQByAGUAZAAgAGYAbwByACAAYwBvAG0AYgB1AHMAdABpAG8AbgAgACgAbQAzACAAQwBIADQAKQBcAG4AUQBfAGYAbABhAHIAZQBkACAAPQAgAHEAdQBhAG4AdABpAHQAeQAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAIABpAG4AIABzAGwAdQBkAGcAZQAgAGIAaQBvAGcAYQBzACAAZgBsAGEAcgBlAGQAIAAoAG0AMwAgAEMASAA0ACkAXABuAFEAXwBvAHUAdAAgAD0AIABxAHUAYQBuAHQAaQB0AHkAIABvAGYAIABtAGUAdABoAGEAbgBlACAAaQBuACAAcwBsAHUAZABnAGUAIABiAGkAbwBnAGEAcwAgAHQAcgBhAG4AcwBmAGUAcgByAGUAZAAgAG8AdQB0ACAAbwBmACAAdABoAGUAIAB0AHIAZQBhAHQAbQBlAG4AdAAgAGYAYQBjAGkAbABpAHQAeQAgACgAbQAzACAAQwBIADQAKQBcAG4ARQBDAF8AZgBsAGEAcgBlAGQAIAA9ACAAZQBuAGUAcgBnAHkAIABjAG8AbgB0AGUAbgB0ACAAZgBhAGMAdABvAHIAIABvAGYAIABtAGUAdABoAGEAbgBlACAAaQBuACAAcwBsAHUAZABnAGUAIABiAGkAbwBnAGEAcwAgAGYAbABhAHIAZQBkACAAKABHAEoALwBtADMAKQBcAG4ARQBGAF8AZgBsAGEAcgBlAGQAXwBDAEgANAAgAD0AIABtAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHMAbAB1AGQAZwBlACAAYgBpAG8AZwBhAHMAIABmAGwAYQByAGUAZAAgACgAawBnACAAQwBPADIAZQAvAEcASgApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADEAMQBfADEAXwAxAF8AMQBfAF8AMQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBXAGEAcwB0AGUAdwBhAHQAZQByAFQAcgBlAGEAdABtAGUAbgB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFcAXwB0ACwAIABDAE8ARABfAGkAbgAsACAARgBfAHMAbAB1AGQAZwBlACwAIABDAE8ARABfAG8AdQB0ACwAIABDAEYAXwB3AHcAXwB0ACwAIABFAEYAXwB3AHcALAAgAEYAXwByAGUAbQBvAHYAZQBkACwAIABDAEYAXwBzAGwAdQBkAGcAZQBfAHQALAAgAEUARgBfAHMAbAB1AGQAZwBlACwAIABRAF8AYwBhAHAALAAgAFEAXwBmAGwAYQByAGUAZAAsACAAUQBfAG8AdQB0ACwAIABFAEMAXwBmAGwAYQByAGUAZAAsACAARQBGAF8AZgBsAGEAcgBlAGQAQwBIADQALABcAG4AIAAgACAAIAAoADEALwAxADAAMAAwACkAIAAqACAAKAAoAFcAXwB0ACAAKgAgACgAQwBPAEQAXwBpAG4AIAAqACAAKAAxACAALQAgAEYAXwBzAGwAdQBkAGcAZQApACAALQAgAEMATwBEAF8AbwB1AHQAKQAgACoAIABDAEYAXwB3AHcAXwB0ACAAKgAgAEUARgBfAHcAdwApACAAKwAgACgAVwBfAHQAIAAqACAAKABDAE8ARABfAGkAbgAgACoAIAAoAEYAXwBzAGwAdQBkAGcAZQAgAC0AIABGAF8AcgBlAG0AbwB2AGUAZAApACkAIAAqACAAQwBGAF8AcwBsAHUAZABnAGUAXwB0ACAAKgAgAEUARgBfAHMAbAB1AGQAZwBlACkAIAAtACAAKAA2AC4ANwA4ADQAIAAqACAAMQAwAF4ALQA0ACAAKgAgACgAUQBfAGMAYQBwACAAKwAgAFEAXwBmAGwAYQByAGUAZAAgACsAIABRAF8AbwB1AHQAKQApACAAKwAgACgAUQBfAGYAbABhAHIAZQBkACAAKgAgACgARQBDAF8AZgBsAGEAcgBlAGQAIAAqACAARQBGAF8AZgBsAGEAcgBlAGQAQwBIADQAKQApACkAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADEAXwAxAF8AMQBfADEAXwBfADEAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AVwBhAHMAdABlAHcAYQB0AGUAcgBUAHIAZQBhAHQAbQBlAG4AdABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAHcAYQBzAHQAZQB3AGEAdABlAHIAIAB0AHIAZQBhAHQAbQBlAG4AdABcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQAxAF8AMQBfADEAXwAxAF8AXwAxAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFcAYQBzAHQAZQB3AGEAdABlAHIAVAByAGUAYQB0AG0AZQBuAHQAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwBDAEgANABcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQAxAF8AMQBfADEAXwAxAF8AXwAxAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFcAYQBzAHQAZQB3AGEAdABlAHIAVAByAGUAYQB0AG0AZQBuAHQAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgB0ACAAQwBIADQAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEAMQBfADEAXwAxAF8AMQBfAF8AMQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBXAGEAcwB0AGUAdwBhAHQAZQByAFQAcgBlAGEAdABtAGUAbgB0AF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADEAMQAuADEALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAxACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEAMQBfADEAXwAxAF8AMQBfAF8AMQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBXAGEAcwB0AGUAdwBhAHQAZQByAFQAcgBlAGEAdABtAGUAbgB0AF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEcAcgBlAGUAbgBoAG8AdQBzAGUAIABhAG4AZAAgAEUAbgBlAHIAZwB5ACAAUgBlAHAAbwByAHQAaQBuAGcAIABNAGUAYQBzAHUAcgBlAG0AZQBuAHQAIABEAGUAdABlAHIAbQBpAG4AYQB0AGkAbwBuACAAMgAwADAAOABcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQAxAF8AMQBfADEAXwAxAF8AXwAxAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFcAYQBzAHQAZQB3AGEAdABlAHIAVAByAGUAYQB0AG0AZQBuAHQAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAF8AewBDAEgANAB9AD0AXABcAGYAcgBhAGMAewAxAH0AewAxADAAMAAwAH0AXABcAHQAaQBtAGUAcwBcAFwAbABlAGYAdAB7AFwAXABsAGUAZgB0AHsAVwBfAHQAXABcAHQAaQBtAGUAcwBcAFwAbABlAGYAdABbAEMATwBEAF8AewBpAG4AfQBcAFwAdABpAG0AZQBzACgAMQAtAEYAXwB7AHMAbAB1AGQAZwBlAH0AKQAtAEMATwBEAF8AewBvAHUAdAB9AFwAXAByAGkAZwBoAHQAXQBcAFwAdABpAG0AZQBzACAAQwBGAF8AewB3AHcALAB0AH0AXABcAHQAaQBtAGUAcwAgAEUARgBfAHsAdwB3AH0AXABcAHIAaQBnAGgAdAB9ACsAXABcAGwAZQBmAHQAewBXAF8AdABcAFwAdABpAG0AZQBzAFwAXABsAGUAZgB0AFsAQwBPAEQAXwB7AGkAbgB9AFwAXAB0AGkAbQBlAHMAKABGAF8AewBzAGwAdQBkAGcAZQB9AC0ARgBfAHsAcgBlAG0AbwB2AGUAZAB9ACkAXABcAHIAaQBnAGgAdABdAFwAXAB0AGkAbQBlAHMAIABDAEYAXwB7AHMAbAB1AGQAZwBlACwAdAB9AFwAXAB0AGkAbQBlAHMAIABFAEYAXwB7AHMAbAB1AGQAZwBlAH0AXABcAHIAaQBnAGgAdAB9AC0AXABcAGwAZQBmAHQAewA2AC4ANwA4ADQAXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQA0AH0AXABcAHQAaQBtAGUAcwAgAFwAXABsAGUAZgB0AFsAIABRAF8AewBjAGEAcAB9ACsAUQBfAHsAZgBsAGEAcgBlAGQAfQArAFEAXwB7AG8AdQB0AH0AXABcAHIAaQBnAGgAdABdAFwAXAByAGkAZwBoAHQAfQArAFwAXABsAGUAZgB0AHsAUQBfAHsAZgBsAGEAcgBlAGQAfQBcAFwAdABpAG0AZQBzACAAXABcAGwAZQBmAHQAWwAgAEUAQwBfAHsAZgBsAGEAcgBlAGQAfQBcAFwAdABpAG0AZQBzACAARQBGAF8AewBmAGwAYQByAGUAZAAsAEMASAA0AH0AXABcAHIAaQBnAGgAdABdAFwAXAByAGkAZwBoAHQAfQBcAFwAcgBpAGcAaAB0AH0AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEAMQBfADEAXwAxAF8AMQBfAF8AMQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBXAGEAcwB0AGUAdwBhAHQAZQByAFQAcgBlAGEAdABtAGUAbgB0AF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADUALAAgADQALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBfAHQAXAAiACwAIABcACIAcQB1AGEAbgB0AGkAdAB5ACAAbwBmACAAdwBhAHMAdABlAHcAYQB0AGUAcgAgAHQAcgBlAGEAdABlAGQAIABhAHQAIABmAGEAYwBpAGwAaQB0AHkAIAB0AHkAcABlACAAdABcACIALAAgAFwAIgBtADMAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAE8ARABfAGkAbgBcACIALAAgAFwAIgBhAHYAZQByAGEAZwBlACAAaQBuAGwAZQB0ACAAQwBoAGUAbQBpAGMAYQBsACAATwB4AHkAZwBlAG4AIABEAGUAbQBhAG4AZAAgAGMAbwBuAGMAZQBuAHQAcgBhAHQAaQBvAG4AIABvAGYAIAB3AGEAcwB0AGUAdwBhAHQAZQByAFwAIgAsACAAXAAiAGsAZwAgAEMATwBEAC8AbQAzAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBfAHMAbAB1AGQAZwBlAFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAEMATwBEACAAcgBlAG0AbwB2AGUAZAAgAGYAcgBvAG0AIAB3AGEAcwB0AGUAdwBhAHQAZQByACAAYQBzACAAcwBsAHUAZABnAGUAXAAiACwAIABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPAEQAXwBvAHUAdABcACIALAAgAFwAIgBhAHYAZQByAGEAZwBlACAAbwB1AHQAbABlAHQAIABDAE8ARAAgAGMAbwBuAGMAZQBuAHQAcgBhAHQAaQBvAG4AIABvAGYAIAB3AGEAcwB0AGUAdwBhAHQAZQByAFwAIgAsACAAXAAiAGsAZwAgAEMATwBEAC8AbQAzAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBGAF8AdwB3AF8AdABcACIALAAgAFwAIgBtAGUAdABoAGEAbgBlACAAYwBvAHIAcgBlAGMAdABpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABmAGEAYwBpAGwAaQB0AHkAIAB0AHkAcABlACAAdAAgAHUAcwBlAGQAIAB0AG8AIAB0AHIAZQBhAHQAIAB3AGEAcwB0AGUAdwBhAHQAZQByAFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARgBfAHcAdwBcACIALAAgAFwAIgBtAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHcAYQBzAHQAZQB3AGEAdABlAHIAXAAiACwAIABcACIAawBnACAAQwBIADQALwBrAGcAIABDAE8ARABcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAXwByAGUAbQBvAHYAZQBkAFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAEMATwBEACAAcgBlAG0AbwB2AGUAZAAgAGYAcgBvAG0AIAB0AGgAZQAgAHcAYQBzAHQAZQB3AGEAdABlAHIAIAB0AHIAZQBhAHQAbQBlAG4AdAAgAGYAYQBjAGkAbABpAHQAeQAgAGEAbgBkACAAdAByAGEAbgBzAGYAZQByAHIAZQBkACAAZQBsAHMAZQB3AGgAZQByAGUAXAAiACwAIABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBGAF8AcwBsAHUAZABnAGUAXwB0AFwAIgAsACAAXAAiAG0AZQB0AGgAYQBuAGUAIABjAG8AcgByAGUAYwB0AGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAGYAYQBjAGkAbABpAHQAeQAgAHQAeQBwAGUAIAB0ACAAdQBzAGUAZAAgAHQAbwAgAHQAcgBlAGEAdAAgAHMAbAB1AGQAZwBlAFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARgBfAHMAbAB1AGQAZwBlAFwAIgAsACAAXAAiAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAcwBsAHUAZABnAGUAXAAiACwAIABcACIAawBnACAAQwBIADQALwBrAGcAIABDAE8ARABcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEAXwBjAGEAcABcACIALAAgAFwAIgBxAHUAYQBuAHQAaQB0AHkAIABvAGYAIABtAGUAdABoAGEAbgBlACAAaQBuACAAcwBsAHUAZABnAGUAIABiAGkAbwBnAGEAcwAgAGMAYQBwAHQAdQByAGUAZAAgAGYAbwByACAAYwBvAG0AYgB1AHMAdABpAG8AbgBcACIALAAgAFwAIgBtADMAIABDAEgANABcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEAXwBmAGwAYQByAGUAZABcACIALAAgAFwAIgBxAHUAYQBuAHQAaQB0AHkAIABvAGYAIABtAGUAdABoAGEAbgBlACAAaQBuACAAcwBsAHUAZABnAGUAIABiAGkAbwBnAGEAcwAgAGYAbABhAHIAZQBkACAAYgB5ACAAdABoAGUAIAB0AHIAZQBhAHQAbQBlAG4AdAAgAGYAYQBjAGkAbABpAHQAeQBcACIALAAgAFwAIgBtADMAIABDAEgANABcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEAXwBvAHUAdABcACIALAAgAFwAIgBxAHUAYQBuAHQAaQB0AHkAIABvAGYAIABtAGUAdABoAGEAbgBlACAAaQBuACAAcwBsAHUAZABnAGUAIABiAGkAbwBnAGEAcwAgAHQAcgBhAG4AcwBmAGUAcgByAGUAZAAgAG8AdQB0ACAAbwBmACAAdABoAGUAIAB0AHIAZQBhAHQAbQBlAG4AdAAgAGYAYQBjAGkAbABpAHQAeQBcACIALAAgAFwAIgBtADMAIABDAEgANABcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUAQwBfAGYAbABhAHIAZQBkAFwAIgAsACAAXAAiAGUAbgBlAHIAZwB5ACAAYwBvAG4AdABlAG4AdAAgAGYAYQBjAHQAbwByACAAbwBmACAAbQBlAHQAaABhAG4AZQAgAGkAbgAgAHMAbAB1AGQAZwBlACAAYgBpAG8AZwBhAHMAIABmAGwAYQByAGUAZABcACIALAAgAFwAIgBHAEoALwBtADMAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAEYAXwBmAGwAYQByAGUAZABDAEgANABcACIALAAgAFwAIgBtAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHMAbAB1AGQAZwBlACAAYgBpAG8AZwBhAHMAIABmAGwAYQByAGUAZABcACIALAAgAFwAIgBrAGcAIABDAEgANAAvAEcASgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAHQAXAAiACwAIABcACIAdAByAGUAYQB0AG0AZQBuAHQAIABmAGEAYwBpAGwAaQB0AHkAIAB0AHkAcABlAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgBWAEUARQBSAEcAXwAxADEAXwAxAF8AMQBfADEAXwBfADEAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AVwBhAHMAdABlAHcAYQB0AGUAcgBUAHIAZQBhAHQAbQBlAG4AdABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ATgAgAFMATwBVAFIAQwBFADoAIABDAGgAYQBuAGcAZQBkACAAdQBuAGkAdABzACAAbwBmACAARQBGAF8AdwB3ACwAIABFAEYAXwBTAGwAdQBkAGcAZQAgAGEAbgBkACAARQBGAF8AZgBsAGEAcgBlAGQAIABmAHIAbwBtACAAQwBPADIAZQAgAHQAbwAgAEMASAA0ACAAdABvACAAbQBhAHQAYwBoACAAZABhAHQAYQAgAGkAbgAgAFQAYQBiAGwAZQAgAFwAIgApADsAIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAGEAcwB0AGUAdwBhAHQAZQByAF8AUwBvAHUAcgBjAGUARABhAHQAYQAiACwAIgB0AGUAeAB0ACIAOgAiAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AVABhAGIAbABlACAAQQAuADQALgAxAC4AMwA6ACAATQBlAHQAaABhAG4AZQAgAGMAbwByAHIAZQBjAHQAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAdAByAGUAYQB0AG0AZQBuAHQAIABmAGEAYwBpAGwAaQB0AHkAIAB0AHkAcABlACAAdAAgAHUAcwBlAGQAIAB0AG8AIAB0AHIAZQBhAHQAIAB3AGEAcwB0AGUAdwBhAHQAZQByACAAKABmAHIAYQBjAHQAaQBvAG4AKQAgACgAQwBGAHcAdwAsAHQAKQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBDAG8AcgByAGUAYwB0AGkAbwBuAEYAYQBjAHQAbwByAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBUAGkAdABsAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBNAGUAdABoAGEAbgBlACAAYwBvAHIAcgBlAGMAdABpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB0AHIAZQBhAHQAbQBlAG4AdAAgAGYAYQBjAGkAbABpAHQAeQAgAHQAeQBwAGUAIAB0ACAAdQBzAGUAZAAgAHQAbwAgAHQAcgBlAGEAdAAgAHcAYQBzAHQAZQB3AGEAdABlAHIAXAAiACkAKQA7AFwAbgBcAG4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBDAG8AcgByAGUAYwB0AGkAbwBuAEYAYQBjAHQAbwByAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBWAGEAcgBpAGEAYgBsAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBDAEYAdwB3ACwAdABcACIAKQApADsAXABuAFwAbgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEMAbwByAHIAZQBjAHQAaQBvAG4ARgBhAGMAdABvAHIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFUAbgBpAHQAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACkAKQA7AFwAbgBcAG4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBDAG8AcgByAGUAYwB0AGkAbwBuAEYAYQBjAHQAbwByAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBTAG8AdQByAGMAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgA0AC4AMQAuADMAXAAiACkAKQA7AFwAbgBcAG4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBDAG8AcgByAGUAYwB0AGkAbwBuAEYAYQBjAHQAbwByAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBEAGEAdABhAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADIALABcAG4AIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIABcACIARgBhAGMAaQBsAGkAdAB5ACAAdAB5AHAAZQAgAHQAXAAiACwAIABcACIAQwBGAHcAdwAsAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIATQBhAG4AYQBnAGUAZAAgAGEAZQByAG8AYgBpAGMAIAB0AHIAZQBhAHQAbQBlAG4AdABcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBVAG4AbQBhAG4AYQBnAGUAZAAgAGEAZQByAG8AYgBpAGMAIAB0AHIAZQBhAHQAbQBlAG4AdABcACIALAAgADAALgAzADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQQBuAGEAZQByAG8AYgBpAGMAIABkAGkAZwBlAHMAdABvAHIALwByAGUAYQBjAHQAbwByAFwAIgAsACAAMAAuADgAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBTAGgAYQBsAGwAbwB3ACAAYQBuAGEAZQByAG8AYgBpAGMAIABsAGEAZwBvAG8AbgAgACgAZCIgADIAIABtACkAXAAiACwAIAAwAC4AMgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEQAZQBlAHAAIABhAG4AYQBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuACAAKABcAHUAMAAwADMAZQAgADIAbQApAFwAIgAsACAAMAAuADgAXABuACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AKQApACkAOwBcAG4AXABuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUAQwBvAHIAcgBlAGMAdABpAG8AbgBGAGEAYwB0AG8AcgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBcACIAKQApADsAXABuAFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgBUAGEAYgBsAGUAIABBAC4ANAAuADEALgA0ADoAIABNAGUAdABoAGEAbgBlACAAYwBvAHIAcgBlAGMAdABpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB0AHIAZQBhAHQAbQBlAG4AdAAgAGYAYQBjAGkAbABpAHQAeQAgAHQAeQBwAGUAIAB0ACAAdQBzAGUAZAAgAHQAbwAgAHQAcgBlAGEAdAAgAHMAbAB1AGQAZwBlACAAKABmAHIAYQBjAHQAaQBvAG4AKQAgACgAQwBGAHMAbAB1AGQAZwBlACwAdAApAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEMAbwByAHIAZQBjAHQAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAXwBUAGkAdABsAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBNAGUAdABoAGEAbgBlACAAYwBvAHIAcgBlAGMAdABpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB0AHIAZQBhAHQAbQBlAG4AdAAgAGYAYQBjAGkAbABpAHQAeQAgAHQAeQBwAGUAIAB0ACAAdQBzAGUAZAAgAHQAbwAgAHQAcgBlAGEAdAAgAHMAbAB1AGQAZwBlAFwAIgApACkAOwBcAG4AXABuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUAQwBvAHIAcgBlAGMAdABpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBfAFYAYQByAGkAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEMARgBzAGwAdQBkAGcAZQAsAHQAXAAiACkAKQA7AFwAbgBcAG4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBDAG8AcgByAGUAYwB0AGkAbwBuAEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAF8AVQBuAGkAdABcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIAKQApADsAXABuAFwAbgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEMAbwByAHIAZQBjAHQAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAXwBTAG8AdQByAGMAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgA0AC4AMQAuADQAXAAiACkAKQA7AFwAbgBcAG4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBDAG8AcgByAGUAYwB0AGkAbwBuAEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAF8ARABhAHQAYQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAAyACwAXABuACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEYAYQBjAGkAbABpAHQAeQAgAHQAeQBwAGUAIAB0AFwAIgAsACAAXAAiAEMARgBzAGwAdQBkAGcAZQAsAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIATQBhAG4AYQBnAGUAZAAgAGEAZQByAG8AYgBpAGMAIAB0AHIAZQBhAHQAbQBlAG4AdABcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBVAG4AbQBhAG4AYQBnAGUAZAAgAGEAZQByAG8AYgBpAGMAIAB0AHIAZQBhAHQAbQBlAG4AdABcACIALAAgADAALgAzADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQQBuAGEAZQByAG8AYgBpAGMAIABkAGkAZwBlAHMAdABvAHIALwByAGUAYQBjAHQAbwByAFwAIgAsACAAMAAuADgAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBTAGgAYQBsAGwAbwB3ACAAYQBuAGEAZQByAG8AYgBpAGMAIABsAGEAZwBvAG8AbgAgACgAZCIgADIAIABtACkAXAAiACwAIAAwAC4AMgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEQAZQBlAHAAIABhAG4AYQBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuACAAKABcAHUAMAAwADMAZQAgADIAbQApAFwAIgAsACAAMAAuADgAXABuACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AKQApACkAOwBcAG4AXABuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUAQwBvAHIAcgBlAGMAdABpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AVABpAHQAbABlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIATQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB3AGEAcwB0AGUAdwBhAHQAZQByAFwAIgApACkAOwBcAG4AXABuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBWAGEAcgBpAGEAYgBsAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBFAEYAdwB3AFwAIgApACkAOwBcAG4AXABuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBVAG4AaQB0AFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAawBnACAAQwBIADQAIAAvACAAawBnACAAQwBPAEQAXAAiACkAKQA7AFwAbgBcAG4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAMQAxAC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAcwBcACIAKQApADsAXABuAFwAbgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBXAGEAcwB0AGUAdwBhAHQAZQByAF8ARABhAHQAYQBcAG4APQBMAEEATQBCAEQAQQAoACAAMAAuADIANQApADsAXABuAFwAbgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAF8AVABpAHQAbABlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIATQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABzAGwAdQBkAGcAZQBcACIAKQApADsAXABuAFwAbgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBfAFYAYQByAGkAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEUARgBzAGwAdQBkAGcAZQBcACIAKQApADsAXABuAFwAbgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBfAFUAbgBpAHQAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBrAGcAIABDAEgANAAgAC8AIABrAGcAIABDAE8ARABcACIAKQApADsAXABuAFwAbgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBfAFMAbwB1AHIAYwBlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAMQAxAC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAcwBcACIAKQApADsAXABuAFwAbgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBfAEQAYQB0AGEAXABuAD0ATABBAE0AQgBEAEEAKAAwAC4AMgA1ACkAOwBcAG4AXABuAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4AVwBhAHMAdABlAF8ARQBuAGUAcgBnAHkAQwBvAG4AdABlAG4AdABGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBCAGkAbwBnAGEAcwBGAGwAYQByAGUAZABfAFQAaQB0AGwAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEUAbgBlAHIAZwB5ACAAYwBvAG4AdABlAG4AdAAgAGYAYQBjAHQAbwByACAAbwBmACAAcwBsAHUAZABnAGUAIABiAGkAbwBnAGEAcwAgAGYAbABhAHIAZQBkAFwAIgApACkAOwBcAG4AXABuAFcAYQBzAHQAZQBfAEUAbgBlAHIAZwB5AEMAbwBuAHQAZQBuAHQARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAQgBpAG8AZwBhAHMARgBsAGEAcgBlAGQAXwBWAGEAcgBpAGEAYgBsAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBFAEMAZgBsAGEAcgBlAGQAXAAiACkAKQA7AFwAbgBcAG4AVwBhAHMAdABlAF8ARQBuAGUAcgBnAHkAQwBvAG4AdABlAG4AdABGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBCAGkAbwBnAGEAcwBGAGwAYQByAGUAZABfAFUAbgBpAHQAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBHAEoAIAAvACAAbQAzAFwAIgApACkAOwBcAG4AXABuAFcAYQBzAHQAZQBfAEUAbgBlAHIAZwB5AEMAbwBuAHQAZQBuAHQARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAQgBpAG8AZwBhAHMARgBsAGEAcgBlAGQAXwBTAG8AdQByAGMAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADEAMQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0AHMAXAAiACkAKQA7AFwAbgBcAG4AVwBhAHMAdABlAF8ARQBuAGUAcgBnAHkAQwBvAG4AdABlAG4AdABGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBCAGkAbwBnAGEAcwBGAGwAYQByAGUAZABfAEQAYQB0AGEAXABuAD0ATABBAE0AQgBEAEEAKAAwAC4AMAAzADcANwApADsAXABuAFwAbgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAEIAaQBvAGcAYQBzAEYAbABhAHIAZQBkAF8AVABpAHQAbABlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIATQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABzAGwAdQBkAGcAZQAgAGIAaQBvAGcAYQBzACAAZgBsAGEAcgBlAGQAXAAiACkAKQA7AFwAbgBcAG4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAQgBpAG8AZwBhAHMARgBsAGEAcgBlAGQAXwBWAGEAcgBpAGEAYgBsAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBFAEYAZgBsAGEAcgBlAGQALABDAEgANABcACIAKQApADsAXABuAFwAbgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBCAGkAbwBnAGEAcwBGAGwAYQByAGUAZABfAFUAbgBpAHQAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBrAGcAIABDAEgANAAgAC8AIABHAEoAXAAiACkAKQA7AFwAbgBcAG4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAQgBpAG8AZwBhAHMARgBsAGEAcgBlAGQAXwBTAG8AdQByAGMAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADEAMQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0AHMAXAAiACkAKQA7AFwAbgBcAG4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAQgBpAG8AZwBhAHMARgBsAGEAcgBlAGQAXwBEAGEAdABhAFwAbgA9AEwAQQBNAEIARABBACgAMAAuADIAMgA4ADkAKQA7AFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgBXAGEAcwB0AGUAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAQgBpAG8AZwBhAHMARgBsAGEAcgBlAGQAXwBUAGkAdABsAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHMAbAB1AGQAZwBlACAAYgBpAG8AZwBhAHMAIABmAGwAYQByAGUAZABcACIAKQApADsAXABuAFwAbgBXAGEAcwB0AGUAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAQgBpAG8AZwBhAHMARgBsAGEAcgBlAGQAXwBWAGEAcgBpAGEAYgBsAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBFAEYAZgBsAGEAcgBlAGQALABOADIATwBcACIAKQApADsAXABuAFwAbgBXAGEAcwB0AGUAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAQgBpAG8AZwBhAHMARgBsAGEAcgBlAGQAXwBVAG4AaQB0AFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAawBnACAATgAyAE8AIAAvACAARwBKAFwAIgApACkAOwBcAG4AXABuAFcAYQBzAHQAZQBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBCAGkAbwBnAGEAcwBGAGwAYQByAGUAZABfAFMAbwB1AHIAYwBlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAMQAxAC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAcwBcACIAKQApADsAXABuAFwAbgBXAGEAcwB0AGUAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAQgBpAG8AZwBhAHMARgBsAGEAcgBlAGQAXwBEAGEAdABhAFwAbgA9AEwAQQBNAEIARABBACgAMQAuADEAMwAyAGUALQA0ACkAOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAGEAcwB0AGUAdwBhAHQAZQByAF8ATgAyAE8AXwBFAHEAdQBhAHQAaQBvAG4AcwAiACwAIgB0AGUAeAB0ACIAOgAiAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AMQAxAC4AMQA6ACAAVwBhAHMAdABlAHcAYQB0AGUAcgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AMQAxAC4AMQAuADMALgAxACAATQBlAHQAaABvAGQAIAAxACAALQAgAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABvAG4AcwBpAHQAZQAgAFcAYQBzAHQAZQB3AGEAdABlAHIAIABNAGEAbgBhAGcAZQBtAGUAbgB0AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8AMQAxAF8AMQBfADMAXwAxAF8AXwAxAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBGAGwAYQByAGUAZABCAGkAbwBnAGEAcwBcAG4ATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAGYAbABhAHIAZQBkACAAYgBpAG8AZwBhAHMAXABuAEUAXwBOADIATwBcAG4AdAAgAE4AMgBPAFwAbgBFAF8AewBOADIATwB9AD0AXABcAGYAcgBhAGMAewBRAF8AewBmAGwAYQByAGUAZAB9AH0AewAxADAAMAAwAH0AXABcAHQAaQBtAGUAcwAgAEUARgBfAHsAZgBsAGEAcgBlAGQALABOADIATwB9AFwAbgBRAF8AZgBsAGEAcgBlAGQAIAA9ACAAdgBvAGwAdQBtAGUAIABvAGYAIABiAGkAbwBnAGEAcwAgAGYAbABhAHIAZQBkACAAKABtADMAIABvAHIAIABHAEoAKQBcAG4ARQBGAF8AZgBsAGEAcgBlAGQAXwBOADIATwAgAD0AIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAGYAbABhAHIAZQBkACAAYgBpAG8AZwBhAHMAIAAoAGsAZwAgAE4AMgBPAC8ARwBKACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8AMQAxAF8AMQBfADMAXwAxAF8AXwAxAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBGAGwAYQByAGUAZABCAGkAbwBnAGEAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABRAF8AZgBsAGEAcgBlAGQALAAgAEUAQwBfAGYAbABhAHIAZQBkACwAIABFAEYAXwBmAGwAYQByAGUAZABOADIATwAsAFwAbgAgACAAIAAgACgAUQBfAGYAbABhAHIAZQBkACAALwAgADEAMAAwADAAKQAgACoAIAAoAEUAQwBfAGYAbABhAHIAZQBkACAAKgAgAEUARgBfAGYAbABhAHIAZQBkAE4AMgBPACkAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADEAXwAxAF8AMwBfADEAXwBfADEAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEYAbABhAHIAZQBkAEIAaQBvAGcAYQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAZgBsAGEAcgBlAGQAIABiAGkAbwBnAGEAcwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQAxAF8AMQBfADMAXwAxAF8AXwAxAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBGAGwAYQByAGUAZABCAGkAbwBnAGEAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBfAE4AMgBPAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADEAXwAxAF8AMwBfADEAXwBfADEAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEYAbABhAHIAZQBkAEIAaQBvAGcAYQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAE4AMgBPAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADEAXwAxAF8AMwBfADEAXwBfADEAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEYAbABhAHIAZQBkAEIAaQBvAGcAYQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADEAMQAuADEALgAzAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAxACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEAMQBfADEAXwAzAF8AMQBfAF8AMQBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ARgBsAGEAcgBlAGQAQgBpAG8AZwBhAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEAMQBfADEAXwAzAF8AMQBfAF8AMQBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ARgBsAGEAcgBlAGQAQgBpAG8AZwBhAHMAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAF8AewBOADIATwB9AD0AXABcAGYAcgBhAGMAewBRAF8AewBmAGwAYQByAGUAZAB9AH0AewAxADAAMAAwAH0AXABcAHQAaQBtAGUAcwAgAFwAXABsAGUAZgB0AFsARQBDAF8AewBmAGwAYQByAGUAZAB9ACAAXABcAHQAaQBtAGUAcwAgAEUARgBfAHsAZgBsAGEAcgBlAGQALABOADIATwB9AFwAXAByAGkAZwBoAHQAXQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQAxAF8AMQBfADMAXwAxAF8AXwAxAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBGAGwAYQByAGUAZABCAGkAbwBnAGEAcwBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAANAAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBRAF8AZgBsAGEAcgBlAGQAXAAiACwAIABcACIAdgBvAGwAdQBtAGUAIABvAGYAIABiAGkAbwBnAGEAcwAgAGYAbABhAHIAZQBkAFwAIgAsACAAXAAiAG0AMwBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUAQwBfAGYAbABhAHIAZQBkAFwAIgAsACAAXAAiAGUAbgBlAHIAZwB5ACAAYwBvAG4AdABlAG4AdAAgAGYAYQBjAHQAbwByACAAbwBmACAAcwBsAHUAZABnAGUAIABiAGkAbwBnAGEAcwAgAGYAbABhAHIAZQBkAFwAIgAsACAAXAAiAEcASgAvAG0AMwBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARgBfAGYAbABhAHIAZQBkAE4AMgBPAFwAIgAsACAAXAAiAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAZgBsAGEAcgBlAGQAIABiAGkAbwBnAGEAcwBcACIALAAgAFwAIgBrAGcAIABOADIATwAvAEcASgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuACIAfQBdACwAIgBwAHIAbwBqAGUAYwB0AE4AYQBtAGUAcwAiADoAWwAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBBAHAAcABlAG4AZABpAGMAZQBzACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAFIAbwB3AFMAdABhAHIAdABOAHUAbQBiAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAEMAbwBsAHUAbQBuAFMAdABhAHIAdABOAHUAbQBiAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgByAGEAeQBJAG4AVABhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAFQAdwBvAEMAbwBsAHUAbQBuAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATwBuAGUAQwBvAGwAdQBtAG4AQQBuAGQASABlAGEAZABlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AUwBwAGwAaQB0AFMAdAByAGkAbgBnAEkAbgB0AG8AQQByAHIAYQB5ACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEMAbABpAG0AYQB0AGUAWgBvAG4AZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABJAHQAZQBtAEYAcgBvAG0ATQBpAG4ATQBhAHgAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AUwB1AG0AUQB1AGEAbgB0AGkAdAB5AEYAcgBvAG0AQwByAGkAdABlAHIAaQBhACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBzACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAFAAZQByAGkAbwBkAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBGAHUAbgBjAHQAaQBvAG4ATgBhAG0AZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABOADIATwBFAEYARgByAG8AbQBQAHIAbwBkAEkAcgByAGkAZwBhAHQAaQBvAG4AUgBhAGkAbgBmAGEAbABsACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ARwBlAHQARgByAGEAYwBXAEUAVAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBDAG8AbgB2AGUAcgB0AFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAFQAbwBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQAxAF8AMQBfADEAXwAxAF8AXwAxAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFcAYQBzAHQAZQB3AGEAdABlAHIAVAByAGUAYQB0AG0AZQBuAHQAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEAMQBfADEAXwAxAF8AMQBfAF8AMQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBXAGEAcwB0AGUAdwBhAHQAZQByAFQAcgBlAGEAdABtAGUAbgB0AF8AVABpAHQAbABlACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADEAXwAxAF8AMQBfADEAXwBfADEAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AVwBhAHMAdABlAHcAYQB0AGUAcgBUAHIAZQBhAHQAbQBlAG4AdABfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQAxAF8AMQBfADEAXwAxAF8AXwAxAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFcAYQBzAHQAZQB3AGEAdABlAHIAVAByAGUAYQB0AG0AZQBuAHQAXwBVAG4AaQB0ACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADEAXwAxAF8AMQBfADEAXwBfADEAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AVwBhAHMAdABlAHcAYQB0AGUAcgBUAHIAZQBhAHQAbQBlAG4AdABfAFMAbwB1AHIAYwBlACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADEAXwAxAF8AMQBfADEAXwBfADEAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AVwBhAHMAdABlAHcAYQB0AGUAcgBUAHIAZQBhAHQAbQBlAG4AdABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADEAXwAxAF8AMQBfADEAXwBfADEAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AVwBhAHMAdABlAHcAYQB0AGUAcgBUAHIAZQBhAHQAbQBlAG4AdABfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEAMQBfADEAXwAxAF8AMQBfAF8AMQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBXAGEAcwB0AGUAdwBhAHQAZQByAFQAcgBlAGEAdABtAGUAbgB0AF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEAMQBfADEAXwAxAF8AMQBfAF8AMQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBXAGEAcwB0AGUAdwBhAHQAZQByAFQAcgBlAGEAdABtAGUAbgB0AF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEMAbwByAHIAZQBjAHQAaQBvAG4ARgBhAGMAdABvAHIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFQAaQB0AGwAZQAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUAQwBvAHIAcgBlAGMAdABpAG8AbgBGAGEAYwB0AG8AcgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBDAG8AcgByAGUAYwB0AGkAbwBuAEYAYQBjAHQAbwByAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBVAG4AaQB0ACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBDAG8AcgByAGUAYwB0AGkAbwBuAEYAYQBjAHQAbwByAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBTAG8AdQByAGMAZQAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUAQwBvAHIAcgBlAGMAdABpAG8AbgBGAGEAYwB0AG8AcgBXAGEAcwB0AGUAdwBhAHQAZQByAF8ARABhAHQAYQAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUAQwBvAHIAcgBlAGMAdABpAG8AbgBGAGEAYwB0AG8AcgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEMAbwByAHIAZQBjAHQAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAXwBUAGkAdABsAGUAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEMAbwByAHIAZQBjAHQAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEMAbwByAHIAZQBjAHQAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAXwBVAG4AaQB0ACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBDAG8AcgByAGUAYwB0AGkAbwBuAEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAF8AUwBvAHUAcgBjAGUAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEMAbwByAHIAZQBjAHQAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAXwBEAGEAdABhACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBDAG8AcgByAGUAYwB0AGkAbwBuAEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AVABpAHQAbABlACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBVAG4AaQB0ACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAEQAYQB0AGEAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBfAFQAaQB0AGwAZQAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAXwBVAG4AaQB0ACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAXwBTAG8AdQByAGMAZQAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAF8ARABhAHQAYQAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFcAYQBzAHQAZQBfAEUAbgBlAHIAZwB5AEMAbwBuAHQAZQBuAHQARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAQgBpAG8AZwBhAHMARgBsAGEAcgBlAGQAXwBUAGkAdABsAGUAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBXAGEAcwB0AGUAXwBFAG4AZQByAGcAeQBDAG8AbgB0AGUAbgB0AEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAEIAaQBvAGcAYQBzAEYAbABhAHIAZQBkAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AVwBhAHMAdABlAF8ARQBuAGUAcgBnAHkAQwBvAG4AdABlAG4AdABGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBCAGkAbwBnAGEAcwBGAGwAYQByAGUAZABfAFUAbgBpAHQAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBXAGEAcwB0AGUAXwBFAG4AZQByAGcAeQBDAG8AbgB0AGUAbgB0AEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAEIAaQBvAGcAYQBzAEYAbABhAHIAZQBkAF8AUwBvAHUAcgBjAGUAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBXAGEAcwB0AGUAXwBFAG4AZQByAGcAeQBDAG8AbgB0AGUAbgB0AEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAEIAaQBvAGcAYQBzAEYAbABhAHIAZQBkAF8ARABhAHQAYQAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAEIAaQBvAGcAYQBzAEYAbABhAHIAZQBkAF8AVABpAHQAbABlACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAQgBpAG8AZwBhAHMARgBsAGEAcgBlAGQAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBCAGkAbwBnAGEAcwBGAGwAYQByAGUAZABfAFUAbgBpAHQAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBCAGkAbwBnAGEAcwBGAGwAYQByAGUAZABfAFMAbwB1AHIAYwBlACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAQgBpAG8AZwBhAHMARgBsAGEAcgBlAGQAXwBEAGEAdABhACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AVwBhAHMAdABlAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAEIAaQBvAGcAYQBzAEYAbABhAHIAZQBkAF8AVABpAHQAbABlACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AVwBhAHMAdABlAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAEIAaQBvAGcAYQBzAEYAbABhAHIAZQBkAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AVwBhAHMAdABlAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAEIAaQBvAGcAYQBzAEYAbABhAHIAZQBkAF8AVQBuAGkAdAAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFcAYQBzAHQAZQBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBCAGkAbwBnAGEAcwBGAGwAYQByAGUAZABfAFMAbwB1AHIAYwBlACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AVwBhAHMAdABlAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAEIAaQBvAGcAYQBzAEYAbABhAHIAZQBkAF8ARABhAHQAYQAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8ATgAyAE8AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEAMQBfADEAXwAzAF8AMQBfAF8AMQBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ARgBsAGEAcgBlAGQAQgBpAG8AZwBhAHMAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAE4AMgBPAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADEAXwAxAF8AMwBfADEAXwBfADEAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEYAbABhAHIAZQBkAEIAaQBvAGcAYQBzAF8AVABpAHQAbABlACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBOADIATwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQAxAF8AMQBfADMAXwAxAF8AXwAxAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBGAGwAYQByAGUAZABCAGkAbwBnAGEAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8ATgAyAE8AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEAMQBfADEAXwAzAF8AMQBfAF8AMQBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ARgBsAGEAcgBlAGQAQgBpAG8AZwBhAHMAXwBVAG4AaQB0ACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBOADIATwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQAxAF8AMQBfADMAXwAxAF8AXwAxAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBGAGwAYQByAGUAZABCAGkAbwBnAGEAcwBfAFMAbwB1AHIAYwBlACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBOADIATwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQAxAF8AMQBfADMAXwAxAF8AXwAxAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBGAGwAYQByAGUAZABCAGkAbwBnAGEAcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBOADIATwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQAxAF8AMQBfADMAXwAxAF8AXwAxAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBGAGwAYQByAGUAZABCAGkAbwBnAGEAcwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAE4AMgBPAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADEAXwAxAF8AMwBfADEAXwBfADEAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEYAbABhAHIAZQBkAEIAaQBvAGcAYQBzAF8AQQByAGcAdQBtAGUAbgB0AHMAIgBdACwAIgBsAG8AYwBhAGwAZQAiADoAewAiAGwAaQBzAHQAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgByAG8AdwBTAGUAcABhAHIAYQB0AG8AcgAiADoAIgA7ACIALAAiAGMAbwBsAHUAbQBuAFMAZQBwAGEAcgBhAHQAbwByACIAOgAiACwAIgAsACIAdABoAG8AdQBzAGEAbgBkAHMAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgB0AGgAbwB1AHMAYQBuAGQAcwBQAG8AcwBpAHQAaQBvAG4AcwAiADoAWwAzAF0ALAAiAGQAZQBjAGkAbQBhAGwAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALgAiACwAIgBkAGEAdABlAE8AcgBkAGUAcgAiADoAIgBEAE0AWQAiACwAIgBjAHUAcgByAGUAbgBjAHkAUwB5AG0AYgBvAGwAIgA6ACIAJAAiACwAIgBpAHMAQwB1AHIAcgBlAG4AYwB5AFMAeQBtAGIAbwBsAEwAZQBhAGQAIgA6AHQAcgB1AGUALAAiAGkAcwBDAHUAcgByAGUAbgBjAHkAUwBlAHAAQgB5AFMAcABhAGMAZQAiADoAZgBhAGwAcwBlACwAIgByAG8AdwBMAGUAdAB0AGUAcgAiADoAIgBSACIALAAiAGMAbwBsAHUAbQBuAEwAZQB0AHQAZQByACIAOgAiAEMAIgAsACIAcgBjAEwAZQBmAHQAQgByAGEAYwBrAGUAdAAiADoAIgBbACIALAAiAHIAYwBSAGkAZwBoAHQAQgByAGEAYwBrAGUAdAAiADoAIgBdACIALAAiAHMAdABhAHQAZQBtAGUAbgB0AFMAZQBwAGEAcgBhAHQAbwByACIAOgAiADsAIgAsACIAbABvAGMAYQBsAGUATgBhAG0AZQAiADoAIgBlAG4ALQB1AHMAIgB9AH0A</AFEJSONBlob>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100ACB660BB23738846A00119B5826AC974" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3e3613359d4ae7f6bda6c57be713f101">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="7291119c-fce9-4911-96ae-b800be5dccd8" xmlns:ns3="09eef6d6-daa8-4301-8f9f-b1ec38079286" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="87491bfad7f11426ad96486e70428b3e" ns2:_="" ns3:_="">
     <xsd:import namespace="7291119c-fce9-4911-96ae-b800be5dccd8"/>
@@ -13972,11 +13977,15 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
-<AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgAvAC8AIAAtAC0ALQAgAFcAbwByAGsAYgBvAG8AawAgAG0AbwBkAHUAbABlACAALQAtAC0AXABuAC8ALwAgAEEAIABmAGkAbABlACAAbwBmACAAbgBhAG0AZQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAG8AZgAgAHQAaABlACAAZgBvAHIAbQA6AFwAbgAvAC8AIAAgACAAIABuAGEAbQBlACAAPQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AOwBcAG4AXABuACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhACIALAAiAHQAZQB4AHQAIgA6ACIALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgBTAG8AdQByAGMAZQAgAGQAYQB0AGEAIAB0AGgAYQB0ACAAaQBzACAAYwBvAG0AbQBvAG4AIABhAGMAcgBvAHMAcwAgAGEAbABsACAAZQBuAHQAZQByAHAAcgBpAHMAZQAgAHQAeQBwAGUAcwBcAG4ARQB4AGMAZQBsACAAbQBvAGQAdQBsAGUAIABuAGEAbQBlADoAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFMAbwB1AHIAYwBlADoAIABOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQBcAG4ATgBJAFIAXwAyADAAMgAzAF8AVgBvAGwAMQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXABuAHAAIAA9ACAAZABlAG4AcwBpAHQAeQAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAIAAoADAALgA2ADcAOAA0ACAAawBnAC8AbQAzACkAXABuAFQAYQBrAGUAbgAgAGYAcgBvAG0AIAB0AGgAZQAgAE4AYQB0AGkAbwBuAGEAbAAgAEcAcgBlAGUAbgBoAG8AdQBzAGUAIABhAG4AZAAgAEUAbgBlAHIAZwB5ACAAUgBlAHAAbwByAHQAaQBuAGcAIABcAG4AKABNAGUAYQBzAHUAcgBlAG0AZQBuAHQAKQAgAEQAZQB0AGUAcgBtAGkAbgBhAHQAaQBvAG4AIAAyADAAMAA4AFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHAAIAA9ACAAZABlAG4AcwBpAHQAeQAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcALwBtADMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgADIAMAAyADMAIABWAG8AbAB1AG0AZQAgADEAOgAgAEUAcQB1AGEAdABpAG8AbgBzACAAMwAuAEIALgAxAGEAXwAyACwAIAAzAC4AQgAuADEAYwBfADIALAAgADMALgBCAC4AMwBfADEALAAgADMALgBCAC4ANABnAF8AMgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAMAAuADYANwA4ADQAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAFwAbgBDAGcAIAA9ACAANAA0AC8AMgA4ACAAZgBhAGMAdABvAHIAIAB0AG8AIABjAG8AbgB2AGUAcgB0ACAAZQBsAGUAbQBlAG4AdABhAGwAIABtAGEAcwBzACAAbwBmACAATgAyAE8AIAB0AG8AIABtAG8AbABlAGMAdQBsAGEAcgAgAG0AYQBzAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABOADIATwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBDAGcATgAyAE8AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAYQBjAHQAbwByAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgADIAMAAyADMAIABWAG8AbAB1AG0AZQAgADEAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgANAA0AC8AMgA4ACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAFwAbgBGAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABnAGEAcwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgBhAGMAdABvAHIAIAB0AG8AIABjAG8AbgB2AGUAcgB0ACAAZQBsAGUAbQBlAG4AdABhAGwAIABtAGEAcwBzACAAbwBmACAAZwBhAHMAIAB0AG8AIABtAG8AbABlAGMAdQBsAGEAcgAgAG0AYQBzAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBDAGcAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgBhAGMAdABvAHIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFgAWABYAFgAWABYAFgAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADgALAAgADQALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAYQBzAFwAIgAsACAAXAAiAEMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBcACIALAAgAFwAIgBDAG8AbgB2AGUAcgBzAGkAbwBuACAAZgBhAGMAdABvAHIAIAAxAFwAIgAsACAAXAAiAEMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgADIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyAFwAIgAsACAAXAAiADQANAAvADEAMgBcACIALAAgADQANAAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMASAA0AFwAIgAsACAAXAAiADEANgAvADEAMgBcACIALAAgADEANgAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AMgBPAFwAIgAsACAAXAAiADQANAAvADIAOABcACIALAAgADQANAAsACAAMgA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB4AFwAIgAsACAAXAAiADQANgAvADEANABcACIALAAgADQANgAsACAAMQA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwBcACIALAAgAFwAIgAyADgALwAxADIAXAAiACwAIAAyADgALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAE8AMgAgAEwAaQBtAGUAXAAiACwAIABcACIANAA0AC8AMQAyAFwAIgAsACAANAA0ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBNAFYATwBDAFwAIgAsACAAXAAiADEANAAvADEAMgBcACIALAAgADEANAAsACAAMQAyAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABOADIATwBcAG4ARwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAGcAcgBlAGUAbgBoAG8AdQBzAGUAIABnAGEAcwBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABnAHIAZQBlAG4AaABvAHUAcwBlACAAZwBhAHMAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARwBXAFAATgAyAE8AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgBhAGMAdABvAHIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFgAWABYAFgAWABYAFgAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADgALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAYQBzAFwAIgAsACAAXAAiAEMATwAyAC0AZQAgAGYAYQBjAHQAbwByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAE8AMgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBIADQAXAAiACwAIAAyADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgAyAE8AXAAiACwAIAAyADYANQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAEYANABcACIALAAgADYANgAzADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwAyAEYANgBcACIALAAgADEAMgAyADAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAEYANgBcACIALAAgADIAMgA4ADAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAEYAMwBcACIALAAgADEANwAyADAAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAcwB0AGEAdABlAHMAIABhAG4AZAAgAHQAZQByAHIAaQB0AG8AcgBpAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA5ACwAIAAzACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHQAYQB0AGUALwBUAGUAcgByAGkAdABvAHIAeQBcACIALAAgAFwAIgBDAG8AbQBtAG8AbgAgAE4AYQBtAGUAXAAiACwAIABcACIAQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AZQB3ACAAUwBvAHUAdABoACAAVwBhAGwAZQBzAFwAIgAsACAAXAAiAE4AZQB3ACAAUwBvAHUAdABoACAAVwBhAGwAZQBzAFwAIgAsACAAXAAiAE4AUwBXAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAQwBhAHAAaQB0AGEAbAAgAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAEEAQwBUAFwAIgAsACAAXAAiAEEAQwBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAGkAYwB0AG8AcgBpAGEAXAAiACwAIABcACIAVgBpAGMAdABvAHIAaQBhAFwAIgAsACAAXAAiAFYASQBDAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBRAHUAZQBlAG4AcwBsAGEAbgBkAFwAIgAsACAAXAAiAFEAdQBlAGUAbgBzAGwAYQBuAGQAXAAiACwAIABcACIAUQBMAEQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAbwB1AHQAaAAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFMAbwB1AHQAaAAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFMAQQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQBcACIALAAgAFwAIgBXAEEAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAYQBzAG0AYQBuAGkAYQBcACIALAAgAFwAIgBUAGEAcwBtAGEAbgBpAGEAXAAiACwAIABcACIAVABBAFMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwByAHQAaABlAHIAbgAgAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAE4AbwByAHQAaABlAHIAbgAgAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAE4AVABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQBCAFMAIABTAHQAYQB0AGkAcwB0AGMAYQBsACAAQQByAGUAYQBzACAATABlAHYAZQBsACAANAAgAC0AIABXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAEIAdQByAGUAYQB1ACAAbwBmACAAUwB0AGEAdABpAHMAdABpAGMAcwAgACgAQQBCAFMAKQAgAC0AIABTAHQAYQB0AGkAcwB0AGkAYwBhAGwAIABBAHIAZQBhAHMAIABMAGUAdgBlAGwAIAAyACAALQAgADIAMAAyADEAIAAtACAAUwBoAGEAcABlAGYAaQBsAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADEALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAQQAgADQAIABOAGEAbQBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBCAHUAbgBiAHUAcgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAGEAbgBkAHUAcgBhAGgAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABJAG4AbgBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABOAG8AcgB0AGgAIABFAGEAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAATgBvAHIAdABoACAAVwBlAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAFMAbwB1AHQAaAAgAEUAYQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABTAG8AdQB0AGgAIABXAGUAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAAVwBoAGUAYQB0ACAAQgBlAGwAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhACAALQAgAE8AdQB0AGIAYQBjAGsAIAAoAE4AbwByAHQAaAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAATwB1AHQAYgBhAGMAawAgACgAUwBvAHUAdABoACkAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAdwBlAHQAIABhAG4AZAAgAGQAcgB5ACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAyADoAIABUAHIAYQBuAHMAbABhAHQAaQBuAGcAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBzACAAdABvACAAdwBlAHQAIABhAG4AZAAgAGQAcgB5ACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAdwBhAHIAbQAgAC8AIABjAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAvACAAZAByAHkAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAIABhAG4AZAAgAGgAaQBnAGgAIAB0AGUAbQBwACAAYwBsAGEAcwBzAGUAcwAgAHQAbwAgAGEAYwBjAG8AbQBtAG8AZABhAHQAZQAgAGMAbABpAG0AYQB0AGUAIABzAGMAZQBuAGEAcgBpAG8AcwAgAGUAeABjAGwAdQBkAGUAZAAgAGIAeQAgAFYARQBFAFIARwAgAGMAcgBpAHQAZQByAGkAYQAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAGkAeABlAGQAIAB0AHkAcABvACAALQAgAEMAaABhAG4AZwBlAGQAIABcAHUAMAAwADIANwBGAHIAeQBcAHUAMAAwADIANwAgAHQAbwAgAFwAdQAwADAAMgA3AEQAcgB5AFwAdQAwADAAMgA3AC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADUALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAFcAZQB0ACAAbwByACAARAByAHkAIABaAG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABtAG8AbgB0AGEAbgBlAFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAHcAZQB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABkAHIAeQBcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdABcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAtACAAaABpAGcAaAAgAHQAZQBtAHAAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAaABpAGcAaAAgAHQAZQBtAHAAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA1ACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAB3AGEAcgBtACAALwAgAGMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC8AIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdAAgAGEAbgBkACAAaABpAGcAaAAgAHQAZQBtAHAAIABjAGwAYQBzAHMAZQBzACAAdABvACAAYQBjAGMAbwBtAG0AbwBkAGEAdABlACAAYwBsAGkAbQBhAHQAZQAgAHMAYwBlAG4AYQByAGkAbwBzACAAZQB4AGMAbAB1AGQAZQBkACAAYgB5ACAAVgBFAEUAUgBHACAAYwByAGkAdABlAHIAaQBhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAaQB4AGUAZAAgAHQAeQBwAG8AIABpAG4AIABNAEEAVAAgAHYAYQBsAHUAZQAgAGYAbwByACAAdwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAYwBoAGEAbgBnAGUAZAAgADEAMAAgAHQAbwAgADEAMQAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIABtAGkAbgAgAGEAbgBkACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAZgBvAHIAIABNAEEAVAAsACAATQBBAFAALAAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAIABwAGUAcgAgAHkAZQBhAHIALAAgAGUAbABlAHYAYQB0AGkAbwBuACwAIABNAEEAUAA6AFAARQBUACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlAHMAIABmAHIAbwBtACAAcgBlAGEAbAAgAGMAbABpAG0AYQB0AGUAIABkAGEAdABhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAQQBGACAAYQBjAGMAZQBwAHQAcwAgAHIAYQBpAG4AZgBhAGwAbAAgAGEAcwAgAGEAIABwAHIAbwB4AHkAIABmAG8AcgAgAHAAcgBlAGMAaQBwAGkAdABhAHQAaQBvAG4ALgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOQAsACAAMQA2ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAGwAaQBtAGEAdABlACAAWgBvAG4AZQBcACIALAAgAFwAIgBNAEEAVABcACIALAAgAFwAIgBNAEEAUABcACIALAAgAFwAIgBGAHIAbwBzAHQAIABkAGEAeQBzACAAcABlAHIAIAB5AGUAYQByAFwAIgAsACAAXAAiAEUAbABlAHYAYQB0AGkAbwBuAFwAIgAsACAAXAAiAE0AQQBQADoAUABFAFQAXAAiACwAIABcACIATQBpAG4AIAB0AGUAbQBwAFwAIgAsACAAXAAiAE0AYQB4ACAAdABlAG0AcABcACIALAAgAFwAIgBNAGkAbgAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBNAGEAeAAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBNAGkAbgAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAXAAiACwAIABcACIATQBhAHgAIABmAHIAbwBzAHQAIABkAGEAeQBzAFwAIgAsACAAXAAiAE0AaQBuACAAZQBsAGUAdgBhAHQAaQBvAG4AXAAiACwAIABcACIATQBhAHgAIABlAGwAZQB2AGEAdABpAG8AbgBcACIALAAgAFwAIgBNAGkAbgAgAE0AQQBQADoAUABFAFQAXAAiACwAIABcACIATQBpAG4AIABNAEEAUAA6AFAARQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABtAG8AbgB0AGEAbgBlAFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQA4ACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAwADAAIABtAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAMQA4AC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAANwAsACAAMQAwADAAMAAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAHcAZQB0AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQA4ACAAQwBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADIAMAAwADAAIABtAG0AXAAiACwAIABcACIAZCIgADcAXAAiACwAIABcACIAZCIgADEAMAAwADAAIABtAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAMQA4AC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAyADAAMAAwAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQAuADkAOQA5ACwAIAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAOAAgAEMAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADAAMAAwACAAbQBtACAALQAgAGQiIAAyADAAMAAwACAAbQBtAFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgADEAOAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAAMQAwADAAMAAuADAAMAAxACwAIAAyADAAMAAwACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQAuADkAOQA5ACwAIAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAGQAcgB5AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQA4ACAAQwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAwADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAXAAiACwAIAAxADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgADEALgAwADAAMQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAGQiIAAxAFwAIgAsACAAMQAwAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAgAC0AOQA5ADkAOQA5ADkALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMAAgAEMAIAAtACAAZCIgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxAFwAIgAsACAALQA5ADkAOQA5ADkAOQAsACAAMQAwACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAxAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMAAgAEMAIAAtACAAZCIgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAZCIgADEAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAMQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBBAHAAcABlAG4AZABpAGMAZQBzAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdABlADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AQQBUACAAPQAgAG0AZQBhAG4AIABhAG4AbgB1AGEAbAAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBBAFAAIAA9ACAAbQBlAGEAbgAgAGEAbgBuAHUAYQBsACAAcAByAGUAYwBpAHAAaQB0AGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABFAFQAIAA9ACAAcABvAHQAZQBuAHQAaQBhAGwAIABlAHYAYQBwAG8AdAByAGEAbgBzAHAAaQByAGEAdABpAG8AbgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABBAGQAZABlAGQAIABlAHgAdAByAGEAIABNAEEAVAAgAG0AaQBuACAAYQBuAGQAIABNAEEAVAAgAG0AYQB4ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGMAYQBsAGMAdQBsAGEAdABlACAAegBvAG4AZQAgAGYAcgBvAG0AIAByAGUAYQBsACAAdABlAG0AcABlAHIAYQB0AHUAcgBlACAAZABhAHQAYQAuAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANAAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AHUAcgBlACAAWgBvAG4AZQBcACIALAAgAFwAIgBNAGUAZABpAGEAbgAgAEEAbgBuAHUAYQBsACAAVABlAG0AcABlAHIAYQB0AHUAcgBlACAAKABNAEEAVAApAFwAIgAsACAAXAAiAE0AaQBuACAATQBBAFQAXAAiACwAIABcACIATQBhAHgAIABNAEEAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgAFwAIgBlIiAAMgA2ACAAQwBcACIALAAgADIANgAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIABcACIAMQA1ACAALQAgADIANQAgAEMAXAAiACwAIAAxADUALAAgADIANQAuADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIABcACIAZCIgADEANAAgAEMAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADQALgA5ADkAOQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAAQQBkAGQAZQBkACAAZQB4AHQAcgBhACAAUgBhAGkAbgBmAGEAbABsACAAbQBpAG4AIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAG0AYQB4ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGMAYQBsAGMAdQBsAGEAdABlACAAegBvAG4AZQAgAGYAcgBvAG0AIAByAGUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAZABhAHQAYQAuAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBhAGkAbgBmAGEAbABsACAAWgBvAG4AZQBcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABtAGkAbgBcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABtAGEAeABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbAAgAFwAdQAwADAAMwBlACAANgAwADAAbQBtAFwAIgAsACAANgAwADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATABvAHcAIAByAGEAaQBuAGYAYQBsAGwAXAAiACwAIABcACIAQQBuAG4AdQBhAGwAIAByAGEAaQBuAGYAYQBsAGwAIABkIiAANgAwADAAbQBtAFwAIgAsACAALQA5ADkAOQA5ADkAOQAsACAANgAwADAAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABaAG8AbgBlAFwAIgAsACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAGMAcgBpAHQAZQByAGkAYQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATABlAGEAYwBoAGkAbgBnACAAbwBjAGMAdQByAHMAXAAiACwAIABcACIAowMoADXYX9w12E7cNdhW3DXYW9wpAFwAdQAwADAAMwBlAKMDKAA12DjcNdhH3DAAKQArADXYYNw12FzcNdhW3DXYWdwgADXYZNw12E7cNdhh3DXYUtw12F/cIAAOITXYXNw12FncNdhR3DXYVtw12FvcNdhU3CAANdhQ3DXYTtw12F3cNdhO3DXYUNw12FbcNdhh3DXYZtxcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATABlAGEAYwBoAGkAbgBnACAAZABvAGUAcwAgAG4AbwB0ACAAbwBjAGMAdQByAFwAIgAsACAAXAAiAKMDKAA12F/cNdhO3DXYVtw12FvcKQBkIqMDKAA12DjcNdhH3DAAKQArADXYYNw12FzcNdhW3DXYWdwgADXYZNw12E7cNdhh3DXYUtw12F/cIAAOITXYXNw12FncNdhR3DXYVtw12FvcNdhU3CAANdhQ3DXYTtw12F3cNdhO3DXYUNw12FbcNdhh3DXYZtxcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXABuADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAbgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAEQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcwAgAGkAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAXAAiACwAXAAiAEYAcgBhAGMAVwBFAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFkAZQBzACAALQAgAGkAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwAgAC0AIABuAG8AdAAgAGkAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAXAAiACwAIAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoACgAXAAiAFwAIgApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAGQAYQB0AGEAIABzAGMAbwByAGUAcwAgAGYAbwByACAAcwBjAG8AcABlACAAMwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABYAFgAWABYAFgAWABYAFgAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABhAHQAYQAgAHMAbwB1AHIAYwBlAFwAIgAsACAAXAAiAEQAYQB0AGEAIABzAGMAbwByAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAbgB0AGUAcgBuAGEAdABpAG8AbgBhAGwAIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAcwBjAG8AcABlACAAMwAgAGQAYQB0AGEAYgBhAHMAZQBcACIALAAgADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB0AGEAdABlACAAbwByACAAcgBlAGcAaQBvAG4AYQBsACAAcwBjAG8AcABlACAAMwAgAGQAYQB0AGEAYgBhAHMAZQBcACIALAAgADMAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBtAGkAcwBzAGkAbwBuAHMAIABpAG4AdABlAG4AcwBpAHQAeQAgAGMAYQBsAGMAdQBsAGEAdABlAGQAIABmAHIAbwBtACAAYQBwAHAAcgBvAHYAZQBkACAAbQBlAHQAaABvAGQAXAAiACwAIAA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAZQByAGkAZgBpAGUAZAAgAGMAcgBlAGQAZQBuAHQAaQBhAGwAIABtAGEAdABjAGgAaQBuAGcAIABJAFMATwAxADQAMAA2ADcAXAAiACwAIAA1AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXABuADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAbgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgARABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAVgBvAGwAdQBtAGUAIAAxADoAIABMAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmACAAKAAzAC4ARAAuAGIALgAyACkAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAcgBhAGMATABFAEEAQwBIAFwAIgAsADAALgAyADQAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoACgAXAAiAFwAIgApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABuAGkAdAByAG8AZwBlAG4AIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABuAGkAdAByAG8AZwBlAG4AIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABrAGcAIABOADIATwAtAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgAFYAbwBsAHUAbQBlACAAMQA6ACAARQBxAHUAYQB0AGkAbwBuACAAMwAuAEQALgBCAF8AMQAwAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARgBsAGUAYQBjAGgAXAAiACwAMAAuADAAMQAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoACgAXAAiAFwAIgApACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXABuAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADEAXABuAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAZgBvAHIAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AIAAoAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AKQAgACgARQBGAE4AMgBPACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAGYAbwByACAAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAGsAZwAgAE4AMgBPAC0ATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADIALgAyAC4AMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQA1ACwAIAA1ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABqAFwAIgAsAFwAIgBFAEYATgAyAE8AXAAiACwAIABcACIAUAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAbwBuAGwAeQBcACIALAAgAFwAIgBJAHIAcgBpAGcAYQB0AGkAbwBuACAAbQBlAHQAaABvAGQAXAAiACwAIABcACIAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsADAALgAwADAANQA5ACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwAFwAIgAsADAALgAwADAANwAsACAAXAAiAEMAcgBvAHAAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsADAALgAwADAAMQA4ACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEwAbwB3ACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQBcACIALAAwAC4AMAAwADEAOAAsACAAXAAiAFAAYQBzAHQAdQByAGUAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcAAgACgAbABvAHcAIAByAGEAaQBuAGYAYQBsAGwAKQBcACIALAAwAC4AMAAwADIAOQAsACAAXAAiAEMAcgBvAHAAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAGMAcgBvAHAAIAAoAGgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAKQBcACIALAAwAC4AMAAwADgALAAgAFwAIgBDAHIAbwBwAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIASABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB1AGcAYQByAFwAIgAsADAALgAwADEAOQA5ACwAIABcACIAUwB1AGcAYQByAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AdAB0AG8AbgBcACIALAAwAC4AMAAwADUAMwAsACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAG8AcgB0AGkAYwB1AGwAdAB1AHIAYQBsACAAYwByAG8AcABzAFwAIgAsADAALgAwADAANgA0ACwAIABcACIASABvAHIAdABpAGMAdQBsAHQAdQByAGEAbAAgAGMAcgBvAHAAcwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBpAGMAZQAgACgAYwBvAG4AdABpAG4AdQBvAHUAcwAgAGYAbABvAG8AZABpAG4AZwApAFwAIgAsADAALgAwADAAMwAsACAAXAAiAFIAaQBjAGUAXAAiACwAIABcACIAQwBvAG4AdABpAG4AdQBvAHUAcwAgAGYAbABvAG8AZABpAG4AZwBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBpAGMAZQAgACgAcwBpAG4AZwBsAGUAIABhAG4AZAAgAG0AdQBsAHQAaQBwAGwAZQAgAGQAcgBhAGkAbgBhAGcAZQAsACAAbwByACAAYQBsAHQAZQByAG4AYQB0AGUAIAB3AGUAdAB0AGkAbgBnACAAYQBuAGQAIABkAHIAeQBpAG4AZwApAFwAIgAsADAALgAwADAANQAsACAAXAAiAFIAaQBjAGUAXAAiACwAIABcACIAUwBpAG4AZwBsAGUAIABhAG4AZAAgAG0AdQBsAHQAaQBwAGwAZQAgAGQAcgBhAGkAbgBhAGcAZQAsACAAbwByACAAYQBsAHQAZQByAG4AYQB0AGUAIAB3AGUAdAB0AGkAbgBnACAAYQBuAGQAIABkAHIAeQBpAG4AZwBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBxAHUAYQBjAHUAbAB0AHUAcgBlAFwAIgAsADAALgAwADAAMgA2ACwAIABcACIAQQBxAHUAYQBjAHUAbAB0AHUAcgBlAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAG8AcgBlAHMAdAByAHkAXAAiACwAMAAuADAAMAAxADgALAAgAFwAIgBGAG8AcgBlAHMAdAByAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA1ACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGUAbQBvAHYAZQBkACAAZAB1AHAAbABpAGMAYQB0AGUAIABcAHUAMAAwADIANwBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAB1ADAAMAAyADcAIAByAG8AdwAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGUAbQBvAHYAZQBkACAAYQBzAHQAZQByAGkAcwBrAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAFwAdQAwADAAMgA3AHAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAG8AbgBsAHkAXAB1ADAAMAAyADcALAAgAFwAdQAwADAAMgA3AHIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAXAB1ADAAMAAyADcAIABhAG4AZAAgAFwAdQAwADAAMgA3AGkAcgByAGkAZwBhAHQAaQBvAG4AIABtAGUAdABoAG8AZABcAHUAMAAwADIANwAgAGMAbwBsAHUAbQBuAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAdQBwAGwAaQBjAGEAdABlAGQAIABcAHUAMAAwADIANwBuAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQBcAHUAMAAwADIANwAgAHIAbwB3ACAAdwBpAHQAaAAgAHMAYQBtAGUAIABFAEYAIABmAG8AcgAgAGwAbwB3ACAAYQBuAGQAIABoAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAFwAbgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABDAGgAYQBwAHQAZQByACAAMQAsACAAcwBlAGMAdABpAG8AbgAgADEALgA4AC4AMgAgAEwAZQBhAGMAaABpAG4AZwAsACAAYwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBzAFwAbgBJAFAAQwBDADoAIABOADIATwAgAEUATQBJAFMAUwBJAE8ATgBTACAARgBSAE8ATQAgAE0AQQBOAEEARwBFAEQAIABTAE8ASQBMAFMALAAgAEEATgBEACAAQwBPADIAIABFAE0ASQBTAFMASQBPAE4AUwAgAEYAUgBPAE0AIABMAEkATQBFACAAQQBOAEQAIABVAFIARQBBACAAQQBQAFAATABJAEMAQQBUAEkATwBOAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwBXAEUAVAAgAGYAbwByACAAaQByAHIAaQBnAGEAdABpAG8AbgAgAHQAeQBwAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAEMAaABhAHAAdABlAHIAIAAxACwAIABzAGUAYwB0AGkAbwBuACAAMQAuADgALgAyACAATABlAGEAYwBoAGkAbgBnACwAIABjAGwAaQBtAGEAdABlACAAYQBuAGQAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBJAFAAQwBDACAAMgAwADEAOQAgAFIAZQBmAGkAbgBlAG0AZQBuAHQAIABWAG8AbAB1AG0AZQAgADQAOgAgAEMAaABhAHAAdABlAHIAIAAxADEAOgAgAE4AMgBPACAARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAATQBhAG4AYQBnAGUAZAAgAFMAbwBpAGwAcwAsACAAYQBuAGQAIABDAE8AMgAgAEUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAEwAaQBtAGUAIABhAG4AZAAgAFUAcgBlAGEAIABBAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGkAbwBuACAAdAB5AHAAZQAgAGkAcgBcACIALABcACIARgByAGEAYwBXAEUAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAByAGkAcAAgAGkAcgByAGkAZwBhAHQAaQBvAG4AXAAiACwAIAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAcAByAGkAbgBrAGwAZQByACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB1AHIAZgBhAGMAZQAgAGkAcgByAGkAZwBhAHQAaQBvAG4AXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AdABoAGUAcgAgAGkAcgByAGkAZwBhAHQAaQBvAG4AXAAiACwAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAARgBSAE8ATQAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAAVABhAGIAbABlACAAYwByAGUAYQB0AGUAZAAgAGIAYQBzAGUAZAAgAG8AbgAgAFYARQBFAFIARwAgAHQAZQB4AHQAIABcAHUAMAAwADIANwBBAHIAZQBhAHMAIABhAHIAZQAgAHMAdQBiAGoAZQBjAHQAIAB0AG8AIABsAGUAYQBjAGgAaQBuAGcAIAAoAGkALgBlAC4ALAAgAGkAbgAgAHQAaABlACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQApACAAdwBoAGUAbgAuAC4ALgAgAHQAaABlACAAbABhAG4AZAAgAGkAcwAgAGkAcgByAGkAZwBhAHQAZQBkACAAKABlAHgAYwBlAHAAdAAgAGQAcgBpAHAAIABpAHIAcgBpAGcAYQB0AGkAbwBuACkALgBcAHUAMAAwADIANwBcACIAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAFwAbgBUAGEAYgBsAGUAIABBAC4AMgAuADIALgAyADoAIABFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAdQByAGkAbgBlACAAYQBuAGQAIABkAHUAbgBnACAAZABlAHAAbwBzAGkAdABlAGQAIABvAG4AIABwAGEAcwB0AHUAcgBlACwAIAByAGEAbgBnAGUAIABvAHIAIABwAGEAZABkAG8AYwBrACAAKABrAGcAIABOADIATwAtAE4ALwBrAGcAIABOACkAIAAoAEUARgBQAFIAUAApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAdQByAGkAbgBlACAAYQBuAGQAIABkAHUAbgBnACAAZABlAHAAbwBzAGkAdABlAGQAIABvAG4AIABwAGEAcwB0AHUAcgBlACwAIAByAGEAbgBnAGUAIABvAHIAIABwAGEAZABkAG8AYwBrAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AMgBPACAALQAgAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADIALgAyAC4AMgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAEUARgBQAFIAUABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAAyAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABDAGgAYQBuAGcAZQBkACAAXAB1ADAAMAAyADcARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBzAFwAdQAwADAAMgA3ACAAdABvACAAcwBpAG4AZwB1AGwAYQByACAAXAB1ADAAMAAyADcARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcAHUAMAAwADIANwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAG8AbgB0AGgAcwAgAHQAbwAgAFMAZQBhAHMAbwBuAHMAIABNAGEAcABwAGkAbgBnAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBvAG4AdABoAFwAIgAsACAAXAAiAFMAZQBhAHMAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAGEAbgB1AGEAcgB5AFwAIgAsACAAXAAiAFMAdQBtAG0AZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAGUAYgByAHUAYQByAHkAXAAiACwAIABcACIAUwB1AG0AbQBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQByAGMAaABcACIALAAgAFwAIgBBAHUAdAB1AG0AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBwAHIAaQBsAFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAGEAeQBcACIALAAgAFwAIgBBAHUAdAB1AG0AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASgB1AG4AZQBcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASgB1AGwAeQBcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQB1AGcAdQBzAHQAXAAiACwAIABcACIAVwBpAG4AdABlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAZQBwAHQAZQBtAGIAZQByAFwAIgAsACAAXAAiAFMAcAByAGkAbgBnAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBPAGMAdABvAGIAZQByAFwAIgAsACAAXAAiAFMAcAByAGkAbgBnAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdgBlAG0AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAZQBjAGUAbQBiAGUAcgBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBhAG4AdQByAGUAIABNAGEAbgBhAGcAZQBtAGUAbgB0ACAAEyAgAE0AZQB0AGgAYQBuAGUAIABjAG8AbgB2AGUAcgBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABwAGUAcgAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAIAAoAGYAcgBhAGMAdABpAG8AbgApACAAKABNAEMARgBpAG0AKQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAxAC4AOAAuADEAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIAMgAsACAAMQA2ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAE0AQQBUACAAKAC6AEMAKQBcACIALAAgAFwAIgBVAG4AYwBvAHYAZQByAGUAZAAgAGEAbgBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuAFwAIgAsACAAXAAiAEMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBcACIALAAgAFwAIgBMAGkAcQB1AGkAZAAgAFMAbAB1AHIAcgB5ACAAKAB3AGkAdABoAG8AdQB0ACAAbgBhAHQAdQByAGEAbAAgAGMAcgB1AHMAdAApAFwAIgAsACAAXAAiAEQAYQBpAGwAeQAgAHMAcAByAGUAYQBkACAAKABiACkAXAAiACwAIABcACIAQwBvAG0AcABvAHMAdABpAG4AZwAgACgAcABhAHMAcwBpAHYAZQAgAHcAaQBuAGQAcgBvAHcAKQBcACIALAAgAFwAIgBTAG8AbABpAGQAIABTAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAFAAaQB0ACAAUwB0AG8AcgBhAGcAZQAgAFwAdQAwADAAMwBjADEAIABtAG8AbgB0AGgAXAAiACwAIABcACIARABlAGUAcAAgAEwAaQB0AHQAZQByAFwAIgAsACAAXAAiAFAAbwB1AGwAdAByAHkAIABNAGEAbgB1AHIAZQAgACgAdwBpAHQAaAAvAHcAaQB0AGgAbwB1AHQAIABsAGkAdAB0AGUAcgApAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAcAByAG8AYwBlAHMAcwBpAG4AZwAgAGkAbgB0AG8AIABwAGUAbABsAGUAdABpAHoAZQBkACAAZgBlAHIAdABpAGwAaQBzAGUAcgBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgAgAHQAbwAgAHMAbwBpAGwAXAAiACwAIABcACIAUABhAHMAdAB1AHIAZQAsACAAUgBhAG4AZwBlACAAYQBuAGQAIABQAGEAZABkAG8AYwBrACAAKABjACkAKABkACkAXAAiACwAIABcACIATQBBAFQAIAByAGEAdwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgAFwAIgBkIjEAMABcACIALAAgADAALgA2ADYALAAgADAALgAxACwAIAAwAC4AMQAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIAAxADEALAAgADAALgA2ADgALAAgADAALgAxACwAIAAwAC4AMQAxACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgADEAMgAsACAAMAAuADcALAAgADAALgAxACwAIAAwAC4AMQAzACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgADEAMwAsACAAMAAuADcAMQAsACAAMAAuADEALAAgADAALgAxADQALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQA0ACwAIAAwAC4ANwAzACwAIAAwAC4AMQAsACAAMAAuADEANQAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA1ACwAIAAwAC4ANwA0ACwAIAAwAC4AMQAsACAAMAAuADEANwAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEANQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEANgAsACAAMAAuADcANQAsACAAMAAuADEALAAgADAALgAxADgALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADcALAAgADAALgA3ADYALAAgADAALgAxACwAIAAwAC4AMgAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEANwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEAOAAsACAAMAAuADcANwAsACAAMAAuADEALAAgADAALgAyADIALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADkALAAgADAALgA3ADcALAAgADAALgAxACwAIAAwAC4AMgA0ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgAwACwAIAAwAC4ANwA4ACwAIAAwAC4AMQAsACAAMAAuADIANgAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIAMQAsACAAMAAuADcAOAAsACAAMAAuADEALAAgADAALgAyADkALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADIALAAgADAALgA3ADgALAAgADAALgAxACwAIAAwAC4AMwAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgAzACwAIAAwAC4ANwA5ACwAIAAwAC4AMQAsACAAMAAuADMANAAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIANAAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgAzADcALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADUALAAgADAALgA3ADkALAAgADAALgAxACwAIAAwAC4ANAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AXAAiACwAIAAyADYALAAgADAALgA3ADkALAAgADAALgAxACwAIAAwAC4ANAA0ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AXAAiACwAIAAyADcALAAgADAALgA4ACwAIAAwAC4AMQAsACAAMAAuADQAOAAsACAAMAAuADAAMQAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIANwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtAFwAIgAsACAAXAAiAGUiMgA4AFwAIgAsACAAMAAuADgALAAgADAALgAxACwAIAAwAC4ANQAsACAAMAAuADAAMQAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBBAG4AYQBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuAFwAIgAsACAAXAAiAEQAaQBnAGUAcwB0AGUAcgAgAC8AIABjAG8AdgBlAHIAZQBkACAAbABhAGcAbwBvAG4AcwBcACIALAAgAFwAIgBMAGkAcQB1AGkAZAAgAHMAeQBzAHQAZQBtAHMAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAXAAiACwAIABcACIAQwBvAG0AcABvAHMAdABpAG4AZwAgACgAcABhAHMAcwBpAHYAZQAgAHcAaQBuAGQAcgBvAHcAKQBcACIALAAgAFwAIgBTAG8AbABpAGQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAFAAaQB0ACAAcwB0AG8AcgBhAGcAZQBcACIALAAgAFwAIgBEAGUAZQBwACAAbABpAHQAdABlAHIAXAAiACwAIABcACIAUABvAHUAbAB0AHIAeQAgAG0AYQBuAHUAcgBlACAAdwBpAHQAaAAgAGIAZQBkAGQAaQBuAGcAXAAiACwAIABcACIAUABvAHUAbAB0AHIAeQAgAG0AYQBuAHUAcgBlACAAdwBpAHQAaABvAHUAdAAgAGIAZQBkAGQAaQBuAGcAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABwAHIAbwBjAGUAcwBzAGkAbgBnAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuAFwAIgAsACAAXAAiAFAAYQBzAHQAdQByAGUAIAByAGEAbgBnAGUAIABhAG4AZAAgAHAAYQBkAGQAbwBjAGsAXAAiACwAIABcACIATQBBAFQAIAByAGEAdwBcACIAIABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAOgAgAEEAZABkAGUAZAAgAHIAbwB3ACAAbwBmACAATgBJAFIAIABNAE0AQQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgAgAEQAdQBwAGwAaQBjAGEAdABlAGQAIABcAHUAMAAwADIANwBQAG8AdQBsAHQAcgB5ACAAdwBpAHQAaAAgAGEAbgBkACAAdwBpAHQAaABvAHUAdAAgAGwAaQB0AHQAZQByAFwAdQAwADAAMgA3ACAAYwBvAGwAdQBtAG4AIAB3AGkAdABoACAAcwBlAHAAYQByAGEAdABlACAATgBJAFIAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AIABBAGQAZABlAGQAIABcAHUAMAAwADIANwBNAEEAVAAgAHIAYQB3AFwAdQAwADAAMgA3ACAAYwBvAGwAdQBtAG4AIAB0AG8AIABhAGwAbABvAHcAIABsAG8AbwBrAHUAcAAgAG8AZgAgAG4AdQBtAGIAZQByAHMALgBcACIAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAbgBkACAAYwByAG8AcAAgAHIAZQBzAGkAZAB1AGUAcwAgAHIAZQB0AHUAcgBuAGUAZAAgAHQAbwAgAHQAaABlACAAcwBvAGkAbABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBGAE4AaQAgAFwAdQAwADAAMgA2ACAARQBGAE4AMgBPAGkAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABOADIATwAgAC0AIABOACAALwAgAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADIALgAxAC4ANABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgAFwAIgBFAEYATgBpACAAXAB1ADAAMAAyADYAIABFAEYATgAyAE8AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIAAwAC4AMAAwADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAANQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIAXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBcAG4AQwBvAG4AdgBlAHIAdAAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcAG4ARQBOADIATwAgAEMATwAyAGUAXABuAHQAIABDAE8AMgBlAFwAbgBFAE4AMgBPADoAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAAoAHQAIABOADIATwApAFwAbgBHAFcAUABOADIATwA6ACAAZwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIAAoAHQAIABDAE8AMgAtAGUAIAAvACAAdAAgAE4AMgBPACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABFAF8ATgAyAE8ALAAgAEcAVwBQAF8ATgAyAE8ALABcAG4AIAAgACAAIABFAF8ATgAyAE8AIAAqACAARwBXAFAAXwBOADIATwBcAG4AIAAgACkAXABuADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAbwBuAHYAZQByAHQAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAB0AG8AIABjAGEAcgBiAG8AbgAgAGQAaQBvAHgAaQBkAGUAIABlAHEAdQBpAHYAYQBsAGUAbgB0ACAAZQBtAGkAcwBzAGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBOADIATwAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAE8AMgBlAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMATwAyAF8AZQAgAD0AIABFAF8AewBOADIATwB9ACAAXABcAHQAaQBtAGUAcwAgAEcAVwBQAF8AewBOADIATwB9AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUATgAyAE8AXAAiACwAXAAiAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAE4AMgBPACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAVwBQAE4AMgBPAFwAIgAsAFwAIgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAATgAyAE8AKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBcAG4AQwBvAG4AdgBlAHIAdAAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcAG4ARQBDAEgANAAgAEMATwAyAGUAXABuAHQAIABDAE8AMgBlAFwAbgBFAEMASAA0ADoAIABtAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAAoAHQAIABDAEgANAApAFwAbgBHAFcAUABDAEgANAA6ACAAZwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAG0AZQB0AGgAYQBuAGUAIAAoAHQAIABDAE8AMgAtAGUAIAAvACAAdAAgAEMASAA0ACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABFAF8AQwBIADQALAAgAEcAVwBQAF8AQwBIADQALABcAG4AIAAgACAAIABFAF8AQwBIADQAIAAqACAARwBXAFAAXwBDAEgANABcAG4AIAAgACkAXABuADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAbwBuAHYAZQByAHQAIABtAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAB0AG8AIABjAGEAcgBiAG8AbgAgAGQAaQBvAHgAaQBkAGUAIABlAHEAdQBpAHYAYQBsAGUAbgB0ACAAZQBtAGkAcwBzAGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBDAEgANAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAE8AMgBlAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMATwAyAF8AZQAgAD0AIABFAF8AewBDAEgANAB9ACAAXABcAHQAaQBtAGUAcwAgAEcAVwBQAF8AewBDAEgANAB9AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUAQwBIADQAXAAiACwAXAAiAE0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAEMASAA0ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAVwBQAEMASAA0AFwAIgAsAFwAIgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbQBlAHQAaABhAG4AZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAAQwBIADQAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIAVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAUgBvAHcAUwB0AGEAcgB0AE4AdQBtAGIAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwALABSAG8AdwBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAYQBuAGQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAUgBPAFcAKABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAApACAAKwAgAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkAIAAtACAAMQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABUAGEAYgBsAGUASABlAGEAZABlAHIAQwBlAGwAbAAsAFwAbgAgACAAQwBPAEwAVQBNAE4AKABUAGEAYgBsAGUASABlAGEAZABlAHIAQwBlAGwAbAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBBAHIAcgBhAHkASQBuAFQAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgAEEAcgByAGEAeQBEAGEAdABhACwAIABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQAsACAAWwBDAG8AbAB1AG0AbgBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAQQBuAGQAQQByAHIAYQB5AF0ALABcAG4AIABJAEYARQBSAFIATwBSACgAXABuACAAIAAgACAAIABJAE4ARABFAFgAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAVQBOAEkAUQBVAEUAKABBAHIAcgBhAHkARABhAHQAYQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBPAFcAKAApAC0AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAUgBvAHcAUwB0AGEAcgB0AE4AdQBtAGIAZQByACgAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwALAAgAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEMATwBMAFUATQBOACgAKQAtAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAEMAbwBsAHUAbQBuAFMAdABhAHIAdABOAHUAbQBiAGUAcgAoAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACkAIAArAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAEMAbwBsAHUAbQBuAHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBBAG4AZABBAHIAcgBhAHkAKQAsACAAMQAsACAAQwBvAGwAdQBtAG4AcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAEEAbgBkAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACAAIAAgACAAKQAsACAAXAAiAFwAIgBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFwAIgBcACIAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEkARgAoAEkAUwBOAFUATQBCAEUAUgAoAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFwAIgBcACIAKQBcAG4AIAAgACAAIAApACwAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApACwAIAAwACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBUAHcAbwBDAG8AbAB1AG0AbgBzAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlADEALAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADIALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAWwBWAGEAbAB1AGUASQBGAEYAYQBsAHMAZQBdACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoADEALAAgACgATABvAG8AawB1AHAAQQByAHIAYQB5ADEAPQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQApACoAKABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABWAGEAbAB1AGUASQBGAEYAYQBsAHMAZQApACwAIABcACIAXAAiACwAIABWAGEAbAB1AGUASQBGAEYAYQBsAHMAZQApACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBPAG4AZQBDAG8AbAB1AG0AbgBBAG4AZABIAGUAYQBkAGUAcgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACwAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMgAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADEALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFsAVgBhAGwAdQBlAEkAZgBGAGEAbABzAGUAXQAsAFwAbgAgACAAIAAgAEkARgBFAFIAUgBPAFIAKABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADEALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACkAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAFYAYQBsAHUAZQBJAGYARgBhAGwAcwBlACkALAAgAFwAIgBcACIALAAgAFYAYQBsAHUAZQBJAGYARgBhAGwAcwBlACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAcABsAGkAdABTAHQAcgBpAG4AZwBJAG4AdABvAEEAcgByAGEAeQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEMAZQBsAGwALAAgAEQAZQBsAGkAbQBpAHQAZQByACwAIABbAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAxAF0ALAAgAFsAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADIAXQAsAFwAbgAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAWABNAEwAKABcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBcAHUAMAAwADMAYwB0AFwAdQAwADAAMwBlAFwAdQAwADAAMwBjAHMAXAB1ADAAMAAzAGUAXAAiACAAXAB1ADAAMAAyADYAXABuACAAIAAgACAAIAAgACAAIABTAFUAQgBTAFQASQBUAFUAVABFACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFMAVQBCAFMAVABJAFQAVQBUAEUAKABTAFUAQgBTAFQASQBUAFUAVABFACgAQwBlAGwAbAAsAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAxACwAXAAiAFwAIgApACwAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADIALABcACIAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAARABlAGwAaQBtAGkAdABlAHIALABcACIAXAB1ADAAMAAzAGMALwBzAFwAdQAwADAAMwBlAFwAdQAwADAAMwBjAHMAXAB1ADAAMAAzAGUAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAKQAgAFwAdQAwADAAMgA2AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFwAdQAwADAAMwBjAC8AcwBcAHUAMAAwADMAZQBcAHUAMAAwADMAYwAvAHQAXAB1ADAAMAAzAGUAXAAiACwAXABuACAAIAAgACAAIAAgACAAIABcACIALwAvAHMAXAAiAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABDAGwAaQBtAGEAdABlAFoAbwBuAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABhAHYAZwBUAGUAbQBwACwAYQB2AGcAUgBhAGkAbgAsAGYAcgBvAHMAdABEAGEAeQBzACwAZQBsAGUAdgAsAG0AYQBwAF8AcABlAHQALABcAG4AIAAgACAAIABtAGkAbgBUAGUAbQBwAEEAcgByAGEAeQAsAG0AYQB4AFQAZQBtAHAAQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4AUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQAsAG0AYQB4AFIAYQBpAG4AZgBhAGwAbABBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBGAHIAbwBzAHQAQQByAHIAYQB5ACwAbQBhAHgARgByAG8AcwB0AEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAEUAbABlAHYAYQB0AGkAbwBuAEEAcgByAGEAeQAsAG0AYQB4AEUAbABlAHYAYQB0AGkAbwBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAFAARQBUAEEAcgByAGEAeQAsAG0AYQB4AFAARQBUAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAGMAbABpAG0AYQB0AGUAWgBvAG4AZQBBAHIAcgBhAHkALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAbQBhAHMAawAsAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBUAGUAbQBwAEEAcgByAGEAeQApAFwAdQAwADAAMwBjAD0AYQB2AGcAVABlAG0AcAApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AFQAZQBtAHAAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBhAHYAZwBUAGUAbQBwACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4AUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQApAFwAdQAwADAAMwBjAD0AYQB2AGcAUgBhAGkAbgApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AFIAYQBpAG4AZgBhAGwAbABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGEAdgBnAFIAYQBpAG4AKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBGAHIAbwBzAHQAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBmAHIAbwBzAHQARABhAHkAcwApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AEYAcgBvAHMAdABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGYAcgBvAHMAdABEAGEAeQBzACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4ARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBlAGwAZQB2ACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBlAGwAZQB2ACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4AUABFAFQAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBtAGEAcABfAHAAZQB0ACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgAUABFAFQAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBtAGEAcABfAHAAZQB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAFQAQQBLAEUAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAKABjAGwAaQBtAGEAdABlAFoAbwBuAGUAQQByAHIAYQB5ACwAbQBhAHMAawAsACAAXAAiAE4AbwAgAG0AYQB0AGMAaABcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAASQB0AGUAbQBGAHIAbwBtAE0AaQBuAE0AYQB4AFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABNAGkAbgBBAHIAcgBhAHkALAAgAE0AYQB4AEEAcgByAGEAeQAsACAASQB0AGUAbQBBAHIAcgBhAHkALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAbQBhAHMAawAsAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABNAGkAbgBBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAE0AYQB4AEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0ATABvAG8AawB1AHAAVgBhAGwAdQBlACkALABcAG4AIAAgACAAIAAgACAAIAAgAEYASQBMAFQARQBSACgASQB0AGUAbQBBAHIAcgBhAHkALAAgAG0AYQBzAGsALAAgAFwAIgBOAG8AIABtAGEAdABjAGgAXAAiACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBTAHUAbQBRAHUAYQBuAHQAaQB0AHkARgByAG8AbQBDAHIAaQB0AGUAcgBpAGEAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAEMAcgBpAHQAZQByAGkAYQAxACwAIABDAHIAaQB0AGUAcgBpAGEAMQBUAHkAcABlAEEAcgByAGEAeQAsACAAUQB1AGEAbgB0AGkAdAB5ACwAIABbAE0AdQBsAHQAaQBwAGwAaQBlAHIAXQAsACAAWwBDAHIAaQB0AGUAcgBpAGEAMgBdACwAWwBDAHIAaQB0AGUAcgBpAGEAMgBBAHIAcgBhAHkAXQAsAFwAbgAgACAATABFAFQAKABcAG4AIAAgACAAIABtAHUAbAB0AGkAcABsAGkAZQByACwAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAE0AdQBsAHQAaQBwAGwAaQBlAHIAKQAsADEALABNAHUAbAB0AGkAcABsAGkAZQByACkALABcAG4AIAAgACAAIABxAHUAYQBuAHQAaQB0AHkALAAgAFEAdQBhAG4AdABpAHQAeQAqAE0AdQBsAHQAaQBwAGwAaQBlAHIALABcAG4AIAAgACAAIABjAHIAaQB0AGUAcgBpAGEAMQAsAC0ALQAoAEMAcgBpAHQAZQByAGkAYQAxAFQAeQBwAGUAQQByAHIAYQB5AD0AQwByAGkAdABlAHIAaQBhADEAKQAsAFwAbgAgACAAIAAgAGMAcgBpAHQAZQByAGkAYQAyACwASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABDAHIAaQB0AGUAcgBpAGEAMgApACwAMQAsAC0ALQAoAEMAcgBpAHQAZQByAGkAYQAyAEEAcgByAGEAeQA9AEMAcgBpAHQAZQByAGkAYQAyACkAKQAsAFwAbgAgACAAIAAgAFMAVQBNAFAAUgBPAEQAVQBDAFQAKABjAHIAaQB0AGUAcgBpAGEAMQAqAGMAcgBpAHQAZQByAGkAYQAyACoAcQB1AGEAbgB0AGkAdAB5ACkAXABuACAAIAApAFwAbgApADsAXABuAFwAbgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAHMAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBTAHQAYQByAHQALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBFAG4AZAAsAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAUwAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgACAAIAAgACAARQAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAXABuACAAIAAgACAAIAAgACAAIABtACwATQBPAE4AVABIACgAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAApACwAXABuACAAIAAgACAAIAAgACAAIABkACwARABBAFkAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAFAAZQByAGkAbwBkAEUAbgBkACwATABBAE0AQgBEAEEAKABzAHQALABFAEQAQQBUAEUAKABzAHQALAAxADIAKQAtADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAQQAsAFMALQAzADYANQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBhACwAWQBFAEEAUgAoAEEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBiACwAWQBFAEEAUgAoAEUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZgBpAHIAcwB0AFkAZQBhAHIALAB5AGEAKwAoAFAAZQByAGkAbwBkAEUAbgBkACgARABBAFQARQAoAHkAYQAsAG0ALABkACkAKQBcAHUAMAAwADMAYwAgAFMAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAbABhAHMAdABZAGUAYQByACwAeQBiAC0AKABEAEEAVABFACgAeQBiACwAbQAsAGQAKQBcAHUAMAAwADMAZQAgAEUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAATQBBAFgAKAAwACwAbABhAHMAdABZAGUAYQByAC0AZgBpAHIAcwB0AFkAZQBhAHIAKwAxACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAFAAZQByAGkAbwBkAHMAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBTAHQAYQByAHQALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBFAG4AZAAsAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAUwAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgACAAIAAgACAARQAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAXABuACAAIAAgACAAIAAgACAAIABtACwATQBPAE4AVABIACgAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAApACwAXABuACAAIAAgACAAIAAgACAAIABkACwARABBAFkAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALAAgAC8AKgBoAGUAbABwAGUAcgA6ACAAZQBuAGQAIABkAGEAdABlACAAZgBvAHIAIABhACAAcgBlAHAAbwByAHQAaQBuAGcAIABwAGUAcgBpAG8AZAAgAHMAdABhAHIAdABpAG4AZwAgAGEAdAAgAGEAIABnAGkAdgBlAG4AIABkAGEAdABlACoALwBcAG4AIAAgACAAIAAgACAAIAAgAFAAZQByAGkAbwBkAEUAbgBkACwATABBAE0AQgBEAEEAKABzAHQALABFAEQAQQBUAEUAKABzAHQALAAxADIAKQAtADEAKQAsACAALwAqAG8AbgBsAHkAIABuAGUAZQBkACAAdABvACAAbABvAG8AawAgAGIAYQBjAGsAIAAzADYANQAgAGQAYQB5AHMAKABtAGEAeAAgAG8AdgBlAHIAbABhAHAAIAB3AGkAbgBkAG8AdwApACoALwBcAG4AIAAgACAAIAAgACAAIAAgAEEALABTAC0AMwA2ADUALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYQAsAFkARQBBAFIAKABBACkALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYgAsAFkARQBBAFIAKABFACkALAAgAC8AKgBpAGYAIAB0AGgAZQAgAGEAbgBjAGgAbwByACAAZgBvAHIAIAB5AGEAIABlAG4AZABzACAAYgBlAGYAbwByAGUAIABTACwAaQB0ACAAYwBhAG4AXAB1ADAAMAAyADcAdAAgAG8AdgBlAHIAbABhAHAAOwAgAG0AbwB2AGUAIAB0AG8AIABuAGUAeAB0ACAAeQBlAGEAcgAqAC8AXABuACAAIAAgACAAIAAgACAAIABmAGkAcgBzAHQAWQBlAGEAcgAsAHkAYQArACgAUABlAHIAaQBvAGQARQBuAGQAKABEAEEAVABFACgAeQBhACwAbQAsAGQAKQApAFwAdQAwADAAMwBjAFMAKQAsACAALwAqAGkAZgAgAHQAaABlACAAYQBuAGMAaABvAHIAIABmAG8AcgAgAHkAYgAgAHMAdABhAHIAdABzACAAYQBmAHQAZQByACAARQAsAGkAdAAgAGMAYQBuAFwAdQAwADAAMgA3AHQAIABvAHYAZQByAGwAYQBwADsAIABtAG8AdgBlACAAdABvACAAcAByAGUAdgBpAG8AdQBzACAAeQBlAGEAcgAqAC8AXABuACAAIAAgACAAIAAgACAAIABsAGEAcwB0AFkAZQBhAHIALAB5AGIALQAoAEQAQQBUAEUAKAB5AGIALABtACwAZAApAFwAdQAwADAAMwBlAEUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAbgAsAE0AQQBYACgAMAAsAGwAYQBzAHQAWQBlAGEAcgAtAGYAaQByAHMAdABZAGUAYQByACsAMQApACwAXABuACAAIAAgACAAIAAgACAAIAB5AHIAcwAsAFMARQBRAFUARQBOAEMARQAoAG4ALAAxACwAZgBpAHIAcwB0AFkAZQBhAHIALAAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAHMAdABhAHIAdABzACwARABBAFQARQAoAHkAcgBzACwAbQAsAGQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZQBuAGQAcwAsAE0AQQBQACgAcwB0AGEAcgB0AHMALABQAGUAcgBpAG8AZABFAG4AZAApACwAXABuACAAIAAgACAAIAAgACAAIAB0AGEAZwAsAEkARgAoAHMAdABhAHIAdABzAD0AUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAIgAgACgAVABoAGkAcwAgAHIAZQBwAG8AcgB0AGkAbgBnACAAYwB5AGMAbABlACkAXAAiACwAXAAiAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABzAHQAYQByAHQAcwBUAGUAeAB0ACwAVABFAFgAVAAoAHMAdABhAHIAdABzACwAXAAiAGQAZAAgAG0AbQBtACAAeQB5AHkAeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZQBuAGQAcwBUAGUAeAB0ACwAVABFAFgAVAAoAGUAbgBkAHMALABcACIAZABkACAAbQBtAG0AIAB5AHkAeQB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABuAD0AMAAsAFwAIgBcACIALABIAFMAVABBAEMASwAoAHMAdABhAHIAdABzAFQAZQB4AHQAIABcAHUAMAAwADIANgAgAFwAIgAgAHQAbwAgAFwAIgAgAFwAdQAwADAAMgA2ACAAZQBuAGQAcwBUAGUAeAB0ACAAXAB1ADAAMAAyADYAIAB0AGEAZwApACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkARgB1AG4AYwB0AGkAbwBuAE4AYQBtAGUAXABuAD0ATABBAE0AQgBEAEEAKABGAHUAbgBjAHQAaQBvAG4ALAAgAFQARQBYAFQAQgBFAEYATwBSAEUAKABGAE8AUgBNAFUATABBAFQARQBYAFQAKABGAHUAbgBjAHQAaQBvAG4AKQAsACAAXAAiACgAXAAiACkAKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAE4AMgBPAEUARgBGAHIAbwBtAFAAcgBvAGQASQByAHIAaQBnAGEAdABpAG8AbgBSAGEAaQBuAGYAYQBsAGwAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAIABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACwAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AQQByAHIAYQB5ACwAIABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkAEEAcgByAGEAeQAsACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAQQByAHIAYQB5ACwAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQALAAgAEkARgAoAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAPQBcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEEAbgB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQAsACAASQBGACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAAgAD0AIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAIABcACIAQQBuAHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKAAxACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEEAcgByAGEAeQA9AFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AKQAqAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAoAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAQQByAHIAYQB5AD0ASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAApACoAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACgAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAQQByAHIAYQB5AD0AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEcAZQB0AEYAcgBhAGMAVwBFAFQAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ALABcAG4AIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQALAAgAFwAbgAgACAAIAAgACAAIAAgACAAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUALABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBMAG8AbwBrAHUAcAAsAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQALAAgAFwAbgAgACAAIAAgACAAIAAgACAAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ATABvAG8AawB1AHAALABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBGAHIAYQBjAFcARQBUACAAKwAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVABcAHUAMAAwADMAZQAwACwAIAAxACwAIAAwACkAXABuACAAIAAgACAAKQApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEMAbwBuAHYAZQByAHQAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAVABvAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUALABcAG4AIAAgACAAIABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBBAHIAcgBhAHkALAAgAFMAdABhAHQAZQBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUALAAgAFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAEEAcgByAGEAeQAsACAAUwB0AGEAdABlAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwBvAHUAcgBjAGUASAB5AHAAZQByAGwAaQBuAGsAXABuAD0ATABBAE0AQgBEAEEAKABUAGEAcgBnAGUAdABDAGUAbABsACwAXABuACAAIABMAEUAVAAoAFwAbgAgACAAIAAgAHMAaAAsACAAVABFAFgAVABBAEYAVABFAFIAKABDAEUATABMACgAXAAiAGYAaQBsAGUAbgBhAG0AZQBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsACAAXAAiAF0AXAAiACkALABcAG4AIAAgACAAIABhAGQAZAByACwAIABDAEUATABMACgAXAAiAGEAZABkAHIAZQBzAHMAXAAiACwAIABUAGEAcgBnAGUAdABDAGUAbABsACkALABcAG4AIAAgACAAIABcACIAIwBcAHUAMAAwADIANwBcACIAIABcAHUAMAAwADIANgAgAHMAaAAgAFwAdQAwADAAMgA2ACAAXAAiAFwAdQAwADAAMgA3ACEAXAAiACAAXAB1ADAAMAAyADYAIABhAGQAZAByAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAbwB1AHIAYwBlAEgAeQBwAGUAcgBsAGkAbgBrAEQAaQBmAGYAZQByAGUAbgB0AFMAaABlAGUAdABcAG4APQBMAEEATQBCAEQAQQAoAFQAYQByAGcAZQB0AEMAZQBsAGwALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAcwBoACwAIABUAEUAWABUAEEARgBUAEUAUgAoAEMARQBMAEwAKABcACIAZgBpAGwAZQBuAGEAbQBlAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAIABcACIAXQBcACIAKQAsAFwAbgAgACAAIAAgAGEAZABkAHIALAAgAEMARQBMAEwAKABcACIAYQBkAGQAcgBlAHMAcwBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsAFwAbgAgACAAIAAgAFwAIgAjAFwAIgAgAFwAdQAwADAAMgA2ACAAYQBkAGQAcgBcAG4AIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgBnAHUAbQBlAG4AdABzAF8AMQBfADIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALABcAG4AIAAgACAAIABDAEgATwBPAFMARQBDAE8ATABTACgAQQByAGcAdQBtAGUAbgB0AHMAQQByAHIAYQB5ACwAIAAxACwAIAAyACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgBnAHUAbQBlAG4AdABzAF8AMwBfADQAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALABcAG4AIAAgACAAIABDAEgATwBPAFMARQBDAE8ATABTACgAQQByAGcAdQBtAGUAbgB0AHMAQQByAHIAYQB5ACwAIAAzACwAIAA0ACkAXABuACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8ARwBlAHQATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUALAAgAE0ATQBTACwAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUAQQByAHIAYQB5ACwAIABNAE0AUwBBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKABcAG4AIAAgACAAIAAgACAAIAAgAE0ARQBEAEkAQQBOACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAE0ASQBOACgAVABlAG0AcABlAHIAYQB0AHUAcgBlAEEAcgByAGEAeQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATQBBAFgAKABUAGUAbQBwAGUAcgBhAHQAdQByAGUAQQByAHIAYQB5ACkAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUAQQByAHIAYQB5ACwAXABuACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATQBNAFMALAAgAE0ATQBTAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBSAGUAcwB1AGwAdABzAEkAdABlAG0ARgByAG8AbQBFAHEAdQBhAHQAaQBvAG4AVABpAHQAbABlAEEAbgBkAFMAbwB1AHIAYwBlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAVABpAHQAbABlAEMAZQBsAGwALAAgAFMAbwB1AHIAYwBlAEMAZQBsAGwALABcAG4AIAAgACAAIABTAFUAQgBTAFQASQBUAFUAVABFACgATABFAEYAVAAoAFMAbwB1AHIAYwBlAEMAZQBsAGwALAAgAEYASQBOAEQAKABcACIALABcACIALAAgAFMAbwB1AHIAYwBlAEMAZQBsAGwAKQAgAC0AMQApACwAIABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAXAAiACwAIABcACIAXAAiACkAIABcAHUAMAAwADIANgAgAFwAIgAgAFwAIgAgAFwAdQAwADAAMgA2ACAAVABpAHQAbABlAEMAZQBsAGwAXABuACkAOwAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuADEAMQAuADEAOgAgAFcAYQBzAHQAZQB3AGEAdABlAHIAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuADEAMQAuADEALgAxAC4AMQAgAE0AZQB0AGgAbwBkACAAMQAgAC0AIABNAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAbwBuAHMAaQB0AGUAIABXAGEAcwB0AGUAdwBhAHQAZQByACAATQBhAG4AYQBnAGUAbQBlAG4AdABcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADEAMQBfADEAXwAxAF8AMQBfAF8AMQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBXAGEAcwB0AGUAdwBhAHQAZQByAFQAcgBlAGEAdABtAGUAbgB0AFwAbgBNAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAdwBhAHMAdABlAHcAYQB0AGUAcgAgAHQAcgBlAGEAdABtAGUAbgB0AFwAbgBFAF8AQwBIADQAXABuAHQAIABDAEgANABcAG4ARQBfAHsAQwBIADQAfQA9AFwAXABmAHIAYQBjAHsAMQB9AHsAMQAwADAAMAB9AFwAXAB0AGkAbQBlAHMAXABcAGwAZQBmAHQAWwBcAFwAbABlAGYAdAAoAFcAXwB0AFwAXAB0AGkAbQBlAHMAXABcAGwAZQBmAHQAKABDAE8ARABfAHsAaQBuAH0AXABcAHQAaQBtAGUAcwAoADEALQBGAF8AewBzAGwAdQBkAGcAZQB9ACkALQBDAE8ARABfAHsAbwB1AHQAfQBcAFwAcgBpAGcAaAB0ACkAXABcAHQAaQBtAGUAcwAgAEMARgBfAHsAdwB3ACwAdAB9AFwAXAB0AGkAbQBlAHMAIABFAEYAXwB7AHcAdwB9AFwAXAByAGkAZwBoAHQAKQArAFwAXABsAGUAZgB0ACgAVwBfAHQAXABcAHQAaQBtAGUAcwBcAFwAbABlAGYAdAAoAEMATwBEAF8AewBpAG4AfQBcAFwAdABpAG0AZQBzACgARgBfAHsAcwBsAHUAZABnAGUAfQAtAEYAXwB7AHIAZQBtAG8AdgBlAGQAfQApAFwAXAByAGkAZwBoAHQAKQBcAFwAdABpAG0AZQBzACAAQwBGAF8AewBzAGwAdQBkAGcAZQAsAHQAfQBcAFwAdABpAG0AZQBzACAARQBGAF8AewBzAGwAdQBkAGcAZQB9AFwAXAByAGkAZwBoAHQAKQAtAFwAXABsAGUAZgB0ACgANgAuADcAOAA0AFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0ANAB9AFwAXAB0AGkAbQBlAHMAKABRAF8AewBjAGEAcAB9ACsAUQBfAHsAZgBsAGEAcgBlAGQAfQArAFEAXwB7AG8AdQB0AH0AKQBcAFwAcgBpAGcAaAB0ACkAKwBcAFwAbABlAGYAdAAoAFEAXwB7AGYAbABhAHIAZQBkAH0AXABcAHQAaQBtAGUAcwAgAEUAQwBfAHsAZgBsAGEAcgBlAGQAfQBcAFwAdABpAG0AZQBzACAARQBGAF8AewBmAGwAYQByAGUAZAAsAEMASAA0AH0AXABcAHIAaQBnAGgAdAApAFwAXAByAGkAZwBoAHQAXQBcAG4AVwBfAHQAIAA9ACAAcQB1AGEAbgB0AGkAdAB5ACAAbwBmACAAdwBhAHMAdABlAHcAYQB0AGUAcgAgAHQAcgBlAGEAdABlAGQAIABhAHQAIABmAGEAYwBpAGwAaQB0AHkAIAB0AHkAcABlACAAdAAgACgAbQAzACkAXABuAEMATwBEAF8AaQBuACAAPQAgAGEAdgBlAHIAYQBnAGUAIABpAG4AbABlAHQAIABDAGgAZQBtAGkAYwBhAGwAIABPAHgAeQBnAGUAbgAgAEQAZQBtAGEAbgBkACAAYwBvAG4AYwBlAG4AdAByAGEAdABpAG8AbgAgAG8AZgAgAHcAYQBzAHQAZQB3AGEAdABlAHIAIAAoAGsAZwAgAEMATwBEAC8AbQAzACkAXABuAEYAXwBzAGwAdQBkAGcAZQAgAD0AIABmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABDAE8ARAAgAHIAZQBtAG8AdgBlAGQAIABmAHIAbwBtACAAdwBhAHMAdABlAHcAYQB0AGUAcgAgAGEAcwAgAHMAbAB1AGQAZwBlAFwAbgBDAE8ARABfAG8AdQB0ACAAPQAgAGEAdgBlAHIAYQBnAGUAIABvAHUAdABsAGUAdAAgAEMATwBEACAAYwBvAG4AYwBlAG4AdAByAGEAdABpAG8AbgAgAG8AZgAgAHcAYQBzAHQAZQB3AGEAdABlAHIAIAAoAGsAZwAgAEMATwBEAC8AbQAzACkAXABuAEMARgBfAHcAdwBfAHQAIAA9ACAAbQBlAHQAaABhAG4AZQAgAGMAbwByAHIAZQBjAHQAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAZgBhAGMAaQBsAGkAdAB5ACAAdAB5AHAAZQAgAHQAIAB1AHMAZQBkACAAdABvACAAdAByAGUAYQB0ACAAdwBhAHMAdABlAHcAYQB0AGUAcgBcAG4ARQBGAF8AdwB3ACAAPQAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAdwBhAHMAdABlAHcAYQB0AGUAcgAgACgAawBnACAAQwBPADIAZQAvAGsAZwAgAEMATwBEACkAXABuAEYAXwByAGUAbQBvAHYAZQBkACAAPQAgAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAEMATwBEACAAcgBlAG0AbwB2AGUAZAAgAGYAcgBvAG0AIAB0AGgAZQAgAHcAYQBzAHQAZQB3AGEAdABlAHIAIAB0AHIAZQBhAHQAbQBlAG4AdAAgAGYAYQBjAGkAbABpAHQAeQAgAGEAbgBkACAAdAByAGEAbgBzAGYAZQByAHIAZQBkACAAZQBsAHMAZQB3AGgAZQByAGUAXABuAEMARgBfAHMAbAB1AGQAZwBlAF8AdAAgAD0AIABtAGUAdABoAGEAbgBlACAAYwBvAHIAcgBlAGMAdABpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABmAGEAYwBpAGwAaQB0AHkAIAB0AHkAcABlACAAdAAgAHUAcwBlAGQAIAB0AG8AIAB0AHIAZQBhAHQAIABzAGwAdQBkAGcAZQBcAG4ARQBGAF8AcwBsAHUAZABnAGUAIAA9ACAAbQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABzAGwAdQBkAGcAZQAgACgAawBnACAAQwBPADIAZQAvAGsAZwAgAEMATwBEACkAXABuAFEAXwBjAGEAcAAgAD0AIABxAHUAYQBuAHQAaQB0AHkAIABvAGYAIABtAGUAdABoAGEAbgBlACAAaQBuACAAcwBsAHUAZABnAGUAIABiAGkAbwBnAGEAcwAgAGMAYQBwAHQAdQByAGUAZAAgAGYAbwByACAAYwBvAG0AYgB1AHMAdABpAG8AbgAgACgAbQAzACAAQwBIADQAKQBcAG4AUQBfAGYAbABhAHIAZQBkACAAPQAgAHEAdQBhAG4AdABpAHQAeQAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAIABpAG4AIABzAGwAdQBkAGcAZQAgAGIAaQBvAGcAYQBzACAAZgBsAGEAcgBlAGQAIAAoAG0AMwAgAEMASAA0ACkAXABuAFEAXwBvAHUAdAAgAD0AIABxAHUAYQBuAHQAaQB0AHkAIABvAGYAIABtAGUAdABoAGEAbgBlACAAaQBuACAAcwBsAHUAZABnAGUAIABiAGkAbwBnAGEAcwAgAHQAcgBhAG4AcwBmAGUAcgByAGUAZAAgAG8AdQB0ACAAbwBmACAAdABoAGUAIAB0AHIAZQBhAHQAbQBlAG4AdAAgAGYAYQBjAGkAbABpAHQAeQAgACgAbQAzACAAQwBIADQAKQBcAG4ARQBDAF8AZgBsAGEAcgBlAGQAIAA9ACAAZQBuAGUAcgBnAHkAIABjAG8AbgB0AGUAbgB0ACAAZgBhAGMAdABvAHIAIABvAGYAIABtAGUAdABoAGEAbgBlACAAaQBuACAAcwBsAHUAZABnAGUAIABiAGkAbwBnAGEAcwAgAGYAbABhAHIAZQBkACAAKABHAEoALwBtADMAKQBcAG4ARQBGAF8AZgBsAGEAcgBlAGQAXwBDAEgANAAgAD0AIABtAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHMAbAB1AGQAZwBlACAAYgBpAG8AZwBhAHMAIABmAGwAYQByAGUAZAAgACgAawBnACAAQwBPADIAZQAvAEcASgApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADEAMQBfADEAXwAxAF8AMQBfAF8AMQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBXAGEAcwB0AGUAdwBhAHQAZQByAFQAcgBlAGEAdABtAGUAbgB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFcAXwB0ACwAIABDAE8ARABfAGkAbgAsACAARgBfAHMAbAB1AGQAZwBlACwAIABDAE8ARABfAG8AdQB0ACwAIABDAEYAXwB3AHcAXwB0ACwAIABFAEYAXwB3AHcALAAgAEYAXwByAGUAbQBvAHYAZQBkACwAIABDAEYAXwBzAGwAdQBkAGcAZQBfAHQALAAgAEUARgBfAHMAbAB1AGQAZwBlACwAIABRAF8AYwBhAHAALAAgAFEAXwBmAGwAYQByAGUAZAAsACAAUQBfAG8AdQB0ACwAIABFAEMAXwBmAGwAYQByAGUAZAAsACAARQBGAF8AZgBsAGEAcgBlAGQAQwBIADQALABcAG4AIAAgACAAIAAoADEALwAxADAAMAAwACkAIAAqACAAKAAoAFcAXwB0ACAAKgAgACgAQwBPAEQAXwBpAG4AIAAqACAAKAAxACAALQAgAEYAXwBzAGwAdQBkAGcAZQApACAALQAgAEMATwBEAF8AbwB1AHQAKQAgACoAIABDAEYAXwB3AHcAXwB0ACAAKgAgAEUARgBfAHcAdwApACAAKwAgACgAVwBfAHQAIAAqACAAKABDAE8ARABfAGkAbgAgACoAIAAoAEYAXwBzAGwAdQBkAGcAZQAgAC0AIABGAF8AcgBlAG0AbwB2AGUAZAApACkAIAAqACAAQwBGAF8AcwBsAHUAZABnAGUAXwB0ACAAKgAgAEUARgBfAHMAbAB1AGQAZwBlACkAIAAtACAAKAA2AC4ANwA4ADQAIAAqACAAMQAwAF4ALQA0ACAAKgAgACgAUQBfAGMAYQBwACAAKwAgAFEAXwBmAGwAYQByAGUAZAAgACsAIABRAF8AbwB1AHQAKQApACAAKwAgACgAUQBfAGYAbABhAHIAZQBkACAAKgAgACgARQBDAF8AZgBsAGEAcgBlAGQAIAAqACAARQBGAF8AZgBsAGEAcgBlAGQAQwBIADQAKQApACkAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADEAXwAxAF8AMQBfADEAXwBfADEAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AVwBhAHMAdABlAHcAYQB0AGUAcgBUAHIAZQBhAHQAbQBlAG4AdABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAHcAYQBzAHQAZQB3AGEAdABlAHIAIAB0AHIAZQBhAHQAbQBlAG4AdABcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQAxAF8AMQBfADEAXwAxAF8AXwAxAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFcAYQBzAHQAZQB3AGEAdABlAHIAVAByAGUAYQB0AG0AZQBuAHQAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwBDAEgANABcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQAxAF8AMQBfADEAXwAxAF8AXwAxAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFcAYQBzAHQAZQB3AGEAdABlAHIAVAByAGUAYQB0AG0AZQBuAHQAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgB0ACAAQwBIADQAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEAMQBfADEAXwAxAF8AMQBfAF8AMQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBXAGEAcwB0AGUAdwBhAHQAZQByAFQAcgBlAGEAdABtAGUAbgB0AF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADEAMQAuADEALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAxACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEAMQBfADEAXwAxAF8AMQBfAF8AMQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBXAGEAcwB0AGUAdwBhAHQAZQByAFQAcgBlAGEAdABtAGUAbgB0AF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEcAcgBlAGUAbgBoAG8AdQBzAGUAIABhAG4AZAAgAEUAbgBlAHIAZwB5ACAAUgBlAHAAbwByAHQAaQBuAGcAIABNAGUAYQBzAHUAcgBlAG0AZQBuAHQAIABEAGUAdABlAHIAbQBpAG4AYQB0AGkAbwBuACAAMgAwADAAOABcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQAxAF8AMQBfADEAXwAxAF8AXwAxAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFcAYQBzAHQAZQB3AGEAdABlAHIAVAByAGUAYQB0AG0AZQBuAHQAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAF8AewBDAEgANAB9AD0AXABcAGYAcgBhAGMAewAxAH0AewAxADAAMAAwAH0AXABcAHQAaQBtAGUAcwBcAFwAbABlAGYAdAB7AFwAXABsAGUAZgB0AHsAVwBfAHQAXABcAHQAaQBtAGUAcwBcAFwAbABlAGYAdABbAEMATwBEAF8AewBpAG4AfQBcAFwAdABpAG0AZQBzACgAMQAtAEYAXwB7AHMAbAB1AGQAZwBlAH0AKQAtAEMATwBEAF8AewBvAHUAdAB9AFwAXAByAGkAZwBoAHQAXQBcAFwAdABpAG0AZQBzACAAQwBGAF8AewB3AHcALAB0AH0AXABcAHQAaQBtAGUAcwAgAEUARgBfAHsAdwB3AH0AXABcAHIAaQBnAGgAdAB9ACsAXABcAGwAZQBmAHQAewBXAF8AdABcAFwAdABpAG0AZQBzAFwAXABsAGUAZgB0AFsAQwBPAEQAXwB7AGkAbgB9AFwAXAB0AGkAbQBlAHMAKABGAF8AewBzAGwAdQBkAGcAZQB9AC0ARgBfAHsAcgBlAG0AbwB2AGUAZAB9ACkAXABcAHIAaQBnAGgAdABdAFwAXAB0AGkAbQBlAHMAIABDAEYAXwB7AHMAbAB1AGQAZwBlACwAdAB9AFwAXAB0AGkAbQBlAHMAIABFAEYAXwB7AHMAbAB1AGQAZwBlAH0AXABcAHIAaQBnAGgAdAB9AC0AXABcAGwAZQBmAHQAewA2AC4ANwA4ADQAXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQA0AH0AXABcAHQAaQBtAGUAcwAgAFwAXABsAGUAZgB0AFsAIABRAF8AewBjAGEAcAB9ACsAUQBfAHsAZgBsAGEAcgBlAGQAfQArAFEAXwB7AG8AdQB0AH0AXABcAHIAaQBnAGgAdABdAFwAXAByAGkAZwBoAHQAfQArAFwAXABsAGUAZgB0AHsAUQBfAHsAZgBsAGEAcgBlAGQAfQBcAFwAdABpAG0AZQBzACAAXABcAGwAZQBmAHQAWwAgAEUAQwBfAHsAZgBsAGEAcgBlAGQAfQBcAFwAdABpAG0AZQBzACAARQBGAF8AewBmAGwAYQByAGUAZAAsAEMASAA0AH0AXABcAHIAaQBnAGgAdABdAFwAXAByAGkAZwBoAHQAfQBcAFwAcgBpAGcAaAB0AH0AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEAMQBfADEAXwAxAF8AMQBfAF8AMQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBXAGEAcwB0AGUAdwBhAHQAZQByAFQAcgBlAGEAdABtAGUAbgB0AF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADUALAAgADQALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBfAHQAXAAiACwAIABcACIAcQB1AGEAbgB0AGkAdAB5ACAAbwBmACAAdwBhAHMAdABlAHcAYQB0AGUAcgAgAHQAcgBlAGEAdABlAGQAIABhAHQAIABmAGEAYwBpAGwAaQB0AHkAIAB0AHkAcABlACAAdABcACIALAAgAFwAIgBtADMAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAE8ARABfAGkAbgBcACIALAAgAFwAIgBhAHYAZQByAGEAZwBlACAAaQBuAGwAZQB0ACAAQwBoAGUAbQBpAGMAYQBsACAATwB4AHkAZwBlAG4AIABEAGUAbQBhAG4AZAAgAGMAbwBuAGMAZQBuAHQAcgBhAHQAaQBvAG4AIABvAGYAIAB3AGEAcwB0AGUAdwBhAHQAZQByAFwAIgAsACAAXAAiAGsAZwAgAEMATwBEAC8AbQAzAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBfAHMAbAB1AGQAZwBlAFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAEMATwBEACAAcgBlAG0AbwB2AGUAZAAgAGYAcgBvAG0AIAB3AGEAcwB0AGUAdwBhAHQAZQByACAAYQBzACAAcwBsAHUAZABnAGUAXAAiACwAIABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPAEQAXwBvAHUAdABcACIALAAgAFwAIgBhAHYAZQByAGEAZwBlACAAbwB1AHQAbABlAHQAIABDAE8ARAAgAGMAbwBuAGMAZQBuAHQAcgBhAHQAaQBvAG4AIABvAGYAIAB3AGEAcwB0AGUAdwBhAHQAZQByAFwAIgAsACAAXAAiAGsAZwAgAEMATwBEAC8AbQAzAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBGAF8AdwB3AF8AdABcACIALAAgAFwAIgBtAGUAdABoAGEAbgBlACAAYwBvAHIAcgBlAGMAdABpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABmAGEAYwBpAGwAaQB0AHkAIAB0AHkAcABlACAAdAAgAHUAcwBlAGQAIAB0AG8AIAB0AHIAZQBhAHQAIAB3AGEAcwB0AGUAdwBhAHQAZQByAFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARgBfAHcAdwBcACIALAAgAFwAIgBtAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHcAYQBzAHQAZQB3AGEAdABlAHIAXAAiACwAIABcACIAawBnACAAQwBIADQALwBrAGcAIABDAE8ARABcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAXwByAGUAbQBvAHYAZQBkAFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAEMATwBEACAAcgBlAG0AbwB2AGUAZAAgAGYAcgBvAG0AIAB0AGgAZQAgAHcAYQBzAHQAZQB3AGEAdABlAHIAIAB0AHIAZQBhAHQAbQBlAG4AdAAgAGYAYQBjAGkAbABpAHQAeQAgAGEAbgBkACAAdAByAGEAbgBzAGYAZQByAHIAZQBkACAAZQBsAHMAZQB3AGgAZQByAGUAXAAiACwAIABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBGAF8AcwBsAHUAZABnAGUAXwB0AFwAIgAsACAAXAAiAG0AZQB0AGgAYQBuAGUAIABjAG8AcgByAGUAYwB0AGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAGYAYQBjAGkAbABpAHQAeQAgAHQAeQBwAGUAIAB0ACAAdQBzAGUAZAAgAHQAbwAgAHQAcgBlAGEAdAAgAHMAbAB1AGQAZwBlAFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARgBfAHMAbAB1AGQAZwBlAFwAIgAsACAAXAAiAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAcwBsAHUAZABnAGUAXAAiACwAIABcACIAawBnACAAQwBIADQALwBrAGcAIABDAE8ARABcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEAXwBjAGEAcABcACIALAAgAFwAIgBxAHUAYQBuAHQAaQB0AHkAIABvAGYAIABtAGUAdABoAGEAbgBlACAAaQBuACAAcwBsAHUAZABnAGUAIABiAGkAbwBnAGEAcwAgAGMAYQBwAHQAdQByAGUAZAAgAGYAbwByACAAYwBvAG0AYgB1AHMAdABpAG8AbgBcACIALAAgAFwAIgBtADMAIABDAEgANABcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEAXwBmAGwAYQByAGUAZABcACIALAAgAFwAIgBxAHUAYQBuAHQAaQB0AHkAIABvAGYAIABtAGUAdABoAGEAbgBlACAAaQBuACAAcwBsAHUAZABnAGUAIABiAGkAbwBnAGEAcwAgAGYAbABhAHIAZQBkACAAYgB5ACAAdABoAGUAIAB0AHIAZQBhAHQAbQBlAG4AdAAgAGYAYQBjAGkAbABpAHQAeQBcACIALAAgAFwAIgBtADMAIABDAEgANABcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEAXwBvAHUAdABcACIALAAgAFwAIgBxAHUAYQBuAHQAaQB0AHkAIABvAGYAIABtAGUAdABoAGEAbgBlACAAaQBuACAAcwBsAHUAZABnAGUAIABiAGkAbwBnAGEAcwAgAHQAcgBhAG4AcwBmAGUAcgByAGUAZAAgAG8AdQB0ACAAbwBmACAAdABoAGUAIAB0AHIAZQBhAHQAbQBlAG4AdAAgAGYAYQBjAGkAbABpAHQAeQBcACIALAAgAFwAIgBtADMAIABDAEgANABcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUAQwBfAGYAbABhAHIAZQBkAFwAIgAsACAAXAAiAGUAbgBlAHIAZwB5ACAAYwBvAG4AdABlAG4AdAAgAGYAYQBjAHQAbwByACAAbwBmACAAbQBlAHQAaABhAG4AZQAgAGkAbgAgAHMAbAB1AGQAZwBlACAAYgBpAG8AZwBhAHMAIABmAGwAYQByAGUAZABcACIALAAgAFwAIgBHAEoALwBtADMAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAEYAXwBmAGwAYQByAGUAZABDAEgANABcACIALAAgAFwAIgBtAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHMAbAB1AGQAZwBlACAAYgBpAG8AZwBhAHMAIABmAGwAYQByAGUAZABcACIALAAgAFwAIgBrAGcAIABDAEgANAAvAEcASgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAHQAXAAiACwAIABcACIAdAByAGUAYQB0AG0AZQBuAHQAIABmAGEAYwBpAGwAaQB0AHkAIAB0AHkAcABlAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgBWAEUARQBSAEcAXwAxADEAXwAxAF8AMQBfADEAXwBfADEAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AVwBhAHMAdABlAHcAYQB0AGUAcgBUAHIAZQBhAHQAbQBlAG4AdABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ATgAgAFMATwBVAFIAQwBFADoAIABDAGgAYQBuAGcAZQBkACAAdQBuAGkAdABzACAAbwBmACAARQBGAF8AdwB3ACwAIABFAEYAXwBTAGwAdQBkAGcAZQAgAGEAbgBkACAARQBGAF8AZgBsAGEAcgBlAGQAIABmAHIAbwBtACAAQwBPADIAZQAgAHQAbwAgAEMASAA0ACAAdABvACAAbQBhAHQAYwBoACAAZABhAHQAYQAgAGkAbgAgAFQAYQBiAGwAZQAgAFwAIgApADsAIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAGEAcwB0AGUAdwBhAHQAZQByAF8AUwBvAHUAcgBjAGUARABhAHQAYQAiACwAIgB0AGUAeAB0ACIAOgAiAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AVABhAGIAbABlACAAQQAuADQALgAxAC4AMwA6ACAATQBlAHQAaABhAG4AZQAgAGMAbwByAHIAZQBjAHQAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAdAByAGUAYQB0AG0AZQBuAHQAIABmAGEAYwBpAGwAaQB0AHkAIAB0AHkAcABlACAAdAAgAHUAcwBlAGQAIAB0AG8AIAB0AHIAZQBhAHQAIAB3AGEAcwB0AGUAdwBhAHQAZQByACAAKABmAHIAYQBjAHQAaQBvAG4AKQAgACgAQwBGAHcAdwAsAHQAKQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBDAG8AcgByAGUAYwB0AGkAbwBuAEYAYQBjAHQAbwByAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBUAGkAdABsAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBNAGUAdABoAGEAbgBlACAAYwBvAHIAcgBlAGMAdABpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB0AHIAZQBhAHQAbQBlAG4AdAAgAGYAYQBjAGkAbABpAHQAeQAgAHQAeQBwAGUAIAB0ACAAdQBzAGUAZAAgAHQAbwAgAHQAcgBlAGEAdAAgAHcAYQBzAHQAZQB3AGEAdABlAHIAXAAiACkAKQA7AFwAbgBcAG4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBDAG8AcgByAGUAYwB0AGkAbwBuAEYAYQBjAHQAbwByAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBWAGEAcgBpAGEAYgBsAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBDAEYAdwB3ACwAdABcACIAKQApADsAXABuAFwAbgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEMAbwByAHIAZQBjAHQAaQBvAG4ARgBhAGMAdABvAHIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFUAbgBpAHQAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACkAKQA7AFwAbgBcAG4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBDAG8AcgByAGUAYwB0AGkAbwBuAEYAYQBjAHQAbwByAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBTAG8AdQByAGMAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgA0AC4AMQAuADMAXAAiACkAKQA7AFwAbgBcAG4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBDAG8AcgByAGUAYwB0AGkAbwBuAEYAYQBjAHQAbwByAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBEAGEAdABhAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADIALABcAG4AIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIABcACIARgBhAGMAaQBsAGkAdAB5ACAAdAB5AHAAZQAgAHQAXAAiACwAIABcACIAQwBGAHcAdwAsAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIATQBhAG4AYQBnAGUAZAAgAGEAZQByAG8AYgBpAGMAIAB0AHIAZQBhAHQAbQBlAG4AdABcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBVAG4AbQBhAG4AYQBnAGUAZAAgAGEAZQByAG8AYgBpAGMAIAB0AHIAZQBhAHQAbQBlAG4AdABcACIALAAgADAALgAzADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQQBuAGEAZQByAG8AYgBpAGMAIABkAGkAZwBlAHMAdABvAHIALwByAGUAYQBjAHQAbwByAFwAIgAsACAAMAAuADgAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBTAGgAYQBsAGwAbwB3ACAAYQBuAGEAZQByAG8AYgBpAGMAIABsAGEAZwBvAG8AbgAgACgAZCIgADIAIABtACkAXAAiACwAIAAwAC4AMgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEQAZQBlAHAAIABhAG4AYQBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuACAAKABcAHUAMAAwADMAZQAgADIAbQApAFwAIgAsACAAMAAuADgAXABuACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AKQApACkAOwBcAG4AXABuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUAQwBvAHIAcgBlAGMAdABpAG8AbgBGAGEAYwB0AG8AcgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBcACIAKQApADsAXABuAFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgBUAGEAYgBsAGUAIABBAC4ANAAuADEALgA0ADoAIABNAGUAdABoAGEAbgBlACAAYwBvAHIAcgBlAGMAdABpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB0AHIAZQBhAHQAbQBlAG4AdAAgAGYAYQBjAGkAbABpAHQAeQAgAHQAeQBwAGUAIAB0ACAAdQBzAGUAZAAgAHQAbwAgAHQAcgBlAGEAdAAgAHMAbAB1AGQAZwBlACAAKABmAHIAYQBjAHQAaQBvAG4AKQAgACgAQwBGAHMAbAB1AGQAZwBlACwAdAApAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEMAbwByAHIAZQBjAHQAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAXwBUAGkAdABsAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBNAGUAdABoAGEAbgBlACAAYwBvAHIAcgBlAGMAdABpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB0AHIAZQBhAHQAbQBlAG4AdAAgAGYAYQBjAGkAbABpAHQAeQAgAHQAeQBwAGUAIAB0ACAAdQBzAGUAZAAgAHQAbwAgAHQAcgBlAGEAdAAgAHMAbAB1AGQAZwBlAFwAIgApACkAOwBcAG4AXABuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUAQwBvAHIAcgBlAGMAdABpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBfAFYAYQByAGkAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEMARgBzAGwAdQBkAGcAZQAsAHQAXAAiACkAKQA7AFwAbgBcAG4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBDAG8AcgByAGUAYwB0AGkAbwBuAEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAF8AVQBuAGkAdABcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIAKQApADsAXABuAFwAbgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEMAbwByAHIAZQBjAHQAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAXwBTAG8AdQByAGMAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgA0AC4AMQAuADQAXAAiACkAKQA7AFwAbgBcAG4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBDAG8AcgByAGUAYwB0AGkAbwBuAEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAF8ARABhAHQAYQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAAyACwAXABuACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEYAYQBjAGkAbABpAHQAeQAgAHQAeQBwAGUAIAB0AFwAIgAsACAAXAAiAEMARgBzAGwAdQBkAGcAZQAsAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIATQBhAG4AYQBnAGUAZAAgAGEAZQByAG8AYgBpAGMAIAB0AHIAZQBhAHQAbQBlAG4AdABcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBVAG4AbQBhAG4AYQBnAGUAZAAgAGEAZQByAG8AYgBpAGMAIAB0AHIAZQBhAHQAbQBlAG4AdABcACIALAAgADAALgAzADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQQBuAGEAZQByAG8AYgBpAGMAIABkAGkAZwBlAHMAdABvAHIALwByAGUAYQBjAHQAbwByAFwAIgAsACAAMAAuADgAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBTAGgAYQBsAGwAbwB3ACAAYQBuAGEAZQByAG8AYgBpAGMAIABsAGEAZwBvAG8AbgAgACgAZCIgADIAIABtACkAXAAiACwAIAAwAC4AMgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEQAZQBlAHAAIABhAG4AYQBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuACAAKABcAHUAMAAwADMAZQAgADIAbQApAFwAIgAsACAAMAAuADgAXABuACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AKQApACkAOwBcAG4AXABuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUAQwBvAHIAcgBlAGMAdABpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AVABpAHQAbABlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIATQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB3AGEAcwB0AGUAdwBhAHQAZQByAFwAIgApACkAOwBcAG4AXABuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBWAGEAcgBpAGEAYgBsAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBFAEYAdwB3AFwAIgApACkAOwBcAG4AXABuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBVAG4AaQB0AFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAawBnACAAQwBIADQAIAAvACAAawBnACAAQwBPAEQAXAAiACkAKQA7AFwAbgBcAG4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAMQAxAC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAcwBcACIAKQApADsAXABuAFwAbgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBXAGEAcwB0AGUAdwBhAHQAZQByAF8ARABhAHQAYQBcAG4APQBMAEEATQBCAEQAQQAoACAAMAAuADIANQApADsAXABuAFwAbgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAF8AVABpAHQAbABlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIATQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABzAGwAdQBkAGcAZQBcACIAKQApADsAXABuAFwAbgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBfAFYAYQByAGkAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEUARgBzAGwAdQBkAGcAZQBcACIAKQApADsAXABuAFwAbgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBfAFUAbgBpAHQAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBrAGcAIABDAEgANAAgAC8AIABrAGcAIABDAE8ARABcACIAKQApADsAXABuAFwAbgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBfAFMAbwB1AHIAYwBlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAMQAxAC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAcwBcACIAKQApADsAXABuAFwAbgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBfAEQAYQB0AGEAXABuAD0ATABBAE0AQgBEAEEAKAAwAC4AMgA1ACkAOwBcAG4AXABuAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4AVwBhAHMAdABlAF8ARQBuAGUAcgBnAHkAQwBvAG4AdABlAG4AdABGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBCAGkAbwBnAGEAcwBGAGwAYQByAGUAZABfAFQAaQB0AGwAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEUAbgBlAHIAZwB5ACAAYwBvAG4AdABlAG4AdAAgAGYAYQBjAHQAbwByACAAbwBmACAAcwBsAHUAZABnAGUAIABiAGkAbwBnAGEAcwAgAGYAbABhAHIAZQBkAFwAIgApACkAOwBcAG4AXABuAFcAYQBzAHQAZQBfAEUAbgBlAHIAZwB5AEMAbwBuAHQAZQBuAHQARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAQgBpAG8AZwBhAHMARgBsAGEAcgBlAGQAXwBWAGEAcgBpAGEAYgBsAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBFAEMAZgBsAGEAcgBlAGQAXAAiACkAKQA7AFwAbgBcAG4AVwBhAHMAdABlAF8ARQBuAGUAcgBnAHkAQwBvAG4AdABlAG4AdABGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBCAGkAbwBnAGEAcwBGAGwAYQByAGUAZABfAFUAbgBpAHQAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBHAEoAIAAvACAAbQAzAFwAIgApACkAOwBcAG4AXABuAFcAYQBzAHQAZQBfAEUAbgBlAHIAZwB5AEMAbwBuAHQAZQBuAHQARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAQgBpAG8AZwBhAHMARgBsAGEAcgBlAGQAXwBTAG8AdQByAGMAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADEAMQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0AHMAXAAiACkAKQA7AFwAbgBcAG4AVwBhAHMAdABlAF8ARQBuAGUAcgBnAHkAQwBvAG4AdABlAG4AdABGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBCAGkAbwBnAGEAcwBGAGwAYQByAGUAZABfAEQAYQB0AGEAXABuAD0ATABBAE0AQgBEAEEAKAAwAC4AMAAzADcANwApADsAXABuAFwAbgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAEIAaQBvAGcAYQBzAEYAbABhAHIAZQBkAF8AVABpAHQAbABlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIATQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABzAGwAdQBkAGcAZQAgAGIAaQBvAGcAYQBzACAAZgBsAGEAcgBlAGQAXAAiACkAKQA7AFwAbgBcAG4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAQgBpAG8AZwBhAHMARgBsAGEAcgBlAGQAXwBWAGEAcgBpAGEAYgBsAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBFAEYAZgBsAGEAcgBlAGQALABDAEgANABcACIAKQApADsAXABuAFwAbgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBCAGkAbwBnAGEAcwBGAGwAYQByAGUAZABfAFUAbgBpAHQAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBrAGcAIABDAEgANAAgAC8AIABHAEoAXAAiACkAKQA7AFwAbgBcAG4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAQgBpAG8AZwBhAHMARgBsAGEAcgBlAGQAXwBTAG8AdQByAGMAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADEAMQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0AHMAXAAiACkAKQA7AFwAbgBcAG4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAQgBpAG8AZwBhAHMARgBsAGEAcgBlAGQAXwBEAGEAdABhAFwAbgA9AEwAQQBNAEIARABBACgAMAAuADIAMgA4ADkAKQA7AFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgBXAGEAcwB0AGUAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAQgBpAG8AZwBhAHMARgBsAGEAcgBlAGQAXwBUAGkAdABsAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHMAbAB1AGQAZwBlACAAYgBpAG8AZwBhAHMAIABmAGwAYQByAGUAZABcACIAKQApADsAXABuAFwAbgBXAGEAcwB0AGUAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAQgBpAG8AZwBhAHMARgBsAGEAcgBlAGQAXwBWAGEAcgBpAGEAYgBsAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBFAEYAZgBsAGEAcgBlAGQALABOADIATwBcACIAKQApADsAXABuAFwAbgBXAGEAcwB0AGUAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAQgBpAG8AZwBhAHMARgBsAGEAcgBlAGQAXwBVAG4AaQB0AFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAawBnACAATgAyAE8AIAAvACAARwBKAFwAIgApACkAOwBcAG4AXABuAFcAYQBzAHQAZQBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBCAGkAbwBnAGEAcwBGAGwAYQByAGUAZABfAFMAbwB1AHIAYwBlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAMQAxAC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAcwBcACIAKQApADsAXABuAFwAbgBXAGEAcwB0AGUAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAQgBpAG8AZwBhAHMARgBsAGEAcgBlAGQAXwBEAGEAdABhAFwAbgA9AEwAQQBNAEIARABBACgAMQAuADEAMwAyAGUALQA0ACkAOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAGEAcwB0AGUAdwBhAHQAZQByAF8ATgAyAE8AXwBFAHEAdQBhAHQAaQBvAG4AcwAiACwAIgB0AGUAeAB0ACIAOgAiAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AMQAxAC4AMQA6ACAAVwBhAHMAdABlAHcAYQB0AGUAcgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AMQAxAC4AMQAuADMALgAxACAATQBlAHQAaABvAGQAIAAxACAALQAgAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABvAG4AcwBpAHQAZQAgAFcAYQBzAHQAZQB3AGEAdABlAHIAIABNAGEAbgBhAGcAZQBtAGUAbgB0AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8AMQAxAF8AMQBfADMAXwAxAF8AXwAxAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBGAGwAYQByAGUAZABCAGkAbwBnAGEAcwBcAG4ATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAGYAbABhAHIAZQBkACAAYgBpAG8AZwBhAHMAXABuAEUAXwBOADIATwBcAG4AdAAgAE4AMgBPAFwAbgBFAF8AewBOADIATwB9AD0AXABcAGYAcgBhAGMAewBRAF8AewBmAGwAYQByAGUAZAB9AH0AewAxADAAMAAwAH0AXABcAHQAaQBtAGUAcwAgAEUARgBfAHsAZgBsAGEAcgBlAGQALABOADIATwB9AFwAbgBRAF8AZgBsAGEAcgBlAGQAIAA9ACAAdgBvAGwAdQBtAGUAIABvAGYAIABiAGkAbwBnAGEAcwAgAGYAbABhAHIAZQBkACAAKABtADMAIABvAHIAIABHAEoAKQBcAG4ARQBGAF8AZgBsAGEAcgBlAGQAXwBOADIATwAgAD0AIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAGYAbABhAHIAZQBkACAAYgBpAG8AZwBhAHMAIAAoAGsAZwAgAE4AMgBPAC8ARwBKACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8AMQAxAF8AMQBfADMAXwAxAF8AXwAxAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBGAGwAYQByAGUAZABCAGkAbwBnAGEAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABRAF8AZgBsAGEAcgBlAGQALAAgAEUAQwBfAGYAbABhAHIAZQBkACwAIABFAEYAXwBmAGwAYQByAGUAZABOADIATwAsAFwAbgAgACAAIAAgACgAUQBfAGYAbABhAHIAZQBkACAALwAgADEAMAAwADAAKQAgACoAIAAoAEUAQwBfAGYAbABhAHIAZQBkACAAKgAgAEUARgBfAGYAbABhAHIAZQBkAE4AMgBPACkAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADEAXwAxAF8AMwBfADEAXwBfADEAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEYAbABhAHIAZQBkAEIAaQBvAGcAYQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAZgBsAGEAcgBlAGQAIABiAGkAbwBnAGEAcwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQAxAF8AMQBfADMAXwAxAF8AXwAxAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBGAGwAYQByAGUAZABCAGkAbwBnAGEAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBfAE4AMgBPAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADEAXwAxAF8AMwBfADEAXwBfADEAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEYAbABhAHIAZQBkAEIAaQBvAGcAYQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAE4AMgBPAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADEAXwAxAF8AMwBfADEAXwBfADEAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEYAbABhAHIAZQBkAEIAaQBvAGcAYQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADEAMQAuADEALgAzAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAxACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEAMQBfADEAXwAzAF8AMQBfAF8AMQBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ARgBsAGEAcgBlAGQAQgBpAG8AZwBhAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEAMQBfADEAXwAzAF8AMQBfAF8AMQBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ARgBsAGEAcgBlAGQAQgBpAG8AZwBhAHMAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAF8AewBOADIATwB9AD0AXABcAGYAcgBhAGMAewBRAF8AewBmAGwAYQByAGUAZAB9AH0AewAxADAAMAAwAH0AXABcAHQAaQBtAGUAcwAgAFwAXABsAGUAZgB0AFsARQBDAF8AewBmAGwAYQByAGUAZAB9ACAAXABcAHQAaQBtAGUAcwAgAEUARgBfAHsAZgBsAGEAcgBlAGQALABOADIATwB9AFwAXAByAGkAZwBoAHQAXQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQAxAF8AMQBfADMAXwAxAF8AXwAxAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBGAGwAYQByAGUAZABCAGkAbwBnAGEAcwBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAANAAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBRAF8AZgBsAGEAcgBlAGQAXAAiACwAIABcACIAdgBvAGwAdQBtAGUAIABvAGYAIABiAGkAbwBnAGEAcwAgAGYAbABhAHIAZQBkAFwAIgAsACAAXAAiAG0AMwBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUAQwBfAGYAbABhAHIAZQBkAFwAIgAsACAAXAAiAGUAbgBlAHIAZwB5ACAAYwBvAG4AdABlAG4AdAAgAGYAYQBjAHQAbwByACAAbwBmACAAcwBsAHUAZABnAGUAIABiAGkAbwBnAGEAcwAgAGYAbABhAHIAZQBkAFwAIgAsACAAXAAiAEcASgAvAG0AMwBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARgBfAGYAbABhAHIAZQBkAE4AMgBPAFwAIgAsACAAXAAiAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAZgBsAGEAcgBlAGQAIABiAGkAbwBnAGEAcwBcACIALAAgAFwAIgBrAGcAIABOADIATwAvAEcASgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuACIAfQBdACwAIgBwAHIAbwBqAGUAYwB0AE4AYQBtAGUAcwAiADoAWwAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBBAHAAcABlAG4AZABpAGMAZQBzACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAFIAbwB3AFMAdABhAHIAdABOAHUAbQBiAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAEMAbwBsAHUAbQBuAFMAdABhAHIAdABOAHUAbQBiAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgByAGEAeQBJAG4AVABhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAFQAdwBvAEMAbwBsAHUAbQBuAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATwBuAGUAQwBvAGwAdQBtAG4AQQBuAGQASABlAGEAZABlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AUwBwAGwAaQB0AFMAdAByAGkAbgBnAEkAbgB0AG8AQQByAHIAYQB5ACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEMAbABpAG0AYQB0AGUAWgBvAG4AZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABJAHQAZQBtAEYAcgBvAG0ATQBpAG4ATQBhAHgAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AUwB1AG0AUQB1AGEAbgB0AGkAdAB5AEYAcgBvAG0AQwByAGkAdABlAHIAaQBhACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBzACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAFAAZQByAGkAbwBkAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBGAHUAbgBjAHQAaQBvAG4ATgBhAG0AZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABOADIATwBFAEYARgByAG8AbQBQAHIAbwBkAEkAcgByAGkAZwBhAHQAaQBvAG4AUgBhAGkAbgBmAGEAbABsACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ARwBlAHQARgByAGEAYwBXAEUAVAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBDAG8AbgB2AGUAcgB0AFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAFQAbwBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQAxAF8AMQBfADEAXwAxAF8AXwAxAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFcAYQBzAHQAZQB3AGEAdABlAHIAVAByAGUAYQB0AG0AZQBuAHQAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEAMQBfADEAXwAxAF8AMQBfAF8AMQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBXAGEAcwB0AGUAdwBhAHQAZQByAFQAcgBlAGEAdABtAGUAbgB0AF8AVABpAHQAbABlACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADEAXwAxAF8AMQBfADEAXwBfADEAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AVwBhAHMAdABlAHcAYQB0AGUAcgBUAHIAZQBhAHQAbQBlAG4AdABfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQAxAF8AMQBfADEAXwAxAF8AXwAxAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFcAYQBzAHQAZQB3AGEAdABlAHIAVAByAGUAYQB0AG0AZQBuAHQAXwBVAG4AaQB0ACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADEAXwAxAF8AMQBfADEAXwBfADEAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AVwBhAHMAdABlAHcAYQB0AGUAcgBUAHIAZQBhAHQAbQBlAG4AdABfAFMAbwB1AHIAYwBlACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADEAXwAxAF8AMQBfADEAXwBfADEAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AVwBhAHMAdABlAHcAYQB0AGUAcgBUAHIAZQBhAHQAbQBlAG4AdABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADEAXwAxAF8AMQBfADEAXwBfADEAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AVwBhAHMAdABlAHcAYQB0AGUAcgBUAHIAZQBhAHQAbQBlAG4AdABfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEAMQBfADEAXwAxAF8AMQBfAF8AMQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBXAGEAcwB0AGUAdwBhAHQAZQByAFQAcgBlAGEAdABtAGUAbgB0AF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEAMQBfADEAXwAxAF8AMQBfAF8AMQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBXAGEAcwB0AGUAdwBhAHQAZQByAFQAcgBlAGEAdABtAGUAbgB0AF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEMAbwByAHIAZQBjAHQAaQBvAG4ARgBhAGMAdABvAHIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFQAaQB0AGwAZQAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUAQwBvAHIAcgBlAGMAdABpAG8AbgBGAGEAYwB0AG8AcgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBDAG8AcgByAGUAYwB0AGkAbwBuAEYAYQBjAHQAbwByAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBVAG4AaQB0ACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBDAG8AcgByAGUAYwB0AGkAbwBuAEYAYQBjAHQAbwByAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBTAG8AdQByAGMAZQAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUAQwBvAHIAcgBlAGMAdABpAG8AbgBGAGEAYwB0AG8AcgBXAGEAcwB0AGUAdwBhAHQAZQByAF8ARABhAHQAYQAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUAQwBvAHIAcgBlAGMAdABpAG8AbgBGAGEAYwB0AG8AcgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEMAbwByAHIAZQBjAHQAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAXwBUAGkAdABsAGUAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEMAbwByAHIAZQBjAHQAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEMAbwByAHIAZQBjAHQAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAXwBVAG4AaQB0ACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBDAG8AcgByAGUAYwB0AGkAbwBuAEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAF8AUwBvAHUAcgBjAGUAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEMAbwByAHIAZQBjAHQAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAXwBEAGEAdABhACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBDAG8AcgByAGUAYwB0AGkAbwBuAEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AVABpAHQAbABlACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBVAG4AaQB0ACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAEQAYQB0AGEAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBfAFQAaQB0AGwAZQAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAXwBVAG4AaQB0ACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAXwBTAG8AdQByAGMAZQAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAF8ARABhAHQAYQAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFcAYQBzAHQAZQBfAEUAbgBlAHIAZwB5AEMAbwBuAHQAZQBuAHQARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAQgBpAG8AZwBhAHMARgBsAGEAcgBlAGQAXwBUAGkAdABsAGUAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBXAGEAcwB0AGUAXwBFAG4AZQByAGcAeQBDAG8AbgB0AGUAbgB0AEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAEIAaQBvAGcAYQBzAEYAbABhAHIAZQBkAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AVwBhAHMAdABlAF8ARQBuAGUAcgBnAHkAQwBvAG4AdABlAG4AdABGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBCAGkAbwBnAGEAcwBGAGwAYQByAGUAZABfAFUAbgBpAHQAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBXAGEAcwB0AGUAXwBFAG4AZQByAGcAeQBDAG8AbgB0AGUAbgB0AEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAEIAaQBvAGcAYQBzAEYAbABhAHIAZQBkAF8AUwBvAHUAcgBjAGUAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBXAGEAcwB0AGUAXwBFAG4AZQByAGcAeQBDAG8AbgB0AGUAbgB0AEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAEIAaQBvAGcAYQBzAEYAbABhAHIAZQBkAF8ARABhAHQAYQAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAEIAaQBvAGcAYQBzAEYAbABhAHIAZQBkAF8AVABpAHQAbABlACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAQgBpAG8AZwBhAHMARgBsAGEAcgBlAGQAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBCAGkAbwBnAGEAcwBGAGwAYQByAGUAZABfAFUAbgBpAHQAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBCAGkAbwBnAGEAcwBGAGwAYQByAGUAZABfAFMAbwB1AHIAYwBlACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAQgBpAG8AZwBhAHMARgBsAGEAcgBlAGQAXwBEAGEAdABhACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AVwBhAHMAdABlAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAEIAaQBvAGcAYQBzAEYAbABhAHIAZQBkAF8AVABpAHQAbABlACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AVwBhAHMAdABlAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAEIAaQBvAGcAYQBzAEYAbABhAHIAZQBkAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AVwBhAHMAdABlAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAEIAaQBvAGcAYQBzAEYAbABhAHIAZQBkAF8AVQBuAGkAdAAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFcAYQBzAHQAZQBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBCAGkAbwBnAGEAcwBGAGwAYQByAGUAZABfAFMAbwB1AHIAYwBlACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AVwBhAHMAdABlAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAEIAaQBvAGcAYQBzAEYAbABhAHIAZQBkAF8ARABhAHQAYQAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8ATgAyAE8AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEAMQBfADEAXwAzAF8AMQBfAF8AMQBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ARgBsAGEAcgBlAGQAQgBpAG8AZwBhAHMAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAE4AMgBPAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADEAXwAxAF8AMwBfADEAXwBfADEAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEYAbABhAHIAZQBkAEIAaQBvAGcAYQBzAF8AVABpAHQAbABlACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBOADIATwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQAxAF8AMQBfADMAXwAxAF8AXwAxAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBGAGwAYQByAGUAZABCAGkAbwBnAGEAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8ATgAyAE8AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEAMQBfADEAXwAzAF8AMQBfAF8AMQBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ARgBsAGEAcgBlAGQAQgBpAG8AZwBhAHMAXwBVAG4AaQB0ACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBOADIATwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQAxAF8AMQBfADMAXwAxAF8AXwAxAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBGAGwAYQByAGUAZABCAGkAbwBnAGEAcwBfAFMAbwB1AHIAYwBlACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBOADIATwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQAxAF8AMQBfADMAXwAxAF8AXwAxAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBGAGwAYQByAGUAZABCAGkAbwBnAGEAcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBOADIATwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQAxAF8AMQBfADMAXwAxAF8AXwAxAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBGAGwAYQByAGUAZABCAGkAbwBnAGEAcwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAE4AMgBPAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADEAXwAxAF8AMwBfADEAXwBfADEAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEYAbABhAHIAZQBkAEIAaQBvAGcAYQBzAF8AQQByAGcAdQBtAGUAbgB0AHMAIgBdACwAIgBsAG8AYwBhAGwAZQAiADoAewAiAGwAaQBzAHQAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgByAG8AdwBTAGUAcABhAHIAYQB0AG8AcgAiADoAIgA7ACIALAAiAGMAbwBsAHUAbQBuAFMAZQBwAGEAcgBhAHQAbwByACIAOgAiACwAIgAsACIAdABoAG8AdQBzAGEAbgBkAHMAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgB0AGgAbwB1AHMAYQBuAGQAcwBQAG8AcwBpAHQAaQBvAG4AcwAiADoAWwAzAF0ALAAiAGQAZQBjAGkAbQBhAGwAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALgAiACwAIgBkAGEAdABlAE8AcgBkAGUAcgAiADoAIgBEAE0AWQAiACwAIgBjAHUAcgByAGUAbgBjAHkAUwB5AG0AYgBvAGwAIgA6ACIAJAAiACwAIgBpAHMAQwB1AHIAcgBlAG4AYwB5AFMAeQBtAGIAbwBsAEwAZQBhAGQAIgA6AHQAcgB1AGUALAAiAGkAcwBDAHUAcgByAGUAbgBjAHkAUwBlAHAAQgB5AFMAcABhAGMAZQAiADoAZgBhAGwAcwBlACwAIgByAG8AdwBMAGUAdAB0AGUAcgAiADoAIgBSACIALAAiAGMAbwBsAHUAbQBuAEwAZQB0AHQAZQByACIAOgAiAEMAIgAsACIAcgBjAEwAZQBmAHQAQgByAGEAYwBrAGUAdAAiADoAIgBbACIALAAiAHIAYwBSAGkAZwBoAHQAQgByAGEAYwBrAGUAdAAiADoAIgBdACIALAAiAHMAdABhAHQAZQBtAGUAbgB0AFMAZQBwAGEAcgBhAHQAbwByACIAOgAiADsAIgAsACIAbABvAGMAYQBsAGUATgBhAG0AZQAiADoAIgBlAG4ALQB1AHMAIgB9AH0A</AFEJSONBlob>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9A9CF321-0D35-4044-BC72-33748FE2B865}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD460F9D-420A-4723-B323-396E4D19EC9B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -13987,15 +13996,15 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9A9CF321-0D35-4044-BC72-33748FE2B865}">
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6BE249C-20B1-4A62-BBCD-F2A46D88BCAB}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{809E3D44-A88D-4EBF-A307-6B8CE77A3361}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -14012,12 +14021,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6BE249C-20B1-4A62-BBCD-F2A46D88BCAB}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Excel/11_Wastewater_WIP_v02.xlsx
+++ b/Excel/11_Wastewater_WIP_v02.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\htdocs\zneagcrc\GAF-VEERG-Functions\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB2C339C-F995-4455-B4BE-0A75E09419A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8C476C3-6B8F-4A33-9F75-51D660C516B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1350" yWindow="360" windowWidth="36255" windowHeight="19140" activeTab="2" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
+    <workbookView xWindow="3510" yWindow="3510" windowWidth="28800" windowHeight="15345" firstSheet="7" activeTab="7" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
   </bookViews>
   <sheets>
     <sheet name="Home" sheetId="71" r:id="rId1"/>
@@ -20,8 +20,11 @@
     <sheet name="11.1.1-2 Wastewater CH4" sheetId="69" r:id="rId5"/>
     <sheet name="11.1.3-4 Wastewater N2O" sheetId="120" r:id="rId6"/>
     <sheet name="Constants - Wastewater" sheetId="110" r:id="rId7"/>
-    <sheet name="Constants - Common" sheetId="124" r:id="rId8"/>
+    <sheet name="Constants - Common" sheetId="125" r:id="rId8"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId9"/>
+  </externalReferences>
   <definedNames>
     <definedName name="Common_Equations.Common_ConvertCH4ToCO2e">_xlfn.LAMBDA(_xlpm.E_CH4,_xlpm.GWP_CH4, _xlpm.E_CH4 * _xlpm.GWP_CH4)</definedName>
     <definedName name="Common_Equations.Common_ConvertCH4ToCO2e_Arguments">_xlfn.LAMBDA(_xlfn.MAKEARRAY(2, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"ECH4","Methane emissions (t CH4)";"GWPCH4","Global warming potential for methane (t CO2-e / t CH4)"}, _xlpm.r, _xlpm.c))))</definedName>
@@ -1948,176 +1951,6 @@
   <dxfs count="71">
     <dxf>
       <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <b val="0"/>
         <i val="0"/>
         <strike val="0"/>
@@ -2977,6 +2810,176 @@
         <patternFill patternType="none">
           <fgColor indexed="64"/>
           <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
     </dxf>
@@ -5238,6 +5241,26 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Home"/>
+      <sheetName val="Constants - Common"/>
+      <sheetName val="Acknowledgements"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
 <file path=xl/richData/rdRichValueTypes.xml><?xml version="1.0" encoding="utf-8"?>
 <rvTypesInfo xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x">
   <global>
@@ -5321,7 +5344,7 @@
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="27" xr:uid="{AFAB6A22-121F-4A50-9152-A8E580122815}" name="Table_SourceData_RainfallZones" displayName="Table_SourceData_RainfallZones" ref="D119:G121" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{8D6029C1-B08F-4B80-A995-B6C014F37307}" name="Table_SourceData_RainfallZones" displayName="Table_SourceData_RainfallZones" ref="D119:G121" totalsRowShown="0">
   <autoFilter ref="D119:G121" xr:uid="{E08772F3-2E8C-40A8-B755-08A5BBDF4130}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -5329,16 +5352,16 @@
     <filterColumn colId="3" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{F2A7B006-3B9B-490B-A956-7F904A9BC1A0}" name="Rainfall Zone">
+    <tableColumn id="1" xr3:uid="{5CE8C325-C380-4784-A602-47123F36EF5C}" name="Rainfall Zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{A3178854-1904-46B6-9601-FBCC390F839C}" name="Annual rainfall">
+    <tableColumn id="2" xr3:uid="{25028200-89C9-46AE-8B23-93D29CCACEF2}" name="Annual rainfall">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{D21F920E-74C3-43C6-8E18-6CFD69944EC3}" name="Min rainfall">
+    <tableColumn id="3" xr3:uid="{BC302063-B300-4BE0-A8DD-DD8C4B1F21FD}" name="Min rainfall">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{39CF9EA2-C9B6-41EC-AC58-E1943DCC6E03}" name="Max rainfall">
+    <tableColumn id="4" xr3:uid="{55BED667-88E3-463B-8AFF-4A641BA5DF88}" name="Max rainfall">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5347,16 +5370,16 @@
 </file>
 
 <file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="28" xr:uid="{DB5808CD-4C52-49C0-8D9C-DDD27E7ABF86}" name="Table_SourceData_LeachingZones" displayName="Table_SourceData_LeachingZones" ref="D127:E129" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{4BF50408-A854-4EF4-8E68-A080A9C0D658}" name="Table_SourceData_LeachingZones" displayName="Table_SourceData_LeachingZones" ref="D127:E129" totalsRowShown="0">
   <autoFilter ref="D127:E129" xr:uid="{A159E140-02ED-4547-B6E1-6695D8B16A11}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{4B17C9DE-741E-4223-8B98-9DA237A2543C}" name="Leaching Zone">
+    <tableColumn id="1" xr3:uid="{56109D87-DD06-40E8-858E-A98E14F2505A}" name="Leaching Zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_LeachingZones_Data(), Table_SourceData_LeachingZones[[#Headers],[Leaching Zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{9AE87DF0-C92B-4748-9688-790D35C88B2F}" name="Leaching criteria">
+    <tableColumn id="2" xr3:uid="{DC0D3050-4F7E-43AE-AC42-89AB2C82A6D0}" name="Leaching criteria">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_LeachingZones_Data(), Table_SourceData_LeachingZones[[#Headers],[Leaching Zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5365,16 +5388,16 @@
 </file>
 
 <file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="29" xr:uid="{F67892C5-921B-4BA8-8C3E-941A4EBD5456}" name="Table_SourceData_DataScores_Scope3" displayName="Table_SourceData_DataScores_Scope3" ref="D153:E158" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="14" xr:uid="{261B593E-497B-4BEF-9B69-2007BDE64FE1}" name="Table_SourceData_DataScores_Scope3" displayName="Table_SourceData_DataScores_Scope3" ref="D153:E158" totalsRowShown="0">
   <autoFilter ref="D153:E158" xr:uid="{133D42B0-F6D2-470A-858A-37E6A7F5EC2B}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{F1C79171-18D4-4538-B8B5-4035B9BDADE4}" name="Data source">
+    <tableColumn id="1" xr3:uid="{C1EE8A11-4C9E-4966-A5C3-26B37DE11981}" name="Data source">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{F4879EF9-AFF2-4FBB-8AC4-10E9136CB398}" name="Data score">
+    <tableColumn id="2" xr3:uid="{E2FB9D2B-C748-4304-9DFD-C036ADBC0CC4}" name="Data score">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5383,16 +5406,16 @@
 </file>
 
 <file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="30" xr:uid="{B1B8ACAC-A09F-4E48-8944-728EA0065A24}" name="Table_SourceData_FracWET" displayName="Table_SourceData_FracWET" ref="D134:E136" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{BF469EB8-2588-4054-B098-A53F3E410858}" name="Table_SourceData_FracWET" displayName="Table_SourceData_FracWET" ref="D134:E136" totalsRowShown="0">
   <autoFilter ref="D134:E136" xr:uid="{308E99BE-FE1F-47A4-B2CA-97217277C4E9}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{AC686EA2-8D9A-4D6D-A8A8-062FB3B515CC}" name="Is in leaching zone">
+    <tableColumn id="1" xr3:uid="{F6AC79CD-A94F-48C7-A176-2A272B85F3D0}" name="Is in leaching zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWET_Data(),Table_SourceData_FracWET[[#Headers],[Is in leaching zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{1FCEBDA5-65F4-46B1-B370-C11FB49932FA}" name="FracWET" dataDxfId="36">
+    <tableColumn id="2" xr3:uid="{6170DAC4-0744-47E0-AAD9-DAC43CFE5AB9}" name="FracWET" dataDxfId="19">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWET_Data(),Table_SourceData_FracWET[[#Headers],[Is in leaching zone]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5401,7 +5424,7 @@
 </file>
 
 <file path=xl/tables/table14.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="31" xr:uid="{90C0F7AC-0F98-4652-98CC-95BA4A16C131}" name="Table_SourceData_Common_EFN2O" displayName="Table_SourceData_Common_EFN2O" ref="D186:H199" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="16" xr:uid="{4305B1C9-19CD-4B8D-8B96-79A2D8536944}" name="Table_SourceData_Common_EFN2O" displayName="Table_SourceData_Common_EFN2O" ref="D186:H199" totalsRowShown="0">
   <autoFilter ref="D186:H199" xr:uid="{D41FBEA4-8379-4DF7-A068-BF94D364F1A2}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -5410,19 +5433,19 @@
     <filterColumn colId="4" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{DC10BB70-498C-4145-BAE7-7A04D5280125}" name="Production system j">
+    <tableColumn id="1" xr3:uid="{58415BDE-7033-4D41-99CD-E1505A0958DA}" name="Production system j">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{9A35A152-BB7C-4846-9F6E-3E9C99E73442}" name="EFN2O">
+    <tableColumn id="2" xr3:uid="{AD2AE3C7-1D5D-466B-8F40-4456DF3CEC0C}" name="EFN2O">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{748EC603-7F46-49E5-A98E-535FE8846206}" name="Production system only">
+    <tableColumn id="3" xr3:uid="{4E9D6B84-0855-4CD0-B792-D0F042A170D0}" name="Production system only">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{A56CD644-C6AA-445E-9F25-4B23A92A9B64}" name="Irrigation method">
+    <tableColumn id="4" xr3:uid="{0566DB93-5A8E-4AE3-BF74-80208370D941}" name="Irrigation method">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{CCAB1984-3AF3-43D3-81A5-8CE900C98160}" name="Rainfall zone">
+    <tableColumn id="5" xr3:uid="{19F4D5C9-3BED-4B10-BF43-4F3062FFD290}" name="Rainfall zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5431,16 +5454,16 @@
 </file>
 
 <file path=xl/tables/table15.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="32" xr:uid="{4165A077-B250-4DEE-B369-59E4E7679902}" name="Table_SourceData_FracWETIrrigation" displayName="Table_SourceData_FracWETIrrigation" ref="D142:E147" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="17" xr:uid="{FAB45731-39BC-4119-AF44-EDC8FB1709F6}" name="Table_SourceData_FracWETIrrigation" displayName="Table_SourceData_FracWETIrrigation" ref="D142:E147" totalsRowShown="0">
   <autoFilter ref="D142:E147" xr:uid="{1F48CA34-50DE-46D5-B32A-BB3A1E818E37}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{F2C9E476-6A55-47D9-B3E7-C67EA63535FA}" name="Irrigation type i">
+    <tableColumn id="1" xr3:uid="{ECA1D689-15C8-4240-AF0B-2339B2505350}" name="Irrigation type i">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{88DAA629-0590-41E1-A2CC-610CF9FDB97C}" name="FracWET" dataDxfId="35" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{63F443AA-AF92-4972-9A43-28DD5303AB7A}" name="FracWET" dataDxfId="18" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5449,16 +5472,16 @@
 </file>
 
 <file path=xl/tables/table16.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="33" xr:uid="{87CE216A-9BD9-485A-9EB8-B9E0DFCC2C93}" name="Table_SourceData_EFPastureRangeAndPaddock" displayName="Table_SourceData_EFPastureRangeAndPaddock" ref="D206:E208" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="18" xr:uid="{371B522F-917F-4ACD-9458-69FC198B61EC}" name="Table_SourceData_EFPastureRangeAndPaddock" displayName="Table_SourceData_EFPastureRangeAndPaddock" ref="D206:E208" totalsRowShown="0">
   <autoFilter ref="D206:E208" xr:uid="{D5BE3F89-D70E-4C53-A71C-E756622DEF38}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{AF9CBDC1-27EF-4EED-B8DF-92F594F394C9}" name="Climate zone">
+    <tableColumn id="1" xr3:uid="{57BA94E0-4353-4531-A9B7-0BD09C2F39A5}" name="Climate zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data(), Table_SourceData_EFPastureRangeAndPaddock[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{F1AF672B-1B1A-422D-A6B3-621D6214B60E}" name="EFPRP" dataDxfId="34" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{ECF28C34-784F-4443-AC3F-91CC4B569429}" name="EFPRP" dataDxfId="17" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data(), Table_SourceData_EFPastureRangeAndPaddock[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5467,16 +5490,16 @@
 </file>
 
 <file path=xl/tables/table17.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="34" xr:uid="{DEDBE9B8-7638-405B-BBEA-28F4A90E5FDC}" name="Table_SourceData_Common_MonthToSeason" displayName="Table_SourceData_Common_MonthToSeason" ref="D212:E224" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="19" xr:uid="{369329C8-DB8D-4D0E-9B06-EFA978CF5551}" name="Table_SourceData_Common_MonthToSeason" displayName="Table_SourceData_Common_MonthToSeason" ref="D212:E224" totalsRowShown="0">
   <autoFilter ref="D212:E224" xr:uid="{97796C3A-D95E-4077-AA20-A8FE4145DAAD}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{F56D4BDC-1A8D-48FE-B31E-DE67F81E1C52}" name="Month">
+    <tableColumn id="1" xr3:uid="{7BBAB911-7034-463A-A259-26F762291EFF}" name="Month">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{84A8C1F6-0D04-4FAE-AC8C-5DCE94CD2667}" name="Season" dataDxfId="33" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{852E648F-5F9C-46FA-9908-6794C77296AF}" name="Season" dataDxfId="16" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5485,7 +5508,7 @@
 </file>
 
 <file path=xl/tables/table18.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="35" xr:uid="{FB2C0D77-D19C-4F62-8E5B-44E9019BF690}" name="Table_SourceData_Common_MCFTemperatureZone" displayName="Table_SourceData_Common_MCFTemperatureZone" ref="D231:S250" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="20" xr:uid="{1CD7F9BA-A860-4D13-96A5-D248791B9E7B}" name="Table_SourceData_Common_MCFTemperatureZone" displayName="Table_SourceData_Common_MCFTemperatureZone" ref="D231:S250" totalsRowShown="0">
   <autoFilter ref="D231:S250" xr:uid="{1D72DD9B-C8FA-48F4-9A11-20231FF87B5A}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -5505,52 +5528,52 @@
     <filterColumn colId="15" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="16">
-    <tableColumn id="1" xr3:uid="{F0787CE1-8BC3-48A0-BD72-4D31FF2981AB}" name="Temperature zone">
+    <tableColumn id="1" xr3:uid="{201D8979-FF7C-453A-B667-199024E2B34C}" name="Temperature zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{236F7AC5-AA7A-4B5B-A91D-B3234A850B1F}" name="MAT (ºC)" dataDxfId="32" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{4D1AC02F-8E82-4509-89B1-2716B66F0486}" name="MAT (ºC)" dataDxfId="15" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{C188DBCE-83A9-4948-B739-6D8CFA8FB1F1}" name="Anaerobic lagoon" dataDxfId="31" dataCellStyle="Content normal">
+    <tableColumn id="3" xr3:uid="{3E8ABD04-AEA1-4D47-BC62-EFBF6C896BB6}" name="Anaerobic lagoon" dataDxfId="14" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{7F0A7CCE-9091-445B-A615-A547A51F5200}" name="Digester / covered lagoons" dataDxfId="30" dataCellStyle="Content normal">
+    <tableColumn id="4" xr3:uid="{80DBE677-B4C3-417A-A665-EB564D28BB0D}" name="Digester / covered lagoons" dataDxfId="13" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{F45FD72F-73B7-4580-B927-C93DC98F52E5}" name="Liquid systems" dataDxfId="29" dataCellStyle="Content normal">
+    <tableColumn id="5" xr3:uid="{19D86A12-CF53-41E1-91FC-BBFAE1337C22}" name="Liquid systems" dataDxfId="12" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{C72DB022-C4D0-41C7-A672-C4F576EDC815}" name="Daily spread" dataDxfId="28" dataCellStyle="Content normal">
+    <tableColumn id="6" xr3:uid="{D8B7A5D5-4EE7-4138-B10E-8585772D484D}" name="Daily spread" dataDxfId="11" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{98BE1154-A30B-4B37-8D42-1FCB8196ADFF}" name="Composting (passive windrow)" dataDxfId="27" dataCellStyle="Content normal">
+    <tableColumn id="7" xr3:uid="{90823DD6-BAEF-4FF6-8B30-22943C6CDCF3}" name="Composting (passive windrow)" dataDxfId="10" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{FE6F67A9-BD27-47E8-B501-A2D2DDFAFD2B}" name="Solid storage" dataDxfId="26" dataCellStyle="Content normal">
+    <tableColumn id="8" xr3:uid="{6B7D7166-8E93-4AE1-B051-1F04B4681401}" name="Solid storage" dataDxfId="9" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{1612D188-6F19-4A62-9F7B-984763732FCD}" name="Pit storage" dataDxfId="25" dataCellStyle="Content normal">
+    <tableColumn id="9" xr3:uid="{DC1D60D4-29B5-471C-BAA2-3DEE5AAB8583}" name="Pit storage" dataDxfId="8" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{F2B629FE-D9AC-43BB-8712-0244FAFED160}" name="Deep litter" dataDxfId="24" dataCellStyle="Content normal">
+    <tableColumn id="10" xr3:uid="{41DACAC1-0D98-48B5-8460-B0116A3AF04F}" name="Deep litter" dataDxfId="7" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{AEB1AAB3-C1F7-4609-811C-C8F71F27BEA7}" name="Poultry manure with bedding" dataDxfId="23" dataCellStyle="Content normal">
+    <tableColumn id="11" xr3:uid="{BF6B9A03-9FD2-4ED4-84CB-31D1AF5E4C81}" name="Poultry manure with bedding" dataDxfId="6" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{30CD3C79-0D8E-4E7F-87FD-8F4EA6115707}" name="Poultry manure without bedding" dataDxfId="22" dataCellStyle="Content normal">
+    <tableColumn id="12" xr3:uid="{F8BEEA81-CBF5-4D71-919E-51AD5C895CCE}" name="Poultry manure without bedding" dataDxfId="5" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{B6966C78-6D1B-4D36-AF62-930896F91722}" name="Direct processing" dataDxfId="21" dataCellStyle="Content normal">
+    <tableColumn id="13" xr3:uid="{72CF2D5A-601E-4D6E-A8F7-4E38EE26BEDD}" name="Direct processing" dataDxfId="4" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{319A832A-BD0E-4DCC-BA3B-3FE865BD158B}" name="Direct application" dataDxfId="20" dataCellStyle="Content normal">
+    <tableColumn id="14" xr3:uid="{0FA785A1-F692-4116-B111-DF035FDAB2E0}" name="Direct application" dataDxfId="3" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{1A0A5924-316D-4A5B-BC7C-60065B83EB70}" name="Pasture range and paddock" dataDxfId="19" dataCellStyle="Content normal">
+    <tableColumn id="15" xr3:uid="{CA3B68FC-2459-4B41-8FA5-89F71CACEA45}" name="Pasture range and paddock" dataDxfId="2" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{41772124-674F-460B-8395-C3AE2FD9C178}" name="MAT raw" dataDxfId="18" dataCellStyle="Content normal">
+    <tableColumn id="16" xr3:uid="{3CE97BDD-6B3C-444F-A89E-CBCF5BE8630A}" name="MAT raw" dataDxfId="1" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5559,16 +5582,16 @@
 </file>
 
 <file path=xl/tables/table19.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="36" xr:uid="{79E744CC-76BA-4DD4-AC67-44F809197B90}" name="Table_SourceData_Common_EFOrganicFertCropResidues" displayName="Table_SourceData_Common_EFOrganicFertCropResidues" ref="D257:E259" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="21" xr:uid="{2427E3FE-20C9-48BC-9900-B053F33E4DB1}" name="Table_SourceData_Common_EFOrganicFertCropResidues" displayName="Table_SourceData_Common_EFOrganicFertCropResidues" ref="D257:E259" totalsRowShown="0">
   <autoFilter ref="D257:E259" xr:uid="{56E01C14-1BB8-4015-9158-4CEB4D3B605C}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{9399ABC9-646D-4864-8875-225CB798A120}" name="Climate Zone">
+    <tableColumn id="1" xr3:uid="{81CD9500-E293-4F47-8F44-0A9637B40A71}" name="Climate Zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data(), Table_SourceData_Common_EFOrganicFertCropResidues[[#Headers],[Climate Zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{828CCD4A-4F4D-4667-8FE5-C00753040270}" name="EFNi &amp; EFN2Oi" dataDxfId="17" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{9498A226-47F2-4947-A630-33C016BE7207}" name="EFNi &amp; EFN2Oi" dataDxfId="0" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data(), Table_SourceData_Common_EFOrganicFertCropResidues[[#Headers],[Climate Zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5595,20 +5618,20 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{BAB9D8D8-A94C-4765-A2F4-FBF3EB858A25}" name="Table_AustralianStates" displayName="Table_AustralianStates" ref="D6:F14" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1AA2A8B4-A80C-4AB2-BA43-6F04FDC3537D}" name="Table_AustralianStates" displayName="Table_AustralianStates" ref="D6:F14" totalsRowShown="0">
   <autoFilter ref="D6:F14" xr:uid="{E0906749-7FC7-47DE-82F6-F796C4463018}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{171512E4-DD77-45F5-A7DC-7F756E38E58B}" name="State/Territory">
+    <tableColumn id="1" xr3:uid="{1E459E17-570F-473A-8980-7B6D81D37E5B}" name="State/Territory">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{67A2E349-9D96-4192-BF1C-973FE556FADB}" name="Common Name">
+    <tableColumn id="2" xr3:uid="{5A6E954E-3668-4779-A7E1-DEA029D5ABA5}" name="Common Name">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{6C9B778A-6BC0-4CBC-92FC-621305E6382A}" name="Abbreviation">
+    <tableColumn id="3" xr3:uid="{4BDA8551-47F3-405A-BA82-AD4CBD4171A0}" name="Abbreviation">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5617,12 +5640,12 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{D149E782-62CC-4024-A8A1-E5EA1E498D2A}" name="Table_WASA4Areas" displayName="Table_WASA4Areas" ref="D20:D30" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{FF0E4ED5-BF92-435A-81DD-28BC628CA69F}" name="Table_WASA4Areas" displayName="Table_WASA4Areas" ref="D20:D30" totalsRowShown="0">
   <autoFilter ref="D20:D30" xr:uid="{5FA81339-C6C8-4D36-BEEA-6C4AEDD9E676}">
     <filterColumn colId="0" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="1">
-    <tableColumn id="1" xr3:uid="{9D56D53A-6694-4B57-A02F-8E9551CB7A14}" name="SA 4 Name">
+    <tableColumn id="1" xr3:uid="{92D4788C-B668-4467-9E20-1F2C4ACA6AA0}" name="SA 4 Name">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5631,16 +5654,16 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="22" xr:uid="{BDA15D44-60E0-4864-879A-DD3FCF3315EE}" name="Table_GWPData" displayName="Table_GWPData" ref="D36:E43" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{4A342019-1CD6-43F1-9B8B-19844FB619F3}" name="Table_GWPData" displayName="Table_GWPData" ref="D36:E43" totalsRowShown="0">
   <autoFilter ref="D36:E43" xr:uid="{B8E87A66-3E41-4AD3-925D-01EE21B43D7A}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{29D0E979-289C-49F4-93D3-6124A7F51BE5}" name="Gas">
+    <tableColumn id="1" xr3:uid="{FB490942-3D54-4BE0-91CA-449605238280}" name="Gas">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{F1769B4A-4D35-4F1E-B9DA-F65441424CD9}" name="CO2-e factor">
+    <tableColumn id="2" xr3:uid="{A459959B-FF39-40B6-B6DC-F2780A74EB69}" name="CO2-e factor">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5649,7 +5672,7 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="23" xr:uid="{F352728F-1C63-4F70-B975-4EF1CA2C819D}" name="Table_GasToMolecularConversionFactor" displayName="Table_GasToMolecularConversionFactor" ref="D47:H54" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{A341AE40-1449-4647-BEF7-F9D3F0C9E643}" name="Table_GasToMolecularConversionFactor" displayName="Table_GasToMolecularConversionFactor" ref="D47:H54" totalsRowShown="0">
   <autoFilter ref="D47:H54" xr:uid="{C1F562BB-DAA6-45BB-951A-7BAFA5B64B45}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -5658,19 +5681,19 @@
     <filterColumn colId="4" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{4AD24F5B-C1DA-4F22-BB17-81A6F8D71410}" name="Gas">
+    <tableColumn id="1" xr3:uid="{C0DDF328-1BED-4360-BFEF-924C6AC4D82E}" name="Gas">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{B50E9557-5672-4944-AC8B-E65E187DE052}" name="Conversion factor">
+    <tableColumn id="5" xr3:uid="{BAB18FB3-08A2-4934-BB20-538BE79A7A18}" name="Conversion factor">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{85EF82D1-0A91-4FC0-96CC-52E8DE88242E}" name="Conversion factor 1">
+    <tableColumn id="2" xr3:uid="{4949AC83-09D6-4011-9029-279D974A3305}" name="Conversion factor 1">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{CC9DBC6F-DAFE-493B-A2AD-0B39C1BB80DB}" name="Conversion factor 2">
+    <tableColumn id="3" xr3:uid="{C76FA6ED-4341-46F9-BFED-7CBABCA64676}" name="Conversion factor 2">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{B37F38D1-8FCD-4B3A-A678-FA02F0A28A61}" name="Conversion factor combined">
+    <tableColumn id="4" xr3:uid="{CDFDD25F-DED0-4488-B31E-82904829EBEA}" name="Conversion factor combined">
       <calculatedColumnFormula>Table_GasToMolecularConversionFactor[[#This Row],[Conversion factor 1]]/Table_GasToMolecularConversionFactor[[#This Row],[Conversion factor 2]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5679,7 +5702,7 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="24" xr:uid="{0570EA12-3286-4560-9BE6-60258611BC9D}" name="Table_SourceData_ClimateZones" displayName="Table_SourceData_ClimateZones" ref="D89:S97" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{4E3050EA-B79B-49D4-B5B9-D1A9CCC6CE93}" name="Table_SourceData_ClimateZones" displayName="Table_SourceData_ClimateZones" ref="D89:S97" totalsRowShown="0">
   <autoFilter ref="D89:S97" xr:uid="{5A437AE9-7724-4CF2-ACCF-291078682FB9}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -5699,52 +5722,52 @@
     <filterColumn colId="15" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="16">
-    <tableColumn id="1" xr3:uid="{6ED0CF1D-7CD9-4066-8EE4-25FE923E5D3B}" name="Climate zone" totalsRowCellStyle="Content bold">
+    <tableColumn id="1" xr3:uid="{45884169-378B-4498-ADF1-E96DC5275FE2}" name="Climate zone" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{CF963462-2F2C-4BF6-A892-086541529F20}" name="MAT" totalsRowDxfId="52" totalsRowCellStyle="Content bold">
+    <tableColumn id="2" xr3:uid="{ED0A42F7-E0D4-42BC-9323-7AC1E8B79522}" name="MAT" totalsRowDxfId="35" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{1B3F3876-9D6F-447A-A423-66E21AC0558A}" name="MAP" totalsRowDxfId="51" totalsRowCellStyle="Content bold">
+    <tableColumn id="3" xr3:uid="{622E8002-CAE7-49C2-9FFA-1A4BAFB06DFC}" name="MAP" totalsRowDxfId="34" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{A4802F3E-DC20-40F1-AC5A-D182C68519BB}" name="Frost days per year" totalsRowDxfId="50" totalsRowCellStyle="Content bold">
+    <tableColumn id="4" xr3:uid="{F8E36194-7A47-4596-B5DF-0A053B710457}" name="Frost days per year" totalsRowDxfId="33" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{1F7F9556-3126-439E-875C-D76E463F8036}" name="Elevation" totalsRowDxfId="49" totalsRowCellStyle="Content bold">
+    <tableColumn id="5" xr3:uid="{EE33DF38-3BFD-4B2F-9290-9B33D7636732}" name="Elevation" totalsRowDxfId="32" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{DBB23AF3-C817-42CE-BE89-ADDA8D904773}" name="MAP:PET" totalsRowDxfId="48" totalsRowCellStyle="Content bold">
+    <tableColumn id="6" xr3:uid="{DB707C1D-8B5A-40AE-B0CB-ACC5F5BAED97}" name="MAP:PET" totalsRowDxfId="31" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{60216B5C-783A-4916-AACF-4280FF3BECAD}" name="Min temp" totalsRowDxfId="47" totalsRowCellStyle="Content bold">
+    <tableColumn id="7" xr3:uid="{DAEF6587-4D6A-471A-B522-BF43D986CCE7}" name="Min temp" totalsRowDxfId="30" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{1FE05885-DAC3-47B8-BEB3-6920E3033122}" name="Max temp" totalsRowDxfId="46" totalsRowCellStyle="Content bold">
+    <tableColumn id="8" xr3:uid="{A7A388B4-D412-4A7C-B6D2-34F31643DDE2}" name="Max temp" totalsRowDxfId="29" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{2B644226-778B-401E-99C4-CEB1DE3EDAE1}" name="Min rainfall" totalsRowDxfId="45" totalsRowCellStyle="Content bold">
+    <tableColumn id="9" xr3:uid="{C7774772-3E03-4EC3-AC58-04273FF2770F}" name="Min rainfall" totalsRowDxfId="28" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{B73B8CF5-08DF-4843-B82E-B9FB1813470C}" name="Max rainfall" totalsRowDxfId="44" totalsRowCellStyle="Content bold">
+    <tableColumn id="10" xr3:uid="{1C785463-634C-4A75-9E08-1460391DDE5F}" name="Max rainfall" totalsRowDxfId="27" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{2516891E-4C4A-426D-8B84-5149409BFCBC}" name="Min frost days" totalsRowDxfId="43" totalsRowCellStyle="Content bold">
+    <tableColumn id="11" xr3:uid="{F5A7C9F9-EF30-4040-BC45-6B92F662AE9B}" name="Min frost days" totalsRowDxfId="26" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{189C1E5A-6304-4676-A9EB-8B293F4544B2}" name="Max frost days" totalsRowDxfId="42" totalsRowCellStyle="Content bold">
+    <tableColumn id="15" xr3:uid="{F977A7B1-31AE-494D-974F-3D327EAFF2F3}" name="Max frost days" totalsRowDxfId="25" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{14B9E9DB-0BCC-48C2-8CCA-57C75DB45D61}" name="Min elevation" totalsRowDxfId="41" totalsRowCellStyle="Content bold">
+    <tableColumn id="12" xr3:uid="{1459972D-2D14-42EE-BC43-754376D25250}" name="Min elevation" totalsRowDxfId="24" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{67D82299-FF27-4038-A32D-781A02A531ED}" name="Max elevation" totalsRowDxfId="40" totalsRowCellStyle="Content bold">
+    <tableColumn id="16" xr3:uid="{3AA61A84-02F5-46DD-A817-E0CDAFC9780D}" name="Max elevation" totalsRowDxfId="23" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{FB2C0315-064C-437A-86D7-3E8FA9F4822B}" name="Min MAP:PET" totalsRowDxfId="39" totalsRowCellStyle="Content bold">
+    <tableColumn id="13" xr3:uid="{C26C9901-FD25-4AAD-B733-940BFE803266}" name="Min MAP:PET" totalsRowDxfId="22" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{378C37E5-D887-4B5C-9001-232EF0A792B4}" name="Max MAP:PET" totalsRowDxfId="38" totalsRowCellStyle="Content bold">
+    <tableColumn id="17" xr3:uid="{9A372779-77EF-4DB9-AB02-ECFD5B7D98D2}" name="Max MAP:PET" totalsRowDxfId="21" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5753,16 +5776,16 @@
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="25" xr:uid="{4D2F7A40-370B-4A1A-BB7E-6930F4763E13}" name="Table_SourceData_WetDryZones" displayName="Table_SourceData_WetDryZones" ref="D63:E77" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{47A643D6-250B-4288-95C7-D531914A05DD}" name="Table_SourceData_WetDryZones" displayName="Table_SourceData_WetDryZones" ref="D63:E77" totalsRowShown="0">
   <autoFilter ref="D63:E77" xr:uid="{3597E019-B21E-4B76-BCC8-D02D497BCFA9}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{44AAB7B6-31A0-4522-84AE-3428F2D4D02F}" name="Climate zone" totalsRowCellStyle="Content bold">
+    <tableColumn id="1" xr3:uid="{4E9B4188-5808-495A-A79C-64E72C0B70A0}" name="Climate zone" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{8619F0C7-D005-4F89-B453-E75937AA076E}" name="Wet or Dry Zone" totalsRowDxfId="37" totalsRowCellStyle="Content bold">
+    <tableColumn id="2" xr3:uid="{5CB38AB7-C02B-48C0-895B-24D1A618FE0B}" name="Wet or Dry Zone" totalsRowDxfId="20" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5771,7 +5794,7 @@
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="26" xr:uid="{DA18547E-C2B9-4253-9B23-ECFAF5D3F0C4}" name="Table_SourceData_TemperatureZones" displayName="Table_SourceData_TemperatureZones" ref="D109:G112" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{B4DFA00C-D850-4006-8609-B45FCAAE779C}" name="Table_SourceData_TemperatureZones" displayName="Table_SourceData_TemperatureZones" ref="D109:G112" totalsRowShown="0">
   <autoFilter ref="D109:G112" xr:uid="{AB16FEAB-AB03-45E1-BBD4-66D29CD412DF}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -5779,16 +5802,16 @@
     <filterColumn colId="3" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{05952A61-6A28-4826-9977-99686E3CA96D}" name="Temperature Zone">
+    <tableColumn id="1" xr3:uid="{CD9A6B60-1C08-4D63-8066-1589EC35997E}" name="Temperature Zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{F49ABE84-00CE-4251-9431-9E6E70A546AC}" name="MAT">
+    <tableColumn id="2" xr3:uid="{83B2600F-93D9-4755-9041-01F6534CE049}" name="MAT">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{0323FC01-6733-41DC-9E79-98C1FED01EC8}" name="Min MAT">
+    <tableColumn id="3" xr3:uid="{F49B0660-4DA0-4849-82F9-CF78D665A4FF}" name="Min MAT">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{F9992E54-F3A7-462B-BC56-E5BA0C72765F}" name="Max MAT">
+    <tableColumn id="4" xr3:uid="{208E1DC2-ECC8-450C-9EC7-877BF3C64AA8}" name="Max MAT">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -7819,87 +7842,87 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="D39:H43">
-    <cfRule type="cellIs" dxfId="16" priority="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="52" priority="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F148:F149">
-    <cfRule type="cellIs" dxfId="15" priority="21" operator="lessThan">
+    <cfRule type="cellIs" dxfId="51" priority="21" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F160:F161">
-    <cfRule type="cellIs" dxfId="14" priority="20" operator="lessThan">
+    <cfRule type="cellIs" dxfId="50" priority="20" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F172:F173">
-    <cfRule type="cellIs" dxfId="13" priority="19" operator="lessThan">
+    <cfRule type="cellIs" dxfId="49" priority="19" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F260:F261">
-    <cfRule type="cellIs" dxfId="12" priority="94" operator="lessThan">
+    <cfRule type="cellIs" dxfId="48" priority="94" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F265:F266">
-    <cfRule type="cellIs" dxfId="11" priority="93" operator="lessThan">
+    <cfRule type="cellIs" dxfId="47" priority="93" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F270:F271">
-    <cfRule type="cellIs" dxfId="10" priority="92" operator="lessThan">
+    <cfRule type="cellIs" dxfId="46" priority="92" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F294:F295">
-    <cfRule type="cellIs" dxfId="9" priority="86" operator="lessThan">
+    <cfRule type="cellIs" dxfId="45" priority="86" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F299:F300">
-    <cfRule type="cellIs" dxfId="8" priority="85" operator="lessThan">
+    <cfRule type="cellIs" dxfId="44" priority="85" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F304:F305">
-    <cfRule type="cellIs" dxfId="7" priority="84" operator="lessThan">
+    <cfRule type="cellIs" dxfId="43" priority="84" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I65:I69">
-    <cfRule type="cellIs" dxfId="6" priority="6" operator="lessThan">
+    <cfRule type="cellIs" dxfId="42" priority="6" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I73 I132">
-    <cfRule type="cellIs" dxfId="5" priority="75" operator="lessThan">
+    <cfRule type="cellIs" dxfId="41" priority="75" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I84:I86">
-    <cfRule type="cellIs" dxfId="4" priority="5" operator="lessThan">
+    <cfRule type="cellIs" dxfId="40" priority="5" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I90:I93">
-    <cfRule type="cellIs" dxfId="3" priority="4" operator="lessThan">
+    <cfRule type="cellIs" dxfId="39" priority="4" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I97:I101">
-    <cfRule type="cellIs" dxfId="2" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="38" priority="2" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J8 I51:I52 H53:H55 I54 I56:I58 I60:I61 I212 I218 E220:G220">
-    <cfRule type="cellIs" dxfId="1" priority="80" operator="lessThan">
+    <cfRule type="cellIs" dxfId="37" priority="80" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J37 I45 F136:F137">
-    <cfRule type="cellIs" dxfId="0" priority="22" operator="lessThan">
+    <cfRule type="cellIs" dxfId="36" priority="22" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9767,7 +9790,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7BB47BE6-A391-432F-B8D2-A68CD0E0E20E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04C6ACEF-654B-46AE-A369-1B5BAE8FE3CB}">
   <dimension ref="A1:BY259"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
@@ -13759,15 +13782,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="09eef6d6-daa8-4301-8f9f-b1ec38079286" xsi:nil="true"/>
@@ -13778,11 +13792,16 @@
 </p:properties>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgAvAC8AIAAtAC0ALQAgAFcAbwByAGsAYgBvAG8AawAgAG0AbwBkAHUAbABlACAALQAtAC0AXABuAC8ALwAgAEEAIABmAGkAbABlACAAbwBmACAAbgBhAG0AZQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAG8AZgAgAHQAaABlACAAZgBvAHIAbQA6AFwAbgAvAC8AIAAgACAAIABuAGEAbQBlACAAPQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AOwBcAG4AXABuACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhACIALAAiAHQAZQB4AHQAIgA6ACIALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgBTAG8AdQByAGMAZQAgAGQAYQB0AGEAIAB0AGgAYQB0ACAAaQBzACAAYwBvAG0AbQBvAG4AIABhAGMAcgBvAHMAcwAgAGEAbABsACAAZQBuAHQAZQByAHAAcgBpAHMAZQAgAHQAeQBwAGUAcwBcAG4ARQB4AGMAZQBsACAAbQBvAGQAdQBsAGUAIABuAGEAbQBlADoAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFMAbwB1AHIAYwBlADoAIABOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQBcAG4ATgBJAFIAXwAyADAAMgAzAF8AVgBvAGwAMQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXABuAHAAIAA9ACAAZABlAG4AcwBpAHQAeQAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAIAAoADAALgA2ADcAOAA0ACAAawBnAC8AbQAzACkAXABuAFQAYQBrAGUAbgAgAGYAcgBvAG0AIAB0AGgAZQAgAE4AYQB0AGkAbwBuAGEAbAAgAEcAcgBlAGUAbgBoAG8AdQBzAGUAIABhAG4AZAAgAEUAbgBlAHIAZwB5ACAAUgBlAHAAbwByAHQAaQBuAGcAIABcAG4AKABNAGUAYQBzAHUAcgBlAG0AZQBuAHQAKQAgAEQAZQB0AGUAcgBtAGkAbgBhAHQAaQBvAG4AIAAyADAAMAA4AFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHAAIAA9ACAAZABlAG4AcwBpAHQAeQAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcALwBtADMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgADIAMAAyADMAIABWAG8AbAB1AG0AZQAgADEAOgAgAEUAcQB1AGEAdABpAG8AbgBzACAAMwAuAEIALgAxAGEAXwAyACwAIAAzAC4AQgAuADEAYwBfADIALAAgADMALgBCAC4AMwBfADEALAAgADMALgBCAC4ANABnAF8AMgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAMAAuADYANwA4ADQAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAFwAbgBDAGcAIAA9ACAANAA0AC8AMgA4ACAAZgBhAGMAdABvAHIAIAB0AG8AIABjAG8AbgB2AGUAcgB0ACAAZQBsAGUAbQBlAG4AdABhAGwAIABtAGEAcwBzACAAbwBmACAATgAyAE8AIAB0AG8AIABtAG8AbABlAGMAdQBsAGEAcgAgAG0AYQBzAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABOADIATwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBDAGcATgAyAE8AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAYQBjAHQAbwByAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgADIAMAAyADMAIABWAG8AbAB1AG0AZQAgADEAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgANAA0AC8AMgA4ACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAFwAbgBGAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABnAGEAcwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgBhAGMAdABvAHIAIAB0AG8AIABjAG8AbgB2AGUAcgB0ACAAZQBsAGUAbQBlAG4AdABhAGwAIABtAGEAcwBzACAAbwBmACAAZwBhAHMAIAB0AG8AIABtAG8AbABlAGMAdQBsAGEAcgAgAG0AYQBzAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBDAGcAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgBhAGMAdABvAHIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFgAWABYAFgAWABYAFgAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADgALAAgADQALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAYQBzAFwAIgAsACAAXAAiAEMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBcACIALAAgAFwAIgBDAG8AbgB2AGUAcgBzAGkAbwBuACAAZgBhAGMAdABvAHIAIAAxAFwAIgAsACAAXAAiAEMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgADIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyAFwAIgAsACAAXAAiADQANAAvADEAMgBcACIALAAgADQANAAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMASAA0AFwAIgAsACAAXAAiADEANgAvADEAMgBcACIALAAgADEANgAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AMgBPAFwAIgAsACAAXAAiADQANAAvADIAOABcACIALAAgADQANAAsACAAMgA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB4AFwAIgAsACAAXAAiADQANgAvADEANABcACIALAAgADQANgAsACAAMQA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwBcACIALAAgAFwAIgAyADgALwAxADIAXAAiACwAIAAyADgALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAE8AMgAgAEwAaQBtAGUAXAAiACwAIABcACIANAA0AC8AMQAyAFwAIgAsACAANAA0ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBNAFYATwBDAFwAIgAsACAAXAAiADEANAAvADEAMgBcACIALAAgADEANAAsACAAMQAyAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABOADIATwBcAG4ARwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAGcAcgBlAGUAbgBoAG8AdQBzAGUAIABnAGEAcwBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABnAHIAZQBlAG4AaABvAHUAcwBlACAAZwBhAHMAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARwBXAFAATgAyAE8AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgBhAGMAdABvAHIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFgAWABYAFgAWABYAFgAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADgALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAYQBzAFwAIgAsACAAXAAiAEMATwAyAC0AZQAgAGYAYQBjAHQAbwByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAE8AMgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBIADQAXAAiACwAIAAyADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgAyAE8AXAAiACwAIAAyADYANQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAEYANABcACIALAAgADYANgAzADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwAyAEYANgBcACIALAAgADEAMgAyADAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAEYANgBcACIALAAgADIAMgA4ADAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAEYAMwBcACIALAAgADEANwAyADAAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAcwB0AGEAdABlAHMAIABhAG4AZAAgAHQAZQByAHIAaQB0AG8AcgBpAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA5ACwAIAAzACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHQAYQB0AGUALwBUAGUAcgByAGkAdABvAHIAeQBcACIALAAgAFwAIgBDAG8AbQBtAG8AbgAgAE4AYQBtAGUAXAAiACwAIABcACIAQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AZQB3ACAAUwBvAHUAdABoACAAVwBhAGwAZQBzAFwAIgAsACAAXAAiAE4AZQB3ACAAUwBvAHUAdABoACAAVwBhAGwAZQBzAFwAIgAsACAAXAAiAE4AUwBXAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAQwBhAHAAaQB0AGEAbAAgAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAEEAQwBUAFwAIgAsACAAXAAiAEEAQwBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAGkAYwB0AG8AcgBpAGEAXAAiACwAIABcACIAVgBpAGMAdABvAHIAaQBhAFwAIgAsACAAXAAiAFYASQBDAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBRAHUAZQBlAG4AcwBsAGEAbgBkAFwAIgAsACAAXAAiAFEAdQBlAGUAbgBzAGwAYQBuAGQAXAAiACwAIABcACIAUQBMAEQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAbwB1AHQAaAAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFMAbwB1AHQAaAAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFMAQQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQBcACIALAAgAFwAIgBXAEEAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAYQBzAG0AYQBuAGkAYQBcACIALAAgAFwAIgBUAGEAcwBtAGEAbgBpAGEAXAAiACwAIABcACIAVABBAFMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwByAHQAaABlAHIAbgAgAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAE4AbwByAHQAaABlAHIAbgAgAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAE4AVABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQBCAFMAIABTAHQAYQB0AGkAcwB0AGMAYQBsACAAQQByAGUAYQBzACAATABlAHYAZQBsACAANAAgAC0AIABXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAEIAdQByAGUAYQB1ACAAbwBmACAAUwB0AGEAdABpAHMAdABpAGMAcwAgACgAQQBCAFMAKQAgAC0AIABTAHQAYQB0AGkAcwB0AGkAYwBhAGwAIABBAHIAZQBhAHMAIABMAGUAdgBlAGwAIAAyACAALQAgADIAMAAyADEAIAAtACAAUwBoAGEAcABlAGYAaQBsAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADEALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAQQAgADQAIABOAGEAbQBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBCAHUAbgBiAHUAcgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAGEAbgBkAHUAcgBhAGgAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABJAG4AbgBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABOAG8AcgB0AGgAIABFAGEAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAATgBvAHIAdABoACAAVwBlAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAFMAbwB1AHQAaAAgAEUAYQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABTAG8AdQB0AGgAIABXAGUAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAAVwBoAGUAYQB0ACAAQgBlAGwAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhACAALQAgAE8AdQB0AGIAYQBjAGsAIAAoAE4AbwByAHQAaAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAATwB1AHQAYgBhAGMAawAgACgAUwBvAHUAdABoACkAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAdwBlAHQAIABhAG4AZAAgAGQAcgB5ACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAyADoAIABUAHIAYQBuAHMAbABhAHQAaQBuAGcAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBzACAAdABvACAAdwBlAHQAIABhAG4AZAAgAGQAcgB5ACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAdwBhAHIAbQAgAC8AIABjAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAvACAAZAByAHkAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAIABhAG4AZAAgAGgAaQBnAGgAIAB0AGUAbQBwACAAYwBsAGEAcwBzAGUAcwAgAHQAbwAgAGEAYwBjAG8AbQBtAG8AZABhAHQAZQAgAGMAbABpAG0AYQB0AGUAIABzAGMAZQBuAGEAcgBpAG8AcwAgAGUAeABjAGwAdQBkAGUAZAAgAGIAeQAgAFYARQBFAFIARwAgAGMAcgBpAHQAZQByAGkAYQAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAGkAeABlAGQAIAB0AHkAcABvACAALQAgAEMAaABhAG4AZwBlAGQAIABcAHUAMAAwADIANwBGAHIAeQBcAHUAMAAwADIANwAgAHQAbwAgAFwAdQAwADAAMgA3AEQAcgB5AFwAdQAwADAAMgA3AC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADUALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAFcAZQB0ACAAbwByACAARAByAHkAIABaAG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABtAG8AbgB0AGEAbgBlAFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAHcAZQB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABkAHIAeQBcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdABcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAtACAAaABpAGcAaAAgAHQAZQBtAHAAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAaABpAGcAaAAgAHQAZQBtAHAAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA1ACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAB3AGEAcgBtACAALwAgAGMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC8AIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdAAgAGEAbgBkACAAaABpAGcAaAAgAHQAZQBtAHAAIABjAGwAYQBzAHMAZQBzACAAdABvACAAYQBjAGMAbwBtAG0AbwBkAGEAdABlACAAYwBsAGkAbQBhAHQAZQAgAHMAYwBlAG4AYQByAGkAbwBzACAAZQB4AGMAbAB1AGQAZQBkACAAYgB5ACAAVgBFAEUAUgBHACAAYwByAGkAdABlAHIAaQBhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAaQB4AGUAZAAgAHQAeQBwAG8AIABpAG4AIABNAEEAVAAgAHYAYQBsAHUAZQAgAGYAbwByACAAdwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAYwBoAGEAbgBnAGUAZAAgADEAMAAgAHQAbwAgADEAMQAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIABtAGkAbgAgAGEAbgBkACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAZgBvAHIAIABNAEEAVAAsACAATQBBAFAALAAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAIABwAGUAcgAgAHkAZQBhAHIALAAgAGUAbABlAHYAYQB0AGkAbwBuACwAIABNAEEAUAA6AFAARQBUACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlAHMAIABmAHIAbwBtACAAcgBlAGEAbAAgAGMAbABpAG0AYQB0AGUAIABkAGEAdABhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAQQBGACAAYQBjAGMAZQBwAHQAcwAgAHIAYQBpAG4AZgBhAGwAbAAgAGEAcwAgAGEAIABwAHIAbwB4AHkAIABmAG8AcgAgAHAAcgBlAGMAaQBwAGkAdABhAHQAaQBvAG4ALgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOQAsACAAMQA2ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAGwAaQBtAGEAdABlACAAWgBvAG4AZQBcACIALAAgAFwAIgBNAEEAVABcACIALAAgAFwAIgBNAEEAUABcACIALAAgAFwAIgBGAHIAbwBzAHQAIABkAGEAeQBzACAAcABlAHIAIAB5AGUAYQByAFwAIgAsACAAXAAiAEUAbABlAHYAYQB0AGkAbwBuAFwAIgAsACAAXAAiAE0AQQBQADoAUABFAFQAXAAiACwAIABcACIATQBpAG4AIAB0AGUAbQBwAFwAIgAsACAAXAAiAE0AYQB4ACAAdABlAG0AcABcACIALAAgAFwAIgBNAGkAbgAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBNAGEAeAAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBNAGkAbgAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAXAAiACwAIABcACIATQBhAHgAIABmAHIAbwBzAHQAIABkAGEAeQBzAFwAIgAsACAAXAAiAE0AaQBuACAAZQBsAGUAdgBhAHQAaQBvAG4AXAAiACwAIABcACIATQBhAHgAIABlAGwAZQB2AGEAdABpAG8AbgBcACIALAAgAFwAIgBNAGkAbgAgAE0AQQBQADoAUABFAFQAXAAiACwAIABcACIATQBpAG4AIABNAEEAUAA6AFAARQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABtAG8AbgB0AGEAbgBlAFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQA4ACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAwADAAIABtAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAMQA4AC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAANwAsACAAMQAwADAAMAAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAHcAZQB0AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQA4ACAAQwBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADIAMAAwADAAIABtAG0AXAAiACwAIABcACIAZCIgADcAXAAiACwAIABcACIAZCIgADEAMAAwADAAIABtAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAMQA4AC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAyADAAMAAwAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQAuADkAOQA5ACwAIAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAOAAgAEMAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADAAMAAwACAAbQBtACAALQAgAGQiIAAyADAAMAAwACAAbQBtAFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgADEAOAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAAMQAwADAAMAAuADAAMAAxACwAIAAyADAAMAAwACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQAuADkAOQA5ACwAIAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAGQAcgB5AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQA4ACAAQwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAwADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAXAAiACwAIAAxADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgADEALgAwADAAMQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAGQiIAAxAFwAIgAsACAAMQAwAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAgAC0AOQA5ADkAOQA5ADkALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMAAgAEMAIAAtACAAZCIgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxAFwAIgAsACAALQA5ADkAOQA5ADkAOQAsACAAMQAwACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAxAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMAAgAEMAIAAtACAAZCIgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAZCIgADEAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAMQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBBAHAAcABlAG4AZABpAGMAZQBzAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdABlADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AQQBUACAAPQAgAG0AZQBhAG4AIABhAG4AbgB1AGEAbAAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBBAFAAIAA9ACAAbQBlAGEAbgAgAGEAbgBuAHUAYQBsACAAcAByAGUAYwBpAHAAaQB0AGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABFAFQAIAA9ACAAcABvAHQAZQBuAHQAaQBhAGwAIABlAHYAYQBwAG8AdAByAGEAbgBzAHAAaQByAGEAdABpAG8AbgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABBAGQAZABlAGQAIABlAHgAdAByAGEAIABNAEEAVAAgAG0AaQBuACAAYQBuAGQAIABNAEEAVAAgAG0AYQB4ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGMAYQBsAGMAdQBsAGEAdABlACAAegBvAG4AZQAgAGYAcgBvAG0AIAByAGUAYQBsACAAdABlAG0AcABlAHIAYQB0AHUAcgBlACAAZABhAHQAYQAuAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANAAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AHUAcgBlACAAWgBvAG4AZQBcACIALAAgAFwAIgBNAGUAZABpAGEAbgAgAEEAbgBuAHUAYQBsACAAVABlAG0AcABlAHIAYQB0AHUAcgBlACAAKABNAEEAVAApAFwAIgAsACAAXAAiAE0AaQBuACAATQBBAFQAXAAiACwAIABcACIATQBhAHgAIABNAEEAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgAFwAIgBlIiAAMgA2ACAAQwBcACIALAAgADIANgAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIABcACIAMQA1ACAALQAgADIANQAgAEMAXAAiACwAIAAxADUALAAgADIANQAuADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIABcACIAZCIgADEANAAgAEMAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADQALgA5ADkAOQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAAQQBkAGQAZQBkACAAZQB4AHQAcgBhACAAUgBhAGkAbgBmAGEAbABsACAAbQBpAG4AIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAG0AYQB4ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGMAYQBsAGMAdQBsAGEAdABlACAAegBvAG4AZQAgAGYAcgBvAG0AIAByAGUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAZABhAHQAYQAuAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBhAGkAbgBmAGEAbABsACAAWgBvAG4AZQBcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABtAGkAbgBcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABtAGEAeABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbAAgAFwAdQAwADAAMwBlACAANgAwADAAbQBtAFwAIgAsACAANgAwADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATABvAHcAIAByAGEAaQBuAGYAYQBsAGwAXAAiACwAIABcACIAQQBuAG4AdQBhAGwAIAByAGEAaQBuAGYAYQBsAGwAIABkIiAANgAwADAAbQBtAFwAIgAsACAALQA5ADkAOQA5ADkAOQAsACAANgAwADAAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABaAG8AbgBlAFwAIgAsACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAGMAcgBpAHQAZQByAGkAYQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATABlAGEAYwBoAGkAbgBnACAAbwBjAGMAdQByAHMAXAAiACwAIABcACIAowMoADXYX9w12E7cNdhW3DXYW9wpAFwAdQAwADAAMwBlAKMDKAA12DjcNdhH3DAAKQArADXYYNw12FzcNdhW3DXYWdwgADXYZNw12E7cNdhh3DXYUtw12F/cIAAOITXYXNw12FncNdhR3DXYVtw12FvcNdhU3CAANdhQ3DXYTtw12F3cNdhO3DXYUNw12FbcNdhh3DXYZtxcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATABlAGEAYwBoAGkAbgBnACAAZABvAGUAcwAgAG4AbwB0ACAAbwBjAGMAdQByAFwAIgAsACAAXAAiAKMDKAA12F/cNdhO3DXYVtw12FvcKQBkIqMDKAA12DjcNdhH3DAAKQArADXYYNw12FzcNdhW3DXYWdwgADXYZNw12E7cNdhh3DXYUtw12F/cIAAOITXYXNw12FncNdhR3DXYVtw12FvcNdhU3CAANdhQ3DXYTtw12F3cNdhO3DXYUNw12FbcNdhh3DXYZtxcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXABuADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAbgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAEQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcwAgAGkAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAXAAiACwAXAAiAEYAcgBhAGMAVwBFAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFkAZQBzACAALQAgAGkAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwAgAC0AIABuAG8AdAAgAGkAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAXAAiACwAIAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoACgAXAAiAFwAIgApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAGQAYQB0AGEAIABzAGMAbwByAGUAcwAgAGYAbwByACAAcwBjAG8AcABlACAAMwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABYAFgAWABYAFgAWABYAFgAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABhAHQAYQAgAHMAbwB1AHIAYwBlAFwAIgAsACAAXAAiAEQAYQB0AGEAIABzAGMAbwByAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAbgB0AGUAcgBuAGEAdABpAG8AbgBhAGwAIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAcwBjAG8AcABlACAAMwAgAGQAYQB0AGEAYgBhAHMAZQBcACIALAAgADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB0AGEAdABlACAAbwByACAAcgBlAGcAaQBvAG4AYQBsACAAcwBjAG8AcABlACAAMwAgAGQAYQB0AGEAYgBhAHMAZQBcACIALAAgADMAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBtAGkAcwBzAGkAbwBuAHMAIABpAG4AdABlAG4AcwBpAHQAeQAgAGMAYQBsAGMAdQBsAGEAdABlAGQAIABmAHIAbwBtACAAYQBwAHAAcgBvAHYAZQBkACAAbQBlAHQAaABvAGQAXAAiACwAIAA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAZQByAGkAZgBpAGUAZAAgAGMAcgBlAGQAZQBuAHQAaQBhAGwAIABtAGEAdABjAGgAaQBuAGcAIABJAFMATwAxADQAMAA2ADcAXAAiACwAIAA1AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXABuADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAbgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgARABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAVgBvAGwAdQBtAGUAIAAxADoAIABMAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmACAAKAAzAC4ARAAuAGIALgAyACkAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAcgBhAGMATABFAEEAQwBIAFwAIgAsADAALgAyADQAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoACgAXAAiAFwAIgApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABuAGkAdAByAG8AZwBlAG4AIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABuAGkAdAByAG8AZwBlAG4AIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABrAGcAIABOADIATwAtAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgAFYAbwBsAHUAbQBlACAAMQA6ACAARQBxAHUAYQB0AGkAbwBuACAAMwAuAEQALgBCAF8AMQAwAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARgBsAGUAYQBjAGgAXAAiACwAMAAuADAAMQAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoACgAXAAiAFwAIgApACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXABuAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADEAXABuAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAZgBvAHIAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AIAAoAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AKQAgACgARQBGAE4AMgBPACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAGYAbwByACAAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAGsAZwAgAE4AMgBPAC0ATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADIALgAyAC4AMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQA1ACwAIAA1ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABqAFwAIgAsAFwAIgBFAEYATgAyAE8AXAAiACwAIABcACIAUAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAbwBuAGwAeQBcACIALAAgAFwAIgBJAHIAcgBpAGcAYQB0AGkAbwBuACAAbQBlAHQAaABvAGQAXAAiACwAIABcACIAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsADAALgAwADAANQA5ACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwAFwAIgAsADAALgAwADAANwAsACAAXAAiAEMAcgBvAHAAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsADAALgAwADAAMQA4ACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEwAbwB3ACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQBcACIALAAwAC4AMAAwADEAOAAsACAAXAAiAFAAYQBzAHQAdQByAGUAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcAAgACgAbABvAHcAIAByAGEAaQBuAGYAYQBsAGwAKQBcACIALAAwAC4AMAAwADIAOQAsACAAXAAiAEMAcgBvAHAAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAGMAcgBvAHAAIAAoAGgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAKQBcACIALAAwAC4AMAAwADgALAAgAFwAIgBDAHIAbwBwAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIASABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB1AGcAYQByAFwAIgAsADAALgAwADEAOQA5ACwAIABcACIAUwB1AGcAYQByAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AdAB0AG8AbgBcACIALAAwAC4AMAAwADUAMwAsACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAG8AcgB0AGkAYwB1AGwAdAB1AHIAYQBsACAAYwByAG8AcABzAFwAIgAsADAALgAwADAANgA0ACwAIABcACIASABvAHIAdABpAGMAdQBsAHQAdQByAGEAbAAgAGMAcgBvAHAAcwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBpAGMAZQAgACgAYwBvAG4AdABpAG4AdQBvAHUAcwAgAGYAbABvAG8AZABpAG4AZwApAFwAIgAsADAALgAwADAAMwAsACAAXAAiAFIAaQBjAGUAXAAiACwAIABcACIAQwBvAG4AdABpAG4AdQBvAHUAcwAgAGYAbABvAG8AZABpAG4AZwBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBpAGMAZQAgACgAcwBpAG4AZwBsAGUAIABhAG4AZAAgAG0AdQBsAHQAaQBwAGwAZQAgAGQAcgBhAGkAbgBhAGcAZQAsACAAbwByACAAYQBsAHQAZQByAG4AYQB0AGUAIAB3AGUAdAB0AGkAbgBnACAAYQBuAGQAIABkAHIAeQBpAG4AZwApAFwAIgAsADAALgAwADAANQAsACAAXAAiAFIAaQBjAGUAXAAiACwAIABcACIAUwBpAG4AZwBsAGUAIABhAG4AZAAgAG0AdQBsAHQAaQBwAGwAZQAgAGQAcgBhAGkAbgBhAGcAZQAsACAAbwByACAAYQBsAHQAZQByAG4AYQB0AGUAIAB3AGUAdAB0AGkAbgBnACAAYQBuAGQAIABkAHIAeQBpAG4AZwBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBxAHUAYQBjAHUAbAB0AHUAcgBlAFwAIgAsADAALgAwADAAMgA2ACwAIABcACIAQQBxAHUAYQBjAHUAbAB0AHUAcgBlAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAG8AcgBlAHMAdAByAHkAXAAiACwAMAAuADAAMAAxADgALAAgAFwAIgBGAG8AcgBlAHMAdAByAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA1ACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGUAbQBvAHYAZQBkACAAZAB1AHAAbABpAGMAYQB0AGUAIABcAHUAMAAwADIANwBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAB1ADAAMAAyADcAIAByAG8AdwAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGUAbQBvAHYAZQBkACAAYQBzAHQAZQByAGkAcwBrAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAFwAdQAwADAAMgA3AHAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAG8AbgBsAHkAXAB1ADAAMAAyADcALAAgAFwAdQAwADAAMgA3AHIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAXAB1ADAAMAAyADcAIABhAG4AZAAgAFwAdQAwADAAMgA3AGkAcgByAGkAZwBhAHQAaQBvAG4AIABtAGUAdABoAG8AZABcAHUAMAAwADIANwAgAGMAbwBsAHUAbQBuAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAdQBwAGwAaQBjAGEAdABlAGQAIABcAHUAMAAwADIANwBuAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQBcAHUAMAAwADIANwAgAHIAbwB3ACAAdwBpAHQAaAAgAHMAYQBtAGUAIABFAEYAIABmAG8AcgAgAGwAbwB3ACAAYQBuAGQAIABoAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAFwAbgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABDAGgAYQBwAHQAZQByACAAMQAsACAAcwBlAGMAdABpAG8AbgAgADEALgA4AC4AMgAgAEwAZQBhAGMAaABpAG4AZwAsACAAYwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBzAFwAbgBJAFAAQwBDADoAIABOADIATwAgAEUATQBJAFMAUwBJAE8ATgBTACAARgBSAE8ATQAgAE0AQQBOAEEARwBFAEQAIABTAE8ASQBMAFMALAAgAEEATgBEACAAQwBPADIAIABFAE0ASQBTAFMASQBPAE4AUwAgAEYAUgBPAE0AIABMAEkATQBFACAAQQBOAEQAIABVAFIARQBBACAAQQBQAFAATABJAEMAQQBUAEkATwBOAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwBXAEUAVAAgAGYAbwByACAAaQByAHIAaQBnAGEAdABpAG8AbgAgAHQAeQBwAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAEMAaABhAHAAdABlAHIAIAAxACwAIABzAGUAYwB0AGkAbwBuACAAMQAuADgALgAyACAATABlAGEAYwBoAGkAbgBnACwAIABjAGwAaQBtAGEAdABlACAAYQBuAGQAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBJAFAAQwBDACAAMgAwADEAOQAgAFIAZQBmAGkAbgBlAG0AZQBuAHQAIABWAG8AbAB1AG0AZQAgADQAOgAgAEMAaABhAHAAdABlAHIAIAAxADEAOgAgAE4AMgBPACAARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAATQBhAG4AYQBnAGUAZAAgAFMAbwBpAGwAcwAsACAAYQBuAGQAIABDAE8AMgAgAEUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAEwAaQBtAGUAIABhAG4AZAAgAFUAcgBlAGEAIABBAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGkAbwBuACAAdAB5AHAAZQAgAGkAcgBcACIALABcACIARgByAGEAYwBXAEUAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAByAGkAcAAgAGkAcgByAGkAZwBhAHQAaQBvAG4AXAAiACwAIAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAcAByAGkAbgBrAGwAZQByACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB1AHIAZgBhAGMAZQAgAGkAcgByAGkAZwBhAHQAaQBvAG4AXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AdABoAGUAcgAgAGkAcgByAGkAZwBhAHQAaQBvAG4AXAAiACwAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAARgBSAE8ATQAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAAVABhAGIAbABlACAAYwByAGUAYQB0AGUAZAAgAGIAYQBzAGUAZAAgAG8AbgAgAFYARQBFAFIARwAgAHQAZQB4AHQAIABcAHUAMAAwADIANwBBAHIAZQBhAHMAIABhAHIAZQAgAHMAdQBiAGoAZQBjAHQAIAB0AG8AIABsAGUAYQBjAGgAaQBuAGcAIAAoAGkALgBlAC4ALAAgAGkAbgAgAHQAaABlACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQApACAAdwBoAGUAbgAuAC4ALgAgAHQAaABlACAAbABhAG4AZAAgAGkAcwAgAGkAcgByAGkAZwBhAHQAZQBkACAAKABlAHgAYwBlAHAAdAAgAGQAcgBpAHAAIABpAHIAcgBpAGcAYQB0AGkAbwBuACkALgBcAHUAMAAwADIANwBcACIAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAFwAbgBUAGEAYgBsAGUAIABBAC4AMgAuADIALgAyADoAIABFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAdQByAGkAbgBlACAAYQBuAGQAIABkAHUAbgBnACAAZABlAHAAbwBzAGkAdABlAGQAIABvAG4AIABwAGEAcwB0AHUAcgBlACwAIAByAGEAbgBnAGUAIABvAHIAIABwAGEAZABkAG8AYwBrACAAKABrAGcAIABOADIATwAtAE4ALwBrAGcAIABOACkAIAAoAEUARgBQAFIAUAApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAdQByAGkAbgBlACAAYQBuAGQAIABkAHUAbgBnACAAZABlAHAAbwBzAGkAdABlAGQAIABvAG4AIABwAGEAcwB0AHUAcgBlACwAIAByAGEAbgBnAGUAIABvAHIAIABwAGEAZABkAG8AYwBrAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AMgBPACAALQAgAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADIALgAyAC4AMgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAEUARgBQAFIAUABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAAyAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABDAGgAYQBuAGcAZQBkACAAXAB1ADAAMAAyADcARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBzAFwAdQAwADAAMgA3ACAAdABvACAAcwBpAG4AZwB1AGwAYQByACAAXAB1ADAAMAAyADcARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcAHUAMAAwADIANwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAG8AbgB0AGgAcwAgAHQAbwAgAFMAZQBhAHMAbwBuAHMAIABNAGEAcABwAGkAbgBnAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBvAG4AdABoAFwAIgAsACAAXAAiAFMAZQBhAHMAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAGEAbgB1AGEAcgB5AFwAIgAsACAAXAAiAFMAdQBtAG0AZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAGUAYgByAHUAYQByAHkAXAAiACwAIABcACIAUwB1AG0AbQBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQByAGMAaABcACIALAAgAFwAIgBBAHUAdAB1AG0AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBwAHIAaQBsAFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAGEAeQBcACIALAAgAFwAIgBBAHUAdAB1AG0AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASgB1AG4AZQBcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASgB1AGwAeQBcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQB1AGcAdQBzAHQAXAAiACwAIABcACIAVwBpAG4AdABlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAZQBwAHQAZQBtAGIAZQByAFwAIgAsACAAXAAiAFMAcAByAGkAbgBnAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBPAGMAdABvAGIAZQByAFwAIgAsACAAXAAiAFMAcAByAGkAbgBnAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdgBlAG0AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAZQBjAGUAbQBiAGUAcgBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBhAG4AdQByAGUAIABNAGEAbgBhAGcAZQBtAGUAbgB0ACAAEyAgAE0AZQB0AGgAYQBuAGUAIABjAG8AbgB2AGUAcgBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABwAGUAcgAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAIAAoAGYAcgBhAGMAdABpAG8AbgApACAAKABNAEMARgBpAG0AKQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAxAC4AOAAuADEAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIAMgAsACAAMQA2ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAE0AQQBUACAAKAC6AEMAKQBcACIALAAgAFwAIgBVAG4AYwBvAHYAZQByAGUAZAAgAGEAbgBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuAFwAIgAsACAAXAAiAEMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBcACIALAAgAFwAIgBMAGkAcQB1AGkAZAAgAFMAbAB1AHIAcgB5ACAAKAB3AGkAdABoAG8AdQB0ACAAbgBhAHQAdQByAGEAbAAgAGMAcgB1AHMAdAApAFwAIgAsACAAXAAiAEQAYQBpAGwAeQAgAHMAcAByAGUAYQBkACAAKABiACkAXAAiACwAIABcACIAQwBvAG0AcABvAHMAdABpAG4AZwAgACgAcABhAHMAcwBpAHYAZQAgAHcAaQBuAGQAcgBvAHcAKQBcACIALAAgAFwAIgBTAG8AbABpAGQAIABTAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAFAAaQB0ACAAUwB0AG8AcgBhAGcAZQAgAFwAdQAwADAAMwBjADEAIABtAG8AbgB0AGgAXAAiACwAIABcACIARABlAGUAcAAgAEwAaQB0AHQAZQByAFwAIgAsACAAXAAiAFAAbwB1AGwAdAByAHkAIABNAGEAbgB1AHIAZQAgACgAdwBpAHQAaAAvAHcAaQB0AGgAbwB1AHQAIABsAGkAdAB0AGUAcgApAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAcAByAG8AYwBlAHMAcwBpAG4AZwAgAGkAbgB0AG8AIABwAGUAbABsAGUAdABpAHoAZQBkACAAZgBlAHIAdABpAGwAaQBzAGUAcgBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgAgAHQAbwAgAHMAbwBpAGwAXAAiACwAIABcACIAUABhAHMAdAB1AHIAZQAsACAAUgBhAG4AZwBlACAAYQBuAGQAIABQAGEAZABkAG8AYwBrACAAKABjACkAKABkACkAXAAiACwAIABcACIATQBBAFQAIAByAGEAdwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgAFwAIgBkIjEAMABcACIALAAgADAALgA2ADYALAAgADAALgAxACwAIAAwAC4AMQAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIAAxADEALAAgADAALgA2ADgALAAgADAALgAxACwAIAAwAC4AMQAxACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgADEAMgAsACAAMAAuADcALAAgADAALgAxACwAIAAwAC4AMQAzACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgADEAMwAsACAAMAAuADcAMQAsACAAMAAuADEALAAgADAALgAxADQALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQA0ACwAIAAwAC4ANwAzACwAIAAwAC4AMQAsACAAMAAuADEANQAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA1ACwAIAAwAC4ANwA0ACwAIAAwAC4AMQAsACAAMAAuADEANwAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEANQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEANgAsACAAMAAuADcANQAsACAAMAAuADEALAAgADAALgAxADgALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADcALAAgADAALgA3ADYALAAgADAALgAxACwAIAAwAC4AMgAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEANwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEAOAAsACAAMAAuADcANwAsACAAMAAuADEALAAgADAALgAyADIALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADkALAAgADAALgA3ADcALAAgADAALgAxACwAIAAwAC4AMgA0ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgAwACwAIAAwAC4ANwA4ACwAIAAwAC4AMQAsACAAMAAuADIANgAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIAMQAsACAAMAAuADcAOAAsACAAMAAuADEALAAgADAALgAyADkALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADIALAAgADAALgA3ADgALAAgADAALgAxACwAIAAwAC4AMwAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgAzACwAIAAwAC4ANwA5ACwAIAAwAC4AMQAsACAAMAAuADMANAAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIANAAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgAzADcALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADUALAAgADAALgA3ADkALAAgADAALgAxACwAIAAwAC4ANAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AXAAiACwAIAAyADYALAAgADAALgA3ADkALAAgADAALgAxACwAIAAwAC4ANAA0ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AXAAiACwAIAAyADcALAAgADAALgA4ACwAIAAwAC4AMQAsACAAMAAuADQAOAAsACAAMAAuADAAMQAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIANwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtAFwAIgAsACAAXAAiAGUiMgA4AFwAIgAsACAAMAAuADgALAAgADAALgAxACwAIAAwAC4ANQAsACAAMAAuADAAMQAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBBAG4AYQBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuAFwAIgAsACAAXAAiAEQAaQBnAGUAcwB0AGUAcgAgAC8AIABjAG8AdgBlAHIAZQBkACAAbABhAGcAbwBvAG4AcwBcACIALAAgAFwAIgBMAGkAcQB1AGkAZAAgAHMAeQBzAHQAZQBtAHMAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAXAAiACwAIABcACIAQwBvAG0AcABvAHMAdABpAG4AZwAgACgAcABhAHMAcwBpAHYAZQAgAHcAaQBuAGQAcgBvAHcAKQBcACIALAAgAFwAIgBTAG8AbABpAGQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAFAAaQB0ACAAcwB0AG8AcgBhAGcAZQBcACIALAAgAFwAIgBEAGUAZQBwACAAbABpAHQAdABlAHIAXAAiACwAIABcACIAUABvAHUAbAB0AHIAeQAgAG0AYQBuAHUAcgBlACAAdwBpAHQAaAAgAGIAZQBkAGQAaQBuAGcAXAAiACwAIABcACIAUABvAHUAbAB0AHIAeQAgAG0AYQBuAHUAcgBlACAAdwBpAHQAaABvAHUAdAAgAGIAZQBkAGQAaQBuAGcAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABwAHIAbwBjAGUAcwBzAGkAbgBnAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuAFwAIgAsACAAXAAiAFAAYQBzAHQAdQByAGUAIAByAGEAbgBnAGUAIABhAG4AZAAgAHAAYQBkAGQAbwBjAGsAXAAiACwAIABcACIATQBBAFQAIAByAGEAdwBcACIAIABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAOgAgAEEAZABkAGUAZAAgAHIAbwB3ACAAbwBmACAATgBJAFIAIABNAE0AQQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgAgAEQAdQBwAGwAaQBjAGEAdABlAGQAIABcAHUAMAAwADIANwBQAG8AdQBsAHQAcgB5ACAAdwBpAHQAaAAgAGEAbgBkACAAdwBpAHQAaABvAHUAdAAgAGwAaQB0AHQAZQByAFwAdQAwADAAMgA3ACAAYwBvAGwAdQBtAG4AIAB3AGkAdABoACAAcwBlAHAAYQByAGEAdABlACAATgBJAFIAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AIABBAGQAZABlAGQAIABcAHUAMAAwADIANwBNAEEAVAAgAHIAYQB3AFwAdQAwADAAMgA3ACAAYwBvAGwAdQBtAG4AIAB0AG8AIABhAGwAbABvAHcAIABsAG8AbwBrAHUAcAAgAG8AZgAgAG4AdQBtAGIAZQByAHMALgBcACIAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAbgBkACAAYwByAG8AcAAgAHIAZQBzAGkAZAB1AGUAcwAgAHIAZQB0AHUAcgBuAGUAZAAgAHQAbwAgAHQAaABlACAAcwBvAGkAbABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBGAE4AaQAgAFwAdQAwADAAMgA2ACAARQBGAE4AMgBPAGkAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABOADIATwAgAC0AIABOACAALwAgAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADIALgAxAC4ANABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgAFwAIgBFAEYATgBpACAAXAB1ADAAMAAyADYAIABFAEYATgAyAE8AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIAAwAC4AMAAwADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAANQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIAXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBcAG4AQwBvAG4AdgBlAHIAdAAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcAG4ARQBOADIATwAgAEMATwAyAGUAXABuAHQAIABDAE8AMgBlAFwAbgBFAE4AMgBPADoAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAAoAHQAIABOADIATwApAFwAbgBHAFcAUABOADIATwA6ACAAZwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIAAoAHQAIABDAE8AMgAtAGUAIAAvACAAdAAgAE4AMgBPACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABFAF8ATgAyAE8ALAAgAEcAVwBQAF8ATgAyAE8ALABcAG4AIAAgACAAIABFAF8ATgAyAE8AIAAqACAARwBXAFAAXwBOADIATwBcAG4AIAAgACkAXABuADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAbwBuAHYAZQByAHQAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAB0AG8AIABjAGEAcgBiAG8AbgAgAGQAaQBvAHgAaQBkAGUAIABlAHEAdQBpAHYAYQBsAGUAbgB0ACAAZQBtAGkAcwBzAGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBOADIATwAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAE8AMgBlAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMATwAyAF8AZQAgAD0AIABFAF8AewBOADIATwB9ACAAXABcAHQAaQBtAGUAcwAgAEcAVwBQAF8AewBOADIATwB9AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUATgAyAE8AXAAiACwAXAAiAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAE4AMgBPACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAVwBQAE4AMgBPAFwAIgAsAFwAIgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAATgAyAE8AKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBcAG4AQwBvAG4AdgBlAHIAdAAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcAG4ARQBDAEgANAAgAEMATwAyAGUAXABuAHQAIABDAE8AMgBlAFwAbgBFAEMASAA0ADoAIABtAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAAoAHQAIABDAEgANAApAFwAbgBHAFcAUABDAEgANAA6ACAAZwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAG0AZQB0AGgAYQBuAGUAIAAoAHQAIABDAE8AMgAtAGUAIAAvACAAdAAgAEMASAA0ACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABFAF8AQwBIADQALAAgAEcAVwBQAF8AQwBIADQALABcAG4AIAAgACAAIABFAF8AQwBIADQAIAAqACAARwBXAFAAXwBDAEgANABcAG4AIAAgACkAXABuADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAbwBuAHYAZQByAHQAIABtAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAB0AG8AIABjAGEAcgBiAG8AbgAgAGQAaQBvAHgAaQBkAGUAIABlAHEAdQBpAHYAYQBsAGUAbgB0ACAAZQBtAGkAcwBzAGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBDAEgANAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAE8AMgBlAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMATwAyAF8AZQAgAD0AIABFAF8AewBDAEgANAB9ACAAXABcAHQAaQBtAGUAcwAgAEcAVwBQAF8AewBDAEgANAB9AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUAQwBIADQAXAAiACwAXAAiAE0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAEMASAA0ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAVwBQAEMASAA0AFwAIgAsAFwAIgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbQBlAHQAaABhAG4AZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAAQwBIADQAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIAVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAUgBvAHcAUwB0AGEAcgB0AE4AdQBtAGIAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwALABSAG8AdwBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAYQBuAGQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAUgBPAFcAKABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAApACAAKwAgAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkAIAAtACAAMQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABUAGEAYgBsAGUASABlAGEAZABlAHIAQwBlAGwAbAAsAFwAbgAgACAAQwBPAEwAVQBNAE4AKABUAGEAYgBsAGUASABlAGEAZABlAHIAQwBlAGwAbAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBBAHIAcgBhAHkASQBuAFQAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgAEEAcgByAGEAeQBEAGEAdABhACwAIABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQAsACAAWwBDAG8AbAB1AG0AbgBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAQQBuAGQAQQByAHIAYQB5AF0ALABcAG4AIABJAEYARQBSAFIATwBSACgAXABuACAAIAAgACAAIABJAE4ARABFAFgAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAVQBOAEkAUQBVAEUAKABBAHIAcgBhAHkARABhAHQAYQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBPAFcAKAApAC0AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAUgBvAHcAUwB0AGEAcgB0AE4AdQBtAGIAZQByACgAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwALAAgAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEMATwBMAFUATQBOACgAKQAtAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAEMAbwBsAHUAbQBuAFMAdABhAHIAdABOAHUAbQBiAGUAcgAoAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACkAIAArAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAEMAbwBsAHUAbQBuAHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBBAG4AZABBAHIAcgBhAHkAKQAsACAAMQAsACAAQwBvAGwAdQBtAG4AcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAEEAbgBkAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACAAIAAgACAAKQAsACAAXAAiAFwAIgBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFwAIgBcACIAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEkARgAoAEkAUwBOAFUATQBCAEUAUgAoAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFwAIgBcACIAKQBcAG4AIAAgACAAIAApACwAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApACwAIAAwACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBUAHcAbwBDAG8AbAB1AG0AbgBzAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlADEALAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADIALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAWwBWAGEAbAB1AGUASQBGAEYAYQBsAHMAZQBdACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoADEALAAgACgATABvAG8AawB1AHAAQQByAHIAYQB5ADEAPQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQApACoAKABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABWAGEAbAB1AGUASQBGAEYAYQBsAHMAZQApACwAIABcACIAXAAiACwAIABWAGEAbAB1AGUASQBGAEYAYQBsAHMAZQApACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBPAG4AZQBDAG8AbAB1AG0AbgBBAG4AZABIAGUAYQBkAGUAcgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACwAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMgAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADEALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFsAVgBhAGwAdQBlAEkAZgBGAGEAbABzAGUAXQAsAFwAbgAgACAAIAAgAEkARgBFAFIAUgBPAFIAKABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADEALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACkAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAFYAYQBsAHUAZQBJAGYARgBhAGwAcwBlACkALAAgAFwAIgBcACIALAAgAFYAYQBsAHUAZQBJAGYARgBhAGwAcwBlACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAcABsAGkAdABTAHQAcgBpAG4AZwBJAG4AdABvAEEAcgByAGEAeQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEMAZQBsAGwALAAgAEQAZQBsAGkAbQBpAHQAZQByACwAIABbAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAxAF0ALAAgAFsAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADIAXQAsAFwAbgAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAWABNAEwAKABcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBcAHUAMAAwADMAYwB0AFwAdQAwADAAMwBlAFwAdQAwADAAMwBjAHMAXAB1ADAAMAAzAGUAXAAiACAAXAB1ADAAMAAyADYAXABuACAAIAAgACAAIAAgACAAIABTAFUAQgBTAFQASQBUAFUAVABFACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFMAVQBCAFMAVABJAFQAVQBUAEUAKABTAFUAQgBTAFQASQBUAFUAVABFACgAQwBlAGwAbAAsAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAxACwAXAAiAFwAIgApACwAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADIALABcACIAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAARABlAGwAaQBtAGkAdABlAHIALABcACIAXAB1ADAAMAAzAGMALwBzAFwAdQAwADAAMwBlAFwAdQAwADAAMwBjAHMAXAB1ADAAMAAzAGUAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAKQAgAFwAdQAwADAAMgA2AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFwAdQAwADAAMwBjAC8AcwBcAHUAMAAwADMAZQBcAHUAMAAwADMAYwAvAHQAXAB1ADAAMAAzAGUAXAAiACwAXABuACAAIAAgACAAIAAgACAAIABcACIALwAvAHMAXAAiAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABDAGwAaQBtAGEAdABlAFoAbwBuAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABhAHYAZwBUAGUAbQBwACwAYQB2AGcAUgBhAGkAbgAsAGYAcgBvAHMAdABEAGEAeQBzACwAZQBsAGUAdgAsAG0AYQBwAF8AcABlAHQALABcAG4AIAAgACAAIABtAGkAbgBUAGUAbQBwAEEAcgByAGEAeQAsAG0AYQB4AFQAZQBtAHAAQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4AUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQAsAG0AYQB4AFIAYQBpAG4AZgBhAGwAbABBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBGAHIAbwBzAHQAQQByAHIAYQB5ACwAbQBhAHgARgByAG8AcwB0AEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAEUAbABlAHYAYQB0AGkAbwBuAEEAcgByAGEAeQAsAG0AYQB4AEUAbABlAHYAYQB0AGkAbwBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAFAARQBUAEEAcgByAGEAeQAsAG0AYQB4AFAARQBUAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAGMAbABpAG0AYQB0AGUAWgBvAG4AZQBBAHIAcgBhAHkALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAbQBhAHMAawAsAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBUAGUAbQBwAEEAcgByAGEAeQApAFwAdQAwADAAMwBjAD0AYQB2AGcAVABlAG0AcAApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AFQAZQBtAHAAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBhAHYAZwBUAGUAbQBwACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4AUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQApAFwAdQAwADAAMwBjAD0AYQB2AGcAUgBhAGkAbgApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AFIAYQBpAG4AZgBhAGwAbABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGEAdgBnAFIAYQBpAG4AKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBGAHIAbwBzAHQAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBmAHIAbwBzAHQARABhAHkAcwApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AEYAcgBvAHMAdABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGYAcgBvAHMAdABEAGEAeQBzACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4ARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBlAGwAZQB2ACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBlAGwAZQB2ACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4AUABFAFQAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBtAGEAcABfAHAAZQB0ACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgAUABFAFQAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBtAGEAcABfAHAAZQB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAFQAQQBLAEUAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAKABjAGwAaQBtAGEAdABlAFoAbwBuAGUAQQByAHIAYQB5ACwAbQBhAHMAawAsACAAXAAiAE4AbwAgAG0AYQB0AGMAaABcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAASQB0AGUAbQBGAHIAbwBtAE0AaQBuAE0AYQB4AFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABNAGkAbgBBAHIAcgBhAHkALAAgAE0AYQB4AEEAcgByAGEAeQAsACAASQB0AGUAbQBBAHIAcgBhAHkALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAbQBhAHMAawAsAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABNAGkAbgBBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAE0AYQB4AEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0ATABvAG8AawB1AHAAVgBhAGwAdQBlACkALABcAG4AIAAgACAAIAAgACAAIAAgAEYASQBMAFQARQBSACgASQB0AGUAbQBBAHIAcgBhAHkALAAgAG0AYQBzAGsALAAgAFwAIgBOAG8AIABtAGEAdABjAGgAXAAiACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBTAHUAbQBRAHUAYQBuAHQAaQB0AHkARgByAG8AbQBDAHIAaQB0AGUAcgBpAGEAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAEMAcgBpAHQAZQByAGkAYQAxACwAIABDAHIAaQB0AGUAcgBpAGEAMQBUAHkAcABlAEEAcgByAGEAeQAsACAAUQB1AGEAbgB0AGkAdAB5ACwAIABbAE0AdQBsAHQAaQBwAGwAaQBlAHIAXQAsACAAWwBDAHIAaQB0AGUAcgBpAGEAMgBdACwAWwBDAHIAaQB0AGUAcgBpAGEAMgBBAHIAcgBhAHkAXQAsAFwAbgAgACAATABFAFQAKABcAG4AIAAgACAAIABtAHUAbAB0AGkAcABsAGkAZQByACwAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAE0AdQBsAHQAaQBwAGwAaQBlAHIAKQAsADEALABNAHUAbAB0AGkAcABsAGkAZQByACkALABcAG4AIAAgACAAIABxAHUAYQBuAHQAaQB0AHkALAAgAFEAdQBhAG4AdABpAHQAeQAqAE0AdQBsAHQAaQBwAGwAaQBlAHIALABcAG4AIAAgACAAIABjAHIAaQB0AGUAcgBpAGEAMQAsAC0ALQAoAEMAcgBpAHQAZQByAGkAYQAxAFQAeQBwAGUAQQByAHIAYQB5AD0AQwByAGkAdABlAHIAaQBhADEAKQAsAFwAbgAgACAAIAAgAGMAcgBpAHQAZQByAGkAYQAyACwASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABDAHIAaQB0AGUAcgBpAGEAMgApACwAMQAsAC0ALQAoAEMAcgBpAHQAZQByAGkAYQAyAEEAcgByAGEAeQA9AEMAcgBpAHQAZQByAGkAYQAyACkAKQAsAFwAbgAgACAAIAAgAFMAVQBNAFAAUgBPAEQAVQBDAFQAKABjAHIAaQB0AGUAcgBpAGEAMQAqAGMAcgBpAHQAZQByAGkAYQAyACoAcQB1AGEAbgB0AGkAdAB5ACkAXABuACAAIAApAFwAbgApADsAXABuAFwAbgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAHMAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBTAHQAYQByAHQALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBFAG4AZAAsAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAUwAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgACAAIAAgACAARQAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAXABuACAAIAAgACAAIAAgACAAIABtACwATQBPAE4AVABIACgAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAApACwAXABuACAAIAAgACAAIAAgACAAIABkACwARABBAFkAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAFAAZQByAGkAbwBkAEUAbgBkACwATABBAE0AQgBEAEEAKABzAHQALABFAEQAQQBUAEUAKABzAHQALAAxADIAKQAtADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAQQAsAFMALQAzADYANQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBhACwAWQBFAEEAUgAoAEEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBiACwAWQBFAEEAUgAoAEUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZgBpAHIAcwB0AFkAZQBhAHIALAB5AGEAKwAoAFAAZQByAGkAbwBkAEUAbgBkACgARABBAFQARQAoAHkAYQAsAG0ALABkACkAKQBcAHUAMAAwADMAYwAgAFMAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAbABhAHMAdABZAGUAYQByACwAeQBiAC0AKABEAEEAVABFACgAeQBiACwAbQAsAGQAKQBcAHUAMAAwADMAZQAgAEUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAATQBBAFgAKAAwACwAbABhAHMAdABZAGUAYQByAC0AZgBpAHIAcwB0AFkAZQBhAHIAKwAxACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAFAAZQByAGkAbwBkAHMAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBTAHQAYQByAHQALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBFAG4AZAAsAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAUwAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgACAAIAAgACAARQAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAXABuACAAIAAgACAAIAAgACAAIABtACwATQBPAE4AVABIACgAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAApACwAXABuACAAIAAgACAAIAAgACAAIABkACwARABBAFkAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALAAgAC8AKgBoAGUAbABwAGUAcgA6ACAAZQBuAGQAIABkAGEAdABlACAAZgBvAHIAIABhACAAcgBlAHAAbwByAHQAaQBuAGcAIABwAGUAcgBpAG8AZAAgAHMAdABhAHIAdABpAG4AZwAgAGEAdAAgAGEAIABnAGkAdgBlAG4AIABkAGEAdABlACoALwBcAG4AIAAgACAAIAAgACAAIAAgAFAAZQByAGkAbwBkAEUAbgBkACwATABBAE0AQgBEAEEAKABzAHQALABFAEQAQQBUAEUAKABzAHQALAAxADIAKQAtADEAKQAsACAALwAqAG8AbgBsAHkAIABuAGUAZQBkACAAdABvACAAbABvAG8AawAgAGIAYQBjAGsAIAAzADYANQAgAGQAYQB5AHMAKABtAGEAeAAgAG8AdgBlAHIAbABhAHAAIAB3AGkAbgBkAG8AdwApACoALwBcAG4AIAAgACAAIAAgACAAIAAgAEEALABTAC0AMwA2ADUALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYQAsAFkARQBBAFIAKABBACkALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYgAsAFkARQBBAFIAKABFACkALAAgAC8AKgBpAGYAIAB0AGgAZQAgAGEAbgBjAGgAbwByACAAZgBvAHIAIAB5AGEAIABlAG4AZABzACAAYgBlAGYAbwByAGUAIABTACwAaQB0ACAAYwBhAG4AXAB1ADAAMAAyADcAdAAgAG8AdgBlAHIAbABhAHAAOwAgAG0AbwB2AGUAIAB0AG8AIABuAGUAeAB0ACAAeQBlAGEAcgAqAC8AXABuACAAIAAgACAAIAAgACAAIABmAGkAcgBzAHQAWQBlAGEAcgAsAHkAYQArACgAUABlAHIAaQBvAGQARQBuAGQAKABEAEEAVABFACgAeQBhACwAbQAsAGQAKQApAFwAdQAwADAAMwBjAFMAKQAsACAALwAqAGkAZgAgAHQAaABlACAAYQBuAGMAaABvAHIAIABmAG8AcgAgAHkAYgAgAHMAdABhAHIAdABzACAAYQBmAHQAZQByACAARQAsAGkAdAAgAGMAYQBuAFwAdQAwADAAMgA3AHQAIABvAHYAZQByAGwAYQBwADsAIABtAG8AdgBlACAAdABvACAAcAByAGUAdgBpAG8AdQBzACAAeQBlAGEAcgAqAC8AXABuACAAIAAgACAAIAAgACAAIABsAGEAcwB0AFkAZQBhAHIALAB5AGIALQAoAEQAQQBUAEUAKAB5AGIALABtACwAZAApAFwAdQAwADAAMwBlAEUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAbgAsAE0AQQBYACgAMAAsAGwAYQBzAHQAWQBlAGEAcgAtAGYAaQByAHMAdABZAGUAYQByACsAMQApACwAXABuACAAIAAgACAAIAAgACAAIAB5AHIAcwAsAFMARQBRAFUARQBOAEMARQAoAG4ALAAxACwAZgBpAHIAcwB0AFkAZQBhAHIALAAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAHMAdABhAHIAdABzACwARABBAFQARQAoAHkAcgBzACwAbQAsAGQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZQBuAGQAcwAsAE0AQQBQACgAcwB0AGEAcgB0AHMALABQAGUAcgBpAG8AZABFAG4AZAApACwAXABuACAAIAAgACAAIAAgACAAIAB0AGEAZwAsAEkARgAoAHMAdABhAHIAdABzAD0AUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAIgAgACgAVABoAGkAcwAgAHIAZQBwAG8AcgB0AGkAbgBnACAAYwB5AGMAbABlACkAXAAiACwAXAAiAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABzAHQAYQByAHQAcwBUAGUAeAB0ACwAVABFAFgAVAAoAHMAdABhAHIAdABzACwAXAAiAGQAZAAgAG0AbQBtACAAeQB5AHkAeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZQBuAGQAcwBUAGUAeAB0ACwAVABFAFgAVAAoAGUAbgBkAHMALABcACIAZABkACAAbQBtAG0AIAB5AHkAeQB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABuAD0AMAAsAFwAIgBcACIALABIAFMAVABBAEMASwAoAHMAdABhAHIAdABzAFQAZQB4AHQAIABcAHUAMAAwADIANgAgAFwAIgAgAHQAbwAgAFwAIgAgAFwAdQAwADAAMgA2ACAAZQBuAGQAcwBUAGUAeAB0ACAAXAB1ADAAMAAyADYAIAB0AGEAZwApACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkARgB1AG4AYwB0AGkAbwBuAE4AYQBtAGUAXABuAD0ATABBAE0AQgBEAEEAKABGAHUAbgBjAHQAaQBvAG4ALAAgAFQARQBYAFQAQgBFAEYATwBSAEUAKABGAE8AUgBNAFUATABBAFQARQBYAFQAKABGAHUAbgBjAHQAaQBvAG4AKQAsACAAXAAiACgAXAAiACkAKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAE4AMgBPAEUARgBGAHIAbwBtAFAAcgBvAGQASQByAHIAaQBnAGEAdABpAG8AbgBSAGEAaQBuAGYAYQBsAGwAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAIABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACwAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AQQByAHIAYQB5ACwAIABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkAEEAcgByAGEAeQAsACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAQQByAHIAYQB5ACwAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQALAAgAEkARgAoAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAPQBcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEEAbgB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQAsACAASQBGACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAAgAD0AIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAIABcACIAQQBuAHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKAAxACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEEAcgByAGEAeQA9AFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AKQAqAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAoAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAQQByAHIAYQB5AD0ASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAApACoAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACgAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAQQByAHIAYQB5AD0AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEcAZQB0AEYAcgBhAGMAVwBFAFQAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ALABcAG4AIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQALAAgAFwAbgAgACAAIAAgACAAIAAgACAAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUALABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBMAG8AbwBrAHUAcAAsAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQALAAgAFwAbgAgACAAIAAgACAAIAAgACAAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ATABvAG8AawB1AHAALABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBGAHIAYQBjAFcARQBUACAAKwAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVABcAHUAMAAwADMAZQAwACwAIAAxACwAIAAwACkAXABuACAAIAAgACAAKQApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEMAbwBuAHYAZQByAHQAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAVABvAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUALABcAG4AIAAgACAAIABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBBAHIAcgBhAHkALAAgAFMAdABhAHQAZQBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUALAAgAFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAEEAcgByAGEAeQAsACAAUwB0AGEAdABlAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwBvAHUAcgBjAGUASAB5AHAAZQByAGwAaQBuAGsAXABuAD0ATABBAE0AQgBEAEEAKABUAGEAcgBnAGUAdABDAGUAbABsACwAXABuACAAIABMAEUAVAAoAFwAbgAgACAAIAAgAHMAaAAsACAAVABFAFgAVABBAEYAVABFAFIAKABDAEUATABMACgAXAAiAGYAaQBsAGUAbgBhAG0AZQBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsACAAXAAiAF0AXAAiACkALABcAG4AIAAgACAAIABhAGQAZAByACwAIABDAEUATABMACgAXAAiAGEAZABkAHIAZQBzAHMAXAAiACwAIABUAGEAcgBnAGUAdABDAGUAbABsACkALABcAG4AIAAgACAAIABcACIAIwBcAHUAMAAwADIANwBcACIAIABcAHUAMAAwADIANgAgAHMAaAAgAFwAdQAwADAAMgA2ACAAXAAiAFwAdQAwADAAMgA3ACEAXAAiACAAXAB1ADAAMAAyADYAIABhAGQAZAByAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAbwB1AHIAYwBlAEgAeQBwAGUAcgBsAGkAbgBrAEQAaQBmAGYAZQByAGUAbgB0AFMAaABlAGUAdABcAG4APQBMAEEATQBCAEQAQQAoAFQAYQByAGcAZQB0AEMAZQBsAGwALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAcwBoACwAIABUAEUAWABUAEEARgBUAEUAUgAoAEMARQBMAEwAKABcACIAZgBpAGwAZQBuAGEAbQBlAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAIABcACIAXQBcACIAKQAsAFwAbgAgACAAIAAgAGEAZABkAHIALAAgAEMARQBMAEwAKABcACIAYQBkAGQAcgBlAHMAcwBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsAFwAbgAgACAAIAAgAFwAIgAjAFwAIgAgAFwAdQAwADAAMgA2ACAAYQBkAGQAcgBcAG4AIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgBnAHUAbQBlAG4AdABzAF8AMQBfADIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALABcAG4AIAAgACAAIABDAEgATwBPAFMARQBDAE8ATABTACgAQQByAGcAdQBtAGUAbgB0AHMAQQByAHIAYQB5ACwAIAAxACwAIAAyACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgBnAHUAbQBlAG4AdABzAF8AMwBfADQAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALABcAG4AIAAgACAAIABDAEgATwBPAFMARQBDAE8ATABTACgAQQByAGcAdQBtAGUAbgB0AHMAQQByAHIAYQB5ACwAIAAzACwAIAA0ACkAXABuACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8ARwBlAHQATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUALAAgAE0ATQBTACwAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUAQQByAHIAYQB5ACwAIABNAE0AUwBBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKABcAG4AIAAgACAAIAAgACAAIAAgAE0ARQBEAEkAQQBOACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAE0ASQBOACgAVABlAG0AcABlAHIAYQB0AHUAcgBlAEEAcgByAGEAeQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATQBBAFgAKABUAGUAbQBwAGUAcgBhAHQAdQByAGUAQQByAHIAYQB5ACkAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUAQQByAHIAYQB5ACwAXABuACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATQBNAFMALAAgAE0ATQBTAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBSAGUAcwB1AGwAdABzAEkAdABlAG0ARgByAG8AbQBFAHEAdQBhAHQAaQBvAG4AVABpAHQAbABlAEEAbgBkAFMAbwB1AHIAYwBlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAVABpAHQAbABlAEMAZQBsAGwALAAgAFMAbwB1AHIAYwBlAEMAZQBsAGwALABcAG4AIAAgACAAIABTAFUAQgBTAFQASQBUAFUAVABFACgATABFAEYAVAAoAFMAbwB1AHIAYwBlAEMAZQBsAGwALAAgAEYASQBOAEQAKABcACIALABcACIALAAgAFMAbwB1AHIAYwBlAEMAZQBsAGwAKQAgAC0AMQApACwAIABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAXAAiACwAIABcACIAXAAiACkAIABcAHUAMAAwADIANgAgAFwAIgAgAFwAIgAgAFwAdQAwADAAMgA2ACAAVABpAHQAbABlAEMAZQBsAGwAXABuACkAOwAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuADEAMQAuADEAOgAgAFcAYQBzAHQAZQB3AGEAdABlAHIAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuADEAMQAuADEALgAxAC4AMQAgAE0AZQB0AGgAbwBkACAAMQAgAC0AIABNAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAbwBuAHMAaQB0AGUAIABXAGEAcwB0AGUAdwBhAHQAZQByACAATQBhAG4AYQBnAGUAbQBlAG4AdABcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADEAMQBfADEAXwAxAF8AMQBfAF8AMQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBXAGEAcwB0AGUAdwBhAHQAZQByAFQAcgBlAGEAdABtAGUAbgB0AFwAbgBNAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAdwBhAHMAdABlAHcAYQB0AGUAcgAgAHQAcgBlAGEAdABtAGUAbgB0AFwAbgBFAF8AQwBIADQAXABuAHQAIABDAEgANABcAG4ARQBfAHsAQwBIADQAfQA9AFwAXABmAHIAYQBjAHsAMQB9AHsAMQAwADAAMAB9AFwAXAB0AGkAbQBlAHMAXABcAGwAZQBmAHQAWwBcAFwAbABlAGYAdAAoAFcAXwB0AFwAXAB0AGkAbQBlAHMAXABcAGwAZQBmAHQAKABDAE8ARABfAHsAaQBuAH0AXABcAHQAaQBtAGUAcwAoADEALQBGAF8AewBzAGwAdQBkAGcAZQB9ACkALQBDAE8ARABfAHsAbwB1AHQAfQBcAFwAcgBpAGcAaAB0ACkAXABcAHQAaQBtAGUAcwAgAEMARgBfAHsAdwB3ACwAdAB9AFwAXAB0AGkAbQBlAHMAIABFAEYAXwB7AHcAdwB9AFwAXAByAGkAZwBoAHQAKQArAFwAXABsAGUAZgB0ACgAVwBfAHQAXABcAHQAaQBtAGUAcwBcAFwAbABlAGYAdAAoAEMATwBEAF8AewBpAG4AfQBcAFwAdABpAG0AZQBzACgARgBfAHsAcwBsAHUAZABnAGUAfQAtAEYAXwB7AHIAZQBtAG8AdgBlAGQAfQApAFwAXAByAGkAZwBoAHQAKQBcAFwAdABpAG0AZQBzACAAQwBGAF8AewBzAGwAdQBkAGcAZQAsAHQAfQBcAFwAdABpAG0AZQBzACAARQBGAF8AewBzAGwAdQBkAGcAZQB9AFwAXAByAGkAZwBoAHQAKQAtAFwAXABsAGUAZgB0ACgANgAuADcAOAA0AFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0ANAB9AFwAXAB0AGkAbQBlAHMAKABRAF8AewBjAGEAcAB9ACsAUQBfAHsAZgBsAGEAcgBlAGQAfQArAFEAXwB7AG8AdQB0AH0AKQBcAFwAcgBpAGcAaAB0ACkAKwBcAFwAbABlAGYAdAAoAFEAXwB7AGYAbABhAHIAZQBkAH0AXABcAHQAaQBtAGUAcwAgAEUAQwBfAHsAZgBsAGEAcgBlAGQAfQBcAFwAdABpAG0AZQBzACAARQBGAF8AewBmAGwAYQByAGUAZAAsAEMASAA0AH0AXABcAHIAaQBnAGgAdAApAFwAXAByAGkAZwBoAHQAXQBcAG4AVwBfAHQAIAA9ACAAcQB1AGEAbgB0AGkAdAB5ACAAbwBmACAAdwBhAHMAdABlAHcAYQB0AGUAcgAgAHQAcgBlAGEAdABlAGQAIABhAHQAIABmAGEAYwBpAGwAaQB0AHkAIAB0AHkAcABlACAAdAAgACgAbQAzACkAXABuAEMATwBEAF8AaQBuACAAPQAgAGEAdgBlAHIAYQBnAGUAIABpAG4AbABlAHQAIABDAGgAZQBtAGkAYwBhAGwAIABPAHgAeQBnAGUAbgAgAEQAZQBtAGEAbgBkACAAYwBvAG4AYwBlAG4AdAByAGEAdABpAG8AbgAgAG8AZgAgAHcAYQBzAHQAZQB3AGEAdABlAHIAIAAoAGsAZwAgAEMATwBEAC8AbQAzACkAXABuAEYAXwBzAGwAdQBkAGcAZQAgAD0AIABmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABDAE8ARAAgAHIAZQBtAG8AdgBlAGQAIABmAHIAbwBtACAAdwBhAHMAdABlAHcAYQB0AGUAcgAgAGEAcwAgAHMAbAB1AGQAZwBlAFwAbgBDAE8ARABfAG8AdQB0ACAAPQAgAGEAdgBlAHIAYQBnAGUAIABvAHUAdABsAGUAdAAgAEMATwBEACAAYwBvAG4AYwBlAG4AdAByAGEAdABpAG8AbgAgAG8AZgAgAHcAYQBzAHQAZQB3AGEAdABlAHIAIAAoAGsAZwAgAEMATwBEAC8AbQAzACkAXABuAEMARgBfAHcAdwBfAHQAIAA9ACAAbQBlAHQAaABhAG4AZQAgAGMAbwByAHIAZQBjAHQAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAZgBhAGMAaQBsAGkAdAB5ACAAdAB5AHAAZQAgAHQAIAB1AHMAZQBkACAAdABvACAAdAByAGUAYQB0ACAAdwBhAHMAdABlAHcAYQB0AGUAcgBcAG4ARQBGAF8AdwB3ACAAPQAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAdwBhAHMAdABlAHcAYQB0AGUAcgAgACgAawBnACAAQwBPADIAZQAvAGsAZwAgAEMATwBEACkAXABuAEYAXwByAGUAbQBvAHYAZQBkACAAPQAgAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAEMATwBEACAAcgBlAG0AbwB2AGUAZAAgAGYAcgBvAG0AIAB0AGgAZQAgAHcAYQBzAHQAZQB3AGEAdABlAHIAIAB0AHIAZQBhAHQAbQBlAG4AdAAgAGYAYQBjAGkAbABpAHQAeQAgAGEAbgBkACAAdAByAGEAbgBzAGYAZQByAHIAZQBkACAAZQBsAHMAZQB3AGgAZQByAGUAXABuAEMARgBfAHMAbAB1AGQAZwBlAF8AdAAgAD0AIABtAGUAdABoAGEAbgBlACAAYwBvAHIAcgBlAGMAdABpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABmAGEAYwBpAGwAaQB0AHkAIAB0AHkAcABlACAAdAAgAHUAcwBlAGQAIAB0AG8AIAB0AHIAZQBhAHQAIABzAGwAdQBkAGcAZQBcAG4ARQBGAF8AcwBsAHUAZABnAGUAIAA9ACAAbQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABzAGwAdQBkAGcAZQAgACgAawBnACAAQwBPADIAZQAvAGsAZwAgAEMATwBEACkAXABuAFEAXwBjAGEAcAAgAD0AIABxAHUAYQBuAHQAaQB0AHkAIABvAGYAIABtAGUAdABoAGEAbgBlACAAaQBuACAAcwBsAHUAZABnAGUAIABiAGkAbwBnAGEAcwAgAGMAYQBwAHQAdQByAGUAZAAgAGYAbwByACAAYwBvAG0AYgB1AHMAdABpAG8AbgAgACgAbQAzACAAQwBIADQAKQBcAG4AUQBfAGYAbABhAHIAZQBkACAAPQAgAHEAdQBhAG4AdABpAHQAeQAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAIABpAG4AIABzAGwAdQBkAGcAZQAgAGIAaQBvAGcAYQBzACAAZgBsAGEAcgBlAGQAIAAoAG0AMwAgAEMASAA0ACkAXABuAFEAXwBvAHUAdAAgAD0AIABxAHUAYQBuAHQAaQB0AHkAIABvAGYAIABtAGUAdABoAGEAbgBlACAAaQBuACAAcwBsAHUAZABnAGUAIABiAGkAbwBnAGEAcwAgAHQAcgBhAG4AcwBmAGUAcgByAGUAZAAgAG8AdQB0ACAAbwBmACAAdABoAGUAIAB0AHIAZQBhAHQAbQBlAG4AdAAgAGYAYQBjAGkAbABpAHQAeQAgACgAbQAzACAAQwBIADQAKQBcAG4ARQBDAF8AZgBsAGEAcgBlAGQAIAA9ACAAZQBuAGUAcgBnAHkAIABjAG8AbgB0AGUAbgB0ACAAZgBhAGMAdABvAHIAIABvAGYAIABtAGUAdABoAGEAbgBlACAAaQBuACAAcwBsAHUAZABnAGUAIABiAGkAbwBnAGEAcwAgAGYAbABhAHIAZQBkACAAKABHAEoALwBtADMAKQBcAG4ARQBGAF8AZgBsAGEAcgBlAGQAXwBDAEgANAAgAD0AIABtAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHMAbAB1AGQAZwBlACAAYgBpAG8AZwBhAHMAIABmAGwAYQByAGUAZAAgACgAawBnACAAQwBPADIAZQAvAEcASgApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADEAMQBfADEAXwAxAF8AMQBfAF8AMQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBXAGEAcwB0AGUAdwBhAHQAZQByAFQAcgBlAGEAdABtAGUAbgB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFcAXwB0ACwAIABDAE8ARABfAGkAbgAsACAARgBfAHMAbAB1AGQAZwBlACwAIABDAE8ARABfAG8AdQB0ACwAIABDAEYAXwB3AHcAXwB0ACwAIABFAEYAXwB3AHcALAAgAEYAXwByAGUAbQBvAHYAZQBkACwAIABDAEYAXwBzAGwAdQBkAGcAZQBfAHQALAAgAEUARgBfAHMAbAB1AGQAZwBlACwAIABRAF8AYwBhAHAALAAgAFEAXwBmAGwAYQByAGUAZAAsACAAUQBfAG8AdQB0ACwAIABFAEMAXwBmAGwAYQByAGUAZAAsACAARQBGAF8AZgBsAGEAcgBlAGQAQwBIADQALABcAG4AIAAgACAAIAAoADEALwAxADAAMAAwACkAIAAqACAAKAAoAFcAXwB0ACAAKgAgACgAQwBPAEQAXwBpAG4AIAAqACAAKAAxACAALQAgAEYAXwBzAGwAdQBkAGcAZQApACAALQAgAEMATwBEAF8AbwB1AHQAKQAgACoAIABDAEYAXwB3AHcAXwB0ACAAKgAgAEUARgBfAHcAdwApACAAKwAgACgAVwBfAHQAIAAqACAAKABDAE8ARABfAGkAbgAgACoAIAAoAEYAXwBzAGwAdQBkAGcAZQAgAC0AIABGAF8AcgBlAG0AbwB2AGUAZAApACkAIAAqACAAQwBGAF8AcwBsAHUAZABnAGUAXwB0ACAAKgAgAEUARgBfAHMAbAB1AGQAZwBlACkAIAAtACAAKAA2AC4ANwA4ADQAIAAqACAAMQAwAF4ALQA0ACAAKgAgACgAUQBfAGMAYQBwACAAKwAgAFEAXwBmAGwAYQByAGUAZAAgACsAIABRAF8AbwB1AHQAKQApACAAKwAgACgAUQBfAGYAbABhAHIAZQBkACAAKgAgACgARQBDAF8AZgBsAGEAcgBlAGQAIAAqACAARQBGAF8AZgBsAGEAcgBlAGQAQwBIADQAKQApACkAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADEAXwAxAF8AMQBfADEAXwBfADEAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AVwBhAHMAdABlAHcAYQB0AGUAcgBUAHIAZQBhAHQAbQBlAG4AdABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAHcAYQBzAHQAZQB3AGEAdABlAHIAIAB0AHIAZQBhAHQAbQBlAG4AdABcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQAxAF8AMQBfADEAXwAxAF8AXwAxAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFcAYQBzAHQAZQB3AGEAdABlAHIAVAByAGUAYQB0AG0AZQBuAHQAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwBDAEgANABcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQAxAF8AMQBfADEAXwAxAF8AXwAxAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFcAYQBzAHQAZQB3AGEAdABlAHIAVAByAGUAYQB0AG0AZQBuAHQAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgB0ACAAQwBIADQAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEAMQBfADEAXwAxAF8AMQBfAF8AMQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBXAGEAcwB0AGUAdwBhAHQAZQByAFQAcgBlAGEAdABtAGUAbgB0AF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADEAMQAuADEALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAxACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEAMQBfADEAXwAxAF8AMQBfAF8AMQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBXAGEAcwB0AGUAdwBhAHQAZQByAFQAcgBlAGEAdABtAGUAbgB0AF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEcAcgBlAGUAbgBoAG8AdQBzAGUAIABhAG4AZAAgAEUAbgBlAHIAZwB5ACAAUgBlAHAAbwByAHQAaQBuAGcAIABNAGUAYQBzAHUAcgBlAG0AZQBuAHQAIABEAGUAdABlAHIAbQBpAG4AYQB0AGkAbwBuACAAMgAwADAAOABcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQAxAF8AMQBfADEAXwAxAF8AXwAxAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFcAYQBzAHQAZQB3AGEAdABlAHIAVAByAGUAYQB0AG0AZQBuAHQAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAF8AewBDAEgANAB9AD0AXABcAGYAcgBhAGMAewAxAH0AewAxADAAMAAwAH0AXABcAHQAaQBtAGUAcwBcAFwAbABlAGYAdAB7AFwAXABsAGUAZgB0AHsAVwBfAHQAXABcAHQAaQBtAGUAcwBcAFwAbABlAGYAdABbAEMATwBEAF8AewBpAG4AfQBcAFwAdABpAG0AZQBzACgAMQAtAEYAXwB7AHMAbAB1AGQAZwBlAH0AKQAtAEMATwBEAF8AewBvAHUAdAB9AFwAXAByAGkAZwBoAHQAXQBcAFwAdABpAG0AZQBzACAAQwBGAF8AewB3AHcALAB0AH0AXABcAHQAaQBtAGUAcwAgAEUARgBfAHsAdwB3AH0AXABcAHIAaQBnAGgAdAB9ACsAXABcAGwAZQBmAHQAewBXAF8AdABcAFwAdABpAG0AZQBzAFwAXABsAGUAZgB0AFsAQwBPAEQAXwB7AGkAbgB9AFwAXAB0AGkAbQBlAHMAKABGAF8AewBzAGwAdQBkAGcAZQB9AC0ARgBfAHsAcgBlAG0AbwB2AGUAZAB9ACkAXABcAHIAaQBnAGgAdABdAFwAXAB0AGkAbQBlAHMAIABDAEYAXwB7AHMAbAB1AGQAZwBlACwAdAB9AFwAXAB0AGkAbQBlAHMAIABFAEYAXwB7AHMAbAB1AGQAZwBlAH0AXABcAHIAaQBnAGgAdAB9AC0AXABcAGwAZQBmAHQAewA2AC4ANwA4ADQAXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQA0AH0AXABcAHQAaQBtAGUAcwAgAFwAXABsAGUAZgB0AFsAIABRAF8AewBjAGEAcAB9ACsAUQBfAHsAZgBsAGEAcgBlAGQAfQArAFEAXwB7AG8AdQB0AH0AXABcAHIAaQBnAGgAdABdAFwAXAByAGkAZwBoAHQAfQArAFwAXABsAGUAZgB0AHsAUQBfAHsAZgBsAGEAcgBlAGQAfQBcAFwAdABpAG0AZQBzACAAXABcAGwAZQBmAHQAWwAgAEUAQwBfAHsAZgBsAGEAcgBlAGQAfQBcAFwAdABpAG0AZQBzACAARQBGAF8AewBmAGwAYQByAGUAZAAsAEMASAA0AH0AXABcAHIAaQBnAGgAdABdAFwAXAByAGkAZwBoAHQAfQBcAFwAcgBpAGcAaAB0AH0AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEAMQBfADEAXwAxAF8AMQBfAF8AMQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBXAGEAcwB0AGUAdwBhAHQAZQByAFQAcgBlAGEAdABtAGUAbgB0AF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADUALAAgADQALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBfAHQAXAAiACwAIABcACIAcQB1AGEAbgB0AGkAdAB5ACAAbwBmACAAdwBhAHMAdABlAHcAYQB0AGUAcgAgAHQAcgBlAGEAdABlAGQAIABhAHQAIABmAGEAYwBpAGwAaQB0AHkAIAB0AHkAcABlACAAdABcACIALAAgAFwAIgBtADMAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAE8ARABfAGkAbgBcACIALAAgAFwAIgBhAHYAZQByAGEAZwBlACAAaQBuAGwAZQB0ACAAQwBoAGUAbQBpAGMAYQBsACAATwB4AHkAZwBlAG4AIABEAGUAbQBhAG4AZAAgAGMAbwBuAGMAZQBuAHQAcgBhAHQAaQBvAG4AIABvAGYAIAB3AGEAcwB0AGUAdwBhAHQAZQByAFwAIgAsACAAXAAiAGsAZwAgAEMATwBEAC8AbQAzAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBfAHMAbAB1AGQAZwBlAFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAEMATwBEACAAcgBlAG0AbwB2AGUAZAAgAGYAcgBvAG0AIAB3AGEAcwB0AGUAdwBhAHQAZQByACAAYQBzACAAcwBsAHUAZABnAGUAXAAiACwAIABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPAEQAXwBvAHUAdABcACIALAAgAFwAIgBhAHYAZQByAGEAZwBlACAAbwB1AHQAbABlAHQAIABDAE8ARAAgAGMAbwBuAGMAZQBuAHQAcgBhAHQAaQBvAG4AIABvAGYAIAB3AGEAcwB0AGUAdwBhAHQAZQByAFwAIgAsACAAXAAiAGsAZwAgAEMATwBEAC8AbQAzAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBGAF8AdwB3AF8AdABcACIALAAgAFwAIgBtAGUAdABoAGEAbgBlACAAYwBvAHIAcgBlAGMAdABpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABmAGEAYwBpAGwAaQB0AHkAIAB0AHkAcABlACAAdAAgAHUAcwBlAGQAIAB0AG8AIAB0AHIAZQBhAHQAIAB3AGEAcwB0AGUAdwBhAHQAZQByAFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARgBfAHcAdwBcACIALAAgAFwAIgBtAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHcAYQBzAHQAZQB3AGEAdABlAHIAXAAiACwAIABcACIAawBnACAAQwBIADQALwBrAGcAIABDAE8ARABcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAXwByAGUAbQBvAHYAZQBkAFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAEMATwBEACAAcgBlAG0AbwB2AGUAZAAgAGYAcgBvAG0AIAB0AGgAZQAgAHcAYQBzAHQAZQB3AGEAdABlAHIAIAB0AHIAZQBhAHQAbQBlAG4AdAAgAGYAYQBjAGkAbABpAHQAeQAgAGEAbgBkACAAdAByAGEAbgBzAGYAZQByAHIAZQBkACAAZQBsAHMAZQB3AGgAZQByAGUAXAAiACwAIABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBGAF8AcwBsAHUAZABnAGUAXwB0AFwAIgAsACAAXAAiAG0AZQB0AGgAYQBuAGUAIABjAG8AcgByAGUAYwB0AGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAGYAYQBjAGkAbABpAHQAeQAgAHQAeQBwAGUAIAB0ACAAdQBzAGUAZAAgAHQAbwAgAHQAcgBlAGEAdAAgAHMAbAB1AGQAZwBlAFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARgBfAHMAbAB1AGQAZwBlAFwAIgAsACAAXAAiAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAcwBsAHUAZABnAGUAXAAiACwAIABcACIAawBnACAAQwBIADQALwBrAGcAIABDAE8ARABcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEAXwBjAGEAcABcACIALAAgAFwAIgBxAHUAYQBuAHQAaQB0AHkAIABvAGYAIABtAGUAdABoAGEAbgBlACAAaQBuACAAcwBsAHUAZABnAGUAIABiAGkAbwBnAGEAcwAgAGMAYQBwAHQAdQByAGUAZAAgAGYAbwByACAAYwBvAG0AYgB1AHMAdABpAG8AbgBcACIALAAgAFwAIgBtADMAIABDAEgANABcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEAXwBmAGwAYQByAGUAZABcACIALAAgAFwAIgBxAHUAYQBuAHQAaQB0AHkAIABvAGYAIABtAGUAdABoAGEAbgBlACAAaQBuACAAcwBsAHUAZABnAGUAIABiAGkAbwBnAGEAcwAgAGYAbABhAHIAZQBkACAAYgB5ACAAdABoAGUAIAB0AHIAZQBhAHQAbQBlAG4AdAAgAGYAYQBjAGkAbABpAHQAeQBcACIALAAgAFwAIgBtADMAIABDAEgANABcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEAXwBvAHUAdABcACIALAAgAFwAIgBxAHUAYQBuAHQAaQB0AHkAIABvAGYAIABtAGUAdABoAGEAbgBlACAAaQBuACAAcwBsAHUAZABnAGUAIABiAGkAbwBnAGEAcwAgAHQAcgBhAG4AcwBmAGUAcgByAGUAZAAgAG8AdQB0ACAAbwBmACAAdABoAGUAIAB0AHIAZQBhAHQAbQBlAG4AdAAgAGYAYQBjAGkAbABpAHQAeQBcACIALAAgAFwAIgBtADMAIABDAEgANABcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUAQwBfAGYAbABhAHIAZQBkAFwAIgAsACAAXAAiAGUAbgBlAHIAZwB5ACAAYwBvAG4AdABlAG4AdAAgAGYAYQBjAHQAbwByACAAbwBmACAAbQBlAHQAaABhAG4AZQAgAGkAbgAgAHMAbAB1AGQAZwBlACAAYgBpAG8AZwBhAHMAIABmAGwAYQByAGUAZABcACIALAAgAFwAIgBHAEoALwBtADMAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAEYAXwBmAGwAYQByAGUAZABDAEgANABcACIALAAgAFwAIgBtAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHMAbAB1AGQAZwBlACAAYgBpAG8AZwBhAHMAIABmAGwAYQByAGUAZABcACIALAAgAFwAIgBrAGcAIABDAEgANAAvAEcASgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAHQAXAAiACwAIABcACIAdAByAGUAYQB0AG0AZQBuAHQAIABmAGEAYwBpAGwAaQB0AHkAIAB0AHkAcABlAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgBWAEUARQBSAEcAXwAxADEAXwAxAF8AMQBfADEAXwBfADEAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AVwBhAHMAdABlAHcAYQB0AGUAcgBUAHIAZQBhAHQAbQBlAG4AdABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ATgAgAFMATwBVAFIAQwBFADoAIABDAGgAYQBuAGcAZQBkACAAdQBuAGkAdABzACAAbwBmACAARQBGAF8AdwB3ACwAIABFAEYAXwBTAGwAdQBkAGcAZQAgAGEAbgBkACAARQBGAF8AZgBsAGEAcgBlAGQAIABmAHIAbwBtACAAQwBPADIAZQAgAHQAbwAgAEMASAA0ACAAdABvACAAbQBhAHQAYwBoACAAZABhAHQAYQAgAGkAbgAgAFQAYQBiAGwAZQAgAFwAIgApADsAIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAGEAcwB0AGUAdwBhAHQAZQByAF8AUwBvAHUAcgBjAGUARABhAHQAYQAiACwAIgB0AGUAeAB0ACIAOgAiAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AVABhAGIAbABlACAAQQAuADQALgAxAC4AMwA6ACAATQBlAHQAaABhAG4AZQAgAGMAbwByAHIAZQBjAHQAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAdAByAGUAYQB0AG0AZQBuAHQAIABmAGEAYwBpAGwAaQB0AHkAIAB0AHkAcABlACAAdAAgAHUAcwBlAGQAIAB0AG8AIAB0AHIAZQBhAHQAIAB3AGEAcwB0AGUAdwBhAHQAZQByACAAKABmAHIAYQBjAHQAaQBvAG4AKQAgACgAQwBGAHcAdwAsAHQAKQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBDAG8AcgByAGUAYwB0AGkAbwBuAEYAYQBjAHQAbwByAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBUAGkAdABsAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBNAGUAdABoAGEAbgBlACAAYwBvAHIAcgBlAGMAdABpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB0AHIAZQBhAHQAbQBlAG4AdAAgAGYAYQBjAGkAbABpAHQAeQAgAHQAeQBwAGUAIAB0ACAAdQBzAGUAZAAgAHQAbwAgAHQAcgBlAGEAdAAgAHcAYQBzAHQAZQB3AGEAdABlAHIAXAAiACkAKQA7AFwAbgBcAG4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBDAG8AcgByAGUAYwB0AGkAbwBuAEYAYQBjAHQAbwByAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBWAGEAcgBpAGEAYgBsAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBDAEYAdwB3ACwAdABcACIAKQApADsAXABuAFwAbgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEMAbwByAHIAZQBjAHQAaQBvAG4ARgBhAGMAdABvAHIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFUAbgBpAHQAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACkAKQA7AFwAbgBcAG4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBDAG8AcgByAGUAYwB0AGkAbwBuAEYAYQBjAHQAbwByAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBTAG8AdQByAGMAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgA0AC4AMQAuADMAXAAiACkAKQA7AFwAbgBcAG4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBDAG8AcgByAGUAYwB0AGkAbwBuAEYAYQBjAHQAbwByAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBEAGEAdABhAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADIALABcAG4AIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIABcACIARgBhAGMAaQBsAGkAdAB5ACAAdAB5AHAAZQAgAHQAXAAiACwAIABcACIAQwBGAHcAdwAsAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIATQBhAG4AYQBnAGUAZAAgAGEAZQByAG8AYgBpAGMAIAB0AHIAZQBhAHQAbQBlAG4AdABcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBVAG4AbQBhAG4AYQBnAGUAZAAgAGEAZQByAG8AYgBpAGMAIAB0AHIAZQBhAHQAbQBlAG4AdABcACIALAAgADAALgAzADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQQBuAGEAZQByAG8AYgBpAGMAIABkAGkAZwBlAHMAdABvAHIALwByAGUAYQBjAHQAbwByAFwAIgAsACAAMAAuADgAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBTAGgAYQBsAGwAbwB3ACAAYQBuAGEAZQByAG8AYgBpAGMAIABsAGEAZwBvAG8AbgAgACgAZCIgADIAIABtACkAXAAiACwAIAAwAC4AMgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEQAZQBlAHAAIABhAG4AYQBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuACAAKABcAHUAMAAwADMAZQAgADIAbQApAFwAIgAsACAAMAAuADgAXABuACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AKQApACkAOwBcAG4AXABuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUAQwBvAHIAcgBlAGMAdABpAG8AbgBGAGEAYwB0AG8AcgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBcACIAKQApADsAXABuAFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgBUAGEAYgBsAGUAIABBAC4ANAAuADEALgA0ADoAIABNAGUAdABoAGEAbgBlACAAYwBvAHIAcgBlAGMAdABpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB0AHIAZQBhAHQAbQBlAG4AdAAgAGYAYQBjAGkAbABpAHQAeQAgAHQAeQBwAGUAIAB0ACAAdQBzAGUAZAAgAHQAbwAgAHQAcgBlAGEAdAAgAHMAbAB1AGQAZwBlACAAKABmAHIAYQBjAHQAaQBvAG4AKQAgACgAQwBGAHMAbAB1AGQAZwBlACwAdAApAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEMAbwByAHIAZQBjAHQAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAXwBUAGkAdABsAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBNAGUAdABoAGEAbgBlACAAYwBvAHIAcgBlAGMAdABpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB0AHIAZQBhAHQAbQBlAG4AdAAgAGYAYQBjAGkAbABpAHQAeQAgAHQAeQBwAGUAIAB0ACAAdQBzAGUAZAAgAHQAbwAgAHQAcgBlAGEAdAAgAHMAbAB1AGQAZwBlAFwAIgApACkAOwBcAG4AXABuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUAQwBvAHIAcgBlAGMAdABpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBfAFYAYQByAGkAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEMARgBzAGwAdQBkAGcAZQAsAHQAXAAiACkAKQA7AFwAbgBcAG4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBDAG8AcgByAGUAYwB0AGkAbwBuAEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAF8AVQBuAGkAdABcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIAKQApADsAXABuAFwAbgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEMAbwByAHIAZQBjAHQAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAXwBTAG8AdQByAGMAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgA0AC4AMQAuADQAXAAiACkAKQA7AFwAbgBcAG4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBDAG8AcgByAGUAYwB0AGkAbwBuAEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAF8ARABhAHQAYQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAAyACwAXABuACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEYAYQBjAGkAbABpAHQAeQAgAHQAeQBwAGUAIAB0AFwAIgAsACAAXAAiAEMARgBzAGwAdQBkAGcAZQAsAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIATQBhAG4AYQBnAGUAZAAgAGEAZQByAG8AYgBpAGMAIAB0AHIAZQBhAHQAbQBlAG4AdABcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBVAG4AbQBhAG4AYQBnAGUAZAAgAGEAZQByAG8AYgBpAGMAIAB0AHIAZQBhAHQAbQBlAG4AdABcACIALAAgADAALgAzADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQQBuAGEAZQByAG8AYgBpAGMAIABkAGkAZwBlAHMAdABvAHIALwByAGUAYQBjAHQAbwByAFwAIgAsACAAMAAuADgAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBTAGgAYQBsAGwAbwB3ACAAYQBuAGEAZQByAG8AYgBpAGMAIABsAGEAZwBvAG8AbgAgACgAZCIgADIAIABtACkAXAAiACwAIAAwAC4AMgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEQAZQBlAHAAIABhAG4AYQBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuACAAKABcAHUAMAAwADMAZQAgADIAbQApAFwAIgAsACAAMAAuADgAXABuACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AKQApACkAOwBcAG4AXABuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUAQwBvAHIAcgBlAGMAdABpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AVABpAHQAbABlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIATQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB3AGEAcwB0AGUAdwBhAHQAZQByAFwAIgApACkAOwBcAG4AXABuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBWAGEAcgBpAGEAYgBsAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBFAEYAdwB3AFwAIgApACkAOwBcAG4AXABuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBVAG4AaQB0AFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAawBnACAAQwBIADQAIAAvACAAawBnACAAQwBPAEQAXAAiACkAKQA7AFwAbgBcAG4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAMQAxAC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAcwBcACIAKQApADsAXABuAFwAbgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBXAGEAcwB0AGUAdwBhAHQAZQByAF8ARABhAHQAYQBcAG4APQBMAEEATQBCAEQAQQAoACAAMAAuADIANQApADsAXABuAFwAbgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAF8AVABpAHQAbABlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIATQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABzAGwAdQBkAGcAZQBcACIAKQApADsAXABuAFwAbgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBfAFYAYQByAGkAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEUARgBzAGwAdQBkAGcAZQBcACIAKQApADsAXABuAFwAbgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBfAFUAbgBpAHQAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBrAGcAIABDAEgANAAgAC8AIABrAGcAIABDAE8ARABcACIAKQApADsAXABuAFwAbgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBfAFMAbwB1AHIAYwBlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAMQAxAC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAcwBcACIAKQApADsAXABuAFwAbgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBfAEQAYQB0AGEAXABuAD0ATABBAE0AQgBEAEEAKAAwAC4AMgA1ACkAOwBcAG4AXABuAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4AVwBhAHMAdABlAF8ARQBuAGUAcgBnAHkAQwBvAG4AdABlAG4AdABGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBCAGkAbwBnAGEAcwBGAGwAYQByAGUAZABfAFQAaQB0AGwAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEUAbgBlAHIAZwB5ACAAYwBvAG4AdABlAG4AdAAgAGYAYQBjAHQAbwByACAAbwBmACAAcwBsAHUAZABnAGUAIABiAGkAbwBnAGEAcwAgAGYAbABhAHIAZQBkAFwAIgApACkAOwBcAG4AXABuAFcAYQBzAHQAZQBfAEUAbgBlAHIAZwB5AEMAbwBuAHQAZQBuAHQARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAQgBpAG8AZwBhAHMARgBsAGEAcgBlAGQAXwBWAGEAcgBpAGEAYgBsAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBFAEMAZgBsAGEAcgBlAGQAXAAiACkAKQA7AFwAbgBcAG4AVwBhAHMAdABlAF8ARQBuAGUAcgBnAHkAQwBvAG4AdABlAG4AdABGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBCAGkAbwBnAGEAcwBGAGwAYQByAGUAZABfAFUAbgBpAHQAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBHAEoAIAAvACAAbQAzAFwAIgApACkAOwBcAG4AXABuAFcAYQBzAHQAZQBfAEUAbgBlAHIAZwB5AEMAbwBuAHQAZQBuAHQARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAQgBpAG8AZwBhAHMARgBsAGEAcgBlAGQAXwBTAG8AdQByAGMAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADEAMQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0AHMAXAAiACkAKQA7AFwAbgBcAG4AVwBhAHMAdABlAF8ARQBuAGUAcgBnAHkAQwBvAG4AdABlAG4AdABGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBCAGkAbwBnAGEAcwBGAGwAYQByAGUAZABfAEQAYQB0AGEAXABuAD0ATABBAE0AQgBEAEEAKAAwAC4AMAAzADcANwApADsAXABuAFwAbgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAEIAaQBvAGcAYQBzAEYAbABhAHIAZQBkAF8AVABpAHQAbABlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIATQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABzAGwAdQBkAGcAZQAgAGIAaQBvAGcAYQBzACAAZgBsAGEAcgBlAGQAXAAiACkAKQA7AFwAbgBcAG4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAQgBpAG8AZwBhAHMARgBsAGEAcgBlAGQAXwBWAGEAcgBpAGEAYgBsAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBFAEYAZgBsAGEAcgBlAGQALABDAEgANABcACIAKQApADsAXABuAFwAbgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBCAGkAbwBnAGEAcwBGAGwAYQByAGUAZABfAFUAbgBpAHQAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBrAGcAIABDAEgANAAgAC8AIABHAEoAXAAiACkAKQA7AFwAbgBcAG4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAQgBpAG8AZwBhAHMARgBsAGEAcgBlAGQAXwBTAG8AdQByAGMAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADEAMQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0AHMAXAAiACkAKQA7AFwAbgBcAG4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAQgBpAG8AZwBhAHMARgBsAGEAcgBlAGQAXwBEAGEAdABhAFwAbgA9AEwAQQBNAEIARABBACgAMAAuADIAMgA4ADkAKQA7AFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgBXAGEAcwB0AGUAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAQgBpAG8AZwBhAHMARgBsAGEAcgBlAGQAXwBUAGkAdABsAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHMAbAB1AGQAZwBlACAAYgBpAG8AZwBhAHMAIABmAGwAYQByAGUAZABcACIAKQApADsAXABuAFwAbgBXAGEAcwB0AGUAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAQgBpAG8AZwBhAHMARgBsAGEAcgBlAGQAXwBWAGEAcgBpAGEAYgBsAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBFAEYAZgBsAGEAcgBlAGQALABOADIATwBcACIAKQApADsAXABuAFwAbgBXAGEAcwB0AGUAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAQgBpAG8AZwBhAHMARgBsAGEAcgBlAGQAXwBVAG4AaQB0AFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAawBnACAATgAyAE8AIAAvACAARwBKAFwAIgApACkAOwBcAG4AXABuAFcAYQBzAHQAZQBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBCAGkAbwBnAGEAcwBGAGwAYQByAGUAZABfAFMAbwB1AHIAYwBlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAMQAxAC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAcwBcACIAKQApADsAXABuAFwAbgBXAGEAcwB0AGUAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAQgBpAG8AZwBhAHMARgBsAGEAcgBlAGQAXwBEAGEAdABhAFwAbgA9AEwAQQBNAEIARABBACgAMQAuADEAMwAyAGUALQA0ACkAOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAGEAcwB0AGUAdwBhAHQAZQByAF8ATgAyAE8AXwBFAHEAdQBhAHQAaQBvAG4AcwAiACwAIgB0AGUAeAB0ACIAOgAiAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AMQAxAC4AMQA6ACAAVwBhAHMAdABlAHcAYQB0AGUAcgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AMQAxAC4AMQAuADMALgAxACAATQBlAHQAaABvAGQAIAAxACAALQAgAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABvAG4AcwBpAHQAZQAgAFcAYQBzAHQAZQB3AGEAdABlAHIAIABNAGEAbgBhAGcAZQBtAGUAbgB0AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8AMQAxAF8AMQBfADMAXwAxAF8AXwAxAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBGAGwAYQByAGUAZABCAGkAbwBnAGEAcwBcAG4ATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAGYAbABhAHIAZQBkACAAYgBpAG8AZwBhAHMAXABuAEUAXwBOADIATwBcAG4AdAAgAE4AMgBPAFwAbgBFAF8AewBOADIATwB9AD0AXABcAGYAcgBhAGMAewBRAF8AewBmAGwAYQByAGUAZAB9AH0AewAxADAAMAAwAH0AXABcAHQAaQBtAGUAcwAgAEUARgBfAHsAZgBsAGEAcgBlAGQALABOADIATwB9AFwAbgBRAF8AZgBsAGEAcgBlAGQAIAA9ACAAdgBvAGwAdQBtAGUAIABvAGYAIABiAGkAbwBnAGEAcwAgAGYAbABhAHIAZQBkACAAKABtADMAIABvAHIAIABHAEoAKQBcAG4ARQBGAF8AZgBsAGEAcgBlAGQAXwBOADIATwAgAD0AIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAGYAbABhAHIAZQBkACAAYgBpAG8AZwBhAHMAIAAoAGsAZwAgAE4AMgBPAC8ARwBKACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8AMQAxAF8AMQBfADMAXwAxAF8AXwAxAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBGAGwAYQByAGUAZABCAGkAbwBnAGEAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABRAF8AZgBsAGEAcgBlAGQALAAgAEUAQwBfAGYAbABhAHIAZQBkACwAIABFAEYAXwBmAGwAYQByAGUAZABOADIATwAsAFwAbgAgACAAIAAgACgAUQBfAGYAbABhAHIAZQBkACAALwAgADEAMAAwADAAKQAgACoAIAAoAEUAQwBfAGYAbABhAHIAZQBkACAAKgAgAEUARgBfAGYAbABhAHIAZQBkAE4AMgBPACkAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADEAXwAxAF8AMwBfADEAXwBfADEAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEYAbABhAHIAZQBkAEIAaQBvAGcAYQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAZgBsAGEAcgBlAGQAIABiAGkAbwBnAGEAcwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQAxAF8AMQBfADMAXwAxAF8AXwAxAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBGAGwAYQByAGUAZABCAGkAbwBnAGEAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBfAE4AMgBPAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADEAXwAxAF8AMwBfADEAXwBfADEAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEYAbABhAHIAZQBkAEIAaQBvAGcAYQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAE4AMgBPAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADEAXwAxAF8AMwBfADEAXwBfADEAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEYAbABhAHIAZQBkAEIAaQBvAGcAYQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADEAMQAuADEALgAzAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAxACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEAMQBfADEAXwAzAF8AMQBfAF8AMQBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ARgBsAGEAcgBlAGQAQgBpAG8AZwBhAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEAMQBfADEAXwAzAF8AMQBfAF8AMQBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ARgBsAGEAcgBlAGQAQgBpAG8AZwBhAHMAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAF8AewBOADIATwB9AD0AXABcAGYAcgBhAGMAewBRAF8AewBmAGwAYQByAGUAZAB9AH0AewAxADAAMAAwAH0AXABcAHQAaQBtAGUAcwAgAFwAXABsAGUAZgB0AFsARQBDAF8AewBmAGwAYQByAGUAZAB9ACAAXABcAHQAaQBtAGUAcwAgAEUARgBfAHsAZgBsAGEAcgBlAGQALABOADIATwB9AFwAXAByAGkAZwBoAHQAXQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQAxAF8AMQBfADMAXwAxAF8AXwAxAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBGAGwAYQByAGUAZABCAGkAbwBnAGEAcwBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAANAAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBRAF8AZgBsAGEAcgBlAGQAXAAiACwAIABcACIAdgBvAGwAdQBtAGUAIABvAGYAIABiAGkAbwBnAGEAcwAgAGYAbABhAHIAZQBkAFwAIgAsACAAXAAiAG0AMwBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUAQwBfAGYAbABhAHIAZQBkAFwAIgAsACAAXAAiAGUAbgBlAHIAZwB5ACAAYwBvAG4AdABlAG4AdAAgAGYAYQBjAHQAbwByACAAbwBmACAAcwBsAHUAZABnAGUAIABiAGkAbwBnAGEAcwAgAGYAbABhAHIAZQBkAFwAIgAsACAAXAAiAEcASgAvAG0AMwBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARgBfAGYAbABhAHIAZQBkAE4AMgBPAFwAIgAsACAAXAAiAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAZgBsAGEAcgBlAGQAIABiAGkAbwBnAGEAcwBcACIALAAgAFwAIgBrAGcAIABOADIATwAvAEcASgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuACIAfQBdACwAIgBwAHIAbwBqAGUAYwB0AE4AYQBtAGUAcwAiADoAWwAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBBAHAAcABlAG4AZABpAGMAZQBzACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAFIAbwB3AFMAdABhAHIAdABOAHUAbQBiAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAEMAbwBsAHUAbQBuAFMAdABhAHIAdABOAHUAbQBiAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgByAGEAeQBJAG4AVABhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAFQAdwBvAEMAbwBsAHUAbQBuAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATwBuAGUAQwBvAGwAdQBtAG4AQQBuAGQASABlAGEAZABlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AUwBwAGwAaQB0AFMAdAByAGkAbgBnAEkAbgB0AG8AQQByAHIAYQB5ACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEMAbABpAG0AYQB0AGUAWgBvAG4AZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABJAHQAZQBtAEYAcgBvAG0ATQBpAG4ATQBhAHgAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AUwB1AG0AUQB1AGEAbgB0AGkAdAB5AEYAcgBvAG0AQwByAGkAdABlAHIAaQBhACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBzACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAFAAZQByAGkAbwBkAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBGAHUAbgBjAHQAaQBvAG4ATgBhAG0AZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABOADIATwBFAEYARgByAG8AbQBQAHIAbwBkAEkAcgByAGkAZwBhAHQAaQBvAG4AUgBhAGkAbgBmAGEAbABsACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ARwBlAHQARgByAGEAYwBXAEUAVAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBDAG8AbgB2AGUAcgB0AFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAFQAbwBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQAxAF8AMQBfADEAXwAxAF8AXwAxAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFcAYQBzAHQAZQB3AGEAdABlAHIAVAByAGUAYQB0AG0AZQBuAHQAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEAMQBfADEAXwAxAF8AMQBfAF8AMQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBXAGEAcwB0AGUAdwBhAHQAZQByAFQAcgBlAGEAdABtAGUAbgB0AF8AVABpAHQAbABlACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADEAXwAxAF8AMQBfADEAXwBfADEAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AVwBhAHMAdABlAHcAYQB0AGUAcgBUAHIAZQBhAHQAbQBlAG4AdABfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQAxAF8AMQBfADEAXwAxAF8AXwAxAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFcAYQBzAHQAZQB3AGEAdABlAHIAVAByAGUAYQB0AG0AZQBuAHQAXwBVAG4AaQB0ACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADEAXwAxAF8AMQBfADEAXwBfADEAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AVwBhAHMAdABlAHcAYQB0AGUAcgBUAHIAZQBhAHQAbQBlAG4AdABfAFMAbwB1AHIAYwBlACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADEAXwAxAF8AMQBfADEAXwBfADEAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AVwBhAHMAdABlAHcAYQB0AGUAcgBUAHIAZQBhAHQAbQBlAG4AdABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADEAXwAxAF8AMQBfADEAXwBfADEAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AVwBhAHMAdABlAHcAYQB0AGUAcgBUAHIAZQBhAHQAbQBlAG4AdABfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEAMQBfADEAXwAxAF8AMQBfAF8AMQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBXAGEAcwB0AGUAdwBhAHQAZQByAFQAcgBlAGEAdABtAGUAbgB0AF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEAMQBfADEAXwAxAF8AMQBfAF8AMQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBXAGEAcwB0AGUAdwBhAHQAZQByAFQAcgBlAGEAdABtAGUAbgB0AF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEMAbwByAHIAZQBjAHQAaQBvAG4ARgBhAGMAdABvAHIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFQAaQB0AGwAZQAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUAQwBvAHIAcgBlAGMAdABpAG8AbgBGAGEAYwB0AG8AcgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBDAG8AcgByAGUAYwB0AGkAbwBuAEYAYQBjAHQAbwByAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBVAG4AaQB0ACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBDAG8AcgByAGUAYwB0AGkAbwBuAEYAYQBjAHQAbwByAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBTAG8AdQByAGMAZQAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUAQwBvAHIAcgBlAGMAdABpAG8AbgBGAGEAYwB0AG8AcgBXAGEAcwB0AGUAdwBhAHQAZQByAF8ARABhAHQAYQAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUAQwBvAHIAcgBlAGMAdABpAG8AbgBGAGEAYwB0AG8AcgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEMAbwByAHIAZQBjAHQAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAXwBUAGkAdABsAGUAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEMAbwByAHIAZQBjAHQAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEMAbwByAHIAZQBjAHQAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAXwBVAG4AaQB0ACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBDAG8AcgByAGUAYwB0AGkAbwBuAEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAF8AUwBvAHUAcgBjAGUAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEMAbwByAHIAZQBjAHQAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAXwBEAGEAdABhACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBDAG8AcgByAGUAYwB0AGkAbwBuAEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AVABpAHQAbABlACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBVAG4AaQB0ACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAEQAYQB0AGEAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBfAFQAaQB0AGwAZQAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAXwBVAG4AaQB0ACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAXwBTAG8AdQByAGMAZQAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAF8ARABhAHQAYQAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFcAYQBzAHQAZQBfAEUAbgBlAHIAZwB5AEMAbwBuAHQAZQBuAHQARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAQgBpAG8AZwBhAHMARgBsAGEAcgBlAGQAXwBUAGkAdABsAGUAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBXAGEAcwB0AGUAXwBFAG4AZQByAGcAeQBDAG8AbgB0AGUAbgB0AEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAEIAaQBvAGcAYQBzAEYAbABhAHIAZQBkAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AVwBhAHMAdABlAF8ARQBuAGUAcgBnAHkAQwBvAG4AdABlAG4AdABGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBCAGkAbwBnAGEAcwBGAGwAYQByAGUAZABfAFUAbgBpAHQAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBXAGEAcwB0AGUAXwBFAG4AZQByAGcAeQBDAG8AbgB0AGUAbgB0AEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAEIAaQBvAGcAYQBzAEYAbABhAHIAZQBkAF8AUwBvAHUAcgBjAGUAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBXAGEAcwB0AGUAXwBFAG4AZQByAGcAeQBDAG8AbgB0AGUAbgB0AEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAEIAaQBvAGcAYQBzAEYAbABhAHIAZQBkAF8ARABhAHQAYQAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAEIAaQBvAGcAYQBzAEYAbABhAHIAZQBkAF8AVABpAHQAbABlACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAQgBpAG8AZwBhAHMARgBsAGEAcgBlAGQAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBCAGkAbwBnAGEAcwBGAGwAYQByAGUAZABfAFUAbgBpAHQAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBCAGkAbwBnAGEAcwBGAGwAYQByAGUAZABfAFMAbwB1AHIAYwBlACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAQgBpAG8AZwBhAHMARgBsAGEAcgBlAGQAXwBEAGEAdABhACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AVwBhAHMAdABlAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAEIAaQBvAGcAYQBzAEYAbABhAHIAZQBkAF8AVABpAHQAbABlACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AVwBhAHMAdABlAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAEIAaQBvAGcAYQBzAEYAbABhAHIAZQBkAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AVwBhAHMAdABlAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAEIAaQBvAGcAYQBzAEYAbABhAHIAZQBkAF8AVQBuAGkAdAAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFcAYQBzAHQAZQBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBCAGkAbwBnAGEAcwBGAGwAYQByAGUAZABfAFMAbwB1AHIAYwBlACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AVwBhAHMAdABlAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAEIAaQBvAGcAYQBzAEYAbABhAHIAZQBkAF8ARABhAHQAYQAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8ATgAyAE8AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEAMQBfADEAXwAzAF8AMQBfAF8AMQBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ARgBsAGEAcgBlAGQAQgBpAG8AZwBhAHMAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAE4AMgBPAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADEAXwAxAF8AMwBfADEAXwBfADEAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEYAbABhAHIAZQBkAEIAaQBvAGcAYQBzAF8AVABpAHQAbABlACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBOADIATwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQAxAF8AMQBfADMAXwAxAF8AXwAxAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBGAGwAYQByAGUAZABCAGkAbwBnAGEAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8ATgAyAE8AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEAMQBfADEAXwAzAF8AMQBfAF8AMQBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ARgBsAGEAcgBlAGQAQgBpAG8AZwBhAHMAXwBVAG4AaQB0ACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBOADIATwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQAxAF8AMQBfADMAXwAxAF8AXwAxAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBGAGwAYQByAGUAZABCAGkAbwBnAGEAcwBfAFMAbwB1AHIAYwBlACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBOADIATwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQAxAF8AMQBfADMAXwAxAF8AXwAxAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBGAGwAYQByAGUAZABCAGkAbwBnAGEAcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBOADIATwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQAxAF8AMQBfADMAXwAxAF8AXwAxAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBGAGwAYQByAGUAZABCAGkAbwBnAGEAcwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAE4AMgBPAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADEAXwAxAF8AMwBfADEAXwBfADEAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEYAbABhAHIAZQBkAEIAaQBvAGcAYQBzAF8AQQByAGcAdQBtAGUAbgB0AHMAIgBdACwAIgBsAG8AYwBhAGwAZQAiADoAewAiAGwAaQBzAHQAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgByAG8AdwBTAGUAcABhAHIAYQB0AG8AcgAiADoAIgA7ACIALAAiAGMAbwBsAHUAbQBuAFMAZQBwAGEAcgBhAHQAbwByACIAOgAiACwAIgAsACIAdABoAG8AdQBzAGEAbgBkAHMAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgB0AGgAbwB1AHMAYQBuAGQAcwBQAG8AcwBpAHQAaQBvAG4AcwAiADoAWwAzAF0ALAAiAGQAZQBjAGkAbQBhAGwAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALgAiACwAIgBkAGEAdABlAE8AcgBkAGUAcgAiADoAIgBEAE0AWQAiACwAIgBjAHUAcgByAGUAbgBjAHkAUwB5AG0AYgBvAGwAIgA6ACIAJAAiACwAIgBpAHMAQwB1AHIAcgBlAG4AYwB5AFMAeQBtAGIAbwBsAEwAZQBhAGQAIgA6AHQAcgB1AGUALAAiAGkAcwBDAHUAcgByAGUAbgBjAHkAUwBlAHAAQgB5AFMAcABhAGMAZQAiADoAZgBhAGwAcwBlACwAIgByAG8AdwBMAGUAdAB0AGUAcgAiADoAIgBSACIALAAiAGMAbwBsAHUAbQBuAEwAZQB0AHQAZQByACIAOgAiAEMAIgAsACIAcgBjAEwAZQBmAHQAQgByAGEAYwBrAGUAdAAiADoAIgBbACIALAAiAHIAYwBSAGkAZwBoAHQAQgByAGEAYwBrAGUAdAAiADoAIgBdACIALAAiAHMAdABhAHQAZQBtAGUAbgB0AFMAZQBwAGEAcgBhAHQAbwByACIAOgAiADsAIgAsACIAbABvAGMAYQBsAGUATgBhAG0AZQAiADoAIgBlAG4ALQB1AHMAIgB9AH0A</AFEJSONBlob>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100ACB660BB23738846A00119B5826AC974" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3e3613359d4ae7f6bda6c57be713f101">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="7291119c-fce9-4911-96ae-b800be5dccd8" xmlns:ns3="09eef6d6-daa8-4301-8f9f-b1ec38079286" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="87491bfad7f11426ad96486e70428b3e" ns2:_="" ns3:_="">
     <xsd:import namespace="7291119c-fce9-4911-96ae-b800be5dccd8"/>
@@ -13977,15 +13996,11 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9A9CF321-0D35-4044-BC72-33748FE2B865}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
+<AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgAvAC8AIAAtAC0ALQAgAFcAbwByAGsAYgBvAG8AawAgAG0AbwBkAHUAbABlACAALQAtAC0AXABuAC8ALwAgAEEAIABmAGkAbABlACAAbwBmACAAbgBhAG0AZQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAG8AZgAgAHQAaABlACAAZgBvAHIAbQA6AFwAbgAvAC8AIAAgACAAIABuAGEAbQBlACAAPQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AOwBcAG4AXABuACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhACIALAAiAHQAZQB4AHQAIgA6ACIALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgBTAG8AdQByAGMAZQAgAGQAYQB0AGEAIAB0AGgAYQB0ACAAaQBzACAAYwBvAG0AbQBvAG4AIABhAGMAcgBvAHMAcwAgAGEAbABsACAAZQBuAHQAZQByAHAAcgBpAHMAZQAgAHQAeQBwAGUAcwBcAG4ARQB4AGMAZQBsACAAbQBvAGQAdQBsAGUAIABuAGEAbQBlADoAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFMAbwB1AHIAYwBlADoAIABOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQBcAG4ATgBJAFIAXwAyADAAMgAzAF8AVgBvAGwAMQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXABuAHAAIAA9ACAAZABlAG4AcwBpAHQAeQAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAIAAoADAALgA2ADcAOAA0ACAAawBnAC8AbQAzACkAXABuAFQAYQBrAGUAbgAgAGYAcgBvAG0AIAB0AGgAZQAgAE4AYQB0AGkAbwBuAGEAbAAgAEcAcgBlAGUAbgBoAG8AdQBzAGUAIABhAG4AZAAgAEUAbgBlAHIAZwB5ACAAUgBlAHAAbwByAHQAaQBuAGcAIABcAG4AKABNAGUAYQBzAHUAcgBlAG0AZQBuAHQAKQAgAEQAZQB0AGUAcgBtAGkAbgBhAHQAaQBvAG4AIAAyADAAMAA4AFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHAAIAA9ACAAZABlAG4AcwBpAHQAeQAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcALwBtADMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgADIAMAAyADMAIABWAG8AbAB1AG0AZQAgADEAOgAgAEUAcQB1AGEAdABpAG8AbgBzACAAMwAuAEIALgAxAGEAXwAyACwAIAAzAC4AQgAuADEAYwBfADIALAAgADMALgBCAC4AMwBfADEALAAgADMALgBCAC4ANABnAF8AMgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAMAAuADYANwA4ADQAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAFwAbgBDAGcAIAA9ACAANAA0AC8AMgA4ACAAZgBhAGMAdABvAHIAIAB0AG8AIABjAG8AbgB2AGUAcgB0ACAAZQBsAGUAbQBlAG4AdABhAGwAIABtAGEAcwBzACAAbwBmACAATgAyAE8AIAB0AG8AIABtAG8AbABlAGMAdQBsAGEAcgAgAG0AYQBzAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABOADIATwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBDAGcATgAyAE8AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAYQBjAHQAbwByAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgADIAMAAyADMAIABWAG8AbAB1AG0AZQAgADEAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgANAA0AC8AMgA4ACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAFwAbgBGAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABnAGEAcwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgBhAGMAdABvAHIAIAB0AG8AIABjAG8AbgB2AGUAcgB0ACAAZQBsAGUAbQBlAG4AdABhAGwAIABtAGEAcwBzACAAbwBmACAAZwBhAHMAIAB0AG8AIABtAG8AbABlAGMAdQBsAGEAcgAgAG0AYQBzAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBDAGcAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgBhAGMAdABvAHIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFgAWABYAFgAWABYAFgAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADgALAAgADQALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAYQBzAFwAIgAsACAAXAAiAEMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBcACIALAAgAFwAIgBDAG8AbgB2AGUAcgBzAGkAbwBuACAAZgBhAGMAdABvAHIAIAAxAFwAIgAsACAAXAAiAEMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgADIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyAFwAIgAsACAAXAAiADQANAAvADEAMgBcACIALAAgADQANAAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMASAA0AFwAIgAsACAAXAAiADEANgAvADEAMgBcACIALAAgADEANgAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AMgBPAFwAIgAsACAAXAAiADQANAAvADIAOABcACIALAAgADQANAAsACAAMgA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB4AFwAIgAsACAAXAAiADQANgAvADEANABcACIALAAgADQANgAsACAAMQA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwBcACIALAAgAFwAIgAyADgALwAxADIAXAAiACwAIAAyADgALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAE8AMgAgAEwAaQBtAGUAXAAiACwAIABcACIANAA0AC8AMQAyAFwAIgAsACAANAA0ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBNAFYATwBDAFwAIgAsACAAXAAiADEANAAvADEAMgBcACIALAAgADEANAAsACAAMQAyAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABOADIATwBcAG4ARwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAGcAcgBlAGUAbgBoAG8AdQBzAGUAIABnAGEAcwBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABnAHIAZQBlAG4AaABvAHUAcwBlACAAZwBhAHMAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARwBXAFAATgAyAE8AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgBhAGMAdABvAHIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFgAWABYAFgAWABYAFgAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADgALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAYQBzAFwAIgAsACAAXAAiAEMATwAyAC0AZQAgAGYAYQBjAHQAbwByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAE8AMgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBIADQAXAAiACwAIAAyADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgAyAE8AXAAiACwAIAAyADYANQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAEYANABcACIALAAgADYANgAzADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwAyAEYANgBcACIALAAgADEAMgAyADAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAEYANgBcACIALAAgADIAMgA4ADAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAEYAMwBcACIALAAgADEANwAyADAAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAcwB0AGEAdABlAHMAIABhAG4AZAAgAHQAZQByAHIAaQB0AG8AcgBpAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA5ACwAIAAzACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHQAYQB0AGUALwBUAGUAcgByAGkAdABvAHIAeQBcACIALAAgAFwAIgBDAG8AbQBtAG8AbgAgAE4AYQBtAGUAXAAiACwAIABcACIAQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AZQB3ACAAUwBvAHUAdABoACAAVwBhAGwAZQBzAFwAIgAsACAAXAAiAE4AZQB3ACAAUwBvAHUAdABoACAAVwBhAGwAZQBzAFwAIgAsACAAXAAiAE4AUwBXAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAQwBhAHAAaQB0AGEAbAAgAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAEEAQwBUAFwAIgAsACAAXAAiAEEAQwBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAGkAYwB0AG8AcgBpAGEAXAAiACwAIABcACIAVgBpAGMAdABvAHIAaQBhAFwAIgAsACAAXAAiAFYASQBDAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBRAHUAZQBlAG4AcwBsAGEAbgBkAFwAIgAsACAAXAAiAFEAdQBlAGUAbgBzAGwAYQBuAGQAXAAiACwAIABcACIAUQBMAEQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAbwB1AHQAaAAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFMAbwB1AHQAaAAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFMAQQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQBcACIALAAgAFwAIgBXAEEAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAYQBzAG0AYQBuAGkAYQBcACIALAAgAFwAIgBUAGEAcwBtAGEAbgBpAGEAXAAiACwAIABcACIAVABBAFMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwByAHQAaABlAHIAbgAgAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAE4AbwByAHQAaABlAHIAbgAgAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAE4AVABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQBCAFMAIABTAHQAYQB0AGkAcwB0AGMAYQBsACAAQQByAGUAYQBzACAATABlAHYAZQBsACAANAAgAC0AIABXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAEIAdQByAGUAYQB1ACAAbwBmACAAUwB0AGEAdABpAHMAdABpAGMAcwAgACgAQQBCAFMAKQAgAC0AIABTAHQAYQB0AGkAcwB0AGkAYwBhAGwAIABBAHIAZQBhAHMAIABMAGUAdgBlAGwAIAAyACAALQAgADIAMAAyADEAIAAtACAAUwBoAGEAcABlAGYAaQBsAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADEALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAQQAgADQAIABOAGEAbQBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBCAHUAbgBiAHUAcgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAGEAbgBkAHUAcgBhAGgAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABJAG4AbgBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABOAG8AcgB0AGgAIABFAGEAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAATgBvAHIAdABoACAAVwBlAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAFMAbwB1AHQAaAAgAEUAYQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABTAG8AdQB0AGgAIABXAGUAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAAVwBoAGUAYQB0ACAAQgBlAGwAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhACAALQAgAE8AdQB0AGIAYQBjAGsAIAAoAE4AbwByAHQAaAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAATwB1AHQAYgBhAGMAawAgACgAUwBvAHUAdABoACkAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAdwBlAHQAIABhAG4AZAAgAGQAcgB5ACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAyADoAIABUAHIAYQBuAHMAbABhAHQAaQBuAGcAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBzACAAdABvACAAdwBlAHQAIABhAG4AZAAgAGQAcgB5ACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAdwBhAHIAbQAgAC8AIABjAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAvACAAZAByAHkAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAIABhAG4AZAAgAGgAaQBnAGgAIAB0AGUAbQBwACAAYwBsAGEAcwBzAGUAcwAgAHQAbwAgAGEAYwBjAG8AbQBtAG8AZABhAHQAZQAgAGMAbABpAG0AYQB0AGUAIABzAGMAZQBuAGEAcgBpAG8AcwAgAGUAeABjAGwAdQBkAGUAZAAgAGIAeQAgAFYARQBFAFIARwAgAGMAcgBpAHQAZQByAGkAYQAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAGkAeABlAGQAIAB0AHkAcABvACAALQAgAEMAaABhAG4AZwBlAGQAIABcAHUAMAAwADIANwBGAHIAeQBcAHUAMAAwADIANwAgAHQAbwAgAFwAdQAwADAAMgA3AEQAcgB5AFwAdQAwADAAMgA3AC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADUALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAFcAZQB0ACAAbwByACAARAByAHkAIABaAG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABtAG8AbgB0AGEAbgBlAFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAHcAZQB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABkAHIAeQBcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdABcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAtACAAaABpAGcAaAAgAHQAZQBtAHAAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAaABpAGcAaAAgAHQAZQBtAHAAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA1ACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAB3AGEAcgBtACAALwAgAGMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC8AIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdAAgAGEAbgBkACAAaABpAGcAaAAgAHQAZQBtAHAAIABjAGwAYQBzAHMAZQBzACAAdABvACAAYQBjAGMAbwBtAG0AbwBkAGEAdABlACAAYwBsAGkAbQBhAHQAZQAgAHMAYwBlAG4AYQByAGkAbwBzACAAZQB4AGMAbAB1AGQAZQBkACAAYgB5ACAAVgBFAEUAUgBHACAAYwByAGkAdABlAHIAaQBhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAaQB4AGUAZAAgAHQAeQBwAG8AIABpAG4AIABNAEEAVAAgAHYAYQBsAHUAZQAgAGYAbwByACAAdwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAYwBoAGEAbgBnAGUAZAAgADEAMAAgAHQAbwAgADEAMQAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIABtAGkAbgAgAGEAbgBkACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAZgBvAHIAIABNAEEAVAAsACAATQBBAFAALAAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAIABwAGUAcgAgAHkAZQBhAHIALAAgAGUAbABlAHYAYQB0AGkAbwBuACwAIABNAEEAUAA6AFAARQBUACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlAHMAIABmAHIAbwBtACAAcgBlAGEAbAAgAGMAbABpAG0AYQB0AGUAIABkAGEAdABhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAQQBGACAAYQBjAGMAZQBwAHQAcwAgAHIAYQBpAG4AZgBhAGwAbAAgAGEAcwAgAGEAIABwAHIAbwB4AHkAIABmAG8AcgAgAHAAcgBlAGMAaQBwAGkAdABhAHQAaQBvAG4ALgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOQAsACAAMQA2ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAGwAaQBtAGEAdABlACAAWgBvAG4AZQBcACIALAAgAFwAIgBNAEEAVABcACIALAAgAFwAIgBNAEEAUABcACIALAAgAFwAIgBGAHIAbwBzAHQAIABkAGEAeQBzACAAcABlAHIAIAB5AGUAYQByAFwAIgAsACAAXAAiAEUAbABlAHYAYQB0AGkAbwBuAFwAIgAsACAAXAAiAE0AQQBQADoAUABFAFQAXAAiACwAIABcACIATQBpAG4AIAB0AGUAbQBwAFwAIgAsACAAXAAiAE0AYQB4ACAAdABlAG0AcABcACIALAAgAFwAIgBNAGkAbgAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBNAGEAeAAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBNAGkAbgAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAXAAiACwAIABcACIATQBhAHgAIABmAHIAbwBzAHQAIABkAGEAeQBzAFwAIgAsACAAXAAiAE0AaQBuACAAZQBsAGUAdgBhAHQAaQBvAG4AXAAiACwAIABcACIATQBhAHgAIABlAGwAZQB2AGEAdABpAG8AbgBcACIALAAgAFwAIgBNAGkAbgAgAE0AQQBQADoAUABFAFQAXAAiACwAIABcACIATQBpAG4AIABNAEEAUAA6AFAARQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABtAG8AbgB0AGEAbgBlAFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQA4ACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAwADAAIABtAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAMQA4AC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAANwAsACAAMQAwADAAMAAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAHcAZQB0AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQA4ACAAQwBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADIAMAAwADAAIABtAG0AXAAiACwAIABcACIAZCIgADcAXAAiACwAIABcACIAZCIgADEAMAAwADAAIABtAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAMQA4AC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAyADAAMAAwAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQAuADkAOQA5ACwAIAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAOAAgAEMAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADAAMAAwACAAbQBtACAALQAgAGQiIAAyADAAMAAwACAAbQBtAFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgADEAOAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAAMQAwADAAMAAuADAAMAAxACwAIAAyADAAMAAwACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQAuADkAOQA5ACwAIAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAGQAcgB5AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQA4ACAAQwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAwADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAXAAiACwAIAAxADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgADEALgAwADAAMQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAGQiIAAxAFwAIgAsACAAMQAwAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAgAC0AOQA5ADkAOQA5ADkALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMAAgAEMAIAAtACAAZCIgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxAFwAIgAsACAALQA5ADkAOQA5ADkAOQAsACAAMQAwACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAxAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMAAgAEMAIAAtACAAZCIgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAZCIgADEAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAMQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBBAHAAcABlAG4AZABpAGMAZQBzAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdABlADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AQQBUACAAPQAgAG0AZQBhAG4AIABhAG4AbgB1AGEAbAAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBBAFAAIAA9ACAAbQBlAGEAbgAgAGEAbgBuAHUAYQBsACAAcAByAGUAYwBpAHAAaQB0AGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABFAFQAIAA9ACAAcABvAHQAZQBuAHQAaQBhAGwAIABlAHYAYQBwAG8AdAByAGEAbgBzAHAAaQByAGEAdABpAG8AbgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABBAGQAZABlAGQAIABlAHgAdAByAGEAIABNAEEAVAAgAG0AaQBuACAAYQBuAGQAIABNAEEAVAAgAG0AYQB4ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGMAYQBsAGMAdQBsAGEAdABlACAAegBvAG4AZQAgAGYAcgBvAG0AIAByAGUAYQBsACAAdABlAG0AcABlAHIAYQB0AHUAcgBlACAAZABhAHQAYQAuAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANAAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AHUAcgBlACAAWgBvAG4AZQBcACIALAAgAFwAIgBNAGUAZABpAGEAbgAgAEEAbgBuAHUAYQBsACAAVABlAG0AcABlAHIAYQB0AHUAcgBlACAAKABNAEEAVAApAFwAIgAsACAAXAAiAE0AaQBuACAATQBBAFQAXAAiACwAIABcACIATQBhAHgAIABNAEEAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgAFwAIgBlIiAAMgA2ACAAQwBcACIALAAgADIANgAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIABcACIAMQA1ACAALQAgADIANQAgAEMAXAAiACwAIAAxADUALAAgADIANQAuADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIABcACIAZCIgADEANAAgAEMAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADQALgA5ADkAOQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAAQQBkAGQAZQBkACAAZQB4AHQAcgBhACAAUgBhAGkAbgBmAGEAbABsACAAbQBpAG4AIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAG0AYQB4ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGMAYQBsAGMAdQBsAGEAdABlACAAegBvAG4AZQAgAGYAcgBvAG0AIAByAGUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAZABhAHQAYQAuAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBhAGkAbgBmAGEAbABsACAAWgBvAG4AZQBcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABtAGkAbgBcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABtAGEAeABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbAAgAFwAdQAwADAAMwBlACAANgAwADAAbQBtAFwAIgAsACAANgAwADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATABvAHcAIAByAGEAaQBuAGYAYQBsAGwAXAAiACwAIABcACIAQQBuAG4AdQBhAGwAIAByAGEAaQBuAGYAYQBsAGwAIABkIiAANgAwADAAbQBtAFwAIgAsACAALQA5ADkAOQA5ADkAOQAsACAANgAwADAAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABaAG8AbgBlAFwAIgAsACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAGMAcgBpAHQAZQByAGkAYQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATABlAGEAYwBoAGkAbgBnACAAbwBjAGMAdQByAHMAXAAiACwAIABcACIAowMoADXYX9w12E7cNdhW3DXYW9wpAFwAdQAwADAAMwBlAKMDKAA12DjcNdhH3DAAKQArADXYYNw12FzcNdhW3DXYWdwgADXYZNw12E7cNdhh3DXYUtw12F/cIAAOITXYXNw12FncNdhR3DXYVtw12FvcNdhU3CAANdhQ3DXYTtw12F3cNdhO3DXYUNw12FbcNdhh3DXYZtxcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATABlAGEAYwBoAGkAbgBnACAAZABvAGUAcwAgAG4AbwB0ACAAbwBjAGMAdQByAFwAIgAsACAAXAAiAKMDKAA12F/cNdhO3DXYVtw12FvcKQBkIqMDKAA12DjcNdhH3DAAKQArADXYYNw12FzcNdhW3DXYWdwgADXYZNw12E7cNdhh3DXYUtw12F/cIAAOITXYXNw12FncNdhR3DXYVtw12FvcNdhU3CAANdhQ3DXYTtw12F3cNdhO3DXYUNw12FbcNdhh3DXYZtxcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXABuADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAbgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAEQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcwAgAGkAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAXAAiACwAXAAiAEYAcgBhAGMAVwBFAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFkAZQBzACAALQAgAGkAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwAgAC0AIABuAG8AdAAgAGkAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAXAAiACwAIAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoACgAXAAiAFwAIgApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAGQAYQB0AGEAIABzAGMAbwByAGUAcwAgAGYAbwByACAAcwBjAG8AcABlACAAMwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABYAFgAWABYAFgAWABYAFgAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABhAHQAYQAgAHMAbwB1AHIAYwBlAFwAIgAsACAAXAAiAEQAYQB0AGEAIABzAGMAbwByAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAbgB0AGUAcgBuAGEAdABpAG8AbgBhAGwAIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAcwBjAG8AcABlACAAMwAgAGQAYQB0AGEAYgBhAHMAZQBcACIALAAgADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB0AGEAdABlACAAbwByACAAcgBlAGcAaQBvAG4AYQBsACAAcwBjAG8AcABlACAAMwAgAGQAYQB0AGEAYgBhAHMAZQBcACIALAAgADMAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBtAGkAcwBzAGkAbwBuAHMAIABpAG4AdABlAG4AcwBpAHQAeQAgAGMAYQBsAGMAdQBsAGEAdABlAGQAIABmAHIAbwBtACAAYQBwAHAAcgBvAHYAZQBkACAAbQBlAHQAaABvAGQAXAAiACwAIAA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAZQByAGkAZgBpAGUAZAAgAGMAcgBlAGQAZQBuAHQAaQBhAGwAIABtAGEAdABjAGgAaQBuAGcAIABJAFMATwAxADQAMAA2ADcAXAAiACwAIAA1AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXABuADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAbgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgARABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAVgBvAGwAdQBtAGUAIAAxADoAIABMAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmACAAKAAzAC4ARAAuAGIALgAyACkAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAcgBhAGMATABFAEEAQwBIAFwAIgAsADAALgAyADQAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoACgAXAAiAFwAIgApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABuAGkAdAByAG8AZwBlAG4AIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABuAGkAdAByAG8AZwBlAG4AIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABrAGcAIABOADIATwAtAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgAFYAbwBsAHUAbQBlACAAMQA6ACAARQBxAHUAYQB0AGkAbwBuACAAMwAuAEQALgBCAF8AMQAwAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARgBsAGUAYQBjAGgAXAAiACwAMAAuADAAMQAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoACgAXAAiAFwAIgApACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXABuAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADEAXABuAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAZgBvAHIAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AIAAoAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AKQAgACgARQBGAE4AMgBPACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAGYAbwByACAAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAGsAZwAgAE4AMgBPAC0ATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADIALgAyAC4AMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQA1ACwAIAA1ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABqAFwAIgAsAFwAIgBFAEYATgAyAE8AXAAiACwAIABcACIAUAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAbwBuAGwAeQBcACIALAAgAFwAIgBJAHIAcgBpAGcAYQB0AGkAbwBuACAAbQBlAHQAaABvAGQAXAAiACwAIABcACIAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsADAALgAwADAANQA5ACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwAFwAIgAsADAALgAwADAANwAsACAAXAAiAEMAcgBvAHAAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsADAALgAwADAAMQA4ACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEwAbwB3ACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQBcACIALAAwAC4AMAAwADEAOAAsACAAXAAiAFAAYQBzAHQAdQByAGUAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcAAgACgAbABvAHcAIAByAGEAaQBuAGYAYQBsAGwAKQBcACIALAAwAC4AMAAwADIAOQAsACAAXAAiAEMAcgBvAHAAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAGMAcgBvAHAAIAAoAGgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAKQBcACIALAAwAC4AMAAwADgALAAgAFwAIgBDAHIAbwBwAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIASABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB1AGcAYQByAFwAIgAsADAALgAwADEAOQA5ACwAIABcACIAUwB1AGcAYQByAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AdAB0AG8AbgBcACIALAAwAC4AMAAwADUAMwAsACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAG8AcgB0AGkAYwB1AGwAdAB1AHIAYQBsACAAYwByAG8AcABzAFwAIgAsADAALgAwADAANgA0ACwAIABcACIASABvAHIAdABpAGMAdQBsAHQAdQByAGEAbAAgAGMAcgBvAHAAcwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBpAGMAZQAgACgAYwBvAG4AdABpAG4AdQBvAHUAcwAgAGYAbABvAG8AZABpAG4AZwApAFwAIgAsADAALgAwADAAMwAsACAAXAAiAFIAaQBjAGUAXAAiACwAIABcACIAQwBvAG4AdABpAG4AdQBvAHUAcwAgAGYAbABvAG8AZABpAG4AZwBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBpAGMAZQAgACgAcwBpAG4AZwBsAGUAIABhAG4AZAAgAG0AdQBsAHQAaQBwAGwAZQAgAGQAcgBhAGkAbgBhAGcAZQAsACAAbwByACAAYQBsAHQAZQByAG4AYQB0AGUAIAB3AGUAdAB0AGkAbgBnACAAYQBuAGQAIABkAHIAeQBpAG4AZwApAFwAIgAsADAALgAwADAANQAsACAAXAAiAFIAaQBjAGUAXAAiACwAIABcACIAUwBpAG4AZwBsAGUAIABhAG4AZAAgAG0AdQBsAHQAaQBwAGwAZQAgAGQAcgBhAGkAbgBhAGcAZQAsACAAbwByACAAYQBsAHQAZQByAG4AYQB0AGUAIAB3AGUAdAB0AGkAbgBnACAAYQBuAGQAIABkAHIAeQBpAG4AZwBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBxAHUAYQBjAHUAbAB0AHUAcgBlAFwAIgAsADAALgAwADAAMgA2ACwAIABcACIAQQBxAHUAYQBjAHUAbAB0AHUAcgBlAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAG8AcgBlAHMAdAByAHkAXAAiACwAMAAuADAAMAAxADgALAAgAFwAIgBGAG8AcgBlAHMAdAByAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA1ACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGUAbQBvAHYAZQBkACAAZAB1AHAAbABpAGMAYQB0AGUAIABcAHUAMAAwADIANwBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAB1ADAAMAAyADcAIAByAG8AdwAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGUAbQBvAHYAZQBkACAAYQBzAHQAZQByAGkAcwBrAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAFwAdQAwADAAMgA3AHAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAG8AbgBsAHkAXAB1ADAAMAAyADcALAAgAFwAdQAwADAAMgA3AHIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAXAB1ADAAMAAyADcAIABhAG4AZAAgAFwAdQAwADAAMgA3AGkAcgByAGkAZwBhAHQAaQBvAG4AIABtAGUAdABoAG8AZABcAHUAMAAwADIANwAgAGMAbwBsAHUAbQBuAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAdQBwAGwAaQBjAGEAdABlAGQAIABcAHUAMAAwADIANwBuAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQBcAHUAMAAwADIANwAgAHIAbwB3ACAAdwBpAHQAaAAgAHMAYQBtAGUAIABFAEYAIABmAG8AcgAgAGwAbwB3ACAAYQBuAGQAIABoAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAFwAbgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABDAGgAYQBwAHQAZQByACAAMQAsACAAcwBlAGMAdABpAG8AbgAgADEALgA4AC4AMgAgAEwAZQBhAGMAaABpAG4AZwAsACAAYwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBzAFwAbgBJAFAAQwBDADoAIABOADIATwAgAEUATQBJAFMAUwBJAE8ATgBTACAARgBSAE8ATQAgAE0AQQBOAEEARwBFAEQAIABTAE8ASQBMAFMALAAgAEEATgBEACAAQwBPADIAIABFAE0ASQBTAFMASQBPAE4AUwAgAEYAUgBPAE0AIABMAEkATQBFACAAQQBOAEQAIABVAFIARQBBACAAQQBQAFAATABJAEMAQQBUAEkATwBOAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwBXAEUAVAAgAGYAbwByACAAaQByAHIAaQBnAGEAdABpAG8AbgAgAHQAeQBwAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAEMAaABhAHAAdABlAHIAIAAxACwAIABzAGUAYwB0AGkAbwBuACAAMQAuADgALgAyACAATABlAGEAYwBoAGkAbgBnACwAIABjAGwAaQBtAGEAdABlACAAYQBuAGQAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBJAFAAQwBDACAAMgAwADEAOQAgAFIAZQBmAGkAbgBlAG0AZQBuAHQAIABWAG8AbAB1AG0AZQAgADQAOgAgAEMAaABhAHAAdABlAHIAIAAxADEAOgAgAE4AMgBPACAARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAATQBhAG4AYQBnAGUAZAAgAFMAbwBpAGwAcwAsACAAYQBuAGQAIABDAE8AMgAgAEUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAEwAaQBtAGUAIABhAG4AZAAgAFUAcgBlAGEAIABBAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGkAbwBuACAAdAB5AHAAZQAgAGkAcgBcACIALABcACIARgByAGEAYwBXAEUAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAByAGkAcAAgAGkAcgByAGkAZwBhAHQAaQBvAG4AXAAiACwAIAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAcAByAGkAbgBrAGwAZQByACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB1AHIAZgBhAGMAZQAgAGkAcgByAGkAZwBhAHQAaQBvAG4AXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AdABoAGUAcgAgAGkAcgByAGkAZwBhAHQAaQBvAG4AXAAiACwAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAARgBSAE8ATQAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAAVABhAGIAbABlACAAYwByAGUAYQB0AGUAZAAgAGIAYQBzAGUAZAAgAG8AbgAgAFYARQBFAFIARwAgAHQAZQB4AHQAIABcAHUAMAAwADIANwBBAHIAZQBhAHMAIABhAHIAZQAgAHMAdQBiAGoAZQBjAHQAIAB0AG8AIABsAGUAYQBjAGgAaQBuAGcAIAAoAGkALgBlAC4ALAAgAGkAbgAgAHQAaABlACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQApACAAdwBoAGUAbgAuAC4ALgAgAHQAaABlACAAbABhAG4AZAAgAGkAcwAgAGkAcgByAGkAZwBhAHQAZQBkACAAKABlAHgAYwBlAHAAdAAgAGQAcgBpAHAAIABpAHIAcgBpAGcAYQB0AGkAbwBuACkALgBcAHUAMAAwADIANwBcACIAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAFwAbgBUAGEAYgBsAGUAIABBAC4AMgAuADIALgAyADoAIABFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAdQByAGkAbgBlACAAYQBuAGQAIABkAHUAbgBnACAAZABlAHAAbwBzAGkAdABlAGQAIABvAG4AIABwAGEAcwB0AHUAcgBlACwAIAByAGEAbgBnAGUAIABvAHIAIABwAGEAZABkAG8AYwBrACAAKABrAGcAIABOADIATwAtAE4ALwBrAGcAIABOACkAIAAoAEUARgBQAFIAUAApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAdQByAGkAbgBlACAAYQBuAGQAIABkAHUAbgBnACAAZABlAHAAbwBzAGkAdABlAGQAIABvAG4AIABwAGEAcwB0AHUAcgBlACwAIAByAGEAbgBnAGUAIABvAHIAIABwAGEAZABkAG8AYwBrAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AMgBPACAALQAgAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADIALgAyAC4AMgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAEUARgBQAFIAUABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAAyAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABDAGgAYQBuAGcAZQBkACAAXAB1ADAAMAAyADcARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBzAFwAdQAwADAAMgA3ACAAdABvACAAcwBpAG4AZwB1AGwAYQByACAAXAB1ADAAMAAyADcARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcAHUAMAAwADIANwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAG8AbgB0AGgAcwAgAHQAbwAgAFMAZQBhAHMAbwBuAHMAIABNAGEAcABwAGkAbgBnAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBvAG4AdABoAFwAIgAsACAAXAAiAFMAZQBhAHMAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAGEAbgB1AGEAcgB5AFwAIgAsACAAXAAiAFMAdQBtAG0AZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAGUAYgByAHUAYQByAHkAXAAiACwAIABcACIAUwB1AG0AbQBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQByAGMAaABcACIALAAgAFwAIgBBAHUAdAB1AG0AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBwAHIAaQBsAFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAGEAeQBcACIALAAgAFwAIgBBAHUAdAB1AG0AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASgB1AG4AZQBcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASgB1AGwAeQBcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQB1AGcAdQBzAHQAXAAiACwAIABcACIAVwBpAG4AdABlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAZQBwAHQAZQBtAGIAZQByAFwAIgAsACAAXAAiAFMAcAByAGkAbgBnAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBPAGMAdABvAGIAZQByAFwAIgAsACAAXAAiAFMAcAByAGkAbgBnAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdgBlAG0AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAZQBjAGUAbQBiAGUAcgBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBhAG4AdQByAGUAIABNAGEAbgBhAGcAZQBtAGUAbgB0ACAAEyAgAE0AZQB0AGgAYQBuAGUAIABjAG8AbgB2AGUAcgBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABwAGUAcgAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAIAAoAGYAcgBhAGMAdABpAG8AbgApACAAKABNAEMARgBpAG0AKQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAxAC4AOAAuADEAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIAMgAsACAAMQA2ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAE0AQQBUACAAKAC6AEMAKQBcACIALAAgAFwAIgBVAG4AYwBvAHYAZQByAGUAZAAgAGEAbgBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuAFwAIgAsACAAXAAiAEMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBcACIALAAgAFwAIgBMAGkAcQB1AGkAZAAgAFMAbAB1AHIAcgB5ACAAKAB3AGkAdABoAG8AdQB0ACAAbgBhAHQAdQByAGEAbAAgAGMAcgB1AHMAdAApAFwAIgAsACAAXAAiAEQAYQBpAGwAeQAgAHMAcAByAGUAYQBkACAAKABiACkAXAAiACwAIABcACIAQwBvAG0AcABvAHMAdABpAG4AZwAgACgAcABhAHMAcwBpAHYAZQAgAHcAaQBuAGQAcgBvAHcAKQBcACIALAAgAFwAIgBTAG8AbABpAGQAIABTAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAFAAaQB0ACAAUwB0AG8AcgBhAGcAZQAgAFwAdQAwADAAMwBjADEAIABtAG8AbgB0AGgAXAAiACwAIABcACIARABlAGUAcAAgAEwAaQB0AHQAZQByAFwAIgAsACAAXAAiAFAAbwB1AGwAdAByAHkAIABNAGEAbgB1AHIAZQAgACgAdwBpAHQAaAAvAHcAaQB0AGgAbwB1AHQAIABsAGkAdAB0AGUAcgApAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAcAByAG8AYwBlAHMAcwBpAG4AZwAgAGkAbgB0AG8AIABwAGUAbABsAGUAdABpAHoAZQBkACAAZgBlAHIAdABpAGwAaQBzAGUAcgBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgAgAHQAbwAgAHMAbwBpAGwAXAAiACwAIABcACIAUABhAHMAdAB1AHIAZQAsACAAUgBhAG4AZwBlACAAYQBuAGQAIABQAGEAZABkAG8AYwBrACAAKABjACkAKABkACkAXAAiACwAIABcACIATQBBAFQAIAByAGEAdwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgAFwAIgBkIjEAMABcACIALAAgADAALgA2ADYALAAgADAALgAxACwAIAAwAC4AMQAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIAAxADEALAAgADAALgA2ADgALAAgADAALgAxACwAIAAwAC4AMQAxACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgADEAMgAsACAAMAAuADcALAAgADAALgAxACwAIAAwAC4AMQAzACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgADEAMwAsACAAMAAuADcAMQAsACAAMAAuADEALAAgADAALgAxADQALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQA0ACwAIAAwAC4ANwAzACwAIAAwAC4AMQAsACAAMAAuADEANQAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA1ACwAIAAwAC4ANwA0ACwAIAAwAC4AMQAsACAAMAAuADEANwAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEANQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEANgAsACAAMAAuADcANQAsACAAMAAuADEALAAgADAALgAxADgALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADcALAAgADAALgA3ADYALAAgADAALgAxACwAIAAwAC4AMgAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEANwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEAOAAsACAAMAAuADcANwAsACAAMAAuADEALAAgADAALgAyADIALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADkALAAgADAALgA3ADcALAAgADAALgAxACwAIAAwAC4AMgA0ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgAwACwAIAAwAC4ANwA4ACwAIAAwAC4AMQAsACAAMAAuADIANgAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIAMQAsACAAMAAuADcAOAAsACAAMAAuADEALAAgADAALgAyADkALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADIALAAgADAALgA3ADgALAAgADAALgAxACwAIAAwAC4AMwAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgAzACwAIAAwAC4ANwA5ACwAIAAwAC4AMQAsACAAMAAuADMANAAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIANAAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgAzADcALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADUALAAgADAALgA3ADkALAAgADAALgAxACwAIAAwAC4ANAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AXAAiACwAIAAyADYALAAgADAALgA3ADkALAAgADAALgAxACwAIAAwAC4ANAA0ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AXAAiACwAIAAyADcALAAgADAALgA4ACwAIAAwAC4AMQAsACAAMAAuADQAOAAsACAAMAAuADAAMQAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIANwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtAFwAIgAsACAAXAAiAGUiMgA4AFwAIgAsACAAMAAuADgALAAgADAALgAxACwAIAAwAC4ANQAsACAAMAAuADAAMQAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBBAG4AYQBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuAFwAIgAsACAAXAAiAEQAaQBnAGUAcwB0AGUAcgAgAC8AIABjAG8AdgBlAHIAZQBkACAAbABhAGcAbwBvAG4AcwBcACIALAAgAFwAIgBMAGkAcQB1AGkAZAAgAHMAeQBzAHQAZQBtAHMAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAXAAiACwAIABcACIAQwBvAG0AcABvAHMAdABpAG4AZwAgACgAcABhAHMAcwBpAHYAZQAgAHcAaQBuAGQAcgBvAHcAKQBcACIALAAgAFwAIgBTAG8AbABpAGQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAFAAaQB0ACAAcwB0AG8AcgBhAGcAZQBcACIALAAgAFwAIgBEAGUAZQBwACAAbABpAHQAdABlAHIAXAAiACwAIABcACIAUABvAHUAbAB0AHIAeQAgAG0AYQBuAHUAcgBlACAAdwBpAHQAaAAgAGIAZQBkAGQAaQBuAGcAXAAiACwAIABcACIAUABvAHUAbAB0AHIAeQAgAG0AYQBuAHUAcgBlACAAdwBpAHQAaABvAHUAdAAgAGIAZQBkAGQAaQBuAGcAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABwAHIAbwBjAGUAcwBzAGkAbgBnAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuAFwAIgAsACAAXAAiAFAAYQBzAHQAdQByAGUAIAByAGEAbgBnAGUAIABhAG4AZAAgAHAAYQBkAGQAbwBjAGsAXAAiACwAIABcACIATQBBAFQAIAByAGEAdwBcACIAIABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAOgAgAEEAZABkAGUAZAAgAHIAbwB3ACAAbwBmACAATgBJAFIAIABNAE0AQQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgAgAEQAdQBwAGwAaQBjAGEAdABlAGQAIABcAHUAMAAwADIANwBQAG8AdQBsAHQAcgB5ACAAdwBpAHQAaAAgAGEAbgBkACAAdwBpAHQAaABvAHUAdAAgAGwAaQB0AHQAZQByAFwAdQAwADAAMgA3ACAAYwBvAGwAdQBtAG4AIAB3AGkAdABoACAAcwBlAHAAYQByAGEAdABlACAATgBJAFIAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AIABBAGQAZABlAGQAIABcAHUAMAAwADIANwBNAEEAVAAgAHIAYQB3AFwAdQAwADAAMgA3ACAAYwBvAGwAdQBtAG4AIAB0AG8AIABhAGwAbABvAHcAIABsAG8AbwBrAHUAcAAgAG8AZgAgAG4AdQBtAGIAZQByAHMALgBcACIAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAbgBkACAAYwByAG8AcAAgAHIAZQBzAGkAZAB1AGUAcwAgAHIAZQB0AHUAcgBuAGUAZAAgAHQAbwAgAHQAaABlACAAcwBvAGkAbABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBGAE4AaQAgAFwAdQAwADAAMgA2ACAARQBGAE4AMgBPAGkAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABOADIATwAgAC0AIABOACAALwAgAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADIALgAxAC4ANABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgAFwAIgBFAEYATgBpACAAXAB1ADAAMAAyADYAIABFAEYATgAyAE8AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIAAwAC4AMAAwADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAANQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIAXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBcAG4AQwBvAG4AdgBlAHIAdAAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcAG4ARQBOADIATwAgAEMATwAyAGUAXABuAHQAIABDAE8AMgBlAFwAbgBFAE4AMgBPADoAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAAoAHQAIABOADIATwApAFwAbgBHAFcAUABOADIATwA6ACAAZwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIAAoAHQAIABDAE8AMgAtAGUAIAAvACAAdAAgAE4AMgBPACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABFAF8ATgAyAE8ALAAgAEcAVwBQAF8ATgAyAE8ALABcAG4AIAAgACAAIABFAF8ATgAyAE8AIAAqACAARwBXAFAAXwBOADIATwBcAG4AIAAgACkAXABuADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAbwBuAHYAZQByAHQAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAB0AG8AIABjAGEAcgBiAG8AbgAgAGQAaQBvAHgAaQBkAGUAIABlAHEAdQBpAHYAYQBsAGUAbgB0ACAAZQBtAGkAcwBzAGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBOADIATwAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAE8AMgBlAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMATwAyAF8AZQAgAD0AIABFAF8AewBOADIATwB9ACAAXABcAHQAaQBtAGUAcwAgAEcAVwBQAF8AewBOADIATwB9AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUATgAyAE8AXAAiACwAXAAiAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAE4AMgBPACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAVwBQAE4AMgBPAFwAIgAsAFwAIgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAATgAyAE8AKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBcAG4AQwBvAG4AdgBlAHIAdAAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcAG4ARQBDAEgANAAgAEMATwAyAGUAXABuAHQAIABDAE8AMgBlAFwAbgBFAEMASAA0ADoAIABtAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAAoAHQAIABDAEgANAApAFwAbgBHAFcAUABDAEgANAA6ACAAZwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAG0AZQB0AGgAYQBuAGUAIAAoAHQAIABDAE8AMgAtAGUAIAAvACAAdAAgAEMASAA0ACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABFAF8AQwBIADQALAAgAEcAVwBQAF8AQwBIADQALABcAG4AIAAgACAAIABFAF8AQwBIADQAIAAqACAARwBXAFAAXwBDAEgANABcAG4AIAAgACkAXABuADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAbwBuAHYAZQByAHQAIABtAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAB0AG8AIABjAGEAcgBiAG8AbgAgAGQAaQBvAHgAaQBkAGUAIABlAHEAdQBpAHYAYQBsAGUAbgB0ACAAZQBtAGkAcwBzAGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBDAEgANAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAE8AMgBlAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMATwAyAF8AZQAgAD0AIABFAF8AewBDAEgANAB9ACAAXABcAHQAaQBtAGUAcwAgAEcAVwBQAF8AewBDAEgANAB9AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUAQwBIADQAXAAiACwAXAAiAE0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAEMASAA0ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAVwBQAEMASAA0AFwAIgAsAFwAIgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbQBlAHQAaABhAG4AZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAAQwBIADQAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIAVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAUgBvAHcAUwB0AGEAcgB0AE4AdQBtAGIAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwALABSAG8AdwBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAYQBuAGQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAUgBPAFcAKABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAApACAAKwAgAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkAIAAtACAAMQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABUAGEAYgBsAGUASABlAGEAZABlAHIAQwBlAGwAbAAsAFwAbgAgACAAQwBPAEwAVQBNAE4AKABUAGEAYgBsAGUASABlAGEAZABlAHIAQwBlAGwAbAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBBAHIAcgBhAHkASQBuAFQAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgAEEAcgByAGEAeQBEAGEAdABhACwAIABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQAsACAAWwBDAG8AbAB1AG0AbgBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAQQBuAGQAQQByAHIAYQB5AF0ALABcAG4AIABJAEYARQBSAFIATwBSACgAXABuACAAIAAgACAAIABJAE4ARABFAFgAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAVQBOAEkAUQBVAEUAKABBAHIAcgBhAHkARABhAHQAYQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBPAFcAKAApAC0AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAUgBvAHcAUwB0AGEAcgB0AE4AdQBtAGIAZQByACgAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwALAAgAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEMATwBMAFUATQBOACgAKQAtAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAEMAbwBsAHUAbQBuAFMAdABhAHIAdABOAHUAbQBiAGUAcgAoAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACkAIAArAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAEMAbwBsAHUAbQBuAHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBBAG4AZABBAHIAcgBhAHkAKQAsACAAMQAsACAAQwBvAGwAdQBtAG4AcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAEEAbgBkAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACAAIAAgACAAKQAsACAAXAAiAFwAIgBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFwAIgBcACIAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEkARgAoAEkAUwBOAFUATQBCAEUAUgAoAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFwAIgBcACIAKQBcAG4AIAAgACAAIAApACwAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApACwAIAAwACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBUAHcAbwBDAG8AbAB1AG0AbgBzAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlADEALAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADIALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAWwBWAGEAbAB1AGUASQBGAEYAYQBsAHMAZQBdACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoADEALAAgACgATABvAG8AawB1AHAAQQByAHIAYQB5ADEAPQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQApACoAKABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABWAGEAbAB1AGUASQBGAEYAYQBsAHMAZQApACwAIABcACIAXAAiACwAIABWAGEAbAB1AGUASQBGAEYAYQBsAHMAZQApACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBPAG4AZQBDAG8AbAB1AG0AbgBBAG4AZABIAGUAYQBkAGUAcgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACwAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMgAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADEALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFsAVgBhAGwAdQBlAEkAZgBGAGEAbABzAGUAXQAsAFwAbgAgACAAIAAgAEkARgBFAFIAUgBPAFIAKABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADEALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACkAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAFYAYQBsAHUAZQBJAGYARgBhAGwAcwBlACkALAAgAFwAIgBcACIALAAgAFYAYQBsAHUAZQBJAGYARgBhAGwAcwBlACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAcABsAGkAdABTAHQAcgBpAG4AZwBJAG4AdABvAEEAcgByAGEAeQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEMAZQBsAGwALAAgAEQAZQBsAGkAbQBpAHQAZQByACwAIABbAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAxAF0ALAAgAFsAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADIAXQAsAFwAbgAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAWABNAEwAKABcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBcAHUAMAAwADMAYwB0AFwAdQAwADAAMwBlAFwAdQAwADAAMwBjAHMAXAB1ADAAMAAzAGUAXAAiACAAXAB1ADAAMAAyADYAXABuACAAIAAgACAAIAAgACAAIABTAFUAQgBTAFQASQBUAFUAVABFACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFMAVQBCAFMAVABJAFQAVQBUAEUAKABTAFUAQgBTAFQASQBUAFUAVABFACgAQwBlAGwAbAAsAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAxACwAXAAiAFwAIgApACwAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADIALABcACIAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAARABlAGwAaQBtAGkAdABlAHIALABcACIAXAB1ADAAMAAzAGMALwBzAFwAdQAwADAAMwBlAFwAdQAwADAAMwBjAHMAXAB1ADAAMAAzAGUAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAKQAgAFwAdQAwADAAMgA2AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFwAdQAwADAAMwBjAC8AcwBcAHUAMAAwADMAZQBcAHUAMAAwADMAYwAvAHQAXAB1ADAAMAAzAGUAXAAiACwAXABuACAAIAAgACAAIAAgACAAIABcACIALwAvAHMAXAAiAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABDAGwAaQBtAGEAdABlAFoAbwBuAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABhAHYAZwBUAGUAbQBwACwAYQB2AGcAUgBhAGkAbgAsAGYAcgBvAHMAdABEAGEAeQBzACwAZQBsAGUAdgAsAG0AYQBwAF8AcABlAHQALABcAG4AIAAgACAAIABtAGkAbgBUAGUAbQBwAEEAcgByAGEAeQAsAG0AYQB4AFQAZQBtAHAAQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4AUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQAsAG0AYQB4AFIAYQBpAG4AZgBhAGwAbABBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBGAHIAbwBzAHQAQQByAHIAYQB5ACwAbQBhAHgARgByAG8AcwB0AEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAEUAbABlAHYAYQB0AGkAbwBuAEEAcgByAGEAeQAsAG0AYQB4AEUAbABlAHYAYQB0AGkAbwBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAFAARQBUAEEAcgByAGEAeQAsAG0AYQB4AFAARQBUAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAGMAbABpAG0AYQB0AGUAWgBvAG4AZQBBAHIAcgBhAHkALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAbQBhAHMAawAsAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBUAGUAbQBwAEEAcgByAGEAeQApAFwAdQAwADAAMwBjAD0AYQB2AGcAVABlAG0AcAApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AFQAZQBtAHAAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBhAHYAZwBUAGUAbQBwACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4AUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQApAFwAdQAwADAAMwBjAD0AYQB2AGcAUgBhAGkAbgApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AFIAYQBpAG4AZgBhAGwAbABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGEAdgBnAFIAYQBpAG4AKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBGAHIAbwBzAHQAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBmAHIAbwBzAHQARABhAHkAcwApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AEYAcgBvAHMAdABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGYAcgBvAHMAdABEAGEAeQBzACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4ARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBlAGwAZQB2ACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBlAGwAZQB2ACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4AUABFAFQAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBtAGEAcABfAHAAZQB0ACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgAUABFAFQAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBtAGEAcABfAHAAZQB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAFQAQQBLAEUAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAKABjAGwAaQBtAGEAdABlAFoAbwBuAGUAQQByAHIAYQB5ACwAbQBhAHMAawAsACAAXAAiAE4AbwAgAG0AYQB0AGMAaABcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAASQB0AGUAbQBGAHIAbwBtAE0AaQBuAE0AYQB4AFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABNAGkAbgBBAHIAcgBhAHkALAAgAE0AYQB4AEEAcgByAGEAeQAsACAASQB0AGUAbQBBAHIAcgBhAHkALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAbQBhAHMAawAsAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABNAGkAbgBBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAE0AYQB4AEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0ATABvAG8AawB1AHAAVgBhAGwAdQBlACkALABcAG4AIAAgACAAIAAgACAAIAAgAEYASQBMAFQARQBSACgASQB0AGUAbQBBAHIAcgBhAHkALAAgAG0AYQBzAGsALAAgAFwAIgBOAG8AIABtAGEAdABjAGgAXAAiACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBTAHUAbQBRAHUAYQBuAHQAaQB0AHkARgByAG8AbQBDAHIAaQB0AGUAcgBpAGEAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAEMAcgBpAHQAZQByAGkAYQAxACwAIABDAHIAaQB0AGUAcgBpAGEAMQBUAHkAcABlAEEAcgByAGEAeQAsACAAUQB1AGEAbgB0AGkAdAB5ACwAIABbAE0AdQBsAHQAaQBwAGwAaQBlAHIAXQAsACAAWwBDAHIAaQB0AGUAcgBpAGEAMgBdACwAWwBDAHIAaQB0AGUAcgBpAGEAMgBBAHIAcgBhAHkAXQAsAFwAbgAgACAATABFAFQAKABcAG4AIAAgACAAIABtAHUAbAB0AGkAcABsAGkAZQByACwAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAE0AdQBsAHQAaQBwAGwAaQBlAHIAKQAsADEALABNAHUAbAB0AGkAcABsAGkAZQByACkALABcAG4AIAAgACAAIABxAHUAYQBuAHQAaQB0AHkALAAgAFEAdQBhAG4AdABpAHQAeQAqAE0AdQBsAHQAaQBwAGwAaQBlAHIALABcAG4AIAAgACAAIABjAHIAaQB0AGUAcgBpAGEAMQAsAC0ALQAoAEMAcgBpAHQAZQByAGkAYQAxAFQAeQBwAGUAQQByAHIAYQB5AD0AQwByAGkAdABlAHIAaQBhADEAKQAsAFwAbgAgACAAIAAgAGMAcgBpAHQAZQByAGkAYQAyACwASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABDAHIAaQB0AGUAcgBpAGEAMgApACwAMQAsAC0ALQAoAEMAcgBpAHQAZQByAGkAYQAyAEEAcgByAGEAeQA9AEMAcgBpAHQAZQByAGkAYQAyACkAKQAsAFwAbgAgACAAIAAgAFMAVQBNAFAAUgBPAEQAVQBDAFQAKABjAHIAaQB0AGUAcgBpAGEAMQAqAGMAcgBpAHQAZQByAGkAYQAyACoAcQB1AGEAbgB0AGkAdAB5ACkAXABuACAAIAApAFwAbgApADsAXABuAFwAbgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAHMAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBTAHQAYQByAHQALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBFAG4AZAAsAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAUwAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgACAAIAAgACAARQAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAXABuACAAIAAgACAAIAAgACAAIABtACwATQBPAE4AVABIACgAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAApACwAXABuACAAIAAgACAAIAAgACAAIABkACwARABBAFkAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAFAAZQByAGkAbwBkAEUAbgBkACwATABBAE0AQgBEAEEAKABzAHQALABFAEQAQQBUAEUAKABzAHQALAAxADIAKQAtADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAQQAsAFMALQAzADYANQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBhACwAWQBFAEEAUgAoAEEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBiACwAWQBFAEEAUgAoAEUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZgBpAHIAcwB0AFkAZQBhAHIALAB5AGEAKwAoAFAAZQByAGkAbwBkAEUAbgBkACgARABBAFQARQAoAHkAYQAsAG0ALABkACkAKQBcAHUAMAAwADMAYwAgAFMAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAbABhAHMAdABZAGUAYQByACwAeQBiAC0AKABEAEEAVABFACgAeQBiACwAbQAsAGQAKQBcAHUAMAAwADMAZQAgAEUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAATQBBAFgAKAAwACwAbABhAHMAdABZAGUAYQByAC0AZgBpAHIAcwB0AFkAZQBhAHIAKwAxACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAFAAZQByAGkAbwBkAHMAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBTAHQAYQByAHQALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBFAG4AZAAsAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAUwAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgACAAIAAgACAARQAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAXABuACAAIAAgACAAIAAgACAAIABtACwATQBPAE4AVABIACgAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAApACwAXABuACAAIAAgACAAIAAgACAAIABkACwARABBAFkAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALAAgAC8AKgBoAGUAbABwAGUAcgA6ACAAZQBuAGQAIABkAGEAdABlACAAZgBvAHIAIABhACAAcgBlAHAAbwByAHQAaQBuAGcAIABwAGUAcgBpAG8AZAAgAHMAdABhAHIAdABpAG4AZwAgAGEAdAAgAGEAIABnAGkAdgBlAG4AIABkAGEAdABlACoALwBcAG4AIAAgACAAIAAgACAAIAAgAFAAZQByAGkAbwBkAEUAbgBkACwATABBAE0AQgBEAEEAKABzAHQALABFAEQAQQBUAEUAKABzAHQALAAxADIAKQAtADEAKQAsACAALwAqAG8AbgBsAHkAIABuAGUAZQBkACAAdABvACAAbABvAG8AawAgAGIAYQBjAGsAIAAzADYANQAgAGQAYQB5AHMAKABtAGEAeAAgAG8AdgBlAHIAbABhAHAAIAB3AGkAbgBkAG8AdwApACoALwBcAG4AIAAgACAAIAAgACAAIAAgAEEALABTAC0AMwA2ADUALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYQAsAFkARQBBAFIAKABBACkALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYgAsAFkARQBBAFIAKABFACkALAAgAC8AKgBpAGYAIAB0AGgAZQAgAGEAbgBjAGgAbwByACAAZgBvAHIAIAB5AGEAIABlAG4AZABzACAAYgBlAGYAbwByAGUAIABTACwAaQB0ACAAYwBhAG4AXAB1ADAAMAAyADcAdAAgAG8AdgBlAHIAbABhAHAAOwAgAG0AbwB2AGUAIAB0AG8AIABuAGUAeAB0ACAAeQBlAGEAcgAqAC8AXABuACAAIAAgACAAIAAgACAAIABmAGkAcgBzAHQAWQBlAGEAcgAsAHkAYQArACgAUABlAHIAaQBvAGQARQBuAGQAKABEAEEAVABFACgAeQBhACwAbQAsAGQAKQApAFwAdQAwADAAMwBjAFMAKQAsACAALwAqAGkAZgAgAHQAaABlACAAYQBuAGMAaABvAHIAIABmAG8AcgAgAHkAYgAgAHMAdABhAHIAdABzACAAYQBmAHQAZQByACAARQAsAGkAdAAgAGMAYQBuAFwAdQAwADAAMgA3AHQAIABvAHYAZQByAGwAYQBwADsAIABtAG8AdgBlACAAdABvACAAcAByAGUAdgBpAG8AdQBzACAAeQBlAGEAcgAqAC8AXABuACAAIAAgACAAIAAgACAAIABsAGEAcwB0AFkAZQBhAHIALAB5AGIALQAoAEQAQQBUAEUAKAB5AGIALABtACwAZAApAFwAdQAwADAAMwBlAEUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAbgAsAE0AQQBYACgAMAAsAGwAYQBzAHQAWQBlAGEAcgAtAGYAaQByAHMAdABZAGUAYQByACsAMQApACwAXABuACAAIAAgACAAIAAgACAAIAB5AHIAcwAsAFMARQBRAFUARQBOAEMARQAoAG4ALAAxACwAZgBpAHIAcwB0AFkAZQBhAHIALAAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAHMAdABhAHIAdABzACwARABBAFQARQAoAHkAcgBzACwAbQAsAGQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZQBuAGQAcwAsAE0AQQBQACgAcwB0AGEAcgB0AHMALABQAGUAcgBpAG8AZABFAG4AZAApACwAXABuACAAIAAgACAAIAAgACAAIAB0AGEAZwAsAEkARgAoAHMAdABhAHIAdABzAD0AUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAIgAgACgAVABoAGkAcwAgAHIAZQBwAG8AcgB0AGkAbgBnACAAYwB5AGMAbABlACkAXAAiACwAXAAiAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABzAHQAYQByAHQAcwBUAGUAeAB0ACwAVABFAFgAVAAoAHMAdABhAHIAdABzACwAXAAiAGQAZAAgAG0AbQBtACAAeQB5AHkAeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZQBuAGQAcwBUAGUAeAB0ACwAVABFAFgAVAAoAGUAbgBkAHMALABcACIAZABkACAAbQBtAG0AIAB5AHkAeQB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABuAD0AMAAsAFwAIgBcACIALABIAFMAVABBAEMASwAoAHMAdABhAHIAdABzAFQAZQB4AHQAIABcAHUAMAAwADIANgAgAFwAIgAgAHQAbwAgAFwAIgAgAFwAdQAwADAAMgA2ACAAZQBuAGQAcwBUAGUAeAB0ACAAXAB1ADAAMAAyADYAIAB0AGEAZwApACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkARgB1AG4AYwB0AGkAbwBuAE4AYQBtAGUAXABuAD0ATABBAE0AQgBEAEEAKABGAHUAbgBjAHQAaQBvAG4ALAAgAFQARQBYAFQAQgBFAEYATwBSAEUAKABGAE8AUgBNAFUATABBAFQARQBYAFQAKABGAHUAbgBjAHQAaQBvAG4AKQAsACAAXAAiACgAXAAiACkAKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAE4AMgBPAEUARgBGAHIAbwBtAFAAcgBvAGQASQByAHIAaQBnAGEAdABpAG8AbgBSAGEAaQBuAGYAYQBsAGwAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAIABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACwAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AQQByAHIAYQB5ACwAIABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkAEEAcgByAGEAeQAsACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAQQByAHIAYQB5ACwAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQALAAgAEkARgAoAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAPQBcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEEAbgB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQAsACAASQBGACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAAgAD0AIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAIABcACIAQQBuAHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKAAxACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEEAcgByAGEAeQA9AFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AKQAqAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAoAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAQQByAHIAYQB5AD0ASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAApACoAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACgAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAQQByAHIAYQB5AD0AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEcAZQB0AEYAcgBhAGMAVwBFAFQAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ALABcAG4AIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQALAAgAFwAbgAgACAAIAAgACAAIAAgACAAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUALABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBMAG8AbwBrAHUAcAAsAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQALAAgAFwAbgAgACAAIAAgACAAIAAgACAAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ATABvAG8AawB1AHAALABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBGAHIAYQBjAFcARQBUACAAKwAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVABcAHUAMAAwADMAZQAwACwAIAAxACwAIAAwACkAXABuACAAIAAgACAAKQApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEMAbwBuAHYAZQByAHQAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAVABvAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUALABcAG4AIAAgACAAIABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBBAHIAcgBhAHkALAAgAFMAdABhAHQAZQBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUALAAgAFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAEEAcgByAGEAeQAsACAAUwB0AGEAdABlAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwBvAHUAcgBjAGUASAB5AHAAZQByAGwAaQBuAGsAXABuAD0ATABBAE0AQgBEAEEAKABUAGEAcgBnAGUAdABDAGUAbABsACwAXABuACAAIABMAEUAVAAoAFwAbgAgACAAIAAgAHMAaAAsACAAVABFAFgAVABBAEYAVABFAFIAKABDAEUATABMACgAXAAiAGYAaQBsAGUAbgBhAG0AZQBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsACAAXAAiAF0AXAAiACkALABcAG4AIAAgACAAIABhAGQAZAByACwAIABDAEUATABMACgAXAAiAGEAZABkAHIAZQBzAHMAXAAiACwAIABUAGEAcgBnAGUAdABDAGUAbABsACkALABcAG4AIAAgACAAIABcACIAIwBcAHUAMAAwADIANwBcACIAIABcAHUAMAAwADIANgAgAHMAaAAgAFwAdQAwADAAMgA2ACAAXAAiAFwAdQAwADAAMgA3ACEAXAAiACAAXAB1ADAAMAAyADYAIABhAGQAZAByAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAbwB1AHIAYwBlAEgAeQBwAGUAcgBsAGkAbgBrAEQAaQBmAGYAZQByAGUAbgB0AFMAaABlAGUAdABcAG4APQBMAEEATQBCAEQAQQAoAFQAYQByAGcAZQB0AEMAZQBsAGwALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAcwBoACwAIABUAEUAWABUAEEARgBUAEUAUgAoAEMARQBMAEwAKABcACIAZgBpAGwAZQBuAGEAbQBlAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAIABcACIAXQBcACIAKQAsAFwAbgAgACAAIAAgAGEAZABkAHIALAAgAEMARQBMAEwAKABcACIAYQBkAGQAcgBlAHMAcwBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsAFwAbgAgACAAIAAgAFwAIgAjAFwAIgAgAFwAdQAwADAAMgA2ACAAYQBkAGQAcgBcAG4AIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgBnAHUAbQBlAG4AdABzAF8AMQBfADIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALABcAG4AIAAgACAAIABDAEgATwBPAFMARQBDAE8ATABTACgAQQByAGcAdQBtAGUAbgB0AHMAQQByAHIAYQB5ACwAIAAxACwAIAAyACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgBnAHUAbQBlAG4AdABzAF8AMwBfADQAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALABcAG4AIAAgACAAIABDAEgATwBPAFMARQBDAE8ATABTACgAQQByAGcAdQBtAGUAbgB0AHMAQQByAHIAYQB5ACwAIAAzACwAIAA0ACkAXABuACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8ARwBlAHQATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUALAAgAE0ATQBTACwAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUAQQByAHIAYQB5ACwAIABNAE0AUwBBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKABcAG4AIAAgACAAIAAgACAAIAAgAE0ARQBEAEkAQQBOACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFIATwBVAE4ARAAoAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAsACAAMAApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATQBJAE4AKABUAGUAbQBwAGUAcgBhAHQAdQByAGUAQQByAHIAYQB5ACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABNAEEAWAAoAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkALABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKABNAE0AUwAsACAATQBNAFMAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFIAZQBzAHUAbAB0AHMASQB0AGUAbQBGAHIAbwBtAEUAcQB1AGEAdABpAG8AbgBUAGkAdABsAGUAQQBuAGQAUwBvAHUAcgBjAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGkAdABsAGUAQwBlAGwAbAAsACAAUwBvAHUAcgBjAGUAQwBlAGwAbAAsAFwAbgAgACAAIAAgAFMAVQBCAFMAVABJAFQAVQBUAEUAKABMAEUARgBUACgAUwBvAHUAcgBjAGUAQwBlAGwAbAAsACAARgBJAE4ARAAoAFwAIgAsAFwAIgAsACAAUwBvAHUAcgBjAGUAQwBlAGwAbAApACAALQAxACkALAAgAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABcACIALAAgAFwAIgBcACIAKQAgAFwAdQAwADAAMgA2ACAAXAAiACAAXAAiACAAXAB1ADAAMAAyADYAIABUAGkAdABsAGUAQwBlAGwAbABcAG4AKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AVwBhAHMAdABlAHcAYQB0AGUAcgBfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAiACwAIgB0AGUAeAB0ACIAOgAiAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AMQAxAC4AMQA6ACAAVwBhAHMAdABlAHcAYQB0AGUAcgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AMQAxAC4AMQAuADEALgAxACAATQBlAHQAaABvAGQAIAAxACAALQAgAE0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABvAG4AcwBpAHQAZQAgAFcAYQBzAHQAZQB3AGEAdABlAHIAIABNAGEAbgBhAGcAZQBtAGUAbgB0AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8AMQAxAF8AMQBfADEAXwAxAF8AXwAxAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFcAYQBzAHQAZQB3AGEAdABlAHIAVAByAGUAYQB0AG0AZQBuAHQAXABuAE0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIAB3AGEAcwB0AGUAdwBhAHQAZQByACAAdAByAGUAYQB0AG0AZQBuAHQAXABuAEUAXwBDAEgANABcAG4AdAAgAEMASAA0AFwAbgBFAF8AewBDAEgANAB9AD0AXABcAGYAcgBhAGMAewAxAH0AewAxADAAMAAwAH0AXABcAHQAaQBtAGUAcwBcAFwAbABlAGYAdABbAFwAXABsAGUAZgB0ACgAVwBfAHQAXABcAHQAaQBtAGUAcwBcAFwAbABlAGYAdAAoAEMATwBEAF8AewBpAG4AfQBcAFwAdABpAG0AZQBzACgAMQAtAEYAXwB7AHMAbAB1AGQAZwBlAH0AKQAtAEMATwBEAF8AewBvAHUAdAB9AFwAXAByAGkAZwBoAHQAKQBcAFwAdABpAG0AZQBzACAAQwBGAF8AewB3AHcALAB0AH0AXABcAHQAaQBtAGUAcwAgAEUARgBfAHsAdwB3AH0AXABcAHIAaQBnAGgAdAApACsAXABcAGwAZQBmAHQAKABXAF8AdABcAFwAdABpAG0AZQBzAFwAXABsAGUAZgB0ACgAQwBPAEQAXwB7AGkAbgB9AFwAXAB0AGkAbQBlAHMAKABGAF8AewBzAGwAdQBkAGcAZQB9AC0ARgBfAHsAcgBlAG0AbwB2AGUAZAB9ACkAXABcAHIAaQBnAGgAdAApAFwAXAB0AGkAbQBlAHMAIABDAEYAXwB7AHMAbAB1AGQAZwBlACwAdAB9AFwAXAB0AGkAbQBlAHMAIABFAEYAXwB7AHMAbAB1AGQAZwBlAH0AXABcAHIAaQBnAGgAdAApAC0AXABcAGwAZQBmAHQAKAA2AC4ANwA4ADQAXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQA0AH0AXABcAHQAaQBtAGUAcwAoAFEAXwB7AGMAYQBwAH0AKwBRAF8AewBmAGwAYQByAGUAZAB9ACsAUQBfAHsAbwB1AHQAfQApAFwAXAByAGkAZwBoAHQAKQArAFwAXABsAGUAZgB0ACgAUQBfAHsAZgBsAGEAcgBlAGQAfQBcAFwAdABpAG0AZQBzACAARQBDAF8AewBmAGwAYQByAGUAZAB9AFwAXAB0AGkAbQBlAHMAIABFAEYAXwB7AGYAbABhAHIAZQBkACwAQwBIADQAfQBcAFwAcgBpAGcAaAB0ACkAXABcAHIAaQBnAGgAdABdAFwAbgBXAF8AdAAgAD0AIABxAHUAYQBuAHQAaQB0AHkAIABvAGYAIAB3AGEAcwB0AGUAdwBhAHQAZQByACAAdAByAGUAYQB0AGUAZAAgAGEAdAAgAGYAYQBjAGkAbABpAHQAeQAgAHQAeQBwAGUAIAB0ACAAKABtADMAKQBcAG4AQwBPAEQAXwBpAG4AIAA9ACAAYQB2AGUAcgBhAGcAZQAgAGkAbgBsAGUAdAAgAEMAaABlAG0AaQBjAGEAbAAgAE8AeAB5AGcAZQBuACAARABlAG0AYQBuAGQAIABjAG8AbgBjAGUAbgB0AHIAYQB0AGkAbwBuACAAbwBmACAAdwBhAHMAdABlAHcAYQB0AGUAcgAgACgAawBnACAAQwBPAEQALwBtADMAKQBcAG4ARgBfAHMAbAB1AGQAZwBlACAAPQAgAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAEMATwBEACAAcgBlAG0AbwB2AGUAZAAgAGYAcgBvAG0AIAB3AGEAcwB0AGUAdwBhAHQAZQByACAAYQBzACAAcwBsAHUAZABnAGUAXABuAEMATwBEAF8AbwB1AHQAIAA9ACAAYQB2AGUAcgBhAGcAZQAgAG8AdQB0AGwAZQB0ACAAQwBPAEQAIABjAG8AbgBjAGUAbgB0AHIAYQB0AGkAbwBuACAAbwBmACAAdwBhAHMAdABlAHcAYQB0AGUAcgAgACgAawBnACAAQwBPAEQALwBtADMAKQBcAG4AQwBGAF8AdwB3AF8AdAAgAD0AIABtAGUAdABoAGEAbgBlACAAYwBvAHIAcgBlAGMAdABpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABmAGEAYwBpAGwAaQB0AHkAIAB0AHkAcABlACAAdAAgAHUAcwBlAGQAIAB0AG8AIAB0AHIAZQBhAHQAIAB3AGEAcwB0AGUAdwBhAHQAZQByAFwAbgBFAEYAXwB3AHcAIAA9ACAAbQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB3AGEAcwB0AGUAdwBhAHQAZQByACAAKABrAGcAIABDAE8AMgBlAC8AawBnACAAQwBPAEQAKQBcAG4ARgBfAHIAZQBtAG8AdgBlAGQAIAA9ACAAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAQwBPAEQAIAByAGUAbQBvAHYAZQBkACAAZgByAG8AbQAgAHQAaABlACAAdwBhAHMAdABlAHcAYQB0AGUAcgAgAHQAcgBlAGEAdABtAGUAbgB0ACAAZgBhAGMAaQBsAGkAdAB5ACAAYQBuAGQAIAB0AHIAYQBuAHMAZgBlAHIAcgBlAGQAIABlAGwAcwBlAHcAaABlAHIAZQBcAG4AQwBGAF8AcwBsAHUAZABnAGUAXwB0ACAAPQAgAG0AZQB0AGgAYQBuAGUAIABjAG8AcgByAGUAYwB0AGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAGYAYQBjAGkAbABpAHQAeQAgAHQAeQBwAGUAIAB0ACAAdQBzAGUAZAAgAHQAbwAgAHQAcgBlAGEAdAAgAHMAbAB1AGQAZwBlAFwAbgBFAEYAXwBzAGwAdQBkAGcAZQAgAD0AIABtAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHMAbAB1AGQAZwBlACAAKABrAGcAIABDAE8AMgBlAC8AawBnACAAQwBPAEQAKQBcAG4AUQBfAGMAYQBwACAAPQAgAHEAdQBhAG4AdABpAHQAeQAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAIABpAG4AIABzAGwAdQBkAGcAZQAgAGIAaQBvAGcAYQBzACAAYwBhAHAAdAB1AHIAZQBkACAAZgBvAHIAIABjAG8AbQBiAHUAcwB0AGkAbwBuACAAKABtADMAIABDAEgANAApAFwAbgBRAF8AZgBsAGEAcgBlAGQAIAA9ACAAcQB1AGEAbgB0AGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQAgAGkAbgAgAHMAbAB1AGQAZwBlACAAYgBpAG8AZwBhAHMAIABmAGwAYQByAGUAZAAgACgAbQAzACAAQwBIADQAKQBcAG4AUQBfAG8AdQB0ACAAPQAgAHEAdQBhAG4AdABpAHQAeQAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAIABpAG4AIABzAGwAdQBkAGcAZQAgAGIAaQBvAGcAYQBzACAAdAByAGEAbgBzAGYAZQByAHIAZQBkACAAbwB1AHQAIABvAGYAIAB0AGgAZQAgAHQAcgBlAGEAdABtAGUAbgB0ACAAZgBhAGMAaQBsAGkAdAB5ACAAKABtADMAIABDAEgANAApAFwAbgBFAEMAXwBmAGwAYQByAGUAZAAgAD0AIABlAG4AZQByAGcAeQAgAGMAbwBuAHQAZQBuAHQAIABmAGEAYwB0AG8AcgAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAIABpAG4AIABzAGwAdQBkAGcAZQAgAGIAaQBvAGcAYQBzACAAZgBsAGEAcgBlAGQAIAAoAEcASgAvAG0AMwApAFwAbgBFAEYAXwBmAGwAYQByAGUAZABfAEMASAA0ACAAPQAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAcwBsAHUAZABnAGUAIABiAGkAbwBnAGEAcwAgAGYAbABhAHIAZQBkACAAKABrAGcAIABDAE8AMgBlAC8ARwBKACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8AMQAxAF8AMQBfADEAXwAxAF8AXwAxAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFcAYQBzAHQAZQB3AGEAdABlAHIAVAByAGUAYQB0AG0AZQBuAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAVwBfAHQALAAgAEMATwBEAF8AaQBuACwAIABGAF8AcwBsAHUAZABnAGUALAAgAEMATwBEAF8AbwB1AHQALAAgAEMARgBfAHcAdwBfAHQALAAgAEUARgBfAHcAdwAsACAARgBfAHIAZQBtAG8AdgBlAGQALAAgAEMARgBfAHMAbAB1AGQAZwBlAF8AdAAsACAARQBGAF8AcwBsAHUAZABnAGUALAAgAFEAXwBjAGEAcAAsACAAUQBfAGYAbABhAHIAZQBkACwAIABRAF8AbwB1AHQALAAgAEUAQwBfAGYAbABhAHIAZQBkACwAIABFAEYAXwBmAGwAYQByAGUAZABDAEgANAAsAFwAbgAgACAAIAAgACgAMQAvADEAMAAwADAAKQAgACoAIAAoACgAVwBfAHQAIAAqACAAKABDAE8ARABfAGkAbgAgACoAIAAoADEAIAAtACAARgBfAHMAbAB1AGQAZwBlACkAIAAtACAAQwBPAEQAXwBvAHUAdAApACAAKgAgAEMARgBfAHcAdwBfAHQAIAAqACAARQBGAF8AdwB3ACkAIAArACAAKABXAF8AdAAgACoAIAAoAEMATwBEAF8AaQBuACAAKgAgACgARgBfAHMAbAB1AGQAZwBlACAALQAgAEYAXwByAGUAbQBvAHYAZQBkACkAKQAgACoAIABDAEYAXwBzAGwAdQBkAGcAZQBfAHQAIAAqACAARQBGAF8AcwBsAHUAZABnAGUAKQAgAC0AIAAoADYALgA3ADgANAAgACoAIAAxADAAXgAtADQAIAAqACAAKABRAF8AYwBhAHAAIAArACAAUQBfAGYAbABhAHIAZQBkACAAKwAgAFEAXwBvAHUAdAApACkAIAArACAAKABRAF8AZgBsAGEAcgBlAGQAIAAqACAAKABFAEMAXwBmAGwAYQByAGUAZAAgACoAIABFAEYAXwBmAGwAYQByAGUAZABDAEgANAApACkAKQBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEAMQBfADEAXwAxAF8AMQBfAF8AMQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBXAGEAcwB0AGUAdwBhAHQAZQByAFQAcgBlAGEAdABtAGUAbgB0AF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAdwBhAHMAdABlAHcAYQB0AGUAcgAgAHQAcgBlAGEAdABtAGUAbgB0AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADEAXwAxAF8AMQBfADEAXwBfADEAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AVwBhAHMAdABlAHcAYQB0AGUAcgBUAHIAZQBhAHQAbQBlAG4AdABfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBfAEMASAA0AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADEAXwAxAF8AMQBfADEAXwBfADEAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AVwBhAHMAdABlAHcAYQB0AGUAcgBUAHIAZQBhAHQAbQBlAG4AdABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAEgANABcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQAxAF8AMQBfADEAXwAxAF8AXwAxAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFcAYQBzAHQAZQB3AGEAdABlAHIAVAByAGUAYQB0AG0AZQBuAHQAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAMQAxAC4AMQAuADEALgAxACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADEAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQAxAF8AMQBfADEAXwAxAF8AXwAxAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFcAYQBzAHQAZQB3AGEAdABlAHIAVAByAGUAYQB0AG0AZQBuAHQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAARwByAGUAZQBuAGgAbwB1AHMAZQAgAGEAbgBkACAARQBuAGUAcgBnAHkAIABSAGUAcABvAHIAdABpAG4AZwAgAE0AZQBhAHMAdQByAGUAbQBlAG4AdAAgAEQAZQB0AGUAcgBtAGkAbgBhAHQAaQBvAG4AIAAyADAAMAA4AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADEAXwAxAF8AMQBfADEAXwBfADEAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AVwBhAHMAdABlAHcAYQB0AGUAcgBUAHIAZQBhAHQAbQBlAG4AdABfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwB7AEMASAA0AH0APQBcAFwAZgByAGEAYwB7ADEAfQB7ADEAMAAwADAAfQBcAFwAdABpAG0AZQBzAFwAXABsAGUAZgB0AHsAXABcAGwAZQBmAHQAewBXAF8AdABcAFwAdABpAG0AZQBzAFwAXABsAGUAZgB0AFsAQwBPAEQAXwB7AGkAbgB9AFwAXAB0AGkAbQBlAHMAKAAxAC0ARgBfAHsAcwBsAHUAZABnAGUAfQApAC0AQwBPAEQAXwB7AG8AdQB0AH0AXABcAHIAaQBnAGgAdABdAFwAXAB0AGkAbQBlAHMAIABDAEYAXwB7AHcAdwAsAHQAfQBcAFwAdABpAG0AZQBzACAARQBGAF8AewB3AHcAfQBcAFwAcgBpAGcAaAB0AH0AKwBcAFwAbABlAGYAdAB7AFcAXwB0AFwAXAB0AGkAbQBlAHMAXABcAGwAZQBmAHQAWwBDAE8ARABfAHsAaQBuAH0AXABcAHQAaQBtAGUAcwAoAEYAXwB7AHMAbAB1AGQAZwBlAH0ALQBGAF8AewByAGUAbQBvAHYAZQBkAH0AKQBcAFwAcgBpAGcAaAB0AF0AXABcAHQAaQBtAGUAcwAgAEMARgBfAHsAcwBsAHUAZABnAGUALAB0AH0AXABcAHQAaQBtAGUAcwAgAEUARgBfAHsAcwBsAHUAZABnAGUAfQBcAFwAcgBpAGcAaAB0AH0ALQBcAFwAbABlAGYAdAB7ADYALgA3ADgANABcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADQAfQBcAFwAdABpAG0AZQBzACAAXABcAGwAZQBmAHQAWwAgAFEAXwB7AGMAYQBwAH0AKwBRAF8AewBmAGwAYQByAGUAZAB9ACsAUQBfAHsAbwB1AHQAfQBcAFwAcgBpAGcAaAB0AF0AXABcAHIAaQBnAGgAdAB9ACsAXABcAGwAZQBmAHQAewBRAF8AewBmAGwAYQByAGUAZAB9AFwAXAB0AGkAbQBlAHMAIABcAFwAbABlAGYAdABbACAARQBDAF8AewBmAGwAYQByAGUAZAB9AFwAXAB0AGkAbQBlAHMAIABFAEYAXwB7AGYAbABhAHIAZQBkACwAQwBIADQAfQBcAFwAcgBpAGcAaAB0AF0AXABcAHIAaQBnAGgAdAB9AFwAXAByAGkAZwBoAHQAfQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQAxAF8AMQBfADEAXwAxAF8AXwAxAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFcAYQBzAHQAZQB3AGEAdABlAHIAVAByAGUAYQB0AG0AZQBuAHQAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEANQAsACAANAAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAF8AdABcACIALAAgAFwAIgBxAHUAYQBuAHQAaQB0AHkAIABvAGYAIAB3AGEAcwB0AGUAdwBhAHQAZQByACAAdAByAGUAYQB0AGUAZAAgAGEAdAAgAGYAYQBjAGkAbABpAHQAeQAgAHQAeQBwAGUAIAB0AFwAIgAsACAAXAAiAG0AMwBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwBEAF8AaQBuAFwAIgAsACAAXAAiAGEAdgBlAHIAYQBnAGUAIABpAG4AbABlAHQAIABDAGgAZQBtAGkAYwBhAGwAIABPAHgAeQBnAGUAbgAgAEQAZQBtAGEAbgBkACAAYwBvAG4AYwBlAG4AdAByAGEAdABpAG8AbgAgAG8AZgAgAHcAYQBzAHQAZQB3AGEAdABlAHIAXAAiACwAIABcACIAawBnACAAQwBPAEQALwBtADMAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAF8AcwBsAHUAZABnAGUAXAAiACwAIABcACIAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAQwBPAEQAIAByAGUAbQBvAHYAZQBkACAAZgByAG8AbQAgAHcAYQBzAHQAZQB3AGEAdABlAHIAIABhAHMAIABzAGwAdQBkAGcAZQBcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAE8ARABfAG8AdQB0AFwAIgAsACAAXAAiAGEAdgBlAHIAYQBnAGUAIABvAHUAdABsAGUAdAAgAEMATwBEACAAYwBvAG4AYwBlAG4AdAByAGEAdABpAG8AbgAgAG8AZgAgAHcAYQBzAHQAZQB3AGEAdABlAHIAXAAiACwAIABcACIAawBnACAAQwBPAEQALwBtADMAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAEYAXwB3AHcAXwB0AFwAIgAsACAAXAAiAG0AZQB0AGgAYQBuAGUAIABjAG8AcgByAGUAYwB0AGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAGYAYQBjAGkAbABpAHQAeQAgAHQAeQBwAGUAIAB0ACAAdQBzAGUAZAAgAHQAbwAgAHQAcgBlAGEAdAAgAHcAYQBzAHQAZQB3AGEAdABlAHIAXAAiACwAIABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAF8AdwB3AFwAIgAsACAAXAAiAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAdwBhAHMAdABlAHcAYQB0AGUAcgBcACIALAAgAFwAIgBrAGcAIABDAEgANAAvAGsAZwAgAEMATwBEAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBfAHIAZQBtAG8AdgBlAGQAXAAiACwAIABcACIAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAQwBPAEQAIAByAGUAbQBvAHYAZQBkACAAZgByAG8AbQAgAHQAaABlACAAdwBhAHMAdABlAHcAYQB0AGUAcgAgAHQAcgBlAGEAdABtAGUAbgB0ACAAZgBhAGMAaQBsAGkAdAB5ACAAYQBuAGQAIAB0AHIAYQBuAHMAZgBlAHIAcgBlAGQAIABlAGwAcwBlAHcAaABlAHIAZQBcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAEYAXwBzAGwAdQBkAGcAZQBfAHQAXAAiACwAIABcACIAbQBlAHQAaABhAG4AZQAgAGMAbwByAHIAZQBjAHQAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAZgBhAGMAaQBsAGkAdAB5ACAAdAB5AHAAZQAgAHQAIAB1AHMAZQBkACAAdABvACAAdAByAGUAYQB0ACAAcwBsAHUAZABnAGUAXAAiACwAIABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAF8AcwBsAHUAZABnAGUAXAAiACwAIABcACIAbQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABzAGwAdQBkAGcAZQBcACIALAAgAFwAIgBrAGcAIABDAEgANAAvAGsAZwAgAEMATwBEAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUQBfAGMAYQBwAFwAIgAsACAAXAAiAHEAdQBhAG4AdABpAHQAeQAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAIABpAG4AIABzAGwAdQBkAGcAZQAgAGIAaQBvAGcAYQBzACAAYwBhAHAAdAB1AHIAZQBkACAAZgBvAHIAIABjAG8AbQBiAHUAcwB0AGkAbwBuAFwAIgAsACAAXAAiAG0AMwAgAEMASAA0AFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUQBfAGYAbABhAHIAZQBkAFwAIgAsACAAXAAiAHEAdQBhAG4AdABpAHQAeQAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAIABpAG4AIABzAGwAdQBkAGcAZQAgAGIAaQBvAGcAYQBzACAAZgBsAGEAcgBlAGQAIABiAHkAIAB0AGgAZQAgAHQAcgBlAGEAdABtAGUAbgB0ACAAZgBhAGMAaQBsAGkAdAB5AFwAIgAsACAAXAAiAG0AMwAgAEMASAA0AFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUQBfAG8AdQB0AFwAIgAsACAAXAAiAHEAdQBhAG4AdABpAHQAeQAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAIABpAG4AIABzAGwAdQBkAGcAZQAgAGIAaQBvAGcAYQBzACAAdAByAGEAbgBzAGYAZQByAHIAZQBkACAAbwB1AHQAIABvAGYAIAB0AGgAZQAgAHQAcgBlAGEAdABtAGUAbgB0ACAAZgBhAGMAaQBsAGkAdAB5AFwAIgAsACAAXAAiAG0AMwAgAEMASAA0AFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBDAF8AZgBsAGEAcgBlAGQAXAAiACwAIABcACIAZQBuAGUAcgBnAHkAIABjAG8AbgB0AGUAbgB0ACAAZgBhAGMAdABvAHIAIABvAGYAIABtAGUAdABoAGEAbgBlACAAaQBuACAAcwBsAHUAZABnAGUAIABiAGkAbwBnAGEAcwAgAGYAbABhAHIAZQBkAFwAIgAsACAAXAAiAEcASgAvAG0AMwBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARgBfAGYAbABhAHIAZQBkAEMASAA0AFwAIgAsACAAXAAiAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAcwBsAHUAZABnAGUAIABiAGkAbwBnAGEAcwAgAGYAbABhAHIAZQBkAFwAIgAsACAAXAAiAGsAZwAgAEMASAA0AC8ARwBKAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAdABcACIALAAgAFwAIgB0AHIAZQBhAHQAbQBlAG4AdAAgAGYAYQBjAGkAbABpAHQAeQAgAHQAeQBwAGUAXAAiACwAIABcACIAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAFYARQBFAFIARwBfADEAMQBfADEAXwAxAF8AMQBfAF8AMQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBXAGEAcwB0AGUAdwBhAHQAZQByAFQAcgBlAGEAdABtAGUAbgB0AF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBOACAAUwBPAFUAUgBDAEUAOgAgAEMAaABhAG4AZwBlAGQAIAB1AG4AaQB0AHMAIABvAGYAIABFAEYAXwB3AHcALAAgAEUARgBfAFMAbAB1AGQAZwBlACAAYQBuAGQAIABFAEYAXwBmAGwAYQByAGUAZAAgAGYAcgBvAG0AIABDAE8AMgBlACAAdABvACAAQwBIADQAIAB0AG8AIABtAGEAdABjAGgAIABkAGEAdABhACAAaQBuACAAVABhAGIAbABlACAAXAAiACkAOwAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBTAG8AdQByAGMAZQBEAGEAdABhACIALAAiAHQAZQB4AHQAIgA6ACIALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgBUAGEAYgBsAGUAIABBAC4ANAAuADEALgAzADoAIABNAGUAdABoAGEAbgBlACAAYwBvAHIAcgBlAGMAdABpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB0AHIAZQBhAHQAbQBlAG4AdAAgAGYAYQBjAGkAbABpAHQAeQAgAHQAeQBwAGUAIAB0ACAAdQBzAGUAZAAgAHQAbwAgAHQAcgBlAGEAdAAgAHcAYQBzAHQAZQB3AGEAdABlAHIAIAAoAGYAcgBhAGMAdABpAG8AbgApACAAKABDAEYAdwB3ACwAdAApAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEMAbwByAHIAZQBjAHQAaQBvAG4ARgBhAGMAdABvAHIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFQAaQB0AGwAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAE0AZQB0AGgAYQBuAGUAIABjAG8AcgByAGUAYwB0AGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHQAcgBlAGEAdABtAGUAbgB0ACAAZgBhAGMAaQBsAGkAdAB5ACAAdAB5AHAAZQAgAHQAIAB1AHMAZQBkACAAdABvACAAdAByAGUAYQB0ACAAdwBhAHMAdABlAHcAYQB0AGUAcgBcACIAKQApADsAXABuAFwAbgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEMAbwByAHIAZQBjAHQAaQBvAG4ARgBhAGMAdABvAHIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFYAYQByAGkAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEMARgB3AHcALAB0AFwAIgApACkAOwBcAG4AXABuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUAQwBvAHIAcgBlAGMAdABpAG8AbgBGAGEAYwB0AG8AcgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AVQBuAGkAdABcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIAKQApADsAXABuAFwAbgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEMAbwByAHIAZQBjAHQAaQBvAG4ARgBhAGMAdABvAHIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADQALgAxAC4AMwBcACIAKQApADsAXABuAFwAbgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEMAbwByAHIAZQBjAHQAaQBvAG4ARgBhAGMAdABvAHIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAEQAYQB0AGEAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANgAsACAAMgAsAFwAbgAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBGAGEAYwBpAGwAaQB0AHkAIAB0AHkAcABlACAAdABcACIALAAgAFwAIgBDAEYAdwB3ACwAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBNAGEAbgBhAGcAZQBkACAAYQBlAHIAbwBiAGkAYwAgAHQAcgBlAGEAdABtAGUAbgB0AFwAIgAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFUAbgBtAGEAbgBhAGcAZQBkACAAYQBlAHIAbwBiAGkAYwAgAHQAcgBlAGEAdABtAGUAbgB0AFwAIgAsACAAMAAuADMAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBBAG4AYQBlAHIAbwBiAGkAYwAgAGQAaQBnAGUAcwB0AG8AcgAvAHIAZQBhAGMAdABvAHIAXAAiACwAIAAwAC4AOAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFMAaABhAGwAbABvAHcAIABhAG4AYQBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuACAAKABkIiAAMgAgAG0AKQBcACIALAAgADAALgAyADsAXABuACAAIAAgACAAIAAgACAAIABcACIARABlAGUAcAAgAGEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AIAAoAFwAdQAwADAAMwBlACAAMgBtACkAXAAiACwAIAAwAC4AOABcAG4AIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgApACkAKQA7AFwAbgBcAG4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBDAG8AcgByAGUAYwB0AGkAbwBuAEYAYQBjAHQAbwByAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAFwAIgApACkAOwBcAG4AXABuAFwAbgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFQAYQBiAGwAZQAgAEEALgA0AC4AMQAuADQAOgAgAE0AZQB0AGgAYQBuAGUAIABjAG8AcgByAGUAYwB0AGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHQAcgBlAGEAdABtAGUAbgB0ACAAZgBhAGMAaQBsAGkAdAB5ACAAdAB5AHAAZQAgAHQAIAB1AHMAZQBkACAAdABvACAAdAByAGUAYQB0ACAAcwBsAHUAZABnAGUAIAAoAGYAcgBhAGMAdABpAG8AbgApACAAKABDAEYAcwBsAHUAZABnAGUALAB0ACkAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUAQwBvAHIAcgBlAGMAdABpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBfAFQAaQB0AGwAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAE0AZQB0AGgAYQBuAGUAIABjAG8AcgByAGUAYwB0AGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHQAcgBlAGEAdABtAGUAbgB0ACAAZgBhAGMAaQBsAGkAdAB5ACAAdAB5AHAAZQAgAHQAIAB1AHMAZQBkACAAdABvACAAdAByAGUAYQB0ACAAcwBsAHUAZABnAGUAXAAiACkAKQA7AFwAbgBcAG4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBDAG8AcgByAGUAYwB0AGkAbwBuAEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAQwBGAHMAbAB1AGQAZwBlACwAdABcACIAKQApADsAXABuAFwAbgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEMAbwByAHIAZQBjAHQAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAXwBVAG4AaQB0AFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgApACkAOwBcAG4AXABuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUAQwBvAHIAcgBlAGMAdABpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBfAFMAbwB1AHIAYwBlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADQALgAxAC4ANABcACIAKQApADsAXABuAFwAbgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEMAbwByAHIAZQBjAHQAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAXwBEAGEAdABhAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADIALABcAG4AIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIABcACIARgBhAGMAaQBsAGkAdAB5ACAAdAB5AHAAZQAgAHQAXAAiACwAIABcACIAQwBGAHMAbAB1AGQAZwBlACwAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBNAGEAbgBhAGcAZQBkACAAYQBlAHIAbwBiAGkAYwAgAHQAcgBlAGEAdABtAGUAbgB0AFwAIgAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFUAbgBtAGEAbgBhAGcAZQBkACAAYQBlAHIAbwBiAGkAYwAgAHQAcgBlAGEAdABtAGUAbgB0AFwAIgAsACAAMAAuADMAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBBAG4AYQBlAHIAbwBiAGkAYwAgAGQAaQBnAGUAcwB0AG8AcgAvAHIAZQBhAGMAdABvAHIAXAAiACwAIAAwAC4AOAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFMAaABhAGwAbABvAHcAIABhAG4AYQBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuACAAKABkIiAAMgAgAG0AKQBcACIALAAgADAALgAyADsAXABuACAAIAAgACAAIAAgACAAIABcACIARABlAGUAcAAgAGEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AIAAoAFwAdQAwADAAMwBlACAAMgBtACkAXAAiACwAIAAwAC4AOABcAG4AIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgApACkAKQA7AFwAbgBcAG4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBDAG8AcgByAGUAYwB0AGkAbwBuAEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBcACIAKQApADsAXABuAFwAbgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBUAGkAdABsAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBNAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHcAYQBzAHQAZQB3AGEAdABlAHIAXAAiACkAKQA7AFwAbgBcAG4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFYAYQByAGkAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEUARgB3AHcAXAAiACkAKQA7AFwAbgBcAG4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFUAbgBpAHQAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBrAGcAIABDAEgANAAgAC8AIABrAGcAIABDAE8ARABcACIAKQApADsAXABuAFwAbgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AUwBvAHUAcgBjAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAAxADEALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdABzAFwAIgApACkAOwBcAG4AXABuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBEAGEAdABhAFwAbgA9AEwAQQBNAEIARABBACgAIAAwAC4AMgA1ACkAOwBcAG4AXABuAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAXwBUAGkAdABsAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBNAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHMAbAB1AGQAZwBlAFwAIgApACkAOwBcAG4AXABuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIARQBGAHMAbAB1AGQAZwBlAFwAIgApACkAOwBcAG4AXABuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAF8AVQBuAGkAdABcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAGsAZwAgAEMASAA0ACAALwAgAGsAZwAgAEMATwBEAFwAIgApACkAOwBcAG4AXABuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAF8AUwBvAHUAcgBjAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAAxADEALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdABzAFwAIgApACkAOwBcAG4AXABuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAF8ARABhAHQAYQBcAG4APQBMAEEATQBCAEQAQQAoADAALgAyADUAKQA7AFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgBXAGEAcwB0AGUAXwBFAG4AZQByAGcAeQBDAG8AbgB0AGUAbgB0AEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAEIAaQBvAGcAYQBzAEYAbABhAHIAZQBkAF8AVABpAHQAbABlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIARQBuAGUAcgBnAHkAIABjAG8AbgB0AGUAbgB0ACAAZgBhAGMAdABvAHIAIABvAGYAIABzAGwAdQBkAGcAZQAgAGIAaQBvAGcAYQBzACAAZgBsAGEAcgBlAGQAXAAiACkAKQA7AFwAbgBcAG4AVwBhAHMAdABlAF8ARQBuAGUAcgBnAHkAQwBvAG4AdABlAG4AdABGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBCAGkAbwBnAGEAcwBGAGwAYQByAGUAZABfAFYAYQByAGkAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEUAQwBmAGwAYQByAGUAZABcACIAKQApADsAXABuAFwAbgBXAGEAcwB0AGUAXwBFAG4AZQByAGcAeQBDAG8AbgB0AGUAbgB0AEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAEIAaQBvAGcAYQBzAEYAbABhAHIAZQBkAF8AVQBuAGkAdABcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEcASgAgAC8AIABtADMAXAAiACkAKQA7AFwAbgBcAG4AVwBhAHMAdABlAF8ARQBuAGUAcgBnAHkAQwBvAG4AdABlAG4AdABGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBCAGkAbwBnAGEAcwBGAGwAYQByAGUAZABfAFMAbwB1AHIAYwBlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAMQAxAC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAcwBcACIAKQApADsAXABuAFwAbgBXAGEAcwB0AGUAXwBFAG4AZQByAGcAeQBDAG8AbgB0AGUAbgB0AEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAEIAaQBvAGcAYQBzAEYAbABhAHIAZQBkAF8ARABhAHQAYQBcAG4APQBMAEEATQBCAEQAQQAoADAALgAwADMANwA3ACkAOwBcAG4AXABuAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAQgBpAG8AZwBhAHMARgBsAGEAcgBlAGQAXwBUAGkAdABsAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBNAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHMAbAB1AGQAZwBlACAAYgBpAG8AZwBhAHMAIABmAGwAYQByAGUAZABcACIAKQApADsAXABuAFwAbgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBCAGkAbwBnAGEAcwBGAGwAYQByAGUAZABfAFYAYQByAGkAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEUARgBmAGwAYQByAGUAZAAsAEMASAA0AFwAIgApACkAOwBcAG4AXABuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAEIAaQBvAGcAYQBzAEYAbABhAHIAZQBkAF8AVQBuAGkAdABcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAGsAZwAgAEMASAA0ACAALwAgAEcASgBcACIAKQApADsAXABuAFwAbgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBCAGkAbwBnAGEAcwBGAGwAYQByAGUAZABfAFMAbwB1AHIAYwBlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAMQAxAC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAcwBcACIAKQApADsAXABuAFwAbgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBCAGkAbwBnAGEAcwBGAGwAYQByAGUAZABfAEQAYQB0AGEAXABuAD0ATABBAE0AQgBEAEEAKAAwAC4AMgAyADgAOQApADsAXABuAFwAbgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAFcAYQBzAHQAZQBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBCAGkAbwBnAGEAcwBGAGwAYQByAGUAZABfAFQAaQB0AGwAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAcwBsAHUAZABnAGUAIABiAGkAbwBnAGEAcwAgAGYAbABhAHIAZQBkAFwAIgApACkAOwBcAG4AXABuAFcAYQBzAHQAZQBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBCAGkAbwBnAGEAcwBGAGwAYQByAGUAZABfAFYAYQByAGkAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEUARgBmAGwAYQByAGUAZAAsAE4AMgBPAFwAIgApACkAOwBcAG4AXABuAFcAYQBzAHQAZQBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBCAGkAbwBnAGEAcwBGAGwAYQByAGUAZABfAFUAbgBpAHQAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBrAGcAIABOADIATwAgAC8AIABHAEoAXAAiACkAKQA7AFwAbgBcAG4AVwBhAHMAdABlAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAEIAaQBvAGcAYQBzAEYAbABhAHIAZQBkAF8AUwBvAHUAcgBjAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAAxADEALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdABzAFwAIgApACkAOwBcAG4AXABuAFcAYQBzAHQAZQBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBCAGkAbwBnAGEAcwBGAGwAYQByAGUAZABfAEQAYQB0AGEAXABuAD0ATABBAE0AQgBEAEEAKAAxAC4AMQAzADIAZQAtADQAKQA7AFwAbgAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBOADIATwBfAEUAcQB1AGEAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAxADEALgAxADoAIABXAGEAcwB0AGUAdwBhAHQAZQByAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAxADEALgAxAC4AMwAuADEAIABNAGUAdABoAG8AZAAgADEAIAAtACAATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAG8AbgBzAGkAdABlACAAVwBhAHMAdABlAHcAYQB0AGUAcgAgAE0AYQBuAGEAZwBlAG0AZQBuAHQAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwAxADEAXwAxAF8AMwBfADEAXwBfADEAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEYAbABhAHIAZQBkAEIAaQBvAGcAYQBzAFwAbgBOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAZgBsAGEAcgBlAGQAIABiAGkAbwBnAGEAcwBcAG4ARQBfAE4AMgBPAFwAbgB0ACAATgAyAE8AXABuAEUAXwB7AE4AMgBPAH0APQBcAFwAZgByAGEAYwB7AFEAXwB7AGYAbABhAHIAZQBkAH0AfQB7ADEAMAAwADAAfQBcAFwAdABpAG0AZQBzACAARQBGAF8AewBmAGwAYQByAGUAZAAsAE4AMgBPAH0AXABuAFEAXwBmAGwAYQByAGUAZAAgAD0AIAB2AG8AbAB1AG0AZQAgAG8AZgAgAGIAaQBvAGcAYQBzACAAZgBsAGEAcgBlAGQAIAAoAG0AMwAgAG8AcgAgAEcASgApAFwAbgBFAEYAXwBmAGwAYQByAGUAZABfAE4AMgBPACAAPQAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAZgBsAGEAcgBlAGQAIABiAGkAbwBnAGEAcwAgACgAawBnACAATgAyAE8ALwBHAEoAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwAxADEAXwAxAF8AMwBfADEAXwBfADEAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEYAbABhAHIAZQBkAEIAaQBvAGcAYQBzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFEAXwBmAGwAYQByAGUAZAAsACAARQBDAF8AZgBsAGEAcgBlAGQALAAgAEUARgBfAGYAbABhAHIAZQBkAE4AMgBPACwAXABuACAAIAAgACAAKABRAF8AZgBsAGEAcgBlAGQAIAAvACAAMQAwADAAMAApACAAKgAgACgARQBDAF8AZgBsAGEAcgBlAGQAIAAqACAARQBGAF8AZgBsAGEAcgBlAGQATgAyAE8AKQBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEAMQBfADEAXwAzAF8AMQBfAF8AMQBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ARgBsAGEAcgBlAGQAQgBpAG8AZwBhAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABmAGwAYQByAGUAZAAgAGIAaQBvAGcAYQBzAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADEAXwAxAF8AMwBfADEAXwBfADEAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEYAbABhAHIAZQBkAEIAaQBvAGcAYQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAF8ATgAyAE8AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEAMQBfADEAXwAzAF8AMQBfAF8AMQBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ARgBsAGEAcgBlAGQAQgBpAG8AZwBhAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgB0ACAATgAyAE8AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEAMQBfADEAXwAzAF8AMQBfAF8AMQBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ARgBsAGEAcgBlAGQAQgBpAG8AZwBhAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAMQAxAC4AMQAuADMALgAxACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADEAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQAxAF8AMQBfADMAXwAxAF8AXwAxAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBGAGwAYQByAGUAZABCAGkAbwBnAGEAcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQAxAF8AMQBfADMAXwAxAF8AXwAxAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBGAGwAYQByAGUAZABCAGkAbwBnAGEAcwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwB7AE4AMgBPAH0APQBcAFwAZgByAGEAYwB7AFEAXwB7AGYAbABhAHIAZQBkAH0AfQB7ADEAMAAwADAAfQBcAFwAdABpAG0AZQBzACAAXABcAGwAZQBmAHQAWwBFAEMAXwB7AGYAbABhAHIAZQBkAH0AIABcAFwAdABpAG0AZQBzACAARQBGAF8AewBmAGwAYQByAGUAZAAsAE4AMgBPAH0AXABcAHIAaQBnAGgAdABdAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADEAXwAxAF8AMwBfADEAXwBfADEAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEYAbABhAHIAZQBkAEIAaQBvAGcAYQBzAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAA0ACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEAXwBmAGwAYQByAGUAZABcACIALAAgAFwAIgB2AG8AbAB1AG0AZQAgAG8AZgAgAGIAaQBvAGcAYQBzACAAZgBsAGEAcgBlAGQAXAAiACwAIABcACIAbQAzAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBDAF8AZgBsAGEAcgBlAGQAXAAiACwAIABcACIAZQBuAGUAcgBnAHkAIABjAG8AbgB0AGUAbgB0ACAAZgBhAGMAdABvAHIAIABvAGYAIABzAGwAdQBkAGcAZQAgAGIAaQBvAGcAYQBzACAAZgBsAGEAcgBlAGQAXAAiACwAIABcACIARwBKAC8AbQAzAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAF8AZgBsAGEAcgBlAGQATgAyAE8AXAAiACwAIABcACIAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABmAGwAYQByAGUAZAAgAGIAaQBvAGcAYQBzAFwAIgAsACAAXAAiAGsAZwAgAE4AMgBPAC8ARwBKAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AIgB9AF0ALAAiAHAAcgBvAGoAZQBjAHQATgBhAG0AZQBzACIAOgBbACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEEAcABwAGUAbgBkAGkAYwBlAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAUgBvAHcAUwB0AGEAcgB0AE4AdQBtAGIAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAHIAYQB5AEkAbgBUAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUAVAB3AG8AQwBvAGwAdQBtAG4AcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBPAG4AZQBDAG8AbAB1AG0AbgBBAG4AZABIAGUAYQBkAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBTAHAAbABpAHQAUwB0AHIAaQBuAGcASQBuAHQAbwBBAHIAcgBhAHkAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQwBsAGkAbQBhAHQAZQBaAG8AbgBlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAEkAdABlAG0ARgByAG8AbQBNAGkAbgBNAGEAeAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBTAHUAbQBRAHUAYQBuAHQAaQB0AHkARgByAG8AbQBDAHIAaQB0AGUAcgBpAGEAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAUABlAHIAaQBvAGQAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEYAdQBuAGMAdABpAG8AbgBOAGEAbQBlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAE4AMgBPAEUARgBGAHIAbwBtAFAAcgBvAGQASQByAHIAaQBnAGEAdABpAG8AbgBSAGEAaQBuAGYAYQBsAGwAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBHAGUAdABGAHIAYQBjAFcARQBUACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEMAbwBuAHYAZQByAHQAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAVABvAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADEAXwAxAF8AMQBfADEAXwBfADEAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AVwBhAHMAdABlAHcAYQB0AGUAcgBUAHIAZQBhAHQAbQBlAG4AdAAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQAxAF8AMQBfADEAXwAxAF8AXwAxAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFcAYQBzAHQAZQB3AGEAdABlAHIAVAByAGUAYQB0AG0AZQBuAHQAXwBUAGkAdABsAGUAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEAMQBfADEAXwAxAF8AMQBfAF8AMQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBXAGEAcwB0AGUAdwBhAHQAZQByAFQAcgBlAGEAdABtAGUAbgB0AF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADEAXwAxAF8AMQBfADEAXwBfADEAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AVwBhAHMAdABlAHcAYQB0AGUAcgBUAHIAZQBhAHQAbQBlAG4AdABfAFUAbgBpAHQAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEAMQBfADEAXwAxAF8AMQBfAF8AMQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBXAGEAcwB0AGUAdwBhAHQAZQByAFQAcgBlAGEAdABtAGUAbgB0AF8AUwBvAHUAcgBjAGUAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEAMQBfADEAXwAxAF8AMQBfAF8AMQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBXAGEAcwB0AGUAdwBhAHQAZQByAFQAcgBlAGEAdABtAGUAbgB0AF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEAMQBfADEAXwAxAF8AMQBfAF8AMQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBXAGEAcwB0AGUAdwBhAHQAZQByAFQAcgBlAGEAdABtAGUAbgB0AF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQAxAF8AMQBfADEAXwAxAF8AXwAxAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFcAYQBzAHQAZQB3AGEAdABlAHIAVAByAGUAYQB0AG0AZQBuAHQAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQAxAF8AMQBfADEAXwAxAF8AXwAxAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFcAYQBzAHQAZQB3AGEAdABlAHIAVAByAGUAYQB0AG0AZQBuAHQAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUAQwBvAHIAcgBlAGMAdABpAG8AbgBGAGEAYwB0AG8AcgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AVABpAHQAbABlACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBDAG8AcgByAGUAYwB0AGkAbwBuAEYAYQBjAHQAbwByAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEMAbwByAHIAZQBjAHQAaQBvAG4ARgBhAGMAdABvAHIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFUAbgBpAHQAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEMAbwByAHIAZQBjAHQAaQBvAG4ARgBhAGMAdABvAHIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBDAG8AcgByAGUAYwB0AGkAbwBuAEYAYQBjAHQAbwByAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBEAGEAdABhACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBDAG8AcgByAGUAYwB0AGkAbwBuAEYAYQBjAHQAbwByAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUAQwBvAHIAcgBlAGMAdABpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBfAFQAaQB0AGwAZQAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUAQwBvAHIAcgBlAGMAdABpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUAQwBvAHIAcgBlAGMAdABpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBfAFUAbgBpAHQAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEMAbwByAHIAZQBjAHQAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAXwBTAG8AdQByAGMAZQAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUAQwBvAHIAcgBlAGMAdABpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBfAEQAYQB0AGEAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEMAbwByAHIAZQBjAHQAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBUAGkAdABsAGUAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFUAbgBpAHQAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AUwBvAHUAcgBjAGUAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBXAGEAcwB0AGUAdwBhAHQAZQByAF8ARABhAHQAYQAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAF8AVABpAHQAbABlACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBfAFUAbgBpAHQAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBfAFMAbwB1AHIAYwBlACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAXwBEAGEAdABhACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AVwBhAHMAdABlAF8ARQBuAGUAcgBnAHkAQwBvAG4AdABlAG4AdABGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBCAGkAbwBnAGEAcwBGAGwAYQByAGUAZABfAFQAaQB0AGwAZQAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFcAYQBzAHQAZQBfAEUAbgBlAHIAZwB5AEMAbwBuAHQAZQBuAHQARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAQgBpAG8AZwBhAHMARgBsAGEAcgBlAGQAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBXAGEAcwB0AGUAXwBFAG4AZQByAGcAeQBDAG8AbgB0AGUAbgB0AEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAEIAaQBvAGcAYQBzAEYAbABhAHIAZQBkAF8AVQBuAGkAdAAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFcAYQBzAHQAZQBfAEUAbgBlAHIAZwB5AEMAbwBuAHQAZQBuAHQARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAQgBpAG8AZwBhAHMARgBsAGEAcgBlAGQAXwBTAG8AdQByAGMAZQAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFcAYQBzAHQAZQBfAEUAbgBlAHIAZwB5AEMAbwBuAHQAZQBuAHQARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAQgBpAG8AZwBhAHMARgBsAGEAcgBlAGQAXwBEAGEAdABhACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAQgBpAG8AZwBhAHMARgBsAGEAcgBlAGQAXwBUAGkAdABsAGUAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBCAGkAbwBnAGEAcwBGAGwAYQByAGUAZABfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAEIAaQBvAGcAYQBzAEYAbABhAHIAZQBkAF8AVQBuAGkAdAAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAEIAaQBvAGcAYQBzAEYAbABhAHIAZQBkAF8AUwBvAHUAcgBjAGUAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBCAGkAbwBnAGEAcwBGAGwAYQByAGUAZABfAEQAYQB0AGEAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBXAGEAcwB0AGUAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAQgBpAG8AZwBhAHMARgBsAGEAcgBlAGQAXwBUAGkAdABsAGUAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBXAGEAcwB0AGUAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAQgBpAG8AZwBhAHMARgBsAGEAcgBlAGQAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBXAGEAcwB0AGUAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAQgBpAG8AZwBhAHMARgBsAGEAcgBlAGQAXwBVAG4AaQB0ACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AVwBhAHMAdABlAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAEIAaQBvAGcAYQBzAEYAbABhAHIAZQBkAF8AUwBvAHUAcgBjAGUAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBXAGEAcwB0AGUAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAQgBpAG8AZwBhAHMARgBsAGEAcgBlAGQAXwBEAGEAdABhACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBOADIATwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQAxAF8AMQBfADMAXwAxAF8AXwAxAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBGAGwAYQByAGUAZABCAGkAbwBnAGEAcwAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8ATgAyAE8AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEAMQBfADEAXwAzAF8AMQBfAF8AMQBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ARgBsAGEAcgBlAGQAQgBpAG8AZwBhAHMAXwBUAGkAdABsAGUAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAE4AMgBPAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADEAXwAxAF8AMwBfADEAXwBfADEAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEYAbABhAHIAZQBkAEIAaQBvAGcAYQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBOADIATwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQAxAF8AMQBfADMAXwAxAF8AXwAxAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBGAGwAYQByAGUAZABCAGkAbwBnAGEAcwBfAFUAbgBpAHQAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAE4AMgBPAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADEAXwAxAF8AMwBfADEAXwBfADEAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEYAbABhAHIAZQBkAEIAaQBvAGcAYQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAE4AMgBPAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADEAXwAxAF8AMwBfADEAXwBfADEAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEYAbABhAHIAZQBkAEIAaQBvAGcAYQBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAE4AMgBPAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADEAXwAxAF8AMwBfADEAXwBfADEAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEYAbABhAHIAZQBkAEIAaQBvAGcAYQBzAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8ATgAyAE8AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEAMQBfADEAXwAzAF8AMQBfAF8AMQBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ARgBsAGEAcgBlAGQAQgBpAG8AZwBhAHMAXwBBAHIAZwB1AG0AZQBuAHQAcwAiAF0ALAAiAGwAbwBjAGEAbABlACIAOgB7ACIAbABpAHMAdABTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAsACIALAAiAHIAbwB3AFMAZQBwAGEAcgBhAHQAbwByACIAOgAiADsAIgAsACIAYwBvAGwAdQBtAG4AUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgB0AGgAbwB1AHMAYQBuAGQAcwBTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAsACIALAAiAHQAaABvAHUAcwBhAG4AZABzAFAAbwBzAGkAdABpAG8AbgBzACIAOgBbADMAXQAsACIAZABlAGMAaQBtAGEAbABTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAuACIALAAiAGQAYQB0AGUATwByAGQAZQByACIAOgAiAEQATQBZACIALAAiAGMAdQByAHIAZQBuAGMAeQBTAHkAbQBiAG8AbAAiADoAIgAkACIALAAiAGkAcwBDAHUAcgByAGUAbgBjAHkAUwB5AG0AYgBvAGwATABlAGEAZAAiADoAdAByAHUAZQAsACIAaQBzAEMAdQByAHIAZQBuAGMAeQBTAGUAcABCAHkAUwBwAGEAYwBlACIAOgBmAGEAbABzAGUALAAiAHIAbwB3AEwAZQB0AHQAZQByACIAOgAiAFIAIgAsACIAYwBvAGwAdQBtAG4ATABlAHQAdABlAHIAIgA6ACIAQwAiACwAIgByAGMATABlAGYAdABCAHIAYQBjAGsAZQB0ACIAOgAiAFsAIgAsACIAcgBjAFIAaQBnAGgAdABCAHIAYQBjAGsAZQB0ACIAOgAiAF0AIgAsACIAcwB0AGEAdABlAG0AZQBuAHQAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIAOwAiACwAIgBsAG8AYwBhAGwAZQBOAGEAbQBlACIAOgAiAGUAbgAtAHUAcwAiAH0AfQA=</AFEJSONBlob>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD460F9D-420A-4723-B323-396E4D19EC9B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -13996,15 +14011,15 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6BE249C-20B1-4A62-BBCD-F2A46D88BCAB}">
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9A9CF321-0D35-4044-BC72-33748FE2B865}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{809E3D44-A88D-4EBF-A307-6B8CE77A3361}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -14021,4 +14036,12 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6BE249C-20B1-4A62-BBCD-F2A46D88BCAB}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/Excel/11_Wastewater_WIP_v02.xlsx
+++ b/Excel/11_Wastewater_WIP_v02.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\htdocs\zneagcrc\GAF-VEERG-Functions\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8C476C3-6B8F-4A33-9F75-51D660C516B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7411F62B-5BC6-4323-9336-3217D798D237}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3510" yWindow="3510" windowWidth="28800" windowHeight="15345" firstSheet="7" activeTab="7" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
+    <workbookView xWindow="1950" yWindow="1950" windowWidth="28800" windowHeight="15345" firstSheet="7" activeTab="7" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
   </bookViews>
   <sheets>
     <sheet name="Home" sheetId="71" r:id="rId1"/>
@@ -20,7 +20,7 @@
     <sheet name="11.1.1-2 Wastewater CH4" sheetId="69" r:id="rId5"/>
     <sheet name="11.1.3-4 Wastewater N2O" sheetId="120" r:id="rId6"/>
     <sheet name="Constants - Wastewater" sheetId="110" r:id="rId7"/>
-    <sheet name="Constants - Common" sheetId="125" r:id="rId8"/>
+    <sheet name="Constants - Common" sheetId="126" r:id="rId8"/>
   </sheets>
   <externalReferences>
     <externalReference r:id="rId9"/>
@@ -40,7 +40,17 @@
     <definedName name="Common_Equations.Common_ConvertN2OToCO2e_Title">_xlfn.LAMBDA("Convert nitrous oxide emissions to carbon dioxide equivalent emissions")</definedName>
     <definedName name="Common_Equations.Common_ConvertN2OToCO2e_Unit">_xlfn.LAMBDA("t CO2e")</definedName>
     <definedName name="Common_Equations.Common_ConvertN2OToCO2e_Variable">_xlfn.LAMBDA("EN2O CO2e")</definedName>
-    <definedName name="Common_InputFunctions.Common_GetMCFTemperatureZone">_xlfn.LAMBDA(_xlpm.Temperature,_xlpm.MMS,_xlpm.TemperatureArray,_xlpm.MMSArray,_xlpm.ReturnArray, _xlfn.XLOOKUP(MEDIAN(_xlpm.Temperature, MIN(_xlpm.TemperatureArray), MAX(_xlpm.TemperatureArray)), _xlpm.TemperatureArray, _xlfn.XLOOKUP(_xlpm.MMS, _xlpm.MMSArray, _xlpm.ReturnArray)))</definedName>
+    <definedName name="Common_InputFunctions.Common_GetMCFTemperatureZone">_xlfn.LAMBDA(_xlpm.Temperature,_xlpm.MMS,_xlpm.TemperatureArray,_xlpm.MMSArray,_xlpm.ReturnArray,
+    _xlfn.XLOOKUP(
+        MEDIAN(
+            ROUND(_xlpm.Temperature, 0),
+            MIN(_xlpm.TemperatureArray),
+            MAX(_xlpm.TemperatureArray)
+        ),
+        _xlpm.TemperatureArray,
+        _xlfn.XLOOKUP(_xlpm.MMS, _xlpm.MMSArray, _xlpm.ReturnArray)
+    )
+)</definedName>
     <definedName name="Common_InputFunctions.CommonCropping_GetFracWET">_xlfn.LAMBDA(_xlpm.LeachingZone,_xlpm.ProductionSystem,_xlpm.LeachingZoneLookup,_xlpm.LeachingZoneFracWETLookup,_xlpm.ProductionSystemLookup,_xlpm.ProductionSystemFracWETLookup, _xlfn.LET(_xlpm.LeachingZoneFracWET, Common_InputFunctions.Utility_LookupValueInTableNumber(_xlpm.LeachingZone, _xlpm.LeachingZoneLookup, _xlpm.LeachingZoneFracWETLookup), _xlpm.ProductionSystemFracWET, Common_InputFunctions.Utility_LookupValueInTableNumber(_xlpm.ProductionSystem, _xlpm.ProductionSystemLookup, _xlpm.ProductionSystemFracWETLookup), IF(_xlpm.LeachingZoneFracWET + _xlpm.ProductionSystemFracWET &gt; 0, 1, 0)))</definedName>
     <definedName name="Common_InputFunctions.getOverlappingReportingCycles">_xlfn.LAMBDA(_xlpm.ProductionCycleStart,_xlpm.ProductionCycleEnd,_xlpm.ReportingCycleStart, _xlfn.LET(_xlpm.S, _xlpm.ProductionCycleStart, _xlpm.E, _xlpm.ProductionCycleEnd, _xlpm.m, MONTH(_xlpm.ReportingCycleStart), _xlpm.d, DAY(_xlpm.ReportingCycleStart), _xlpm.PeriodEnd, _xlfn.LAMBDA(_xlpm.st, EDATE(_xlpm.st, 12) - 1), _xlpm.A, _xlpm.S - 365, _xlpm.ya, YEAR(_xlpm.A), _xlpm.yb, YEAR(_xlpm.E), _xlpm.firstYear, _xlpm.ya + (_xlpm.PeriodEnd(DATE(_xlpm.ya, _xlpm.m, _xlpm.d)) &lt; _xlpm.S), _xlpm.lastYear, _xlpm.yb - (DATE(_xlpm.yb, _xlpm.m, _xlpm.d) &gt; _xlpm.E), MAX(0, _xlpm.lastYear - _xlpm.firstYear + 1)))</definedName>
     <definedName name="Common_InputFunctions.getOverlappingReportingPeriods">_xlfn.LAMBDA(_xlpm.ProductionCycleStart,_xlpm.ProductionCycleEnd,_xlpm.ReportingCycleStart, _xlfn.LET(_xlpm.S, _xlpm.ProductionCycleStart, _xlpm.E, _xlpm.ProductionCycleEnd, _xlpm.m, MONTH(_xlpm.ReportingCycleStart), _xlpm.d, DAY(_xlpm.ReportingCycleStart), _xlpm.PeriodEnd, _xlfn.LAMBDA(_xlpm.st, EDATE(_xlpm.st, 12) - 1), _xlpm.A, _xlpm.S - 365, _xlpm.ya, YEAR(_xlpm.A), _xlpm.yb, YEAR(_xlpm.E), _xlpm.firstYear, _xlpm.ya + (_xlpm.PeriodEnd(DATE(_xlpm.ya, _xlpm.m, _xlpm.d)) &lt; _xlpm.S), _xlpm.lastYear, _xlpm.yb - (DATE(_xlpm.yb, _xlpm.m, _xlpm.d) &gt; _xlpm.E), _xlpm.n, MAX(0, _xlpm.lastYear - _xlpm.firstYear + 1), _xlpm.yrs, _xlfn.SEQUENCE(_xlpm.n, 1, _xlpm.firstYear, 1), _xlpm.starts, DATE(_xlpm.yrs, _xlpm.m, _xlpm.d), _xlpm.ends, _xlfn.MAP(_xlpm.starts, _xlpm.PeriodEnd), _xlpm.tag, IF(_xlpm.starts = _xlpm.ReportingCycleStart, " (This reporting cycle)", ""), _xlpm.startsText, TEXT(_xlpm.starts, "dd mmm yyyy"), _xlpm.endsText, TEXT(_xlpm.ends, "dd mmm yyyy"), IF(_xlpm.n = 0, "", _xlfn.HSTACK(_xlpm.startsText &amp; " to " &amp; _xlpm.endsText &amp; _xlpm.tag))))</definedName>
@@ -56,9 +66,28 @@
     <definedName name="Common_InputFunctions.Utility_LookupN2OEFFromProdIrrigationRainfall">_xlfn.LAMBDA(_xlpm.ProductionSystem,_xlpm.IrrigationMethod,_xlpm.RainfallZone,_xlpm.ProductionSystemArray,_xlpm.IrrigationMethodArray,_xlpm.RainfallZoneArray,_xlpm.ReturnArray, _xlfn.LET(_xlpm.IrrigationMethod, IF(_xlpm.IrrigationMethod = "Not irrigated", "Not irrigated", "Any"), _xlpm.RainfallZone, IF(_xlpm.IrrigationMethod = "Not irrigated", _xlpm.RainfallZone, "Any"), _xlfn.XLOOKUP(1, (_xlpm.ProductionSystemArray = _xlpm.ProductionSystem) * (_xlpm.IrrigationMethodArray = _xlpm.IrrigationMethod) * (_xlpm.RainfallZoneArray = _xlpm.RainfallZone), _xlpm.ReturnArray)))</definedName>
     <definedName name="Common_InputFunctions.Utility_LookupValueInTable">_xlfn.LAMBDA(_xlpm.LookupValue,_xlpm.LookupArray,_xlpm.ReturnArray, _xlfn.XLOOKUP(_xlpm.LookupValue, _xlpm.LookupArray, _xlpm.ReturnArray, ""))</definedName>
     <definedName name="Common_InputFunctions.Utility_LookupValueInTableNumber">_xlfn.LAMBDA(_xlpm.LookupValue,_xlpm.LookupArray,_xlpm.ReturnArray, IF(ISNUMBER(_xlfn.XLOOKUP(_xlpm.LookupValue, _xlpm.LookupArray, _xlpm.ReturnArray, "")), _xlfn.XLOOKUP(_xlpm.LookupValue, _xlpm.LookupArray, _xlpm.ReturnArray, ""), 0))</definedName>
-    <definedName name="Common_InputFunctions.Utility_LookupValueInTableOneColumnAndHeader">_xlfn.LAMBDA(_xlpm.LookupValue1,_xlpm.LookupValue2,_xlpm.LookupArray1,_xlpm.LookupArray2,_xlpm.ReturnArray, _xlfn.XLOOKUP(_xlpm.LookupValue1, _xlpm.LookupArray1, _xlfn.XLOOKUP(_xlpm.LookupValue2, _xlpm.LookupArray2, _xlpm.ReturnArray)))</definedName>
-    <definedName name="Common_InputFunctions.Utility_LookupValueInTableTwoColumns">_xlfn.LAMBDA(_xlpm.LookupValue1,_xlpm.LookupValue2,_xlpm.LookupArray1,_xlpm.LookupArray2,_xlpm.ReturnArray, _xlfn.XLOOKUP(1, (_xlpm.LookupArray1 = _xlpm.LookupValue1) * (_xlpm.LookupArray2 = _xlpm.LookupValue2), _xlpm.ReturnArray, ""))</definedName>
+    <definedName name="Common_InputFunctions.Utility_LookupValueInTableOneColumnAndHeader">_xlfn.LAMBDA(_xlpm.LookupValue1,_xlpm.LookupValue2,_xlpm.LookupArray1,_xlpm.LookupArray2,_xlpm.ReturnArray,_xlop.ValueIfFalse,
+    IFERROR(
+        _xlfn.XLOOKUP(_xlpm.LookupValue1, _xlpm.LookupArray1,
+            _xlfn.XLOOKUP(_xlpm.LookupValue2, _xlpm.LookupArray2, _xlpm.ReturnArray)
+        ),
+        IF(_xlfn.ISOMITTED(_xlpm.ValueIfFalse), "", _xlpm.ValueIfFalse)
+    )
+)</definedName>
+    <definedName name="Common_InputFunctions.Utility_LookupValueInTableTwoColumns">_xlfn.LAMBDA(_xlpm.LookupValue1,_xlpm.LookupValue2,_xlpm.LookupArray1,_xlpm.LookupArray2,_xlpm.ReturnArray,_xlop.ValueIFFalse,
+    _xlfn.XLOOKUP(1, (_xlpm.LookupArray1=_xlpm.LookupValue1)*(_xlpm.LookupArray2=_xlpm.LookupValue2), _xlpm.ReturnArray, IF(_xlfn.ISOMITTED(_xlpm.ValueIFFalse), "", _xlpm.ValueIFFalse))
+)</definedName>
+    <definedName name="Common_InputFunctions.Utility_ResultsItemFromEquationTitleAndSource">_xlfn.LAMBDA(_xlpm.TitleCell,_xlpm.SourceCell,
+    SUBSTITUTE(LEFT(_xlpm.SourceCell, FIND(",", _xlpm.SourceCell) -1), "VEERG 2026: ", "") &amp; " " &amp; _xlpm.TitleCell
+)</definedName>
     <definedName name="Common_InputFunctions.Utility_SourceHyperlink">_xlfn.LAMBDA(_xlpm.TargetCell, _xlfn.LET(_xlpm.sh, _xlfn.TEXTAFTER(CELL("filename", _xlpm.TargetCell), "]"), _xlpm.addr, CELL("address", _xlpm.TargetCell), "#'" &amp; _xlpm.sh &amp; "'!" &amp; _xlpm.addr))</definedName>
+    <definedName name="Common_InputFunctions.Utility_SourceHyperlinkDifferentSheet">_xlfn.LAMBDA(_xlpm.TargetCell,
+  _xlfn.LET(
+    _xlpm.sh, _xlfn.TEXTAFTER(CELL("filename", _xlpm.TargetCell), "]"),
+    _xlpm.addr, CELL("address", _xlpm.TargetCell),
+    "#" &amp; _xlpm.addr
+  )
+)</definedName>
     <definedName name="Common_InputFunctions.Utility_SplitStringIntoArray">_xlfn.LAMBDA(_xlpm.Cell,_xlpm.Delimiter,_xlop.CharacterToRemove1,_xlop.CharacterToRemove2, _xlfn.FILTERXML("&lt;t&gt;&lt;s&gt;" &amp; SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.Cell, _xlpm.CharacterToRemove1, ""), _xlpm.CharacterToRemove2, ""), _xlpm.Delimiter, "&lt;/s&gt;&lt;s&gt;") &amp; "&lt;/s&gt;&lt;/t&gt;", "//s"))</definedName>
     <definedName name="Common_InputFunctions.Utility_SumQuantityFromCriteria">_xlfn.LAMBDA(_xlpm.Criteria1,_xlpm.Criteria1TypeArray,_xlpm.Quantity,_xlop.Multiplier,_xlop.Criteria2,_xlop.Criteria2Array, _xlfn.LET(_xlpm.multiplier, IF(_xlfn.ISOMITTED(_xlpm.Multiplier), 1, _xlpm.Multiplier), _xlpm.quantity, _xlpm.Quantity * _xlpm.multiplier, _xlpm.criteria1, --(_xlpm.Criteria1TypeArray = _xlpm.Criteria1), _xlpm.criteria2, IF(_xlfn.ISOMITTED(_xlpm.Criteria2), 1, --(_xlpm.Criteria2Array = _xlpm.Criteria2)), SUMPRODUCT(_xlpm.criteria1 * _xlpm.criteria2 * _xlpm.quantity)))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(9, 3, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"State/Territory","Common Name","Abbreviation";"New South Wales","New South Wales","NSW";"Australian Capital Territory","ACT","ACT";"Victoria","Victoria","VIC";"Queensland","Queensland","QLD";"South Australia","South Australia","SA";"Western Australia","Western Australia","WA";"Tasmania","Tasmania","TAS";"Northern Territory","Northern Territory","NT"}, _xlpm.r, _xlpm.c))))</definedName>
@@ -5344,7 +5373,7 @@
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{8D6029C1-B08F-4B80-A995-B6C014F37307}" name="Table_SourceData_RainfallZones" displayName="Table_SourceData_RainfallZones" ref="D119:G121" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="27" xr:uid="{85309467-765B-4B94-8584-08DA6915B57D}" name="Table_SourceData_RainfallZones" displayName="Table_SourceData_RainfallZones" ref="D119:G121" totalsRowShown="0">
   <autoFilter ref="D119:G121" xr:uid="{E08772F3-2E8C-40A8-B755-08A5BBDF4130}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -5352,16 +5381,16 @@
     <filterColumn colId="3" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{5CE8C325-C380-4784-A602-47123F36EF5C}" name="Rainfall Zone">
+    <tableColumn id="1" xr3:uid="{8471FF18-87B1-48D8-B4B5-5A60B311127B}" name="Rainfall Zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{25028200-89C9-46AE-8B23-93D29CCACEF2}" name="Annual rainfall">
+    <tableColumn id="2" xr3:uid="{D28DC9EE-82D3-4672-A649-FC74C1256A4D}" name="Annual rainfall">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{BC302063-B300-4BE0-A8DD-DD8C4B1F21FD}" name="Min rainfall">
+    <tableColumn id="3" xr3:uid="{864292BE-FF8A-4034-BEB8-594E669F7D72}" name="Min rainfall">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{55BED667-88E3-463B-8AFF-4A641BA5DF88}" name="Max rainfall">
+    <tableColumn id="4" xr3:uid="{9B41CF01-C2D0-4168-A3CC-D6EE46CFE082}" name="Max rainfall">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5370,16 +5399,16 @@
 </file>
 
 <file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{4BF50408-A854-4EF4-8E68-A080A9C0D658}" name="Table_SourceData_LeachingZones" displayName="Table_SourceData_LeachingZones" ref="D127:E129" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="28" xr:uid="{43C23522-9E9D-44F8-8336-C06AF43B79CA}" name="Table_SourceData_LeachingZones" displayName="Table_SourceData_LeachingZones" ref="D127:E129" totalsRowShown="0">
   <autoFilter ref="D127:E129" xr:uid="{A159E140-02ED-4547-B6E1-6695D8B16A11}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{56109D87-DD06-40E8-858E-A98E14F2505A}" name="Leaching Zone">
+    <tableColumn id="1" xr3:uid="{08922A4B-9C89-46CA-8E64-8BD8B7E28956}" name="Leaching Zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_LeachingZones_Data(), Table_SourceData_LeachingZones[[#Headers],[Leaching Zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{DC0D3050-4F7E-43AE-AC42-89AB2C82A6D0}" name="Leaching criteria">
+    <tableColumn id="2" xr3:uid="{FB5AAD60-432B-40CF-9A10-32A95B59991C}" name="Leaching criteria">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_LeachingZones_Data(), Table_SourceData_LeachingZones[[#Headers],[Leaching Zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5388,16 +5417,16 @@
 </file>
 
 <file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="14" xr:uid="{261B593E-497B-4BEF-9B69-2007BDE64FE1}" name="Table_SourceData_DataScores_Scope3" displayName="Table_SourceData_DataScores_Scope3" ref="D153:E158" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="29" xr:uid="{7A615DB4-CDA2-43C7-8BBD-245FE9C24A32}" name="Table_SourceData_DataScores_Scope3" displayName="Table_SourceData_DataScores_Scope3" ref="D153:E158" totalsRowShown="0">
   <autoFilter ref="D153:E158" xr:uid="{133D42B0-F6D2-470A-858A-37E6A7F5EC2B}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{C1EE8A11-4C9E-4966-A5C3-26B37DE11981}" name="Data source">
+    <tableColumn id="1" xr3:uid="{51090E5A-1810-49EB-BCFC-D8A93F1B5BB7}" name="Data source">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{E2FB9D2B-C748-4304-9DFD-C036ADBC0CC4}" name="Data score">
+    <tableColumn id="2" xr3:uid="{549056A9-6139-4141-8419-133BF7F0CB03}" name="Data score">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5406,16 +5435,16 @@
 </file>
 
 <file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{BF469EB8-2588-4054-B098-A53F3E410858}" name="Table_SourceData_FracWET" displayName="Table_SourceData_FracWET" ref="D134:E136" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="30" xr:uid="{7F96C5B8-244B-4352-9A57-A52F72FEF06D}" name="Table_SourceData_FracWET" displayName="Table_SourceData_FracWET" ref="D134:E136" totalsRowShown="0">
   <autoFilter ref="D134:E136" xr:uid="{308E99BE-FE1F-47A4-B2CA-97217277C4E9}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{F6AC79CD-A94F-48C7-A176-2A272B85F3D0}" name="Is in leaching zone">
+    <tableColumn id="1" xr3:uid="{4C4A6D74-20F8-4403-8C9B-E918177D37BA}" name="Is in leaching zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWET_Data(),Table_SourceData_FracWET[[#Headers],[Is in leaching zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{6170DAC4-0744-47E0-AAD9-DAC43CFE5AB9}" name="FracWET" dataDxfId="19">
+    <tableColumn id="2" xr3:uid="{927B7BBA-6E6F-4B41-AD64-57BC67EADAF2}" name="FracWET" dataDxfId="19">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWET_Data(),Table_SourceData_FracWET[[#Headers],[Is in leaching zone]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5424,7 +5453,7 @@
 </file>
 
 <file path=xl/tables/table14.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="16" xr:uid="{4305B1C9-19CD-4B8D-8B96-79A2D8536944}" name="Table_SourceData_Common_EFN2O" displayName="Table_SourceData_Common_EFN2O" ref="D186:H199" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="31" xr:uid="{7735D655-506C-4162-9223-8CDD640948F7}" name="Table_SourceData_Common_EFN2O" displayName="Table_SourceData_Common_EFN2O" ref="D186:H199" totalsRowShown="0">
   <autoFilter ref="D186:H199" xr:uid="{D41FBEA4-8379-4DF7-A068-BF94D364F1A2}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -5433,19 +5462,19 @@
     <filterColumn colId="4" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{58415BDE-7033-4D41-99CD-E1505A0958DA}" name="Production system j">
+    <tableColumn id="1" xr3:uid="{83A924E3-84DE-4BF7-9397-70DCCDC92771}" name="Production system j">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{AD2AE3C7-1D5D-466B-8F40-4456DF3CEC0C}" name="EFN2O">
+    <tableColumn id="2" xr3:uid="{7CCE1CE0-3549-410F-B6C6-6B4D834CE41D}" name="EFN2O">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{4E9D6B84-0855-4CD0-B792-D0F042A170D0}" name="Production system only">
+    <tableColumn id="3" xr3:uid="{A161BDA7-827E-4EE1-8909-FCCDD5EED965}" name="Production system only">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{0566DB93-5A8E-4AE3-BF74-80208370D941}" name="Irrigation method">
+    <tableColumn id="4" xr3:uid="{31CE4569-521F-4634-B509-10F42D229D26}" name="Irrigation method">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{19F4D5C9-3BED-4B10-BF43-4F3062FFD290}" name="Rainfall zone">
+    <tableColumn id="5" xr3:uid="{8AA2CDF3-F5D4-4178-9C99-A5971CE8024F}" name="Rainfall zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5454,16 +5483,16 @@
 </file>
 
 <file path=xl/tables/table15.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="17" xr:uid="{FAB45731-39BC-4119-AF44-EDC8FB1709F6}" name="Table_SourceData_FracWETIrrigation" displayName="Table_SourceData_FracWETIrrigation" ref="D142:E147" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="32" xr:uid="{030651BA-F6AA-4CD5-8D87-D6B68CD9E569}" name="Table_SourceData_FracWETIrrigation" displayName="Table_SourceData_FracWETIrrigation" ref="D142:E147" totalsRowShown="0">
   <autoFilter ref="D142:E147" xr:uid="{1F48CA34-50DE-46D5-B32A-BB3A1E818E37}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{ECA1D689-15C8-4240-AF0B-2339B2505350}" name="Irrigation type i">
+    <tableColumn id="1" xr3:uid="{3FEE1AC2-D8BF-439B-929A-0E1A17D616BC}" name="Irrigation type i">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{63F443AA-AF92-4972-9A43-28DD5303AB7A}" name="FracWET" dataDxfId="18" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{F4A9A605-754F-427A-A047-09B491F3E3F3}" name="FracWET" dataDxfId="18" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5472,16 +5501,16 @@
 </file>
 
 <file path=xl/tables/table16.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="18" xr:uid="{371B522F-917F-4ACD-9458-69FC198B61EC}" name="Table_SourceData_EFPastureRangeAndPaddock" displayName="Table_SourceData_EFPastureRangeAndPaddock" ref="D206:E208" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="33" xr:uid="{C85E657B-A70C-4772-935F-B3FE5750BB5C}" name="Table_SourceData_EFPastureRangeAndPaddock" displayName="Table_SourceData_EFPastureRangeAndPaddock" ref="D206:E208" totalsRowShown="0">
   <autoFilter ref="D206:E208" xr:uid="{D5BE3F89-D70E-4C53-A71C-E756622DEF38}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{57BA94E0-4353-4531-A9B7-0BD09C2F39A5}" name="Climate zone">
+    <tableColumn id="1" xr3:uid="{E3B9452A-0D0D-4336-B1FA-9B49DEDEB1A1}" name="Climate zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data(), Table_SourceData_EFPastureRangeAndPaddock[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{ECF28C34-784F-4443-AC3F-91CC4B569429}" name="EFPRP" dataDxfId="17" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{851858C8-5465-42EA-84B8-B18B16187376}" name="EFPRP" dataDxfId="17" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data(), Table_SourceData_EFPastureRangeAndPaddock[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5490,16 +5519,16 @@
 </file>
 
 <file path=xl/tables/table17.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="19" xr:uid="{369329C8-DB8D-4D0E-9B06-EFA978CF5551}" name="Table_SourceData_Common_MonthToSeason" displayName="Table_SourceData_Common_MonthToSeason" ref="D212:E224" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="34" xr:uid="{D8A1032A-4E0E-4678-BF62-41AFAC385695}" name="Table_SourceData_Common_MonthToSeason" displayName="Table_SourceData_Common_MonthToSeason" ref="D212:E224" totalsRowShown="0">
   <autoFilter ref="D212:E224" xr:uid="{97796C3A-D95E-4077-AA20-A8FE4145DAAD}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{7BBAB911-7034-463A-A259-26F762291EFF}" name="Month">
+    <tableColumn id="1" xr3:uid="{BEC06FF8-9F42-4E82-A71A-B23978FE85F4}" name="Month">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{852E648F-5F9C-46FA-9908-6794C77296AF}" name="Season" dataDxfId="16" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{4DE004E1-7EB7-43F1-A618-7C4A35E7ECA2}" name="Season" dataDxfId="16" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5508,7 +5537,7 @@
 </file>
 
 <file path=xl/tables/table18.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="20" xr:uid="{1CD7F9BA-A860-4D13-96A5-D248791B9E7B}" name="Table_SourceData_Common_MCFTemperatureZone" displayName="Table_SourceData_Common_MCFTemperatureZone" ref="D231:S250" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="35" xr:uid="{2A03D208-CF3E-4849-A4DA-23BC9B58A689}" name="Table_SourceData_Common_MCFTemperatureZone" displayName="Table_SourceData_Common_MCFTemperatureZone" ref="D231:S250" totalsRowShown="0">
   <autoFilter ref="D231:S250" xr:uid="{1D72DD9B-C8FA-48F4-9A11-20231FF87B5A}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -5528,52 +5557,52 @@
     <filterColumn colId="15" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="16">
-    <tableColumn id="1" xr3:uid="{201D8979-FF7C-453A-B667-199024E2B34C}" name="Temperature zone">
+    <tableColumn id="1" xr3:uid="{C7BD02DD-8DF0-4ECB-9857-A00B6832CB61}" name="Temperature zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{4D1AC02F-8E82-4509-89B1-2716B66F0486}" name="MAT (ºC)" dataDxfId="15" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{8D59A1CA-957C-484C-85EF-53E72157ED2C}" name="MAT (ºC)" dataDxfId="15" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{3E8ABD04-AEA1-4D47-BC62-EFBF6C896BB6}" name="Anaerobic lagoon" dataDxfId="14" dataCellStyle="Content normal">
+    <tableColumn id="3" xr3:uid="{B04462D2-A921-430A-A3AE-13A509AA54C9}" name="Anaerobic lagoon" dataDxfId="14" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{80DBE677-B4C3-417A-A665-EB564D28BB0D}" name="Digester / covered lagoons" dataDxfId="13" dataCellStyle="Content normal">
+    <tableColumn id="4" xr3:uid="{E402B89D-7F0C-472A-8E84-042EC8C1C51C}" name="Digester / covered lagoons" dataDxfId="13" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{19D86A12-CF53-41E1-91FC-BBFAE1337C22}" name="Liquid systems" dataDxfId="12" dataCellStyle="Content normal">
+    <tableColumn id="5" xr3:uid="{429746F9-9824-4163-85B6-802EBFF8CFED}" name="Liquid systems" dataDxfId="12" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{D8B7A5D5-4EE7-4138-B10E-8585772D484D}" name="Daily spread" dataDxfId="11" dataCellStyle="Content normal">
+    <tableColumn id="6" xr3:uid="{0843E2B1-6F87-447C-975B-C49E032B65D3}" name="Daily spread" dataDxfId="11" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{90823DD6-BAEF-4FF6-8B30-22943C6CDCF3}" name="Composting (passive windrow)" dataDxfId="10" dataCellStyle="Content normal">
+    <tableColumn id="7" xr3:uid="{B35124B8-74CB-4E5F-8FDC-0F88CB76089D}" name="Composting (passive windrow)" dataDxfId="10" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{6B7D7166-8E93-4AE1-B051-1F04B4681401}" name="Solid storage" dataDxfId="9" dataCellStyle="Content normal">
+    <tableColumn id="8" xr3:uid="{E4C1CED1-0ECF-4912-B899-53606483D342}" name="Solid storage" dataDxfId="9" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{DC1D60D4-29B5-471C-BAA2-3DEE5AAB8583}" name="Pit storage" dataDxfId="8" dataCellStyle="Content normal">
+    <tableColumn id="9" xr3:uid="{20289777-FA8F-4CE3-B2E0-F7AA23D7F743}" name="Pit storage" dataDxfId="8" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{41DACAC1-0D98-48B5-8460-B0116A3AF04F}" name="Deep litter" dataDxfId="7" dataCellStyle="Content normal">
+    <tableColumn id="10" xr3:uid="{472727FA-208E-45F1-BA53-9C6D68CA4B2A}" name="Deep litter" dataDxfId="7" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{BF6B9A03-9FD2-4ED4-84CB-31D1AF5E4C81}" name="Poultry manure with bedding" dataDxfId="6" dataCellStyle="Content normal">
+    <tableColumn id="11" xr3:uid="{16C38AB5-A1D4-4FE9-BE30-C422550C9606}" name="Poultry manure with bedding" dataDxfId="6" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{F8BEEA81-CBF5-4D71-919E-51AD5C895CCE}" name="Poultry manure without bedding" dataDxfId="5" dataCellStyle="Content normal">
+    <tableColumn id="12" xr3:uid="{7EABE97B-0FD8-48FD-8756-FE63185F4FDC}" name="Poultry manure without bedding" dataDxfId="5" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{72CF2D5A-601E-4D6E-A8F7-4E38EE26BEDD}" name="Direct processing" dataDxfId="4" dataCellStyle="Content normal">
+    <tableColumn id="13" xr3:uid="{AEEA4CDA-6757-4352-9233-5449A9598531}" name="Direct processing" dataDxfId="4" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{0FA785A1-F692-4116-B111-DF035FDAB2E0}" name="Direct application" dataDxfId="3" dataCellStyle="Content normal">
+    <tableColumn id="14" xr3:uid="{B618B227-3888-4E54-BA6B-9F6C4F1B1798}" name="Direct application" dataDxfId="3" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{CA3B68FC-2459-4B41-8FA5-89F71CACEA45}" name="Pasture range and paddock" dataDxfId="2" dataCellStyle="Content normal">
+    <tableColumn id="15" xr3:uid="{F3049CBE-13F5-4945-BB22-68A29336BC20}" name="Pasture range and paddock" dataDxfId="2" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{3CE97BDD-6B3C-444F-A89E-CBCF5BE8630A}" name="MAT raw" dataDxfId="1" dataCellStyle="Content normal">
+    <tableColumn id="16" xr3:uid="{C57331C5-698C-4B8E-BA8D-279F0612FD28}" name="MAT raw" dataDxfId="1" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5582,16 +5611,16 @@
 </file>
 
 <file path=xl/tables/table19.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="21" xr:uid="{2427E3FE-20C9-48BC-9900-B053F33E4DB1}" name="Table_SourceData_Common_EFOrganicFertCropResidues" displayName="Table_SourceData_Common_EFOrganicFertCropResidues" ref="D257:E259" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="36" xr:uid="{E36CDA43-E8DC-4ADE-9F8B-49C4D68A3FD1}" name="Table_SourceData_Common_EFOrganicFertCropResidues" displayName="Table_SourceData_Common_EFOrganicFertCropResidues" ref="D257:E259" totalsRowShown="0">
   <autoFilter ref="D257:E259" xr:uid="{56E01C14-1BB8-4015-9158-4CEB4D3B605C}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{81CD9500-E293-4F47-8F44-0A9637B40A71}" name="Climate Zone">
+    <tableColumn id="1" xr3:uid="{48E93F2D-D728-48B5-90C6-D582AA92CB40}" name="Climate Zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data(), Table_SourceData_Common_EFOrganicFertCropResidues[[#Headers],[Climate Zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{9498A226-47F2-4947-A630-33C016BE7207}" name="EFNi &amp; EFN2Oi" dataDxfId="0" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{9AF6E213-C0B8-4B2B-9BFC-25CD0D5E9A6E}" name="EFNi &amp; EFN2Oi" dataDxfId="0" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data(), Table_SourceData_Common_EFOrganicFertCropResidues[[#Headers],[Climate Zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5618,20 +5647,20 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1AA2A8B4-A80C-4AB2-BA43-6F04FDC3537D}" name="Table_AustralianStates" displayName="Table_AustralianStates" ref="D6:F14" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{24A8BF73-AB1F-4876-97DB-FB9A59CDC3B5}" name="Table_AustralianStates" displayName="Table_AustralianStates" ref="D6:F14" totalsRowShown="0">
   <autoFilter ref="D6:F14" xr:uid="{E0906749-7FC7-47DE-82F6-F796C4463018}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{1E459E17-570F-473A-8980-7B6D81D37E5B}" name="State/Territory">
+    <tableColumn id="1" xr3:uid="{D4E0E87C-74DB-459F-8D38-4A92FCFAF92C}" name="State/Territory">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{5A6E954E-3668-4779-A7E1-DEA029D5ABA5}" name="Common Name">
+    <tableColumn id="2" xr3:uid="{B0770D34-8F9E-4D6E-8ECE-07DD6443B418}" name="Common Name">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{4BDA8551-47F3-405A-BA82-AD4CBD4171A0}" name="Abbreviation">
+    <tableColumn id="3" xr3:uid="{2DF21ADF-7676-4B64-BA33-AC56F90712B0}" name="Abbreviation">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5640,12 +5669,12 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{FF0E4ED5-BF92-435A-81DD-28BC628CA69F}" name="Table_WASA4Areas" displayName="Table_WASA4Areas" ref="D20:D30" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{480028BA-C056-4027-A942-09366FE560EE}" name="Table_WASA4Areas" displayName="Table_WASA4Areas" ref="D20:D30" totalsRowShown="0">
   <autoFilter ref="D20:D30" xr:uid="{5FA81339-C6C8-4D36-BEEA-6C4AEDD9E676}">
     <filterColumn colId="0" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="1">
-    <tableColumn id="1" xr3:uid="{92D4788C-B668-4467-9E20-1F2C4ACA6AA0}" name="SA 4 Name">
+    <tableColumn id="1" xr3:uid="{EF471855-05EC-440A-91DB-3E6BF22DEC81}" name="SA 4 Name">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5654,16 +5683,16 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{4A342019-1CD6-43F1-9B8B-19844FB619F3}" name="Table_GWPData" displayName="Table_GWPData" ref="D36:E43" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="22" xr:uid="{F3C94305-F4C5-4CF3-852E-A0C29CC85D52}" name="Table_GWPData" displayName="Table_GWPData" ref="D36:E43" totalsRowShown="0">
   <autoFilter ref="D36:E43" xr:uid="{B8E87A66-3E41-4AD3-925D-01EE21B43D7A}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{FB490942-3D54-4BE0-91CA-449605238280}" name="Gas">
+    <tableColumn id="1" xr3:uid="{6BFDB535-1902-44B2-B400-CD82F7B55B30}" name="Gas">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{A459959B-FF39-40B6-B6DC-F2780A74EB69}" name="CO2-e factor">
+    <tableColumn id="2" xr3:uid="{4054A850-E3E9-4208-8F49-31B351D86D71}" name="CO2-e factor">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5672,7 +5701,7 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{A341AE40-1449-4647-BEF7-F9D3F0C9E643}" name="Table_GasToMolecularConversionFactor" displayName="Table_GasToMolecularConversionFactor" ref="D47:H54" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="23" xr:uid="{19FA6EFC-F767-4F03-9595-93D12005005E}" name="Table_GasToMolecularConversionFactor" displayName="Table_GasToMolecularConversionFactor" ref="D47:H54" totalsRowShown="0">
   <autoFilter ref="D47:H54" xr:uid="{C1F562BB-DAA6-45BB-951A-7BAFA5B64B45}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -5681,19 +5710,19 @@
     <filterColumn colId="4" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{C0DDF328-1BED-4360-BFEF-924C6AC4D82E}" name="Gas">
+    <tableColumn id="1" xr3:uid="{85D8FB12-91D1-4D75-8C29-81CF1719CF75}" name="Gas">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{BAB18FB3-08A2-4934-BB20-538BE79A7A18}" name="Conversion factor">
+    <tableColumn id="5" xr3:uid="{5B206A8A-A046-4E95-917C-8311C5D26F5E}" name="Conversion factor">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{4949AC83-09D6-4011-9029-279D974A3305}" name="Conversion factor 1">
+    <tableColumn id="2" xr3:uid="{6B8264DD-67B3-4A71-A211-02B91A63A08F}" name="Conversion factor 1">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{C76FA6ED-4341-46F9-BFED-7CBABCA64676}" name="Conversion factor 2">
+    <tableColumn id="3" xr3:uid="{CDCE3117-153C-4991-9DAB-F7B4917A0A5D}" name="Conversion factor 2">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{CDFDD25F-DED0-4488-B31E-82904829EBEA}" name="Conversion factor combined">
+    <tableColumn id="4" xr3:uid="{471CC504-21C3-4FAD-B783-C73055500CC3}" name="Conversion factor combined">
       <calculatedColumnFormula>Table_GasToMolecularConversionFactor[[#This Row],[Conversion factor 1]]/Table_GasToMolecularConversionFactor[[#This Row],[Conversion factor 2]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5702,7 +5731,7 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{4E3050EA-B79B-49D4-B5B9-D1A9CCC6CE93}" name="Table_SourceData_ClimateZones" displayName="Table_SourceData_ClimateZones" ref="D89:S97" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="24" xr:uid="{7A8A5644-FEF2-4F23-8350-4B25BF47833B}" name="Table_SourceData_ClimateZones" displayName="Table_SourceData_ClimateZones" ref="D89:S97" totalsRowShown="0">
   <autoFilter ref="D89:S97" xr:uid="{5A437AE9-7724-4CF2-ACCF-291078682FB9}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -5722,52 +5751,52 @@
     <filterColumn colId="15" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="16">
-    <tableColumn id="1" xr3:uid="{45884169-378B-4498-ADF1-E96DC5275FE2}" name="Climate zone" totalsRowCellStyle="Content bold">
+    <tableColumn id="1" xr3:uid="{6B79B743-50F4-4EF1-8356-AA9C4A60C2C7}" name="Climate zone" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{ED0A42F7-E0D4-42BC-9323-7AC1E8B79522}" name="MAT" totalsRowDxfId="35" totalsRowCellStyle="Content bold">
+    <tableColumn id="2" xr3:uid="{22AC2A8A-13C1-467A-8907-B685D3A9EB24}" name="MAT" totalsRowDxfId="35" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{622E8002-CAE7-49C2-9FFA-1A4BAFB06DFC}" name="MAP" totalsRowDxfId="34" totalsRowCellStyle="Content bold">
+    <tableColumn id="3" xr3:uid="{816D4DD7-7FBE-40DF-A5D0-A42A8D498973}" name="MAP" totalsRowDxfId="34" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{F8E36194-7A47-4596-B5DF-0A053B710457}" name="Frost days per year" totalsRowDxfId="33" totalsRowCellStyle="Content bold">
+    <tableColumn id="4" xr3:uid="{D88DB054-1FC7-49B8-A267-C1C7EFCDEB9E}" name="Frost days per year" totalsRowDxfId="33" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{EE33DF38-3BFD-4B2F-9290-9B33D7636732}" name="Elevation" totalsRowDxfId="32" totalsRowCellStyle="Content bold">
+    <tableColumn id="5" xr3:uid="{3B608F0C-BF5B-46D0-92FC-6F2B5D5BB1F9}" name="Elevation" totalsRowDxfId="32" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{DB707C1D-8B5A-40AE-B0CB-ACC5F5BAED97}" name="MAP:PET" totalsRowDxfId="31" totalsRowCellStyle="Content bold">
+    <tableColumn id="6" xr3:uid="{A01F1254-1B3D-4A35-8C85-F0536AF9024B}" name="MAP:PET" totalsRowDxfId="31" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{DAEF6587-4D6A-471A-B522-BF43D986CCE7}" name="Min temp" totalsRowDxfId="30" totalsRowCellStyle="Content bold">
+    <tableColumn id="7" xr3:uid="{29DCCB92-BB35-4455-9C8F-B0599D6F2CEC}" name="Min temp" totalsRowDxfId="30" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{A7A388B4-D412-4A7C-B6D2-34F31643DDE2}" name="Max temp" totalsRowDxfId="29" totalsRowCellStyle="Content bold">
+    <tableColumn id="8" xr3:uid="{BAF8145E-1292-4752-932A-83438A0D6A79}" name="Max temp" totalsRowDxfId="29" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{C7774772-3E03-4EC3-AC58-04273FF2770F}" name="Min rainfall" totalsRowDxfId="28" totalsRowCellStyle="Content bold">
+    <tableColumn id="9" xr3:uid="{E6848A1F-BC28-4BAD-98C5-84C27707488A}" name="Min rainfall" totalsRowDxfId="28" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{1C785463-634C-4A75-9E08-1460391DDE5F}" name="Max rainfall" totalsRowDxfId="27" totalsRowCellStyle="Content bold">
+    <tableColumn id="10" xr3:uid="{69FFF62D-4812-4984-9F65-DCB7BCD9A909}" name="Max rainfall" totalsRowDxfId="27" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{F5A7C9F9-EF30-4040-BC45-6B92F662AE9B}" name="Min frost days" totalsRowDxfId="26" totalsRowCellStyle="Content bold">
+    <tableColumn id="11" xr3:uid="{8312F0B7-9284-4CC8-9964-B19BC1F4AAA1}" name="Min frost days" totalsRowDxfId="26" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{F977A7B1-31AE-494D-974F-3D327EAFF2F3}" name="Max frost days" totalsRowDxfId="25" totalsRowCellStyle="Content bold">
+    <tableColumn id="15" xr3:uid="{1D3746FF-D9FF-45D2-8037-85C5F6D3AEC1}" name="Max frost days" totalsRowDxfId="25" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{1459972D-2D14-42EE-BC43-754376D25250}" name="Min elevation" totalsRowDxfId="24" totalsRowCellStyle="Content bold">
+    <tableColumn id="12" xr3:uid="{757AAC29-B4B9-421B-BF37-11A1F02960DB}" name="Min elevation" totalsRowDxfId="24" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{3AA61A84-02F5-46DD-A817-E0CDAFC9780D}" name="Max elevation" totalsRowDxfId="23" totalsRowCellStyle="Content bold">
+    <tableColumn id="16" xr3:uid="{F5F07B98-8F3B-43DE-8868-8B6521EE70BA}" name="Max elevation" totalsRowDxfId="23" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{C26C9901-FD25-4AAD-B733-940BFE803266}" name="Min MAP:PET" totalsRowDxfId="22" totalsRowCellStyle="Content bold">
+    <tableColumn id="13" xr3:uid="{54854D9D-3B0B-4FAC-911A-2F06DA7073DC}" name="Min MAP:PET" totalsRowDxfId="22" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{9A372779-77EF-4DB9-AB02-ECFD5B7D98D2}" name="Max MAP:PET" totalsRowDxfId="21" totalsRowCellStyle="Content bold">
+    <tableColumn id="17" xr3:uid="{1C1FDB01-8B0D-4AB2-B0BB-435B21235AF0}" name="Max MAP:PET" totalsRowDxfId="21" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5776,16 +5805,16 @@
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{47A643D6-250B-4288-95C7-D531914A05DD}" name="Table_SourceData_WetDryZones" displayName="Table_SourceData_WetDryZones" ref="D63:E77" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="25" xr:uid="{9AB30C9A-68A6-4E05-BD40-E763298777F3}" name="Table_SourceData_WetDryZones" displayName="Table_SourceData_WetDryZones" ref="D63:E77" totalsRowShown="0">
   <autoFilter ref="D63:E77" xr:uid="{3597E019-B21E-4B76-BCC8-D02D497BCFA9}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{4E9B4188-5808-495A-A79C-64E72C0B70A0}" name="Climate zone" totalsRowCellStyle="Content bold">
+    <tableColumn id="1" xr3:uid="{F23A3ECC-39D0-48A8-AA45-F9862E202457}" name="Climate zone" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{5CB38AB7-C02B-48C0-895B-24D1A618FE0B}" name="Wet or Dry Zone" totalsRowDxfId="20" totalsRowCellStyle="Content bold">
+    <tableColumn id="2" xr3:uid="{F9D975DC-0646-44FB-A9C6-DAC7D2D476C0}" name="Wet or Dry Zone" totalsRowDxfId="20" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5794,7 +5823,7 @@
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{B4DFA00C-D850-4006-8609-B45FCAAE779C}" name="Table_SourceData_TemperatureZones" displayName="Table_SourceData_TemperatureZones" ref="D109:G112" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="26" xr:uid="{F35FD7F6-BFEE-4A32-B504-C9C8FF8D143B}" name="Table_SourceData_TemperatureZones" displayName="Table_SourceData_TemperatureZones" ref="D109:G112" totalsRowShown="0">
   <autoFilter ref="D109:G112" xr:uid="{AB16FEAB-AB03-45E1-BBD4-66D29CD412DF}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -5802,16 +5831,16 @@
     <filterColumn colId="3" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{CD9A6B60-1C08-4D63-8066-1589EC35997E}" name="Temperature Zone">
+    <tableColumn id="1" xr3:uid="{673B00C1-3A07-4CF7-A093-491807F38D70}" name="Temperature Zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{83B2600F-93D9-4755-9041-01F6534CE049}" name="MAT">
+    <tableColumn id="2" xr3:uid="{48E05620-9CFF-45B1-8B9B-D606D44FA94F}" name="MAT">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{F49B0660-4DA0-4849-82F9-CF78D665A4FF}" name="Min MAT">
+    <tableColumn id="3" xr3:uid="{B1FD170D-4DF7-4386-BE47-2F44EA68243E}" name="Min MAT">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{208E1DC2-ECC8-450C-9EC7-877BF3C64AA8}" name="Max MAT">
+    <tableColumn id="4" xr3:uid="{FB1CD6A0-82C1-4157-B50D-DA3E1C3D1988}" name="Max MAT">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -9790,7 +9819,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04C6ACEF-654B-46AE-A369-1B5BAE8FE3CB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C01035A7-00F4-4A58-AF60-DFD77BBE8707}">
   <dimension ref="A1:BY259"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
@@ -13782,17 +13811,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="09eef6d6-daa8-4301-8f9f-b1ec38079286" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7291119c-fce9-4911-96ae-b800be5dccd8">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -13801,7 +13819,7 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100ACB660BB23738846A00119B5826AC974" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3e3613359d4ae7f6bda6c57be713f101">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="7291119c-fce9-4911-96ae-b800be5dccd8" xmlns:ns3="09eef6d6-daa8-4301-8f9f-b1ec38079286" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="87491bfad7f11426ad96486e70428b3e" ns2:_="" ns3:_="">
     <xsd:import namespace="7291119c-fce9-4911-96ae-b800be5dccd8"/>
@@ -13996,22 +14014,22 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgAvAC8AIAAtAC0ALQAgAFcAbwByAGsAYgBvAG8AawAgAG0AbwBkAHUAbABlACAALQAtAC0AXABuAC8ALwAgAEEAIABmAGkAbABlACAAbwBmACAAbgBhAG0AZQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAG8AZgAgAHQAaABlACAAZgBvAHIAbQA6AFwAbgAvAC8AIAAgACAAIABuAGEAbQBlACAAPQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AOwBcAG4AXABuACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhACIALAAiAHQAZQB4AHQAIgA6ACIALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgBTAG8AdQByAGMAZQAgAGQAYQB0AGEAIAB0AGgAYQB0ACAAaQBzACAAYwBvAG0AbQBvAG4AIABhAGMAcgBvAHMAcwAgAGEAbABsACAAZQBuAHQAZQByAHAAcgBpAHMAZQAgAHQAeQBwAGUAcwBcAG4ARQB4AGMAZQBsACAAbQBvAGQAdQBsAGUAIABuAGEAbQBlADoAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFMAbwB1AHIAYwBlADoAIABOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQBcAG4ATgBJAFIAXwAyADAAMgAzAF8AVgBvAGwAMQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXABuAHAAIAA9ACAAZABlAG4AcwBpAHQAeQAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAIAAoADAALgA2ADcAOAA0ACAAawBnAC8AbQAzACkAXABuAFQAYQBrAGUAbgAgAGYAcgBvAG0AIAB0AGgAZQAgAE4AYQB0AGkAbwBuAGEAbAAgAEcAcgBlAGUAbgBoAG8AdQBzAGUAIABhAG4AZAAgAEUAbgBlAHIAZwB5ACAAUgBlAHAAbwByAHQAaQBuAGcAIABcAG4AKABNAGUAYQBzAHUAcgBlAG0AZQBuAHQAKQAgAEQAZQB0AGUAcgBtAGkAbgBhAHQAaQBvAG4AIAAyADAAMAA4AFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHAAIAA9ACAAZABlAG4AcwBpAHQAeQAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcALwBtADMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgADIAMAAyADMAIABWAG8AbAB1AG0AZQAgADEAOgAgAEUAcQB1AGEAdABpAG8AbgBzACAAMwAuAEIALgAxAGEAXwAyACwAIAAzAC4AQgAuADEAYwBfADIALAAgADMALgBCAC4AMwBfADEALAAgADMALgBCAC4ANABnAF8AMgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAMAAuADYANwA4ADQAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAFwAbgBDAGcAIAA9ACAANAA0AC8AMgA4ACAAZgBhAGMAdABvAHIAIAB0AG8AIABjAG8AbgB2AGUAcgB0ACAAZQBsAGUAbQBlAG4AdABhAGwAIABtAGEAcwBzACAAbwBmACAATgAyAE8AIAB0AG8AIABtAG8AbABlAGMAdQBsAGEAcgAgAG0AYQBzAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABOADIATwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBDAGcATgAyAE8AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAYQBjAHQAbwByAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgADIAMAAyADMAIABWAG8AbAB1AG0AZQAgADEAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgANAA0AC8AMgA4ACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAFwAbgBGAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABnAGEAcwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgBhAGMAdABvAHIAIAB0AG8AIABjAG8AbgB2AGUAcgB0ACAAZQBsAGUAbQBlAG4AdABhAGwAIABtAGEAcwBzACAAbwBmACAAZwBhAHMAIAB0AG8AIABtAG8AbABlAGMAdQBsAGEAcgAgAG0AYQBzAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBDAGcAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgBhAGMAdABvAHIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFgAWABYAFgAWABYAFgAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADgALAAgADQALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAYQBzAFwAIgAsACAAXAAiAEMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBcACIALAAgAFwAIgBDAG8AbgB2AGUAcgBzAGkAbwBuACAAZgBhAGMAdABvAHIAIAAxAFwAIgAsACAAXAAiAEMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgADIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyAFwAIgAsACAAXAAiADQANAAvADEAMgBcACIALAAgADQANAAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMASAA0AFwAIgAsACAAXAAiADEANgAvADEAMgBcACIALAAgADEANgAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AMgBPAFwAIgAsACAAXAAiADQANAAvADIAOABcACIALAAgADQANAAsACAAMgA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB4AFwAIgAsACAAXAAiADQANgAvADEANABcACIALAAgADQANgAsACAAMQA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwBcACIALAAgAFwAIgAyADgALwAxADIAXAAiACwAIAAyADgALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAE8AMgAgAEwAaQBtAGUAXAAiACwAIABcACIANAA0AC8AMQAyAFwAIgAsACAANAA0ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBNAFYATwBDAFwAIgAsACAAXAAiADEANAAvADEAMgBcACIALAAgADEANAAsACAAMQAyAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABOADIATwBcAG4ARwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAGcAcgBlAGUAbgBoAG8AdQBzAGUAIABnAGEAcwBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABnAHIAZQBlAG4AaABvAHUAcwBlACAAZwBhAHMAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARwBXAFAATgAyAE8AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgBhAGMAdABvAHIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFgAWABYAFgAWABYAFgAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADgALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAYQBzAFwAIgAsACAAXAAiAEMATwAyAC0AZQAgAGYAYQBjAHQAbwByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAE8AMgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBIADQAXAAiACwAIAAyADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgAyAE8AXAAiACwAIAAyADYANQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAEYANABcACIALAAgADYANgAzADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwAyAEYANgBcACIALAAgADEAMgAyADAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAEYANgBcACIALAAgADIAMgA4ADAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAEYAMwBcACIALAAgADEANwAyADAAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAcwB0AGEAdABlAHMAIABhAG4AZAAgAHQAZQByAHIAaQB0AG8AcgBpAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA5ACwAIAAzACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHQAYQB0AGUALwBUAGUAcgByAGkAdABvAHIAeQBcACIALAAgAFwAIgBDAG8AbQBtAG8AbgAgAE4AYQBtAGUAXAAiACwAIABcACIAQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AZQB3ACAAUwBvAHUAdABoACAAVwBhAGwAZQBzAFwAIgAsACAAXAAiAE4AZQB3ACAAUwBvAHUAdABoACAAVwBhAGwAZQBzAFwAIgAsACAAXAAiAE4AUwBXAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAQwBhAHAAaQB0AGEAbAAgAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAEEAQwBUAFwAIgAsACAAXAAiAEEAQwBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAGkAYwB0AG8AcgBpAGEAXAAiACwAIABcACIAVgBpAGMAdABvAHIAaQBhAFwAIgAsACAAXAAiAFYASQBDAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBRAHUAZQBlAG4AcwBsAGEAbgBkAFwAIgAsACAAXAAiAFEAdQBlAGUAbgBzAGwAYQBuAGQAXAAiACwAIABcACIAUQBMAEQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAbwB1AHQAaAAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFMAbwB1AHQAaAAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFMAQQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQBcACIALAAgAFwAIgBXAEEAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAYQBzAG0AYQBuAGkAYQBcACIALAAgAFwAIgBUAGEAcwBtAGEAbgBpAGEAXAAiACwAIABcACIAVABBAFMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwByAHQAaABlAHIAbgAgAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAE4AbwByAHQAaABlAHIAbgAgAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAE4AVABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQBCAFMAIABTAHQAYQB0AGkAcwB0AGMAYQBsACAAQQByAGUAYQBzACAATABlAHYAZQBsACAANAAgAC0AIABXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAEIAdQByAGUAYQB1ACAAbwBmACAAUwB0AGEAdABpAHMAdABpAGMAcwAgACgAQQBCAFMAKQAgAC0AIABTAHQAYQB0AGkAcwB0AGkAYwBhAGwAIABBAHIAZQBhAHMAIABMAGUAdgBlAGwAIAAyACAALQAgADIAMAAyADEAIAAtACAAUwBoAGEAcABlAGYAaQBsAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADEALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAQQAgADQAIABOAGEAbQBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBCAHUAbgBiAHUAcgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAGEAbgBkAHUAcgBhAGgAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABJAG4AbgBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABOAG8AcgB0AGgAIABFAGEAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAATgBvAHIAdABoACAAVwBlAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAFMAbwB1AHQAaAAgAEUAYQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABTAG8AdQB0AGgAIABXAGUAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAAVwBoAGUAYQB0ACAAQgBlAGwAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhACAALQAgAE8AdQB0AGIAYQBjAGsAIAAoAE4AbwByAHQAaAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAATwB1AHQAYgBhAGMAawAgACgAUwBvAHUAdABoACkAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAdwBlAHQAIABhAG4AZAAgAGQAcgB5ACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAyADoAIABUAHIAYQBuAHMAbABhAHQAaQBuAGcAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBzACAAdABvACAAdwBlAHQAIABhAG4AZAAgAGQAcgB5ACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAdwBhAHIAbQAgAC8AIABjAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAvACAAZAByAHkAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAIABhAG4AZAAgAGgAaQBnAGgAIAB0AGUAbQBwACAAYwBsAGEAcwBzAGUAcwAgAHQAbwAgAGEAYwBjAG8AbQBtAG8AZABhAHQAZQAgAGMAbABpAG0AYQB0AGUAIABzAGMAZQBuAGEAcgBpAG8AcwAgAGUAeABjAGwAdQBkAGUAZAAgAGIAeQAgAFYARQBFAFIARwAgAGMAcgBpAHQAZQByAGkAYQAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAGkAeABlAGQAIAB0AHkAcABvACAALQAgAEMAaABhAG4AZwBlAGQAIABcAHUAMAAwADIANwBGAHIAeQBcAHUAMAAwADIANwAgAHQAbwAgAFwAdQAwADAAMgA3AEQAcgB5AFwAdQAwADAAMgA3AC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADUALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAFcAZQB0ACAAbwByACAARAByAHkAIABaAG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABtAG8AbgB0AGEAbgBlAFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAHcAZQB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABkAHIAeQBcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdABcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAtACAAaABpAGcAaAAgAHQAZQBtAHAAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAaABpAGcAaAAgAHQAZQBtAHAAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA1ACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAB3AGEAcgBtACAALwAgAGMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC8AIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdAAgAGEAbgBkACAAaABpAGcAaAAgAHQAZQBtAHAAIABjAGwAYQBzAHMAZQBzACAAdABvACAAYQBjAGMAbwBtAG0AbwBkAGEAdABlACAAYwBsAGkAbQBhAHQAZQAgAHMAYwBlAG4AYQByAGkAbwBzACAAZQB4AGMAbAB1AGQAZQBkACAAYgB5ACAAVgBFAEUAUgBHACAAYwByAGkAdABlAHIAaQBhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAaQB4AGUAZAAgAHQAeQBwAG8AIABpAG4AIABNAEEAVAAgAHYAYQBsAHUAZQAgAGYAbwByACAAdwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAYwBoAGEAbgBnAGUAZAAgADEAMAAgAHQAbwAgADEAMQAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIABtAGkAbgAgAGEAbgBkACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAZgBvAHIAIABNAEEAVAAsACAATQBBAFAALAAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAIABwAGUAcgAgAHkAZQBhAHIALAAgAGUAbABlAHYAYQB0AGkAbwBuACwAIABNAEEAUAA6AFAARQBUACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlAHMAIABmAHIAbwBtACAAcgBlAGEAbAAgAGMAbABpAG0AYQB0AGUAIABkAGEAdABhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAQQBGACAAYQBjAGMAZQBwAHQAcwAgAHIAYQBpAG4AZgBhAGwAbAAgAGEAcwAgAGEAIABwAHIAbwB4AHkAIABmAG8AcgAgAHAAcgBlAGMAaQBwAGkAdABhAHQAaQBvAG4ALgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOQAsACAAMQA2ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAGwAaQBtAGEAdABlACAAWgBvAG4AZQBcACIALAAgAFwAIgBNAEEAVABcACIALAAgAFwAIgBNAEEAUABcACIALAAgAFwAIgBGAHIAbwBzAHQAIABkAGEAeQBzACAAcABlAHIAIAB5AGUAYQByAFwAIgAsACAAXAAiAEUAbABlAHYAYQB0AGkAbwBuAFwAIgAsACAAXAAiAE0AQQBQADoAUABFAFQAXAAiACwAIABcACIATQBpAG4AIAB0AGUAbQBwAFwAIgAsACAAXAAiAE0AYQB4ACAAdABlAG0AcABcACIALAAgAFwAIgBNAGkAbgAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBNAGEAeAAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBNAGkAbgAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAXAAiACwAIABcACIATQBhAHgAIABmAHIAbwBzAHQAIABkAGEAeQBzAFwAIgAsACAAXAAiAE0AaQBuACAAZQBsAGUAdgBhAHQAaQBvAG4AXAAiACwAIABcACIATQBhAHgAIABlAGwAZQB2AGEAdABpAG8AbgBcACIALAAgAFwAIgBNAGkAbgAgAE0AQQBQADoAUABFAFQAXAAiACwAIABcACIATQBpAG4AIABNAEEAUAA6AFAARQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABtAG8AbgB0AGEAbgBlAFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQA4ACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAwADAAIABtAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAMQA4AC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAANwAsACAAMQAwADAAMAAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAHcAZQB0AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQA4ACAAQwBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADIAMAAwADAAIABtAG0AXAAiACwAIABcACIAZCIgADcAXAAiACwAIABcACIAZCIgADEAMAAwADAAIABtAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAMQA4AC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAyADAAMAAwAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQAuADkAOQA5ACwAIAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAOAAgAEMAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADAAMAAwACAAbQBtACAALQAgAGQiIAAyADAAMAAwACAAbQBtAFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgADEAOAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAAMQAwADAAMAAuADAAMAAxACwAIAAyADAAMAAwACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQAuADkAOQA5ACwAIAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAGQAcgB5AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQA4ACAAQwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAwADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAXAAiACwAIAAxADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgADEALgAwADAAMQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAGQiIAAxAFwAIgAsACAAMQAwAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAgAC0AOQA5ADkAOQA5ADkALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMAAgAEMAIAAtACAAZCIgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxAFwAIgAsACAALQA5ADkAOQA5ADkAOQAsACAAMQAwACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAxAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMAAgAEMAIAAtACAAZCIgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAZCIgADEAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAMQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBBAHAAcABlAG4AZABpAGMAZQBzAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdABlADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AQQBUACAAPQAgAG0AZQBhAG4AIABhAG4AbgB1AGEAbAAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBBAFAAIAA9ACAAbQBlAGEAbgAgAGEAbgBuAHUAYQBsACAAcAByAGUAYwBpAHAAaQB0AGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABFAFQAIAA9ACAAcABvAHQAZQBuAHQAaQBhAGwAIABlAHYAYQBwAG8AdAByAGEAbgBzAHAAaQByAGEAdABpAG8AbgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABBAGQAZABlAGQAIABlAHgAdAByAGEAIABNAEEAVAAgAG0AaQBuACAAYQBuAGQAIABNAEEAVAAgAG0AYQB4ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGMAYQBsAGMAdQBsAGEAdABlACAAegBvAG4AZQAgAGYAcgBvAG0AIAByAGUAYQBsACAAdABlAG0AcABlAHIAYQB0AHUAcgBlACAAZABhAHQAYQAuAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANAAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AHUAcgBlACAAWgBvAG4AZQBcACIALAAgAFwAIgBNAGUAZABpAGEAbgAgAEEAbgBuAHUAYQBsACAAVABlAG0AcABlAHIAYQB0AHUAcgBlACAAKABNAEEAVAApAFwAIgAsACAAXAAiAE0AaQBuACAATQBBAFQAXAAiACwAIABcACIATQBhAHgAIABNAEEAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgAFwAIgBlIiAAMgA2ACAAQwBcACIALAAgADIANgAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIABcACIAMQA1ACAALQAgADIANQAgAEMAXAAiACwAIAAxADUALAAgADIANQAuADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIABcACIAZCIgADEANAAgAEMAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADQALgA5ADkAOQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAAQQBkAGQAZQBkACAAZQB4AHQAcgBhACAAUgBhAGkAbgBmAGEAbABsACAAbQBpAG4AIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAG0AYQB4ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGMAYQBsAGMAdQBsAGEAdABlACAAegBvAG4AZQAgAGYAcgBvAG0AIAByAGUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAZABhAHQAYQAuAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBhAGkAbgBmAGEAbABsACAAWgBvAG4AZQBcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABtAGkAbgBcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABtAGEAeABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbAAgAFwAdQAwADAAMwBlACAANgAwADAAbQBtAFwAIgAsACAANgAwADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATABvAHcAIAByAGEAaQBuAGYAYQBsAGwAXAAiACwAIABcACIAQQBuAG4AdQBhAGwAIAByAGEAaQBuAGYAYQBsAGwAIABkIiAANgAwADAAbQBtAFwAIgAsACAALQA5ADkAOQA5ADkAOQAsACAANgAwADAAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABaAG8AbgBlAFwAIgAsACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAGMAcgBpAHQAZQByAGkAYQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATABlAGEAYwBoAGkAbgBnACAAbwBjAGMAdQByAHMAXAAiACwAIABcACIAowMoADXYX9w12E7cNdhW3DXYW9wpAFwAdQAwADAAMwBlAKMDKAA12DjcNdhH3DAAKQArADXYYNw12FzcNdhW3DXYWdwgADXYZNw12E7cNdhh3DXYUtw12F/cIAAOITXYXNw12FncNdhR3DXYVtw12FvcNdhU3CAANdhQ3DXYTtw12F3cNdhO3DXYUNw12FbcNdhh3DXYZtxcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATABlAGEAYwBoAGkAbgBnACAAZABvAGUAcwAgAG4AbwB0ACAAbwBjAGMAdQByAFwAIgAsACAAXAAiAKMDKAA12F/cNdhO3DXYVtw12FvcKQBkIqMDKAA12DjcNdhH3DAAKQArADXYYNw12FzcNdhW3DXYWdwgADXYZNw12E7cNdhh3DXYUtw12F/cIAAOITXYXNw12FncNdhR3DXYVtw12FvcNdhU3CAANdhQ3DXYTtw12F3cNdhO3DXYUNw12FbcNdhh3DXYZtxcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXABuADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAbgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAEQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcwAgAGkAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAXAAiACwAXAAiAEYAcgBhAGMAVwBFAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFkAZQBzACAALQAgAGkAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwAgAC0AIABuAG8AdAAgAGkAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAXAAiACwAIAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoACgAXAAiAFwAIgApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAGQAYQB0AGEAIABzAGMAbwByAGUAcwAgAGYAbwByACAAcwBjAG8AcABlACAAMwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABYAFgAWABYAFgAWABYAFgAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABhAHQAYQAgAHMAbwB1AHIAYwBlAFwAIgAsACAAXAAiAEQAYQB0AGEAIABzAGMAbwByAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAbgB0AGUAcgBuAGEAdABpAG8AbgBhAGwAIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAcwBjAG8AcABlACAAMwAgAGQAYQB0AGEAYgBhAHMAZQBcACIALAAgADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB0AGEAdABlACAAbwByACAAcgBlAGcAaQBvAG4AYQBsACAAcwBjAG8AcABlACAAMwAgAGQAYQB0AGEAYgBhAHMAZQBcACIALAAgADMAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBtAGkAcwBzAGkAbwBuAHMAIABpAG4AdABlAG4AcwBpAHQAeQAgAGMAYQBsAGMAdQBsAGEAdABlAGQAIABmAHIAbwBtACAAYQBwAHAAcgBvAHYAZQBkACAAbQBlAHQAaABvAGQAXAAiACwAIAA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAZQByAGkAZgBpAGUAZAAgAGMAcgBlAGQAZQBuAHQAaQBhAGwAIABtAGEAdABjAGgAaQBuAGcAIABJAFMATwAxADQAMAA2ADcAXAAiACwAIAA1AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXABuADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAbgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgARABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAVgBvAGwAdQBtAGUAIAAxADoAIABMAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmACAAKAAzAC4ARAAuAGIALgAyACkAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAcgBhAGMATABFAEEAQwBIAFwAIgAsADAALgAyADQAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoACgAXAAiAFwAIgApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABuAGkAdAByAG8AZwBlAG4AIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABuAGkAdAByAG8AZwBlAG4AIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABrAGcAIABOADIATwAtAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgAFYAbwBsAHUAbQBlACAAMQA6ACAARQBxAHUAYQB0AGkAbwBuACAAMwAuAEQALgBCAF8AMQAwAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARgBsAGUAYQBjAGgAXAAiACwAMAAuADAAMQAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoACgAXAAiAFwAIgApACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXABuAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADEAXABuAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAZgBvAHIAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AIAAoAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AKQAgACgARQBGAE4AMgBPACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAGYAbwByACAAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAGsAZwAgAE4AMgBPAC0ATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADIALgAyAC4AMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQA1ACwAIAA1ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABqAFwAIgAsAFwAIgBFAEYATgAyAE8AXAAiACwAIABcACIAUAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAbwBuAGwAeQBcACIALAAgAFwAIgBJAHIAcgBpAGcAYQB0AGkAbwBuACAAbQBlAHQAaABvAGQAXAAiACwAIABcACIAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsADAALgAwADAANQA5ACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwAFwAIgAsADAALgAwADAANwAsACAAXAAiAEMAcgBvAHAAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsADAALgAwADAAMQA4ACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEwAbwB3ACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQBcACIALAAwAC4AMAAwADEAOAAsACAAXAAiAFAAYQBzAHQAdQByAGUAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcAAgACgAbABvAHcAIAByAGEAaQBuAGYAYQBsAGwAKQBcACIALAAwAC4AMAAwADIAOQAsACAAXAAiAEMAcgBvAHAAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAGMAcgBvAHAAIAAoAGgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAKQBcACIALAAwAC4AMAAwADgALAAgAFwAIgBDAHIAbwBwAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIASABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB1AGcAYQByAFwAIgAsADAALgAwADEAOQA5ACwAIABcACIAUwB1AGcAYQByAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AdAB0AG8AbgBcACIALAAwAC4AMAAwADUAMwAsACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAG8AcgB0AGkAYwB1AGwAdAB1AHIAYQBsACAAYwByAG8AcABzAFwAIgAsADAALgAwADAANgA0ACwAIABcACIASABvAHIAdABpAGMAdQBsAHQAdQByAGEAbAAgAGMAcgBvAHAAcwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBpAGMAZQAgACgAYwBvAG4AdABpAG4AdQBvAHUAcwAgAGYAbABvAG8AZABpAG4AZwApAFwAIgAsADAALgAwADAAMwAsACAAXAAiAFIAaQBjAGUAXAAiACwAIABcACIAQwBvAG4AdABpAG4AdQBvAHUAcwAgAGYAbABvAG8AZABpAG4AZwBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBpAGMAZQAgACgAcwBpAG4AZwBsAGUAIABhAG4AZAAgAG0AdQBsAHQAaQBwAGwAZQAgAGQAcgBhAGkAbgBhAGcAZQAsACAAbwByACAAYQBsAHQAZQByAG4AYQB0AGUAIAB3AGUAdAB0AGkAbgBnACAAYQBuAGQAIABkAHIAeQBpAG4AZwApAFwAIgAsADAALgAwADAANQAsACAAXAAiAFIAaQBjAGUAXAAiACwAIABcACIAUwBpAG4AZwBsAGUAIABhAG4AZAAgAG0AdQBsAHQAaQBwAGwAZQAgAGQAcgBhAGkAbgBhAGcAZQAsACAAbwByACAAYQBsAHQAZQByAG4AYQB0AGUAIAB3AGUAdAB0AGkAbgBnACAAYQBuAGQAIABkAHIAeQBpAG4AZwBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBxAHUAYQBjAHUAbAB0AHUAcgBlAFwAIgAsADAALgAwADAAMgA2ACwAIABcACIAQQBxAHUAYQBjAHUAbAB0AHUAcgBlAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAG8AcgBlAHMAdAByAHkAXAAiACwAMAAuADAAMAAxADgALAAgAFwAIgBGAG8AcgBlAHMAdAByAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA1ACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGUAbQBvAHYAZQBkACAAZAB1AHAAbABpAGMAYQB0AGUAIABcAHUAMAAwADIANwBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAB1ADAAMAAyADcAIAByAG8AdwAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGUAbQBvAHYAZQBkACAAYQBzAHQAZQByAGkAcwBrAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAFwAdQAwADAAMgA3AHAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAG8AbgBsAHkAXAB1ADAAMAAyADcALAAgAFwAdQAwADAAMgA3AHIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAXAB1ADAAMAAyADcAIABhAG4AZAAgAFwAdQAwADAAMgA3AGkAcgByAGkAZwBhAHQAaQBvAG4AIABtAGUAdABoAG8AZABcAHUAMAAwADIANwAgAGMAbwBsAHUAbQBuAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAdQBwAGwAaQBjAGEAdABlAGQAIABcAHUAMAAwADIANwBuAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQBcAHUAMAAwADIANwAgAHIAbwB3ACAAdwBpAHQAaAAgAHMAYQBtAGUAIABFAEYAIABmAG8AcgAgAGwAbwB3ACAAYQBuAGQAIABoAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAFwAbgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABDAGgAYQBwAHQAZQByACAAMQAsACAAcwBlAGMAdABpAG8AbgAgADEALgA4AC4AMgAgAEwAZQBhAGMAaABpAG4AZwAsACAAYwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBzAFwAbgBJAFAAQwBDADoAIABOADIATwAgAEUATQBJAFMAUwBJAE8ATgBTACAARgBSAE8ATQAgAE0AQQBOAEEARwBFAEQAIABTAE8ASQBMAFMALAAgAEEATgBEACAAQwBPADIAIABFAE0ASQBTAFMASQBPAE4AUwAgAEYAUgBPAE0AIABMAEkATQBFACAAQQBOAEQAIABVAFIARQBBACAAQQBQAFAATABJAEMAQQBUAEkATwBOAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwBXAEUAVAAgAGYAbwByACAAaQByAHIAaQBnAGEAdABpAG8AbgAgAHQAeQBwAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAEMAaABhAHAAdABlAHIAIAAxACwAIABzAGUAYwB0AGkAbwBuACAAMQAuADgALgAyACAATABlAGEAYwBoAGkAbgBnACwAIABjAGwAaQBtAGEAdABlACAAYQBuAGQAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBJAFAAQwBDACAAMgAwADEAOQAgAFIAZQBmAGkAbgBlAG0AZQBuAHQAIABWAG8AbAB1AG0AZQAgADQAOgAgAEMAaABhAHAAdABlAHIAIAAxADEAOgAgAE4AMgBPACAARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAATQBhAG4AYQBnAGUAZAAgAFMAbwBpAGwAcwAsACAAYQBuAGQAIABDAE8AMgAgAEUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAEwAaQBtAGUAIABhAG4AZAAgAFUAcgBlAGEAIABBAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGkAbwBuACAAdAB5AHAAZQAgAGkAcgBcACIALABcACIARgByAGEAYwBXAEUAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAByAGkAcAAgAGkAcgByAGkAZwBhAHQAaQBvAG4AXAAiACwAIAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAcAByAGkAbgBrAGwAZQByACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB1AHIAZgBhAGMAZQAgAGkAcgByAGkAZwBhAHQAaQBvAG4AXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AdABoAGUAcgAgAGkAcgByAGkAZwBhAHQAaQBvAG4AXAAiACwAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAARgBSAE8ATQAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAAVABhAGIAbABlACAAYwByAGUAYQB0AGUAZAAgAGIAYQBzAGUAZAAgAG8AbgAgAFYARQBFAFIARwAgAHQAZQB4AHQAIABcAHUAMAAwADIANwBBAHIAZQBhAHMAIABhAHIAZQAgAHMAdQBiAGoAZQBjAHQAIAB0AG8AIABsAGUAYQBjAGgAaQBuAGcAIAAoAGkALgBlAC4ALAAgAGkAbgAgAHQAaABlACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQApACAAdwBoAGUAbgAuAC4ALgAgAHQAaABlACAAbABhAG4AZAAgAGkAcwAgAGkAcgByAGkAZwBhAHQAZQBkACAAKABlAHgAYwBlAHAAdAAgAGQAcgBpAHAAIABpAHIAcgBpAGcAYQB0AGkAbwBuACkALgBcAHUAMAAwADIANwBcACIAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAFwAbgBUAGEAYgBsAGUAIABBAC4AMgAuADIALgAyADoAIABFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAdQByAGkAbgBlACAAYQBuAGQAIABkAHUAbgBnACAAZABlAHAAbwBzAGkAdABlAGQAIABvAG4AIABwAGEAcwB0AHUAcgBlACwAIAByAGEAbgBnAGUAIABvAHIAIABwAGEAZABkAG8AYwBrACAAKABrAGcAIABOADIATwAtAE4ALwBrAGcAIABOACkAIAAoAEUARgBQAFIAUAApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAdQByAGkAbgBlACAAYQBuAGQAIABkAHUAbgBnACAAZABlAHAAbwBzAGkAdABlAGQAIABvAG4AIABwAGEAcwB0AHUAcgBlACwAIAByAGEAbgBnAGUAIABvAHIAIABwAGEAZABkAG8AYwBrAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AMgBPACAALQAgAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADIALgAyAC4AMgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAEUARgBQAFIAUABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAAyAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABDAGgAYQBuAGcAZQBkACAAXAB1ADAAMAAyADcARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBzAFwAdQAwADAAMgA3ACAAdABvACAAcwBpAG4AZwB1AGwAYQByACAAXAB1ADAAMAAyADcARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcAHUAMAAwADIANwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAG8AbgB0AGgAcwAgAHQAbwAgAFMAZQBhAHMAbwBuAHMAIABNAGEAcABwAGkAbgBnAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBvAG4AdABoAFwAIgAsACAAXAAiAFMAZQBhAHMAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAGEAbgB1AGEAcgB5AFwAIgAsACAAXAAiAFMAdQBtAG0AZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAGUAYgByAHUAYQByAHkAXAAiACwAIABcACIAUwB1AG0AbQBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQByAGMAaABcACIALAAgAFwAIgBBAHUAdAB1AG0AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBwAHIAaQBsAFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAGEAeQBcACIALAAgAFwAIgBBAHUAdAB1AG0AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASgB1AG4AZQBcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASgB1AGwAeQBcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQB1AGcAdQBzAHQAXAAiACwAIABcACIAVwBpAG4AdABlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAZQBwAHQAZQBtAGIAZQByAFwAIgAsACAAXAAiAFMAcAByAGkAbgBnAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBPAGMAdABvAGIAZQByAFwAIgAsACAAXAAiAFMAcAByAGkAbgBnAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdgBlAG0AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAZQBjAGUAbQBiAGUAcgBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBhAG4AdQByAGUAIABNAGEAbgBhAGcAZQBtAGUAbgB0ACAAEyAgAE0AZQB0AGgAYQBuAGUAIABjAG8AbgB2AGUAcgBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABwAGUAcgAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAIAAoAGYAcgBhAGMAdABpAG8AbgApACAAKABNAEMARgBpAG0AKQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAxAC4AOAAuADEAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIAMgAsACAAMQA2ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAE0AQQBUACAAKAC6AEMAKQBcACIALAAgAFwAIgBVAG4AYwBvAHYAZQByAGUAZAAgAGEAbgBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuAFwAIgAsACAAXAAiAEMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBcACIALAAgAFwAIgBMAGkAcQB1AGkAZAAgAFMAbAB1AHIAcgB5ACAAKAB3AGkAdABoAG8AdQB0ACAAbgBhAHQAdQByAGEAbAAgAGMAcgB1AHMAdAApAFwAIgAsACAAXAAiAEQAYQBpAGwAeQAgAHMAcAByAGUAYQBkACAAKABiACkAXAAiACwAIABcACIAQwBvAG0AcABvAHMAdABpAG4AZwAgACgAcABhAHMAcwBpAHYAZQAgAHcAaQBuAGQAcgBvAHcAKQBcACIALAAgAFwAIgBTAG8AbABpAGQAIABTAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAFAAaQB0ACAAUwB0AG8AcgBhAGcAZQAgAFwAdQAwADAAMwBjADEAIABtAG8AbgB0AGgAXAAiACwAIABcACIARABlAGUAcAAgAEwAaQB0AHQAZQByAFwAIgAsACAAXAAiAFAAbwB1AGwAdAByAHkAIABNAGEAbgB1AHIAZQAgACgAdwBpAHQAaAAvAHcAaQB0AGgAbwB1AHQAIABsAGkAdAB0AGUAcgApAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAcAByAG8AYwBlAHMAcwBpAG4AZwAgAGkAbgB0AG8AIABwAGUAbABsAGUAdABpAHoAZQBkACAAZgBlAHIAdABpAGwAaQBzAGUAcgBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgAgAHQAbwAgAHMAbwBpAGwAXAAiACwAIABcACIAUABhAHMAdAB1AHIAZQAsACAAUgBhAG4AZwBlACAAYQBuAGQAIABQAGEAZABkAG8AYwBrACAAKABjACkAKABkACkAXAAiACwAIABcACIATQBBAFQAIAByAGEAdwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgAFwAIgBkIjEAMABcACIALAAgADAALgA2ADYALAAgADAALgAxACwAIAAwAC4AMQAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIAAxADEALAAgADAALgA2ADgALAAgADAALgAxACwAIAAwAC4AMQAxACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgADEAMgAsACAAMAAuADcALAAgADAALgAxACwAIAAwAC4AMQAzACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgADEAMwAsACAAMAAuADcAMQAsACAAMAAuADEALAAgADAALgAxADQALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQA0ACwAIAAwAC4ANwAzACwAIAAwAC4AMQAsACAAMAAuADEANQAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA1ACwAIAAwAC4ANwA0ACwAIAAwAC4AMQAsACAAMAAuADEANwAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEANQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEANgAsACAAMAAuADcANQAsACAAMAAuADEALAAgADAALgAxADgALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADcALAAgADAALgA3ADYALAAgADAALgAxACwAIAAwAC4AMgAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEANwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEAOAAsACAAMAAuADcANwAsACAAMAAuADEALAAgADAALgAyADIALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADkALAAgADAALgA3ADcALAAgADAALgAxACwAIAAwAC4AMgA0ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgAwACwAIAAwAC4ANwA4ACwAIAAwAC4AMQAsACAAMAAuADIANgAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIAMQAsACAAMAAuADcAOAAsACAAMAAuADEALAAgADAALgAyADkALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADIALAAgADAALgA3ADgALAAgADAALgAxACwAIAAwAC4AMwAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgAzACwAIAAwAC4ANwA5ACwAIAAwAC4AMQAsACAAMAAuADMANAAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIANAAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgAzADcALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADUALAAgADAALgA3ADkALAAgADAALgAxACwAIAAwAC4ANAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AXAAiACwAIAAyADYALAAgADAALgA3ADkALAAgADAALgAxACwAIAAwAC4ANAA0ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AXAAiACwAIAAyADcALAAgADAALgA4ACwAIAAwAC4AMQAsACAAMAAuADQAOAAsACAAMAAuADAAMQAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIANwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtAFwAIgAsACAAXAAiAGUiMgA4AFwAIgAsACAAMAAuADgALAAgADAALgAxACwAIAAwAC4ANQAsACAAMAAuADAAMQAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBBAG4AYQBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuAFwAIgAsACAAXAAiAEQAaQBnAGUAcwB0AGUAcgAgAC8AIABjAG8AdgBlAHIAZQBkACAAbABhAGcAbwBvAG4AcwBcACIALAAgAFwAIgBMAGkAcQB1AGkAZAAgAHMAeQBzAHQAZQBtAHMAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAXAAiACwAIABcACIAQwBvAG0AcABvAHMAdABpAG4AZwAgACgAcABhAHMAcwBpAHYAZQAgAHcAaQBuAGQAcgBvAHcAKQBcACIALAAgAFwAIgBTAG8AbABpAGQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAFAAaQB0ACAAcwB0AG8AcgBhAGcAZQBcACIALAAgAFwAIgBEAGUAZQBwACAAbABpAHQAdABlAHIAXAAiACwAIABcACIAUABvAHUAbAB0AHIAeQAgAG0AYQBuAHUAcgBlACAAdwBpAHQAaAAgAGIAZQBkAGQAaQBuAGcAXAAiACwAIABcACIAUABvAHUAbAB0AHIAeQAgAG0AYQBuAHUAcgBlACAAdwBpAHQAaABvAHUAdAAgAGIAZQBkAGQAaQBuAGcAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABwAHIAbwBjAGUAcwBzAGkAbgBnAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuAFwAIgAsACAAXAAiAFAAYQBzAHQAdQByAGUAIAByAGEAbgBnAGUAIABhAG4AZAAgAHAAYQBkAGQAbwBjAGsAXAAiACwAIABcACIATQBBAFQAIAByAGEAdwBcACIAIABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAOgAgAEEAZABkAGUAZAAgAHIAbwB3ACAAbwBmACAATgBJAFIAIABNAE0AQQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgAgAEQAdQBwAGwAaQBjAGEAdABlAGQAIABcAHUAMAAwADIANwBQAG8AdQBsAHQAcgB5ACAAdwBpAHQAaAAgAGEAbgBkACAAdwBpAHQAaABvAHUAdAAgAGwAaQB0AHQAZQByAFwAdQAwADAAMgA3ACAAYwBvAGwAdQBtAG4AIAB3AGkAdABoACAAcwBlAHAAYQByAGEAdABlACAATgBJAFIAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AIABBAGQAZABlAGQAIABcAHUAMAAwADIANwBNAEEAVAAgAHIAYQB3AFwAdQAwADAAMgA3ACAAYwBvAGwAdQBtAG4AIAB0AG8AIABhAGwAbABvAHcAIABsAG8AbwBrAHUAcAAgAG8AZgAgAG4AdQBtAGIAZQByAHMALgBcACIAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAbgBkACAAYwByAG8AcAAgAHIAZQBzAGkAZAB1AGUAcwAgAHIAZQB0AHUAcgBuAGUAZAAgAHQAbwAgAHQAaABlACAAcwBvAGkAbABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBGAE4AaQAgAFwAdQAwADAAMgA2ACAARQBGAE4AMgBPAGkAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABOADIATwAgAC0AIABOACAALwAgAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADIALgAxAC4ANABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgAFwAIgBFAEYATgBpACAAXAB1ADAAMAAyADYAIABFAEYATgAyAE8AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIAAwAC4AMAAwADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAANQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIAXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBcAG4AQwBvAG4AdgBlAHIAdAAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcAG4ARQBOADIATwAgAEMATwAyAGUAXABuAHQAIABDAE8AMgBlAFwAbgBFAE4AMgBPADoAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAAoAHQAIABOADIATwApAFwAbgBHAFcAUABOADIATwA6ACAAZwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIAAoAHQAIABDAE8AMgAtAGUAIAAvACAAdAAgAE4AMgBPACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABFAF8ATgAyAE8ALAAgAEcAVwBQAF8ATgAyAE8ALABcAG4AIAAgACAAIABFAF8ATgAyAE8AIAAqACAARwBXAFAAXwBOADIATwBcAG4AIAAgACkAXABuADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAbwBuAHYAZQByAHQAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAB0AG8AIABjAGEAcgBiAG8AbgAgAGQAaQBvAHgAaQBkAGUAIABlAHEAdQBpAHYAYQBsAGUAbgB0ACAAZQBtAGkAcwBzAGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBOADIATwAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAE8AMgBlAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMATwAyAF8AZQAgAD0AIABFAF8AewBOADIATwB9ACAAXABcAHQAaQBtAGUAcwAgAEcAVwBQAF8AewBOADIATwB9AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUATgAyAE8AXAAiACwAXAAiAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAE4AMgBPACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAVwBQAE4AMgBPAFwAIgAsAFwAIgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAATgAyAE8AKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBcAG4AQwBvAG4AdgBlAHIAdAAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcAG4ARQBDAEgANAAgAEMATwAyAGUAXABuAHQAIABDAE8AMgBlAFwAbgBFAEMASAA0ADoAIABtAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAAoAHQAIABDAEgANAApAFwAbgBHAFcAUABDAEgANAA6ACAAZwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAG0AZQB0AGgAYQBuAGUAIAAoAHQAIABDAE8AMgAtAGUAIAAvACAAdAAgAEMASAA0ACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABFAF8AQwBIADQALAAgAEcAVwBQAF8AQwBIADQALABcAG4AIAAgACAAIABFAF8AQwBIADQAIAAqACAARwBXAFAAXwBDAEgANABcAG4AIAAgACkAXABuADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAbwBuAHYAZQByAHQAIABtAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAB0AG8AIABjAGEAcgBiAG8AbgAgAGQAaQBvAHgAaQBkAGUAIABlAHEAdQBpAHYAYQBsAGUAbgB0ACAAZQBtAGkAcwBzAGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBDAEgANAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAE8AMgBlAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMATwAyAF8AZQAgAD0AIABFAF8AewBDAEgANAB9ACAAXABcAHQAaQBtAGUAcwAgAEcAVwBQAF8AewBDAEgANAB9AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUAQwBIADQAXAAiACwAXAAiAE0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAEMASAA0ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAVwBQAEMASAA0AFwAIgAsAFwAIgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbQBlAHQAaABhAG4AZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAAQwBIADQAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIAVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAUgBvAHcAUwB0AGEAcgB0AE4AdQBtAGIAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwALABSAG8AdwBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAYQBuAGQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAUgBPAFcAKABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAApACAAKwAgAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkAIAAtACAAMQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABUAGEAYgBsAGUASABlAGEAZABlAHIAQwBlAGwAbAAsAFwAbgAgACAAQwBPAEwAVQBNAE4AKABUAGEAYgBsAGUASABlAGEAZABlAHIAQwBlAGwAbAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBBAHIAcgBhAHkASQBuAFQAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgAEEAcgByAGEAeQBEAGEAdABhACwAIABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQAsACAAWwBDAG8AbAB1AG0AbgBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAQQBuAGQAQQByAHIAYQB5AF0ALABcAG4AIABJAEYARQBSAFIATwBSACgAXABuACAAIAAgACAAIABJAE4ARABFAFgAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAVQBOAEkAUQBVAEUAKABBAHIAcgBhAHkARABhAHQAYQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBPAFcAKAApAC0AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAUgBvAHcAUwB0AGEAcgB0AE4AdQBtAGIAZQByACgAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwALAAgAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEMATwBMAFUATQBOACgAKQAtAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAEMAbwBsAHUAbQBuAFMAdABhAHIAdABOAHUAbQBiAGUAcgAoAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACkAIAArAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAEMAbwBsAHUAbQBuAHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBBAG4AZABBAHIAcgBhAHkAKQAsACAAMQAsACAAQwBvAGwAdQBtAG4AcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAEEAbgBkAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACAAIAAgACAAKQAsACAAXAAiAFwAIgBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFwAIgBcACIAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEkARgAoAEkAUwBOAFUATQBCAEUAUgAoAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFwAIgBcACIAKQBcAG4AIAAgACAAIAApACwAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApACwAIAAwACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBUAHcAbwBDAG8AbAB1AG0AbgBzAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlADEALAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADIALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAWwBWAGEAbAB1AGUASQBGAEYAYQBsAHMAZQBdACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoADEALAAgACgATABvAG8AawB1AHAAQQByAHIAYQB5ADEAPQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQApACoAKABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABWAGEAbAB1AGUASQBGAEYAYQBsAHMAZQApACwAIABcACIAXAAiACwAIABWAGEAbAB1AGUASQBGAEYAYQBsAHMAZQApACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBPAG4AZQBDAG8AbAB1AG0AbgBBAG4AZABIAGUAYQBkAGUAcgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACwAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMgAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADEALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFsAVgBhAGwAdQBlAEkAZgBGAGEAbABzAGUAXQAsAFwAbgAgACAAIAAgAEkARgBFAFIAUgBPAFIAKABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADEALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACkAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAFYAYQBsAHUAZQBJAGYARgBhAGwAcwBlACkALAAgAFwAIgBcACIALAAgAFYAYQBsAHUAZQBJAGYARgBhAGwAcwBlACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAcABsAGkAdABTAHQAcgBpAG4AZwBJAG4AdABvAEEAcgByAGEAeQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEMAZQBsAGwALAAgAEQAZQBsAGkAbQBpAHQAZQByACwAIABbAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAxAF0ALAAgAFsAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADIAXQAsAFwAbgAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAWABNAEwAKABcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBcAHUAMAAwADMAYwB0AFwAdQAwADAAMwBlAFwAdQAwADAAMwBjAHMAXAB1ADAAMAAzAGUAXAAiACAAXAB1ADAAMAAyADYAXABuACAAIAAgACAAIAAgACAAIABTAFUAQgBTAFQASQBUAFUAVABFACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFMAVQBCAFMAVABJAFQAVQBUAEUAKABTAFUAQgBTAFQASQBUAFUAVABFACgAQwBlAGwAbAAsAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAxACwAXAAiAFwAIgApACwAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADIALABcACIAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAARABlAGwAaQBtAGkAdABlAHIALABcACIAXAB1ADAAMAAzAGMALwBzAFwAdQAwADAAMwBlAFwAdQAwADAAMwBjAHMAXAB1ADAAMAAzAGUAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAKQAgAFwAdQAwADAAMgA2AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFwAdQAwADAAMwBjAC8AcwBcAHUAMAAwADMAZQBcAHUAMAAwADMAYwAvAHQAXAB1ADAAMAAzAGUAXAAiACwAXABuACAAIAAgACAAIAAgACAAIABcACIALwAvAHMAXAAiAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABDAGwAaQBtAGEAdABlAFoAbwBuAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABhAHYAZwBUAGUAbQBwACwAYQB2AGcAUgBhAGkAbgAsAGYAcgBvAHMAdABEAGEAeQBzACwAZQBsAGUAdgAsAG0AYQBwAF8AcABlAHQALABcAG4AIAAgACAAIABtAGkAbgBUAGUAbQBwAEEAcgByAGEAeQAsAG0AYQB4AFQAZQBtAHAAQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4AUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQAsAG0AYQB4AFIAYQBpAG4AZgBhAGwAbABBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBGAHIAbwBzAHQAQQByAHIAYQB5ACwAbQBhAHgARgByAG8AcwB0AEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAEUAbABlAHYAYQB0AGkAbwBuAEEAcgByAGEAeQAsAG0AYQB4AEUAbABlAHYAYQB0AGkAbwBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAFAARQBUAEEAcgByAGEAeQAsAG0AYQB4AFAARQBUAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAGMAbABpAG0AYQB0AGUAWgBvAG4AZQBBAHIAcgBhAHkALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAbQBhAHMAawAsAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBUAGUAbQBwAEEAcgByAGEAeQApAFwAdQAwADAAMwBjAD0AYQB2AGcAVABlAG0AcAApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AFQAZQBtAHAAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBhAHYAZwBUAGUAbQBwACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4AUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQApAFwAdQAwADAAMwBjAD0AYQB2AGcAUgBhAGkAbgApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AFIAYQBpAG4AZgBhAGwAbABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGEAdgBnAFIAYQBpAG4AKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBGAHIAbwBzAHQAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBmAHIAbwBzAHQARABhAHkAcwApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AEYAcgBvAHMAdABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGYAcgBvAHMAdABEAGEAeQBzACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4ARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBlAGwAZQB2ACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBlAGwAZQB2ACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4AUABFAFQAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBtAGEAcABfAHAAZQB0ACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgAUABFAFQAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBtAGEAcABfAHAAZQB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAFQAQQBLAEUAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAKABjAGwAaQBtAGEAdABlAFoAbwBuAGUAQQByAHIAYQB5ACwAbQBhAHMAawAsACAAXAAiAE4AbwAgAG0AYQB0AGMAaABcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAASQB0AGUAbQBGAHIAbwBtAE0AaQBuAE0AYQB4AFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABNAGkAbgBBAHIAcgBhAHkALAAgAE0AYQB4AEEAcgByAGEAeQAsACAASQB0AGUAbQBBAHIAcgBhAHkALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAbQBhAHMAawAsAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABNAGkAbgBBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAE0AYQB4AEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0ATABvAG8AawB1AHAAVgBhAGwAdQBlACkALABcAG4AIAAgACAAIAAgACAAIAAgAEYASQBMAFQARQBSACgASQB0AGUAbQBBAHIAcgBhAHkALAAgAG0AYQBzAGsALAAgAFwAIgBOAG8AIABtAGEAdABjAGgAXAAiACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBTAHUAbQBRAHUAYQBuAHQAaQB0AHkARgByAG8AbQBDAHIAaQB0AGUAcgBpAGEAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAEMAcgBpAHQAZQByAGkAYQAxACwAIABDAHIAaQB0AGUAcgBpAGEAMQBUAHkAcABlAEEAcgByAGEAeQAsACAAUQB1AGEAbgB0AGkAdAB5ACwAIABbAE0AdQBsAHQAaQBwAGwAaQBlAHIAXQAsACAAWwBDAHIAaQB0AGUAcgBpAGEAMgBdACwAWwBDAHIAaQB0AGUAcgBpAGEAMgBBAHIAcgBhAHkAXQAsAFwAbgAgACAATABFAFQAKABcAG4AIAAgACAAIABtAHUAbAB0AGkAcABsAGkAZQByACwAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAE0AdQBsAHQAaQBwAGwAaQBlAHIAKQAsADEALABNAHUAbAB0AGkAcABsAGkAZQByACkALABcAG4AIAAgACAAIABxAHUAYQBuAHQAaQB0AHkALAAgAFEAdQBhAG4AdABpAHQAeQAqAE0AdQBsAHQAaQBwAGwAaQBlAHIALABcAG4AIAAgACAAIABjAHIAaQB0AGUAcgBpAGEAMQAsAC0ALQAoAEMAcgBpAHQAZQByAGkAYQAxAFQAeQBwAGUAQQByAHIAYQB5AD0AQwByAGkAdABlAHIAaQBhADEAKQAsAFwAbgAgACAAIAAgAGMAcgBpAHQAZQByAGkAYQAyACwASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABDAHIAaQB0AGUAcgBpAGEAMgApACwAMQAsAC0ALQAoAEMAcgBpAHQAZQByAGkAYQAyAEEAcgByAGEAeQA9AEMAcgBpAHQAZQByAGkAYQAyACkAKQAsAFwAbgAgACAAIAAgAFMAVQBNAFAAUgBPAEQAVQBDAFQAKABjAHIAaQB0AGUAcgBpAGEAMQAqAGMAcgBpAHQAZQByAGkAYQAyACoAcQB1AGEAbgB0AGkAdAB5ACkAXABuACAAIAApAFwAbgApADsAXABuAFwAbgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAHMAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBTAHQAYQByAHQALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBFAG4AZAAsAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAUwAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgACAAIAAgACAARQAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAXABuACAAIAAgACAAIAAgACAAIABtACwATQBPAE4AVABIACgAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAApACwAXABuACAAIAAgACAAIAAgACAAIABkACwARABBAFkAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAFAAZQByAGkAbwBkAEUAbgBkACwATABBAE0AQgBEAEEAKABzAHQALABFAEQAQQBUAEUAKABzAHQALAAxADIAKQAtADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAQQAsAFMALQAzADYANQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBhACwAWQBFAEEAUgAoAEEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBiACwAWQBFAEEAUgAoAEUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZgBpAHIAcwB0AFkAZQBhAHIALAB5AGEAKwAoAFAAZQByAGkAbwBkAEUAbgBkACgARABBAFQARQAoAHkAYQAsAG0ALABkACkAKQBcAHUAMAAwADMAYwAgAFMAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAbABhAHMAdABZAGUAYQByACwAeQBiAC0AKABEAEEAVABFACgAeQBiACwAbQAsAGQAKQBcAHUAMAAwADMAZQAgAEUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAATQBBAFgAKAAwACwAbABhAHMAdABZAGUAYQByAC0AZgBpAHIAcwB0AFkAZQBhAHIAKwAxACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAFAAZQByAGkAbwBkAHMAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBTAHQAYQByAHQALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBFAG4AZAAsAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAUwAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgACAAIAAgACAARQAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAXABuACAAIAAgACAAIAAgACAAIABtACwATQBPAE4AVABIACgAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAApACwAXABuACAAIAAgACAAIAAgACAAIABkACwARABBAFkAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALAAgAC8AKgBoAGUAbABwAGUAcgA6ACAAZQBuAGQAIABkAGEAdABlACAAZgBvAHIAIABhACAAcgBlAHAAbwByAHQAaQBuAGcAIABwAGUAcgBpAG8AZAAgAHMAdABhAHIAdABpAG4AZwAgAGEAdAAgAGEAIABnAGkAdgBlAG4AIABkAGEAdABlACoALwBcAG4AIAAgACAAIAAgACAAIAAgAFAAZQByAGkAbwBkAEUAbgBkACwATABBAE0AQgBEAEEAKABzAHQALABFAEQAQQBUAEUAKABzAHQALAAxADIAKQAtADEAKQAsACAALwAqAG8AbgBsAHkAIABuAGUAZQBkACAAdABvACAAbABvAG8AawAgAGIAYQBjAGsAIAAzADYANQAgAGQAYQB5AHMAKABtAGEAeAAgAG8AdgBlAHIAbABhAHAAIAB3AGkAbgBkAG8AdwApACoALwBcAG4AIAAgACAAIAAgACAAIAAgAEEALABTAC0AMwA2ADUALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYQAsAFkARQBBAFIAKABBACkALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYgAsAFkARQBBAFIAKABFACkALAAgAC8AKgBpAGYAIAB0AGgAZQAgAGEAbgBjAGgAbwByACAAZgBvAHIAIAB5AGEAIABlAG4AZABzACAAYgBlAGYAbwByAGUAIABTACwAaQB0ACAAYwBhAG4AXAB1ADAAMAAyADcAdAAgAG8AdgBlAHIAbABhAHAAOwAgAG0AbwB2AGUAIAB0AG8AIABuAGUAeAB0ACAAeQBlAGEAcgAqAC8AXABuACAAIAAgACAAIAAgACAAIABmAGkAcgBzAHQAWQBlAGEAcgAsAHkAYQArACgAUABlAHIAaQBvAGQARQBuAGQAKABEAEEAVABFACgAeQBhACwAbQAsAGQAKQApAFwAdQAwADAAMwBjAFMAKQAsACAALwAqAGkAZgAgAHQAaABlACAAYQBuAGMAaABvAHIAIABmAG8AcgAgAHkAYgAgAHMAdABhAHIAdABzACAAYQBmAHQAZQByACAARQAsAGkAdAAgAGMAYQBuAFwAdQAwADAAMgA3AHQAIABvAHYAZQByAGwAYQBwADsAIABtAG8AdgBlACAAdABvACAAcAByAGUAdgBpAG8AdQBzACAAeQBlAGEAcgAqAC8AXABuACAAIAAgACAAIAAgACAAIABsAGEAcwB0AFkAZQBhAHIALAB5AGIALQAoAEQAQQBUAEUAKAB5AGIALABtACwAZAApAFwAdQAwADAAMwBlAEUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAbgAsAE0AQQBYACgAMAAsAGwAYQBzAHQAWQBlAGEAcgAtAGYAaQByAHMAdABZAGUAYQByACsAMQApACwAXABuACAAIAAgACAAIAAgACAAIAB5AHIAcwAsAFMARQBRAFUARQBOAEMARQAoAG4ALAAxACwAZgBpAHIAcwB0AFkAZQBhAHIALAAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAHMAdABhAHIAdABzACwARABBAFQARQAoAHkAcgBzACwAbQAsAGQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZQBuAGQAcwAsAE0AQQBQACgAcwB0AGEAcgB0AHMALABQAGUAcgBpAG8AZABFAG4AZAApACwAXABuACAAIAAgACAAIAAgACAAIAB0AGEAZwAsAEkARgAoAHMAdABhAHIAdABzAD0AUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAIgAgACgAVABoAGkAcwAgAHIAZQBwAG8AcgB0AGkAbgBnACAAYwB5AGMAbABlACkAXAAiACwAXAAiAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABzAHQAYQByAHQAcwBUAGUAeAB0ACwAVABFAFgAVAAoAHMAdABhAHIAdABzACwAXAAiAGQAZAAgAG0AbQBtACAAeQB5AHkAeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZQBuAGQAcwBUAGUAeAB0ACwAVABFAFgAVAAoAGUAbgBkAHMALABcACIAZABkACAAbQBtAG0AIAB5AHkAeQB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABuAD0AMAAsAFwAIgBcACIALABIAFMAVABBAEMASwAoAHMAdABhAHIAdABzAFQAZQB4AHQAIABcAHUAMAAwADIANgAgAFwAIgAgAHQAbwAgAFwAIgAgAFwAdQAwADAAMgA2ACAAZQBuAGQAcwBUAGUAeAB0ACAAXAB1ADAAMAAyADYAIAB0AGEAZwApACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkARgB1AG4AYwB0AGkAbwBuAE4AYQBtAGUAXABuAD0ATABBAE0AQgBEAEEAKABGAHUAbgBjAHQAaQBvAG4ALAAgAFQARQBYAFQAQgBFAEYATwBSAEUAKABGAE8AUgBNAFUATABBAFQARQBYAFQAKABGAHUAbgBjAHQAaQBvAG4AKQAsACAAXAAiACgAXAAiACkAKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAE4AMgBPAEUARgBGAHIAbwBtAFAAcgBvAGQASQByAHIAaQBnAGEAdABpAG8AbgBSAGEAaQBuAGYAYQBsAGwAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAIABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACwAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AQQByAHIAYQB5ACwAIABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkAEEAcgByAGEAeQAsACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAQQByAHIAYQB5ACwAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQALAAgAEkARgAoAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAPQBcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEEAbgB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQAsACAASQBGACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAAgAD0AIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAIABcACIAQQBuAHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKAAxACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEEAcgByAGEAeQA9AFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AKQAqAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAoAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAQQByAHIAYQB5AD0ASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAApACoAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACgAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAQQByAHIAYQB5AD0AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEcAZQB0AEYAcgBhAGMAVwBFAFQAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ALABcAG4AIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQALAAgAFwAbgAgACAAIAAgACAAIAAgACAAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUALABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBMAG8AbwBrAHUAcAAsAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQALAAgAFwAbgAgACAAIAAgACAAIAAgACAAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ATABvAG8AawB1AHAALABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBGAHIAYQBjAFcARQBUACAAKwAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVABcAHUAMAAwADMAZQAwACwAIAAxACwAIAAwACkAXABuACAAIAAgACAAKQApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEMAbwBuAHYAZQByAHQAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAVABvAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUALABcAG4AIAAgACAAIABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBBAHIAcgBhAHkALAAgAFMAdABhAHQAZQBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUALAAgAFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAEEAcgByAGEAeQAsACAAUwB0AGEAdABlAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwBvAHUAcgBjAGUASAB5AHAAZQByAGwAaQBuAGsAXABuAD0ATABBAE0AQgBEAEEAKABUAGEAcgBnAGUAdABDAGUAbABsACwAXABuACAAIABMAEUAVAAoAFwAbgAgACAAIAAgAHMAaAAsACAAVABFAFgAVABBAEYAVABFAFIAKABDAEUATABMACgAXAAiAGYAaQBsAGUAbgBhAG0AZQBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsACAAXAAiAF0AXAAiACkALABcAG4AIAAgACAAIABhAGQAZAByACwAIABDAEUATABMACgAXAAiAGEAZABkAHIAZQBzAHMAXAAiACwAIABUAGEAcgBnAGUAdABDAGUAbABsACkALABcAG4AIAAgACAAIABcACIAIwBcAHUAMAAwADIANwBcACIAIABcAHUAMAAwADIANgAgAHMAaAAgAFwAdQAwADAAMgA2ACAAXAAiAFwAdQAwADAAMgA3ACEAXAAiACAAXAB1ADAAMAAyADYAIABhAGQAZAByAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAbwB1AHIAYwBlAEgAeQBwAGUAcgBsAGkAbgBrAEQAaQBmAGYAZQByAGUAbgB0AFMAaABlAGUAdABcAG4APQBMAEEATQBCAEQAQQAoAFQAYQByAGcAZQB0AEMAZQBsAGwALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAcwBoACwAIABUAEUAWABUAEEARgBUAEUAUgAoAEMARQBMAEwAKABcACIAZgBpAGwAZQBuAGEAbQBlAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAIABcACIAXQBcACIAKQAsAFwAbgAgACAAIAAgAGEAZABkAHIALAAgAEMARQBMAEwAKABcACIAYQBkAGQAcgBlAHMAcwBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsAFwAbgAgACAAIAAgAFwAIgAjAFwAIgAgAFwAdQAwADAAMgA2ACAAYQBkAGQAcgBcAG4AIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgBnAHUAbQBlAG4AdABzAF8AMQBfADIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALABcAG4AIAAgACAAIABDAEgATwBPAFMARQBDAE8ATABTACgAQQByAGcAdQBtAGUAbgB0AHMAQQByAHIAYQB5ACwAIAAxACwAIAAyACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgBnAHUAbQBlAG4AdABzAF8AMwBfADQAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALABcAG4AIAAgACAAIABDAEgATwBPAFMARQBDAE8ATABTACgAQQByAGcAdQBtAGUAbgB0AHMAQQByAHIAYQB5ACwAIAAzACwAIAA0ACkAXABuACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8ARwBlAHQATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUALAAgAE0ATQBTACwAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUAQQByAHIAYQB5ACwAIABNAE0AUwBBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKABcAG4AIAAgACAAIAAgACAAIAAgAE0ARQBEAEkAQQBOACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFIATwBVAE4ARAAoAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAsACAAMAApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATQBJAE4AKABUAGUAbQBwAGUAcgBhAHQAdQByAGUAQQByAHIAYQB5ACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABNAEEAWAAoAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkALABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKABNAE0AUwAsACAATQBNAFMAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFIAZQBzAHUAbAB0AHMASQB0AGUAbQBGAHIAbwBtAEUAcQB1AGEAdABpAG8AbgBUAGkAdABsAGUAQQBuAGQAUwBvAHUAcgBjAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGkAdABsAGUAQwBlAGwAbAAsACAAUwBvAHUAcgBjAGUAQwBlAGwAbAAsAFwAbgAgACAAIAAgAFMAVQBCAFMAVABJAFQAVQBUAEUAKABMAEUARgBUACgAUwBvAHUAcgBjAGUAQwBlAGwAbAAsACAARgBJAE4ARAAoAFwAIgAsAFwAIgAsACAAUwBvAHUAcgBjAGUAQwBlAGwAbAApACAALQAxACkALAAgAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABcACIALAAgAFwAIgBcACIAKQAgAFwAdQAwADAAMgA2ACAAXAAiACAAXAAiACAAXAB1ADAAMAAyADYAIABUAGkAdABsAGUAQwBlAGwAbABcAG4AKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AVwBhAHMAdABlAHcAYQB0AGUAcgBfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAiACwAIgB0AGUAeAB0ACIAOgAiAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AMQAxAC4AMQA6ACAAVwBhAHMAdABlAHcAYQB0AGUAcgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AMQAxAC4AMQAuADEALgAxACAATQBlAHQAaABvAGQAIAAxACAALQAgAE0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABvAG4AcwBpAHQAZQAgAFcAYQBzAHQAZQB3AGEAdABlAHIAIABNAGEAbgBhAGcAZQBtAGUAbgB0AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8AMQAxAF8AMQBfADEAXwAxAF8AXwAxAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFcAYQBzAHQAZQB3AGEAdABlAHIAVAByAGUAYQB0AG0AZQBuAHQAXABuAE0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIAB3AGEAcwB0AGUAdwBhAHQAZQByACAAdAByAGUAYQB0AG0AZQBuAHQAXABuAEUAXwBDAEgANABcAG4AdAAgAEMASAA0AFwAbgBFAF8AewBDAEgANAB9AD0AXABcAGYAcgBhAGMAewAxAH0AewAxADAAMAAwAH0AXABcAHQAaQBtAGUAcwBcAFwAbABlAGYAdABbAFwAXABsAGUAZgB0ACgAVwBfAHQAXABcAHQAaQBtAGUAcwBcAFwAbABlAGYAdAAoAEMATwBEAF8AewBpAG4AfQBcAFwAdABpAG0AZQBzACgAMQAtAEYAXwB7AHMAbAB1AGQAZwBlAH0AKQAtAEMATwBEAF8AewBvAHUAdAB9AFwAXAByAGkAZwBoAHQAKQBcAFwAdABpAG0AZQBzACAAQwBGAF8AewB3AHcALAB0AH0AXABcAHQAaQBtAGUAcwAgAEUARgBfAHsAdwB3AH0AXABcAHIAaQBnAGgAdAApACsAXABcAGwAZQBmAHQAKABXAF8AdABcAFwAdABpAG0AZQBzAFwAXABsAGUAZgB0ACgAQwBPAEQAXwB7AGkAbgB9AFwAXAB0AGkAbQBlAHMAKABGAF8AewBzAGwAdQBkAGcAZQB9AC0ARgBfAHsAcgBlAG0AbwB2AGUAZAB9ACkAXABcAHIAaQBnAGgAdAApAFwAXAB0AGkAbQBlAHMAIABDAEYAXwB7AHMAbAB1AGQAZwBlACwAdAB9AFwAXAB0AGkAbQBlAHMAIABFAEYAXwB7AHMAbAB1AGQAZwBlAH0AXABcAHIAaQBnAGgAdAApAC0AXABcAGwAZQBmAHQAKAA2AC4ANwA4ADQAXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQA0AH0AXABcAHQAaQBtAGUAcwAoAFEAXwB7AGMAYQBwAH0AKwBRAF8AewBmAGwAYQByAGUAZAB9ACsAUQBfAHsAbwB1AHQAfQApAFwAXAByAGkAZwBoAHQAKQArAFwAXABsAGUAZgB0ACgAUQBfAHsAZgBsAGEAcgBlAGQAfQBcAFwAdABpAG0AZQBzACAARQBDAF8AewBmAGwAYQByAGUAZAB9AFwAXAB0AGkAbQBlAHMAIABFAEYAXwB7AGYAbABhAHIAZQBkACwAQwBIADQAfQBcAFwAcgBpAGcAaAB0ACkAXABcAHIAaQBnAGgAdABdAFwAbgBXAF8AdAAgAD0AIABxAHUAYQBuAHQAaQB0AHkAIABvAGYAIAB3AGEAcwB0AGUAdwBhAHQAZQByACAAdAByAGUAYQB0AGUAZAAgAGEAdAAgAGYAYQBjAGkAbABpAHQAeQAgAHQAeQBwAGUAIAB0ACAAKABtADMAKQBcAG4AQwBPAEQAXwBpAG4AIAA9ACAAYQB2AGUAcgBhAGcAZQAgAGkAbgBsAGUAdAAgAEMAaABlAG0AaQBjAGEAbAAgAE8AeAB5AGcAZQBuACAARABlAG0AYQBuAGQAIABjAG8AbgBjAGUAbgB0AHIAYQB0AGkAbwBuACAAbwBmACAAdwBhAHMAdABlAHcAYQB0AGUAcgAgACgAawBnACAAQwBPAEQALwBtADMAKQBcAG4ARgBfAHMAbAB1AGQAZwBlACAAPQAgAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAEMATwBEACAAcgBlAG0AbwB2AGUAZAAgAGYAcgBvAG0AIAB3AGEAcwB0AGUAdwBhAHQAZQByACAAYQBzACAAcwBsAHUAZABnAGUAXABuAEMATwBEAF8AbwB1AHQAIAA9ACAAYQB2AGUAcgBhAGcAZQAgAG8AdQB0AGwAZQB0ACAAQwBPAEQAIABjAG8AbgBjAGUAbgB0AHIAYQB0AGkAbwBuACAAbwBmACAAdwBhAHMAdABlAHcAYQB0AGUAcgAgACgAawBnACAAQwBPAEQALwBtADMAKQBcAG4AQwBGAF8AdwB3AF8AdAAgAD0AIABtAGUAdABoAGEAbgBlACAAYwBvAHIAcgBlAGMAdABpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABmAGEAYwBpAGwAaQB0AHkAIAB0AHkAcABlACAAdAAgAHUAcwBlAGQAIAB0AG8AIAB0AHIAZQBhAHQAIAB3AGEAcwB0AGUAdwBhAHQAZQByAFwAbgBFAEYAXwB3AHcAIAA9ACAAbQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB3AGEAcwB0AGUAdwBhAHQAZQByACAAKABrAGcAIABDAE8AMgBlAC8AawBnACAAQwBPAEQAKQBcAG4ARgBfAHIAZQBtAG8AdgBlAGQAIAA9ACAAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAQwBPAEQAIAByAGUAbQBvAHYAZQBkACAAZgByAG8AbQAgAHQAaABlACAAdwBhAHMAdABlAHcAYQB0AGUAcgAgAHQAcgBlAGEAdABtAGUAbgB0ACAAZgBhAGMAaQBsAGkAdAB5ACAAYQBuAGQAIAB0AHIAYQBuAHMAZgBlAHIAcgBlAGQAIABlAGwAcwBlAHcAaABlAHIAZQBcAG4AQwBGAF8AcwBsAHUAZABnAGUAXwB0ACAAPQAgAG0AZQB0AGgAYQBuAGUAIABjAG8AcgByAGUAYwB0AGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAGYAYQBjAGkAbABpAHQAeQAgAHQAeQBwAGUAIAB0ACAAdQBzAGUAZAAgAHQAbwAgAHQAcgBlAGEAdAAgAHMAbAB1AGQAZwBlAFwAbgBFAEYAXwBzAGwAdQBkAGcAZQAgAD0AIABtAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHMAbAB1AGQAZwBlACAAKABrAGcAIABDAE8AMgBlAC8AawBnACAAQwBPAEQAKQBcAG4AUQBfAGMAYQBwACAAPQAgAHEAdQBhAG4AdABpAHQAeQAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAIABpAG4AIABzAGwAdQBkAGcAZQAgAGIAaQBvAGcAYQBzACAAYwBhAHAAdAB1AHIAZQBkACAAZgBvAHIAIABjAG8AbQBiAHUAcwB0AGkAbwBuACAAKABtADMAIABDAEgANAApAFwAbgBRAF8AZgBsAGEAcgBlAGQAIAA9ACAAcQB1AGEAbgB0AGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQAgAGkAbgAgAHMAbAB1AGQAZwBlACAAYgBpAG8AZwBhAHMAIABmAGwAYQByAGUAZAAgACgAbQAzACAAQwBIADQAKQBcAG4AUQBfAG8AdQB0ACAAPQAgAHEAdQBhAG4AdABpAHQAeQAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAIABpAG4AIABzAGwAdQBkAGcAZQAgAGIAaQBvAGcAYQBzACAAdAByAGEAbgBzAGYAZQByAHIAZQBkACAAbwB1AHQAIABvAGYAIAB0AGgAZQAgAHQAcgBlAGEAdABtAGUAbgB0ACAAZgBhAGMAaQBsAGkAdAB5ACAAKABtADMAIABDAEgANAApAFwAbgBFAEMAXwBmAGwAYQByAGUAZAAgAD0AIABlAG4AZQByAGcAeQAgAGMAbwBuAHQAZQBuAHQAIABmAGEAYwB0AG8AcgAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAIABpAG4AIABzAGwAdQBkAGcAZQAgAGIAaQBvAGcAYQBzACAAZgBsAGEAcgBlAGQAIAAoAEcASgAvAG0AMwApAFwAbgBFAEYAXwBmAGwAYQByAGUAZABfAEMASAA0ACAAPQAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAcwBsAHUAZABnAGUAIABiAGkAbwBnAGEAcwAgAGYAbABhAHIAZQBkACAAKABrAGcAIABDAE8AMgBlAC8ARwBKACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8AMQAxAF8AMQBfADEAXwAxAF8AXwAxAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFcAYQBzAHQAZQB3AGEAdABlAHIAVAByAGUAYQB0AG0AZQBuAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAVwBfAHQALAAgAEMATwBEAF8AaQBuACwAIABGAF8AcwBsAHUAZABnAGUALAAgAEMATwBEAF8AbwB1AHQALAAgAEMARgBfAHcAdwBfAHQALAAgAEUARgBfAHcAdwAsACAARgBfAHIAZQBtAG8AdgBlAGQALAAgAEMARgBfAHMAbAB1AGQAZwBlAF8AdAAsACAARQBGAF8AcwBsAHUAZABnAGUALAAgAFEAXwBjAGEAcAAsACAAUQBfAGYAbABhAHIAZQBkACwAIABRAF8AbwB1AHQALAAgAEUAQwBfAGYAbABhAHIAZQBkACwAIABFAEYAXwBmAGwAYQByAGUAZABDAEgANAAsAFwAbgAgACAAIAAgACgAMQAvADEAMAAwADAAKQAgACoAIAAoACgAVwBfAHQAIAAqACAAKABDAE8ARABfAGkAbgAgACoAIAAoADEAIAAtACAARgBfAHMAbAB1AGQAZwBlACkAIAAtACAAQwBPAEQAXwBvAHUAdAApACAAKgAgAEMARgBfAHcAdwBfAHQAIAAqACAARQBGAF8AdwB3ACkAIAArACAAKABXAF8AdAAgACoAIAAoAEMATwBEAF8AaQBuACAAKgAgACgARgBfAHMAbAB1AGQAZwBlACAALQAgAEYAXwByAGUAbQBvAHYAZQBkACkAKQAgACoAIABDAEYAXwBzAGwAdQBkAGcAZQBfAHQAIAAqACAARQBGAF8AcwBsAHUAZABnAGUAKQAgAC0AIAAoADYALgA3ADgANAAgACoAIAAxADAAXgAtADQAIAAqACAAKABRAF8AYwBhAHAAIAArACAAUQBfAGYAbABhAHIAZQBkACAAKwAgAFEAXwBvAHUAdAApACkAIAArACAAKABRAF8AZgBsAGEAcgBlAGQAIAAqACAAKABFAEMAXwBmAGwAYQByAGUAZAAgACoAIABFAEYAXwBmAGwAYQByAGUAZABDAEgANAApACkAKQBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEAMQBfADEAXwAxAF8AMQBfAF8AMQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBXAGEAcwB0AGUAdwBhAHQAZQByAFQAcgBlAGEAdABtAGUAbgB0AF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAdwBhAHMAdABlAHcAYQB0AGUAcgAgAHQAcgBlAGEAdABtAGUAbgB0AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADEAXwAxAF8AMQBfADEAXwBfADEAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AVwBhAHMAdABlAHcAYQB0AGUAcgBUAHIAZQBhAHQAbQBlAG4AdABfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBfAEMASAA0AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADEAXwAxAF8AMQBfADEAXwBfADEAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AVwBhAHMAdABlAHcAYQB0AGUAcgBUAHIAZQBhAHQAbQBlAG4AdABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAEgANABcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQAxAF8AMQBfADEAXwAxAF8AXwAxAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFcAYQBzAHQAZQB3AGEAdABlAHIAVAByAGUAYQB0AG0AZQBuAHQAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAMQAxAC4AMQAuADEALgAxACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADEAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQAxAF8AMQBfADEAXwAxAF8AXwAxAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFcAYQBzAHQAZQB3AGEAdABlAHIAVAByAGUAYQB0AG0AZQBuAHQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAARwByAGUAZQBuAGgAbwB1AHMAZQAgAGEAbgBkACAARQBuAGUAcgBnAHkAIABSAGUAcABvAHIAdABpAG4AZwAgAE0AZQBhAHMAdQByAGUAbQBlAG4AdAAgAEQAZQB0AGUAcgBtAGkAbgBhAHQAaQBvAG4AIAAyADAAMAA4AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADEAXwAxAF8AMQBfADEAXwBfADEAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AVwBhAHMAdABlAHcAYQB0AGUAcgBUAHIAZQBhAHQAbQBlAG4AdABfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwB7AEMASAA0AH0APQBcAFwAZgByAGEAYwB7ADEAfQB7ADEAMAAwADAAfQBcAFwAdABpAG0AZQBzAFwAXABsAGUAZgB0AHsAXABcAGwAZQBmAHQAewBXAF8AdABcAFwAdABpAG0AZQBzAFwAXABsAGUAZgB0AFsAQwBPAEQAXwB7AGkAbgB9AFwAXAB0AGkAbQBlAHMAKAAxAC0ARgBfAHsAcwBsAHUAZABnAGUAfQApAC0AQwBPAEQAXwB7AG8AdQB0AH0AXABcAHIAaQBnAGgAdABdAFwAXAB0AGkAbQBlAHMAIABDAEYAXwB7AHcAdwAsAHQAfQBcAFwAdABpAG0AZQBzACAARQBGAF8AewB3AHcAfQBcAFwAcgBpAGcAaAB0AH0AKwBcAFwAbABlAGYAdAB7AFcAXwB0AFwAXAB0AGkAbQBlAHMAXABcAGwAZQBmAHQAWwBDAE8ARABfAHsAaQBuAH0AXABcAHQAaQBtAGUAcwAoAEYAXwB7AHMAbAB1AGQAZwBlAH0ALQBGAF8AewByAGUAbQBvAHYAZQBkAH0AKQBcAFwAcgBpAGcAaAB0AF0AXABcAHQAaQBtAGUAcwAgAEMARgBfAHsAcwBsAHUAZABnAGUALAB0AH0AXABcAHQAaQBtAGUAcwAgAEUARgBfAHsAcwBsAHUAZABnAGUAfQBcAFwAcgBpAGcAaAB0AH0ALQBcAFwAbABlAGYAdAB7ADYALgA3ADgANABcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADQAfQBcAFwAdABpAG0AZQBzACAAXABcAGwAZQBmAHQAWwAgAFEAXwB7AGMAYQBwAH0AKwBRAF8AewBmAGwAYQByAGUAZAB9ACsAUQBfAHsAbwB1AHQAfQBcAFwAcgBpAGcAaAB0AF0AXABcAHIAaQBnAGgAdAB9ACsAXABcAGwAZQBmAHQAewBRAF8AewBmAGwAYQByAGUAZAB9AFwAXAB0AGkAbQBlAHMAIABcAFwAbABlAGYAdABbACAARQBDAF8AewBmAGwAYQByAGUAZAB9AFwAXAB0AGkAbQBlAHMAIABFAEYAXwB7AGYAbABhAHIAZQBkACwAQwBIADQAfQBcAFwAcgBpAGcAaAB0AF0AXABcAHIAaQBnAGgAdAB9AFwAXAByAGkAZwBoAHQAfQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQAxAF8AMQBfADEAXwAxAF8AXwAxAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFcAYQBzAHQAZQB3AGEAdABlAHIAVAByAGUAYQB0AG0AZQBuAHQAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEANQAsACAANAAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAF8AdABcACIALAAgAFwAIgBxAHUAYQBuAHQAaQB0AHkAIABvAGYAIAB3AGEAcwB0AGUAdwBhAHQAZQByACAAdAByAGUAYQB0AGUAZAAgAGEAdAAgAGYAYQBjAGkAbABpAHQAeQAgAHQAeQBwAGUAIAB0AFwAIgAsACAAXAAiAG0AMwBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwBEAF8AaQBuAFwAIgAsACAAXAAiAGEAdgBlAHIAYQBnAGUAIABpAG4AbABlAHQAIABDAGgAZQBtAGkAYwBhAGwAIABPAHgAeQBnAGUAbgAgAEQAZQBtAGEAbgBkACAAYwBvAG4AYwBlAG4AdAByAGEAdABpAG8AbgAgAG8AZgAgAHcAYQBzAHQAZQB3AGEAdABlAHIAXAAiACwAIABcACIAawBnACAAQwBPAEQALwBtADMAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAF8AcwBsAHUAZABnAGUAXAAiACwAIABcACIAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAQwBPAEQAIAByAGUAbQBvAHYAZQBkACAAZgByAG8AbQAgAHcAYQBzAHQAZQB3AGEAdABlAHIAIABhAHMAIABzAGwAdQBkAGcAZQBcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAE8ARABfAG8AdQB0AFwAIgAsACAAXAAiAGEAdgBlAHIAYQBnAGUAIABvAHUAdABsAGUAdAAgAEMATwBEACAAYwBvAG4AYwBlAG4AdAByAGEAdABpAG8AbgAgAG8AZgAgAHcAYQBzAHQAZQB3AGEAdABlAHIAXAAiACwAIABcACIAawBnACAAQwBPAEQALwBtADMAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAEYAXwB3AHcAXwB0AFwAIgAsACAAXAAiAG0AZQB0AGgAYQBuAGUAIABjAG8AcgByAGUAYwB0AGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAGYAYQBjAGkAbABpAHQAeQAgAHQAeQBwAGUAIAB0ACAAdQBzAGUAZAAgAHQAbwAgAHQAcgBlAGEAdAAgAHcAYQBzAHQAZQB3AGEAdABlAHIAXAAiACwAIABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAF8AdwB3AFwAIgAsACAAXAAiAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAdwBhAHMAdABlAHcAYQB0AGUAcgBcACIALAAgAFwAIgBrAGcAIABDAEgANAAvAGsAZwAgAEMATwBEAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBfAHIAZQBtAG8AdgBlAGQAXAAiACwAIABcACIAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAQwBPAEQAIAByAGUAbQBvAHYAZQBkACAAZgByAG8AbQAgAHQAaABlACAAdwBhAHMAdABlAHcAYQB0AGUAcgAgAHQAcgBlAGEAdABtAGUAbgB0ACAAZgBhAGMAaQBsAGkAdAB5ACAAYQBuAGQAIAB0AHIAYQBuAHMAZgBlAHIAcgBlAGQAIABlAGwAcwBlAHcAaABlAHIAZQBcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAEYAXwBzAGwAdQBkAGcAZQBfAHQAXAAiACwAIABcACIAbQBlAHQAaABhAG4AZQAgAGMAbwByAHIAZQBjAHQAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAZgBhAGMAaQBsAGkAdAB5ACAAdAB5AHAAZQAgAHQAIAB1AHMAZQBkACAAdABvACAAdAByAGUAYQB0ACAAcwBsAHUAZABnAGUAXAAiACwAIABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAF8AcwBsAHUAZABnAGUAXAAiACwAIABcACIAbQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABzAGwAdQBkAGcAZQBcACIALAAgAFwAIgBrAGcAIABDAEgANAAvAGsAZwAgAEMATwBEAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUQBfAGMAYQBwAFwAIgAsACAAXAAiAHEAdQBhAG4AdABpAHQAeQAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAIABpAG4AIABzAGwAdQBkAGcAZQAgAGIAaQBvAGcAYQBzACAAYwBhAHAAdAB1AHIAZQBkACAAZgBvAHIAIABjAG8AbQBiAHUAcwB0AGkAbwBuAFwAIgAsACAAXAAiAG0AMwAgAEMASAA0AFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUQBfAGYAbABhAHIAZQBkAFwAIgAsACAAXAAiAHEAdQBhAG4AdABpAHQAeQAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAIABpAG4AIABzAGwAdQBkAGcAZQAgAGIAaQBvAGcAYQBzACAAZgBsAGEAcgBlAGQAIABiAHkAIAB0AGgAZQAgAHQAcgBlAGEAdABtAGUAbgB0ACAAZgBhAGMAaQBsAGkAdAB5AFwAIgAsACAAXAAiAG0AMwAgAEMASAA0AFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUQBfAG8AdQB0AFwAIgAsACAAXAAiAHEAdQBhAG4AdABpAHQAeQAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAIABpAG4AIABzAGwAdQBkAGcAZQAgAGIAaQBvAGcAYQBzACAAdAByAGEAbgBzAGYAZQByAHIAZQBkACAAbwB1AHQAIABvAGYAIAB0AGgAZQAgAHQAcgBlAGEAdABtAGUAbgB0ACAAZgBhAGMAaQBsAGkAdAB5AFwAIgAsACAAXAAiAG0AMwAgAEMASAA0AFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBDAF8AZgBsAGEAcgBlAGQAXAAiACwAIABcACIAZQBuAGUAcgBnAHkAIABjAG8AbgB0AGUAbgB0ACAAZgBhAGMAdABvAHIAIABvAGYAIABtAGUAdABoAGEAbgBlACAAaQBuACAAcwBsAHUAZABnAGUAIABiAGkAbwBnAGEAcwAgAGYAbABhAHIAZQBkAFwAIgAsACAAXAAiAEcASgAvAG0AMwBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARgBfAGYAbABhAHIAZQBkAEMASAA0AFwAIgAsACAAXAAiAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAcwBsAHUAZABnAGUAIABiAGkAbwBnAGEAcwAgAGYAbABhAHIAZQBkAFwAIgAsACAAXAAiAGsAZwAgAEMASAA0AC8ARwBKAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAdABcACIALAAgAFwAIgB0AHIAZQBhAHQAbQBlAG4AdAAgAGYAYQBjAGkAbABpAHQAeQAgAHQAeQBwAGUAXAAiACwAIABcACIAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAFYARQBFAFIARwBfADEAMQBfADEAXwAxAF8AMQBfAF8AMQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBXAGEAcwB0AGUAdwBhAHQAZQByAFQAcgBlAGEAdABtAGUAbgB0AF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBOACAAUwBPAFUAUgBDAEUAOgAgAEMAaABhAG4AZwBlAGQAIAB1AG4AaQB0AHMAIABvAGYAIABFAEYAXwB3AHcALAAgAEUARgBfAFMAbAB1AGQAZwBlACAAYQBuAGQAIABFAEYAXwBmAGwAYQByAGUAZAAgAGYAcgBvAG0AIABDAE8AMgBlACAAdABvACAAQwBIADQAIAB0AG8AIABtAGEAdABjAGgAIABkAGEAdABhACAAaQBuACAAVABhAGIAbABlACAAXAAiACkAOwAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBTAG8AdQByAGMAZQBEAGEAdABhACIALAAiAHQAZQB4AHQAIgA6ACIALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgBUAGEAYgBsAGUAIABBAC4ANAAuADEALgAzADoAIABNAGUAdABoAGEAbgBlACAAYwBvAHIAcgBlAGMAdABpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB0AHIAZQBhAHQAbQBlAG4AdAAgAGYAYQBjAGkAbABpAHQAeQAgAHQAeQBwAGUAIAB0ACAAdQBzAGUAZAAgAHQAbwAgAHQAcgBlAGEAdAAgAHcAYQBzAHQAZQB3AGEAdABlAHIAIAAoAGYAcgBhAGMAdABpAG8AbgApACAAKABDAEYAdwB3ACwAdAApAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEMAbwByAHIAZQBjAHQAaQBvAG4ARgBhAGMAdABvAHIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFQAaQB0AGwAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAE0AZQB0AGgAYQBuAGUAIABjAG8AcgByAGUAYwB0AGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHQAcgBlAGEAdABtAGUAbgB0ACAAZgBhAGMAaQBsAGkAdAB5ACAAdAB5AHAAZQAgAHQAIAB1AHMAZQBkACAAdABvACAAdAByAGUAYQB0ACAAdwBhAHMAdABlAHcAYQB0AGUAcgBcACIAKQApADsAXABuAFwAbgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEMAbwByAHIAZQBjAHQAaQBvAG4ARgBhAGMAdABvAHIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFYAYQByAGkAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEMARgB3AHcALAB0AFwAIgApACkAOwBcAG4AXABuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUAQwBvAHIAcgBlAGMAdABpAG8AbgBGAGEAYwB0AG8AcgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AVQBuAGkAdABcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIAKQApADsAXABuAFwAbgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEMAbwByAHIAZQBjAHQAaQBvAG4ARgBhAGMAdABvAHIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADQALgAxAC4AMwBcACIAKQApADsAXABuAFwAbgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEMAbwByAHIAZQBjAHQAaQBvAG4ARgBhAGMAdABvAHIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAEQAYQB0AGEAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANgAsACAAMgAsAFwAbgAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBGAGEAYwBpAGwAaQB0AHkAIAB0AHkAcABlACAAdABcACIALAAgAFwAIgBDAEYAdwB3ACwAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBNAGEAbgBhAGcAZQBkACAAYQBlAHIAbwBiAGkAYwAgAHQAcgBlAGEAdABtAGUAbgB0AFwAIgAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFUAbgBtAGEAbgBhAGcAZQBkACAAYQBlAHIAbwBiAGkAYwAgAHQAcgBlAGEAdABtAGUAbgB0AFwAIgAsACAAMAAuADMAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBBAG4AYQBlAHIAbwBiAGkAYwAgAGQAaQBnAGUAcwB0AG8AcgAvAHIAZQBhAGMAdABvAHIAXAAiACwAIAAwAC4AOAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFMAaABhAGwAbABvAHcAIABhAG4AYQBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuACAAKABkIiAAMgAgAG0AKQBcACIALAAgADAALgAyADsAXABuACAAIAAgACAAIAAgACAAIABcACIARABlAGUAcAAgAGEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AIAAoAFwAdQAwADAAMwBlACAAMgBtACkAXAAiACwAIAAwAC4AOABcAG4AIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgApACkAKQA7AFwAbgBcAG4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBDAG8AcgByAGUAYwB0AGkAbwBuAEYAYQBjAHQAbwByAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAFwAIgApACkAOwBcAG4AXABuAFwAbgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFQAYQBiAGwAZQAgAEEALgA0AC4AMQAuADQAOgAgAE0AZQB0AGgAYQBuAGUAIABjAG8AcgByAGUAYwB0AGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHQAcgBlAGEAdABtAGUAbgB0ACAAZgBhAGMAaQBsAGkAdAB5ACAAdAB5AHAAZQAgAHQAIAB1AHMAZQBkACAAdABvACAAdAByAGUAYQB0ACAAcwBsAHUAZABnAGUAIAAoAGYAcgBhAGMAdABpAG8AbgApACAAKABDAEYAcwBsAHUAZABnAGUALAB0ACkAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUAQwBvAHIAcgBlAGMAdABpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBfAFQAaQB0AGwAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAE0AZQB0AGgAYQBuAGUAIABjAG8AcgByAGUAYwB0AGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHQAcgBlAGEAdABtAGUAbgB0ACAAZgBhAGMAaQBsAGkAdAB5ACAAdAB5AHAAZQAgAHQAIAB1AHMAZQBkACAAdABvACAAdAByAGUAYQB0ACAAcwBsAHUAZABnAGUAXAAiACkAKQA7AFwAbgBcAG4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBDAG8AcgByAGUAYwB0AGkAbwBuAEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAQwBGAHMAbAB1AGQAZwBlACwAdABcACIAKQApADsAXABuAFwAbgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEMAbwByAHIAZQBjAHQAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAXwBVAG4AaQB0AFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgApACkAOwBcAG4AXABuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUAQwBvAHIAcgBlAGMAdABpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBfAFMAbwB1AHIAYwBlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADQALgAxAC4ANABcACIAKQApADsAXABuAFwAbgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEMAbwByAHIAZQBjAHQAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAXwBEAGEAdABhAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADIALABcAG4AIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIABcACIARgBhAGMAaQBsAGkAdAB5ACAAdAB5AHAAZQAgAHQAXAAiACwAIABcACIAQwBGAHMAbAB1AGQAZwBlACwAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBNAGEAbgBhAGcAZQBkACAAYQBlAHIAbwBiAGkAYwAgAHQAcgBlAGEAdABtAGUAbgB0AFwAIgAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFUAbgBtAGEAbgBhAGcAZQBkACAAYQBlAHIAbwBiAGkAYwAgAHQAcgBlAGEAdABtAGUAbgB0AFwAIgAsACAAMAAuADMAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBBAG4AYQBlAHIAbwBiAGkAYwAgAGQAaQBnAGUAcwB0AG8AcgAvAHIAZQBhAGMAdABvAHIAXAAiACwAIAAwAC4AOAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFMAaABhAGwAbABvAHcAIABhAG4AYQBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuACAAKABkIiAAMgAgAG0AKQBcACIALAAgADAALgAyADsAXABuACAAIAAgACAAIAAgACAAIABcACIARABlAGUAcAAgAGEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AIAAoAFwAdQAwADAAMwBlACAAMgBtACkAXAAiACwAIAAwAC4AOABcAG4AIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgApACkAKQA7AFwAbgBcAG4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBDAG8AcgByAGUAYwB0AGkAbwBuAEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBcACIAKQApADsAXABuAFwAbgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBUAGkAdABsAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBNAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHcAYQBzAHQAZQB3AGEAdABlAHIAXAAiACkAKQA7AFwAbgBcAG4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFYAYQByAGkAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEUARgB3AHcAXAAiACkAKQA7AFwAbgBcAG4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFUAbgBpAHQAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBrAGcAIABDAEgANAAgAC8AIABrAGcAIABDAE8ARABcACIAKQApADsAXABuAFwAbgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AUwBvAHUAcgBjAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAAxADEALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdABzAFwAIgApACkAOwBcAG4AXABuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBEAGEAdABhAFwAbgA9AEwAQQBNAEIARABBACgAIAAwAC4AMgA1ACkAOwBcAG4AXABuAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAXwBUAGkAdABsAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBNAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHMAbAB1AGQAZwBlAFwAIgApACkAOwBcAG4AXABuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIARQBGAHMAbAB1AGQAZwBlAFwAIgApACkAOwBcAG4AXABuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAF8AVQBuAGkAdABcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAGsAZwAgAEMASAA0ACAALwAgAGsAZwAgAEMATwBEAFwAIgApACkAOwBcAG4AXABuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAF8AUwBvAHUAcgBjAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAAxADEALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdABzAFwAIgApACkAOwBcAG4AXABuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAF8ARABhAHQAYQBcAG4APQBMAEEATQBCAEQAQQAoADAALgAyADUAKQA7AFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgBXAGEAcwB0AGUAXwBFAG4AZQByAGcAeQBDAG8AbgB0AGUAbgB0AEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAEIAaQBvAGcAYQBzAEYAbABhAHIAZQBkAF8AVABpAHQAbABlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIARQBuAGUAcgBnAHkAIABjAG8AbgB0AGUAbgB0ACAAZgBhAGMAdABvAHIAIABvAGYAIABzAGwAdQBkAGcAZQAgAGIAaQBvAGcAYQBzACAAZgBsAGEAcgBlAGQAXAAiACkAKQA7AFwAbgBcAG4AVwBhAHMAdABlAF8ARQBuAGUAcgBnAHkAQwBvAG4AdABlAG4AdABGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBCAGkAbwBnAGEAcwBGAGwAYQByAGUAZABfAFYAYQByAGkAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEUAQwBmAGwAYQByAGUAZABcACIAKQApADsAXABuAFwAbgBXAGEAcwB0AGUAXwBFAG4AZQByAGcAeQBDAG8AbgB0AGUAbgB0AEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAEIAaQBvAGcAYQBzAEYAbABhAHIAZQBkAF8AVQBuAGkAdABcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEcASgAgAC8AIABtADMAXAAiACkAKQA7AFwAbgBcAG4AVwBhAHMAdABlAF8ARQBuAGUAcgBnAHkAQwBvAG4AdABlAG4AdABGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBCAGkAbwBnAGEAcwBGAGwAYQByAGUAZABfAFMAbwB1AHIAYwBlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAMQAxAC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAcwBcACIAKQApADsAXABuAFwAbgBXAGEAcwB0AGUAXwBFAG4AZQByAGcAeQBDAG8AbgB0AGUAbgB0AEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAEIAaQBvAGcAYQBzAEYAbABhAHIAZQBkAF8ARABhAHQAYQBcAG4APQBMAEEATQBCAEQAQQAoADAALgAwADMANwA3ACkAOwBcAG4AXABuAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAQgBpAG8AZwBhAHMARgBsAGEAcgBlAGQAXwBUAGkAdABsAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBNAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHMAbAB1AGQAZwBlACAAYgBpAG8AZwBhAHMAIABmAGwAYQByAGUAZABcACIAKQApADsAXABuAFwAbgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBCAGkAbwBnAGEAcwBGAGwAYQByAGUAZABfAFYAYQByAGkAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEUARgBmAGwAYQByAGUAZAAsAEMASAA0AFwAIgApACkAOwBcAG4AXABuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAEIAaQBvAGcAYQBzAEYAbABhAHIAZQBkAF8AVQBuAGkAdABcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAGsAZwAgAEMASAA0ACAALwAgAEcASgBcACIAKQApADsAXABuAFwAbgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBCAGkAbwBnAGEAcwBGAGwAYQByAGUAZABfAFMAbwB1AHIAYwBlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAMQAxAC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAcwBcACIAKQApADsAXABuAFwAbgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBCAGkAbwBnAGEAcwBGAGwAYQByAGUAZABfAEQAYQB0AGEAXABuAD0ATABBAE0AQgBEAEEAKAAwAC4AMgAyADgAOQApADsAXABuAFwAbgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAFcAYQBzAHQAZQBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBCAGkAbwBnAGEAcwBGAGwAYQByAGUAZABfAFQAaQB0AGwAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAcwBsAHUAZABnAGUAIABiAGkAbwBnAGEAcwAgAGYAbABhAHIAZQBkAFwAIgApACkAOwBcAG4AXABuAFcAYQBzAHQAZQBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBCAGkAbwBnAGEAcwBGAGwAYQByAGUAZABfAFYAYQByAGkAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEUARgBmAGwAYQByAGUAZAAsAE4AMgBPAFwAIgApACkAOwBcAG4AXABuAFcAYQBzAHQAZQBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBCAGkAbwBnAGEAcwBGAGwAYQByAGUAZABfAFUAbgBpAHQAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBrAGcAIABOADIATwAgAC8AIABHAEoAXAAiACkAKQA7AFwAbgBcAG4AVwBhAHMAdABlAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAEIAaQBvAGcAYQBzAEYAbABhAHIAZQBkAF8AUwBvAHUAcgBjAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAAxADEALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdABzAFwAIgApACkAOwBcAG4AXABuAFcAYQBzAHQAZQBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBCAGkAbwBnAGEAcwBGAGwAYQByAGUAZABfAEQAYQB0AGEAXABuAD0ATABBAE0AQgBEAEEAKAAxAC4AMQAzADIAZQAtADQAKQA7AFwAbgAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBOADIATwBfAEUAcQB1AGEAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAxADEALgAxADoAIABXAGEAcwB0AGUAdwBhAHQAZQByAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAxADEALgAxAC4AMwAuADEAIABNAGUAdABoAG8AZAAgADEAIAAtACAATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAG8AbgBzAGkAdABlACAAVwBhAHMAdABlAHcAYQB0AGUAcgAgAE0AYQBuAGEAZwBlAG0AZQBuAHQAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwAxADEAXwAxAF8AMwBfADEAXwBfADEAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEYAbABhAHIAZQBkAEIAaQBvAGcAYQBzAFwAbgBOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAZgBsAGEAcgBlAGQAIABiAGkAbwBnAGEAcwBcAG4ARQBfAE4AMgBPAFwAbgB0ACAATgAyAE8AXABuAEUAXwB7AE4AMgBPAH0APQBcAFwAZgByAGEAYwB7AFEAXwB7AGYAbABhAHIAZQBkAH0AfQB7ADEAMAAwADAAfQBcAFwAdABpAG0AZQBzACAARQBGAF8AewBmAGwAYQByAGUAZAAsAE4AMgBPAH0AXABuAFEAXwBmAGwAYQByAGUAZAAgAD0AIAB2AG8AbAB1AG0AZQAgAG8AZgAgAGIAaQBvAGcAYQBzACAAZgBsAGEAcgBlAGQAIAAoAG0AMwAgAG8AcgAgAEcASgApAFwAbgBFAEYAXwBmAGwAYQByAGUAZABfAE4AMgBPACAAPQAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAZgBsAGEAcgBlAGQAIABiAGkAbwBnAGEAcwAgACgAawBnACAATgAyAE8ALwBHAEoAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwAxADEAXwAxAF8AMwBfADEAXwBfADEAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEYAbABhAHIAZQBkAEIAaQBvAGcAYQBzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFEAXwBmAGwAYQByAGUAZAAsACAARQBDAF8AZgBsAGEAcgBlAGQALAAgAEUARgBfAGYAbABhAHIAZQBkAE4AMgBPACwAXABuACAAIAAgACAAKABRAF8AZgBsAGEAcgBlAGQAIAAvACAAMQAwADAAMAApACAAKgAgACgARQBDAF8AZgBsAGEAcgBlAGQAIAAqACAARQBGAF8AZgBsAGEAcgBlAGQATgAyAE8AKQBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEAMQBfADEAXwAzAF8AMQBfAF8AMQBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ARgBsAGEAcgBlAGQAQgBpAG8AZwBhAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABmAGwAYQByAGUAZAAgAGIAaQBvAGcAYQBzAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADEAXwAxAF8AMwBfADEAXwBfADEAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEYAbABhAHIAZQBkAEIAaQBvAGcAYQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAF8ATgAyAE8AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEAMQBfADEAXwAzAF8AMQBfAF8AMQBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ARgBsAGEAcgBlAGQAQgBpAG8AZwBhAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgB0ACAATgAyAE8AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEAMQBfADEAXwAzAF8AMQBfAF8AMQBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ARgBsAGEAcgBlAGQAQgBpAG8AZwBhAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAMQAxAC4AMQAuADMALgAxACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADEAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQAxAF8AMQBfADMAXwAxAF8AXwAxAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBGAGwAYQByAGUAZABCAGkAbwBnAGEAcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQAxAF8AMQBfADMAXwAxAF8AXwAxAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBGAGwAYQByAGUAZABCAGkAbwBnAGEAcwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwB7AE4AMgBPAH0APQBcAFwAZgByAGEAYwB7AFEAXwB7AGYAbABhAHIAZQBkAH0AfQB7ADEAMAAwADAAfQBcAFwAdABpAG0AZQBzACAAXABcAGwAZQBmAHQAWwBFAEMAXwB7AGYAbABhAHIAZQBkAH0AIABcAFwAdABpAG0AZQBzACAARQBGAF8AewBmAGwAYQByAGUAZAAsAE4AMgBPAH0AXABcAHIAaQBnAGgAdABdAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADEAXwAxAF8AMwBfADEAXwBfADEAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEYAbABhAHIAZQBkAEIAaQBvAGcAYQBzAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAA0ACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEAXwBmAGwAYQByAGUAZABcACIALAAgAFwAIgB2AG8AbAB1AG0AZQAgAG8AZgAgAGIAaQBvAGcAYQBzACAAZgBsAGEAcgBlAGQAXAAiACwAIABcACIAbQAzAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBDAF8AZgBsAGEAcgBlAGQAXAAiACwAIABcACIAZQBuAGUAcgBnAHkAIABjAG8AbgB0AGUAbgB0ACAAZgBhAGMAdABvAHIAIABvAGYAIABzAGwAdQBkAGcAZQAgAGIAaQBvAGcAYQBzACAAZgBsAGEAcgBlAGQAXAAiACwAIABcACIARwBKAC8AbQAzAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAF8AZgBsAGEAcgBlAGQATgAyAE8AXAAiACwAIABcACIAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABmAGwAYQByAGUAZAAgAGIAaQBvAGcAYQBzAFwAIgAsACAAXAAiAGsAZwAgAE4AMgBPAC8ARwBKAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AIgB9AF0ALAAiAHAAcgBvAGoAZQBjAHQATgBhAG0AZQBzACIAOgBbACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEEAcABwAGUAbgBkAGkAYwBlAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAUgBvAHcAUwB0AGEAcgB0AE4AdQBtAGIAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAHIAYQB5AEkAbgBUAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUAVAB3AG8AQwBvAGwAdQBtAG4AcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBPAG4AZQBDAG8AbAB1AG0AbgBBAG4AZABIAGUAYQBkAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBTAHAAbABpAHQAUwB0AHIAaQBuAGcASQBuAHQAbwBBAHIAcgBhAHkAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQwBsAGkAbQBhAHQAZQBaAG8AbgBlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAEkAdABlAG0ARgByAG8AbQBNAGkAbgBNAGEAeAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBTAHUAbQBRAHUAYQBuAHQAaQB0AHkARgByAG8AbQBDAHIAaQB0AGUAcgBpAGEAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAUABlAHIAaQBvAGQAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEYAdQBuAGMAdABpAG8AbgBOAGEAbQBlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAE4AMgBPAEUARgBGAHIAbwBtAFAAcgBvAGQASQByAHIAaQBnAGEAdABpAG8AbgBSAGEAaQBuAGYAYQBsAGwAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBHAGUAdABGAHIAYQBjAFcARQBUACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEMAbwBuAHYAZQByAHQAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAVABvAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADEAXwAxAF8AMQBfADEAXwBfADEAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AVwBhAHMAdABlAHcAYQB0AGUAcgBUAHIAZQBhAHQAbQBlAG4AdAAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQAxAF8AMQBfADEAXwAxAF8AXwAxAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFcAYQBzAHQAZQB3AGEAdABlAHIAVAByAGUAYQB0AG0AZQBuAHQAXwBUAGkAdABsAGUAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEAMQBfADEAXwAxAF8AMQBfAF8AMQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBXAGEAcwB0AGUAdwBhAHQAZQByAFQAcgBlAGEAdABtAGUAbgB0AF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADEAXwAxAF8AMQBfADEAXwBfADEAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AVwBhAHMAdABlAHcAYQB0AGUAcgBUAHIAZQBhAHQAbQBlAG4AdABfAFUAbgBpAHQAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEAMQBfADEAXwAxAF8AMQBfAF8AMQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBXAGEAcwB0AGUAdwBhAHQAZQByAFQAcgBlAGEAdABtAGUAbgB0AF8AUwBvAHUAcgBjAGUAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEAMQBfADEAXwAxAF8AMQBfAF8AMQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBXAGEAcwB0AGUAdwBhAHQAZQByAFQAcgBlAGEAdABtAGUAbgB0AF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEAMQBfADEAXwAxAF8AMQBfAF8AMQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBXAGEAcwB0AGUAdwBhAHQAZQByAFQAcgBlAGEAdABtAGUAbgB0AF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQAxAF8AMQBfADEAXwAxAF8AXwAxAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFcAYQBzAHQAZQB3AGEAdABlAHIAVAByAGUAYQB0AG0AZQBuAHQAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQAxAF8AMQBfADEAXwAxAF8AXwAxAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFcAYQBzAHQAZQB3AGEAdABlAHIAVAByAGUAYQB0AG0AZQBuAHQAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUAQwBvAHIAcgBlAGMAdABpAG8AbgBGAGEAYwB0AG8AcgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AVABpAHQAbABlACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBDAG8AcgByAGUAYwB0AGkAbwBuAEYAYQBjAHQAbwByAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEMAbwByAHIAZQBjAHQAaQBvAG4ARgBhAGMAdABvAHIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFUAbgBpAHQAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEMAbwByAHIAZQBjAHQAaQBvAG4ARgBhAGMAdABvAHIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBDAG8AcgByAGUAYwB0AGkAbwBuAEYAYQBjAHQAbwByAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBEAGEAdABhACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBDAG8AcgByAGUAYwB0AGkAbwBuAEYAYQBjAHQAbwByAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUAQwBvAHIAcgBlAGMAdABpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBfAFQAaQB0AGwAZQAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUAQwBvAHIAcgBlAGMAdABpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUAQwBvAHIAcgBlAGMAdABpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBfAFUAbgBpAHQAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEMAbwByAHIAZQBjAHQAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAXwBTAG8AdQByAGMAZQAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUAQwBvAHIAcgBlAGMAdABpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBfAEQAYQB0AGEAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEMAbwByAHIAZQBjAHQAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBUAGkAdABsAGUAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFUAbgBpAHQAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AUwBvAHUAcgBjAGUAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBXAGEAcwB0AGUAdwBhAHQAZQByAF8ARABhAHQAYQAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAF8AVABpAHQAbABlACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBfAFUAbgBpAHQAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBfAFMAbwB1AHIAYwBlACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAXwBEAGEAdABhACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AVwBhAHMAdABlAF8ARQBuAGUAcgBnAHkAQwBvAG4AdABlAG4AdABGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBCAGkAbwBnAGEAcwBGAGwAYQByAGUAZABfAFQAaQB0AGwAZQAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFcAYQBzAHQAZQBfAEUAbgBlAHIAZwB5AEMAbwBuAHQAZQBuAHQARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAQgBpAG8AZwBhAHMARgBsAGEAcgBlAGQAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBXAGEAcwB0AGUAXwBFAG4AZQByAGcAeQBDAG8AbgB0AGUAbgB0AEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAEIAaQBvAGcAYQBzAEYAbABhAHIAZQBkAF8AVQBuAGkAdAAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFcAYQBzAHQAZQBfAEUAbgBlAHIAZwB5AEMAbwBuAHQAZQBuAHQARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAQgBpAG8AZwBhAHMARgBsAGEAcgBlAGQAXwBTAG8AdQByAGMAZQAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFcAYQBzAHQAZQBfAEUAbgBlAHIAZwB5AEMAbwBuAHQAZQBuAHQARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAQgBpAG8AZwBhAHMARgBsAGEAcgBlAGQAXwBEAGEAdABhACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAQgBpAG8AZwBhAHMARgBsAGEAcgBlAGQAXwBUAGkAdABsAGUAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBCAGkAbwBnAGEAcwBGAGwAYQByAGUAZABfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAEIAaQBvAGcAYQBzAEYAbABhAHIAZQBkAF8AVQBuAGkAdAAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAEIAaQBvAGcAYQBzAEYAbABhAHIAZQBkAF8AUwBvAHUAcgBjAGUAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBCAGkAbwBnAGEAcwBGAGwAYQByAGUAZABfAEQAYQB0AGEAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBXAGEAcwB0AGUAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAQgBpAG8AZwBhAHMARgBsAGEAcgBlAGQAXwBUAGkAdABsAGUAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBXAGEAcwB0AGUAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAQgBpAG8AZwBhAHMARgBsAGEAcgBlAGQAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBXAGEAcwB0AGUAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAQgBpAG8AZwBhAHMARgBsAGEAcgBlAGQAXwBVAG4AaQB0ACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AVwBhAHMAdABlAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAEIAaQBvAGcAYQBzAEYAbABhAHIAZQBkAF8AUwBvAHUAcgBjAGUAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBXAGEAcwB0AGUAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAQgBpAG8AZwBhAHMARgBsAGEAcgBlAGQAXwBEAGEAdABhACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBOADIATwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQAxAF8AMQBfADMAXwAxAF8AXwAxAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBGAGwAYQByAGUAZABCAGkAbwBnAGEAcwAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8ATgAyAE8AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEAMQBfADEAXwAzAF8AMQBfAF8AMQBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ARgBsAGEAcgBlAGQAQgBpAG8AZwBhAHMAXwBUAGkAdABsAGUAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAE4AMgBPAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADEAXwAxAF8AMwBfADEAXwBfADEAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEYAbABhAHIAZQBkAEIAaQBvAGcAYQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBOADIATwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQAxAF8AMQBfADMAXwAxAF8AXwAxAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBGAGwAYQByAGUAZABCAGkAbwBnAGEAcwBfAFUAbgBpAHQAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAE4AMgBPAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADEAXwAxAF8AMwBfADEAXwBfADEAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEYAbABhAHIAZQBkAEIAaQBvAGcAYQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAE4AMgBPAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADEAXwAxAF8AMwBfADEAXwBfADEAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEYAbABhAHIAZQBkAEIAaQBvAGcAYQBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAE4AMgBPAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADEAXwAxAF8AMwBfADEAXwBfADEAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEYAbABhAHIAZQBkAEIAaQBvAGcAYQBzAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8ATgAyAE8AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEAMQBfADEAXwAzAF8AMQBfAF8AMQBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ARgBsAGEAcgBlAGQAQgBpAG8AZwBhAHMAXwBBAHIAZwB1AG0AZQBuAHQAcwAiAF0ALAAiAGwAbwBjAGEAbABlACIAOgB7ACIAbABpAHMAdABTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAsACIALAAiAHIAbwB3AFMAZQBwAGEAcgBhAHQAbwByACIAOgAiADsAIgAsACIAYwBvAGwAdQBtAG4AUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgB0AGgAbwB1AHMAYQBuAGQAcwBTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAsACIALAAiAHQAaABvAHUAcwBhAG4AZABzAFAAbwBzAGkAdABpAG8AbgBzACIAOgBbADMAXQAsACIAZABlAGMAaQBtAGEAbABTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAuACIALAAiAGQAYQB0AGUATwByAGQAZQByACIAOgAiAEQATQBZACIALAAiAGMAdQByAHIAZQBuAGMAeQBTAHkAbQBiAG8AbAAiADoAIgAkACIALAAiAGkAcwBDAHUAcgByAGUAbgBjAHkAUwB5AG0AYgBvAGwATABlAGEAZAAiADoAdAByAHUAZQAsACIAaQBzAEMAdQByAHIAZQBuAGMAeQBTAGUAcABCAHkAUwBwAGEAYwBlACIAOgBmAGEAbABzAGUALAAiAHIAbwB3AEwAZQB0AHQAZQByACIAOgAiAFIAIgAsACIAYwBvAGwAdQBtAG4ATABlAHQAdABlAHIAIgA6ACIAQwAiACwAIgByAGMATABlAGYAdABCAHIAYQBjAGsAZQB0ACIAOgAiAFsAIgAsACIAcgBjAFIAaQBnAGgAdABCAHIAYQBjAGsAZQB0ACIAOgAiAF0AIgAsACIAcwB0AGEAdABlAG0AZQBuAHQAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIAOwAiACwAIgBsAG8AYwBhAGwAZQBOAGEAbQBlACIAOgAiAGUAbgAtAHUAcwAiAH0AfQA=</AFEJSONBlob>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD460F9D-420A-4723-B323-396E4D19EC9B}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="09eef6d6-daa8-4301-8f9f-b1ec38079286"/>
-    <ds:schemaRef ds:uri="7291119c-fce9-4911-96ae-b800be5dccd8"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="09eef6d6-daa8-4301-8f9f-b1ec38079286" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7291119c-fce9-4911-96ae-b800be5dccd8">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9A9CF321-0D35-4044-BC72-33748FE2B865}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
@@ -14019,7 +14037,7 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{809E3D44-A88D-4EBF-A307-6B8CE77A3361}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -14038,10 +14056,21 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6BE249C-20B1-4A62-BBCD-F2A46D88BCAB}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD460F9D-420A-4723-B323-396E4D19EC9B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="09eef6d6-daa8-4301-8f9f-b1ec38079286"/>
+    <ds:schemaRef ds:uri="7291119c-fce9-4911-96ae-b800be5dccd8"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/Excel/11_Wastewater_WIP_v02.xlsx
+++ b/Excel/11_Wastewater_WIP_v02.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\htdocs\zneagcrc\GAF-VEERG-Functions\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9297710D-CBA7-4A43-A6C8-494BE58D6622}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B807BA1-44C2-404C-B1E2-E854BDD9954D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4680" yWindow="4680" windowWidth="28800" windowHeight="15345" firstSheet="7" activeTab="7" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
+    <workbookView xWindow="3120" yWindow="3120" windowWidth="28800" windowHeight="15345" firstSheet="7" activeTab="7" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
   </bookViews>
   <sheets>
     <sheet name="Home" sheetId="71" r:id="rId1"/>
@@ -262,6 +262,11 @@
     <definedName name="Step3">#REF!</definedName>
     <definedName name="VEERG_11_1_1_1__1_MethaneEmissionsFromWastewaterTreatment_Result_Method1">'11.1.1-2 Wastewater CH4'!$E$30</definedName>
     <definedName name="VEERG_11_1_3_1__1_NitrousOxideEmissionsFromFlaredBiogas_Result_Method1">'11.1.3-4 Wastewater N2O'!$E$17</definedName>
+    <definedName name="Waste_EnergyContentFactorSludgeBiogasFlared_Data">'Constants - Wastewater'!$E$41</definedName>
+    <definedName name="Waste_MethaneEmissionFactorSludge_Data">'Constants - Wastewater'!$E$36</definedName>
+    <definedName name="Waste_MethaneEmissionFactorSludgeBiogasFlared_Data">'Constants - Wastewater'!$E$46</definedName>
+    <definedName name="Waste_MethaneEmissionFactorWastewater_Data">'Constants - Wastewater'!$E$31</definedName>
+    <definedName name="Waste_NitrousOxideEmissionFactorSludgeBiogasFlared_Data">'Constants - Wastewater'!$E$51</definedName>
     <definedName name="Wastewater_Methane_Equations.VEERG_11_1_1_1__1_MethaneEmissionsFromWastewaterTreatment">_xlfn.LAMBDA(_xlpm.W_t,_xlpm.COD_in,_xlpm.F_sludge,_xlpm.COD_out,_xlpm.CF_ww_t,_xlpm.EF_ww,_xlpm.F_removed,_xlpm.CF_sludge_t,_xlpm.EF_sludge,_xlpm.Q_cap,_xlpm.Q_flared,_xlpm.Q_out,_xlpm.EC_flared,_xlpm.EF_flaredCH4, (1 / 1000) * ((_xlpm.W_t * (_xlpm.COD_in * (1 - _xlpm.F_sludge) - _xlpm.COD_out) * _xlpm.CF_ww_t * _xlpm.EF_ww) + (_xlpm.W_t * (_xlpm.COD_in * (_xlpm.F_sludge - _xlpm.F_removed)) * _xlpm.CF_sludge_t * _xlpm.EF_sludge) - (6.784 * 10 ^ -4 * (_xlpm.Q_cap + _xlpm.Q_flared + _xlpm.Q_out)) + (_xlpm.Q_flared * (_xlpm.EC_flared * _xlpm.EF_flaredCH4))))</definedName>
     <definedName name="Wastewater_Methane_Equations.VEERG_11_1_1_1__1_MethaneEmissionsFromWastewaterTreatment_Arguments">_xlfn.LAMBDA(_xlfn.MAKEARRAY(15, 4, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"W_t","quantity of wastewater treated at facility type t","m3","Input";"COD_in","average inlet Chemical Oxygen Demand concentration of wastewater","kg COD/m3","Input";"F_sludge","fraction of COD removed from wastewater as sludge","fraction","Input";"COD_out","average outlet COD concentration of wastewater","kg COD/m3","Input";"CF_ww_t","methane correction factor for facility type t used to treat wastewater","fraction","Constant";"EF_ww","methane emission factor for wastewater","kg CH4/kg COD","Constant";"F_removed","fraction of COD removed from the wastewater treatment facility and transferred elsewhere","fraction","Input";"CF_sludge_t","methane correction factor for facility type t used to treat sludge","fraction","Constant";"EF_sludge","methane emission factor for sludge","kg CH4/kg COD","Constant";"Q_cap","quantity of methane in sludge biogas captured for combustion","m3 CH4","Input";"Q_flared","quantity of methane in sludge biogas flared by the treatment facility","m3 CH4","Input";"Q_out","quantity of methane in sludge biogas transferred out of the treatment facility","m3 CH4","Input";"EC_flared","energy content factor of methane in sludge biogas flared","GJ/m3","Constant";"EF_flaredCH4","methane emission factor for sludge biogas flared","kg CH4/GJ","Constant";"t","treatment facility type","","Input"}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Wastewater_Methane_Equations.VEERG_11_1_1_1__1_MethaneEmissionsFromWastewaterTreatment_LatexEquation">_xlfn.LAMBDA(_xlfn._LONGTEXT("E_{CH4}=\frac{1}{1000}\times\left{\left{W_t\times\left[COD_{in}\times(1-F_{sludge})-COD_{out}\right]\times CF_{ww,t}\times EF_{ww}\right}+\left{W_t\times\left[COD_{in}\times(F_{sludge}-F_{removed})\right]\times CF_{sludge,t}\times EF_{sludge}\right}-\left","{6.784\times 10^{-4}\times \left[ Q_{cap}+Q_{flared}+Q_{out}\right]\right}+\left{Q_{flared}\times \left[ EC_{flared}\times EF_{flared,CH4}\right]\right}\right}"))</definedName>
@@ -7722,7 +7727,7 @@
     </row>
     <row r="57" spans="4:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D57" s="1">
-        <f>F8*(F14*(1-F15)-F17)</f>
+        <f>X_Cell_Wastewater_QuantityInM3*(X_Cell_Wastewater_InletCOD*(1-X_Cell_Wastewater_FractionCODRemovedAsSludge)-X_Cell_Wastewater_OutletCOD)</f>
         <v>350</v>
       </c>
     </row>
@@ -8050,8 +8055,8 @@
       <c r="D8" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="E8" s="10" t="str" cm="1">
-        <f t="array" aca="1" ref="E8" ca="1">Common_InputFunctions.Utility_DisplayFunctionName(E30)</f>
+      <c r="E8" s="10" t="str">
+        <f ca="1">Common_InputFunctions.Utility_DisplayFunctionName(VEERG_11_1_1_1__1_MethaneEmissionsFromWastewaterTreatment_Result_Method1)</f>
         <v>=Wastewater_Methane_Equations.VEERG_11_1_1_1__1_MethaneEmissionsFromWastewaterTreatment</v>
       </c>
     </row>
@@ -8222,7 +8227,7 @@
         <v>Constant</v>
       </c>
       <c r="J19" s="44">
-        <f>'Constants - Wastewater'!$E$31</f>
+        <f>Waste_MethaneEmissionFactorWastewater_Data</f>
         <v>0.25</v>
       </c>
     </row>
@@ -8282,7 +8287,7 @@
         <v>Constant</v>
       </c>
       <c r="J22" s="44">
-        <f>'Constants - Wastewater'!$E$36</f>
+        <f>Waste_MethaneEmissionFactorSludge_Data</f>
         <v>0.25</v>
       </c>
     </row>
@@ -8362,7 +8367,7 @@
         <v>Constant</v>
       </c>
       <c r="J26" s="44">
-        <f>'Constants - Wastewater'!$E$41</f>
+        <f>Waste_EnergyContentFactorSludgeBiogasFlared_Data</f>
         <v>3.7699999999999997E-2</v>
       </c>
     </row>
@@ -8382,7 +8387,7 @@
         <v>Constant</v>
       </c>
       <c r="J27" s="44">
-        <f>'Constants - Wastewater'!$E$46</f>
+        <f>Waste_MethaneEmissionFactorSludgeBiogasFlared_Data</f>
         <v>0.22889999999999999</v>
       </c>
     </row>
@@ -8431,7 +8436,7 @@
       </c>
       <c r="F32" s="68"/>
       <c r="G32" s="26">
-        <f>E30</f>
+        <f>VEERG_11_1_1_1__1_MethaneEmissionsFromWastewaterTreatment_Result_Method1</f>
         <v>4.7159433000000001E-2</v>
       </c>
     </row>
@@ -8779,8 +8784,8 @@
       <c r="D7" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="E7" s="10" t="str" cm="1">
-        <f t="array" aca="1" ref="E7" ca="1">Common_InputFunctions.Utility_DisplayFunctionName(E17)</f>
+      <c r="E7" s="10" t="str">
+        <f ca="1">Common_InputFunctions.Utility_DisplayFunctionName(VEERG_11_1_3_1__1_NitrousOxideEmissionsFromFlaredBiogas_Result_Method1)</f>
         <v>=Wastewater_N2O_Equations.VEERG_11_1_3_1__1_NitrousOxideEmissionsFromFlaredBiogas</v>
       </c>
     </row>
@@ -8862,7 +8867,7 @@
         <v>Constant</v>
       </c>
       <c r="I14" s="44">
-        <f>'Constants - Wastewater'!E41</f>
+        <f>Waste_EnergyContentFactorSludgeBiogasFlared_Data</f>
         <v>3.7699999999999997E-2</v>
       </c>
     </row>
@@ -8881,7 +8886,7 @@
         <v>Constant</v>
       </c>
       <c r="I15" s="44">
-        <f>'Constants - Wastewater'!E51</f>
+        <f>Waste_NitrousOxideEmissionFactorSludgeBiogasFlared_Data</f>
         <v>1.132E-4</v>
       </c>
     </row>
@@ -8922,7 +8927,7 @@
       </c>
       <c r="F19" s="68"/>
       <c r="G19" s="26">
-        <f>E17</f>
+        <f>VEERG_11_1_3_1__1_NitrousOxideEmissionsFromFlaredBiogas_Result_Method1</f>
         <v>4.26764E-7</v>
       </c>
     </row>

--- a/Excel/11_Wastewater_WIP_v02.xlsx
+++ b/Excel/11_Wastewater_WIP_v02.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\htdocs\zneagcrc\GAF-VEERG-Functions\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B807BA1-44C2-404C-B1E2-E854BDD9954D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{045CF380-4903-4990-B5DA-D003B56E87C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="3120" windowWidth="28800" windowHeight="15345" firstSheet="7" activeTab="7" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
+    <workbookView xWindow="1350" yWindow="990" windowWidth="36255" windowHeight="19140" firstSheet="7" activeTab="7" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
   </bookViews>
   <sheets>
     <sheet name="Home" sheetId="71" r:id="rId1"/>
@@ -243,23 +243,6 @@
     <definedName name="Fertiliser_Equations_Lime.VEERG_5_3_1_1__1_LimeApplication">_xlfn.LAMBDA(_xlpm.Mlime,_xlpm.FracLime,_xlpm.Plime,_xlpm.EFlime,_xlpm.FracDol,_xlpm.Pdol,_xlpm.EFdol,_xlpm.CgCO2, ((_xlpm.Mlime * _xlpm.FracLime * _xlpm.Plime * _xlpm.EFlime) + (_xlpm.Mlime * _xlpm.FracDol * _xlpm.Pdol * _xlpm.EFdol)) * _xlpm.CgCO2 * 10 ^ -3)</definedName>
     <definedName name="Fertiliser_Equations_Organic.VEERG_5_2_1_1__2_MassOfNitrogenInOrganicFertiliser">_xlfn.LAMBDA(_xlpm.Morganicjf,_xlpm.FNorganicf, _xlpm.Morganicjf * _xlpm.FNorganicf)</definedName>
     <definedName name="getOverlappingReportingCycles">_xlfn.LAMBDA(_xlpm.ProductionCycleStart,_xlpm.ProductionCycleEnd,_xlpm.ReportingStartMonth,_xlpm.ReportingStartDay, _xlfn.LET(_xlpm.S, _xlpm.ProductionCycleStart, _xlpm.E, _xlpm.ProductionCycleEnd, _xlpm.m, _xlpm.ReportingStartMonth, _xlpm.d, _xlpm.ReportingStartDay, _xlpm.A, _xlpm.S - 364, _xlpm.ya, YEAR(_xlpm.A), _xlpm.yb, YEAR(_xlpm.E), _xlpm.firstYear, _xlpm.ya + (DATE(_xlpm.ya, _xlpm.m, _xlpm.d) &lt; _xlpm.A), _xlpm.lastYear, _xlpm.yb - (DATE(_xlpm.yb, _xlpm.m, _xlpm.d) &gt; _xlpm.E), MAX(0, _xlpm.lastYear - _xlpm.firstYear + 1)))</definedName>
-    <definedName name="Inoput_Cell_Livestock_antibiotics">#REF!</definedName>
-    <definedName name="Inoput_Cell_Livestockantibiotics">#REF!</definedName>
-    <definedName name="Input_Cell_CO2_for_carbonation">#REF!</definedName>
-    <definedName name="Input_Cell_CO2forcarbonation">#REF!</definedName>
-    <definedName name="Input_Cell_Livestock_antibiotics">#REF!</definedName>
-    <definedName name="Input_Cell_Livestock_tags">#REF!</definedName>
-    <definedName name="Input_Cell_LivestockAntibiotics">#REF!</definedName>
-    <definedName name="Input_Cell_Nylon_netting_for_horticulture">#REF!</definedName>
-    <definedName name="Input_Cell_Nylonnettingforhorticulture">#REF!</definedName>
-    <definedName name="Input_Cell_Pallets__Plastic">#REF!</definedName>
-    <definedName name="Input_Cell_Pallets__Wood">#REF!</definedName>
-    <definedName name="Input_Cell_Pallets_Plastic">#REF!</definedName>
-    <definedName name="Input_Cell_Pallets_Wood">#REF!</definedName>
-    <definedName name="Range_LivestockStartingValues">#REF!</definedName>
-    <definedName name="Step1">#REF!</definedName>
-    <definedName name="Step2">#REF!</definedName>
-    <definedName name="Step3">#REF!</definedName>
     <definedName name="VEERG_11_1_1_1__1_MethaneEmissionsFromWastewaterTreatment_Result_Method1">'11.1.1-2 Wastewater CH4'!$E$30</definedName>
     <definedName name="VEERG_11_1_3_1__1_NitrousOxideEmissionsFromFlaredBiogas_Result_Method1">'11.1.3-4 Wastewater N2O'!$E$17</definedName>
     <definedName name="Waste_EnergyContentFactorSludgeBiogasFlared_Data">'Constants - Wastewater'!$E$41</definedName>
@@ -13928,15 +13911,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100ACB660BB23738846A00119B5826AC974" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3e3613359d4ae7f6bda6c57be713f101">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="7291119c-fce9-4911-96ae-b800be5dccd8" xmlns:ns3="09eef6d6-daa8-4301-8f9f-b1ec38079286" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="87491bfad7f11426ad96486e70428b3e" ns2:_="" ns3:_="">
     <xsd:import namespace="7291119c-fce9-4911-96ae-b800be5dccd8"/>
@@ -14131,11 +14105,16 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgAvAC8AIAAtAC0ALQAgAFcAbwByAGsAYgBvAG8AawAgAG0AbwBkAHUAbABlACAALQAtAC0AXABuAC8ALwAgAEEAIABmAGkAbABlACAAbwBmACAAbgBhAG0AZQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAG8AZgAgAHQAaABlACAAZgBvAHIAbQA6AFwAbgAvAC8AIAAgACAAIABuAGEAbQBlACAAPQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AOwBcAG4AXABuACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhACIALAAiAHQAZQB4AHQAIgA6ACIALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgBTAG8AdQByAGMAZQAgAGQAYQB0AGEAIAB0AGgAYQB0ACAAaQBzACAAYwBvAG0AbQBvAG4AIABhAGMAcgBvAHMAcwAgAGEAbABsACAAZQBuAHQAZQByAHAAcgBpAHMAZQAgAHQAeQBwAGUAcwBcAG4ARQB4AGMAZQBsACAAbQBvAGQAdQBsAGUAIABuAGEAbQBlADoAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFMAbwB1AHIAYwBlADoAIABOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQBcAG4ATgBJAFIAXwAyADAAMgAzAF8AVgBvAGwAMQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXABuAHAAIAA9ACAAZABlAG4AcwBpAHQAeQAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAIAAoADAALgA2ADcAOAA0ACAAawBnAC8AbQAzACkAXABuAFQAYQBrAGUAbgAgAGYAcgBvAG0AIAB0AGgAZQAgAE4AYQB0AGkAbwBuAGEAbAAgAEcAcgBlAGUAbgBoAG8AdQBzAGUAIABhAG4AZAAgAEUAbgBlAHIAZwB5ACAAUgBlAHAAbwByAHQAaQBuAGcAIABcAG4AKABNAGUAYQBzAHUAcgBlAG0AZQBuAHQAKQAgAEQAZQB0AGUAcgBtAGkAbgBhAHQAaQBvAG4AIAAyADAAMAA4AFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHAAIAA9ACAAZABlAG4AcwBpAHQAeQAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcALwBtADMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgADIAMAAyADMAIABWAG8AbAB1AG0AZQAgADEAOgAgAEUAcQB1AGEAdABpAG8AbgBzACAAMwAuAEIALgAxAGEAXwAyACwAIAAzAC4AQgAuADEAYwBfADIALAAgADMALgBCAC4AMwBfADEALAAgADMALgBCAC4ANABnAF8AMgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAMAAuADYANwA4ADQAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAFwAbgBDAGcAIAA9ACAANAA0AC8AMgA4ACAAZgBhAGMAdABvAHIAIAB0AG8AIABjAG8AbgB2AGUAcgB0ACAAZQBsAGUAbQBlAG4AdABhAGwAIABtAGEAcwBzACAAbwBmACAATgAyAE8AIAB0AG8AIABtAG8AbABlAGMAdQBsAGEAcgAgAG0AYQBzAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABOADIATwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBDAGcATgAyAE8AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAYQBjAHQAbwByAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgADIAMAAyADMAIABWAG8AbAB1AG0AZQAgADEAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgANAA0AC8AMgA4ACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAFwAbgBGAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABnAGEAcwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgBhAGMAdABvAHIAIAB0AG8AIABjAG8AbgB2AGUAcgB0ACAAZQBsAGUAbQBlAG4AdABhAGwAIABtAGEAcwBzACAAbwBmACAAZwBhAHMAIAB0AG8AIABtAG8AbABlAGMAdQBsAGEAcgAgAG0AYQBzAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBDAGcAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgBhAGMAdABvAHIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFgAWABYAFgAWABYAFgAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADgALAAgADQALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAYQBzAFwAIgAsACAAXAAiAEMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBcACIALAAgAFwAIgBDAG8AbgB2AGUAcgBzAGkAbwBuACAAZgBhAGMAdABvAHIAIAAxAFwAIgAsACAAXAAiAEMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgADIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyAFwAIgAsACAAXAAiADQANAAvADEAMgBcACIALAAgADQANAAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMASAA0AFwAIgAsACAAXAAiADEANgAvADEAMgBcACIALAAgADEANgAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AMgBPAFwAIgAsACAAXAAiADQANAAvADIAOABcACIALAAgADQANAAsACAAMgA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB4AFwAIgAsACAAXAAiADQANgAvADEANABcACIALAAgADQANgAsACAAMQA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwBcACIALAAgAFwAIgAyADgALwAxADIAXAAiACwAIAAyADgALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAE8AMgAgAEwAaQBtAGUAXAAiACwAIABcACIANAA0AC8AMQAyAFwAIgAsACAANAA0ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBNAFYATwBDAFwAIgAsACAAXAAiADEANAAvADEAMgBcACIALAAgADEANAAsACAAMQAyAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABOADIATwBcAG4ARwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAGcAcgBlAGUAbgBoAG8AdQBzAGUAIABnAGEAcwBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABnAHIAZQBlAG4AaABvAHUAcwBlACAAZwBhAHMAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARwBXAFAATgAyAE8AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgBhAGMAdABvAHIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFgAWABYAFgAWABYAFgAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADgALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAYQBzAFwAIgAsACAAXAAiAEMATwAyAC0AZQAgAGYAYQBjAHQAbwByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAE8AMgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBIADQAXAAiACwAIAAyADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgAyAE8AXAAiACwAIAAyADYANQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAEYANABcACIALAAgADYANgAzADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwAyAEYANgBcACIALAAgADEAMgAyADAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAEYANgBcACIALAAgADIAMgA4ADAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAEYAMwBcACIALAAgADEANwAyADAAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAcwB0AGEAdABlAHMAIABhAG4AZAAgAHQAZQByAHIAaQB0AG8AcgBpAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA5ACwAIAAzACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHQAYQB0AGUALwBUAGUAcgByAGkAdABvAHIAeQBcACIALAAgAFwAIgBDAG8AbQBtAG8AbgAgAE4AYQBtAGUAXAAiACwAIABcACIAQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AZQB3ACAAUwBvAHUAdABoACAAVwBhAGwAZQBzAFwAIgAsACAAXAAiAE4AZQB3ACAAUwBvAHUAdABoACAAVwBhAGwAZQBzAFwAIgAsACAAXAAiAE4AUwBXAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAQwBhAHAAaQB0AGEAbAAgAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAEEAQwBUAFwAIgAsACAAXAAiAEEAQwBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAGkAYwB0AG8AcgBpAGEAXAAiACwAIABcACIAVgBpAGMAdABvAHIAaQBhAFwAIgAsACAAXAAiAFYASQBDAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBRAHUAZQBlAG4AcwBsAGEAbgBkAFwAIgAsACAAXAAiAFEAdQBlAGUAbgBzAGwAYQBuAGQAXAAiACwAIABcACIAUQBMAEQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAbwB1AHQAaAAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFMAbwB1AHQAaAAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFMAQQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQBcACIALAAgAFwAIgBXAEEAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAYQBzAG0AYQBuAGkAYQBcACIALAAgAFwAIgBUAGEAcwBtAGEAbgBpAGEAXAAiACwAIABcACIAVABBAFMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwByAHQAaABlAHIAbgAgAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAE4AbwByAHQAaABlAHIAbgAgAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAE4AVABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQBCAFMAIABTAHQAYQB0AGkAcwB0AGMAYQBsACAAQQByAGUAYQBzACAATABlAHYAZQBsACAANAAgAC0AIABXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAEIAdQByAGUAYQB1ACAAbwBmACAAUwB0AGEAdABpAHMAdABpAGMAcwAgACgAQQBCAFMAKQAgAC0AIABTAHQAYQB0AGkAcwB0AGkAYwBhAGwAIABBAHIAZQBhAHMAIABMAGUAdgBlAGwAIAAyACAALQAgADIAMAAyADEAIAAtACAAUwBoAGEAcABlAGYAaQBsAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADEALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAQQAgADQAIABOAGEAbQBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBCAHUAbgBiAHUAcgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAGEAbgBkAHUAcgBhAGgAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABJAG4AbgBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABOAG8AcgB0AGgAIABFAGEAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAATgBvAHIAdABoACAAVwBlAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAFMAbwB1AHQAaAAgAEUAYQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABTAG8AdQB0AGgAIABXAGUAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAAVwBoAGUAYQB0ACAAQgBlAGwAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhACAALQAgAE8AdQB0AGIAYQBjAGsAIAAoAE4AbwByAHQAaAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAATwB1AHQAYgBhAGMAawAgACgAUwBvAHUAdABoACkAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAdwBlAHQAIABhAG4AZAAgAGQAcgB5ACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAyADoAIABUAHIAYQBuAHMAbABhAHQAaQBuAGcAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBzACAAdABvACAAdwBlAHQAIABhAG4AZAAgAGQAcgB5ACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAdwBhAHIAbQAgAC8AIABjAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAvACAAZAByAHkAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAIABhAG4AZAAgAGgAaQBnAGgAIAB0AGUAbQBwACAAYwBsAGEAcwBzAGUAcwAgAHQAbwAgAGEAYwBjAG8AbQBtAG8AZABhAHQAZQAgAGMAbABpAG0AYQB0AGUAIABzAGMAZQBuAGEAcgBpAG8AcwAgAGUAeABjAGwAdQBkAGUAZAAgAGIAeQAgAFYARQBFAFIARwAgAGMAcgBpAHQAZQByAGkAYQAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAGkAeABlAGQAIAB0AHkAcABvACAALQAgAEMAaABhAG4AZwBlAGQAIABcAHUAMAAwADIANwBGAHIAeQBcAHUAMAAwADIANwAgAHQAbwAgAFwAdQAwADAAMgA3AEQAcgB5AFwAdQAwADAAMgA3AC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADUALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAFcAZQB0ACAAbwByACAARAByAHkAIABaAG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABtAG8AbgB0AGEAbgBlAFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAHcAZQB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABkAHIAeQBcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdABcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAtACAAaABpAGcAaAAgAHQAZQBtAHAAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAaABpAGcAaAAgAHQAZQBtAHAAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA1ACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAB3AGEAcgBtACAALwAgAGMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC8AIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdAAgAGEAbgBkACAAaABpAGcAaAAgAHQAZQBtAHAAIABjAGwAYQBzAHMAZQBzACAAdABvACAAYQBjAGMAbwBtAG0AbwBkAGEAdABlACAAYwBsAGkAbQBhAHQAZQAgAHMAYwBlAG4AYQByAGkAbwBzACAAZQB4AGMAbAB1AGQAZQBkACAAYgB5ACAAVgBFAEUAUgBHACAAYwByAGkAdABlAHIAaQBhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAaQB4AGUAZAAgAHQAeQBwAG8AIABpAG4AIABNAEEAVAAgAHYAYQBsAHUAZQAgAGYAbwByACAAdwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAYwBoAGEAbgBnAGUAZAAgADEAMAAgAHQAbwAgADEAMQAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIABtAGkAbgAgAGEAbgBkACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAZgBvAHIAIABNAEEAVAAsACAATQBBAFAALAAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAIABwAGUAcgAgAHkAZQBhAHIALAAgAGUAbABlAHYAYQB0AGkAbwBuACwAIABNAEEAUAA6AFAARQBUACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlAHMAIABmAHIAbwBtACAAcgBlAGEAbAAgAGMAbABpAG0AYQB0AGUAIABkAGEAdABhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAQQBGACAAYQBjAGMAZQBwAHQAcwAgAHIAYQBpAG4AZgBhAGwAbAAgAGEAcwAgAGEAIABwAHIAbwB4AHkAIABmAG8AcgAgAHAAcgBlAGMAaQBwAGkAdABhAHQAaQBvAG4ALgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOQAsACAAMQA2ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAGwAaQBtAGEAdABlACAAWgBvAG4AZQBcACIALAAgAFwAIgBNAEEAVABcACIALAAgAFwAIgBNAEEAUABcACIALAAgAFwAIgBGAHIAbwBzAHQAIABkAGEAeQBzACAAcABlAHIAIAB5AGUAYQByAFwAIgAsACAAXAAiAEUAbABlAHYAYQB0AGkAbwBuAFwAIgAsACAAXAAiAE0AQQBQADoAUABFAFQAXAAiACwAIABcACIATQBpAG4AIAB0AGUAbQBwAFwAIgAsACAAXAAiAE0AYQB4ACAAdABlAG0AcABcACIALAAgAFwAIgBNAGkAbgAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBNAGEAeAAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBNAGkAbgAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAXAAiACwAIABcACIATQBhAHgAIABmAHIAbwBzAHQAIABkAGEAeQBzAFwAIgAsACAAXAAiAE0AaQBuACAAZQBsAGUAdgBhAHQAaQBvAG4AXAAiACwAIABcACIATQBhAHgAIABlAGwAZQB2AGEAdABpAG8AbgBcACIALAAgAFwAIgBNAGkAbgAgAE0AQQBQADoAUABFAFQAXAAiACwAIABcACIATQBpAG4AIABNAEEAUAA6AFAARQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABtAG8AbgB0AGEAbgBlAFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQA4ACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAwADAAIABtAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAMQA4AC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAANwAsACAAMQAwADAAMAAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAHcAZQB0AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQA4ACAAQwBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADIAMAAwADAAIABtAG0AXAAiACwAIABcACIAZCIgADcAXAAiACwAIABcACIAZCIgADEAMAAwADAAIABtAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAMQA4AC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAyADAAMAAwAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQAuADkAOQA5ACwAIAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAOAAgAEMAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADAAMAAwACAAbQBtACAALQAgAGQiIAAyADAAMAAwACAAbQBtAFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgADEAOAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAAMQAwADAAMAAuADAAMAAxACwAIAAyADAAMAAwACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQAuADkAOQA5ACwAIAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAGQAcgB5AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQA4ACAAQwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAwADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAXAAiACwAIAAxADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgADEALgAwADAAMQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAGQiIAAxAFwAIgAsACAAMQAwAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAgAC0AOQA5ADkAOQA5ADkALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMAAgAEMAIAAtACAAZCIgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxAFwAIgAsACAALQA5ADkAOQA5ADkAOQAsACAAMQAwACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAxAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMAAgAEMAIAAtACAAZCIgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAZCIgADEAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAMQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBBAHAAcABlAG4AZABpAGMAZQBzAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdABlADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AQQBUACAAPQAgAG0AZQBhAG4AIABhAG4AbgB1AGEAbAAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBBAFAAIAA9ACAAbQBlAGEAbgAgAGEAbgBuAHUAYQBsACAAcAByAGUAYwBpAHAAaQB0AGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABFAFQAIAA9ACAAcABvAHQAZQBuAHQAaQBhAGwAIABlAHYAYQBwAG8AdAByAGEAbgBzAHAAaQByAGEAdABpAG8AbgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABBAGQAZABlAGQAIABlAHgAdAByAGEAIABNAEEAVAAgAG0AaQBuACAAYQBuAGQAIABNAEEAVAAgAG0AYQB4ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGMAYQBsAGMAdQBsAGEAdABlACAAegBvAG4AZQAgAGYAcgBvAG0AIAByAGUAYQBsACAAdABlAG0AcABlAHIAYQB0AHUAcgBlACAAZABhAHQAYQAuAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANAAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AHUAcgBlACAAWgBvAG4AZQBcACIALAAgAFwAIgBNAGUAZABpAGEAbgAgAEEAbgBuAHUAYQBsACAAVABlAG0AcABlAHIAYQB0AHUAcgBlACAAKABNAEEAVAApAFwAIgAsACAAXAAiAE0AaQBuACAATQBBAFQAXAAiACwAIABcACIATQBhAHgAIABNAEEAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgAFwAIgBlIiAAMgA2ACAAQwBcACIALAAgADIANgAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIABcACIAMQA1ACAALQAgADIANQAgAEMAXAAiACwAIAAxADUALAAgADIANQAuADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIABcACIAZCIgADEANAAgAEMAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADQALgA5ADkAOQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAAQQBkAGQAZQBkACAAZQB4AHQAcgBhACAAUgBhAGkAbgBmAGEAbABsACAAbQBpAG4AIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAG0AYQB4ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGMAYQBsAGMAdQBsAGEAdABlACAAegBvAG4AZQAgAGYAcgBvAG0AIAByAGUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAZABhAHQAYQAuAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBhAGkAbgBmAGEAbABsACAAWgBvAG4AZQBcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABtAGkAbgBcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABtAGEAeABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbAAgAFwAdQAwADAAMwBlACAANgAwADAAbQBtAFwAIgAsACAANgAwADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATABvAHcAIAByAGEAaQBuAGYAYQBsAGwAXAAiACwAIABcACIAQQBuAG4AdQBhAGwAIAByAGEAaQBuAGYAYQBsAGwAIABkIiAANgAwADAAbQBtAFwAIgAsACAALQA5ADkAOQA5ADkAOQAsACAANgAwADAAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABaAG8AbgBlAFwAIgAsACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAGMAcgBpAHQAZQByAGkAYQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATABlAGEAYwBoAGkAbgBnACAAbwBjAGMAdQByAHMAXAAiACwAIABcACIAowMoADXYX9w12E7cNdhW3DXYW9wpAFwAdQAwADAAMwBlAKMDKAA12DjcNdhH3DAAKQArADXYYNw12FzcNdhW3DXYWdwgADXYZNw12E7cNdhh3DXYUtw12F/cIAAOITXYXNw12FncNdhR3DXYVtw12FvcNdhU3CAANdhQ3DXYTtw12F3cNdhO3DXYUNw12FbcNdhh3DXYZtxcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATABlAGEAYwBoAGkAbgBnACAAZABvAGUAcwAgAG4AbwB0ACAAbwBjAGMAdQByAFwAIgAsACAAXAAiAKMDKAA12F/cNdhO3DXYVtw12FvcKQBkIqMDKAA12DjcNdhH3DAAKQArADXYYNw12FzcNdhW3DXYWdwgADXYZNw12E7cNdhh3DXYUtw12F/cIAAOITXYXNw12FncNdhR3DXYVtw12FvcNdhU3CAANdhQ3DXYTtw12F3cNdhO3DXYUNw12FbcNdhh3DXYZtxcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXABuADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAbgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAEQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcwAgAGkAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAXAAiACwAXAAiAEYAcgBhAGMAVwBFAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFkAZQBzACAALQAgAGkAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwAgAC0AIABuAG8AdAAgAGkAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAXAAiACwAIAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoACgAXAAiAFwAIgApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAGQAYQB0AGEAIABzAGMAbwByAGUAcwAgAGYAbwByACAAcwBjAG8AcABlACAAMwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABYAFgAWABYAFgAWABYAFgAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABhAHQAYQAgAHMAbwB1AHIAYwBlAFwAIgAsACAAXAAiAEQAYQB0AGEAIABzAGMAbwByAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAbgB0AGUAcgBuAGEAdABpAG8AbgBhAGwAIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAcwBjAG8AcABlACAAMwAgAGQAYQB0AGEAYgBhAHMAZQBcACIALAAgADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB0AGEAdABlACAAbwByACAAcgBlAGcAaQBvAG4AYQBsACAAcwBjAG8AcABlACAAMwAgAGQAYQB0AGEAYgBhAHMAZQBcACIALAAgADMAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBtAGkAcwBzAGkAbwBuAHMAIABpAG4AdABlAG4AcwBpAHQAeQAgAGMAYQBsAGMAdQBsAGEAdABlAGQAIABmAHIAbwBtACAAYQBwAHAAcgBvAHYAZQBkACAAbQBlAHQAaABvAGQAXAAiACwAIAA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAZQByAGkAZgBpAGUAZAAgAGMAcgBlAGQAZQBuAHQAaQBhAGwAIABtAGEAdABjAGgAaQBuAGcAIABJAFMATwAxADQAMAA2ADcAXAAiACwAIAA1AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXABuADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAbgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgARABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAVgBvAGwAdQBtAGUAIAAxADoAIABMAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmACAAKAAzAC4ARAAuAGIALgAyACkAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAcgBhAGMATABFAEEAQwBIAFwAIgAsADAALgAyADQAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoACgAXAAiAFwAIgApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABuAGkAdAByAG8AZwBlAG4AIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABuAGkAdAByAG8AZwBlAG4AIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABrAGcAIABOADIATwAtAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgAFYAbwBsAHUAbQBlACAAMQA6ACAARQBxAHUAYQB0AGkAbwBuACAAMwAuAEQALgBCAF8AMQAwAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARgBsAGUAYQBjAGgAXAAiACwAMAAuADAAMQAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoACgAXAAiAFwAIgApACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXABuAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADEAXABuAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAZgBvAHIAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AIAAoAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AKQAgACgARQBGAE4AMgBPACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAGYAbwByACAAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAGsAZwAgAE4AMgBPAC0ATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADIALgAyAC4AMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQA1ACwAIAA1ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABqAFwAIgAsAFwAIgBFAEYATgAyAE8AXAAiACwAIABcACIAUAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAbwBuAGwAeQBcACIALAAgAFwAIgBJAHIAcgBpAGcAYQB0AGkAbwBuACAAbQBlAHQAaABvAGQAXAAiACwAIABcACIAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsADAALgAwADAANQA5ACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwAFwAIgAsADAALgAwADAANwAsACAAXAAiAEMAcgBvAHAAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsADAALgAwADAAMQA4ACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEwAbwB3ACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQBcACIALAAwAC4AMAAwADEAOAAsACAAXAAiAFAAYQBzAHQAdQByAGUAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcAAgACgAbABvAHcAIAByAGEAaQBuAGYAYQBsAGwAKQBcACIALAAwAC4AMAAwADIAOQAsACAAXAAiAEMAcgBvAHAAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAGMAcgBvAHAAIAAoAGgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAKQBcACIALAAwAC4AMAAwADgALAAgAFwAIgBDAHIAbwBwAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIASABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB1AGcAYQByAFwAIgAsADAALgAwADEAOQA5ACwAIABcACIAUwB1AGcAYQByAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AdAB0AG8AbgBcACIALAAwAC4AMAAwADUAMwAsACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAG8AcgB0AGkAYwB1AGwAdAB1AHIAYQBsACAAYwByAG8AcABzAFwAIgAsADAALgAwADAANgA0ACwAIABcACIASABvAHIAdABpAGMAdQBsAHQAdQByAGEAbAAgAGMAcgBvAHAAcwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBpAGMAZQAgACgAYwBvAG4AdABpAG4AdQBvAHUAcwAgAGYAbABvAG8AZABpAG4AZwApAFwAIgAsADAALgAwADAAMwAsACAAXAAiAFIAaQBjAGUAXAAiACwAIABcACIAQwBvAG4AdABpAG4AdQBvAHUAcwAgAGYAbABvAG8AZABpAG4AZwBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBpAGMAZQAgACgAcwBpAG4AZwBsAGUAIABhAG4AZAAgAG0AdQBsAHQAaQBwAGwAZQAgAGQAcgBhAGkAbgBhAGcAZQAsACAAbwByACAAYQBsAHQAZQByAG4AYQB0AGUAIAB3AGUAdAB0AGkAbgBnACAAYQBuAGQAIABkAHIAeQBpAG4AZwApAFwAIgAsADAALgAwADAANQAsACAAXAAiAFIAaQBjAGUAXAAiACwAIABcACIAUwBpAG4AZwBsAGUAIABhAG4AZAAgAG0AdQBsAHQAaQBwAGwAZQAgAGQAcgBhAGkAbgBhAGcAZQAsACAAbwByACAAYQBsAHQAZQByAG4AYQB0AGUAIAB3AGUAdAB0AGkAbgBnACAAYQBuAGQAIABkAHIAeQBpAG4AZwBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBxAHUAYQBjAHUAbAB0AHUAcgBlAFwAIgAsADAALgAwADAAMgA2ACwAIABcACIAQQBxAHUAYQBjAHUAbAB0AHUAcgBlAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAG8AcgBlAHMAdAByAHkAXAAiACwAMAAuADAAMAAxADgALAAgAFwAIgBGAG8AcgBlAHMAdAByAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA1ACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGUAbQBvAHYAZQBkACAAZAB1AHAAbABpAGMAYQB0AGUAIABcAHUAMAAwADIANwBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAB1ADAAMAAyADcAIAByAG8AdwAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGUAbQBvAHYAZQBkACAAYQBzAHQAZQByAGkAcwBrAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAFwAdQAwADAAMgA3AHAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAG8AbgBsAHkAXAB1ADAAMAAyADcALAAgAFwAdQAwADAAMgA3AHIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAXAB1ADAAMAAyADcAIABhAG4AZAAgAFwAdQAwADAAMgA3AGkAcgByAGkAZwBhAHQAaQBvAG4AIABtAGUAdABoAG8AZABcAHUAMAAwADIANwAgAGMAbwBsAHUAbQBuAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAdQBwAGwAaQBjAGEAdABlAGQAIABcAHUAMAAwADIANwBuAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQBcAHUAMAAwADIANwAgAHIAbwB3ACAAdwBpAHQAaAAgAHMAYQBtAGUAIABFAEYAIABmAG8AcgAgAGwAbwB3ACAAYQBuAGQAIABoAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAFwAbgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABDAGgAYQBwAHQAZQByACAAMQAsACAAcwBlAGMAdABpAG8AbgAgADEALgA4AC4AMgAgAEwAZQBhAGMAaABpAG4AZwAsACAAYwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBzAFwAbgBJAFAAQwBDADoAIABOADIATwAgAEUATQBJAFMAUwBJAE8ATgBTACAARgBSAE8ATQAgAE0AQQBOAEEARwBFAEQAIABTAE8ASQBMAFMALAAgAEEATgBEACAAQwBPADIAIABFAE0ASQBTAFMASQBPAE4AUwAgAEYAUgBPAE0AIABMAEkATQBFACAAQQBOAEQAIABVAFIARQBBACAAQQBQAFAATABJAEMAQQBUAEkATwBOAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwBXAEUAVAAgAGYAbwByACAAaQByAHIAaQBnAGEAdABpAG8AbgAgAHQAeQBwAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAEMAaABhAHAAdABlAHIAIAAxACwAIABzAGUAYwB0AGkAbwBuACAAMQAuADgALgAyACAATABlAGEAYwBoAGkAbgBnACwAIABjAGwAaQBtAGEAdABlACAAYQBuAGQAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBJAFAAQwBDACAAMgAwADEAOQAgAFIAZQBmAGkAbgBlAG0AZQBuAHQAIABWAG8AbAB1AG0AZQAgADQAOgAgAEMAaABhAHAAdABlAHIAIAAxADEAOgAgAE4AMgBPACAARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAATQBhAG4AYQBnAGUAZAAgAFMAbwBpAGwAcwAsACAAYQBuAGQAIABDAE8AMgAgAEUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAEwAaQBtAGUAIABhAG4AZAAgAFUAcgBlAGEAIABBAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGkAbwBuACAAdAB5AHAAZQAgAGkAcgBcACIALABcACIARgByAGEAYwBXAEUAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAByAGkAcAAgAGkAcgByAGkAZwBhAHQAaQBvAG4AXAAiACwAIAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAcAByAGkAbgBrAGwAZQByACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB1AHIAZgBhAGMAZQAgAGkAcgByAGkAZwBhAHQAaQBvAG4AXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AdABoAGUAcgAgAGkAcgByAGkAZwBhAHQAaQBvAG4AXAAiACwAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAARgBSAE8ATQAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAAVABhAGIAbABlACAAYwByAGUAYQB0AGUAZAAgAGIAYQBzAGUAZAAgAG8AbgAgAFYARQBFAFIARwAgAHQAZQB4AHQAIABcAHUAMAAwADIANwBBAHIAZQBhAHMAIABhAHIAZQAgAHMAdQBiAGoAZQBjAHQAIAB0AG8AIABsAGUAYQBjAGgAaQBuAGcAIAAoAGkALgBlAC4ALAAgAGkAbgAgAHQAaABlACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQApACAAdwBoAGUAbgAuAC4ALgAgAHQAaABlACAAbABhAG4AZAAgAGkAcwAgAGkAcgByAGkAZwBhAHQAZQBkACAAKABlAHgAYwBlAHAAdAAgAGQAcgBpAHAAIABpAHIAcgBpAGcAYQB0AGkAbwBuACkALgBcAHUAMAAwADIANwBcACIAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAFwAbgBUAGEAYgBsAGUAIABBAC4AMgAuADIALgAyADoAIABFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAdQByAGkAbgBlACAAYQBuAGQAIABkAHUAbgBnACAAZABlAHAAbwBzAGkAdABlAGQAIABvAG4AIABwAGEAcwB0AHUAcgBlACwAIAByAGEAbgBnAGUAIABvAHIAIABwAGEAZABkAG8AYwBrACAAKABrAGcAIABOADIATwAtAE4ALwBrAGcAIABOACkAIAAoAEUARgBQAFIAUAApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAdQByAGkAbgBlACAAYQBuAGQAIABkAHUAbgBnACAAZABlAHAAbwBzAGkAdABlAGQAIABvAG4AIABwAGEAcwB0AHUAcgBlACwAIAByAGEAbgBnAGUAIABvAHIAIABwAGEAZABkAG8AYwBrAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AMgBPACAALQAgAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADIALgAyAC4AMgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAEUARgBQAFIAUABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAAyAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABDAGgAYQBuAGcAZQBkACAAXAB1ADAAMAAyADcARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBzAFwAdQAwADAAMgA3ACAAdABvACAAcwBpAG4AZwB1AGwAYQByACAAXAB1ADAAMAAyADcARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcAHUAMAAwADIANwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAG8AbgB0AGgAcwAgAHQAbwAgAFMAZQBhAHMAbwBuAHMAIABNAGEAcABwAGkAbgBnAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBvAG4AdABoAFwAIgAsACAAXAAiAFMAZQBhAHMAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAGEAbgB1AGEAcgB5AFwAIgAsACAAXAAiAFMAdQBtAG0AZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAGUAYgByAHUAYQByAHkAXAAiACwAIABcACIAUwB1AG0AbQBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQByAGMAaABcACIALAAgAFwAIgBBAHUAdAB1AG0AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBwAHIAaQBsAFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAGEAeQBcACIALAAgAFwAIgBBAHUAdAB1AG0AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASgB1AG4AZQBcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASgB1AGwAeQBcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQB1AGcAdQBzAHQAXAAiACwAIABcACIAVwBpAG4AdABlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAZQBwAHQAZQBtAGIAZQByAFwAIgAsACAAXAAiAFMAcAByAGkAbgBnAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBPAGMAdABvAGIAZQByAFwAIgAsACAAXAAiAFMAcAByAGkAbgBnAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdgBlAG0AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAZQBjAGUAbQBiAGUAcgBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBhAG4AdQByAGUAIABNAGEAbgBhAGcAZQBtAGUAbgB0ACAAEyAgAE0AZQB0AGgAYQBuAGUAIABjAG8AbgB2AGUAcgBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABwAGUAcgAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAIAAoAGYAcgBhAGMAdABpAG8AbgApACAAKABNAEMARgBpAG0AKQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAxAC4AOAAuADEAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIAMgAsACAAMQA2ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAE0AQQBUACAAKAC6AEMAKQBcACIALAAgAFwAIgBVAG4AYwBvAHYAZQByAGUAZAAgAGEAbgBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuAFwAIgAsACAAXAAiAEMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBcACIALAAgAFwAIgBMAGkAcQB1AGkAZAAgAFMAbAB1AHIAcgB5ACAAKAB3AGkAdABoAG8AdQB0ACAAbgBhAHQAdQByAGEAbAAgAGMAcgB1AHMAdAApAFwAIgAsACAAXAAiAEQAYQBpAGwAeQAgAHMAcAByAGUAYQBkACAAKABiACkAXAAiACwAIABcACIAQwBvAG0AcABvAHMAdABpAG4AZwAgACgAcABhAHMAcwBpAHYAZQAgAHcAaQBuAGQAcgBvAHcAKQBcACIALAAgAFwAIgBTAG8AbABpAGQAIABTAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAFAAaQB0ACAAUwB0AG8AcgBhAGcAZQAgAFwAdQAwADAAMwBjADEAIABtAG8AbgB0AGgAXAAiACwAIABcACIARABlAGUAcAAgAEwAaQB0AHQAZQByAFwAIgAsACAAXAAiAFAAbwB1AGwAdAByAHkAIABNAGEAbgB1AHIAZQAgACgAdwBpAHQAaAAvAHcAaQB0AGgAbwB1AHQAIABsAGkAdAB0AGUAcgApAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAcAByAG8AYwBlAHMAcwBpAG4AZwAgAGkAbgB0AG8AIABwAGUAbABsAGUAdABpAHoAZQBkACAAZgBlAHIAdABpAGwAaQBzAGUAcgBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgAgAHQAbwAgAHMAbwBpAGwAXAAiACwAIABcACIAUABhAHMAdAB1AHIAZQAsACAAUgBhAG4AZwBlACAAYQBuAGQAIABQAGEAZABkAG8AYwBrACAAKABjACkAKABkACkAXAAiACwAIABcACIATQBBAFQAIAByAGEAdwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgAFwAIgBkIjEAMABcACIALAAgADAALgA2ADYALAAgADAALgAxACwAIAAwAC4AMQAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIAAxADEALAAgADAALgA2ADgALAAgADAALgAxACwAIAAwAC4AMQAxACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgADEAMgAsACAAMAAuADcALAAgADAALgAxACwAIAAwAC4AMQAzACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgADEAMwAsACAAMAAuADcAMQAsACAAMAAuADEALAAgADAALgAxADQALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQA0ACwAIAAwAC4ANwAzACwAIAAwAC4AMQAsACAAMAAuADEANQAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA1ACwAIAAwAC4ANwA0ACwAIAAwAC4AMQAsACAAMAAuADEANwAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEANQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEANgAsACAAMAAuADcANQAsACAAMAAuADEALAAgADAALgAxADgALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADcALAAgADAALgA3ADYALAAgADAALgAxACwAIAAwAC4AMgAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEANwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEAOAAsACAAMAAuADcANwAsACAAMAAuADEALAAgADAALgAyADIALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADkALAAgADAALgA3ADcALAAgADAALgAxACwAIAAwAC4AMgA0ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgAwACwAIAAwAC4ANwA4ACwAIAAwAC4AMQAsACAAMAAuADIANgAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIAMQAsACAAMAAuADcAOAAsACAAMAAuADEALAAgADAALgAyADkALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADIALAAgADAALgA3ADgALAAgADAALgAxACwAIAAwAC4AMwAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgAzACwAIAAwAC4ANwA5ACwAIAAwAC4AMQAsACAAMAAuADMANAAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIANAAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgAzADcALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADUALAAgADAALgA3ADkALAAgADAALgAxACwAIAAwAC4ANAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AXAAiACwAIAAyADYALAAgADAALgA3ADkALAAgADAALgAxACwAIAAwAC4ANAA0ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AXAAiACwAIAAyADcALAAgADAALgA4ACwAIAAwAC4AMQAsACAAMAAuADQAOAAsACAAMAAuADAAMQAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIANwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtAFwAIgAsACAAXAAiAGUiMgA4AFwAIgAsACAAMAAuADgALAAgADAALgAxACwAIAAwAC4ANQAsACAAMAAuADAAMQAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBBAG4AYQBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuAFwAIgAsACAAXAAiAEQAaQBnAGUAcwB0AGUAcgAgAC8AIABjAG8AdgBlAHIAZQBkACAAbABhAGcAbwBvAG4AcwBcACIALAAgAFwAIgBMAGkAcQB1AGkAZAAgAHMAeQBzAHQAZQBtAHMAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAXAAiACwAIABcACIAQwBvAG0AcABvAHMAdABpAG4AZwAgACgAcABhAHMAcwBpAHYAZQAgAHcAaQBuAGQAcgBvAHcAKQBcACIALAAgAFwAIgBTAG8AbABpAGQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAFAAaQB0ACAAcwB0AG8AcgBhAGcAZQBcACIALAAgAFwAIgBEAGUAZQBwACAAbABpAHQAdABlAHIAXAAiACwAIABcACIAUABvAHUAbAB0AHIAeQAgAG0AYQBuAHUAcgBlACAAdwBpAHQAaAAgAGIAZQBkAGQAaQBuAGcAXAAiACwAIABcACIAUABvAHUAbAB0AHIAeQAgAG0AYQBuAHUAcgBlACAAdwBpAHQAaABvAHUAdAAgAGIAZQBkAGQAaQBuAGcAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABwAHIAbwBjAGUAcwBzAGkAbgBnAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuAFwAIgAsACAAXAAiAFAAYQBzAHQAdQByAGUAIAByAGEAbgBnAGUAIABhAG4AZAAgAHAAYQBkAGQAbwBjAGsAXAAiACwAIABcACIATQBBAFQAIAByAGEAdwBcACIAIABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAOgAgAEEAZABkAGUAZAAgAHIAbwB3ACAAbwBmACAATgBJAFIAIABNAE0AQQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgAgAEQAdQBwAGwAaQBjAGEAdABlAGQAIABcAHUAMAAwADIANwBQAG8AdQBsAHQAcgB5ACAAdwBpAHQAaAAgAGEAbgBkACAAdwBpAHQAaABvAHUAdAAgAGwAaQB0AHQAZQByAFwAdQAwADAAMgA3ACAAYwBvAGwAdQBtAG4AIAB3AGkAdABoACAAcwBlAHAAYQByAGEAdABlACAATgBJAFIAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AIABBAGQAZABlAGQAIABcAHUAMAAwADIANwBNAEEAVAAgAHIAYQB3AFwAdQAwADAAMgA3ACAAYwBvAGwAdQBtAG4AIAB0AG8AIABhAGwAbABvAHcAIABsAG8AbwBrAHUAcAAgAG8AZgAgAG4AdQBtAGIAZQByAHMALgBcACIAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAbgBkACAAYwByAG8AcAAgAHIAZQBzAGkAZAB1AGUAcwAgAHIAZQB0AHUAcgBuAGUAZAAgAHQAbwAgAHQAaABlACAAcwBvAGkAbABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBGAE4AaQAgAFwAdQAwADAAMgA2ACAARQBGAE4AMgBPAGkAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABOADIATwAgAC0AIABOACAALwAgAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADIALgAxAC4ANABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgAFwAIgBFAEYATgBpACAAXAB1ADAAMAAyADYAIABFAEYATgAyAE8AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIAAwAC4AMAAwADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAANQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIAXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBcAG4AQwBvAG4AdgBlAHIAdAAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcAG4ARQBOADIATwAgAEMATwAyAGUAXABuAHQAIABDAE8AMgBlAFwAbgBFAE4AMgBPADoAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAAoAHQAIABOADIATwApAFwAbgBHAFcAUABOADIATwA6ACAAZwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIAAoAHQAIABDAE8AMgAtAGUAIAAvACAAdAAgAE4AMgBPACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABFAF8ATgAyAE8ALAAgAEcAVwBQAF8ATgAyAE8ALABcAG4AIAAgACAAIABFAF8ATgAyAE8AIAAqACAARwBXAFAAXwBOADIATwBcAG4AIAAgACkAXABuADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAbwBuAHYAZQByAHQAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAB0AG8AIABjAGEAcgBiAG8AbgAgAGQAaQBvAHgAaQBkAGUAIABlAHEAdQBpAHYAYQBsAGUAbgB0ACAAZQBtAGkAcwBzAGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBOADIATwAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAE8AMgBlAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMATwAyAF8AZQAgAD0AIABFAF8AewBOADIATwB9ACAAXABcAHQAaQBtAGUAcwAgAEcAVwBQAF8AewBOADIATwB9AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUATgAyAE8AXAAiACwAXAAiAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAE4AMgBPACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAVwBQAE4AMgBPAFwAIgAsAFwAIgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAATgAyAE8AKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBcAG4AQwBvAG4AdgBlAHIAdAAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcAG4ARQBDAEgANAAgAEMATwAyAGUAXABuAHQAIABDAE8AMgBlAFwAbgBFAEMASAA0ADoAIABtAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAAoAHQAIABDAEgANAApAFwAbgBHAFcAUABDAEgANAA6ACAAZwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAG0AZQB0AGgAYQBuAGUAIAAoAHQAIABDAE8AMgAtAGUAIAAvACAAdAAgAEMASAA0ACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABFAF8AQwBIADQALAAgAEcAVwBQAF8AQwBIADQALABcAG4AIAAgACAAIABFAF8AQwBIADQAIAAqACAARwBXAFAAXwBDAEgANABcAG4AIAAgACkAXABuADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAbwBuAHYAZQByAHQAIABtAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAB0AG8AIABjAGEAcgBiAG8AbgAgAGQAaQBvAHgAaQBkAGUAIABlAHEAdQBpAHYAYQBsAGUAbgB0ACAAZQBtAGkAcwBzAGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBDAEgANAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAE8AMgBlAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMATwAyAF8AZQAgAD0AIABFAF8AewBDAEgANAB9ACAAXABcAHQAaQBtAGUAcwAgAEcAVwBQAF8AewBDAEgANAB9AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUAQwBIADQAXAAiACwAXAAiAE0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAEMASAA0ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAVwBQAEMASAA0AFwAIgAsAFwAIgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbQBlAHQAaABhAG4AZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAAQwBIADQAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIAVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAUgBvAHcAUwB0AGEAcgB0AE4AdQBtAGIAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwALABSAG8AdwBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAYQBuAGQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAUgBPAFcAKABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAApACAAKwAgAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkAIAAtACAAMQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABUAGEAYgBsAGUASABlAGEAZABlAHIAQwBlAGwAbAAsAFwAbgAgACAAQwBPAEwAVQBNAE4AKABUAGEAYgBsAGUASABlAGEAZABlAHIAQwBlAGwAbAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBBAHIAcgBhAHkASQBuAFQAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgAEEAcgByAGEAeQBEAGEAdABhACwAIABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQAsACAAWwBDAG8AbAB1AG0AbgBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAQQBuAGQAQQByAHIAYQB5AF0ALABcAG4AIABJAEYARQBSAFIATwBSACgAXABuACAAIAAgACAAIABJAE4ARABFAFgAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAVQBOAEkAUQBVAEUAKABBAHIAcgBhAHkARABhAHQAYQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBPAFcAKAApAC0AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAUgBvAHcAUwB0AGEAcgB0AE4AdQBtAGIAZQByACgAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwALAAgAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEMATwBMAFUATQBOACgAKQAtAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAEMAbwBsAHUAbQBuAFMAdABhAHIAdABOAHUAbQBiAGUAcgAoAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACkAIAArAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAEMAbwBsAHUAbQBuAHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBBAG4AZABBAHIAcgBhAHkAKQAsACAAMQAsACAAQwBvAGwAdQBtAG4AcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAEEAbgBkAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACAAIAAgACAAKQAsACAAXAAiAFwAIgBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFwAIgBcACIAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEkARgAoAEkAUwBOAFUATQBCAEUAUgAoAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFwAIgBcACIAKQBcAG4AIAAgACAAIAApACwAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApACwAIAAwACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBUAHcAbwBDAG8AbAB1AG0AbgBzAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlADEALAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADIALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAWwBWAGEAbAB1AGUASQBGAEYAYQBsAHMAZQBdACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoADEALAAgACgATABvAG8AawB1AHAAQQByAHIAYQB5ADEAPQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQApACoAKABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABWAGEAbAB1AGUASQBGAEYAYQBsAHMAZQApACwAIABcACIAXAAiACwAIABWAGEAbAB1AGUASQBGAEYAYQBsAHMAZQApACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBPAG4AZQBDAG8AbAB1AG0AbgBBAG4AZABIAGUAYQBkAGUAcgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACwAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMgAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADEALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFsAVgBhAGwAdQBlAEkAZgBGAGEAbABzAGUAXQAsAFwAbgAgACAAIAAgAEkARgBFAFIAUgBPAFIAKABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADEALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACkAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAFYAYQBsAHUAZQBJAGYARgBhAGwAcwBlACkALAAgAFwAIgBcACIALAAgAFYAYQBsAHUAZQBJAGYARgBhAGwAcwBlACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAcABsAGkAdABTAHQAcgBpAG4AZwBJAG4AdABvAEEAcgByAGEAeQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEMAZQBsAGwALAAgAEQAZQBsAGkAbQBpAHQAZQByACwAIABbAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAxAF0ALAAgAFsAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADIAXQAsAFwAbgAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAWABNAEwAKABcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBcAHUAMAAwADMAYwB0AFwAdQAwADAAMwBlAFwAdQAwADAAMwBjAHMAXAB1ADAAMAAzAGUAXAAiACAAXAB1ADAAMAAyADYAXABuACAAIAAgACAAIAAgACAAIABTAFUAQgBTAFQASQBUAFUAVABFACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFMAVQBCAFMAVABJAFQAVQBUAEUAKABTAFUAQgBTAFQASQBUAFUAVABFACgAQwBlAGwAbAAsAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAxACwAXAAiAFwAIgApACwAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADIALABcACIAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAARABlAGwAaQBtAGkAdABlAHIALABcACIAXAB1ADAAMAAzAGMALwBzAFwAdQAwADAAMwBlAFwAdQAwADAAMwBjAHMAXAB1ADAAMAAzAGUAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAKQAgAFwAdQAwADAAMgA2AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFwAdQAwADAAMwBjAC8AcwBcAHUAMAAwADMAZQBcAHUAMAAwADMAYwAvAHQAXAB1ADAAMAAzAGUAXAAiACwAXABuACAAIAAgACAAIAAgACAAIABcACIALwAvAHMAXAAiAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABDAGwAaQBtAGEAdABlAFoAbwBuAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABhAHYAZwBUAGUAbQBwACwAYQB2AGcAUgBhAGkAbgAsAGYAcgBvAHMAdABEAGEAeQBzACwAZQBsAGUAdgAsAG0AYQBwAF8AcABlAHQALABcAG4AIAAgACAAIABtAGkAbgBUAGUAbQBwAEEAcgByAGEAeQAsAG0AYQB4AFQAZQBtAHAAQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4AUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQAsAG0AYQB4AFIAYQBpAG4AZgBhAGwAbABBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBGAHIAbwBzAHQAQQByAHIAYQB5ACwAbQBhAHgARgByAG8AcwB0AEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAEUAbABlAHYAYQB0AGkAbwBuAEEAcgByAGEAeQAsAG0AYQB4AEUAbABlAHYAYQB0AGkAbwBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAFAARQBUAEEAcgByAGEAeQAsAG0AYQB4AFAARQBUAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAGMAbABpAG0AYQB0AGUAWgBvAG4AZQBBAHIAcgBhAHkALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAbQBhAHMAawAsAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBUAGUAbQBwAEEAcgByAGEAeQApAFwAdQAwADAAMwBjAD0AYQB2AGcAVABlAG0AcAApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AFQAZQBtAHAAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBhAHYAZwBUAGUAbQBwACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4AUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQApAFwAdQAwADAAMwBjAD0AYQB2AGcAUgBhAGkAbgApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AFIAYQBpAG4AZgBhAGwAbABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGEAdgBnAFIAYQBpAG4AKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBGAHIAbwBzAHQAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBmAHIAbwBzAHQARABhAHkAcwApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AEYAcgBvAHMAdABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGYAcgBvAHMAdABEAGEAeQBzACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4ARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBlAGwAZQB2ACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBlAGwAZQB2ACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4AUABFAFQAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBtAGEAcABfAHAAZQB0ACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgAUABFAFQAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBtAGEAcABfAHAAZQB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAFQAQQBLAEUAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAKABjAGwAaQBtAGEAdABlAFoAbwBuAGUAQQByAHIAYQB5ACwAbQBhAHMAawAsACAAXAAiAE4AbwAgAG0AYQB0AGMAaABcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAASQB0AGUAbQBGAHIAbwBtAE0AaQBuAE0AYQB4AFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABNAGkAbgBBAHIAcgBhAHkALAAgAE0AYQB4AEEAcgByAGEAeQAsACAASQB0AGUAbQBBAHIAcgBhAHkALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAbQBhAHMAawAsAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABNAGkAbgBBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAE0AYQB4AEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0ATABvAG8AawB1AHAAVgBhAGwAdQBlACkALABcAG4AIAAgACAAIAAgACAAIAAgAEYASQBMAFQARQBSACgASQB0AGUAbQBBAHIAcgBhAHkALAAgAG0AYQBzAGsALAAgAFwAIgBOAG8AIABtAGEAdABjAGgAXAAiACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBTAHUAbQBRAHUAYQBuAHQAaQB0AHkARgByAG8AbQBDAHIAaQB0AGUAcgBpAGEAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAEMAcgBpAHQAZQByAGkAYQAxACwAIABDAHIAaQB0AGUAcgBpAGEAMQBUAHkAcABlAEEAcgByAGEAeQAsACAAUQB1AGEAbgB0AGkAdAB5ACwAIABbAE0AdQBsAHQAaQBwAGwAaQBlAHIAXQAsACAAWwBDAHIAaQB0AGUAcgBpAGEAMgBdACwAWwBDAHIAaQB0AGUAcgBpAGEAMgBBAHIAcgBhAHkAXQAsAFwAbgAgACAATABFAFQAKABcAG4AIAAgACAAIABtAHUAbAB0AGkAcABsAGkAZQByACwAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAE0AdQBsAHQAaQBwAGwAaQBlAHIAKQAsADEALABNAHUAbAB0AGkAcABsAGkAZQByACkALABcAG4AIAAgACAAIABxAHUAYQBuAHQAaQB0AHkALAAgAFEAdQBhAG4AdABpAHQAeQAqAE0AdQBsAHQAaQBwAGwAaQBlAHIALABcAG4AIAAgACAAIABjAHIAaQB0AGUAcgBpAGEAMQAsAC0ALQAoAEMAcgBpAHQAZQByAGkAYQAxAFQAeQBwAGUAQQByAHIAYQB5AD0AQwByAGkAdABlAHIAaQBhADEAKQAsAFwAbgAgACAAIAAgAGMAcgBpAHQAZQByAGkAYQAyACwASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABDAHIAaQB0AGUAcgBpAGEAMgApACwAMQAsAC0ALQAoAEMAcgBpAHQAZQByAGkAYQAyAEEAcgByAGEAeQA9AEMAcgBpAHQAZQByAGkAYQAyACkAKQAsAFwAbgAgACAAIAAgAFMAVQBNAFAAUgBPAEQAVQBDAFQAKABjAHIAaQB0AGUAcgBpAGEAMQAqAGMAcgBpAHQAZQByAGkAYQAyACoAcQB1AGEAbgB0AGkAdAB5ACkAXABuACAAIAApAFwAbgApADsAXABuAFwAbgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAHMAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBTAHQAYQByAHQALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBFAG4AZAAsAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAUwAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgACAAIAAgACAARQAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAXABuACAAIAAgACAAIAAgACAAIABtACwATQBPAE4AVABIACgAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAApACwAXABuACAAIAAgACAAIAAgACAAIABkACwARABBAFkAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAFAAZQByAGkAbwBkAEUAbgBkACwATABBAE0AQgBEAEEAKABzAHQALABFAEQAQQBUAEUAKABzAHQALAAxADIAKQAtADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAQQAsAFMALQAzADYANQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBhACwAWQBFAEEAUgAoAEEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBiACwAWQBFAEEAUgAoAEUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZgBpAHIAcwB0AFkAZQBhAHIALAB5AGEAKwAoAFAAZQByAGkAbwBkAEUAbgBkACgARABBAFQARQAoAHkAYQAsAG0ALABkACkAKQBcAHUAMAAwADMAYwAgAFMAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAbABhAHMAdABZAGUAYQByACwAeQBiAC0AKABEAEEAVABFACgAeQBiACwAbQAsAGQAKQBcAHUAMAAwADMAZQAgAEUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAATQBBAFgAKAAwACwAbABhAHMAdABZAGUAYQByAC0AZgBpAHIAcwB0AFkAZQBhAHIAKwAxACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAFAAZQByAGkAbwBkAHMAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBTAHQAYQByAHQALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBFAG4AZAAsAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAUwAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgACAAIAAgACAARQAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAXABuACAAIAAgACAAIAAgACAAIABtACwATQBPAE4AVABIACgAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAApACwAXABuACAAIAAgACAAIAAgACAAIABkACwARABBAFkAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALAAgAC8AKgBoAGUAbABwAGUAcgA6ACAAZQBuAGQAIABkAGEAdABlACAAZgBvAHIAIABhACAAcgBlAHAAbwByAHQAaQBuAGcAIABwAGUAcgBpAG8AZAAgAHMAdABhAHIAdABpAG4AZwAgAGEAdAAgAGEAIABnAGkAdgBlAG4AIABkAGEAdABlACoALwBcAG4AIAAgACAAIAAgACAAIAAgAFAAZQByAGkAbwBkAEUAbgBkACwATABBAE0AQgBEAEEAKABzAHQALABFAEQAQQBUAEUAKABzAHQALAAxADIAKQAtADEAKQAsACAALwAqAG8AbgBsAHkAIABuAGUAZQBkACAAdABvACAAbABvAG8AawAgAGIAYQBjAGsAIAAzADYANQAgAGQAYQB5AHMAKABtAGEAeAAgAG8AdgBlAHIAbABhAHAAIAB3AGkAbgBkAG8AdwApACoALwBcAG4AIAAgACAAIAAgACAAIAAgAEEALABTAC0AMwA2ADUALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYQAsAFkARQBBAFIAKABBACkALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYgAsAFkARQBBAFIAKABFACkALAAgAC8AKgBpAGYAIAB0AGgAZQAgAGEAbgBjAGgAbwByACAAZgBvAHIAIAB5AGEAIABlAG4AZABzACAAYgBlAGYAbwByAGUAIABTACwAaQB0ACAAYwBhAG4AXAB1ADAAMAAyADcAdAAgAG8AdgBlAHIAbABhAHAAOwAgAG0AbwB2AGUAIAB0AG8AIABuAGUAeAB0ACAAeQBlAGEAcgAqAC8AXABuACAAIAAgACAAIAAgACAAIABmAGkAcgBzAHQAWQBlAGEAcgAsAHkAYQArACgAUABlAHIAaQBvAGQARQBuAGQAKABEAEEAVABFACgAeQBhACwAbQAsAGQAKQApAFwAdQAwADAAMwBjAFMAKQAsACAALwAqAGkAZgAgAHQAaABlACAAYQBuAGMAaABvAHIAIABmAG8AcgAgAHkAYgAgAHMAdABhAHIAdABzACAAYQBmAHQAZQByACAARQAsAGkAdAAgAGMAYQBuAFwAdQAwADAAMgA3AHQAIABvAHYAZQByAGwAYQBwADsAIABtAG8AdgBlACAAdABvACAAcAByAGUAdgBpAG8AdQBzACAAeQBlAGEAcgAqAC8AXABuACAAIAAgACAAIAAgACAAIABsAGEAcwB0AFkAZQBhAHIALAB5AGIALQAoAEQAQQBUAEUAKAB5AGIALABtACwAZAApAFwAdQAwADAAMwBlAEUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAbgAsAE0AQQBYACgAMAAsAGwAYQBzAHQAWQBlAGEAcgAtAGYAaQByAHMAdABZAGUAYQByACsAMQApACwAXABuACAAIAAgACAAIAAgACAAIAB5AHIAcwAsAFMARQBRAFUARQBOAEMARQAoAG4ALAAxACwAZgBpAHIAcwB0AFkAZQBhAHIALAAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAHMAdABhAHIAdABzACwARABBAFQARQAoAHkAcgBzACwAbQAsAGQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZQBuAGQAcwAsAE0AQQBQACgAcwB0AGEAcgB0AHMALABQAGUAcgBpAG8AZABFAG4AZAApACwAXABuACAAIAAgACAAIAAgACAAIAB0AGEAZwAsAEkARgAoAHMAdABhAHIAdABzAD0AUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAIgAgACgAVABoAGkAcwAgAHIAZQBwAG8AcgB0AGkAbgBnACAAYwB5AGMAbABlACkAXAAiACwAXAAiAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABzAHQAYQByAHQAcwBUAGUAeAB0ACwAVABFAFgAVAAoAHMAdABhAHIAdABzACwAXAAiAGQAZAAgAG0AbQBtACAAeQB5AHkAeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZQBuAGQAcwBUAGUAeAB0ACwAVABFAFgAVAAoAGUAbgBkAHMALABcACIAZABkACAAbQBtAG0AIAB5AHkAeQB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABuAD0AMAAsAFwAIgBcACIALABIAFMAVABBAEMASwAoAHMAdABhAHIAdABzAFQAZQB4AHQAIABcAHUAMAAwADIANgAgAFwAIgAgAHQAbwAgAFwAIgAgAFwAdQAwADAAMgA2ACAAZQBuAGQAcwBUAGUAeAB0ACAAXAB1ADAAMAAyADYAIAB0AGEAZwApACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkARgB1AG4AYwB0AGkAbwBuAE4AYQBtAGUAXABuAD0ATABBAE0AQgBEAEEAKABGAHUAbgBjAHQAaQBvAG4ALAAgAFQARQBYAFQAQgBFAEYATwBSAEUAKABGAE8AUgBNAFUATABBAFQARQBYAFQAKABGAHUAbgBjAHQAaQBvAG4AKQAsACAAXAAiACgAXAAiACkAKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAE4AMgBPAEUARgBGAHIAbwBtAFAAcgBvAGQASQByAHIAaQBnAGEAdABpAG8AbgBSAGEAaQBuAGYAYQBsAGwAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAIABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACwAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AQQByAHIAYQB5ACwAIABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkAEEAcgByAGEAeQAsACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAQQByAHIAYQB5ACwAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQALAAgAEkARgAoAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAPQBcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEEAbgB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQAsACAASQBGACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAAgAD0AIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAIABcACIAQQBuAHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKAAxACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEEAcgByAGEAeQA9AFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AKQAqAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAoAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAQQByAHIAYQB5AD0ASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAApACoAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACgAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAQQByAHIAYQB5AD0AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEcAZQB0AEYAcgBhAGMAVwBFAFQAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ALABcAG4AIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQALAAgAFwAbgAgACAAIAAgACAAIAAgACAAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUALABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBMAG8AbwBrAHUAcAAsAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQALAAgAFwAbgAgACAAIAAgACAAIAAgACAAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ATABvAG8AawB1AHAALABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBGAHIAYQBjAFcARQBUACAAKwAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVABcAHUAMAAwADMAZQAwACwAIAAxACwAIAAwACkAXABuACAAIAAgACAAKQApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEMAbwBuAHYAZQByAHQAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAVABvAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUALABcAG4AIAAgACAAIABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBBAHIAcgBhAHkALAAgAFMAdABhAHQAZQBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUALAAgAFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAEEAcgByAGEAeQAsACAAUwB0AGEAdABlAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwBvAHUAcgBjAGUASAB5AHAAZQByAGwAaQBuAGsAXABuAD0ATABBAE0AQgBEAEEAKABUAGEAcgBnAGUAdABDAGUAbABsACwAXABuACAAIABMAEUAVAAoAFwAbgAgACAAIAAgAHMAaAAsACAAVABFAFgAVABBAEYAVABFAFIAKABDAEUATABMACgAXAAiAGYAaQBsAGUAbgBhAG0AZQBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsACAAXAAiAF0AXAAiACkALABcAG4AIAAgACAAIABhAGQAZAByACwAIABDAEUATABMACgAXAAiAGEAZABkAHIAZQBzAHMAXAAiACwAIABUAGEAcgBnAGUAdABDAGUAbABsACkALABcAG4AIAAgACAAIABcACIAIwBcAHUAMAAwADIANwBcACIAIABcAHUAMAAwADIANgAgAHMAaAAgAFwAdQAwADAAMgA2ACAAXAAiAFwAdQAwADAAMgA3ACEAXAAiACAAXAB1ADAAMAAyADYAIABhAGQAZAByAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAbwB1AHIAYwBlAEgAeQBwAGUAcgBsAGkAbgBrAEQAaQBmAGYAZQByAGUAbgB0AFMAaABlAGUAdABcAG4APQBMAEEATQBCAEQAQQAoAFQAYQByAGcAZQB0AEMAZQBsAGwALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAcwBoACwAIABUAEUAWABUAEEARgBUAEUAUgAoAEMARQBMAEwAKABcACIAZgBpAGwAZQBuAGEAbQBlAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAIABcACIAXQBcACIAKQAsAFwAbgAgACAAIAAgAGEAZABkAHIALAAgAEMARQBMAEwAKABcACIAYQBkAGQAcgBlAHMAcwBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsAFwAbgAgACAAIAAgAFwAIgAjAFwAIgAgAFwAdQAwADAAMgA2ACAAYQBkAGQAcgBcAG4AIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgBnAHUAbQBlAG4AdABzAF8AMQBfADIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALABcAG4AIAAgACAAIABDAEgATwBPAFMARQBDAE8ATABTACgAQQByAGcAdQBtAGUAbgB0AHMAQQByAHIAYQB5ACwAIAAxACwAIAAyACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgBnAHUAbQBlAG4AdABzAF8AMwBfADQAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALABcAG4AIAAgACAAIABDAEgATwBPAFMARQBDAE8ATABTACgAQQByAGcAdQBtAGUAbgB0AHMAQQByAHIAYQB5ACwAIAAzACwAIAA0ACkAXABuACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8ARwBlAHQATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUALAAgAE0ATQBTACwAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUAQQByAHIAYQB5ACwAIABNAE0AUwBBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKABcAG4AIAAgACAAIAAgACAAIAAgAE0ARQBEAEkAQQBOACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFIATwBVAE4ARAAoAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAsACAAMAApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATQBJAE4AKABUAGUAbQBwAGUAcgBhAHQAdQByAGUAQQByAHIAYQB5ACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABNAEEAWAAoAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkALABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKABNAE0AUwAsACAATQBNAFMAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFIAZQBzAHUAbAB0AHMASQB0AGUAbQBGAHIAbwBtAEUAcQB1AGEAdABpAG8AbgBUAGkAdABsAGUAQQBuAGQAUwBvAHUAcgBjAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGkAdABsAGUAQwBlAGwAbAAsACAAUwBvAHUAcgBjAGUAQwBlAGwAbAAsAFwAbgAgACAAIAAgAFMAVQBCAFMAVABJAFQAVQBUAEUAKABMAEUARgBUACgAUwBvAHUAcgBjAGUAQwBlAGwAbAAsACAARgBJAE4ARAAoAFwAIgAsAFwAIgAsACAAUwBvAHUAcgBjAGUAQwBlAGwAbAApACAALQAxACkALAAgAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABcACIALAAgAFwAIgBcACIAKQAgAFwAdQAwADAAMgA2ACAAXAAiACAAXAAiACAAXAB1ADAAMAAyADYAIABUAGkAdABsAGUAQwBlAGwAbABcAG4AKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AVwBhAHMAdABlAHcAYQB0AGUAcgBfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAiACwAIgB0AGUAeAB0ACIAOgAiAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AMQAxAC4AMQA6ACAAVwBhAHMAdABlAHcAYQB0AGUAcgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AMQAxAC4AMQAuADEALgAxACAATQBlAHQAaABvAGQAIAAxACAALQAgAE0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABvAG4AcwBpAHQAZQAgAFcAYQBzAHQAZQB3AGEAdABlAHIAIABNAGEAbgBhAGcAZQBtAGUAbgB0AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8AMQAxAF8AMQBfADEAXwAxAF8AXwAxAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFcAYQBzAHQAZQB3AGEAdABlAHIAVAByAGUAYQB0AG0AZQBuAHQAXABuAE0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIAB3AGEAcwB0AGUAdwBhAHQAZQByACAAdAByAGUAYQB0AG0AZQBuAHQAXABuAEUAXwBDAEgANABcAG4AdAAgAEMASAA0AFwAbgBFAF8AewBDAEgANAB9AD0AXABcAGYAcgBhAGMAewAxAH0AewAxADAAMAAwAH0AXABcAHQAaQBtAGUAcwBcAFwAbABlAGYAdABbAFwAXABsAGUAZgB0ACgAVwBfAHQAXABcAHQAaQBtAGUAcwBcAFwAbABlAGYAdAAoAEMATwBEAF8AewBpAG4AfQBcAFwAdABpAG0AZQBzACgAMQAtAEYAXwB7AHMAbAB1AGQAZwBlAH0AKQAtAEMATwBEAF8AewBvAHUAdAB9AFwAXAByAGkAZwBoAHQAKQBcAFwAdABpAG0AZQBzACAAQwBGAF8AewB3AHcALAB0AH0AXABcAHQAaQBtAGUAcwAgAEUARgBfAHsAdwB3AH0AXABcAHIAaQBnAGgAdAApACsAXABcAGwAZQBmAHQAKABXAF8AdABcAFwAdABpAG0AZQBzAFwAXABsAGUAZgB0ACgAQwBPAEQAXwB7AGkAbgB9AFwAXAB0AGkAbQBlAHMAKABGAF8AewBzAGwAdQBkAGcAZQB9AC0ARgBfAHsAcgBlAG0AbwB2AGUAZAB9ACkAXABcAHIAaQBnAGgAdAApAFwAXAB0AGkAbQBlAHMAIABDAEYAXwB7AHMAbAB1AGQAZwBlACwAdAB9AFwAXAB0AGkAbQBlAHMAIABFAEYAXwB7AHMAbAB1AGQAZwBlAH0AXABcAHIAaQBnAGgAdAApAC0AXABcAGwAZQBmAHQAKAA2AC4ANwA4ADQAXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQA0AH0AXABcAHQAaQBtAGUAcwAoAFEAXwB7AGMAYQBwAH0AKwBRAF8AewBmAGwAYQByAGUAZAB9ACsAUQBfAHsAbwB1AHQAfQApAFwAXAByAGkAZwBoAHQAKQArAFwAXABsAGUAZgB0ACgAUQBfAHsAZgBsAGEAcgBlAGQAfQBcAFwAdABpAG0AZQBzACAARQBDAF8AewBmAGwAYQByAGUAZAB9AFwAXAB0AGkAbQBlAHMAIABFAEYAXwB7AGYAbABhAHIAZQBkACwAQwBIADQAfQBcAFwAcgBpAGcAaAB0ACkAXABcAHIAaQBnAGgAdABdAFwAbgBXAF8AdAAgAD0AIABxAHUAYQBuAHQAaQB0AHkAIABvAGYAIAB3AGEAcwB0AGUAdwBhAHQAZQByACAAdAByAGUAYQB0AGUAZAAgAGEAdAAgAGYAYQBjAGkAbABpAHQAeQAgAHQAeQBwAGUAIAB0ACAAKABtADMAKQBcAG4AQwBPAEQAXwBpAG4AIAA9ACAAYQB2AGUAcgBhAGcAZQAgAGkAbgBsAGUAdAAgAEMAaABlAG0AaQBjAGEAbAAgAE8AeAB5AGcAZQBuACAARABlAG0AYQBuAGQAIABjAG8AbgBjAGUAbgB0AHIAYQB0AGkAbwBuACAAbwBmACAAdwBhAHMAdABlAHcAYQB0AGUAcgAgACgAawBnACAAQwBPAEQALwBtADMAKQBcAG4ARgBfAHMAbAB1AGQAZwBlACAAPQAgAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAEMATwBEACAAcgBlAG0AbwB2AGUAZAAgAGYAcgBvAG0AIAB3AGEAcwB0AGUAdwBhAHQAZQByACAAYQBzACAAcwBsAHUAZABnAGUAXABuAEMATwBEAF8AbwB1AHQAIAA9ACAAYQB2AGUAcgBhAGcAZQAgAG8AdQB0AGwAZQB0ACAAQwBPAEQAIABjAG8AbgBjAGUAbgB0AHIAYQB0AGkAbwBuACAAbwBmACAAdwBhAHMAdABlAHcAYQB0AGUAcgAgACgAawBnACAAQwBPAEQALwBtADMAKQBcAG4AQwBGAF8AdwB3AF8AdAAgAD0AIABtAGUAdABoAGEAbgBlACAAYwBvAHIAcgBlAGMAdABpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABmAGEAYwBpAGwAaQB0AHkAIAB0AHkAcABlACAAdAAgAHUAcwBlAGQAIAB0AG8AIAB0AHIAZQBhAHQAIAB3AGEAcwB0AGUAdwBhAHQAZQByAFwAbgBFAEYAXwB3AHcAIAA9ACAAbQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB3AGEAcwB0AGUAdwBhAHQAZQByACAAKABrAGcAIABDAE8AMgBlAC8AawBnACAAQwBPAEQAKQBcAG4ARgBfAHIAZQBtAG8AdgBlAGQAIAA9ACAAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAQwBPAEQAIAByAGUAbQBvAHYAZQBkACAAZgByAG8AbQAgAHQAaABlACAAdwBhAHMAdABlAHcAYQB0AGUAcgAgAHQAcgBlAGEAdABtAGUAbgB0ACAAZgBhAGMAaQBsAGkAdAB5ACAAYQBuAGQAIAB0AHIAYQBuAHMAZgBlAHIAcgBlAGQAIABlAGwAcwBlAHcAaABlAHIAZQBcAG4AQwBGAF8AcwBsAHUAZABnAGUAXwB0ACAAPQAgAG0AZQB0AGgAYQBuAGUAIABjAG8AcgByAGUAYwB0AGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAGYAYQBjAGkAbABpAHQAeQAgAHQAeQBwAGUAIAB0ACAAdQBzAGUAZAAgAHQAbwAgAHQAcgBlAGEAdAAgAHMAbAB1AGQAZwBlAFwAbgBFAEYAXwBzAGwAdQBkAGcAZQAgAD0AIABtAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHMAbAB1AGQAZwBlACAAKABrAGcAIABDAE8AMgBlAC8AawBnACAAQwBPAEQAKQBcAG4AUQBfAGMAYQBwACAAPQAgAHEAdQBhAG4AdABpAHQAeQAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAIABpAG4AIABzAGwAdQBkAGcAZQAgAGIAaQBvAGcAYQBzACAAYwBhAHAAdAB1AHIAZQBkACAAZgBvAHIAIABjAG8AbQBiAHUAcwB0AGkAbwBuACAAKABtADMAIABDAEgANAApAFwAbgBRAF8AZgBsAGEAcgBlAGQAIAA9ACAAcQB1AGEAbgB0AGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQAgAGkAbgAgAHMAbAB1AGQAZwBlACAAYgBpAG8AZwBhAHMAIABmAGwAYQByAGUAZAAgACgAbQAzACAAQwBIADQAKQBcAG4AUQBfAG8AdQB0ACAAPQAgAHEAdQBhAG4AdABpAHQAeQAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAIABpAG4AIABzAGwAdQBkAGcAZQAgAGIAaQBvAGcAYQBzACAAdAByAGEAbgBzAGYAZQByAHIAZQBkACAAbwB1AHQAIABvAGYAIAB0AGgAZQAgAHQAcgBlAGEAdABtAGUAbgB0ACAAZgBhAGMAaQBsAGkAdAB5ACAAKABtADMAIABDAEgANAApAFwAbgBFAEMAXwBmAGwAYQByAGUAZAAgAD0AIABlAG4AZQByAGcAeQAgAGMAbwBuAHQAZQBuAHQAIABmAGEAYwB0AG8AcgAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAIABpAG4AIABzAGwAdQBkAGcAZQAgAGIAaQBvAGcAYQBzACAAZgBsAGEAcgBlAGQAIAAoAEcASgAvAG0AMwApAFwAbgBFAEYAXwBmAGwAYQByAGUAZABfAEMASAA0ACAAPQAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAcwBsAHUAZABnAGUAIABiAGkAbwBnAGEAcwAgAGYAbABhAHIAZQBkACAAKABrAGcAIABDAE8AMgBlAC8ARwBKACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8AMQAxAF8AMQBfADEAXwAxAF8AXwAxAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFcAYQBzAHQAZQB3AGEAdABlAHIAVAByAGUAYQB0AG0AZQBuAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAVwBfAHQALAAgAEMATwBEAF8AaQBuACwAIABGAF8AcwBsAHUAZABnAGUALAAgAEMATwBEAF8AbwB1AHQALAAgAEMARgBfAHcAdwBfAHQALAAgAEUARgBfAHcAdwAsACAARgBfAHIAZQBtAG8AdgBlAGQALAAgAEMARgBfAHMAbAB1AGQAZwBlAF8AdAAsACAARQBGAF8AcwBsAHUAZABnAGUALAAgAFEAXwBjAGEAcAAsACAAUQBfAGYAbABhAHIAZQBkACwAIABRAF8AbwB1AHQALAAgAEUAQwBfAGYAbABhAHIAZQBkACwAIABFAEYAXwBmAGwAYQByAGUAZABDAEgANAAsAFwAbgAgACAAIAAgACgAMQAvADEAMAAwADAAKQAgACoAIAAoACgAVwBfAHQAIAAqACAAKABDAE8ARABfAGkAbgAgACoAIAAoADEAIAAtACAARgBfAHMAbAB1AGQAZwBlACkAIAAtACAAQwBPAEQAXwBvAHUAdAApACAAKgAgAEMARgBfAHcAdwBfAHQAIAAqACAARQBGAF8AdwB3ACkAIAArACAAKABXAF8AdAAgACoAIAAoAEMATwBEAF8AaQBuACAAKgAgACgARgBfAHMAbAB1AGQAZwBlACAALQAgAEYAXwByAGUAbQBvAHYAZQBkACkAKQAgACoAIABDAEYAXwBzAGwAdQBkAGcAZQBfAHQAIAAqACAARQBGAF8AcwBsAHUAZABnAGUAKQAgAC0AIAAoADYALgA3ADgANAAgACoAIAAxADAAXgAtADQAIAAqACAAKABRAF8AYwBhAHAAIAArACAAUQBfAGYAbABhAHIAZQBkACAAKwAgAFEAXwBvAHUAdAApACkAIAArACAAKABRAF8AZgBsAGEAcgBlAGQAIAAqACAAKABFAEMAXwBmAGwAYQByAGUAZAAgACoAIABFAEYAXwBmAGwAYQByAGUAZABDAEgANAApACkAKQBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEAMQBfADEAXwAxAF8AMQBfAF8AMQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBXAGEAcwB0AGUAdwBhAHQAZQByAFQAcgBlAGEAdABtAGUAbgB0AF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAdwBhAHMAdABlAHcAYQB0AGUAcgAgAHQAcgBlAGEAdABtAGUAbgB0AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADEAXwAxAF8AMQBfADEAXwBfADEAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AVwBhAHMAdABlAHcAYQB0AGUAcgBUAHIAZQBhAHQAbQBlAG4AdABfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBfAEMASAA0AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADEAXwAxAF8AMQBfADEAXwBfADEAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AVwBhAHMAdABlAHcAYQB0AGUAcgBUAHIAZQBhAHQAbQBlAG4AdABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAEgANABcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQAxAF8AMQBfADEAXwAxAF8AXwAxAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFcAYQBzAHQAZQB3AGEAdABlAHIAVAByAGUAYQB0AG0AZQBuAHQAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAMQAxAC4AMQAuADEALgAxACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADEAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQAxAF8AMQBfADEAXwAxAF8AXwAxAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFcAYQBzAHQAZQB3AGEAdABlAHIAVAByAGUAYQB0AG0AZQBuAHQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAARwByAGUAZQBuAGgAbwB1AHMAZQAgAGEAbgBkACAARQBuAGUAcgBnAHkAIABSAGUAcABvAHIAdABpAG4AZwAgAE0AZQBhAHMAdQByAGUAbQBlAG4AdAAgAEQAZQB0AGUAcgBtAGkAbgBhAHQAaQBvAG4AIAAyADAAMAA4AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADEAXwAxAF8AMQBfADEAXwBfADEAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AVwBhAHMAdABlAHcAYQB0AGUAcgBUAHIAZQBhAHQAbQBlAG4AdABfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwB7AEMASAA0AH0APQBcAFwAZgByAGEAYwB7ADEAfQB7ADEAMAAwADAAfQBcAFwAdABpAG0AZQBzAFwAXABsAGUAZgB0AHsAXABcAGwAZQBmAHQAewBXAF8AdABcAFwAdABpAG0AZQBzAFwAXABsAGUAZgB0AFsAQwBPAEQAXwB7AGkAbgB9AFwAXAB0AGkAbQBlAHMAKAAxAC0ARgBfAHsAcwBsAHUAZABnAGUAfQApAC0AQwBPAEQAXwB7AG8AdQB0AH0AXABcAHIAaQBnAGgAdABdAFwAXAB0AGkAbQBlAHMAIABDAEYAXwB7AHcAdwAsAHQAfQBcAFwAdABpAG0AZQBzACAARQBGAF8AewB3AHcAfQBcAFwAcgBpAGcAaAB0AH0AKwBcAFwAbABlAGYAdAB7AFcAXwB0AFwAXAB0AGkAbQBlAHMAXABcAGwAZQBmAHQAWwBDAE8ARABfAHsAaQBuAH0AXABcAHQAaQBtAGUAcwAoAEYAXwB7AHMAbAB1AGQAZwBlAH0ALQBGAF8AewByAGUAbQBvAHYAZQBkAH0AKQBcAFwAcgBpAGcAaAB0AF0AXABcAHQAaQBtAGUAcwAgAEMARgBfAHsAcwBsAHUAZABnAGUALAB0AH0AXABcAHQAaQBtAGUAcwAgAEUARgBfAHsAcwBsAHUAZABnAGUAfQBcAFwAcgBpAGcAaAB0AH0ALQBcAFwAbABlAGYAdAB7ADYALgA3ADgANABcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADQAfQBcAFwAdABpAG0AZQBzACAAXABcAGwAZQBmAHQAWwAgAFEAXwB7AGMAYQBwAH0AKwBRAF8AewBmAGwAYQByAGUAZAB9ACsAUQBfAHsAbwB1AHQAfQBcAFwAcgBpAGcAaAB0AF0AXABcAHIAaQBnAGgAdAB9ACsAXABcAGwAZQBmAHQAewBRAF8AewBmAGwAYQByAGUAZAB9AFwAXAB0AGkAbQBlAHMAIABcAFwAbABlAGYAdABbACAARQBDAF8AewBmAGwAYQByAGUAZAB9AFwAXAB0AGkAbQBlAHMAIABFAEYAXwB7AGYAbABhAHIAZQBkACwAQwBIADQAfQBcAFwAcgBpAGcAaAB0AF0AXABcAHIAaQBnAGgAdAB9AFwAXAByAGkAZwBoAHQAfQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQAxAF8AMQBfADEAXwAxAF8AXwAxAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFcAYQBzAHQAZQB3AGEAdABlAHIAVAByAGUAYQB0AG0AZQBuAHQAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEANQAsACAANAAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAF8AdABcACIALAAgAFwAIgBxAHUAYQBuAHQAaQB0AHkAIABvAGYAIAB3AGEAcwB0AGUAdwBhAHQAZQByACAAdAByAGUAYQB0AGUAZAAgAGEAdAAgAGYAYQBjAGkAbABpAHQAeQAgAHQAeQBwAGUAIAB0AFwAIgAsACAAXAAiAG0AMwBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwBEAF8AaQBuAFwAIgAsACAAXAAiAGEAdgBlAHIAYQBnAGUAIABpAG4AbABlAHQAIABDAGgAZQBtAGkAYwBhAGwAIABPAHgAeQBnAGUAbgAgAEQAZQBtAGEAbgBkACAAYwBvAG4AYwBlAG4AdAByAGEAdABpAG8AbgAgAG8AZgAgAHcAYQBzAHQAZQB3AGEAdABlAHIAXAAiACwAIABcACIAawBnACAAQwBPAEQALwBtADMAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAF8AcwBsAHUAZABnAGUAXAAiACwAIABcACIAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAQwBPAEQAIAByAGUAbQBvAHYAZQBkACAAZgByAG8AbQAgAHcAYQBzAHQAZQB3AGEAdABlAHIAIABhAHMAIABzAGwAdQBkAGcAZQBcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAE8ARABfAG8AdQB0AFwAIgAsACAAXAAiAGEAdgBlAHIAYQBnAGUAIABvAHUAdABsAGUAdAAgAEMATwBEACAAYwBvAG4AYwBlAG4AdAByAGEAdABpAG8AbgAgAG8AZgAgAHcAYQBzAHQAZQB3AGEAdABlAHIAXAAiACwAIABcACIAawBnACAAQwBPAEQALwBtADMAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAEYAXwB3AHcAXwB0AFwAIgAsACAAXAAiAG0AZQB0AGgAYQBuAGUAIABjAG8AcgByAGUAYwB0AGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAGYAYQBjAGkAbABpAHQAeQAgAHQAeQBwAGUAIAB0ACAAdQBzAGUAZAAgAHQAbwAgAHQAcgBlAGEAdAAgAHcAYQBzAHQAZQB3AGEAdABlAHIAXAAiACwAIABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAF8AdwB3AFwAIgAsACAAXAAiAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAdwBhAHMAdABlAHcAYQB0AGUAcgBcACIALAAgAFwAIgBrAGcAIABDAEgANAAvAGsAZwAgAEMATwBEAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBfAHIAZQBtAG8AdgBlAGQAXAAiACwAIABcACIAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAQwBPAEQAIAByAGUAbQBvAHYAZQBkACAAZgByAG8AbQAgAHQAaABlACAAdwBhAHMAdABlAHcAYQB0AGUAcgAgAHQAcgBlAGEAdABtAGUAbgB0ACAAZgBhAGMAaQBsAGkAdAB5ACAAYQBuAGQAIAB0AHIAYQBuAHMAZgBlAHIAcgBlAGQAIABlAGwAcwBlAHcAaABlAHIAZQBcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAEYAXwBzAGwAdQBkAGcAZQBfAHQAXAAiACwAIABcACIAbQBlAHQAaABhAG4AZQAgAGMAbwByAHIAZQBjAHQAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAZgBhAGMAaQBsAGkAdAB5ACAAdAB5AHAAZQAgAHQAIAB1AHMAZQBkACAAdABvACAAdAByAGUAYQB0ACAAcwBsAHUAZABnAGUAXAAiACwAIABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAF8AcwBsAHUAZABnAGUAXAAiACwAIABcACIAbQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABzAGwAdQBkAGcAZQBcACIALAAgAFwAIgBrAGcAIABDAEgANAAvAGsAZwAgAEMATwBEAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUQBfAGMAYQBwAFwAIgAsACAAXAAiAHEAdQBhAG4AdABpAHQAeQAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAIABpAG4AIABzAGwAdQBkAGcAZQAgAGIAaQBvAGcAYQBzACAAYwBhAHAAdAB1AHIAZQBkACAAZgBvAHIAIABjAG8AbQBiAHUAcwB0AGkAbwBuAFwAIgAsACAAXAAiAG0AMwAgAEMASAA0AFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUQBfAGYAbABhAHIAZQBkAFwAIgAsACAAXAAiAHEAdQBhAG4AdABpAHQAeQAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAIABpAG4AIABzAGwAdQBkAGcAZQAgAGIAaQBvAGcAYQBzACAAZgBsAGEAcgBlAGQAIABiAHkAIAB0AGgAZQAgAHQAcgBlAGEAdABtAGUAbgB0ACAAZgBhAGMAaQBsAGkAdAB5AFwAIgAsACAAXAAiAG0AMwAgAEMASAA0AFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUQBfAG8AdQB0AFwAIgAsACAAXAAiAHEAdQBhAG4AdABpAHQAeQAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAIABpAG4AIABzAGwAdQBkAGcAZQAgAGIAaQBvAGcAYQBzACAAdAByAGEAbgBzAGYAZQByAHIAZQBkACAAbwB1AHQAIABvAGYAIAB0AGgAZQAgAHQAcgBlAGEAdABtAGUAbgB0ACAAZgBhAGMAaQBsAGkAdAB5AFwAIgAsACAAXAAiAG0AMwAgAEMASAA0AFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBDAF8AZgBsAGEAcgBlAGQAXAAiACwAIABcACIAZQBuAGUAcgBnAHkAIABjAG8AbgB0AGUAbgB0ACAAZgBhAGMAdABvAHIAIABvAGYAIABtAGUAdABoAGEAbgBlACAAaQBuACAAcwBsAHUAZABnAGUAIABiAGkAbwBnAGEAcwAgAGYAbABhAHIAZQBkAFwAIgAsACAAXAAiAEcASgAvAG0AMwBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARgBfAGYAbABhAHIAZQBkAEMASAA0AFwAIgAsACAAXAAiAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAcwBsAHUAZABnAGUAIABiAGkAbwBnAGEAcwAgAGYAbABhAHIAZQBkAFwAIgAsACAAXAAiAGsAZwAgAEMASAA0AC8ARwBKAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAdABcACIALAAgAFwAIgB0AHIAZQBhAHQAbQBlAG4AdAAgAGYAYQBjAGkAbABpAHQAeQAgAHQAeQBwAGUAXAAiACwAIABcACIAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAFYARQBFAFIARwBfADEAMQBfADEAXwAxAF8AMQBfAF8AMQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBXAGEAcwB0AGUAdwBhAHQAZQByAFQAcgBlAGEAdABtAGUAbgB0AF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBOACAAUwBPAFUAUgBDAEUAOgAgAEMAaABhAG4AZwBlAGQAIAB1AG4AaQB0AHMAIABvAGYAIABFAEYAXwB3AHcALAAgAEUARgBfAFMAbAB1AGQAZwBlACAAYQBuAGQAIABFAEYAXwBmAGwAYQByAGUAZAAgAGYAcgBvAG0AIABDAE8AMgBlACAAdABvACAAQwBIADQAIAB0AG8AIABtAGEAdABjAGgAIABkAGEAdABhACAAaQBuACAAVABhAGIAbABlACAAXAAiACkAOwAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBTAG8AdQByAGMAZQBEAGEAdABhACIALAAiAHQAZQB4AHQAIgA6ACIALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgBUAGEAYgBsAGUAIABBAC4ANAAuADEALgAzADoAIABNAGUAdABoAGEAbgBlACAAYwBvAHIAcgBlAGMAdABpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB0AHIAZQBhAHQAbQBlAG4AdAAgAGYAYQBjAGkAbABpAHQAeQAgAHQAeQBwAGUAIAB0ACAAdQBzAGUAZAAgAHQAbwAgAHQAcgBlAGEAdAAgAHcAYQBzAHQAZQB3AGEAdABlAHIAIAAoAGYAcgBhAGMAdABpAG8AbgApACAAKABDAEYAdwB3ACwAdAApAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEMAbwByAHIAZQBjAHQAaQBvAG4ARgBhAGMAdABvAHIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFQAaQB0AGwAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAE0AZQB0AGgAYQBuAGUAIABjAG8AcgByAGUAYwB0AGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHQAcgBlAGEAdABtAGUAbgB0ACAAZgBhAGMAaQBsAGkAdAB5ACAAdAB5AHAAZQAgAHQAIAB1AHMAZQBkACAAdABvACAAdAByAGUAYQB0ACAAdwBhAHMAdABlAHcAYQB0AGUAcgBcACIAKQApADsAXABuAFwAbgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEMAbwByAHIAZQBjAHQAaQBvAG4ARgBhAGMAdABvAHIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFYAYQByAGkAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEMARgB3AHcALAB0AFwAIgApACkAOwBcAG4AXABuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUAQwBvAHIAcgBlAGMAdABpAG8AbgBGAGEAYwB0AG8AcgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AVQBuAGkAdABcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIAKQApADsAXABuAFwAbgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEMAbwByAHIAZQBjAHQAaQBvAG4ARgBhAGMAdABvAHIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADQALgAxAC4AMwBcACIAKQApADsAXABuAFwAbgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEMAbwByAHIAZQBjAHQAaQBvAG4ARgBhAGMAdABvAHIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAEQAYQB0AGEAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANgAsACAAMgAsAFwAbgAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBGAGEAYwBpAGwAaQB0AHkAIAB0AHkAcABlACAAdABcACIALAAgAFwAIgBDAEYAdwB3ACwAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBNAGEAbgBhAGcAZQBkACAAYQBlAHIAbwBiAGkAYwAgAHQAcgBlAGEAdABtAGUAbgB0AFwAIgAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFUAbgBtAGEAbgBhAGcAZQBkACAAYQBlAHIAbwBiAGkAYwAgAHQAcgBlAGEAdABtAGUAbgB0AFwAIgAsACAAMAAuADMAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBBAG4AYQBlAHIAbwBiAGkAYwAgAGQAaQBnAGUAcwB0AG8AcgAvAHIAZQBhAGMAdABvAHIAXAAiACwAIAAwAC4AOAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFMAaABhAGwAbABvAHcAIABhAG4AYQBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuACAAKABkIiAAMgAgAG0AKQBcACIALAAgADAALgAyADsAXABuACAAIAAgACAAIAAgACAAIABcACIARABlAGUAcAAgAGEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AIAAoAFwAdQAwADAAMwBlACAAMgBtACkAXAAiACwAIAAwAC4AOABcAG4AIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgApACkAKQA7AFwAbgBcAG4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBDAG8AcgByAGUAYwB0AGkAbwBuAEYAYQBjAHQAbwByAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAFwAIgApACkAOwBcAG4AXABuAFwAbgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFQAYQBiAGwAZQAgAEEALgA0AC4AMQAuADQAOgAgAE0AZQB0AGgAYQBuAGUAIABjAG8AcgByAGUAYwB0AGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHQAcgBlAGEAdABtAGUAbgB0ACAAZgBhAGMAaQBsAGkAdAB5ACAAdAB5AHAAZQAgAHQAIAB1AHMAZQBkACAAdABvACAAdAByAGUAYQB0ACAAcwBsAHUAZABnAGUAIAAoAGYAcgBhAGMAdABpAG8AbgApACAAKABDAEYAcwBsAHUAZABnAGUALAB0ACkAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUAQwBvAHIAcgBlAGMAdABpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBfAFQAaQB0AGwAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAE0AZQB0AGgAYQBuAGUAIABjAG8AcgByAGUAYwB0AGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHQAcgBlAGEAdABtAGUAbgB0ACAAZgBhAGMAaQBsAGkAdAB5ACAAdAB5AHAAZQAgAHQAIAB1AHMAZQBkACAAdABvACAAdAByAGUAYQB0ACAAcwBsAHUAZABnAGUAXAAiACkAKQA7AFwAbgBcAG4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBDAG8AcgByAGUAYwB0AGkAbwBuAEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAQwBGAHMAbAB1AGQAZwBlACwAdABcACIAKQApADsAXABuAFwAbgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEMAbwByAHIAZQBjAHQAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAXwBVAG4AaQB0AFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgApACkAOwBcAG4AXABuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUAQwBvAHIAcgBlAGMAdABpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBfAFMAbwB1AHIAYwBlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADQALgAxAC4ANABcACIAKQApADsAXABuAFwAbgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEMAbwByAHIAZQBjAHQAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAXwBEAGEAdABhAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADIALABcAG4AIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIABcACIARgBhAGMAaQBsAGkAdAB5ACAAdAB5AHAAZQAgAHQAXAAiACwAIABcACIAQwBGAHMAbAB1AGQAZwBlACwAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBNAGEAbgBhAGcAZQBkACAAYQBlAHIAbwBiAGkAYwAgAHQAcgBlAGEAdABtAGUAbgB0AFwAIgAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFUAbgBtAGEAbgBhAGcAZQBkACAAYQBlAHIAbwBiAGkAYwAgAHQAcgBlAGEAdABtAGUAbgB0AFwAIgAsACAAMAAuADMAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBBAG4AYQBlAHIAbwBiAGkAYwAgAGQAaQBnAGUAcwB0AG8AcgAvAHIAZQBhAGMAdABvAHIAXAAiACwAIAAwAC4AOAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFMAaABhAGwAbABvAHcAIABhAG4AYQBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuACAAKABkIiAAMgAgAG0AKQBcACIALAAgADAALgAyADsAXABuACAAIAAgACAAIAAgACAAIABcACIARABlAGUAcAAgAGEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AIAAoAFwAdQAwADAAMwBlACAAMgBtACkAXAAiACwAIAAwAC4AOABcAG4AIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgApACkAKQA7AFwAbgBcAG4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBDAG8AcgByAGUAYwB0AGkAbwBuAEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBcACIAKQApADsAXABuAFwAbgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBUAGkAdABsAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBNAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHcAYQBzAHQAZQB3AGEAdABlAHIAXAAiACkAKQA7AFwAbgBcAG4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFYAYQByAGkAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEUARgB3AHcAXAAiACkAKQA7AFwAbgBcAG4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFUAbgBpAHQAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBrAGcAIABDAEgANAAgAC8AIABrAGcAIABDAE8ARABcACIAKQApADsAXABuAFwAbgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AUwBvAHUAcgBjAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAAxADEALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdABzAFwAIgApACkAOwBcAG4AXABuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBEAGEAdABhAFwAbgA9AEwAQQBNAEIARABBACgAIAAwAC4AMgA1ACkAOwBcAG4AXABuAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAXwBUAGkAdABsAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBNAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHMAbAB1AGQAZwBlAFwAIgApACkAOwBcAG4AXABuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIARQBGAHMAbAB1AGQAZwBlAFwAIgApACkAOwBcAG4AXABuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAF8AVQBuAGkAdABcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAGsAZwAgAEMASAA0ACAALwAgAGsAZwAgAEMATwBEAFwAIgApACkAOwBcAG4AXABuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAF8AUwBvAHUAcgBjAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAAxADEALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdABzAFwAIgApACkAOwBcAG4AXABuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAF8ARABhAHQAYQBcAG4APQBMAEEATQBCAEQAQQAoADAALgAyADUAKQA7AFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgBXAGEAcwB0AGUAXwBFAG4AZQByAGcAeQBDAG8AbgB0AGUAbgB0AEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAEIAaQBvAGcAYQBzAEYAbABhAHIAZQBkAF8AVABpAHQAbABlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIARQBuAGUAcgBnAHkAIABjAG8AbgB0AGUAbgB0ACAAZgBhAGMAdABvAHIAIABvAGYAIABzAGwAdQBkAGcAZQAgAGIAaQBvAGcAYQBzACAAZgBsAGEAcgBlAGQAXAAiACkAKQA7AFwAbgBcAG4AVwBhAHMAdABlAF8ARQBuAGUAcgBnAHkAQwBvAG4AdABlAG4AdABGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBCAGkAbwBnAGEAcwBGAGwAYQByAGUAZABfAFYAYQByAGkAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEUAQwBmAGwAYQByAGUAZABcACIAKQApADsAXABuAFwAbgBXAGEAcwB0AGUAXwBFAG4AZQByAGcAeQBDAG8AbgB0AGUAbgB0AEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAEIAaQBvAGcAYQBzAEYAbABhAHIAZQBkAF8AVQBuAGkAdABcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEcASgAgAC8AIABtADMAXAAiACkAKQA7AFwAbgBcAG4AVwBhAHMAdABlAF8ARQBuAGUAcgBnAHkAQwBvAG4AdABlAG4AdABGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBCAGkAbwBnAGEAcwBGAGwAYQByAGUAZABfAFMAbwB1AHIAYwBlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAMQAxAC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAcwBcACIAKQApADsAXABuAFwAbgBXAGEAcwB0AGUAXwBFAG4AZQByAGcAeQBDAG8AbgB0AGUAbgB0AEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAEIAaQBvAGcAYQBzAEYAbABhAHIAZQBkAF8ARABhAHQAYQBcAG4APQBMAEEATQBCAEQAQQAoADAALgAwADMANwA3ACkAOwBcAG4AXABuAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAQgBpAG8AZwBhAHMARgBsAGEAcgBlAGQAXwBUAGkAdABsAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBNAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHMAbAB1AGQAZwBlACAAYgBpAG8AZwBhAHMAIABmAGwAYQByAGUAZABcACIAKQApADsAXABuAFwAbgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBCAGkAbwBnAGEAcwBGAGwAYQByAGUAZABfAFYAYQByAGkAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEUARgBmAGwAYQByAGUAZAAsAEMASAA0AFwAIgApACkAOwBcAG4AXABuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAEIAaQBvAGcAYQBzAEYAbABhAHIAZQBkAF8AVQBuAGkAdABcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAGsAZwAgAEMASAA0ACAALwAgAEcASgBcACIAKQApADsAXABuAFwAbgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBCAGkAbwBnAGEAcwBGAGwAYQByAGUAZABfAFMAbwB1AHIAYwBlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAMQAxAC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAcwBcACIAKQApADsAXABuAFwAbgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBCAGkAbwBnAGEAcwBGAGwAYQByAGUAZABfAEQAYQB0AGEAXABuAD0ATABBAE0AQgBEAEEAKAAwAC4AMgAyADgAOQApADsAXABuAFwAbgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAFcAYQBzAHQAZQBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBCAGkAbwBnAGEAcwBGAGwAYQByAGUAZABfAFQAaQB0AGwAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAcwBsAHUAZABnAGUAIABiAGkAbwBnAGEAcwAgAGYAbABhAHIAZQBkAFwAIgApACkAOwBcAG4AXABuAFcAYQBzAHQAZQBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBCAGkAbwBnAGEAcwBGAGwAYQByAGUAZABfAFYAYQByAGkAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEUARgBmAGwAYQByAGUAZAAsAE4AMgBPAFwAIgApACkAOwBcAG4AXABuAFcAYQBzAHQAZQBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBCAGkAbwBnAGEAcwBGAGwAYQByAGUAZABfAFUAbgBpAHQAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBrAGcAIABOADIATwAgAC8AIABHAEoAXAAiACkAKQA7AFwAbgBcAG4AVwBhAHMAdABlAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAEIAaQBvAGcAYQBzAEYAbABhAHIAZQBkAF8AUwBvAHUAcgBjAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAAxADEALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdABzAFwAIgApACkAOwBcAG4AXABuAFcAYQBzAHQAZQBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBCAGkAbwBnAGEAcwBGAGwAYQByAGUAZABfAEQAYQB0AGEAXABuAD0ATABBAE0AQgBEAEEAKAAxAC4AMQAzADIAZQAtADQAKQA7AFwAbgAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBOADIATwBfAEUAcQB1AGEAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAxADEALgAxADoAIABXAGEAcwB0AGUAdwBhAHQAZQByAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAxADEALgAxAC4AMwAuADEAIABNAGUAdABoAG8AZAAgADEAIAAtACAATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAG8AbgBzAGkAdABlACAAVwBhAHMAdABlAHcAYQB0AGUAcgAgAE0AYQBuAGEAZwBlAG0AZQBuAHQAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwAxADEAXwAxAF8AMwBfADEAXwBfADEAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEYAbABhAHIAZQBkAEIAaQBvAGcAYQBzAFwAbgBOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAZgBsAGEAcgBlAGQAIABiAGkAbwBnAGEAcwBcAG4ARQBfAE4AMgBPAFwAbgB0ACAATgAyAE8AXABuAEUAXwB7AE4AMgBPAH0APQBcAFwAZgByAGEAYwB7AFEAXwB7AGYAbABhAHIAZQBkAH0AfQB7ADEAMAAwADAAfQBcAFwAdABpAG0AZQBzACAARQBGAF8AewBmAGwAYQByAGUAZAAsAE4AMgBPAH0AXABuAFEAXwBmAGwAYQByAGUAZAAgAD0AIAB2AG8AbAB1AG0AZQAgAG8AZgAgAGIAaQBvAGcAYQBzACAAZgBsAGEAcgBlAGQAIAAoAG0AMwAgAG8AcgAgAEcASgApAFwAbgBFAEYAXwBmAGwAYQByAGUAZABfAE4AMgBPACAAPQAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAZgBsAGEAcgBlAGQAIABiAGkAbwBnAGEAcwAgACgAawBnACAATgAyAE8ALwBHAEoAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwAxADEAXwAxAF8AMwBfADEAXwBfADEAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEYAbABhAHIAZQBkAEIAaQBvAGcAYQBzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFEAXwBmAGwAYQByAGUAZAAsACAARQBDAF8AZgBsAGEAcgBlAGQALAAgAEUARgBfAGYAbABhAHIAZQBkAE4AMgBPACwAXABuACAAIAAgACAAKABRAF8AZgBsAGEAcgBlAGQAIAAvACAAMQAwADAAMAApACAAKgAgACgARQBDAF8AZgBsAGEAcgBlAGQAIAAqACAARQBGAF8AZgBsAGEAcgBlAGQATgAyAE8AKQBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEAMQBfADEAXwAzAF8AMQBfAF8AMQBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ARgBsAGEAcgBlAGQAQgBpAG8AZwBhAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABmAGwAYQByAGUAZAAgAGIAaQBvAGcAYQBzAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADEAXwAxAF8AMwBfADEAXwBfADEAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEYAbABhAHIAZQBkAEIAaQBvAGcAYQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAF8ATgAyAE8AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEAMQBfADEAXwAzAF8AMQBfAF8AMQBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ARgBsAGEAcgBlAGQAQgBpAG8AZwBhAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgB0ACAATgAyAE8AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEAMQBfADEAXwAzAF8AMQBfAF8AMQBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ARgBsAGEAcgBlAGQAQgBpAG8AZwBhAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAMQAxAC4AMQAuADMALgAxACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADEAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQAxAF8AMQBfADMAXwAxAF8AXwAxAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBGAGwAYQByAGUAZABCAGkAbwBnAGEAcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQAxAF8AMQBfADMAXwAxAF8AXwAxAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBGAGwAYQByAGUAZABCAGkAbwBnAGEAcwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwB7AE4AMgBPAH0APQBcAFwAZgByAGEAYwB7AFEAXwB7AGYAbABhAHIAZQBkAH0AfQB7ADEAMAAwADAAfQBcAFwAdABpAG0AZQBzACAAXABcAGwAZQBmAHQAWwBFAEMAXwB7AGYAbABhAHIAZQBkAH0AIABcAFwAdABpAG0AZQBzACAARQBGAF8AewBmAGwAYQByAGUAZAAsAE4AMgBPAH0AXABcAHIAaQBnAGgAdABdAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADEAXwAxAF8AMwBfADEAXwBfADEAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEYAbABhAHIAZQBkAEIAaQBvAGcAYQBzAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAA0ACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEAXwBmAGwAYQByAGUAZABcACIALAAgAFwAIgB2AG8AbAB1AG0AZQAgAG8AZgAgAGIAaQBvAGcAYQBzACAAZgBsAGEAcgBlAGQAXAAiACwAIABcACIAbQAzAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBDAF8AZgBsAGEAcgBlAGQAXAAiACwAIABcACIAZQBuAGUAcgBnAHkAIABjAG8AbgB0AGUAbgB0ACAAZgBhAGMAdABvAHIAIABvAGYAIABzAGwAdQBkAGcAZQAgAGIAaQBvAGcAYQBzACAAZgBsAGEAcgBlAGQAXAAiACwAIABcACIARwBKAC8AbQAzAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAF8AZgBsAGEAcgBlAGQATgAyAE8AXAAiACwAIABcACIAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABmAGwAYQByAGUAZAAgAGIAaQBvAGcAYQBzAFwAIgAsACAAXAAiAGsAZwAgAE4AMgBPAC8ARwBKAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AIgB9AF0ALAAiAHAAcgBvAGoAZQBjAHQATgBhAG0AZQBzACIAOgBbACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEEAcABwAGUAbgBkAGkAYwBlAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAUgBvAHcAUwB0AGEAcgB0AE4AdQBtAGIAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAHIAYQB5AEkAbgBUAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUAVAB3AG8AQwBvAGwAdQBtAG4AcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBPAG4AZQBDAG8AbAB1AG0AbgBBAG4AZABIAGUAYQBkAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBTAHAAbABpAHQAUwB0AHIAaQBuAGcASQBuAHQAbwBBAHIAcgBhAHkAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQwBsAGkAbQBhAHQAZQBaAG8AbgBlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAEkAdABlAG0ARgByAG8AbQBNAGkAbgBNAGEAeAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBTAHUAbQBRAHUAYQBuAHQAaQB0AHkARgByAG8AbQBDAHIAaQB0AGUAcgBpAGEAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAUABlAHIAaQBvAGQAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEYAdQBuAGMAdABpAG8AbgBOAGEAbQBlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAE4AMgBPAEUARgBGAHIAbwBtAFAAcgBvAGQASQByAHIAaQBnAGEAdABpAG8AbgBSAGEAaQBuAGYAYQBsAGwAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBHAGUAdABGAHIAYQBjAFcARQBUACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEMAbwBuAHYAZQByAHQAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAVABvAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADEAXwAxAF8AMQBfADEAXwBfADEAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AVwBhAHMAdABlAHcAYQB0AGUAcgBUAHIAZQBhAHQAbQBlAG4AdAAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQAxAF8AMQBfADEAXwAxAF8AXwAxAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFcAYQBzAHQAZQB3AGEAdABlAHIAVAByAGUAYQB0AG0AZQBuAHQAXwBUAGkAdABsAGUAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEAMQBfADEAXwAxAF8AMQBfAF8AMQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBXAGEAcwB0AGUAdwBhAHQAZQByAFQAcgBlAGEAdABtAGUAbgB0AF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADEAXwAxAF8AMQBfADEAXwBfADEAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AVwBhAHMAdABlAHcAYQB0AGUAcgBUAHIAZQBhAHQAbQBlAG4AdABfAFUAbgBpAHQAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEAMQBfADEAXwAxAF8AMQBfAF8AMQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBXAGEAcwB0AGUAdwBhAHQAZQByAFQAcgBlAGEAdABtAGUAbgB0AF8AUwBvAHUAcgBjAGUAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEAMQBfADEAXwAxAF8AMQBfAF8AMQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBXAGEAcwB0AGUAdwBhAHQAZQByAFQAcgBlAGEAdABtAGUAbgB0AF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEAMQBfADEAXwAxAF8AMQBfAF8AMQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBXAGEAcwB0AGUAdwBhAHQAZQByAFQAcgBlAGEAdABtAGUAbgB0AF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQAxAF8AMQBfADEAXwAxAF8AXwAxAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFcAYQBzAHQAZQB3AGEAdABlAHIAVAByAGUAYQB0AG0AZQBuAHQAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQAxAF8AMQBfADEAXwAxAF8AXwAxAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFcAYQBzAHQAZQB3AGEAdABlAHIAVAByAGUAYQB0AG0AZQBuAHQAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUAQwBvAHIAcgBlAGMAdABpAG8AbgBGAGEAYwB0AG8AcgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AVABpAHQAbABlACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBDAG8AcgByAGUAYwB0AGkAbwBuAEYAYQBjAHQAbwByAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEMAbwByAHIAZQBjAHQAaQBvAG4ARgBhAGMAdABvAHIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFUAbgBpAHQAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEMAbwByAHIAZQBjAHQAaQBvAG4ARgBhAGMAdABvAHIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBDAG8AcgByAGUAYwB0AGkAbwBuAEYAYQBjAHQAbwByAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBEAGEAdABhACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBDAG8AcgByAGUAYwB0AGkAbwBuAEYAYQBjAHQAbwByAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUAQwBvAHIAcgBlAGMAdABpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBfAFQAaQB0AGwAZQAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUAQwBvAHIAcgBlAGMAdABpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUAQwBvAHIAcgBlAGMAdABpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBfAFUAbgBpAHQAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEMAbwByAHIAZQBjAHQAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAXwBTAG8AdQByAGMAZQAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUAQwBvAHIAcgBlAGMAdABpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBfAEQAYQB0AGEAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEMAbwByAHIAZQBjAHQAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBUAGkAdABsAGUAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFUAbgBpAHQAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AUwBvAHUAcgBjAGUAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBXAGEAcwB0AGUAdwBhAHQAZQByAF8ARABhAHQAYQAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAF8AVABpAHQAbABlACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBfAFUAbgBpAHQAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBfAFMAbwB1AHIAYwBlACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAXwBEAGEAdABhACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AVwBhAHMAdABlAF8ARQBuAGUAcgBnAHkAQwBvAG4AdABlAG4AdABGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBCAGkAbwBnAGEAcwBGAGwAYQByAGUAZABfAFQAaQB0AGwAZQAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFcAYQBzAHQAZQBfAEUAbgBlAHIAZwB5AEMAbwBuAHQAZQBuAHQARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAQgBpAG8AZwBhAHMARgBsAGEAcgBlAGQAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBXAGEAcwB0AGUAXwBFAG4AZQByAGcAeQBDAG8AbgB0AGUAbgB0AEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAEIAaQBvAGcAYQBzAEYAbABhAHIAZQBkAF8AVQBuAGkAdAAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFcAYQBzAHQAZQBfAEUAbgBlAHIAZwB5AEMAbwBuAHQAZQBuAHQARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAQgBpAG8AZwBhAHMARgBsAGEAcgBlAGQAXwBTAG8AdQByAGMAZQAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFcAYQBzAHQAZQBfAEUAbgBlAHIAZwB5AEMAbwBuAHQAZQBuAHQARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAQgBpAG8AZwBhAHMARgBsAGEAcgBlAGQAXwBEAGEAdABhACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAQgBpAG8AZwBhAHMARgBsAGEAcgBlAGQAXwBUAGkAdABsAGUAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBCAGkAbwBnAGEAcwBGAGwAYQByAGUAZABfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAEIAaQBvAGcAYQBzAEYAbABhAHIAZQBkAF8AVQBuAGkAdAAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAEIAaQBvAGcAYQBzAEYAbABhAHIAZQBkAF8AUwBvAHUAcgBjAGUAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBCAGkAbwBnAGEAcwBGAGwAYQByAGUAZABfAEQAYQB0AGEAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBXAGEAcwB0AGUAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAQgBpAG8AZwBhAHMARgBsAGEAcgBlAGQAXwBUAGkAdABsAGUAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBXAGEAcwB0AGUAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAQgBpAG8AZwBhAHMARgBsAGEAcgBlAGQAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBXAGEAcwB0AGUAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAQgBpAG8AZwBhAHMARgBsAGEAcgBlAGQAXwBVAG4AaQB0ACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AVwBhAHMAdABlAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAEIAaQBvAGcAYQBzAEYAbABhAHIAZQBkAF8AUwBvAHUAcgBjAGUAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBXAGEAcwB0AGUAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAQgBpAG8AZwBhAHMARgBsAGEAcgBlAGQAXwBEAGEAdABhACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBOADIATwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQAxAF8AMQBfADMAXwAxAF8AXwAxAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBGAGwAYQByAGUAZABCAGkAbwBnAGEAcwAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8ATgAyAE8AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEAMQBfADEAXwAzAF8AMQBfAF8AMQBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ARgBsAGEAcgBlAGQAQgBpAG8AZwBhAHMAXwBUAGkAdABsAGUAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAE4AMgBPAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADEAXwAxAF8AMwBfADEAXwBfADEAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEYAbABhAHIAZQBkAEIAaQBvAGcAYQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBOADIATwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQAxAF8AMQBfADMAXwAxAF8AXwAxAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBGAGwAYQByAGUAZABCAGkAbwBnAGEAcwBfAFUAbgBpAHQAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAE4AMgBPAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADEAXwAxAF8AMwBfADEAXwBfADEAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEYAbABhAHIAZQBkAEIAaQBvAGcAYQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAE4AMgBPAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADEAXwAxAF8AMwBfADEAXwBfADEAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEYAbABhAHIAZQBkAEIAaQBvAGcAYQBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAE4AMgBPAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADEAXwAxAF8AMwBfADEAXwBfADEAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEYAbABhAHIAZQBkAEIAaQBvAGcAYQBzAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8ATgAyAE8AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEAMQBfADEAXwAzAF8AMQBfAF8AMQBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ARgBsAGEAcgBlAGQAQgBpAG8AZwBhAHMAXwBBAHIAZwB1AG0AZQBuAHQAcwAiAF0ALAAiAGwAbwBjAGEAbABlACIAOgB7ACIAbABpAHMAdABTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAsACIALAAiAHIAbwB3AFMAZQBwAGEAcgBhAHQAbwByACIAOgAiADsAIgAsACIAYwBvAGwAdQBtAG4AUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgB0AGgAbwB1AHMAYQBuAGQAcwBTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAsACIALAAiAHQAaABvAHUAcwBhAG4AZABzAFAAbwBzAGkAdABpAG8AbgBzACIAOgBbADMAXQAsACIAZABlAGMAaQBtAGEAbABTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAuACIALAAiAGQAYQB0AGUATwByAGQAZQByACIAOgAiAEQATQBZACIALAAiAGMAdQByAHIAZQBuAGMAeQBTAHkAbQBiAG8AbAAiADoAIgAkACIALAAiAGkAcwBDAHUAcgByAGUAbgBjAHkAUwB5AG0AYgBvAGwATABlAGEAZAAiADoAdAByAHUAZQAsACIAaQBzAEMAdQByAHIAZQBuAGMAeQBTAGUAcABCAHkAUwBwAGEAYwBlACIAOgBmAGEAbABzAGUALAAiAHIAbwB3AEwAZQB0AHQAZQByACIAOgAiAFIAIgAsACIAYwBvAGwAdQBtAG4ATABlAHQAdABlAHIAIgA6ACIAQwAiACwAIgByAGMATABlAGYAdABCAHIAYQBjAGsAZQB0ACIAOgAiAFsAIgAsACIAcgBjAFIAaQBnAGgAdABCAHIAYQBjAGsAZQB0ACIAOgAiAF0AIgAsACIAcwB0AGEAdABlAG0AZQBuAHQAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIAOwAiACwAIgBsAG8AYwBhAGwAZQBOAGEAbQBlACIAOgAiAGUAbgAtAHUAcwAiAH0AfQA=</AFEJSONBlob>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="09eef6d6-daa8-4301-8f9f-b1ec38079286" xsi:nil="true"/>
@@ -14146,15 +14125,11 @@
 </p:properties>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9A9CF321-0D35-4044-BC72-33748FE2B865}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
+<AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgAvAC8AIAAtAC0ALQAgAFcAbwByAGsAYgBvAG8AawAgAG0AbwBkAHUAbABlACAALQAtAC0AXABuAC8ALwAgAEEAIABmAGkAbABlACAAbwBmACAAbgBhAG0AZQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAG8AZgAgAHQAaABlACAAZgBvAHIAbQA6AFwAbgAvAC8AIAAgACAAIABuAGEAbQBlACAAPQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AOwBcAG4AXABuACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhACIALAAiAHQAZQB4AHQAIgA6ACIALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgBTAG8AdQByAGMAZQAgAGQAYQB0AGEAIAB0AGgAYQB0ACAAaQBzACAAYwBvAG0AbQBvAG4AIABhAGMAcgBvAHMAcwAgAGEAbABsACAAZQBuAHQAZQByAHAAcgBpAHMAZQAgAHQAeQBwAGUAcwBcAG4ARQB4AGMAZQBsACAAbQBvAGQAdQBsAGUAIABuAGEAbQBlADoAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFMAbwB1AHIAYwBlADoAIABOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQBcAG4ATgBJAFIAXwAyADAAMgAzAF8AVgBvAGwAMQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXABuAHAAIAA9ACAAZABlAG4AcwBpAHQAeQAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAIAAoADAALgA2ADcAOAA0ACAAawBnAC8AbQAzACkAXABuAFQAYQBrAGUAbgAgAGYAcgBvAG0AIAB0AGgAZQAgAE4AYQB0AGkAbwBuAGEAbAAgAEcAcgBlAGUAbgBoAG8AdQBzAGUAIABhAG4AZAAgAEUAbgBlAHIAZwB5ACAAUgBlAHAAbwByAHQAaQBuAGcAIABcAG4AKABNAGUAYQBzAHUAcgBlAG0AZQBuAHQAKQAgAEQAZQB0AGUAcgBtAGkAbgBhAHQAaQBvAG4AIAAyADAAMAA4AFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHAAIAA9ACAAZABlAG4AcwBpAHQAeQAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcALwBtADMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgADIAMAAyADMAIABWAG8AbAB1AG0AZQAgADEAOgAgAEUAcQB1AGEAdABpAG8AbgBzACAAMwAuAEIALgAxAGEAXwAyACwAIAAzAC4AQgAuADEAYwBfADIALAAgADMALgBCAC4AMwBfADEALAAgADMALgBCAC4ANABnAF8AMgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAMAAuADYANwA4ADQAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAFwAbgBDAGcAIAA9ACAANAA0AC8AMgA4ACAAZgBhAGMAdABvAHIAIAB0AG8AIABjAG8AbgB2AGUAcgB0ACAAZQBsAGUAbQBlAG4AdABhAGwAIABtAGEAcwBzACAAbwBmACAATgAyAE8AIAB0AG8AIABtAG8AbABlAGMAdQBsAGEAcgAgAG0AYQBzAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABOADIATwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBDAGcATgAyAE8AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAYQBjAHQAbwByAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgADIAMAAyADMAIABWAG8AbAB1AG0AZQAgADEAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgANAA0AC8AMgA4ACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAFwAbgBGAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABnAGEAcwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgBhAGMAdABvAHIAIAB0AG8AIABjAG8AbgB2AGUAcgB0ACAAZQBsAGUAbQBlAG4AdABhAGwAIABtAGEAcwBzACAAbwBmACAAZwBhAHMAIAB0AG8AIABtAG8AbABlAGMAdQBsAGEAcgAgAG0AYQBzAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBDAGcAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgBhAGMAdABvAHIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFgAWABYAFgAWABYAFgAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADgALAAgADQALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAYQBzAFwAIgAsACAAXAAiAEMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBcACIALAAgAFwAIgBDAG8AbgB2AGUAcgBzAGkAbwBuACAAZgBhAGMAdABvAHIAIAAxAFwAIgAsACAAXAAiAEMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgADIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyAFwAIgAsACAAXAAiADQANAAvADEAMgBcACIALAAgADQANAAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMASAA0AFwAIgAsACAAXAAiADEANgAvADEAMgBcACIALAAgADEANgAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AMgBPAFwAIgAsACAAXAAiADQANAAvADIAOABcACIALAAgADQANAAsACAAMgA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB4AFwAIgAsACAAXAAiADQANgAvADEANABcACIALAAgADQANgAsACAAMQA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwBcACIALAAgAFwAIgAyADgALwAxADIAXAAiACwAIAAyADgALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAE8AMgAgAEwAaQBtAGUAXAAiACwAIABcACIANAA0AC8AMQAyAFwAIgAsACAANAA0ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBNAFYATwBDAFwAIgAsACAAXAAiADEANAAvADEAMgBcACIALAAgADEANAAsACAAMQAyAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABOADIATwBcAG4ARwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAGcAcgBlAGUAbgBoAG8AdQBzAGUAIABnAGEAcwBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABnAHIAZQBlAG4AaABvAHUAcwBlACAAZwBhAHMAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARwBXAFAATgAyAE8AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgBhAGMAdABvAHIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFgAWABYAFgAWABYAFgAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADgALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAYQBzAFwAIgAsACAAXAAiAEMATwAyAC0AZQAgAGYAYQBjAHQAbwByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAE8AMgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBIADQAXAAiACwAIAAyADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgAyAE8AXAAiACwAIAAyADYANQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAEYANABcACIALAAgADYANgAzADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwAyAEYANgBcACIALAAgADEAMgAyADAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAEYANgBcACIALAAgADIAMgA4ADAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAEYAMwBcACIALAAgADEANwAyADAAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAcwB0AGEAdABlAHMAIABhAG4AZAAgAHQAZQByAHIAaQB0AG8AcgBpAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA5ACwAIAAzACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHQAYQB0AGUALwBUAGUAcgByAGkAdABvAHIAeQBcACIALAAgAFwAIgBDAG8AbQBtAG8AbgAgAE4AYQBtAGUAXAAiACwAIABcACIAQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AZQB3ACAAUwBvAHUAdABoACAAVwBhAGwAZQBzAFwAIgAsACAAXAAiAE4AZQB3ACAAUwBvAHUAdABoACAAVwBhAGwAZQBzAFwAIgAsACAAXAAiAE4AUwBXAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAQwBhAHAAaQB0AGEAbAAgAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAEEAQwBUAFwAIgAsACAAXAAiAEEAQwBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAGkAYwB0AG8AcgBpAGEAXAAiACwAIABcACIAVgBpAGMAdABvAHIAaQBhAFwAIgAsACAAXAAiAFYASQBDAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBRAHUAZQBlAG4AcwBsAGEAbgBkAFwAIgAsACAAXAAiAFEAdQBlAGUAbgBzAGwAYQBuAGQAXAAiACwAIABcACIAUQBMAEQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAbwB1AHQAaAAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFMAbwB1AHQAaAAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFMAQQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQBcACIALAAgAFwAIgBXAEEAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAYQBzAG0AYQBuAGkAYQBcACIALAAgAFwAIgBUAGEAcwBtAGEAbgBpAGEAXAAiACwAIABcACIAVABBAFMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwByAHQAaABlAHIAbgAgAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAE4AbwByAHQAaABlAHIAbgAgAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAE4AVABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQBCAFMAIABTAHQAYQB0AGkAcwB0AGMAYQBsACAAQQByAGUAYQBzACAATABlAHYAZQBsACAANAAgAC0AIABXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAEIAdQByAGUAYQB1ACAAbwBmACAAUwB0AGEAdABpAHMAdABpAGMAcwAgACgAQQBCAFMAKQAgAC0AIABTAHQAYQB0AGkAcwB0AGkAYwBhAGwAIABBAHIAZQBhAHMAIABMAGUAdgBlAGwAIAAyACAALQAgADIAMAAyADEAIAAtACAAUwBoAGEAcABlAGYAaQBsAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADEALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAQQAgADQAIABOAGEAbQBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBCAHUAbgBiAHUAcgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAGEAbgBkAHUAcgBhAGgAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABJAG4AbgBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABOAG8AcgB0AGgAIABFAGEAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAATgBvAHIAdABoACAAVwBlAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAFMAbwB1AHQAaAAgAEUAYQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABTAG8AdQB0AGgAIABXAGUAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAAVwBoAGUAYQB0ACAAQgBlAGwAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhACAALQAgAE8AdQB0AGIAYQBjAGsAIAAoAE4AbwByAHQAaAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAATwB1AHQAYgBhAGMAawAgACgAUwBvAHUAdABoACkAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAdwBlAHQAIABhAG4AZAAgAGQAcgB5ACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAyADoAIABUAHIAYQBuAHMAbABhAHQAaQBuAGcAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBzACAAdABvACAAdwBlAHQAIABhAG4AZAAgAGQAcgB5ACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAdwBhAHIAbQAgAC8AIABjAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAvACAAZAByAHkAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAIABhAG4AZAAgAGgAaQBnAGgAIAB0AGUAbQBwACAAYwBsAGEAcwBzAGUAcwAgAHQAbwAgAGEAYwBjAG8AbQBtAG8AZABhAHQAZQAgAGMAbABpAG0AYQB0AGUAIABzAGMAZQBuAGEAcgBpAG8AcwAgAGUAeABjAGwAdQBkAGUAZAAgAGIAeQAgAFYARQBFAFIARwAgAGMAcgBpAHQAZQByAGkAYQAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAGkAeABlAGQAIAB0AHkAcABvACAALQAgAEMAaABhAG4AZwBlAGQAIABcAHUAMAAwADIANwBGAHIAeQBcAHUAMAAwADIANwAgAHQAbwAgAFwAdQAwADAAMgA3AEQAcgB5AFwAdQAwADAAMgA3AC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADUALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAFcAZQB0ACAAbwByACAARAByAHkAIABaAG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABtAG8AbgB0AGEAbgBlAFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAHcAZQB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABkAHIAeQBcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdABcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAtACAAaABpAGcAaAAgAHQAZQBtAHAAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAaABpAGcAaAAgAHQAZQBtAHAAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA1ACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAB3AGEAcgBtACAALwAgAGMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC8AIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdAAgAGEAbgBkACAAaABpAGcAaAAgAHQAZQBtAHAAIABjAGwAYQBzAHMAZQBzACAAdABvACAAYQBjAGMAbwBtAG0AbwBkAGEAdABlACAAYwBsAGkAbQBhAHQAZQAgAHMAYwBlAG4AYQByAGkAbwBzACAAZQB4AGMAbAB1AGQAZQBkACAAYgB5ACAAVgBFAEUAUgBHACAAYwByAGkAdABlAHIAaQBhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAaQB4AGUAZAAgAHQAeQBwAG8AIABpAG4AIABNAEEAVAAgAHYAYQBsAHUAZQAgAGYAbwByACAAdwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAYwBoAGEAbgBnAGUAZAAgADEAMAAgAHQAbwAgADEAMQAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIABtAGkAbgAgAGEAbgBkACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAZgBvAHIAIABNAEEAVAAsACAATQBBAFAALAAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAIABwAGUAcgAgAHkAZQBhAHIALAAgAGUAbABlAHYAYQB0AGkAbwBuACwAIABNAEEAUAA6AFAARQBUACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlAHMAIABmAHIAbwBtACAAcgBlAGEAbAAgAGMAbABpAG0AYQB0AGUAIABkAGEAdABhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAQQBGACAAYQBjAGMAZQBwAHQAcwAgAHIAYQBpAG4AZgBhAGwAbAAgAGEAcwAgAGEAIABwAHIAbwB4AHkAIABmAG8AcgAgAHAAcgBlAGMAaQBwAGkAdABhAHQAaQBvAG4ALgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOQAsACAAMQA2ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAGwAaQBtAGEAdABlACAAWgBvAG4AZQBcACIALAAgAFwAIgBNAEEAVABcACIALAAgAFwAIgBNAEEAUABcACIALAAgAFwAIgBGAHIAbwBzAHQAIABkAGEAeQBzACAAcABlAHIAIAB5AGUAYQByAFwAIgAsACAAXAAiAEUAbABlAHYAYQB0AGkAbwBuAFwAIgAsACAAXAAiAE0AQQBQADoAUABFAFQAXAAiACwAIABcACIATQBpAG4AIAB0AGUAbQBwAFwAIgAsACAAXAAiAE0AYQB4ACAAdABlAG0AcABcACIALAAgAFwAIgBNAGkAbgAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBNAGEAeAAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBNAGkAbgAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAXAAiACwAIABcACIATQBhAHgAIABmAHIAbwBzAHQAIABkAGEAeQBzAFwAIgAsACAAXAAiAE0AaQBuACAAZQBsAGUAdgBhAHQAaQBvAG4AXAAiACwAIABcACIATQBhAHgAIABlAGwAZQB2AGEAdABpAG8AbgBcACIALAAgAFwAIgBNAGkAbgAgAE0AQQBQADoAUABFAFQAXAAiACwAIABcACIATQBpAG4AIABNAEEAUAA6AFAARQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABtAG8AbgB0AGEAbgBlAFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQA4ACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAwADAAIABtAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAMQA4AC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAANwAsACAAMQAwADAAMAAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAHcAZQB0AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQA4ACAAQwBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADIAMAAwADAAIABtAG0AXAAiACwAIABcACIAZCIgADcAXAAiACwAIABcACIAZCIgADEAMAAwADAAIABtAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAMQA4AC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAyADAAMAAwAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQAuADkAOQA5ACwAIAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAOAAgAEMAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADAAMAAwACAAbQBtACAALQAgAGQiIAAyADAAMAAwACAAbQBtAFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgADEAOAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAAMQAwADAAMAAuADAAMAAxACwAIAAyADAAMAAwACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQAuADkAOQA5ACwAIAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAGQAcgB5AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQA4ACAAQwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAwADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAXAAiACwAIAAxADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgADEALgAwADAAMQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAGQiIAAxAFwAIgAsACAAMQAwAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAgAC0AOQA5ADkAOQA5ADkALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMAAgAEMAIAAtACAAZCIgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxAFwAIgAsACAALQA5ADkAOQA5ADkAOQAsACAAMQAwACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAxAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMAAgAEMAIAAtACAAZCIgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAZCIgADEAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAMQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBBAHAAcABlAG4AZABpAGMAZQBzAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdABlADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AQQBUACAAPQAgAG0AZQBhAG4AIABhAG4AbgB1AGEAbAAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBBAFAAIAA9ACAAbQBlAGEAbgAgAGEAbgBuAHUAYQBsACAAcAByAGUAYwBpAHAAaQB0AGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABFAFQAIAA9ACAAcABvAHQAZQBuAHQAaQBhAGwAIABlAHYAYQBwAG8AdAByAGEAbgBzAHAAaQByAGEAdABpAG8AbgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABBAGQAZABlAGQAIABlAHgAdAByAGEAIABNAEEAVAAgAG0AaQBuACAAYQBuAGQAIABNAEEAVAAgAG0AYQB4ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGMAYQBsAGMAdQBsAGEAdABlACAAegBvAG4AZQAgAGYAcgBvAG0AIAByAGUAYQBsACAAdABlAG0AcABlAHIAYQB0AHUAcgBlACAAZABhAHQAYQAuAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANAAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AHUAcgBlACAAWgBvAG4AZQBcACIALAAgAFwAIgBNAGUAZABpAGEAbgAgAEEAbgBuAHUAYQBsACAAVABlAG0AcABlAHIAYQB0AHUAcgBlACAAKABNAEEAVAApAFwAIgAsACAAXAAiAE0AaQBuACAATQBBAFQAXAAiACwAIABcACIATQBhAHgAIABNAEEAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgAFwAIgBlIiAAMgA2ACAAQwBcACIALAAgADIANgAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIABcACIAMQA1ACAALQAgADIANQAgAEMAXAAiACwAIAAxADUALAAgADIANQAuADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIABcACIAZCIgADEANAAgAEMAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADQALgA5ADkAOQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAAQQBkAGQAZQBkACAAZQB4AHQAcgBhACAAUgBhAGkAbgBmAGEAbABsACAAbQBpAG4AIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAG0AYQB4ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGMAYQBsAGMAdQBsAGEAdABlACAAegBvAG4AZQAgAGYAcgBvAG0AIAByAGUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAZABhAHQAYQAuAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBhAGkAbgBmAGEAbABsACAAWgBvAG4AZQBcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABtAGkAbgBcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABtAGEAeABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbAAgAFwAdQAwADAAMwBlACAANgAwADAAbQBtAFwAIgAsACAANgAwADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATABvAHcAIAByAGEAaQBuAGYAYQBsAGwAXAAiACwAIABcACIAQQBuAG4AdQBhAGwAIAByAGEAaQBuAGYAYQBsAGwAIABkIiAANgAwADAAbQBtAFwAIgAsACAALQA5ADkAOQA5ADkAOQAsACAANgAwADAAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABaAG8AbgBlAFwAIgAsACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAGMAcgBpAHQAZQByAGkAYQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATABlAGEAYwBoAGkAbgBnACAAbwBjAGMAdQByAHMAXAAiACwAIABcACIAowMoADXYX9w12E7cNdhW3DXYW9wpAFwAdQAwADAAMwBlAKMDKAA12DjcNdhH3DAAKQArADXYYNw12FzcNdhW3DXYWdwgADXYZNw12E7cNdhh3DXYUtw12F/cIAAOITXYXNw12FncNdhR3DXYVtw12FvcNdhU3CAANdhQ3DXYTtw12F3cNdhO3DXYUNw12FbcNdhh3DXYZtxcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATABlAGEAYwBoAGkAbgBnACAAZABvAGUAcwAgAG4AbwB0ACAAbwBjAGMAdQByAFwAIgAsACAAXAAiAKMDKAA12F/cNdhO3DXYVtw12FvcKQBkIqMDKAA12DjcNdhH3DAAKQArADXYYNw12FzcNdhW3DXYWdwgADXYZNw12E7cNdhh3DXYUtw12F/cIAAOITXYXNw12FncNdhR3DXYVtw12FvcNdhU3CAANdhQ3DXYTtw12F3cNdhO3DXYUNw12FbcNdhh3DXYZtxcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXABuADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAbgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAEQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcwAgAGkAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAXAAiACwAXAAiAEYAcgBhAGMAVwBFAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFkAZQBzACAALQAgAGkAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwAgAC0AIABuAG8AdAAgAGkAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAXAAiACwAIAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoACgAXAAiAFwAIgApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAGQAYQB0AGEAIABzAGMAbwByAGUAcwAgAGYAbwByACAAcwBjAG8AcABlACAAMwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABYAFgAWABYAFgAWABYAFgAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABhAHQAYQAgAHMAbwB1AHIAYwBlAFwAIgAsACAAXAAiAEQAYQB0AGEAIABzAGMAbwByAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAbgB0AGUAcgBuAGEAdABpAG8AbgBhAGwAIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAcwBjAG8AcABlACAAMwAgAGQAYQB0AGEAYgBhAHMAZQBcACIALAAgADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB0AGEAdABlACAAbwByACAAcgBlAGcAaQBvAG4AYQBsACAAcwBjAG8AcABlACAAMwAgAGQAYQB0AGEAYgBhAHMAZQBcACIALAAgADMAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBtAGkAcwBzAGkAbwBuAHMAIABpAG4AdABlAG4AcwBpAHQAeQAgAGMAYQBsAGMAdQBsAGEAdABlAGQAIABmAHIAbwBtACAAYQBwAHAAcgBvAHYAZQBkACAAbQBlAHQAaABvAGQAXAAiACwAIAA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAZQByAGkAZgBpAGUAZAAgAGMAcgBlAGQAZQBuAHQAaQBhAGwAIABtAGEAdABjAGgAaQBuAGcAIABJAFMATwAxADQAMAA2ADcAXAAiACwAIAA1AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXABuADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAbgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgARABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAVgBvAGwAdQBtAGUAIAAxADoAIABMAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmACAAKAAzAC4ARAAuAGIALgAyACkAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAcgBhAGMATABFAEEAQwBIAFwAIgAsADAALgAyADQAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoACgAXAAiAFwAIgApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABuAGkAdAByAG8AZwBlAG4AIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABuAGkAdAByAG8AZwBlAG4AIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABrAGcAIABOADIATwAtAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgAFYAbwBsAHUAbQBlACAAMQA6ACAARQBxAHUAYQB0AGkAbwBuACAAMwAuAEQALgBCAF8AMQAwAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARgBsAGUAYQBjAGgAXAAiACwAMAAuADAAMQAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoACgAXAAiAFwAIgApACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXABuAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADEAXABuAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAZgBvAHIAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AIAAoAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AKQAgACgARQBGAE4AMgBPACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAGYAbwByACAAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAGsAZwAgAE4AMgBPAC0ATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADIALgAyAC4AMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQA1ACwAIAA1ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABqAFwAIgAsAFwAIgBFAEYATgAyAE8AXAAiACwAIABcACIAUAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAbwBuAGwAeQBcACIALAAgAFwAIgBJAHIAcgBpAGcAYQB0AGkAbwBuACAAbQBlAHQAaABvAGQAXAAiACwAIABcACIAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsADAALgAwADAANQA5ACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwAFwAIgAsADAALgAwADAANwAsACAAXAAiAEMAcgBvAHAAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsADAALgAwADAAMQA4ACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEwAbwB3ACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQBcACIALAAwAC4AMAAwADEAOAAsACAAXAAiAFAAYQBzAHQAdQByAGUAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcAAgACgAbABvAHcAIAByAGEAaQBuAGYAYQBsAGwAKQBcACIALAAwAC4AMAAwADIAOQAsACAAXAAiAEMAcgBvAHAAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAGMAcgBvAHAAIAAoAGgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAKQBcACIALAAwAC4AMAAwADgALAAgAFwAIgBDAHIAbwBwAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIASABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB1AGcAYQByAFwAIgAsADAALgAwADEAOQA5ACwAIABcACIAUwB1AGcAYQByAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AdAB0AG8AbgBcACIALAAwAC4AMAAwADUAMwAsACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAG8AcgB0AGkAYwB1AGwAdAB1AHIAYQBsACAAYwByAG8AcABzAFwAIgAsADAALgAwADAANgA0ACwAIABcACIASABvAHIAdABpAGMAdQBsAHQAdQByAGEAbAAgAGMAcgBvAHAAcwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBpAGMAZQAgACgAYwBvAG4AdABpAG4AdQBvAHUAcwAgAGYAbABvAG8AZABpAG4AZwApAFwAIgAsADAALgAwADAAMwAsACAAXAAiAFIAaQBjAGUAXAAiACwAIABcACIAQwBvAG4AdABpAG4AdQBvAHUAcwAgAGYAbABvAG8AZABpAG4AZwBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBpAGMAZQAgACgAcwBpAG4AZwBsAGUAIABhAG4AZAAgAG0AdQBsAHQAaQBwAGwAZQAgAGQAcgBhAGkAbgBhAGcAZQAsACAAbwByACAAYQBsAHQAZQByAG4AYQB0AGUAIAB3AGUAdAB0AGkAbgBnACAAYQBuAGQAIABkAHIAeQBpAG4AZwApAFwAIgAsADAALgAwADAANQAsACAAXAAiAFIAaQBjAGUAXAAiACwAIABcACIAUwBpAG4AZwBsAGUAIABhAG4AZAAgAG0AdQBsAHQAaQBwAGwAZQAgAGQAcgBhAGkAbgBhAGcAZQAsACAAbwByACAAYQBsAHQAZQByAG4AYQB0AGUAIAB3AGUAdAB0AGkAbgBnACAAYQBuAGQAIABkAHIAeQBpAG4AZwBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBxAHUAYQBjAHUAbAB0AHUAcgBlAFwAIgAsADAALgAwADAAMgA2ACwAIABcACIAQQBxAHUAYQBjAHUAbAB0AHUAcgBlAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAG8AcgBlAHMAdAByAHkAXAAiACwAMAAuADAAMAAxADgALAAgAFwAIgBGAG8AcgBlAHMAdAByAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA1ACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGUAbQBvAHYAZQBkACAAZAB1AHAAbABpAGMAYQB0AGUAIABcAHUAMAAwADIANwBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAB1ADAAMAAyADcAIAByAG8AdwAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGUAbQBvAHYAZQBkACAAYQBzAHQAZQByAGkAcwBrAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAFwAdQAwADAAMgA3AHAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAG8AbgBsAHkAXAB1ADAAMAAyADcALAAgAFwAdQAwADAAMgA3AHIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAXAB1ADAAMAAyADcAIABhAG4AZAAgAFwAdQAwADAAMgA3AGkAcgByAGkAZwBhAHQAaQBvAG4AIABtAGUAdABoAG8AZABcAHUAMAAwADIANwAgAGMAbwBsAHUAbQBuAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAdQBwAGwAaQBjAGEAdABlAGQAIABcAHUAMAAwADIANwBuAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQBcAHUAMAAwADIANwAgAHIAbwB3ACAAdwBpAHQAaAAgAHMAYQBtAGUAIABFAEYAIABmAG8AcgAgAGwAbwB3ACAAYQBuAGQAIABoAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAFwAbgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABDAGgAYQBwAHQAZQByACAAMQAsACAAcwBlAGMAdABpAG8AbgAgADEALgA4AC4AMgAgAEwAZQBhAGMAaABpAG4AZwAsACAAYwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBzAFwAbgBJAFAAQwBDADoAIABOADIATwAgAEUATQBJAFMAUwBJAE8ATgBTACAARgBSAE8ATQAgAE0AQQBOAEEARwBFAEQAIABTAE8ASQBMAFMALAAgAEEATgBEACAAQwBPADIAIABFAE0ASQBTAFMASQBPAE4AUwAgAEYAUgBPAE0AIABMAEkATQBFACAAQQBOAEQAIABVAFIARQBBACAAQQBQAFAATABJAEMAQQBUAEkATwBOAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwBXAEUAVAAgAGYAbwByACAAaQByAHIAaQBnAGEAdABpAG8AbgAgAHQAeQBwAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAEMAaABhAHAAdABlAHIAIAAxACwAIABzAGUAYwB0AGkAbwBuACAAMQAuADgALgAyACAATABlAGEAYwBoAGkAbgBnACwAIABjAGwAaQBtAGEAdABlACAAYQBuAGQAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBJAFAAQwBDACAAMgAwADEAOQAgAFIAZQBmAGkAbgBlAG0AZQBuAHQAIABWAG8AbAB1AG0AZQAgADQAOgAgAEMAaABhAHAAdABlAHIAIAAxADEAOgAgAE4AMgBPACAARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAATQBhAG4AYQBnAGUAZAAgAFMAbwBpAGwAcwAsACAAYQBuAGQAIABDAE8AMgAgAEUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAEwAaQBtAGUAIABhAG4AZAAgAFUAcgBlAGEAIABBAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGkAbwBuACAAdAB5AHAAZQAgAGkAcgBcACIALABcACIARgByAGEAYwBXAEUAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAByAGkAcAAgAGkAcgByAGkAZwBhAHQAaQBvAG4AXAAiACwAIAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAcAByAGkAbgBrAGwAZQByACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB1AHIAZgBhAGMAZQAgAGkAcgByAGkAZwBhAHQAaQBvAG4AXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AdABoAGUAcgAgAGkAcgByAGkAZwBhAHQAaQBvAG4AXAAiACwAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAARgBSAE8ATQAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAAVABhAGIAbABlACAAYwByAGUAYQB0AGUAZAAgAGIAYQBzAGUAZAAgAG8AbgAgAFYARQBFAFIARwAgAHQAZQB4AHQAIABcAHUAMAAwADIANwBBAHIAZQBhAHMAIABhAHIAZQAgAHMAdQBiAGoAZQBjAHQAIAB0AG8AIABsAGUAYQBjAGgAaQBuAGcAIAAoAGkALgBlAC4ALAAgAGkAbgAgAHQAaABlACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQApACAAdwBoAGUAbgAuAC4ALgAgAHQAaABlACAAbABhAG4AZAAgAGkAcwAgAGkAcgByAGkAZwBhAHQAZQBkACAAKABlAHgAYwBlAHAAdAAgAGQAcgBpAHAAIABpAHIAcgBpAGcAYQB0AGkAbwBuACkALgBcAHUAMAAwADIANwBcACIAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAFwAbgBUAGEAYgBsAGUAIABBAC4AMgAuADIALgAyADoAIABFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAdQByAGkAbgBlACAAYQBuAGQAIABkAHUAbgBnACAAZABlAHAAbwBzAGkAdABlAGQAIABvAG4AIABwAGEAcwB0AHUAcgBlACwAIAByAGEAbgBnAGUAIABvAHIAIABwAGEAZABkAG8AYwBrACAAKABrAGcAIABOADIATwAtAE4ALwBrAGcAIABOACkAIAAoAEUARgBQAFIAUAApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAdQByAGkAbgBlACAAYQBuAGQAIABkAHUAbgBnACAAZABlAHAAbwBzAGkAdABlAGQAIABvAG4AIABwAGEAcwB0AHUAcgBlACwAIAByAGEAbgBnAGUAIABvAHIAIABwAGEAZABkAG8AYwBrAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AMgBPACAALQAgAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADIALgAyAC4AMgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAEUARgBQAFIAUABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAAyAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABDAGgAYQBuAGcAZQBkACAAXAB1ADAAMAAyADcARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBzAFwAdQAwADAAMgA3ACAAdABvACAAcwBpAG4AZwB1AGwAYQByACAAXAB1ADAAMAAyADcARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcAHUAMAAwADIANwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAG8AbgB0AGgAcwAgAHQAbwAgAFMAZQBhAHMAbwBuAHMAIABNAGEAcABwAGkAbgBnAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBvAG4AdABoAFwAIgAsACAAXAAiAFMAZQBhAHMAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAGEAbgB1AGEAcgB5AFwAIgAsACAAXAAiAFMAdQBtAG0AZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAGUAYgByAHUAYQByAHkAXAAiACwAIABcACIAUwB1AG0AbQBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQByAGMAaABcACIALAAgAFwAIgBBAHUAdAB1AG0AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBwAHIAaQBsAFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAGEAeQBcACIALAAgAFwAIgBBAHUAdAB1AG0AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASgB1AG4AZQBcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASgB1AGwAeQBcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQB1AGcAdQBzAHQAXAAiACwAIABcACIAVwBpAG4AdABlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAZQBwAHQAZQBtAGIAZQByAFwAIgAsACAAXAAiAFMAcAByAGkAbgBnAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBPAGMAdABvAGIAZQByAFwAIgAsACAAXAAiAFMAcAByAGkAbgBnAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdgBlAG0AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAZQBjAGUAbQBiAGUAcgBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBhAG4AdQByAGUAIABNAGEAbgBhAGcAZQBtAGUAbgB0ACAAEyAgAE0AZQB0AGgAYQBuAGUAIABjAG8AbgB2AGUAcgBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABwAGUAcgAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAIAAoAGYAcgBhAGMAdABpAG8AbgApACAAKABNAEMARgBpAG0AKQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAxAC4AOAAuADEAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIAMgAsACAAMQA2ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAE0AQQBUACAAKAC6AEMAKQBcACIALAAgAFwAIgBVAG4AYwBvAHYAZQByAGUAZAAgAGEAbgBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuAFwAIgAsACAAXAAiAEMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBcACIALAAgAFwAIgBMAGkAcQB1AGkAZAAgAFMAbAB1AHIAcgB5ACAAKAB3AGkAdABoAG8AdQB0ACAAbgBhAHQAdQByAGEAbAAgAGMAcgB1AHMAdAApAFwAIgAsACAAXAAiAEQAYQBpAGwAeQAgAHMAcAByAGUAYQBkACAAKABiACkAXAAiACwAIABcACIAQwBvAG0AcABvAHMAdABpAG4AZwAgACgAcABhAHMAcwBpAHYAZQAgAHcAaQBuAGQAcgBvAHcAKQBcACIALAAgAFwAIgBTAG8AbABpAGQAIABTAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAFAAaQB0ACAAUwB0AG8AcgBhAGcAZQAgAFwAdQAwADAAMwBjADEAIABtAG8AbgB0AGgAXAAiACwAIABcACIARABlAGUAcAAgAEwAaQB0AHQAZQByAFwAIgAsACAAXAAiAFAAbwB1AGwAdAByAHkAIABNAGEAbgB1AHIAZQAgACgAdwBpAHQAaAAvAHcAaQB0AGgAbwB1AHQAIABsAGkAdAB0AGUAcgApAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAcAByAG8AYwBlAHMAcwBpAG4AZwAgAGkAbgB0AG8AIABwAGUAbABsAGUAdABpAHoAZQBkACAAZgBlAHIAdABpAGwAaQBzAGUAcgBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgAgAHQAbwAgAHMAbwBpAGwAXAAiACwAIABcACIAUABhAHMAdAB1AHIAZQAsACAAUgBhAG4AZwBlACAAYQBuAGQAIABQAGEAZABkAG8AYwBrACAAKABjACkAKABkACkAXAAiACwAIABcACIATQBBAFQAIAByAGEAdwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgAFwAIgBkIjEAMABcACIALAAgADAALgA2ADYALAAgADAALgAxACwAIAAwAC4AMQAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIAAxADEALAAgADAALgA2ADgALAAgADAALgAxACwAIAAwAC4AMQAxACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgADEAMgAsACAAMAAuADcALAAgADAALgAxACwAIAAwAC4AMQAzACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgADEAMwAsACAAMAAuADcAMQAsACAAMAAuADEALAAgADAALgAxADQALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQA0ACwAIAAwAC4ANwAzACwAIAAwAC4AMQAsACAAMAAuADEANQAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA1ACwAIAAwAC4ANwA0ACwAIAAwAC4AMQAsACAAMAAuADEANwAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEANQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEANgAsACAAMAAuADcANQAsACAAMAAuADEALAAgADAALgAxADgALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADcALAAgADAALgA3ADYALAAgADAALgAxACwAIAAwAC4AMgAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEANwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEAOAAsACAAMAAuADcANwAsACAAMAAuADEALAAgADAALgAyADIALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADkALAAgADAALgA3ADcALAAgADAALgAxACwAIAAwAC4AMgA0ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgAwACwAIAAwAC4ANwA4ACwAIAAwAC4AMQAsACAAMAAuADIANgAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIAMQAsACAAMAAuADcAOAAsACAAMAAuADEALAAgADAALgAyADkALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADIALAAgADAALgA3ADgALAAgADAALgAxACwAIAAwAC4AMwAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgAzACwAIAAwAC4ANwA5ACwAIAAwAC4AMQAsACAAMAAuADMANAAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIANAAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgAzADcALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADUALAAgADAALgA3ADkALAAgADAALgAxACwAIAAwAC4ANAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AXAAiACwAIAAyADYALAAgADAALgA3ADkALAAgADAALgAxACwAIAAwAC4ANAA0ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AXAAiACwAIAAyADcALAAgADAALgA4ACwAIAAwAC4AMQAsACAAMAAuADQAOAAsACAAMAAuADAAMQAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIANwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtAFwAIgAsACAAXAAiAGUiMgA4AFwAIgAsACAAMAAuADgALAAgADAALgAxACwAIAAwAC4ANQAsACAAMAAuADAAMQAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBBAG4AYQBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuAFwAIgAsACAAXAAiAEQAaQBnAGUAcwB0AGUAcgAgAC8AIABjAG8AdgBlAHIAZQBkACAAbABhAGcAbwBvAG4AcwBcACIALAAgAFwAIgBMAGkAcQB1AGkAZAAgAHMAeQBzAHQAZQBtAHMAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAXAAiACwAIABcACIAQwBvAG0AcABvAHMAdABpAG4AZwAgACgAcABhAHMAcwBpAHYAZQAgAHcAaQBuAGQAcgBvAHcAKQBcACIALAAgAFwAIgBTAG8AbABpAGQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAFAAaQB0ACAAcwB0AG8AcgBhAGcAZQBcACIALAAgAFwAIgBEAGUAZQBwACAAbABpAHQAdABlAHIAXAAiACwAIABcACIAUABvAHUAbAB0AHIAeQAgAG0AYQBuAHUAcgBlACAAdwBpAHQAaAAgAGIAZQBkAGQAaQBuAGcAXAAiACwAIABcACIAUABvAHUAbAB0AHIAeQAgAG0AYQBuAHUAcgBlACAAdwBpAHQAaABvAHUAdAAgAGIAZQBkAGQAaQBuAGcAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABwAHIAbwBjAGUAcwBzAGkAbgBnAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuAFwAIgAsACAAXAAiAFAAYQBzAHQAdQByAGUAIAByAGEAbgBnAGUAIABhAG4AZAAgAHAAYQBkAGQAbwBjAGsAXAAiACwAIABcACIATQBBAFQAIAByAGEAdwBcACIAIABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAOgAgAEEAZABkAGUAZAAgAHIAbwB3ACAAbwBmACAATgBJAFIAIABNAE0AQQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgAgAEQAdQBwAGwAaQBjAGEAdABlAGQAIABcAHUAMAAwADIANwBQAG8AdQBsAHQAcgB5ACAAdwBpAHQAaAAgAGEAbgBkACAAdwBpAHQAaABvAHUAdAAgAGwAaQB0AHQAZQByAFwAdQAwADAAMgA3ACAAYwBvAGwAdQBtAG4AIAB3AGkAdABoACAAcwBlAHAAYQByAGEAdABlACAATgBJAFIAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AIABBAGQAZABlAGQAIABcAHUAMAAwADIANwBNAEEAVAAgAHIAYQB3AFwAdQAwADAAMgA3ACAAYwBvAGwAdQBtAG4AIAB0AG8AIABhAGwAbABvAHcAIABsAG8AbwBrAHUAcAAgAG8AZgAgAG4AdQBtAGIAZQByAHMALgBcACIAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAbgBkACAAYwByAG8AcAAgAHIAZQBzAGkAZAB1AGUAcwAgAHIAZQB0AHUAcgBuAGUAZAAgAHQAbwAgAHQAaABlACAAcwBvAGkAbABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBGAE4AaQAgAFwAdQAwADAAMgA2ACAARQBGAE4AMgBPAGkAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABOADIATwAgAC0AIABOACAALwAgAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADIALgAxAC4ANABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgAFwAIgBFAEYATgBpACAAXAB1ADAAMAAyADYAIABFAEYATgAyAE8AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIAAwAC4AMAAwADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAANQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIAXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBcAG4AQwBvAG4AdgBlAHIAdAAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcAG4ARQBOADIATwAgAEMATwAyAGUAXABuAHQAIABDAE8AMgBlAFwAbgBFAE4AMgBPADoAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAAoAHQAIABOADIATwApAFwAbgBHAFcAUABOADIATwA6ACAAZwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIAAoAHQAIABDAE8AMgAtAGUAIAAvACAAdAAgAE4AMgBPACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABFAF8ATgAyAE8ALAAgAEcAVwBQAF8ATgAyAE8ALABcAG4AIAAgACAAIABFAF8ATgAyAE8AIAAqACAARwBXAFAAXwBOADIATwBcAG4AIAAgACkAXABuADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAbwBuAHYAZQByAHQAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAB0AG8AIABjAGEAcgBiAG8AbgAgAGQAaQBvAHgAaQBkAGUAIABlAHEAdQBpAHYAYQBsAGUAbgB0ACAAZQBtAGkAcwBzAGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBOADIATwAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAE8AMgBlAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMATwAyAF8AZQAgAD0AIABFAF8AewBOADIATwB9ACAAXABcAHQAaQBtAGUAcwAgAEcAVwBQAF8AewBOADIATwB9AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUATgAyAE8AXAAiACwAXAAiAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAE4AMgBPACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAVwBQAE4AMgBPAFwAIgAsAFwAIgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAATgAyAE8AKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBcAG4AQwBvAG4AdgBlAHIAdAAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcAG4ARQBDAEgANAAgAEMATwAyAGUAXABuAHQAIABDAE8AMgBlAFwAbgBFAEMASAA0ADoAIABtAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAAoAHQAIABDAEgANAApAFwAbgBHAFcAUABDAEgANAA6ACAAZwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAG0AZQB0AGgAYQBuAGUAIAAoAHQAIABDAE8AMgAtAGUAIAAvACAAdAAgAEMASAA0ACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABFAF8AQwBIADQALAAgAEcAVwBQAF8AQwBIADQALABcAG4AIAAgACAAIABFAF8AQwBIADQAIAAqACAARwBXAFAAXwBDAEgANABcAG4AIAAgACkAXABuADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAbwBuAHYAZQByAHQAIABtAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAB0AG8AIABjAGEAcgBiAG8AbgAgAGQAaQBvAHgAaQBkAGUAIABlAHEAdQBpAHYAYQBsAGUAbgB0ACAAZQBtAGkAcwBzAGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBDAEgANAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAE8AMgBlAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMATwAyAF8AZQAgAD0AIABFAF8AewBDAEgANAB9ACAAXABcAHQAaQBtAGUAcwAgAEcAVwBQAF8AewBDAEgANAB9AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUAQwBIADQAXAAiACwAXAAiAE0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAEMASAA0ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAVwBQAEMASAA0AFwAIgAsAFwAIgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbQBlAHQAaABhAG4AZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAAQwBIADQAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIAVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAUgBvAHcAUwB0AGEAcgB0AE4AdQBtAGIAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwALABSAG8AdwBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAYQBuAGQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAUgBPAFcAKABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAApACAAKwAgAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkAIAAtACAAMQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABUAGEAYgBsAGUASABlAGEAZABlAHIAQwBlAGwAbAAsAFwAbgAgACAAQwBPAEwAVQBNAE4AKABUAGEAYgBsAGUASABlAGEAZABlAHIAQwBlAGwAbAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBBAHIAcgBhAHkASQBuAFQAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgAEEAcgByAGEAeQBEAGEAdABhACwAIABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQAsACAAWwBDAG8AbAB1AG0AbgBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAQQBuAGQAQQByAHIAYQB5AF0ALABcAG4AIABJAEYARQBSAFIATwBSACgAXABuACAAIAAgACAAIABJAE4ARABFAFgAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAVQBOAEkAUQBVAEUAKABBAHIAcgBhAHkARABhAHQAYQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBPAFcAKAApAC0AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAUgBvAHcAUwB0AGEAcgB0AE4AdQBtAGIAZQByACgAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwALAAgAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEMATwBMAFUATQBOACgAKQAtAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAEMAbwBsAHUAbQBuAFMAdABhAHIAdABOAHUAbQBiAGUAcgAoAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACkAIAArAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAEMAbwBsAHUAbQBuAHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBBAG4AZABBAHIAcgBhAHkAKQAsACAAMQAsACAAQwBvAGwAdQBtAG4AcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAEEAbgBkAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACAAIAAgACAAKQAsACAAXAAiAFwAIgBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFwAIgBcACIAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEkARgAoAEkAUwBOAFUATQBCAEUAUgAoAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFwAIgBcACIAKQBcAG4AIAAgACAAIAApACwAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApACwAIAAwACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBUAHcAbwBDAG8AbAB1AG0AbgBzAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlADEALAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADIALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAWwBWAGEAbAB1AGUASQBGAEYAYQBsAHMAZQBdACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoADEALAAgACgATABvAG8AawB1AHAAQQByAHIAYQB5ADEAPQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQApACoAKABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABWAGEAbAB1AGUASQBGAEYAYQBsAHMAZQApACwAIABcACIAXAAiACwAIABWAGEAbAB1AGUASQBGAEYAYQBsAHMAZQApACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBPAG4AZQBDAG8AbAB1AG0AbgBBAG4AZABIAGUAYQBkAGUAcgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACwAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMgAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADEALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFsAVgBhAGwAdQBlAEkAZgBGAGEAbABzAGUAXQAsAFwAbgAgACAAIAAgAEkARgBFAFIAUgBPAFIAKABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADEALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACkAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAFYAYQBsAHUAZQBJAGYARgBhAGwAcwBlACkALAAgAFwAIgBcACIALAAgAFYAYQBsAHUAZQBJAGYARgBhAGwAcwBlACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAcABsAGkAdABTAHQAcgBpAG4AZwBJAG4AdABvAEEAcgByAGEAeQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEMAZQBsAGwALAAgAEQAZQBsAGkAbQBpAHQAZQByACwAIABbAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAxAF0ALAAgAFsAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADIAXQAsAFwAbgAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAWABNAEwAKABcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBcAHUAMAAwADMAYwB0AFwAdQAwADAAMwBlAFwAdQAwADAAMwBjAHMAXAB1ADAAMAAzAGUAXAAiACAAXAB1ADAAMAAyADYAXABuACAAIAAgACAAIAAgACAAIABTAFUAQgBTAFQASQBUAFUAVABFACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFMAVQBCAFMAVABJAFQAVQBUAEUAKABTAFUAQgBTAFQASQBUAFUAVABFACgAQwBlAGwAbAAsAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAxACwAXAAiAFwAIgApACwAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADIALABcACIAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAARABlAGwAaQBtAGkAdABlAHIALABcACIAXAB1ADAAMAAzAGMALwBzAFwAdQAwADAAMwBlAFwAdQAwADAAMwBjAHMAXAB1ADAAMAAzAGUAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAKQAgAFwAdQAwADAAMgA2AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFwAdQAwADAAMwBjAC8AcwBcAHUAMAAwADMAZQBcAHUAMAAwADMAYwAvAHQAXAB1ADAAMAAzAGUAXAAiACwAXABuACAAIAAgACAAIAAgACAAIABcACIALwAvAHMAXAAiAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABDAGwAaQBtAGEAdABlAFoAbwBuAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABhAHYAZwBUAGUAbQBwACwAYQB2AGcAUgBhAGkAbgAsAGYAcgBvAHMAdABEAGEAeQBzACwAZQBsAGUAdgAsAG0AYQBwAF8AcABlAHQALABcAG4AIAAgACAAIABtAGkAbgBUAGUAbQBwAEEAcgByAGEAeQAsAG0AYQB4AFQAZQBtAHAAQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4AUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQAsAG0AYQB4AFIAYQBpAG4AZgBhAGwAbABBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBGAHIAbwBzAHQAQQByAHIAYQB5ACwAbQBhAHgARgByAG8AcwB0AEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAEUAbABlAHYAYQB0AGkAbwBuAEEAcgByAGEAeQAsAG0AYQB4AEUAbABlAHYAYQB0AGkAbwBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAFAARQBUAEEAcgByAGEAeQAsAG0AYQB4AFAARQBUAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAGMAbABpAG0AYQB0AGUAWgBvAG4AZQBBAHIAcgBhAHkALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAbQBhAHMAawAsAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBUAGUAbQBwAEEAcgByAGEAeQApAFwAdQAwADAAMwBjAD0AYQB2AGcAVABlAG0AcAApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AFQAZQBtAHAAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBhAHYAZwBUAGUAbQBwACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4AUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQApAFwAdQAwADAAMwBjAD0AYQB2AGcAUgBhAGkAbgApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AFIAYQBpAG4AZgBhAGwAbABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGEAdgBnAFIAYQBpAG4AKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBGAHIAbwBzAHQAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBmAHIAbwBzAHQARABhAHkAcwApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AEYAcgBvAHMAdABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGYAcgBvAHMAdABEAGEAeQBzACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4ARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBlAGwAZQB2ACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBlAGwAZQB2ACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4AUABFAFQAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBtAGEAcABfAHAAZQB0ACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgAUABFAFQAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBtAGEAcABfAHAAZQB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAFQAQQBLAEUAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAKABjAGwAaQBtAGEAdABlAFoAbwBuAGUAQQByAHIAYQB5ACwAbQBhAHMAawAsACAAXAAiAE4AbwAgAG0AYQB0AGMAaABcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAASQB0AGUAbQBGAHIAbwBtAE0AaQBuAE0AYQB4AFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABNAGkAbgBBAHIAcgBhAHkALAAgAE0AYQB4AEEAcgByAGEAeQAsACAASQB0AGUAbQBBAHIAcgBhAHkALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAbQBhAHMAawAsAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABNAGkAbgBBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAE0AYQB4AEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0ATABvAG8AawB1AHAAVgBhAGwAdQBlACkALABcAG4AIAAgACAAIAAgACAAIAAgAEYASQBMAFQARQBSACgASQB0AGUAbQBBAHIAcgBhAHkALAAgAG0AYQBzAGsALAAgAFwAIgBOAG8AIABtAGEAdABjAGgAXAAiACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBTAHUAbQBRAHUAYQBuAHQAaQB0AHkARgByAG8AbQBDAHIAaQB0AGUAcgBpAGEAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAEMAcgBpAHQAZQByAGkAYQAxACwAIABDAHIAaQB0AGUAcgBpAGEAMQBUAHkAcABlAEEAcgByAGEAeQAsACAAUQB1AGEAbgB0AGkAdAB5ACwAIABbAE0AdQBsAHQAaQBwAGwAaQBlAHIAXQAsACAAWwBDAHIAaQB0AGUAcgBpAGEAMgBdACwAWwBDAHIAaQB0AGUAcgBpAGEAMgBBAHIAcgBhAHkAXQAsAFwAbgAgACAATABFAFQAKABcAG4AIAAgACAAIABtAHUAbAB0AGkAcABsAGkAZQByACwAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAE0AdQBsAHQAaQBwAGwAaQBlAHIAKQAsADEALABNAHUAbAB0AGkAcABsAGkAZQByACkALABcAG4AIAAgACAAIABxAHUAYQBuAHQAaQB0AHkALAAgAFEAdQBhAG4AdABpAHQAeQAqAE0AdQBsAHQAaQBwAGwAaQBlAHIALABcAG4AIAAgACAAIABjAHIAaQB0AGUAcgBpAGEAMQAsAC0ALQAoAEMAcgBpAHQAZQByAGkAYQAxAFQAeQBwAGUAQQByAHIAYQB5AD0AQwByAGkAdABlAHIAaQBhADEAKQAsAFwAbgAgACAAIAAgAGMAcgBpAHQAZQByAGkAYQAyACwASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABDAHIAaQB0AGUAcgBpAGEAMgApACwAMQAsAC0ALQAoAEMAcgBpAHQAZQByAGkAYQAyAEEAcgByAGEAeQA9AEMAcgBpAHQAZQByAGkAYQAyACkAKQAsAFwAbgAgACAAIAAgAFMAVQBNAFAAUgBPAEQAVQBDAFQAKABjAHIAaQB0AGUAcgBpAGEAMQAqAGMAcgBpAHQAZQByAGkAYQAyACoAcQB1AGEAbgB0AGkAdAB5ACkAXABuACAAIAApAFwAbgApADsAXABuAFwAbgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAHMAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBTAHQAYQByAHQALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBFAG4AZAAsAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAUwAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgACAAIAAgACAARQAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAXABuACAAIAAgACAAIAAgACAAIABtACwATQBPAE4AVABIACgAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAApACwAXABuACAAIAAgACAAIAAgACAAIABkACwARABBAFkAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAFAAZQByAGkAbwBkAEUAbgBkACwATABBAE0AQgBEAEEAKABzAHQALABFAEQAQQBUAEUAKABzAHQALAAxADIAKQAtADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAQQAsAFMALQAzADYANQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBhACwAWQBFAEEAUgAoAEEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBiACwAWQBFAEEAUgAoAEUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZgBpAHIAcwB0AFkAZQBhAHIALAB5AGEAKwAoAFAAZQByAGkAbwBkAEUAbgBkACgARABBAFQARQAoAHkAYQAsAG0ALABkACkAKQBcAHUAMAAwADMAYwAgAFMAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAbABhAHMAdABZAGUAYQByACwAeQBiAC0AKABEAEEAVABFACgAeQBiACwAbQAsAGQAKQBcAHUAMAAwADMAZQAgAEUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAATQBBAFgAKAAwACwAbABhAHMAdABZAGUAYQByAC0AZgBpAHIAcwB0AFkAZQBhAHIAKwAxACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAFAAZQByAGkAbwBkAHMAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBTAHQAYQByAHQALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBFAG4AZAAsAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAUwAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgACAAIAAgACAARQAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAXABuACAAIAAgACAAIAAgACAAIABtACwATQBPAE4AVABIACgAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAApACwAXABuACAAIAAgACAAIAAgACAAIABkACwARABBAFkAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALAAgAC8AKgBoAGUAbABwAGUAcgA6ACAAZQBuAGQAIABkAGEAdABlACAAZgBvAHIAIABhACAAcgBlAHAAbwByAHQAaQBuAGcAIABwAGUAcgBpAG8AZAAgAHMAdABhAHIAdABpAG4AZwAgAGEAdAAgAGEAIABnAGkAdgBlAG4AIABkAGEAdABlACoALwBcAG4AIAAgACAAIAAgACAAIAAgAFAAZQByAGkAbwBkAEUAbgBkACwATABBAE0AQgBEAEEAKABzAHQALABFAEQAQQBUAEUAKABzAHQALAAxADIAKQAtADEAKQAsACAALwAqAG8AbgBsAHkAIABuAGUAZQBkACAAdABvACAAbABvAG8AawAgAGIAYQBjAGsAIAAzADYANQAgAGQAYQB5AHMAKABtAGEAeAAgAG8AdgBlAHIAbABhAHAAIAB3AGkAbgBkAG8AdwApACoALwBcAG4AIAAgACAAIAAgACAAIAAgAEEALABTAC0AMwA2ADUALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYQAsAFkARQBBAFIAKABBACkALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYgAsAFkARQBBAFIAKABFACkALAAgAC8AKgBpAGYAIAB0AGgAZQAgAGEAbgBjAGgAbwByACAAZgBvAHIAIAB5AGEAIABlAG4AZABzACAAYgBlAGYAbwByAGUAIABTACwAaQB0ACAAYwBhAG4AXAB1ADAAMAAyADcAdAAgAG8AdgBlAHIAbABhAHAAOwAgAG0AbwB2AGUAIAB0AG8AIABuAGUAeAB0ACAAeQBlAGEAcgAqAC8AXABuACAAIAAgACAAIAAgACAAIABmAGkAcgBzAHQAWQBlAGEAcgAsAHkAYQArACgAUABlAHIAaQBvAGQARQBuAGQAKABEAEEAVABFACgAeQBhACwAbQAsAGQAKQApAFwAdQAwADAAMwBjAFMAKQAsACAALwAqAGkAZgAgAHQAaABlACAAYQBuAGMAaABvAHIAIABmAG8AcgAgAHkAYgAgAHMAdABhAHIAdABzACAAYQBmAHQAZQByACAARQAsAGkAdAAgAGMAYQBuAFwAdQAwADAAMgA3AHQAIABvAHYAZQByAGwAYQBwADsAIABtAG8AdgBlACAAdABvACAAcAByAGUAdgBpAG8AdQBzACAAeQBlAGEAcgAqAC8AXABuACAAIAAgACAAIAAgACAAIABsAGEAcwB0AFkAZQBhAHIALAB5AGIALQAoAEQAQQBUAEUAKAB5AGIALABtACwAZAApAFwAdQAwADAAMwBlAEUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAbgAsAE0AQQBYACgAMAAsAGwAYQBzAHQAWQBlAGEAcgAtAGYAaQByAHMAdABZAGUAYQByACsAMQApACwAXABuACAAIAAgACAAIAAgACAAIAB5AHIAcwAsAFMARQBRAFUARQBOAEMARQAoAG4ALAAxACwAZgBpAHIAcwB0AFkAZQBhAHIALAAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAHMAdABhAHIAdABzACwARABBAFQARQAoAHkAcgBzACwAbQAsAGQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZQBuAGQAcwAsAE0AQQBQACgAcwB0AGEAcgB0AHMALABQAGUAcgBpAG8AZABFAG4AZAApACwAXABuACAAIAAgACAAIAAgACAAIAB0AGEAZwAsAEkARgAoAHMAdABhAHIAdABzAD0AUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAIgAgACgAVABoAGkAcwAgAHIAZQBwAG8AcgB0AGkAbgBnACAAYwB5AGMAbABlACkAXAAiACwAXAAiAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABzAHQAYQByAHQAcwBUAGUAeAB0ACwAVABFAFgAVAAoAHMAdABhAHIAdABzACwAXAAiAGQAZAAgAG0AbQBtACAAeQB5AHkAeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZQBuAGQAcwBUAGUAeAB0ACwAVABFAFgAVAAoAGUAbgBkAHMALABcACIAZABkACAAbQBtAG0AIAB5AHkAeQB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABuAD0AMAAsAFwAIgBcACIALABIAFMAVABBAEMASwAoAHMAdABhAHIAdABzAFQAZQB4AHQAIABcAHUAMAAwADIANgAgAFwAIgAgAHQAbwAgAFwAIgAgAFwAdQAwADAAMgA2ACAAZQBuAGQAcwBUAGUAeAB0ACAAXAB1ADAAMAAyADYAIAB0AGEAZwApACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkARgB1AG4AYwB0AGkAbwBuAE4AYQBtAGUAXABuAD0ATABBAE0AQgBEAEEAKABGAHUAbgBjAHQAaQBvAG4ALAAgAFQARQBYAFQAQgBFAEYATwBSAEUAKABGAE8AUgBNAFUATABBAFQARQBYAFQAKABGAHUAbgBjAHQAaQBvAG4AKQAsACAAXAAiACgAXAAiACkAKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAE4AMgBPAEUARgBGAHIAbwBtAFAAcgBvAGQASQByAHIAaQBnAGEAdABpAG8AbgBSAGEAaQBuAGYAYQBsAGwAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAIABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACwAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AQQByAHIAYQB5ACwAIABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkAEEAcgByAGEAeQAsACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAQQByAHIAYQB5ACwAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQALAAgAEkARgAoAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAPQBcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEEAbgB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQAsACAASQBGACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAAgAD0AIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAIABcACIAQQBuAHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKAAxACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEEAcgByAGEAeQA9AFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AKQAqAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAoAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAQQByAHIAYQB5AD0ASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAApACoAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACgAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAQQByAHIAYQB5AD0AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEcAZQB0AEYAcgBhAGMAVwBFAFQAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ALABcAG4AIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQALAAgAFwAbgAgACAAIAAgACAAIAAgACAAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUALABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBMAG8AbwBrAHUAcAAsAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQALAAgAFwAbgAgACAAIAAgACAAIAAgACAAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ATABvAG8AawB1AHAALABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBGAHIAYQBjAFcARQBUACAAKwAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVABcAHUAMAAwADMAZQAwACwAIAAxACwAIAAwACkAXABuACAAIAAgACAAKQApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEMAbwBuAHYAZQByAHQAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAVABvAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUALABcAG4AIAAgACAAIABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBBAHIAcgBhAHkALAAgAFMAdABhAHQAZQBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUALAAgAFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAEEAcgByAGEAeQAsACAAUwB0AGEAdABlAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwBvAHUAcgBjAGUASAB5AHAAZQByAGwAaQBuAGsAXABuAD0ATABBAE0AQgBEAEEAKABUAGEAcgBnAGUAdABDAGUAbABsACwAXABuACAAIABMAEUAVAAoAFwAbgAgACAAIAAgAHMAaAAsACAAVABFAFgAVABBAEYAVABFAFIAKABDAEUATABMACgAXAAiAGYAaQBsAGUAbgBhAG0AZQBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsACAAXAAiAF0AXAAiACkALABcAG4AIAAgACAAIABhAGQAZAByACwAIABDAEUATABMACgAXAAiAGEAZABkAHIAZQBzAHMAXAAiACwAIABUAGEAcgBnAGUAdABDAGUAbABsACkALABcAG4AIAAgACAAIABcACIAIwBcAHUAMAAwADIANwBcACIAIABcAHUAMAAwADIANgAgAHMAaAAgAFwAdQAwADAAMgA2ACAAXAAiAFwAdQAwADAAMgA3ACEAXAAiACAAXAB1ADAAMAAyADYAIABhAGQAZAByAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAbwB1AHIAYwBlAEgAeQBwAGUAcgBsAGkAbgBrAEQAaQBmAGYAZQByAGUAbgB0AFMAaABlAGUAdABcAG4APQBMAEEATQBCAEQAQQAoAFQAYQByAGcAZQB0AEMAZQBsAGwALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAcwBoACwAIABUAEUAWABUAEEARgBUAEUAUgAoAEMARQBMAEwAKABcACIAZgBpAGwAZQBuAGEAbQBlAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAIABcACIAXQBcACIAKQAsAFwAbgAgACAAIAAgAGEAZABkAHIALAAgAEMARQBMAEwAKABcACIAYQBkAGQAcgBlAHMAcwBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsAFwAbgAgACAAIAAgAFwAIgAjAFwAIgAgAFwAdQAwADAAMgA2ACAAYQBkAGQAcgBcAG4AIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgBnAHUAbQBlAG4AdABzAF8AMQBfADIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALABcAG4AIAAgACAAIABDAEgATwBPAFMARQBDAE8ATABTACgAQQByAGcAdQBtAGUAbgB0AHMAQQByAHIAYQB5ACwAIAAxACwAIAAyACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgBnAHUAbQBlAG4AdABzAF8AMwBfADQAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALABcAG4AIAAgACAAIABDAEgATwBPAFMARQBDAE8ATABTACgAQQByAGcAdQBtAGUAbgB0AHMAQQByAHIAYQB5ACwAIAAzACwAIAA0ACkAXABuACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8ARwBlAHQATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUALAAgAE0ATQBTACwAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUAQQByAHIAYQB5ACwAIABNAE0AUwBBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKABcAG4AIAAgACAAIAAgACAAIAAgAE0ARQBEAEkAQQBOACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFIATwBVAE4ARAAoAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAsACAAMAApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATQBJAE4AKABUAGUAbQBwAGUAcgBhAHQAdQByAGUAQQByAHIAYQB5ACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABNAEEAWAAoAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkALABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKABNAE0AUwAsACAATQBNAFMAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFIAZQBzAHUAbAB0AHMASQB0AGUAbQBGAHIAbwBtAEUAcQB1AGEAdABpAG8AbgBUAGkAdABsAGUAQQBuAGQAUwBvAHUAcgBjAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGkAdABsAGUAQwBlAGwAbAAsACAAUwBvAHUAcgBjAGUAQwBlAGwAbAAsAFwAbgAgACAAIAAgAFMAVQBCAFMAVABJAFQAVQBUAEUAKABMAEUARgBUACgAUwBvAHUAcgBjAGUAQwBlAGwAbAAsACAARgBJAE4ARAAoAFwAIgAsAFwAIgAsACAAUwBvAHUAcgBjAGUAQwBlAGwAbAApACAALQAxACkALAAgAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABcACIALAAgAFwAIgBcACIAKQAgAFwAdQAwADAAMgA2ACAAXAAiACAAXAAiACAAXAB1ADAAMAAyADYAIABUAGkAdABsAGUAQwBlAGwAbABcAG4AKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AVwBhAHMAdABlAHcAYQB0AGUAcgBfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAiACwAIgB0AGUAeAB0ACIAOgAiAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AMQAxAC4AMQA6ACAAVwBhAHMAdABlAHcAYQB0AGUAcgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AMQAxAC4AMQAuADEALgAxACAATQBlAHQAaABvAGQAIAAxACAALQAgAE0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABvAG4AcwBpAHQAZQAgAFcAYQBzAHQAZQB3AGEAdABlAHIAIABNAGEAbgBhAGcAZQBtAGUAbgB0AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8AMQAxAF8AMQBfADEAXwAxAF8AXwAxAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFcAYQBzAHQAZQB3AGEAdABlAHIAVAByAGUAYQB0AG0AZQBuAHQAXABuAE0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIAB3AGEAcwB0AGUAdwBhAHQAZQByACAAdAByAGUAYQB0AG0AZQBuAHQAXABuAEUAXwBDAEgANABcAG4AdAAgAEMASAA0AFwAbgBFAF8AewBDAEgANAB9AD0AXABcAGYAcgBhAGMAewAxAH0AewAxADAAMAAwAH0AXABcAHQAaQBtAGUAcwBcAFwAbABlAGYAdABbAFwAXABsAGUAZgB0ACgAVwBfAHQAXABcAHQAaQBtAGUAcwBcAFwAbABlAGYAdAAoAEMATwBEAF8AewBpAG4AfQBcAFwAdABpAG0AZQBzACgAMQAtAEYAXwB7AHMAbAB1AGQAZwBlAH0AKQAtAEMATwBEAF8AewBvAHUAdAB9AFwAXAByAGkAZwBoAHQAKQBcAFwAdABpAG0AZQBzACAAQwBGAF8AewB3AHcALAB0AH0AXABcAHQAaQBtAGUAcwAgAEUARgBfAHsAdwB3AH0AXABcAHIAaQBnAGgAdAApACsAXABcAGwAZQBmAHQAKABXAF8AdABcAFwAdABpAG0AZQBzAFwAXABsAGUAZgB0ACgAQwBPAEQAXwB7AGkAbgB9AFwAXAB0AGkAbQBlAHMAKABGAF8AewBzAGwAdQBkAGcAZQB9AC0ARgBfAHsAcgBlAG0AbwB2AGUAZAB9ACkAXABcAHIAaQBnAGgAdAApAFwAXAB0AGkAbQBlAHMAIABDAEYAXwB7AHMAbAB1AGQAZwBlACwAdAB9AFwAXAB0AGkAbQBlAHMAIABFAEYAXwB7AHMAbAB1AGQAZwBlAH0AXABcAHIAaQBnAGgAdAApAC0AXABcAGwAZQBmAHQAKAA2AC4ANwA4ADQAXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQA0AH0AXABcAHQAaQBtAGUAcwAoAFEAXwB7AGMAYQBwAH0AKwBRAF8AewBmAGwAYQByAGUAZAB9ACsAUQBfAHsAbwB1AHQAfQApAFwAXAByAGkAZwBoAHQAKQArAFwAXABsAGUAZgB0ACgAUQBfAHsAZgBsAGEAcgBlAGQAfQBcAFwAdABpAG0AZQBzACAARQBDAF8AewBmAGwAYQByAGUAZAB9AFwAXAB0AGkAbQBlAHMAIABFAEYAXwB7AGYAbABhAHIAZQBkACwAQwBIADQAfQBcAFwAcgBpAGcAaAB0ACkAXABcAHIAaQBnAGgAdABdAFwAbgBXAF8AdAAgAD0AIABxAHUAYQBuAHQAaQB0AHkAIABvAGYAIAB3AGEAcwB0AGUAdwBhAHQAZQByACAAdAByAGUAYQB0AGUAZAAgAGEAdAAgAGYAYQBjAGkAbABpAHQAeQAgAHQAeQBwAGUAIAB0ACAAKABtADMAKQBcAG4AQwBPAEQAXwBpAG4AIAA9ACAAYQB2AGUAcgBhAGcAZQAgAGkAbgBsAGUAdAAgAEMAaABlAG0AaQBjAGEAbAAgAE8AeAB5AGcAZQBuACAARABlAG0AYQBuAGQAIABjAG8AbgBjAGUAbgB0AHIAYQB0AGkAbwBuACAAbwBmACAAdwBhAHMAdABlAHcAYQB0AGUAcgAgACgAawBnACAAQwBPAEQALwBtADMAKQBcAG4ARgBfAHMAbAB1AGQAZwBlACAAPQAgAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAEMATwBEACAAcgBlAG0AbwB2AGUAZAAgAGYAcgBvAG0AIAB3AGEAcwB0AGUAdwBhAHQAZQByACAAYQBzACAAcwBsAHUAZABnAGUAXABuAEMATwBEAF8AbwB1AHQAIAA9ACAAYQB2AGUAcgBhAGcAZQAgAG8AdQB0AGwAZQB0ACAAQwBPAEQAIABjAG8AbgBjAGUAbgB0AHIAYQB0AGkAbwBuACAAbwBmACAAdwBhAHMAdABlAHcAYQB0AGUAcgAgACgAawBnACAAQwBPAEQALwBtADMAKQBcAG4AQwBGAF8AdwB3AF8AdAAgAD0AIABtAGUAdABoAGEAbgBlACAAYwBvAHIAcgBlAGMAdABpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABmAGEAYwBpAGwAaQB0AHkAIAB0AHkAcABlACAAdAAgAHUAcwBlAGQAIAB0AG8AIAB0AHIAZQBhAHQAIAB3AGEAcwB0AGUAdwBhAHQAZQByAFwAbgBFAEYAXwB3AHcAIAA9ACAAbQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB3AGEAcwB0AGUAdwBhAHQAZQByACAAKABrAGcAIABDAE8AMgBlAC8AawBnACAAQwBPAEQAKQBcAG4ARgBfAHIAZQBtAG8AdgBlAGQAIAA9ACAAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAQwBPAEQAIAByAGUAbQBvAHYAZQBkACAAZgByAG8AbQAgAHQAaABlACAAdwBhAHMAdABlAHcAYQB0AGUAcgAgAHQAcgBlAGEAdABtAGUAbgB0ACAAZgBhAGMAaQBsAGkAdAB5ACAAYQBuAGQAIAB0AHIAYQBuAHMAZgBlAHIAcgBlAGQAIABlAGwAcwBlAHcAaABlAHIAZQBcAG4AQwBGAF8AcwBsAHUAZABnAGUAXwB0ACAAPQAgAG0AZQB0AGgAYQBuAGUAIABjAG8AcgByAGUAYwB0AGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAGYAYQBjAGkAbABpAHQAeQAgAHQAeQBwAGUAIAB0ACAAdQBzAGUAZAAgAHQAbwAgAHQAcgBlAGEAdAAgAHMAbAB1AGQAZwBlAFwAbgBFAEYAXwBzAGwAdQBkAGcAZQAgAD0AIABtAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHMAbAB1AGQAZwBlACAAKABrAGcAIABDAE8AMgBlAC8AawBnACAAQwBPAEQAKQBcAG4AUQBfAGMAYQBwACAAPQAgAHEAdQBhAG4AdABpAHQAeQAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAIABpAG4AIABzAGwAdQBkAGcAZQAgAGIAaQBvAGcAYQBzACAAYwBhAHAAdAB1AHIAZQBkACAAZgBvAHIAIABjAG8AbQBiAHUAcwB0AGkAbwBuACAAKABtADMAIABDAEgANAApAFwAbgBRAF8AZgBsAGEAcgBlAGQAIAA9ACAAcQB1AGEAbgB0AGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQAgAGkAbgAgAHMAbAB1AGQAZwBlACAAYgBpAG8AZwBhAHMAIABmAGwAYQByAGUAZAAgACgAbQAzACAAQwBIADQAKQBcAG4AUQBfAG8AdQB0ACAAPQAgAHEAdQBhAG4AdABpAHQAeQAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAIABpAG4AIABzAGwAdQBkAGcAZQAgAGIAaQBvAGcAYQBzACAAdAByAGEAbgBzAGYAZQByAHIAZQBkACAAbwB1AHQAIABvAGYAIAB0AGgAZQAgAHQAcgBlAGEAdABtAGUAbgB0ACAAZgBhAGMAaQBsAGkAdAB5ACAAKABtADMAIABDAEgANAApAFwAbgBFAEMAXwBmAGwAYQByAGUAZAAgAD0AIABlAG4AZQByAGcAeQAgAGMAbwBuAHQAZQBuAHQAIABmAGEAYwB0AG8AcgAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAIABpAG4AIABzAGwAdQBkAGcAZQAgAGIAaQBvAGcAYQBzACAAZgBsAGEAcgBlAGQAIAAoAEcASgAvAG0AMwApAFwAbgBFAEYAXwBmAGwAYQByAGUAZABfAEMASAA0ACAAPQAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAcwBsAHUAZABnAGUAIABiAGkAbwBnAGEAcwAgAGYAbABhAHIAZQBkACAAKABrAGcAIABDAE8AMgBlAC8ARwBKACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8AMQAxAF8AMQBfADEAXwAxAF8AXwAxAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFcAYQBzAHQAZQB3AGEAdABlAHIAVAByAGUAYQB0AG0AZQBuAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAVwBfAHQALAAgAEMATwBEAF8AaQBuACwAIABGAF8AcwBsAHUAZABnAGUALAAgAEMATwBEAF8AbwB1AHQALAAgAEMARgBfAHcAdwBfAHQALAAgAEUARgBfAHcAdwAsACAARgBfAHIAZQBtAG8AdgBlAGQALAAgAEMARgBfAHMAbAB1AGQAZwBlAF8AdAAsACAARQBGAF8AcwBsAHUAZABnAGUALAAgAFEAXwBjAGEAcAAsACAAUQBfAGYAbABhAHIAZQBkACwAIABRAF8AbwB1AHQALAAgAEUAQwBfAGYAbABhAHIAZQBkACwAIABFAEYAXwBmAGwAYQByAGUAZABDAEgANAAsAFwAbgAgACAAIAAgACgAMQAvADEAMAAwADAAKQAgACoAIAAoACgAVwBfAHQAIAAqACAAKABDAE8ARABfAGkAbgAgACoAIAAoADEAIAAtACAARgBfAHMAbAB1AGQAZwBlACkAIAAtACAAQwBPAEQAXwBvAHUAdAApACAAKgAgAEMARgBfAHcAdwBfAHQAIAAqACAARQBGAF8AdwB3ACkAIAArACAAKABXAF8AdAAgACoAIAAoAEMATwBEAF8AaQBuACAAKgAgACgARgBfAHMAbAB1AGQAZwBlACAALQAgAEYAXwByAGUAbQBvAHYAZQBkACkAKQAgACoAIABDAEYAXwBzAGwAdQBkAGcAZQBfAHQAIAAqACAARQBGAF8AcwBsAHUAZABnAGUAKQAgAC0AIAAoADYALgA3ADgANAAgACoAIAAxADAAXgAtADQAIAAqACAAKABRAF8AYwBhAHAAIAArACAAUQBfAGYAbABhAHIAZQBkACAAKwAgAFEAXwBvAHUAdAApACkAIAArACAAKABRAF8AZgBsAGEAcgBlAGQAIAAqACAAKABFAEMAXwBmAGwAYQByAGUAZAAgACoAIABFAEYAXwBmAGwAYQByAGUAZABDAEgANAApACkAKQBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEAMQBfADEAXwAxAF8AMQBfAF8AMQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBXAGEAcwB0AGUAdwBhAHQAZQByAFQAcgBlAGEAdABtAGUAbgB0AF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAdwBhAHMAdABlAHcAYQB0AGUAcgAgAHQAcgBlAGEAdABtAGUAbgB0AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADEAXwAxAF8AMQBfADEAXwBfADEAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AVwBhAHMAdABlAHcAYQB0AGUAcgBUAHIAZQBhAHQAbQBlAG4AdABfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBfAEMASAA0AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADEAXwAxAF8AMQBfADEAXwBfADEAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AVwBhAHMAdABlAHcAYQB0AGUAcgBUAHIAZQBhAHQAbQBlAG4AdABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAEgANABcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQAxAF8AMQBfADEAXwAxAF8AXwAxAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFcAYQBzAHQAZQB3AGEAdABlAHIAVAByAGUAYQB0AG0AZQBuAHQAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAMQAxAC4AMQAuADEALgAxACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADEAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQAxAF8AMQBfADEAXwAxAF8AXwAxAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFcAYQBzAHQAZQB3AGEAdABlAHIAVAByAGUAYQB0AG0AZQBuAHQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAARwByAGUAZQBuAGgAbwB1AHMAZQAgAGEAbgBkACAARQBuAGUAcgBnAHkAIABSAGUAcABvAHIAdABpAG4AZwAgAE0AZQBhAHMAdQByAGUAbQBlAG4AdAAgAEQAZQB0AGUAcgBtAGkAbgBhAHQAaQBvAG4AIAAyADAAMAA4AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADEAXwAxAF8AMQBfADEAXwBfADEAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AVwBhAHMAdABlAHcAYQB0AGUAcgBUAHIAZQBhAHQAbQBlAG4AdABfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwB7AEMASAA0AH0APQBcAFwAZgByAGEAYwB7ADEAfQB7ADEAMAAwADAAfQBcAFwAdABpAG0AZQBzAFwAXABsAGUAZgB0AHsAXABcAGwAZQBmAHQAewBXAF8AdABcAFwAdABpAG0AZQBzAFwAXABsAGUAZgB0AFsAQwBPAEQAXwB7AGkAbgB9AFwAXAB0AGkAbQBlAHMAKAAxAC0ARgBfAHsAcwBsAHUAZABnAGUAfQApAC0AQwBPAEQAXwB7AG8AdQB0AH0AXABcAHIAaQBnAGgAdABdAFwAXAB0AGkAbQBlAHMAIABDAEYAXwB7AHcAdwAsAHQAfQBcAFwAdABpAG0AZQBzACAARQBGAF8AewB3AHcAfQBcAFwAcgBpAGcAaAB0AH0AKwBcAFwAbABlAGYAdAB7AFcAXwB0AFwAXAB0AGkAbQBlAHMAXABcAGwAZQBmAHQAWwBDAE8ARABfAHsAaQBuAH0AXABcAHQAaQBtAGUAcwAoAEYAXwB7AHMAbAB1AGQAZwBlAH0ALQBGAF8AewByAGUAbQBvAHYAZQBkAH0AKQBcAFwAcgBpAGcAaAB0AF0AXABcAHQAaQBtAGUAcwAgAEMARgBfAHsAcwBsAHUAZABnAGUALAB0AH0AXABcAHQAaQBtAGUAcwAgAEUARgBfAHsAcwBsAHUAZABnAGUAfQBcAFwAcgBpAGcAaAB0AH0ALQBcAFwAbABlAGYAdAB7ADYALgA3ADgANABcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADQAfQBcAFwAdABpAG0AZQBzACAAXABcAGwAZQBmAHQAWwAgAFEAXwB7AGMAYQBwAH0AKwBRAF8AewBmAGwAYQByAGUAZAB9ACsAUQBfAHsAbwB1AHQAfQBcAFwAcgBpAGcAaAB0AF0AXABcAHIAaQBnAGgAdAB9ACsAXABcAGwAZQBmAHQAewBRAF8AewBmAGwAYQByAGUAZAB9AFwAXAB0AGkAbQBlAHMAIABcAFwAbABlAGYAdABbACAARQBDAF8AewBmAGwAYQByAGUAZAB9AFwAXAB0AGkAbQBlAHMAIABFAEYAXwB7AGYAbABhAHIAZQBkACwAQwBIADQAfQBcAFwAcgBpAGcAaAB0AF0AXABcAHIAaQBnAGgAdAB9AFwAXAByAGkAZwBoAHQAfQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQAxAF8AMQBfADEAXwAxAF8AXwAxAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFcAYQBzAHQAZQB3AGEAdABlAHIAVAByAGUAYQB0AG0AZQBuAHQAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEANQAsACAANAAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAF8AdABcACIALAAgAFwAIgBxAHUAYQBuAHQAaQB0AHkAIABvAGYAIAB3AGEAcwB0AGUAdwBhAHQAZQByACAAdAByAGUAYQB0AGUAZAAgAGEAdAAgAGYAYQBjAGkAbABpAHQAeQAgAHQAeQBwAGUAIAB0AFwAIgAsACAAXAAiAG0AMwBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwBEAF8AaQBuAFwAIgAsACAAXAAiAGEAdgBlAHIAYQBnAGUAIABpAG4AbABlAHQAIABDAGgAZQBtAGkAYwBhAGwAIABPAHgAeQBnAGUAbgAgAEQAZQBtAGEAbgBkACAAYwBvAG4AYwBlAG4AdAByAGEAdABpAG8AbgAgAG8AZgAgAHcAYQBzAHQAZQB3AGEAdABlAHIAXAAiACwAIABcACIAawBnACAAQwBPAEQALwBtADMAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAF8AcwBsAHUAZABnAGUAXAAiACwAIABcACIAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAQwBPAEQAIAByAGUAbQBvAHYAZQBkACAAZgByAG8AbQAgAHcAYQBzAHQAZQB3AGEAdABlAHIAIABhAHMAIABzAGwAdQBkAGcAZQBcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAE8ARABfAG8AdQB0AFwAIgAsACAAXAAiAGEAdgBlAHIAYQBnAGUAIABvAHUAdABsAGUAdAAgAEMATwBEACAAYwBvAG4AYwBlAG4AdAByAGEAdABpAG8AbgAgAG8AZgAgAHcAYQBzAHQAZQB3AGEAdABlAHIAXAAiACwAIABcACIAawBnACAAQwBPAEQALwBtADMAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAEYAXwB3AHcAXwB0AFwAIgAsACAAXAAiAG0AZQB0AGgAYQBuAGUAIABjAG8AcgByAGUAYwB0AGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAGYAYQBjAGkAbABpAHQAeQAgAHQAeQBwAGUAIAB0ACAAdQBzAGUAZAAgAHQAbwAgAHQAcgBlAGEAdAAgAHcAYQBzAHQAZQB3AGEAdABlAHIAXAAiACwAIABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAF8AdwB3AFwAIgAsACAAXAAiAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAdwBhAHMAdABlAHcAYQB0AGUAcgBcACIALAAgAFwAIgBrAGcAIABDAEgANAAvAGsAZwAgAEMATwBEAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBfAHIAZQBtAG8AdgBlAGQAXAAiACwAIABcACIAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAQwBPAEQAIAByAGUAbQBvAHYAZQBkACAAZgByAG8AbQAgAHQAaABlACAAdwBhAHMAdABlAHcAYQB0AGUAcgAgAHQAcgBlAGEAdABtAGUAbgB0ACAAZgBhAGMAaQBsAGkAdAB5ACAAYQBuAGQAIAB0AHIAYQBuAHMAZgBlAHIAcgBlAGQAIABlAGwAcwBlAHcAaABlAHIAZQBcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAEYAXwBzAGwAdQBkAGcAZQBfAHQAXAAiACwAIABcACIAbQBlAHQAaABhAG4AZQAgAGMAbwByAHIAZQBjAHQAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAZgBhAGMAaQBsAGkAdAB5ACAAdAB5AHAAZQAgAHQAIAB1AHMAZQBkACAAdABvACAAdAByAGUAYQB0ACAAcwBsAHUAZABnAGUAXAAiACwAIABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAF8AcwBsAHUAZABnAGUAXAAiACwAIABcACIAbQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABzAGwAdQBkAGcAZQBcACIALAAgAFwAIgBrAGcAIABDAEgANAAvAGsAZwAgAEMATwBEAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUQBfAGMAYQBwAFwAIgAsACAAXAAiAHEAdQBhAG4AdABpAHQAeQAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAIABpAG4AIABzAGwAdQBkAGcAZQAgAGIAaQBvAGcAYQBzACAAYwBhAHAAdAB1AHIAZQBkACAAZgBvAHIAIABjAG8AbQBiAHUAcwB0AGkAbwBuAFwAIgAsACAAXAAiAG0AMwAgAEMASAA0AFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUQBfAGYAbABhAHIAZQBkAFwAIgAsACAAXAAiAHEAdQBhAG4AdABpAHQAeQAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAIABpAG4AIABzAGwAdQBkAGcAZQAgAGIAaQBvAGcAYQBzACAAZgBsAGEAcgBlAGQAIABiAHkAIAB0AGgAZQAgAHQAcgBlAGEAdABtAGUAbgB0ACAAZgBhAGMAaQBsAGkAdAB5AFwAIgAsACAAXAAiAG0AMwAgAEMASAA0AFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUQBfAG8AdQB0AFwAIgAsACAAXAAiAHEAdQBhAG4AdABpAHQAeQAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAIABpAG4AIABzAGwAdQBkAGcAZQAgAGIAaQBvAGcAYQBzACAAdAByAGEAbgBzAGYAZQByAHIAZQBkACAAbwB1AHQAIABvAGYAIAB0AGgAZQAgAHQAcgBlAGEAdABtAGUAbgB0ACAAZgBhAGMAaQBsAGkAdAB5AFwAIgAsACAAXAAiAG0AMwAgAEMASAA0AFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBDAF8AZgBsAGEAcgBlAGQAXAAiACwAIABcACIAZQBuAGUAcgBnAHkAIABjAG8AbgB0AGUAbgB0ACAAZgBhAGMAdABvAHIAIABvAGYAIABtAGUAdABoAGEAbgBlACAAaQBuACAAcwBsAHUAZABnAGUAIABiAGkAbwBnAGEAcwAgAGYAbABhAHIAZQBkAFwAIgAsACAAXAAiAEcASgAvAG0AMwBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARgBfAGYAbABhAHIAZQBkAEMASAA0AFwAIgAsACAAXAAiAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAcwBsAHUAZABnAGUAIABiAGkAbwBnAGEAcwAgAGYAbABhAHIAZQBkAFwAIgAsACAAXAAiAGsAZwAgAEMASAA0AC8ARwBKAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAdABcACIALAAgAFwAIgB0AHIAZQBhAHQAbQBlAG4AdAAgAGYAYQBjAGkAbABpAHQAeQAgAHQAeQBwAGUAXAAiACwAIABcACIAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAFYARQBFAFIARwBfADEAMQBfADEAXwAxAF8AMQBfAF8AMQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBXAGEAcwB0AGUAdwBhAHQAZQByAFQAcgBlAGEAdABtAGUAbgB0AF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBOACAAUwBPAFUAUgBDAEUAOgAgAEMAaABhAG4AZwBlAGQAIAB1AG4AaQB0AHMAIABvAGYAIABFAEYAXwB3AHcALAAgAEUARgBfAFMAbAB1AGQAZwBlACAAYQBuAGQAIABFAEYAXwBmAGwAYQByAGUAZAAgAGYAcgBvAG0AIABDAE8AMgBlACAAdABvACAAQwBIADQAIAB0AG8AIABtAGEAdABjAGgAIABkAGEAdABhACAAaQBuACAAVABhAGIAbABlACAAXAAiACkAOwAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBTAG8AdQByAGMAZQBEAGEAdABhACIALAAiAHQAZQB4AHQAIgA6ACIALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgBUAGEAYgBsAGUAIABBAC4ANAAuADEALgAzADoAIABNAGUAdABoAGEAbgBlACAAYwBvAHIAcgBlAGMAdABpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB0AHIAZQBhAHQAbQBlAG4AdAAgAGYAYQBjAGkAbABpAHQAeQAgAHQAeQBwAGUAIAB0ACAAdQBzAGUAZAAgAHQAbwAgAHQAcgBlAGEAdAAgAHcAYQBzAHQAZQB3AGEAdABlAHIAIAAoAGYAcgBhAGMAdABpAG8AbgApACAAKABDAEYAdwB3ACwAdAApAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEMAbwByAHIAZQBjAHQAaQBvAG4ARgBhAGMAdABvAHIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFQAaQB0AGwAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAE0AZQB0AGgAYQBuAGUAIABjAG8AcgByAGUAYwB0AGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHQAcgBlAGEAdABtAGUAbgB0ACAAZgBhAGMAaQBsAGkAdAB5ACAAdAB5AHAAZQAgAHQAIAB1AHMAZQBkACAAdABvACAAdAByAGUAYQB0ACAAdwBhAHMAdABlAHcAYQB0AGUAcgBcACIAKQApADsAXABuAFwAbgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEMAbwByAHIAZQBjAHQAaQBvAG4ARgBhAGMAdABvAHIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFYAYQByAGkAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEMARgB3AHcALAB0AFwAIgApACkAOwBcAG4AXABuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUAQwBvAHIAcgBlAGMAdABpAG8AbgBGAGEAYwB0AG8AcgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AVQBuAGkAdABcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIAKQApADsAXABuAFwAbgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEMAbwByAHIAZQBjAHQAaQBvAG4ARgBhAGMAdABvAHIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADQALgAxAC4AMwBcACIAKQApADsAXABuAFwAbgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEMAbwByAHIAZQBjAHQAaQBvAG4ARgBhAGMAdABvAHIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAEQAYQB0AGEAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANgAsACAAMgAsAFwAbgAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBGAGEAYwBpAGwAaQB0AHkAIAB0AHkAcABlACAAdABcACIALAAgAFwAIgBDAEYAdwB3ACwAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBNAGEAbgBhAGcAZQBkACAAYQBlAHIAbwBiAGkAYwAgAHQAcgBlAGEAdABtAGUAbgB0AFwAIgAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFUAbgBtAGEAbgBhAGcAZQBkACAAYQBlAHIAbwBiAGkAYwAgAHQAcgBlAGEAdABtAGUAbgB0AFwAIgAsACAAMAAuADMAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBBAG4AYQBlAHIAbwBiAGkAYwAgAGQAaQBnAGUAcwB0AG8AcgAvAHIAZQBhAGMAdABvAHIAXAAiACwAIAAwAC4AOAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFMAaABhAGwAbABvAHcAIABhAG4AYQBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuACAAKABkIiAAMgAgAG0AKQBcACIALAAgADAALgAyADsAXABuACAAIAAgACAAIAAgACAAIABcACIARABlAGUAcAAgAGEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AIAAoAFwAdQAwADAAMwBlACAAMgBtACkAXAAiACwAIAAwAC4AOABcAG4AIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgApACkAKQA7AFwAbgBcAG4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBDAG8AcgByAGUAYwB0AGkAbwBuAEYAYQBjAHQAbwByAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAFwAIgApACkAOwBcAG4AXABuAFwAbgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFQAYQBiAGwAZQAgAEEALgA0AC4AMQAuADQAOgAgAE0AZQB0AGgAYQBuAGUAIABjAG8AcgByAGUAYwB0AGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHQAcgBlAGEAdABtAGUAbgB0ACAAZgBhAGMAaQBsAGkAdAB5ACAAdAB5AHAAZQAgAHQAIAB1AHMAZQBkACAAdABvACAAdAByAGUAYQB0ACAAcwBsAHUAZABnAGUAIAAoAGYAcgBhAGMAdABpAG8AbgApACAAKABDAEYAcwBsAHUAZABnAGUALAB0ACkAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUAQwBvAHIAcgBlAGMAdABpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBfAFQAaQB0AGwAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAE0AZQB0AGgAYQBuAGUAIABjAG8AcgByAGUAYwB0AGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHQAcgBlAGEAdABtAGUAbgB0ACAAZgBhAGMAaQBsAGkAdAB5ACAAdAB5AHAAZQAgAHQAIAB1AHMAZQBkACAAdABvACAAdAByAGUAYQB0ACAAcwBsAHUAZABnAGUAXAAiACkAKQA7AFwAbgBcAG4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBDAG8AcgByAGUAYwB0AGkAbwBuAEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAQwBGAHMAbAB1AGQAZwBlACwAdABcACIAKQApADsAXABuAFwAbgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEMAbwByAHIAZQBjAHQAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAXwBVAG4AaQB0AFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgApACkAOwBcAG4AXABuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUAQwBvAHIAcgBlAGMAdABpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBfAFMAbwB1AHIAYwBlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADQALgAxAC4ANABcACIAKQApADsAXABuAFwAbgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEMAbwByAHIAZQBjAHQAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAXwBEAGEAdABhAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADIALABcAG4AIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIABcACIARgBhAGMAaQBsAGkAdAB5ACAAdAB5AHAAZQAgAHQAXAAiACwAIABcACIAQwBGAHMAbAB1AGQAZwBlACwAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBNAGEAbgBhAGcAZQBkACAAYQBlAHIAbwBiAGkAYwAgAHQAcgBlAGEAdABtAGUAbgB0AFwAIgAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFUAbgBtAGEAbgBhAGcAZQBkACAAYQBlAHIAbwBiAGkAYwAgAHQAcgBlAGEAdABtAGUAbgB0AFwAIgAsACAAMAAuADMAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBBAG4AYQBlAHIAbwBiAGkAYwAgAGQAaQBnAGUAcwB0AG8AcgAvAHIAZQBhAGMAdABvAHIAXAAiACwAIAAwAC4AOAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFMAaABhAGwAbABvAHcAIABhAG4AYQBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuACAAKABkIiAAMgAgAG0AKQBcACIALAAgADAALgAyADsAXABuACAAIAAgACAAIAAgACAAIABcACIARABlAGUAcAAgAGEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AIAAoAFwAdQAwADAAMwBlACAAMgBtACkAXAAiACwAIAAwAC4AOABcAG4AIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgApACkAKQA7AFwAbgBcAG4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBDAG8AcgByAGUAYwB0AGkAbwBuAEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBcACIAKQApADsAXABuAFwAbgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBUAGkAdABsAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBNAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHcAYQBzAHQAZQB3AGEAdABlAHIAXAAiACkAKQA7AFwAbgBcAG4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFYAYQByAGkAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEUARgB3AHcAXAAiACkAKQA7AFwAbgBcAG4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFUAbgBpAHQAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBrAGcAIABDAEgANAAgAC8AIABrAGcAIABDAE8ARABcACIAKQApADsAXABuAFwAbgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AUwBvAHUAcgBjAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAAxADEALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdABzAFwAIgApACkAOwBcAG4AXABuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBEAGEAdABhAFwAbgA9AEwAQQBNAEIARABBACgAIAAwAC4AMgA1ACkAOwBcAG4AXABuAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAXwBUAGkAdABsAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBNAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHMAbAB1AGQAZwBlAFwAIgApACkAOwBcAG4AXABuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIARQBGAHMAbAB1AGQAZwBlAFwAIgApACkAOwBcAG4AXABuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAF8AVQBuAGkAdABcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAGsAZwAgAEMASAA0ACAALwAgAGsAZwAgAEMATwBEAFwAIgApACkAOwBcAG4AXABuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAF8AUwBvAHUAcgBjAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAAxADEALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdABzAFwAIgApACkAOwBcAG4AXABuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAF8ARABhAHQAYQBcAG4APQBMAEEATQBCAEQAQQAoADAALgAyADUAKQA7AFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgBXAGEAcwB0AGUAXwBFAG4AZQByAGcAeQBDAG8AbgB0AGUAbgB0AEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAEIAaQBvAGcAYQBzAEYAbABhAHIAZQBkAF8AVABpAHQAbABlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIARQBuAGUAcgBnAHkAIABjAG8AbgB0AGUAbgB0ACAAZgBhAGMAdABvAHIAIABvAGYAIABzAGwAdQBkAGcAZQAgAGIAaQBvAGcAYQBzACAAZgBsAGEAcgBlAGQAXAAiACkAKQA7AFwAbgBcAG4AVwBhAHMAdABlAF8ARQBuAGUAcgBnAHkAQwBvAG4AdABlAG4AdABGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBCAGkAbwBnAGEAcwBGAGwAYQByAGUAZABfAFYAYQByAGkAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEUAQwBmAGwAYQByAGUAZABcACIAKQApADsAXABuAFwAbgBXAGEAcwB0AGUAXwBFAG4AZQByAGcAeQBDAG8AbgB0AGUAbgB0AEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAEIAaQBvAGcAYQBzAEYAbABhAHIAZQBkAF8AVQBuAGkAdABcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEcASgAgAC8AIABtADMAXAAiACkAKQA7AFwAbgBcAG4AVwBhAHMAdABlAF8ARQBuAGUAcgBnAHkAQwBvAG4AdABlAG4AdABGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBCAGkAbwBnAGEAcwBGAGwAYQByAGUAZABfAFMAbwB1AHIAYwBlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAMQAxAC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAcwBcACIAKQApADsAXABuAFwAbgBXAGEAcwB0AGUAXwBFAG4AZQByAGcAeQBDAG8AbgB0AGUAbgB0AEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAEIAaQBvAGcAYQBzAEYAbABhAHIAZQBkAF8ARABhAHQAYQBcAG4APQBMAEEATQBCAEQAQQAoADAALgAwADMANwA3ACkAOwBcAG4AXABuAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAQgBpAG8AZwBhAHMARgBsAGEAcgBlAGQAXwBUAGkAdABsAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBNAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHMAbAB1AGQAZwBlACAAYgBpAG8AZwBhAHMAIABmAGwAYQByAGUAZABcACIAKQApADsAXABuAFwAbgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBCAGkAbwBnAGEAcwBGAGwAYQByAGUAZABfAFYAYQByAGkAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEUARgBmAGwAYQByAGUAZAAsAEMASAA0AFwAIgApACkAOwBcAG4AXABuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAEIAaQBvAGcAYQBzAEYAbABhAHIAZQBkAF8AVQBuAGkAdABcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAGsAZwAgAEMASAA0ACAALwAgAEcASgBcACIAKQApADsAXABuAFwAbgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBCAGkAbwBnAGEAcwBGAGwAYQByAGUAZABfAFMAbwB1AHIAYwBlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAMQAxAC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAcwBcACIAKQApADsAXABuAFwAbgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBCAGkAbwBnAGEAcwBGAGwAYQByAGUAZABfAEQAYQB0AGEAXABuAD0ATABBAE0AQgBEAEEAKAAwAC4AMgAyADgAOQApADsAXABuAFwAbgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAFcAYQBzAHQAZQBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBCAGkAbwBnAGEAcwBGAGwAYQByAGUAZABfAFQAaQB0AGwAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAcwBsAHUAZABnAGUAIABiAGkAbwBnAGEAcwAgAGYAbABhAHIAZQBkAFwAIgApACkAOwBcAG4AXABuAFcAYQBzAHQAZQBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBCAGkAbwBnAGEAcwBGAGwAYQByAGUAZABfAFYAYQByAGkAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEUARgBmAGwAYQByAGUAZAAsAE4AMgBPAFwAIgApACkAOwBcAG4AXABuAFcAYQBzAHQAZQBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBCAGkAbwBnAGEAcwBGAGwAYQByAGUAZABfAFUAbgBpAHQAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBrAGcAIABOADIATwAgAC8AIABHAEoAXAAiACkAKQA7AFwAbgBcAG4AVwBhAHMAdABlAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAEIAaQBvAGcAYQBzAEYAbABhAHIAZQBkAF8AUwBvAHUAcgBjAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAAxADEALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdABzAFwAIgApACkAOwBcAG4AXABuAFcAYQBzAHQAZQBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBCAGkAbwBnAGEAcwBGAGwAYQByAGUAZABfAEQAYQB0AGEAXABuAD0ATABBAE0AQgBEAEEAKAAxAC4AMQAzADIAZQAtADQAKQA7AFwAbgAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBOADIATwBfAEUAcQB1AGEAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAxADEALgAxADoAIABXAGEAcwB0AGUAdwBhAHQAZQByAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAxADEALgAxAC4AMwAuADEAIABNAGUAdABoAG8AZAAgADEAIAAtACAATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAG8AbgBzAGkAdABlACAAVwBhAHMAdABlAHcAYQB0AGUAcgAgAE0AYQBuAGEAZwBlAG0AZQBuAHQAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwAxADEAXwAxAF8AMwBfADEAXwBfADEAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEYAbABhAHIAZQBkAEIAaQBvAGcAYQBzAFwAbgBOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAZgBsAGEAcgBlAGQAIABiAGkAbwBnAGEAcwBcAG4ARQBfAE4AMgBPAFwAbgB0ACAATgAyAE8AXABuAEUAXwB7AE4AMgBPAH0APQBcAFwAZgByAGEAYwB7AFEAXwB7AGYAbABhAHIAZQBkAH0AfQB7ADEAMAAwADAAfQBcAFwAdABpAG0AZQBzACAARQBGAF8AewBmAGwAYQByAGUAZAAsAE4AMgBPAH0AXABuAFEAXwBmAGwAYQByAGUAZAAgAD0AIAB2AG8AbAB1AG0AZQAgAG8AZgAgAGIAaQBvAGcAYQBzACAAZgBsAGEAcgBlAGQAIAAoAG0AMwAgAG8AcgAgAEcASgApAFwAbgBFAEYAXwBmAGwAYQByAGUAZABfAE4AMgBPACAAPQAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAZgBsAGEAcgBlAGQAIABiAGkAbwBnAGEAcwAgACgAawBnACAATgAyAE8ALwBHAEoAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwAxADEAXwAxAF8AMwBfADEAXwBfADEAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEYAbABhAHIAZQBkAEIAaQBvAGcAYQBzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFEAXwBmAGwAYQByAGUAZAAsACAARQBDAF8AZgBsAGEAcgBlAGQALAAgAEUARgBfAGYAbABhAHIAZQBkAE4AMgBPACwAXABuACAAIAAgACAAKABRAF8AZgBsAGEAcgBlAGQAIAAvACAAMQAwADAAMAApACAAKgAgACgARQBDAF8AZgBsAGEAcgBlAGQAIAAqACAARQBGAF8AZgBsAGEAcgBlAGQATgAyAE8AKQBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEAMQBfADEAXwAzAF8AMQBfAF8AMQBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ARgBsAGEAcgBlAGQAQgBpAG8AZwBhAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABmAGwAYQByAGUAZAAgAGIAaQBvAGcAYQBzAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADEAXwAxAF8AMwBfADEAXwBfADEAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEYAbABhAHIAZQBkAEIAaQBvAGcAYQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAF8ATgAyAE8AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEAMQBfADEAXwAzAF8AMQBfAF8AMQBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ARgBsAGEAcgBlAGQAQgBpAG8AZwBhAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgB0ACAATgAyAE8AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEAMQBfADEAXwAzAF8AMQBfAF8AMQBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ARgBsAGEAcgBlAGQAQgBpAG8AZwBhAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAMQAxAC4AMQAuADMALgAxACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADEAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQAxAF8AMQBfADMAXwAxAF8AXwAxAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBGAGwAYQByAGUAZABCAGkAbwBnAGEAcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQAxAF8AMQBfADMAXwAxAF8AXwAxAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBGAGwAYQByAGUAZABCAGkAbwBnAGEAcwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwB7AE4AMgBPAH0APQBcAFwAZgByAGEAYwB7AFEAXwB7AGYAbABhAHIAZQBkAH0AfQB7ADEAMAAwADAAfQBcAFwAdABpAG0AZQBzACAAXABcAGwAZQBmAHQAWwBFAEMAXwB7AGYAbABhAHIAZQBkAH0AIABcAFwAdABpAG0AZQBzACAARQBGAF8AewBmAGwAYQByAGUAZAAsAE4AMgBPAH0AXABcAHIAaQBnAGgAdABdAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADEAXwAxAF8AMwBfADEAXwBfADEAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEYAbABhAHIAZQBkAEIAaQBvAGcAYQBzAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAA0ACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEAXwBmAGwAYQByAGUAZABcACIALAAgAFwAIgB2AG8AbAB1AG0AZQAgAG8AZgAgAGIAaQBvAGcAYQBzACAAZgBsAGEAcgBlAGQAXAAiACwAIABcACIAbQAzAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBDAF8AZgBsAGEAcgBlAGQAXAAiACwAIABcACIAZQBuAGUAcgBnAHkAIABjAG8AbgB0AGUAbgB0ACAAZgBhAGMAdABvAHIAIABvAGYAIABzAGwAdQBkAGcAZQAgAGIAaQBvAGcAYQBzACAAZgBsAGEAcgBlAGQAXAAiACwAIABcACIARwBKAC8AbQAzAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAF8AZgBsAGEAcgBlAGQATgAyAE8AXAAiACwAIABcACIAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABmAGwAYQByAGUAZAAgAGIAaQBvAGcAYQBzAFwAIgAsACAAXAAiAGsAZwAgAE4AMgBPAC8ARwBKAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AIgB9AF0ALAAiAHAAcgBvAGoAZQBjAHQATgBhAG0AZQBzACIAOgBbACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEEAcABwAGUAbgBkAGkAYwBlAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAUgBvAHcAUwB0AGEAcgB0AE4AdQBtAGIAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAHIAYQB5AEkAbgBUAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUAVAB3AG8AQwBvAGwAdQBtAG4AcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBPAG4AZQBDAG8AbAB1AG0AbgBBAG4AZABIAGUAYQBkAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBTAHAAbABpAHQAUwB0AHIAaQBuAGcASQBuAHQAbwBBAHIAcgBhAHkAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQwBsAGkAbQBhAHQAZQBaAG8AbgBlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAEkAdABlAG0ARgByAG8AbQBNAGkAbgBNAGEAeAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBTAHUAbQBRAHUAYQBuAHQAaQB0AHkARgByAG8AbQBDAHIAaQB0AGUAcgBpAGEAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAUABlAHIAaQBvAGQAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEYAdQBuAGMAdABpAG8AbgBOAGEAbQBlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAE4AMgBPAEUARgBGAHIAbwBtAFAAcgBvAGQASQByAHIAaQBnAGEAdABpAG8AbgBSAGEAaQBuAGYAYQBsAGwAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBHAGUAdABGAHIAYQBjAFcARQBUACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEMAbwBuAHYAZQByAHQAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAVABvAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADEAXwAxAF8AMQBfADEAXwBfADEAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AVwBhAHMAdABlAHcAYQB0AGUAcgBUAHIAZQBhAHQAbQBlAG4AdAAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQAxAF8AMQBfADEAXwAxAF8AXwAxAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFcAYQBzAHQAZQB3AGEAdABlAHIAVAByAGUAYQB0AG0AZQBuAHQAXwBUAGkAdABsAGUAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEAMQBfADEAXwAxAF8AMQBfAF8AMQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBXAGEAcwB0AGUAdwBhAHQAZQByAFQAcgBlAGEAdABtAGUAbgB0AF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADEAXwAxAF8AMQBfADEAXwBfADEAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AVwBhAHMAdABlAHcAYQB0AGUAcgBUAHIAZQBhAHQAbQBlAG4AdABfAFUAbgBpAHQAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEAMQBfADEAXwAxAF8AMQBfAF8AMQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBXAGEAcwB0AGUAdwBhAHQAZQByAFQAcgBlAGEAdABtAGUAbgB0AF8AUwBvAHUAcgBjAGUAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEAMQBfADEAXwAxAF8AMQBfAF8AMQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBXAGEAcwB0AGUAdwBhAHQAZQByAFQAcgBlAGEAdABtAGUAbgB0AF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEAMQBfADEAXwAxAF8AMQBfAF8AMQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBXAGEAcwB0AGUAdwBhAHQAZQByAFQAcgBlAGEAdABtAGUAbgB0AF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQAxAF8AMQBfADEAXwAxAF8AXwAxAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFcAYQBzAHQAZQB3AGEAdABlAHIAVAByAGUAYQB0AG0AZQBuAHQAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQAxAF8AMQBfADEAXwAxAF8AXwAxAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFcAYQBzAHQAZQB3AGEAdABlAHIAVAByAGUAYQB0AG0AZQBuAHQAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUAQwBvAHIAcgBlAGMAdABpAG8AbgBGAGEAYwB0AG8AcgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AVABpAHQAbABlACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBDAG8AcgByAGUAYwB0AGkAbwBuAEYAYQBjAHQAbwByAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEMAbwByAHIAZQBjAHQAaQBvAG4ARgBhAGMAdABvAHIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFUAbgBpAHQAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEMAbwByAHIAZQBjAHQAaQBvAG4ARgBhAGMAdABvAHIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBDAG8AcgByAGUAYwB0AGkAbwBuAEYAYQBjAHQAbwByAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBEAGEAdABhACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBDAG8AcgByAGUAYwB0AGkAbwBuAEYAYQBjAHQAbwByAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUAQwBvAHIAcgBlAGMAdABpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBfAFQAaQB0AGwAZQAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUAQwBvAHIAcgBlAGMAdABpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUAQwBvAHIAcgBlAGMAdABpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBfAFUAbgBpAHQAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEMAbwByAHIAZQBjAHQAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAXwBTAG8AdQByAGMAZQAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUAQwBvAHIAcgBlAGMAdABpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBfAEQAYQB0AGEAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEMAbwByAHIAZQBjAHQAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBUAGkAdABsAGUAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFUAbgBpAHQAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AUwBvAHUAcgBjAGUAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBXAGEAcwB0AGUAdwBhAHQAZQByAF8ARABhAHQAYQAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAF8AVABpAHQAbABlACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBfAFUAbgBpAHQAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBfAFMAbwB1AHIAYwBlACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAXwBEAGEAdABhACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AVwBhAHMAdABlAF8ARQBuAGUAcgBnAHkAQwBvAG4AdABlAG4AdABGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBCAGkAbwBnAGEAcwBGAGwAYQByAGUAZABfAFQAaQB0AGwAZQAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFcAYQBzAHQAZQBfAEUAbgBlAHIAZwB5AEMAbwBuAHQAZQBuAHQARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAQgBpAG8AZwBhAHMARgBsAGEAcgBlAGQAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBXAGEAcwB0AGUAXwBFAG4AZQByAGcAeQBDAG8AbgB0AGUAbgB0AEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAEIAaQBvAGcAYQBzAEYAbABhAHIAZQBkAF8AVQBuAGkAdAAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFcAYQBzAHQAZQBfAEUAbgBlAHIAZwB5AEMAbwBuAHQAZQBuAHQARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAQgBpAG8AZwBhAHMARgBsAGEAcgBlAGQAXwBTAG8AdQByAGMAZQAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFcAYQBzAHQAZQBfAEUAbgBlAHIAZwB5AEMAbwBuAHQAZQBuAHQARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAQgBpAG8AZwBhAHMARgBsAGEAcgBlAGQAXwBEAGEAdABhACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAQgBpAG8AZwBhAHMARgBsAGEAcgBlAGQAXwBUAGkAdABsAGUAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBCAGkAbwBnAGEAcwBGAGwAYQByAGUAZABfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAEIAaQBvAGcAYQBzAEYAbABhAHIAZQBkAF8AVQBuAGkAdAAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAEIAaQBvAGcAYQBzAEYAbABhAHIAZQBkAF8AUwBvAHUAcgBjAGUAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBCAGkAbwBnAGEAcwBGAGwAYQByAGUAZABfAEQAYQB0AGEAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBXAGEAcwB0AGUAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAQgBpAG8AZwBhAHMARgBsAGEAcgBlAGQAXwBUAGkAdABsAGUAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBXAGEAcwB0AGUAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAQgBpAG8AZwBhAHMARgBsAGEAcgBlAGQAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBXAGEAcwB0AGUAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAQgBpAG8AZwBhAHMARgBsAGEAcgBlAGQAXwBVAG4AaQB0ACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AVwBhAHMAdABlAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAEIAaQBvAGcAYQBzAEYAbABhAHIAZQBkAF8AUwBvAHUAcgBjAGUAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBXAGEAcwB0AGUAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAQgBpAG8AZwBhAHMARgBsAGEAcgBlAGQAXwBEAGEAdABhACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBOADIATwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQAxAF8AMQBfADMAXwAxAF8AXwAxAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBGAGwAYQByAGUAZABCAGkAbwBnAGEAcwAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8ATgAyAE8AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEAMQBfADEAXwAzAF8AMQBfAF8AMQBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ARgBsAGEAcgBlAGQAQgBpAG8AZwBhAHMAXwBUAGkAdABsAGUAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAE4AMgBPAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADEAXwAxAF8AMwBfADEAXwBfADEAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEYAbABhAHIAZQBkAEIAaQBvAGcAYQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBOADIATwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQAxAF8AMQBfADMAXwAxAF8AXwAxAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBGAGwAYQByAGUAZABCAGkAbwBnAGEAcwBfAFUAbgBpAHQAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAE4AMgBPAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADEAXwAxAF8AMwBfADEAXwBfADEAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEYAbABhAHIAZQBkAEIAaQBvAGcAYQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAE4AMgBPAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADEAXwAxAF8AMwBfADEAXwBfADEAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEYAbABhAHIAZQBkAEIAaQBvAGcAYQBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAE4AMgBPAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADEAXwAxAF8AMwBfADEAXwBfADEAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEYAbABhAHIAZQBkAEIAaQBvAGcAYQBzAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8ATgAyAE8AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEAMQBfADEAXwAzAF8AMQBfAF8AMQBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ARgBsAGEAcgBlAGQAQgBpAG8AZwBhAHMAXwBBAHIAZwB1AG0AZQBuAHQAcwAiAF0ALAAiAGwAbwBjAGEAbABlACIAOgB7ACIAbABpAHMAdABTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAsACIALAAiAHIAbwB3AFMAZQBwAGEAcgBhAHQAbwByACIAOgAiADsAIgAsACIAYwBvAGwAdQBtAG4AUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgB0AGgAbwB1AHMAYQBuAGQAcwBTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAsACIALAAiAHQAaABvAHUAcwBhAG4AZABzAFAAbwBzAGkAdABpAG8AbgBzACIAOgBbADMAXQAsACIAZABlAGMAaQBtAGEAbABTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAuACIALAAiAGQAYQB0AGUATwByAGQAZQByACIAOgAiAEQATQBZACIALAAiAGMAdQByAHIAZQBuAGMAeQBTAHkAbQBiAG8AbAAiADoAIgAkACIALAAiAGkAcwBDAHUAcgByAGUAbgBjAHkAUwB5AG0AYgBvAGwATABlAGEAZAAiADoAdAByAHUAZQAsACIAaQBzAEMAdQByAHIAZQBuAGMAeQBTAGUAcABCAHkAUwBwAGEAYwBlACIAOgBmAGEAbABzAGUALAAiAHIAbwB3AEwAZQB0AHQAZQByACIAOgAiAFIAIgAsACIAYwBvAGwAdQBtAG4ATABlAHQAdABlAHIAIgA6ACIAQwAiACwAIgByAGMATABlAGYAdABCAHIAYQBjAGsAZQB0ACIAOgAiAFsAIgAsACIAcgBjAFIAaQBnAGgAdABCAHIAYQBjAGsAZQB0ACIAOgAiAF0AIgAsACIAcwB0AGEAdABlAG0AZQBuAHQAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIAOwAiACwAIgBsAG8AYwBhAGwAZQBOAGEAbQBlACIAOgAiAGUAbgAtAHUAcwAiAH0AfQA=</AFEJSONBlob>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{809E3D44-A88D-4EBF-A307-6B8CE77A3361}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -14173,15 +14148,15 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6BE249C-20B1-4A62-BBCD-F2A46D88BCAB}">
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9A9CF321-0D35-4044-BC72-33748FE2B865}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD460F9D-420A-4723-B323-396E4D19EC9B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -14190,4 +14165,12 @@
     <ds:schemaRef ds:uri="7291119c-fce9-4911-96ae-b800be5dccd8"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6BE249C-20B1-4A62-BBCD-F2A46D88BCAB}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/Excel/11_Wastewater_WIP_v02.xlsx
+++ b/Excel/11_Wastewater_WIP_v02.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\htdocs\zneagcrc\GAF-VEERG-Functions\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{045CF380-4903-4990-B5DA-D003B56E87C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D5F8B7C-7D3F-4184-A05D-AC8131EBEEBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1350" yWindow="990" windowWidth="36255" windowHeight="19140" firstSheet="7" activeTab="7" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
+    <workbookView xWindow="1950" yWindow="1950" windowWidth="28800" windowHeight="15345" firstSheet="7" activeTab="7" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
   </bookViews>
   <sheets>
     <sheet name="Home" sheetId="71" r:id="rId1"/>
@@ -20,7 +20,7 @@
     <sheet name="11.1.1-2 Wastewater CH4" sheetId="69" r:id="rId5"/>
     <sheet name="11.1.3-4 Wastewater N2O" sheetId="120" r:id="rId6"/>
     <sheet name="Constants - Wastewater" sheetId="110" r:id="rId7"/>
-    <sheet name="Constants - Common" sheetId="127" r:id="rId8"/>
+    <sheet name="Constants - Common" sheetId="128" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="Common_Equations.Common_ConvertCH4ToCO2e">_xlfn.LAMBDA(_xlpm.E_CH4,_xlpm.GWP_CH4, _xlpm.E_CH4 * _xlpm.GWP_CH4)</definedName>
@@ -125,7 +125,13 @@
     <definedName name="Common_SourceData.Common_SourceData_EFleach_Title">_xlfn.LAMBDA("Emission factor for nitrogen leaching and runoff")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_EFleach_Unit">_xlfn.LAMBDA("(kg N2O-N / kg N")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_EFleach_Variation">_xlfn.LAMBDA((""))</definedName>
-    <definedName name="Common_SourceData.Common_SourceData_EFN2O_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(15, 5, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Production system j","EFN2O","Production system only","Irrigation method","Rainfall zone";"Irrigated pasture",0.0059,"Pasture","Any","Any";"Irrigated crop",0.007,"Crop","Any","Any";"Non-irrigated pasture",0.0018,"Pasture","Not irrigated","Low rainfall";"Non-irrigated pasture",0.0018,"Pasture","Not irrigated","High rainfall";"Non-irrigated crop (low rainfall)",0.0029,"Crop","Not irrigated","Low rainfall";"Non-irrigated crop (high rainfall)",0.008,"Crop","Not irrigated","High rainfall";"Sugar",0.0199,"Sugar","Any","Any";"Cotton",0.0053,"Cotton","Any","Any";"Horticultural crops",0.0064,"Horticultural crops","Any","Any";"Rice (continuous flooding)",0.003,"Rice","Continuous flooding","Any";"Rice (single and multiple drainage, or alternate wetting and drying)",0.005,"Rice","Single and multiple drainage, or alternate wetting and drying","Any";"Aquaculture",0.0026,"Aquaculture","Any","Any";"Forestry",0.0018,"Forestry","Any","Any"}, _xlpm.r, _xlpm.c))))</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_EFN2O_Data">_xlfn.LAMBDA(
+    _xlfn.MAKEARRAY(14, 5,
+      _xlfn.LAMBDA(_xlpm.r,_xlpm.c,
+        INDEX({"Production system j","EFN2O","Production system only","Irrigation method","Rainfall zone";"Irrigated pasture",0.0059,"Pasture","Any","Any";"Irrigated crop",0.007,"Crop","Any","Any";"Non-irrigated pasture",0.0018,"Pasture","Not irrigated","Low rainfall";"Non-irrigated pasture",0.0018,"Pasture","Not irrigated","High rainfall";"Non-irrigated crop (low rainfall)",0.0029,"Crop","Not irrigated","Low rainfall";"Non-irrigated crop (high rainfall)",0.008,"Crop","Not irrigated","High rainfall";"Sugar",0.0199,"Sugar","Any","Any";"Cotton",0.0053,"Cotton","Any","Any";"Horticultural crops",0.0064,"Horticultural crops","Any","Any";"Rice (continuous flooding)",0.003,"Rice","Continuous flooding","Any";"Rice (single and multiple drainage, or alternate wetting and drying)",0.005,"Rice","Single and multiple drainage, or alternate wetting and drying","Any";"Aquaculture",0.0026,"Aquaculture","Any","Any";"Forestry",0.0018,"Forestry","Any","Any"}, _xlpm.r, _xlpm.c)
+      )
+    )
+  )</definedName>
     <definedName name="Common_SourceData.Common_SourceData_EFN2O_NIRReference">_xlfn.LAMBDA("")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_EFN2O_Source">_xlfn.LAMBDA("VEERG 2026: Table A.2.2.1")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_EFN2O_Title">_xlfn.LAMBDA("Nitrous oxide emission factors for inorganic fertiliser application")</definedName>
@@ -167,13 +173,25 @@
     <definedName name="Common_SourceData.Common_SourceData_GWP_Title">_xlfn.LAMBDA("Global warming potential for greenhouse gases")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_GWP_Unit">_xlfn.LAMBDA("factor")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_GWP_Variable">_xlfn.LAMBDA("GWPN2O")</definedName>
-    <definedName name="Common_SourceData.Common_SourceData_LeachingZones_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(4, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Leaching Zone","Leaching criteria";"Leaching occurs","Σ(𝑟𝑎𝑖𝑛)&gt;Σ(𝐸𝑇0)+𝑠𝑜𝑖𝑙 𝑤𝑎𝑡𝑒𝑟 ℎ𝑜𝑙𝑑𝑖𝑛𝑔 𝑐𝑎𝑝𝑎𝑐𝑖𝑡𝑦";"Leaching does not occur","Σ(𝑟𝑎𝑖𝑛)≤Σ(𝐸𝑇0)+𝑠𝑜𝑖𝑙 𝑤𝑎𝑡𝑒𝑟 ℎ𝑜𝑙𝑑𝑖𝑛𝑔 𝑐𝑎𝑝𝑎𝑐𝑖𝑡𝑦"}, _xlpm.r, _xlpm.c))))</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_LeachingZones_Data">_xlfn.LAMBDA(
+    _xlfn.MAKEARRAY(3, 2,
+      _xlfn.LAMBDA(_xlpm.r,_xlpm.c,
+        INDEX({"Leaching Zone","Leaching criteria";"Leaching occurs","Σ(𝑟𝑎𝑖𝑛)&gt;Σ(𝐸𝑇0)+𝑠𝑜𝑖𝑙 𝑤𝑎𝑡𝑒𝑟 ℎ𝑜𝑙𝑑𝑖𝑛𝑔 𝑐𝑎𝑝𝑎𝑐𝑖𝑡𝑦";"Leaching does not occur","Σ(𝑟𝑎𝑖𝑛)≤Σ(𝐸𝑇0)+𝑠𝑜𝑖𝑙 𝑤𝑎𝑡𝑒𝑟 ℎ𝑜𝑙𝑑𝑖𝑛𝑔 𝑐𝑎𝑝𝑎𝑐𝑖𝑡𝑦"}, _xlpm.r, _xlpm.c)
+      )
+    )
+  )</definedName>
     <definedName name="Common_SourceData.Common_SourceData_LeachingZones_Source">_xlfn.LAMBDA("VEERG 2026: Table 1.3: Climate and Rainfall zone classifications and definitions")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_LeachingZones_Title">_xlfn.LAMBDA("VEERG Australian leaching zones")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_LeachingZones_Unit">_xlfn.LAMBDA("")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_LeachingZones_Variable">_xlfn.LAMBDA("")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_LeachingZones_Variation">_xlfn.LAMBDA("")</definedName>
-    <definedName name="Common_SourceData.Common_SourceData_MCFTemperatureZone_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(22, 16, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Temperature zone","MAT (ºC)","Uncovered anerobic lagoon","Covered lagoon","Liquid Slurry (without natural crust)","Daily spread (b)","Composting (passive windrow)","Solid Storage","Pit Storage &lt;1 month","Deep Litter","Poultry Manure (with/without litter)","","Direct processing into pelletized fertiliser","Direct application to soil","Pasture, Range and Paddock (c)(d)","MAT raw";"Cool","≤10",0.66,0.1,0.1,0.001,0.005,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,10;"Cool",11,0.68,0.1,0.11,0.001,0.005,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,11;"Cool",12,0.7,0.1,0.13,0.001,0.005,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,12;"Cool",13,0.71,0.1,0.14,0.001,0.005,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,13;"Cool",14,0.73,0.1,0.15,0.001,0.005,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,14;"Temperate",15,0.74,0.1,0.17,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,15;"Temperate",16,0.75,0.1,0.18,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,16;"Temperate",17,0.76,0.1,0.2,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,17;"Temperate",18,0.77,0.1,0.22,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,18;"Temperate",19,0.77,0.1,0.24,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,19;"Temperate",20,0.78,0.1,0.26,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,20;"Temperate",21,0.78,0.1,0.29,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,21;"Temperate",22,0.78,0.1,0.31,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,22;"Temperate",23,0.79,0.1,0.34,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,23;"Temperate",24,0.79,0.1,0.37,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,24;"Temperate",25,0.79,0.1,0.41,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,25;"Warm",26,0.79,0.1,0.44,0.01,0.015,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,26;"Warm",27,0.8,0.1,0.48,0.01,0.015,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,27;"Warm","≥28",0.8,0.1,0.5,0.01,0.015,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,28;"","","Anaerobic lagoon","Digester / covered lagoons","Liquid systems","Daily spread","Composting (passive windrow)","Solid storage","Pit storage","Deep litter","Poultry manure with bedding","Poultry manure without bedding","Direct processing","Direct application","Pasture range and paddock","MAT raw"}, _xlpm.r, _xlpm.c))))</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_MCFTemperatureZone_Data">_xlfn.LAMBDA(
+    _xlfn.MAKEARRAY(21, 16,
+      _xlfn.LAMBDA(_xlpm.r,_xlpm.c,
+        INDEX({"Temperature zone","MAT (ºC)","Uncovered anerobic lagoon","Covered lagoon","Liquid Slurry (without natural crust)","Daily spread (b)","Composting (passive windrow)","Solid Storage","Pit Storage &lt;1 month","Deep Litter","Poultry Manure (with/without litter)","","Direct processing into pelletized fertiliser","Direct application to soil","Pasture, Range and Paddock (c)(d)","MAT raw";"Cool","≤10",0.66,0.1,0.1,0.001,0.005,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,10;"Cool",11,0.68,0.1,0.11,0.001,0.005,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,11;"Cool",12,0.7,0.1,0.13,0.001,0.005,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,12;"Cool",13,0.71,0.1,0.14,0.001,0.005,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,13;"Cool",14,0.73,0.1,0.15,0.001,0.005,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,14;"Temperate",15,0.74,0.1,0.17,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,15;"Temperate",16,0.75,0.1,0.18,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,16;"Temperate",17,0.76,0.1,0.2,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,17;"Temperate",18,0.77,0.1,0.22,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,18;"Temperate",19,0.77,0.1,0.24,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,19;"Temperate",20,0.78,0.1,0.26,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,20;"Temperate",21,0.78,0.1,0.29,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,21;"Temperate",22,0.78,0.1,0.31,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,22;"Temperate",23,0.79,0.1,0.34,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,23;"Temperate",24,0.79,0.1,0.37,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,24;"Temperate",25,0.79,0.1,0.41,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,25;"Warm",26,0.79,0.1,0.44,0.01,0.015,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,26;"Warm",27,0.8,0.1,0.48,0.01,0.015,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,27;"Warm","≥28",0.8,0.1,0.5,0.01,0.015,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,28;"","","Anaerobic lagoon","Digester / covered lagoons","Liquid systems","Daily spread","Composting (passive windrow)","Solid storage","Pit storage","Deep litter","Poultry manure with bedding","Poultry manure without bedding","Direct processing","Direct application","Pasture range and paddock","MAT raw"}, _xlpm.r, _xlpm.c)
+      )
+    )
+  )</definedName>
     <definedName name="Common_SourceData.Common_SourceData_MCFTemperatureZone_Source">_xlfn.LAMBDA("VEERG 2026: Table A.1.8.1")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_MCFTemperatureZone_Title">_xlfn.LAMBDA("Manure Management – Methane conversion factor per temperature zone (fraction) (MCFim)")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_MCFTemperatureZone_Unit">_xlfn.LAMBDA("fraction")</definedName>
@@ -240,9 +258,15 @@
     <definedName name="CommonLivestock_InputFunctions.LivestockMovement_TotalLiveweightGrownDuringMonth">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass, IFERROR(SUM(_xlfn._xlws.FILTER(#REF!, (#REF! &gt;= EOMONTH(_xlpm.Month, -1) + 1) * (#REF! &lt;= EOMONTH(_xlpm.Month, 0)) * (#REF! = _xlpm.LivestockClass))), 0))</definedName>
     <definedName name="CommonLivestock_InputFunctions.LivestockMovement_TotalLiveweightGrownDuringMonthAddedAndRemaining">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass,_xlpm.HeadAtStart, [0]!CommonLivestock_InputFunctions.LivestockMovement_LiveweightGrownFromMonthStartTotal(_xlpm.LivestockClass, _xlpm.Month, _xlpm.HeadAtStart) + [0]!CommonLivestock_InputFunctions.LivestockMovement_TotalLiveweightGrownDuringMonth(_xlpm.Month, _xlpm.LivestockClass))</definedName>
     <definedName name="CommonLivestock_SourceData.SourceData_Livestock_Common_SymbolsMMS_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(19, 3, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Symbol","Manure management system","";"1","Anaerobic lagoon","Anaerobic lagoon (m=1)";"2","Liquid systems","Liquid systems (m=2)";"3","Daily spread","Daily spread (m=3)";"3a","Sump and dispersal system","Sump and dispersal system (m=3a)";"3b","Drains to paddock","Drains to paddock (m=3b)";"4","Solid storage","Solid storage (m=4)";"5","Drylot (feed pad)","Drylot (feed pad) (m=5)";"6","Composting (passive windrow)","Composting (passive windrow) (m=6)";"7","Digester / covered lagoons","Digester / covered lagoons (m=7)";"8","Deep litter","Deep litter (m=8)";"9","Pit storage","Pit storage (m=9)";"10","Poultry manure with bedding","Poultry manure with bedding (m=10)";"11","Poultry manure without bedding","Poultry manure without bedding (m=11)";"11a","Belt manure removal","Belt manure removal (m=11a)";"11b","Manure stored in house","Manure stored in house (m=11b)";"12","Direct processing","Direct processing (m=12)";"13","Direct application","Direct application (m=13)";"14","Pasture range and paddock","Pasture range and paddock (m=14)"}, _xlpm.r, _xlpm.c))))</definedName>
+    <definedName name="Enterprise_PastureBeef_InputFunctions.multiplyCorrespondingCells">_xlfn.LAMBDA(_xlpm.range1,_xlpm.range2,_xlpm.range3, _xlfn.LET(_xlpm.numRows, ROWS(_xlpm.range1), _xlpm.numCols, COLUMNS(_xlpm.range1), _xlpm.result, _xlfn.MAKEARRAY(_xlpm.numRows, _xlpm.numCols, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, IF(ISNUMBER(INDEX(_xlpm.range1, _xlpm.r, _xlpm.c)), INDEX(_xlpm.range1, _xlpm.r, _xlpm.c), 0) * IF(ISNUMBER(INDEX(_xlpm.range2, _xlpm.r, _xlpm.c)), INDEX(_xlpm.range2, _xlpm.r, _xlpm.c), 0) * IF(ISNUMBER(INDEX(_xlpm.range3, _xlpm.r, _xlpm.c)), INDEX(_xlpm.range3, _xlpm.r, _xlpm.c), 0))), _xlpm.result))</definedName>
     <definedName name="Fertiliser_Equations_Lime.VEERG_5_3_1_1__1_LimeApplication">_xlfn.LAMBDA(_xlpm.Mlime,_xlpm.FracLime,_xlpm.Plime,_xlpm.EFlime,_xlpm.FracDol,_xlpm.Pdol,_xlpm.EFdol,_xlpm.CgCO2, ((_xlpm.Mlime * _xlpm.FracLime * _xlpm.Plime * _xlpm.EFlime) + (_xlpm.Mlime * _xlpm.FracDol * _xlpm.Pdol * _xlpm.EFdol)) * _xlpm.CgCO2 * 10 ^ -3)</definedName>
     <definedName name="Fertiliser_Equations_Organic.VEERG_5_2_1_1__2_MassOfNitrogenInOrganicFertiliser">_xlfn.LAMBDA(_xlpm.Morganicjf,_xlpm.FNorganicf, _xlpm.Morganicjf * _xlpm.FNorganicf)</definedName>
     <definedName name="getOverlappingReportingCycles">_xlfn.LAMBDA(_xlpm.ProductionCycleStart,_xlpm.ProductionCycleEnd,_xlpm.ReportingStartMonth,_xlpm.ReportingStartDay, _xlfn.LET(_xlpm.S, _xlpm.ProductionCycleStart, _xlpm.E, _xlpm.ProductionCycleEnd, _xlpm.m, _xlpm.ReportingStartMonth, _xlpm.d, _xlpm.ReportingStartDay, _xlpm.A, _xlpm.S - 364, _xlpm.ya, YEAR(_xlpm.A), _xlpm.yb, YEAR(_xlpm.E), _xlpm.firstYear, _xlpm.ya + (DATE(_xlpm.ya, _xlpm.m, _xlpm.d) &lt; _xlpm.A), _xlpm.lastYear, _xlpm.yb - (DATE(_xlpm.yb, _xlpm.m, _xlpm.d) &gt; _xlpm.E), MAX(0, _xlpm.lastYear - _xlpm.firstYear + 1)))</definedName>
+    <definedName name="InputFunctions_PastureBeef.ConvertMonthlyCalvingToSeason">_xlfn.LAMBDA(_xlpm.Season,_xlpm.SumArray,_xlpm.CalvingMonthArray,_xlpm.MonthArray,_xlpm.MonthToSeasonArray, _xlfn.LET(_xlpm.MonthText, TEXT(_xlpm.CalvingMonthArray, "mmmm"), _xlpm.SeasonPerRow, _xlfn.XLOOKUP(_xlpm.MonthText, _xlpm.MonthArray, _xlpm.MonthToSeasonArray, "", 0), SUM(_xlpm.SumArray * (_xlpm.SeasonPerRow = _xlpm.Season))))</definedName>
+    <definedName name="InputFunctions_PastureBeef.LookupLiveweightFromMonth">_xlfn.LAMBDA(_xlpm.State,_xlpm.Region,_xlpm.Month,_xlpm.LivestockClass,_xlpm.StateArray,_xlpm.RegionArray,_xlpm.SeasonArray,_xlpm.LivestockClassArray,_xlpm.ReturnArray,_xlpm.StateCommonNameArray,_xlpm.StateAbbreviationArray,_xlpm.MonthArray,_xlpm.MonthToSeasonArray, _xlfn.LET(_xlpm.Month, TEXT(_xlpm.Month, "mmmm"), _xlpm.State, _xlfn.XLOOKUP(_xlpm.State, _xlpm.StateCommonNameArray, _xlpm.StateAbbreviationArray), _xlpm.Season, _xlfn.XLOOKUP(_xlpm.Month, _xlpm.MonthArray, _xlpm.MonthToSeasonArray), _xlfn.XLOOKUP(1, (_xlpm.StateArray = _xlpm.State) * (_xlpm.RegionArray = _xlpm.Region) * (_xlpm.SeasonArray = _xlpm.Season), _xlfn.XLOOKUP(_xlpm.LivestockClass, _xlpm.LivestockClassArray, _xlpm.ReturnArray))))</definedName>
+    <definedName name="InputFunctions_PastureBeef.LookupLiveweightFromSeason">_xlfn.LAMBDA(_xlpm.State,_xlpm.Region,_xlpm.Season,_xlpm.LivestockClass,_xlpm.StateArray,_xlpm.RegionArray,_xlpm.SeasonArray,_xlpm.LivestockClassArray,_xlpm.ReturnArray,_xlpm.StateCommonNameArray,_xlpm.StateAbbreviationArray, _xlfn.LET(_xlpm.State, _xlfn.XLOOKUP(_xlpm.State, _xlpm.StateCommonNameArray, _xlpm.StateAbbreviationArray), _xlfn.XLOOKUP(1, (_xlpm.StateArray = _xlpm.State) * (_xlpm.RegionArray = _xlpm.Region) * (_xlpm.SeasonArray = _xlpm.Season), _xlfn.XLOOKUP(_xlpm.LivestockClass, _xlpm.LivestockClassArray, _xlpm.ReturnArray))))</definedName>
+    <definedName name="InputFunctions_PastureBeef.LookupValueFromStateRegionMonth">_xlfn.LAMBDA(_xlpm.State,_xlpm.Region,_xlpm.Month,_xlpm.StateArray,_xlpm.RegionArray,_xlpm.SeasonArray,_xlpm.ReturnArray,_xlpm.StateCommonNameArray,_xlpm.StateAbbreviationArray,_xlpm.MonthArray,_xlpm.MonthToSeasonArray, _xlfn.LET(_xlpm.State, _xlfn.XLOOKUP(_xlpm.State, _xlpm.StateCommonNameArray, _xlpm.StateAbbreviationArray), _xlpm.Season, _xlfn.XLOOKUP(TEXT(_xlpm.Month, "mmmm"), _xlpm.MonthArray, _xlpm.MonthToSeasonArray), _xlfn.XLOOKUP(1, (_xlpm.StateArray = _xlpm.State) * (_xlpm.RegionArray = _xlpm.Region), _xlfn.XLOOKUP(_xlpm.Season, _xlpm.SeasonArray, _xlpm.ReturnArray))))</definedName>
+    <definedName name="InputFunctions_PastureBeef.LookupValueFromStateRegionSeason">_xlfn.LAMBDA(_xlpm.State,_xlpm.Region,_xlpm.Season,_xlpm.StateArray,_xlpm.RegionArray,_xlpm.SeasonArray,_xlpm.ReturnArray,_xlpm.StateCommonNameArray,_xlpm.StateAbbreviationArray, _xlfn.LET(_xlpm.State, _xlfn.XLOOKUP(_xlpm.State, _xlpm.StateCommonNameArray, _xlpm.StateAbbreviationArray), _xlfn.XLOOKUP(1, (_xlpm.StateArray = _xlpm.State) * (_xlpm.RegionArray = _xlpm.Region), _xlfn.XLOOKUP(_xlpm.Season, _xlpm.SeasonArray, _xlpm.ReturnArray))))</definedName>
     <definedName name="VEERG_11_1_1_1__1_MethaneEmissionsFromWastewaterTreatment_Result_Method1">'11.1.1-2 Wastewater CH4'!$E$30</definedName>
     <definedName name="VEERG_11_1_3_1__1_NitrousOxideEmissionsFromFlaredBiogas_Result_Method1">'11.1.3-4 Wastewater N2O'!$E$17</definedName>
     <definedName name="Waste_EnergyContentFactorSludgeBiogasFlared_Data">'Constants - Wastewater'!$E$41</definedName>
@@ -372,7 +396,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="180">
   <si>
     <t>INPUTS</t>
   </si>
@@ -816,6 +840,153 @@
   <si>
     <t>Total</t>
   </si>
+  <si>
+    <t>Home</t>
+  </si>
+  <si>
+    <t>Data quality scoring</t>
+  </si>
+  <si>
+    <t>Table_SourceData_DataQuality_TemporalRepresentativeness</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>Score</t>
+  </si>
+  <si>
+    <t>Data collected covers the time-period for which emissions are being estimated  </t>
+  </si>
+  <si>
+    <t>TR5</t>
+  </si>
+  <si>
+    <t>Data collected represents activities that occurred within 2 years of the time-period being assessed  </t>
+  </si>
+  <si>
+    <t>TR4</t>
+  </si>
+  <si>
+    <t>Data collected represents activities that occurred within 3 years of to the time-period being assessed  </t>
+  </si>
+  <si>
+    <t>TR3</t>
+  </si>
+  <si>
+    <t>Data collected represents activities that occurred within 4 years of the time-period being assessed  </t>
+  </si>
+  <si>
+    <t>TR2</t>
+  </si>
+  <si>
+    <t>Age of data unknown or data more than 4 years older than the time-period being reported  </t>
+  </si>
+  <si>
+    <t>TR1</t>
+  </si>
+  <si>
+    <t>Table_SourceData_DataQuality_SpatialRepresentativeness</t>
+  </si>
+  <si>
+    <t>Data covers specific entity location(s) with spatial partitioning or using stratified sampling within property </t>
+  </si>
+  <si>
+    <t>SR5</t>
+  </si>
+  <si>
+    <t>Data covers specific entity location(s) without spatial partitioning within property  </t>
+  </si>
+  <si>
+    <t>SR4</t>
+  </si>
+  <si>
+    <t>Data based on regional data from a government or industry database or survey </t>
+  </si>
+  <si>
+    <t>SR3</t>
+  </si>
+  <si>
+    <t>Data based on state data from a government or industry database or survey </t>
+  </si>
+  <si>
+    <t>SR2</t>
+  </si>
+  <si>
+    <t>Data based on national data from a government or industry database or survey </t>
+  </si>
+  <si>
+    <t>SR1</t>
+  </si>
+  <si>
+    <t>Table_SourceData_DataQuality_SampleSize</t>
+  </si>
+  <si>
+    <t>Data based on sample size of &gt;90% (e.g. total annual fuel purchases) </t>
+  </si>
+  <si>
+    <t>SS5</t>
+  </si>
+  <si>
+    <t>Data based on sample size of 51-90%  </t>
+  </si>
+  <si>
+    <t>SS4</t>
+  </si>
+  <si>
+    <t>Data based on sample size of 21-50%  </t>
+  </si>
+  <si>
+    <t>SS3</t>
+  </si>
+  <si>
+    <t>Data based on sample size of &lt;20% (e.g. liveweight measured for 10% of herd) </t>
+  </si>
+  <si>
+    <t>SS2</t>
+  </si>
+  <si>
+    <t>Unknown (e.g. data based on national/state/regional data source) </t>
+  </si>
+  <si>
+    <t>SS1</t>
+  </si>
+  <si>
+    <t>Table_SourceData_DataQuality_Scope3</t>
+  </si>
+  <si>
+    <t>Verified data provided by supplier consistent with ISO14067:2018 or GHG Protocol Product Lifecycle Accounting and Reporting Standard </t>
+  </si>
+  <si>
+    <t>S35</t>
+  </si>
+  <si>
+    <t>Unverified supplier data, consistent with ISO14067:2018 or GHG Protocol Product Lifecycle Accounting and Reporting Standard, or consistent with these Guidelines (where appropriate)</t>
+  </si>
+  <si>
+    <t>S34</t>
+  </si>
+  <si>
+    <t>Regionally relevant product specific value from database developed using international best practice </t>
+  </si>
+  <si>
+    <t>S33</t>
+  </si>
+  <si>
+    <t>Nationally relevant product specific value from database developed using international best practice   </t>
+  </si>
+  <si>
+    <t>S32</t>
+  </si>
+  <si>
+    <t>Geographically generic product specific value from database developed using international best practice </t>
+  </si>
+  <si>
+    <t>S31</t>
+  </si>
 </sst>
 </file>
 
@@ -830,7 +1001,7 @@
     <numFmt numFmtId="169" formatCode="0.0000"/>
     <numFmt numFmtId="170" formatCode="0.0000000000"/>
   </numFmts>
-  <fonts count="52" x14ac:knownFonts="1">
+  <fonts count="53" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1179,6 +1350,14 @@
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Times New Roman"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="16">
     <fill>
@@ -1478,7 +1657,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="67">
+  <cellStyleXfs count="68">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -1666,8 +1845,9 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="44" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="75">
+  <cellXfs count="76">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="30" fillId="4" borderId="0" xfId="8">
       <alignment horizontal="left" vertical="center"/>
@@ -1873,8 +2053,9 @@
     <xf numFmtId="0" fontId="51" fillId="9" borderId="4" xfId="34" applyFont="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="0" xfId="67"/>
   </cellXfs>
-  <cellStyles count="67">
+  <cellStyles count="68">
     <cellStyle name="Alert" xfId="59" xr:uid="{34EFE908-8095-4010-8F93-8CFE88055637}"/>
     <cellStyle name="Arguments" xfId="65" xr:uid="{E3322BF6-A528-4CDC-9946-1481D9CFA254}"/>
     <cellStyle name="Arguments hyperlink" xfId="64" xr:uid="{D7E69B6D-2E15-48E8-BF41-EE6FEA2FBEBE}"/>
@@ -1890,6 +2071,7 @@
     <cellStyle name="Equation source" xfId="6" xr:uid="{348FC12D-3392-478F-B0B3-D4FA4BBA59E4}"/>
     <cellStyle name="Equation table header" xfId="1" xr:uid="{11780056-D3CA-48D4-90AF-8DF1A50E1B13}"/>
     <cellStyle name="Euqation table row 2" xfId="13" xr:uid="{2CAEAB93-BC87-4606-B5A1-3C2F7B5C52A1}"/>
+    <cellStyle name="Hyperlink" xfId="67" builtinId="8"/>
     <cellStyle name="Information tip" xfId="39" xr:uid="{7D200D09-32E3-4546-9822-1B93AD118A74}"/>
     <cellStyle name="Information variation" xfId="54" xr:uid="{205494A3-14DD-4E6A-BDD3-5C5A864D6FA7}"/>
     <cellStyle name="Input block subheading" xfId="30" xr:uid="{A9FEBDB0-0992-4E30-96E5-9F9CAE92E3FB}"/>
@@ -1943,7 +2125,7 @@
     <cellStyle name="Variable type input" xfId="62" xr:uid="{83ED2376-8555-47B3-98E3-2416CC880284}"/>
     <cellStyle name="Variable type other" xfId="63" xr:uid="{6646F6F7-E4F9-4165-8015-E25083532B5B}"/>
   </cellStyles>
-  <dxfs count="71">
+  <dxfs count="72">
     <dxf>
       <font>
         <color rgb="FFC44340"/>
@@ -2111,6 +2293,30 @@
       <fill>
         <patternFill>
           <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3324,20 +3530,20 @@
   </dxfs>
   <tableStyles count="3" defaultTableStyle="Equation table" defaultPivotStyle="PivotStyleLight16">
     <tableStyle name="Editable table" pivot="0" count="6" xr9:uid="{8C498A1C-5864-4BF8-8739-A3055FE117E0}">
-      <tableStyleElement type="wholeTable" dxfId="70"/>
-      <tableStyleElement type="headerRow" dxfId="69"/>
-      <tableStyleElement type="totalRow" dxfId="68"/>
-      <tableStyleElement type="firstColumn" dxfId="67"/>
-      <tableStyleElement type="firstRowStripe" dxfId="66"/>
-      <tableStyleElement type="secondRowStripe" dxfId="65"/>
+      <tableStyleElement type="wholeTable" dxfId="71"/>
+      <tableStyleElement type="headerRow" dxfId="70"/>
+      <tableStyleElement type="totalRow" dxfId="69"/>
+      <tableStyleElement type="firstColumn" dxfId="68"/>
+      <tableStyleElement type="firstRowStripe" dxfId="67"/>
+      <tableStyleElement type="secondRowStripe" dxfId="66"/>
     </tableStyle>
     <tableStyle name="Equation table" pivot="0" count="6" xr9:uid="{B247698E-E41D-4CCD-AA0A-C14817E9DE65}">
-      <tableStyleElement type="wholeTable" dxfId="64"/>
-      <tableStyleElement type="headerRow" dxfId="63"/>
-      <tableStyleElement type="totalRow" dxfId="62"/>
-      <tableStyleElement type="firstColumn" dxfId="61"/>
-      <tableStyleElement type="firstRowStripe" dxfId="60"/>
-      <tableStyleElement type="secondRowStripe" dxfId="59"/>
+      <tableStyleElement type="wholeTable" dxfId="65"/>
+      <tableStyleElement type="headerRow" dxfId="64"/>
+      <tableStyleElement type="totalRow" dxfId="63"/>
+      <tableStyleElement type="firstColumn" dxfId="62"/>
+      <tableStyleElement type="firstRowStripe" dxfId="61"/>
+      <tableStyleElement type="secondRowStripe" dxfId="60"/>
     </tableStyle>
     <tableStyle name="Table Style 1" pivot="0" count="0" xr9:uid="{97B370DB-5463-4A31-9160-5A96BD6A559D}"/>
   </tableStyles>
@@ -5319,7 +5525,7 @@
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{24F93AA5-118C-4309-9C0F-013815810933}" name="Table_SourceData_RainfallZones" displayName="Table_SourceData_RainfallZones" ref="D119:G121" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="27" xr:uid="{DE84EDD7-04C0-47C7-AA4F-3820B78D37D4}" name="Table_SourceData_RainfallZones" displayName="Table_SourceData_RainfallZones" ref="D119:G121" totalsRowShown="0">
   <autoFilter ref="D119:G121" xr:uid="{E08772F3-2E8C-40A8-B755-08A5BBDF4130}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -5327,16 +5533,16 @@
     <filterColumn colId="3" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{DFA53AAC-E2A2-4B0F-836B-9C665BF91999}" name="Rainfall Zone">
+    <tableColumn id="1" xr3:uid="{3E16FC0D-C113-4C5F-90C1-A34E03C23A16}" name="Rainfall Zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{39ED269E-9F6F-4696-86EC-3C2AD533BAB7}" name="Annual rainfall">
+    <tableColumn id="2" xr3:uid="{B7F050C9-778D-4315-9431-78AF5781A9B0}" name="Annual rainfall">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{39101C93-2904-40A8-8A17-AE5C28A08F28}" name="Min rainfall">
+    <tableColumn id="3" xr3:uid="{79B7BD82-F7C2-4C85-B92E-A0E115EB7144}" name="Min rainfall">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{5A33BFE6-C93F-40B0-A277-58954F8C67A1}" name="Max rainfall">
+    <tableColumn id="4" xr3:uid="{DA8720AF-963B-4B15-BD32-8C6DB96F09A7}" name="Max rainfall">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5345,16 +5551,16 @@
 </file>
 
 <file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{132DE72D-9079-421A-AC06-EF0480E3E250}" name="Table_SourceData_LeachingZones" displayName="Table_SourceData_LeachingZones" ref="D127:E129" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="28" xr:uid="{D0EA9A60-90FF-4308-A059-3461B59D09BE}" name="Table_SourceData_LeachingZones" displayName="Table_SourceData_LeachingZones" ref="D127:E129" totalsRowShown="0">
   <autoFilter ref="D127:E129" xr:uid="{A159E140-02ED-4547-B6E1-6695D8B16A11}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{2E0F5AF1-853B-4A10-9264-E0B7DCD7CBE4}" name="Leaching Zone">
+    <tableColumn id="1" xr3:uid="{E594937C-7947-4AEA-AC55-29200514BD7B}" name="Leaching Zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_LeachingZones_Data(), Table_SourceData_LeachingZones[[#Headers],[Leaching Zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{1B032057-1DA5-4B3E-88ED-94D098D0D8AA}" name="Leaching criteria">
+    <tableColumn id="2" xr3:uid="{790BDA81-D48D-40A1-AAFB-EEC620E9D0AB}" name="Leaching criteria">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_LeachingZones_Data(), Table_SourceData_LeachingZones[[#Headers],[Leaching Zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5363,16 +5569,16 @@
 </file>
 
 <file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="14" xr:uid="{AFDB7734-CDCD-4AD4-9195-767D750D59CE}" name="Table_SourceData_DataScores_Scope3" displayName="Table_SourceData_DataScores_Scope3" ref="D153:E158" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="29" xr:uid="{15324D8B-E213-4FB0-90AE-5AA51DCBF2B3}" name="Table_SourceData_DataScores_Scope3" displayName="Table_SourceData_DataScores_Scope3" ref="D153:E158" totalsRowShown="0">
   <autoFilter ref="D153:E158" xr:uid="{133D42B0-F6D2-470A-858A-37E6A7F5EC2B}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{D66E8DD3-92D2-4702-9BB0-1677117F7516}" name="Data source">
+    <tableColumn id="1" xr3:uid="{B60BCFEE-3050-48B9-853F-6BE6BBA2F7C1}" name="Data source">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{307FFE45-46E9-467A-B702-9D2152AAB0F3}" name="Data score">
+    <tableColumn id="2" xr3:uid="{7428E684-3B5B-4402-9ABD-77578FBEC581}" name="Data score">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5381,16 +5587,16 @@
 </file>
 
 <file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{53215EEF-0F66-46E8-8493-0C2ECB064A1D}" name="Table_SourceData_FracWET" displayName="Table_SourceData_FracWET" ref="D134:E136" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="30" xr:uid="{2C4ED8AD-BA9E-42CE-B6D7-5A005C309C0D}" name="Table_SourceData_FracWET" displayName="Table_SourceData_FracWET" ref="D134:E136" totalsRowShown="0">
   <autoFilter ref="D134:E136" xr:uid="{308E99BE-FE1F-47A4-B2CA-97217277C4E9}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{6C1186E0-21C5-4237-B070-AB9EB32CF2D4}" name="Is in leaching zone">
+    <tableColumn id="1" xr3:uid="{C9BDA189-A4CC-46BB-BCD8-DC01A0AF00C9}" name="Is in leaching zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWET_Data(),Table_SourceData_FracWET[[#Headers],[Is in leaching zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{25E7B126-DAAB-4A7E-8D08-BBC472059358}" name="FracWET" dataDxfId="42">
+    <tableColumn id="2" xr3:uid="{3FEBC7C9-4FF2-4E0B-94BD-F0CB2EA30021}" name="FracWET" dataDxfId="43">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWET_Data(),Table_SourceData_FracWET[[#Headers],[Is in leaching zone]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5399,7 +5605,7 @@
 </file>
 
 <file path=xl/tables/table14.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="16" xr:uid="{6CFE0685-2AD8-4C2D-81AE-58AF89682BAF}" name="Table_SourceData_Common_EFN2O" displayName="Table_SourceData_Common_EFN2O" ref="D186:H199" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="31" xr:uid="{F56B59C1-10E2-409F-95E7-CC8DFF777784}" name="Table_SourceData_Common_EFN2O" displayName="Table_SourceData_Common_EFN2O" ref="D186:H199" totalsRowShown="0">
   <autoFilter ref="D186:H199" xr:uid="{D41FBEA4-8379-4DF7-A068-BF94D364F1A2}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -5408,19 +5614,19 @@
     <filterColumn colId="4" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{86FDDE80-60A6-43F5-B8F2-852C30FFDDD4}" name="Production system j">
+    <tableColumn id="1" xr3:uid="{C1E97D25-90EB-4E8C-95D7-6038DF8738EC}" name="Production system j">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{AF7EE38D-2EA6-471E-AF48-94783A63C084}" name="EFN2O">
+    <tableColumn id="2" xr3:uid="{12D73886-936D-4CBC-ADE4-2BDE24D51F43}" name="EFN2O">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{FF099149-CB77-4055-A9F1-24C624BE731A}" name="Production system only">
+    <tableColumn id="3" xr3:uid="{4A00BD17-AE77-4BA7-BDE7-11914B84E9C7}" name="Production system only">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{D923759D-64DA-4871-BC83-685A00270F3F}" name="Irrigation method">
+    <tableColumn id="4" xr3:uid="{85000787-D1A7-4424-92DD-C8DC5B3A8A73}" name="Irrigation method">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{F8B21283-BD88-4E91-ACED-93E7D567F8DE}" name="Rainfall zone">
+    <tableColumn id="5" xr3:uid="{37F8D12C-4C4C-4CA5-A291-CC5599AD1002}" name="Rainfall zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5429,16 +5635,16 @@
 </file>
 
 <file path=xl/tables/table15.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="17" xr:uid="{3E1E0388-8BE6-4AC3-BA48-F5850C4CCB50}" name="Table_SourceData_FracWETIrrigation" displayName="Table_SourceData_FracWETIrrigation" ref="D142:E147" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="32" xr:uid="{DE9DFFF3-70E2-4C7A-B578-D28ADBC1B7F6}" name="Table_SourceData_FracWETIrrigation" displayName="Table_SourceData_FracWETIrrigation" ref="D142:E147" totalsRowShown="0">
   <autoFilter ref="D142:E147" xr:uid="{1F48CA34-50DE-46D5-B32A-BB3A1E818E37}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{50E771C9-793A-451E-9134-A621AA24F3A7}" name="Irrigation type i">
+    <tableColumn id="1" xr3:uid="{B5AD0AF5-44FA-42C2-92F4-516A88800BB7}" name="Irrigation type i">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{D1715F6E-94A2-4313-A5CD-F60489481CC1}" name="FracWET" dataDxfId="41" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{280511C0-7C74-4B32-85B3-D694148E15B1}" name="FracWET" dataDxfId="42" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5447,16 +5653,16 @@
 </file>
 
 <file path=xl/tables/table16.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="18" xr:uid="{95681F27-3966-43CD-9F25-B93F717ED625}" name="Table_SourceData_EFPastureRangeAndPaddock" displayName="Table_SourceData_EFPastureRangeAndPaddock" ref="D206:E208" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="33" xr:uid="{CA7CF709-8E55-4288-B2C1-8F824EE20562}" name="Table_SourceData_EFPastureRangeAndPaddock" displayName="Table_SourceData_EFPastureRangeAndPaddock" ref="D206:E208" totalsRowShown="0">
   <autoFilter ref="D206:E208" xr:uid="{D5BE3F89-D70E-4C53-A71C-E756622DEF38}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{9D7639FD-A66A-474D-A3A6-A58D9019C41D}" name="Climate zone">
+    <tableColumn id="1" xr3:uid="{3AB53AB9-F280-4F51-B36D-880A18AD2247}" name="Climate zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data(), Table_SourceData_EFPastureRangeAndPaddock[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{B8ABC40B-FC6F-422F-B488-06F01CEBE1E6}" name="EFPRP" dataDxfId="40" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{C3323047-831D-4AB2-8776-29E6D5AF78D6}" name="EFPRP" dataDxfId="41" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data(), Table_SourceData_EFPastureRangeAndPaddock[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5465,16 +5671,16 @@
 </file>
 
 <file path=xl/tables/table17.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="19" xr:uid="{7E5586BB-570A-459F-81DD-BD7B147EF32B}" name="Table_SourceData_Common_MonthToSeason" displayName="Table_SourceData_Common_MonthToSeason" ref="D212:E224" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="34" xr:uid="{C7711168-05B1-413C-8993-599CA2EF5FEF}" name="Table_SourceData_Common_MonthToSeason" displayName="Table_SourceData_Common_MonthToSeason" ref="D212:E224" totalsRowShown="0">
   <autoFilter ref="D212:E224" xr:uid="{97796C3A-D95E-4077-AA20-A8FE4145DAAD}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{17846D73-F428-4903-9879-09547142816D}" name="Month">
+    <tableColumn id="1" xr3:uid="{85877966-3D1F-4760-BB81-4063078CC446}" name="Month">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{D9F4DA30-451D-40FA-BD4F-4A7E1A9E3791}" name="Season" dataDxfId="39" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{B39A3F55-1628-491A-8140-28BEBCC3ECBC}" name="Season" dataDxfId="40" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5483,7 +5689,7 @@
 </file>
 
 <file path=xl/tables/table18.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="20" xr:uid="{0EE8A284-553D-4435-8E34-C191AD888DCF}" name="Table_SourceData_Common_MCFTemperatureZone" displayName="Table_SourceData_Common_MCFTemperatureZone" ref="D231:S250" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="35" xr:uid="{19A54B1E-7BC3-4ED6-B647-F660F22E2EE4}" name="Table_SourceData_Common_MCFTemperatureZone" displayName="Table_SourceData_Common_MCFTemperatureZone" ref="D231:S250" totalsRowShown="0">
   <autoFilter ref="D231:S250" xr:uid="{1D72DD9B-C8FA-48F4-9A11-20231FF87B5A}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -5503,52 +5709,52 @@
     <filterColumn colId="15" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="16">
-    <tableColumn id="1" xr3:uid="{D2DE3766-E17D-4A8F-B5D1-A6BEDF74F33C}" name="Temperature zone">
+    <tableColumn id="1" xr3:uid="{3BA52100-D072-47EC-8911-ABA1898E9034}" name="Temperature zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{76D9FF22-9919-49B7-9087-FEED4F33B186}" name="MAT (ºC)" dataDxfId="38" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{A2B4F5D6-25FB-42F1-B7E8-99F8E1C0398C}" name="MAT (ºC)" dataDxfId="39" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{8156DECE-8836-4D51-AFA2-1ACC408F453A}" name="Anaerobic lagoon" dataDxfId="37" dataCellStyle="Content normal">
+    <tableColumn id="3" xr3:uid="{E5A9667E-8205-4A4F-87BF-0C84BAE4E6F6}" name="Anaerobic lagoon" dataDxfId="38" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{41FA6607-0FB9-4A8F-A0B1-048D5F14FAD8}" name="Digester / covered lagoons" dataDxfId="36" dataCellStyle="Content normal">
+    <tableColumn id="4" xr3:uid="{0DF90A1F-9399-4E8F-9379-21F4FCD395E9}" name="Digester / covered lagoons" dataDxfId="37" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{131F0F9E-F7E6-4B6E-AED1-6987159BDD16}" name="Liquid systems" dataDxfId="35" dataCellStyle="Content normal">
+    <tableColumn id="5" xr3:uid="{8A6C00BF-5550-416F-8EA9-453E3CE17183}" name="Liquid systems" dataDxfId="36" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{C3948707-84DB-4491-A4BA-77144368FA93}" name="Daily spread" dataDxfId="34" dataCellStyle="Content normal">
+    <tableColumn id="6" xr3:uid="{39992EA4-B2E0-4BE2-87B2-B8A23028EEE8}" name="Daily spread" dataDxfId="35" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{6B7863FD-781F-44F0-86FA-D1F65A095B95}" name="Composting (passive windrow)" dataDxfId="33" dataCellStyle="Content normal">
+    <tableColumn id="7" xr3:uid="{D6B69C5D-ECBF-4516-AB1C-B91326E938A6}" name="Composting (passive windrow)" dataDxfId="34" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{9AE0A734-A0E5-4DE9-8F3A-C39D225AC6E6}" name="Solid storage" dataDxfId="32" dataCellStyle="Content normal">
+    <tableColumn id="8" xr3:uid="{247D5521-144E-4CCE-80E1-5AB24EBFBB5D}" name="Solid storage" dataDxfId="33" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{52F058B3-A46E-4D93-966E-EF7A93050304}" name="Pit storage" dataDxfId="31" dataCellStyle="Content normal">
+    <tableColumn id="9" xr3:uid="{332816B4-F16B-4167-A524-6C2A78CB27D6}" name="Pit storage" dataDxfId="32" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{AA187935-F0EA-44C3-8A90-EB2BF8EEDBC6}" name="Deep litter" dataDxfId="30" dataCellStyle="Content normal">
+    <tableColumn id="10" xr3:uid="{6075DFEB-F217-4BCE-A555-DCBC19E62AF9}" name="Deep litter" dataDxfId="31" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{DA6E3942-8BBA-455F-8A15-9AA83B98F5B9}" name="Poultry manure with bedding" dataDxfId="29" dataCellStyle="Content normal">
+    <tableColumn id="11" xr3:uid="{9C5AE16C-BB4E-4F62-A3DF-E4E6A9667B60}" name="Poultry manure with bedding" dataDxfId="30" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{4B87AB1C-B894-4176-A9D3-C5F2B7B3C5F2}" name="Poultry manure without bedding" dataDxfId="28" dataCellStyle="Content normal">
+    <tableColumn id="12" xr3:uid="{0AAF4A70-31D5-4AC6-91D7-3016F11F8F29}" name="Poultry manure without bedding" dataDxfId="29" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{117F3C41-34B6-4E8B-BD75-ABC3FCE32300}" name="Direct processing" dataDxfId="27" dataCellStyle="Content normal">
+    <tableColumn id="13" xr3:uid="{634C7A54-FA29-4043-A442-C1608BF83263}" name="Direct processing" dataDxfId="28" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{835223C8-2C01-4905-B90E-D682FFA0E2BA}" name="Direct application" dataDxfId="26" dataCellStyle="Content normal">
+    <tableColumn id="14" xr3:uid="{C2D32322-788B-4E8C-B317-C5131999872D}" name="Direct application" dataDxfId="27" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{5B535F7B-F2CE-4721-A81E-D78DCEBDBC99}" name="Pasture range and paddock" dataDxfId="25" dataCellStyle="Content normal">
+    <tableColumn id="15" xr3:uid="{EC960663-C506-49AA-BCF9-EAA19D3A3E81}" name="Pasture range and paddock" dataDxfId="26" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{2799D307-CBDD-47DF-9BFB-86243FF1A72A}" name="MAT raw" dataDxfId="24" dataCellStyle="Content normal">
+    <tableColumn id="16" xr3:uid="{A12E1F63-F2C6-401E-80A7-4833FDA041E0}" name="MAT raw" dataDxfId="25" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5557,16 +5763,16 @@
 </file>
 
 <file path=xl/tables/table19.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="21" xr:uid="{4D9584B4-0C6F-4D05-89EA-5DCB7F7F88FE}" name="Table_SourceData_Common_EFOrganicFertCropResidues" displayName="Table_SourceData_Common_EFOrganicFertCropResidues" ref="D257:E259" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="36" xr:uid="{B5F62189-5CEA-424F-A148-6A807AA751BF}" name="Table_SourceData_Common_EFOrganicFertCropResidues" displayName="Table_SourceData_Common_EFOrganicFertCropResidues" ref="D257:E259" totalsRowShown="0">
   <autoFilter ref="D257:E259" xr:uid="{56E01C14-1BB8-4015-9158-4CEB4D3B605C}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{3FE936E2-F1F6-460F-BD4F-F8D56C515AA3}" name="Climate Zone">
+    <tableColumn id="1" xr3:uid="{C2CFF277-1D84-4D50-9500-09E105732EB0}" name="Climate Zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data(), Table_SourceData_Common_EFOrganicFertCropResidues[[#Headers],[Climate Zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{D4BA3B32-6A2F-44C0-B9A3-B1F6116D396C}" name="EFNi &amp; EFN2Oi" dataDxfId="23" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{31499B92-9939-4992-89BF-ACD4D6C5C757}" name="EFNi &amp; EFN2Oi" dataDxfId="24" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data(), Table_SourceData_Common_EFOrganicFertCropResidues[[#Headers],[Climate Zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5592,21 +5798,85 @@
 </table>
 </file>
 
+<file path=xl/tables/table20.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="37" xr:uid="{947E85E4-20D8-412D-93CB-6DA8B0407F44}" name="Table_SourceData_DataQuality_TemporalRepresentativeness" displayName="Table_SourceData_DataQuality_TemporalRepresentativeness" ref="D265:F270" totalsRowShown="0">
+  <autoFilter ref="D265:F270" xr:uid="{9AD44602-D2F2-4D97-923C-A32E98F8C17A}">
+    <filterColumn colId="0" hiddenButton="1"/>
+    <filterColumn colId="1" hiddenButton="1"/>
+    <filterColumn colId="2" hiddenButton="1"/>
+  </autoFilter>
+  <tableColumns count="3">
+    <tableColumn id="2" xr3:uid="{4FB690F7-1FA2-43C0-8D07-7F75F4CEBD1D}" name="Description" dataDxfId="23" dataCellStyle="Content normal"/>
+    <tableColumn id="1" xr3:uid="{1DF1171B-F805-4983-8229-8347FD756B1B}" name="ID"/>
+    <tableColumn id="3" xr3:uid="{6B8F8F0F-2EFE-4E19-9CEA-97224F11C6BD}" name="Score"/>
+  </tableColumns>
+  <tableStyleInfo name="Equation table" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table21.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="38" xr:uid="{20A8ADB8-2B9F-4552-B7BB-7049E2E058EC}" name="Table_SourceData_DataQuality_SpatialRepresentativeness" displayName="Table_SourceData_DataQuality_SpatialRepresentativeness" ref="D274:F279" totalsRowShown="0">
+  <autoFilter ref="D274:F279" xr:uid="{95094D65-3E0E-45CE-A3F4-F41E74C11901}">
+    <filterColumn colId="0" hiddenButton="1"/>
+    <filterColumn colId="1" hiddenButton="1"/>
+    <filterColumn colId="2" hiddenButton="1"/>
+  </autoFilter>
+  <tableColumns count="3">
+    <tableColumn id="1" xr3:uid="{90A853E7-3E43-410E-98FA-615957EF13B2}" name="Description"/>
+    <tableColumn id="2" xr3:uid="{E6BCF510-2CDE-4F4A-895D-70ED9A8C61B6}" name="ID"/>
+    <tableColumn id="3" xr3:uid="{F5660FC8-D279-47FF-9614-F3C5975269D5}" name="Score"/>
+  </tableColumns>
+  <tableStyleInfo name="Equation table" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table22.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="39" xr:uid="{3BED459F-5D79-4003-97DE-EEC466DB94A4}" name="Table_SourceData_DataQuality_SampleSize" displayName="Table_SourceData_DataQuality_SampleSize" ref="D283:F288" totalsRowShown="0">
+  <autoFilter ref="D283:F288" xr:uid="{DE8F748C-E65A-4AA2-81BB-D28A432CF334}">
+    <filterColumn colId="0" hiddenButton="1"/>
+    <filterColumn colId="1" hiddenButton="1"/>
+    <filterColumn colId="2" hiddenButton="1"/>
+  </autoFilter>
+  <tableColumns count="3">
+    <tableColumn id="1" xr3:uid="{3D43B8FC-9FE9-4E78-99FC-65BE31EAB020}" name="Description"/>
+    <tableColumn id="2" xr3:uid="{B7157DFC-B8C1-4CEE-88A5-58533F91BF63}" name="ID"/>
+    <tableColumn id="3" xr3:uid="{672EE14B-5945-4858-8B18-542564057B31}" name="Score"/>
+  </tableColumns>
+  <tableStyleInfo name="Equation table" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table23.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="40" xr:uid="{398C7D01-A0DF-4CB7-A786-586DC24BE420}" name="Table_SourceData_DataQuality_Scope3" displayName="Table_SourceData_DataQuality_Scope3" ref="D292:F297" totalsRowShown="0">
+  <autoFilter ref="D292:F297" xr:uid="{43A1C4DA-75D1-45DF-BA9A-1798C2CC5A4B}">
+    <filterColumn colId="0" hiddenButton="1"/>
+    <filterColumn colId="1" hiddenButton="1"/>
+    <filterColumn colId="2" hiddenButton="1"/>
+  </autoFilter>
+  <tableColumns count="3">
+    <tableColumn id="1" xr3:uid="{BDAA76B7-B15D-4079-AB6B-9DCA2C0AFF47}" name="Description"/>
+    <tableColumn id="2" xr3:uid="{EF9FE234-104A-43E6-8DC0-5A5860EDE80C}" name="ID"/>
+    <tableColumn id="3" xr3:uid="{57630E7A-6099-44EE-ABF1-94DFACB31880}" name="Score"/>
+  </tableColumns>
+  <tableStyleInfo name="Equation table" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{71310740-5886-4F26-8E26-D453895857B2}" name="Table_AustralianStates" displayName="Table_AustralianStates" ref="D6:F14" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{51D4F44B-B470-4339-8B92-F63B342E59A4}" name="Table_AustralianStates" displayName="Table_AustralianStates" ref="D6:F14" totalsRowShown="0">
   <autoFilter ref="D6:F14" xr:uid="{E0906749-7FC7-47DE-82F6-F796C4463018}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{6BE6C3B3-85EE-4327-8A6F-10418E3FDBA4}" name="State/Territory">
+    <tableColumn id="1" xr3:uid="{0F84C2C4-A0A9-49D3-8200-F58B8E8795AC}" name="State/Territory">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{657CA26E-C37E-4B3B-98C6-7BED5AB06C80}" name="Common Name">
+    <tableColumn id="2" xr3:uid="{850109A0-65E6-42D6-9E69-8D2EF6666568}" name="Common Name">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{ED2054A6-B729-4999-B575-5AC537741193}" name="Abbreviation">
+    <tableColumn id="3" xr3:uid="{AFF9A174-94C6-43D2-94A6-6936390502B3}" name="Abbreviation">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5615,12 +5885,12 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{16BD9B0A-7494-419C-8C0E-C2B7E29AC060}" name="Table_WASA4Areas" displayName="Table_WASA4Areas" ref="D20:D30" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{FD6FB40D-C430-40EA-8E14-46867DF62599}" name="Table_WASA4Areas" displayName="Table_WASA4Areas" ref="D20:D30" totalsRowShown="0">
   <autoFilter ref="D20:D30" xr:uid="{5FA81339-C6C8-4D36-BEEA-6C4AEDD9E676}">
     <filterColumn colId="0" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="1">
-    <tableColumn id="1" xr3:uid="{484EFDF8-5661-4DCB-BA4A-C26C1CE4D05A}" name="SA 4 Name">
+    <tableColumn id="1" xr3:uid="{9299852C-1DEE-43D2-B5A7-AB37639E89DE}" name="SA 4 Name">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5629,16 +5899,16 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{E53ECB1A-75C1-44A7-9484-0E1E52E72F96}" name="Table_GWPData" displayName="Table_GWPData" ref="D36:E43" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="22" xr:uid="{FC635525-8648-4490-94CC-F0F89B18F813}" name="Table_GWPData" displayName="Table_GWPData" ref="D36:E43" totalsRowShown="0">
   <autoFilter ref="D36:E43" xr:uid="{B8E87A66-3E41-4AD3-925D-01EE21B43D7A}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{A3D2B92A-FC3A-463F-9E7E-82B2A77AB147}" name="Gas">
+    <tableColumn id="1" xr3:uid="{046DB107-1C13-4246-BD2F-9D4BF3EE68DE}" name="Gas">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{95A84F3B-6F44-411A-86B8-6E64EFD36570}" name="CO2-e factor">
+    <tableColumn id="2" xr3:uid="{991B9B7E-E525-4A85-8A2D-CCC090AAF69B}" name="CO2-e factor">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5647,7 +5917,7 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{874E6A36-A966-4BF7-A9E4-705DBB7888EF}" name="Table_GasToMolecularConversionFactor" displayName="Table_GasToMolecularConversionFactor" ref="D47:H54" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="23" xr:uid="{647034D0-05EB-4A22-9F54-CC85D5A8AEAE}" name="Table_GasToMolecularConversionFactor" displayName="Table_GasToMolecularConversionFactor" ref="D47:H54" totalsRowShown="0">
   <autoFilter ref="D47:H54" xr:uid="{C1F562BB-DAA6-45BB-951A-7BAFA5B64B45}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -5656,19 +5926,19 @@
     <filterColumn colId="4" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{9C198FF8-733E-46BF-81A2-B0D78722D688}" name="Gas">
+    <tableColumn id="1" xr3:uid="{E5FF4C60-079C-467A-9D1F-EA9E19AD4B8F}" name="Gas">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{20AFED79-4B40-4B0E-A99B-7F91615C1379}" name="Conversion factor">
+    <tableColumn id="5" xr3:uid="{5FCED1DA-AE1E-4D32-9964-E7D6B842C1CF}" name="Conversion factor">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{0C318BFB-2EDA-4E53-A2D3-62F69C15B8A5}" name="Conversion factor 1">
+    <tableColumn id="2" xr3:uid="{214C3545-A720-4A79-8FE3-E24C810097EE}" name="Conversion factor 1">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{6C32820B-1E07-4E09-AC74-8C661C1E44D3}" name="Conversion factor 2">
+    <tableColumn id="3" xr3:uid="{E3CA1A79-DB99-4E58-8C20-6C9F34B0E7AA}" name="Conversion factor 2">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{A92684B6-DC34-40F4-A70B-354CB81E0D2A}" name="Conversion factor combined">
+    <tableColumn id="4" xr3:uid="{A79513DA-B1BB-46C2-B453-9774B68AACB3}" name="Conversion factor combined">
       <calculatedColumnFormula>Table_GasToMolecularConversionFactor[[#This Row],[Conversion factor 1]]/Table_GasToMolecularConversionFactor[[#This Row],[Conversion factor 2]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5677,7 +5947,7 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{A3B153B6-41ED-4C89-8A99-1130E123AB45}" name="Table_SourceData_ClimateZones" displayName="Table_SourceData_ClimateZones" ref="D89:S97" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="24" xr:uid="{CCFBA209-A2AF-4523-AF9B-0A89F5C0A087}" name="Table_SourceData_ClimateZones" displayName="Table_SourceData_ClimateZones" ref="D89:S97" totalsRowShown="0">
   <autoFilter ref="D89:S97" xr:uid="{5A437AE9-7724-4CF2-ACCF-291078682FB9}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -5697,52 +5967,52 @@
     <filterColumn colId="15" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="16">
-    <tableColumn id="1" xr3:uid="{BF5CE39F-22B0-49A1-B3E4-0355BE0D99FC}" name="Climate zone" totalsRowCellStyle="Content bold">
+    <tableColumn id="1" xr3:uid="{208F8859-5E32-4BF6-A884-46F1CF9F95DB}" name="Climate zone" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{A9943293-560E-4412-83D9-D0A0880BABB8}" name="MAT" totalsRowDxfId="58" totalsRowCellStyle="Content bold">
+    <tableColumn id="2" xr3:uid="{0D2A9514-0438-4250-87D9-B77F6BCA4904}" name="MAT" totalsRowDxfId="59" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{1C6D6086-5E6E-4948-809B-1B679044D0F3}" name="MAP" totalsRowDxfId="57" totalsRowCellStyle="Content bold">
+    <tableColumn id="3" xr3:uid="{E43055C8-E26B-48DA-815D-75A4377F4C92}" name="MAP" totalsRowDxfId="58" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{E637016B-41CB-4381-943D-8BEF2929F1D7}" name="Frost days per year" totalsRowDxfId="56" totalsRowCellStyle="Content bold">
+    <tableColumn id="4" xr3:uid="{722706E7-2ABC-4ABF-9EBD-275D03B4F5C5}" name="Frost days per year" totalsRowDxfId="57" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{D9A2F0F2-1692-48AE-A5DB-279BBA8E6820}" name="Elevation" totalsRowDxfId="55" totalsRowCellStyle="Content bold">
+    <tableColumn id="5" xr3:uid="{2BB82403-124E-4D98-88F7-440FEBF33F6E}" name="Elevation" totalsRowDxfId="56" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{7F6B93F6-3B0A-4231-BFEA-D7F6DDF25D80}" name="MAP:PET" totalsRowDxfId="54" totalsRowCellStyle="Content bold">
+    <tableColumn id="6" xr3:uid="{875F7F4B-5CC6-4E34-B471-C4EA61519A1C}" name="MAP:PET" totalsRowDxfId="55" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{0B17F5EA-E83A-454D-9B08-6599D497EA0E}" name="Min temp" totalsRowDxfId="53" totalsRowCellStyle="Content bold">
+    <tableColumn id="7" xr3:uid="{9B6D3F56-B3C1-447A-A14C-498BC8A19C22}" name="Min temp" totalsRowDxfId="54" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{703FA166-6F32-4B63-B2FE-E91C9A7A304D}" name="Max temp" totalsRowDxfId="52" totalsRowCellStyle="Content bold">
+    <tableColumn id="8" xr3:uid="{9E642DCC-3FBB-46F1-AD04-B599CCDA2054}" name="Max temp" totalsRowDxfId="53" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{81DAFAC4-A0B6-4185-BDE1-614320AB2934}" name="Min rainfall" totalsRowDxfId="51" totalsRowCellStyle="Content bold">
+    <tableColumn id="9" xr3:uid="{4A4452DF-1DE6-4CF3-B169-B3F856B417A2}" name="Min rainfall" totalsRowDxfId="52" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{E03A1B17-B4FC-4FCA-BBF5-31181766E5C9}" name="Max rainfall" totalsRowDxfId="50" totalsRowCellStyle="Content bold">
+    <tableColumn id="10" xr3:uid="{27EB2CF8-2A73-40FC-8F2E-A3DC492E1A3C}" name="Max rainfall" totalsRowDxfId="51" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{515FCAD1-8901-45CC-ACEF-C22676580F26}" name="Min frost days" totalsRowDxfId="49" totalsRowCellStyle="Content bold">
+    <tableColumn id="11" xr3:uid="{391B58BD-0419-4F6F-9BD9-9AD049A0B340}" name="Min frost days" totalsRowDxfId="50" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{C1557A3C-8CF8-4F9C-8BA3-4787EE5F0417}" name="Max frost days" totalsRowDxfId="48" totalsRowCellStyle="Content bold">
+    <tableColumn id="15" xr3:uid="{0A737FDB-25C6-4907-9BD2-6FFF693B660C}" name="Max frost days" totalsRowDxfId="49" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{C7EE21DF-10E1-49C7-A4F4-6A9A00FC253F}" name="Min elevation" totalsRowDxfId="47" totalsRowCellStyle="Content bold">
+    <tableColumn id="12" xr3:uid="{055BDA20-BE6D-4820-A3D4-7EDBA58A6776}" name="Min elevation" totalsRowDxfId="48" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{55C5D482-B74D-4A0E-99D1-562AB6BAD7E3}" name="Max elevation" totalsRowDxfId="46" totalsRowCellStyle="Content bold">
+    <tableColumn id="16" xr3:uid="{3B9E2850-460E-48CF-B901-7ABBBBB2E674}" name="Max elevation" totalsRowDxfId="47" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{DD112C69-08AE-49D6-89E6-4FF4038192F2}" name="Min MAP:PET" totalsRowDxfId="45" totalsRowCellStyle="Content bold">
+    <tableColumn id="13" xr3:uid="{EB9F67BC-9838-4EBD-B4A9-1E559F3231FF}" name="Min MAP:PET" totalsRowDxfId="46" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{5641B3CD-98FA-43C0-916F-85710AC6BC5E}" name="Max MAP:PET" totalsRowDxfId="44" totalsRowCellStyle="Content bold">
+    <tableColumn id="17" xr3:uid="{F72B4BAF-6FA9-4811-9F60-3B0754C31D6F}" name="Max MAP:PET" totalsRowDxfId="45" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5751,16 +6021,16 @@
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{A4136810-34EA-455C-A54D-9DB715C11457}" name="Table_SourceData_WetDryZones" displayName="Table_SourceData_WetDryZones" ref="D63:E77" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="25" xr:uid="{C0E1A8F0-A915-46D0-9B0D-A1DC02E1D7D9}" name="Table_SourceData_WetDryZones" displayName="Table_SourceData_WetDryZones" ref="D63:E77" totalsRowShown="0">
   <autoFilter ref="D63:E77" xr:uid="{3597E019-B21E-4B76-BCC8-D02D497BCFA9}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{1FC5C2DE-554C-42A3-AC38-8F028D4BEF55}" name="Climate zone" totalsRowCellStyle="Content bold">
+    <tableColumn id="1" xr3:uid="{12082A3D-B227-4592-B813-1E73BDF6169D}" name="Climate zone" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{8ABEC6DD-4445-430B-8B5C-23DF66CFD572}" name="Wet or Dry Zone" totalsRowDxfId="43" totalsRowCellStyle="Content bold">
+    <tableColumn id="2" xr3:uid="{AF7142F6-170D-4ABC-BCFD-AF2783A01549}" name="Wet or Dry Zone" totalsRowDxfId="44" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5769,7 +6039,7 @@
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{0AF3E493-5068-42AE-8750-70278D60E231}" name="Table_SourceData_TemperatureZones" displayName="Table_SourceData_TemperatureZones" ref="D109:G112" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="26" xr:uid="{BA8B8268-3AC7-4EC0-B174-E23A4E1D08EB}" name="Table_SourceData_TemperatureZones" displayName="Table_SourceData_TemperatureZones" ref="D109:G112" totalsRowShown="0">
   <autoFilter ref="D109:G112" xr:uid="{AB16FEAB-AB03-45E1-BBD4-66D29CD412DF}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -5777,16 +6047,16 @@
     <filterColumn colId="3" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{269178F2-2D1D-4091-AF9D-F42662D206E9}" name="Temperature Zone">
+    <tableColumn id="1" xr3:uid="{79BA0019-4F22-411E-9DD8-3391F019CF52}" name="Temperature Zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{FA2333D1-F299-4D46-9AEC-FB381BFF982E}" name="MAT">
+    <tableColumn id="2" xr3:uid="{D29FA8A9-ECF6-47C3-9B83-27A16B6A0975}" name="MAT">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{8172341F-A412-4576-B34D-DE1A46531B7A}" name="Min MAT">
+    <tableColumn id="3" xr3:uid="{DD528CB7-DBDC-40CD-A36A-DED3124A5F15}" name="Min MAT">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{409CB111-50D3-47B3-87BB-97074B5D17AB}" name="Max MAT">
+    <tableColumn id="4" xr3:uid="{6E8E3A42-CFA3-44D0-B564-1E00C5DCDB7C}" name="Max MAT">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -6049,75 +6319,35 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53CF26AA-F4FA-460F-9B3A-C19960195F0B}">
-  <dimension ref="A1:A19"/>
+  <dimension ref="A1:A8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:1" ht="25.5" x14ac:dyDescent="0.35">
-      <c r="A1" s="30" t="e" vm="1">
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="39" t="str">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" s="75" t="str">
         <f>HYPERLINK("#'Home'!A1", "Home")</f>
         <v>Home</v>
       </c>
     </row>
-    <row r="4" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A4" s="12" t="str">
-        <f>HYPERLINK("#'Overview'!A1", "Overview")</f>
-        <v>Overview</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A5" s="12" t="str">
-        <f>HYPERLINK("#'Results'!A1", "Results")</f>
-        <v>Results</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A8" s="14" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A9" s="12" t="str">
-        <f>HYPERLINK("#'Input - Wastewater'!A1", "Wastewater")</f>
-        <v>Wastewater</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A12" s="13" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A13" s="12" t="str">
-        <f>HYPERLINK("#'11.1.1-2 Wastewater CH4'!A1", "11.1.1-2 Wastewater CH4")</f>
-        <v>11.1.1-2 Wastewater CH4</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A14" s="12" t="str">
-        <f>HYPERLINK("#'11.1.3-4 Wastewater N2O'!A1", "11.1.3-4 Wastewater N2O")</f>
-        <v>11.1.3-4 Wastewater N2O</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" s="74" t="s">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6" s="74" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A18" s="12" t="str">
-        <f>HYPERLINK("#'Constants - Wastewater'!A1", "Constants - Wastewater")</f>
-        <v>Constants - Wastewater</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A19" s="12" t="str">
+    <row r="7" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A7" s="12" t="str">
         <f>HYPERLINK("#'Constants - Common'!A1", "Constants - Common")</f>
         <v>Constants - Common</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A8" s="12" t="str">
+        <f>HYPERLINK("#'Acknowledgements'!A1", "Acknowledgements")</f>
+        <v>Acknowledgements</v>
       </c>
     </row>
   </sheetData>
@@ -9748,8 +9978,11 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35C53253-305C-4133-9D22-0F5CB91D3486}">
-  <dimension ref="A1:BY259"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2737F273-4C9D-4D7E-85B8-4FF96E9BC774}">
+  <sheetPr>
+    <tabColor theme="2" tint="-0.499984740745262"/>
+  </sheetPr>
+  <dimension ref="A1:BY297"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30.7109375" style="6" customWidth="1"/>
@@ -9776,7 +10009,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:65" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="30" t="e" vm="1">
+      <c r="A1" s="7" t="e" vm="1">
         <v>#VALUE!</v>
       </c>
       <c r="C1" s="7" t="s">
@@ -9814,17 +10047,11 @@
       <c r="W3" s="9"/>
     </row>
     <row r="4" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="12" t="str">
-        <f>HYPERLINK("#'Overview'!A1", "Overview")</f>
-        <v>Overview</v>
-      </c>
+      <c r="A4"/>
       <c r="BM4" s="2"/>
     </row>
     <row r="5" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="12" t="str">
-        <f>HYPERLINK("#'Results'!A1", "Results")</f>
-        <v>Results</v>
-      </c>
+      <c r="A5"/>
       <c r="D5" s="5" t="str" cm="1">
         <f t="array" ref="D5">Common_SourceData.Common_SourceData_AustralianStatesTerritories_Title()</f>
         <v>Australian states and territories</v>
@@ -9832,7 +10059,9 @@
       <c r="BM5" s="2"/>
     </row>
     <row r="6" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6"/>
+      <c r="A6" s="74" t="s">
+        <v>1</v>
+      </c>
       <c r="D6" s="24" t="s">
         <v>5</v>
       </c>
@@ -9844,7 +10073,10 @@
       </c>
     </row>
     <row r="7" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7"/>
+      <c r="A7" s="53" t="str">
+        <f>HYPERLINK("#'Constants - Common'!A1", "Constants - Common")</f>
+        <v>Constants - Common</v>
+      </c>
       <c r="D7" s="24" t="str" cm="1">
         <f t="array" ref="D7">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
         <v>New South Wales</v>
@@ -9859,8 +10091,9 @@
       </c>
     </row>
     <row r="8" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="14" t="s">
-        <v>0</v>
+      <c r="A8" s="12" t="str">
+        <f>HYPERLINK("#'Acknowledgements'!A1", "Acknowledgements")</f>
+        <v>Acknowledgements</v>
       </c>
       <c r="D8" s="24" t="str" cm="1">
         <f t="array" ref="D8">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
@@ -9876,10 +10109,7 @@
       </c>
     </row>
     <row r="9" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="12" t="str">
-        <f>HYPERLINK("#'Input - Wastewater'!A1", "Wastewater")</f>
-        <v>Wastewater</v>
-      </c>
+      <c r="A9"/>
       <c r="D9" s="24" t="str" cm="1">
         <f t="array" ref="D9">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
         <v>Victoria</v>
@@ -9925,9 +10155,7 @@
       <c r="BM11" s="2"/>
     </row>
     <row r="12" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="13" t="s">
-        <v>44</v>
-      </c>
+      <c r="A12"/>
       <c r="D12" s="24" t="str" cm="1">
         <f t="array" ref="D12">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
         <v>Western Australia</v>
@@ -9943,10 +10171,7 @@
       <c r="BM12" s="2"/>
     </row>
     <row r="13" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="12" t="str">
-        <f>HYPERLINK("#'11.1.1-2 Wastewater CH4'!A1", "11.1.1-2 Wastewater CH4")</f>
-        <v>11.1.1-2 Wastewater CH4</v>
-      </c>
+      <c r="A13"/>
       <c r="D13" s="24" t="str" cm="1">
         <f t="array" ref="D13">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
         <v>Tasmania</v>
@@ -9961,10 +10186,7 @@
       </c>
     </row>
     <row r="14" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="12" t="str">
-        <f>HYPERLINK("#'11.1.3-4 Wastewater N2O'!A1", "11.1.3-4 Wastewater N2O")</f>
-        <v>11.1.3-4 Wastewater N2O</v>
-      </c>
+      <c r="A14"/>
       <c r="D14" s="24" t="str" cm="1">
         <f t="array" ref="D14">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
         <v>Northern Territory</v>
@@ -9985,25 +10207,17 @@
       <c r="A16"/>
     </row>
     <row r="17" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="74" t="s">
-        <v>1</v>
-      </c>
+      <c r="A17"/>
     </row>
     <row r="18" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="12" t="str">
-        <f>HYPERLINK("#'Constants - Wastewater'!A1", "Constants - Wastewater")</f>
-        <v>Constants - Wastewater</v>
-      </c>
+      <c r="A18"/>
       <c r="D18" s="5" t="str" cm="1">
         <f t="array" ref="D18">Common_SourceData.Common_SourceData_WASA4Areas_Title()</f>
         <v>ABS Statistcal Areas Level 4 - Western Australia</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="53" t="str">
-        <f>HYPERLINK("#'Constants - Common'!A1", "Constants - Common")</f>
-        <v>Constants - Common</v>
-      </c>
+      <c r="A19"/>
       <c r="D19" s="4" t="str" cm="1">
         <f t="array" ref="D19">Common_SourceData.Common_SourceData_WASA4Areas_Source()</f>
         <v>Australian Bureau of Statistics (ABS) - Statistical Areas Level 2 - 2021 - Shapefile</v>
@@ -13857,7 +14071,7 @@
         <v>kg N2O - N / kg N</v>
       </c>
     </row>
-    <row r="257" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="257" spans="4:6" x14ac:dyDescent="0.25">
       <c r="D257" s="24" t="s">
         <v>77</v>
       </c>
@@ -13865,7 +14079,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="258" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="258" spans="4:6" x14ac:dyDescent="0.25">
       <c r="D258" s="24" t="str" cm="1">
         <f t="array" ref="D258">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data(), Table_SourceData_Common_EFOrganicFertCropResidues[[#Headers],[Climate Zone]], 0)</f>
         <v>Wet climate zone</v>
@@ -13875,7 +14089,7 @@
         <v>6.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="259" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="259" spans="4:6" x14ac:dyDescent="0.25">
       <c r="D259" s="1" t="str" cm="1">
         <f t="array" ref="D259">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data(), Table_SourceData_Common_EFOrganicFertCropResidues[[#Headers],[Climate Zone]], 0)</f>
         <v>Dry climate zone</v>
@@ -13885,10 +14099,299 @@
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
+    <row r="263" spans="4:6" ht="23.25" x14ac:dyDescent="0.25">
+      <c r="D263" s="5" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="264" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D264" s="1" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="265" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D265" s="24" t="s">
+        <v>134</v>
+      </c>
+      <c r="E265" s="24" t="s">
+        <v>135</v>
+      </c>
+      <c r="F265" s="24" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="266" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D266" s="24" t="s">
+        <v>137</v>
+      </c>
+      <c r="E266" s="24" t="s">
+        <v>138</v>
+      </c>
+      <c r="F266" s="24">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="267" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D267" s="24" t="s">
+        <v>139</v>
+      </c>
+      <c r="E267" s="24" t="s">
+        <v>140</v>
+      </c>
+      <c r="F267" s="24">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="268" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D268" s="24" t="s">
+        <v>141</v>
+      </c>
+      <c r="E268" s="24" t="s">
+        <v>142</v>
+      </c>
+      <c r="F268" s="24">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="269" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D269" s="24" t="s">
+        <v>143</v>
+      </c>
+      <c r="E269" s="24" t="s">
+        <v>144</v>
+      </c>
+      <c r="F269" s="24">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="270" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D270" s="24" t="s">
+        <v>145</v>
+      </c>
+      <c r="E270" s="24" t="s">
+        <v>146</v>
+      </c>
+      <c r="F270" s="24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="273" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D273" s="1" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="274" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D274" s="24" t="s">
+        <v>134</v>
+      </c>
+      <c r="E274" s="24" t="s">
+        <v>135</v>
+      </c>
+      <c r="F274" s="24" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="275" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D275" s="24" t="s">
+        <v>148</v>
+      </c>
+      <c r="E275" s="24" t="s">
+        <v>149</v>
+      </c>
+      <c r="F275" s="24">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="276" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D276" s="24" t="s">
+        <v>150</v>
+      </c>
+      <c r="E276" s="24" t="s">
+        <v>151</v>
+      </c>
+      <c r="F276" s="24">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="277" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D277" s="24" t="s">
+        <v>152</v>
+      </c>
+      <c r="E277" s="24" t="s">
+        <v>153</v>
+      </c>
+      <c r="F277" s="24">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="278" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D278" s="24" t="s">
+        <v>154</v>
+      </c>
+      <c r="E278" s="24" t="s">
+        <v>155</v>
+      </c>
+      <c r="F278" s="24">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="279" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D279" s="24" t="s">
+        <v>156</v>
+      </c>
+      <c r="E279" s="24" t="s">
+        <v>157</v>
+      </c>
+      <c r="F279" s="24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="282" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D282" s="1" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="283" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D283" s="24" t="s">
+        <v>134</v>
+      </c>
+      <c r="E283" s="24" t="s">
+        <v>135</v>
+      </c>
+      <c r="F283" s="24" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="284" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D284" s="24" t="s">
+        <v>159</v>
+      </c>
+      <c r="E284" s="24" t="s">
+        <v>160</v>
+      </c>
+      <c r="F284" s="24">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="285" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D285" s="24" t="s">
+        <v>161</v>
+      </c>
+      <c r="E285" s="24" t="s">
+        <v>162</v>
+      </c>
+      <c r="F285" s="24">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="286" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D286" s="24" t="s">
+        <v>163</v>
+      </c>
+      <c r="E286" s="24" t="s">
+        <v>164</v>
+      </c>
+      <c r="F286" s="24">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="287" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D287" s="24" t="s">
+        <v>165</v>
+      </c>
+      <c r="E287" s="24" t="s">
+        <v>166</v>
+      </c>
+      <c r="F287" s="24">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="288" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D288" s="24" t="s">
+        <v>167</v>
+      </c>
+      <c r="E288" s="24" t="s">
+        <v>168</v>
+      </c>
+      <c r="F288" s="24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="291" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D291" s="1" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="292" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D292" s="24" t="s">
+        <v>134</v>
+      </c>
+      <c r="E292" s="24" t="s">
+        <v>135</v>
+      </c>
+      <c r="F292" s="24" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="293" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D293" s="24" t="s">
+        <v>170</v>
+      </c>
+      <c r="E293" s="24" t="s">
+        <v>171</v>
+      </c>
+      <c r="F293" s="24">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="294" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D294" s="24" t="s">
+        <v>172</v>
+      </c>
+      <c r="E294" s="24" t="s">
+        <v>173</v>
+      </c>
+      <c r="F294" s="24">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="295" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D295" s="24" t="s">
+        <v>174</v>
+      </c>
+      <c r="E295" s="24" t="s">
+        <v>175</v>
+      </c>
+      <c r="F295" s="24">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="296" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D296" s="24" t="s">
+        <v>176</v>
+      </c>
+      <c r="E296" s="24" t="s">
+        <v>177</v>
+      </c>
+      <c r="F296" s="24">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="297" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D297" s="24" t="s">
+        <v>178</v>
+      </c>
+      <c r="E297" s="24" t="s">
+        <v>179</v>
+      </c>
+      <c r="F297" s="24">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-  <tableParts count="17">
+  <tableParts count="21">
     <tablePart r:id="rId2"/>
     <tablePart r:id="rId3"/>
     <tablePart r:id="rId4"/>
@@ -13906,11 +14409,35 @@
     <tablePart r:id="rId16"/>
     <tablePart r:id="rId17"/>
     <tablePart r:id="rId18"/>
+    <tablePart r:id="rId19"/>
+    <tablePart r:id="rId20"/>
+    <tablePart r:id="rId21"/>
+    <tablePart r:id="rId22"/>
   </tableParts>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="09eef6d6-daa8-4301-8f9f-b1ec38079286" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7291119c-fce9-4911-96ae-b800be5dccd8">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100ACB660BB23738846A00119B5826AC974" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3e3613359d4ae7f6bda6c57be713f101">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="7291119c-fce9-4911-96ae-b800be5dccd8" xmlns:ns3="09eef6d6-daa8-4301-8f9f-b1ec38079286" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="87491bfad7f11426ad96486e70428b3e" ns2:_="" ns3:_="">
     <xsd:import namespace="7291119c-fce9-4911-96ae-b800be5dccd8"/>
@@ -14105,31 +14632,30 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="09eef6d6-daa8-4301-8f9f-b1ec38079286" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7291119c-fce9-4911-96ae-b800be5dccd8">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
-<AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgAvAC8AIAAtAC0ALQAgAFcAbwByAGsAYgBvAG8AawAgAG0AbwBkAHUAbABlACAALQAtAC0AXABuAC8ALwAgAEEAIABmAGkAbABlACAAbwBmACAAbgBhAG0AZQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAG8AZgAgAHQAaABlACAAZgBvAHIAbQA6AFwAbgAvAC8AIAAgACAAIABuAGEAbQBlACAAPQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AOwBcAG4AXABuACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhACIALAAiAHQAZQB4AHQAIgA6ACIALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgBTAG8AdQByAGMAZQAgAGQAYQB0AGEAIAB0AGgAYQB0ACAAaQBzACAAYwBvAG0AbQBvAG4AIABhAGMAcgBvAHMAcwAgAGEAbABsACAAZQBuAHQAZQByAHAAcgBpAHMAZQAgAHQAeQBwAGUAcwBcAG4ARQB4AGMAZQBsACAAbQBvAGQAdQBsAGUAIABuAGEAbQBlADoAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFMAbwB1AHIAYwBlADoAIABOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQBcAG4ATgBJAFIAXwAyADAAMgAzAF8AVgBvAGwAMQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXABuAHAAIAA9ACAAZABlAG4AcwBpAHQAeQAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAIAAoADAALgA2ADcAOAA0ACAAawBnAC8AbQAzACkAXABuAFQAYQBrAGUAbgAgAGYAcgBvAG0AIAB0AGgAZQAgAE4AYQB0AGkAbwBuAGEAbAAgAEcAcgBlAGUAbgBoAG8AdQBzAGUAIABhAG4AZAAgAEUAbgBlAHIAZwB5ACAAUgBlAHAAbwByAHQAaQBuAGcAIABcAG4AKABNAGUAYQBzAHUAcgBlAG0AZQBuAHQAKQAgAEQAZQB0AGUAcgBtAGkAbgBhAHQAaQBvAG4AIAAyADAAMAA4AFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHAAIAA9ACAAZABlAG4AcwBpAHQAeQAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcALwBtADMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgADIAMAAyADMAIABWAG8AbAB1AG0AZQAgADEAOgAgAEUAcQB1AGEAdABpAG8AbgBzACAAMwAuAEIALgAxAGEAXwAyACwAIAAzAC4AQgAuADEAYwBfADIALAAgADMALgBCAC4AMwBfADEALAAgADMALgBCAC4ANABnAF8AMgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAMAAuADYANwA4ADQAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAFwAbgBDAGcAIAA9ACAANAA0AC8AMgA4ACAAZgBhAGMAdABvAHIAIAB0AG8AIABjAG8AbgB2AGUAcgB0ACAAZQBsAGUAbQBlAG4AdABhAGwAIABtAGEAcwBzACAAbwBmACAATgAyAE8AIAB0AG8AIABtAG8AbABlAGMAdQBsAGEAcgAgAG0AYQBzAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABOADIATwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBDAGcATgAyAE8AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAYQBjAHQAbwByAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgADIAMAAyADMAIABWAG8AbAB1AG0AZQAgADEAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgANAA0AC8AMgA4ACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAFwAbgBGAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABnAGEAcwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgBhAGMAdABvAHIAIAB0AG8AIABjAG8AbgB2AGUAcgB0ACAAZQBsAGUAbQBlAG4AdABhAGwAIABtAGEAcwBzACAAbwBmACAAZwBhAHMAIAB0AG8AIABtAG8AbABlAGMAdQBsAGEAcgAgAG0AYQBzAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBDAGcAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgBhAGMAdABvAHIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFgAWABYAFgAWABYAFgAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADgALAAgADQALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAYQBzAFwAIgAsACAAXAAiAEMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBcACIALAAgAFwAIgBDAG8AbgB2AGUAcgBzAGkAbwBuACAAZgBhAGMAdABvAHIAIAAxAFwAIgAsACAAXAAiAEMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgADIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyAFwAIgAsACAAXAAiADQANAAvADEAMgBcACIALAAgADQANAAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMASAA0AFwAIgAsACAAXAAiADEANgAvADEAMgBcACIALAAgADEANgAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AMgBPAFwAIgAsACAAXAAiADQANAAvADIAOABcACIALAAgADQANAAsACAAMgA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB4AFwAIgAsACAAXAAiADQANgAvADEANABcACIALAAgADQANgAsACAAMQA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwBcACIALAAgAFwAIgAyADgALwAxADIAXAAiACwAIAAyADgALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAE8AMgAgAEwAaQBtAGUAXAAiACwAIABcACIANAA0AC8AMQAyAFwAIgAsACAANAA0ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBNAFYATwBDAFwAIgAsACAAXAAiADEANAAvADEAMgBcACIALAAgADEANAAsACAAMQAyAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABOADIATwBcAG4ARwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAGcAcgBlAGUAbgBoAG8AdQBzAGUAIABnAGEAcwBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABnAHIAZQBlAG4AaABvAHUAcwBlACAAZwBhAHMAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARwBXAFAATgAyAE8AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgBhAGMAdABvAHIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFgAWABYAFgAWABYAFgAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADgALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAYQBzAFwAIgAsACAAXAAiAEMATwAyAC0AZQAgAGYAYQBjAHQAbwByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAE8AMgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBIADQAXAAiACwAIAAyADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgAyAE8AXAAiACwAIAAyADYANQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAEYANABcACIALAAgADYANgAzADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwAyAEYANgBcACIALAAgADEAMgAyADAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAEYANgBcACIALAAgADIAMgA4ADAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAEYAMwBcACIALAAgADEANwAyADAAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAcwB0AGEAdABlAHMAIABhAG4AZAAgAHQAZQByAHIAaQB0AG8AcgBpAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA5ACwAIAAzACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHQAYQB0AGUALwBUAGUAcgByAGkAdABvAHIAeQBcACIALAAgAFwAIgBDAG8AbQBtAG8AbgAgAE4AYQBtAGUAXAAiACwAIABcACIAQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AZQB3ACAAUwBvAHUAdABoACAAVwBhAGwAZQBzAFwAIgAsACAAXAAiAE4AZQB3ACAAUwBvAHUAdABoACAAVwBhAGwAZQBzAFwAIgAsACAAXAAiAE4AUwBXAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAQwBhAHAAaQB0AGEAbAAgAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAEEAQwBUAFwAIgAsACAAXAAiAEEAQwBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAGkAYwB0AG8AcgBpAGEAXAAiACwAIABcACIAVgBpAGMAdABvAHIAaQBhAFwAIgAsACAAXAAiAFYASQBDAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBRAHUAZQBlAG4AcwBsAGEAbgBkAFwAIgAsACAAXAAiAFEAdQBlAGUAbgBzAGwAYQBuAGQAXAAiACwAIABcACIAUQBMAEQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAbwB1AHQAaAAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFMAbwB1AHQAaAAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFMAQQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQBcACIALAAgAFwAIgBXAEEAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAYQBzAG0AYQBuAGkAYQBcACIALAAgAFwAIgBUAGEAcwBtAGEAbgBpAGEAXAAiACwAIABcACIAVABBAFMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwByAHQAaABlAHIAbgAgAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAE4AbwByAHQAaABlAHIAbgAgAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAE4AVABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQBCAFMAIABTAHQAYQB0AGkAcwB0AGMAYQBsACAAQQByAGUAYQBzACAATABlAHYAZQBsACAANAAgAC0AIABXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAEIAdQByAGUAYQB1ACAAbwBmACAAUwB0AGEAdABpAHMAdABpAGMAcwAgACgAQQBCAFMAKQAgAC0AIABTAHQAYQB0AGkAcwB0AGkAYwBhAGwAIABBAHIAZQBhAHMAIABMAGUAdgBlAGwAIAAyACAALQAgADIAMAAyADEAIAAtACAAUwBoAGEAcABlAGYAaQBsAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADEALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAQQAgADQAIABOAGEAbQBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBCAHUAbgBiAHUAcgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAGEAbgBkAHUAcgBhAGgAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABJAG4AbgBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABOAG8AcgB0AGgAIABFAGEAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAATgBvAHIAdABoACAAVwBlAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAFMAbwB1AHQAaAAgAEUAYQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABTAG8AdQB0AGgAIABXAGUAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAAVwBoAGUAYQB0ACAAQgBlAGwAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhACAALQAgAE8AdQB0AGIAYQBjAGsAIAAoAE4AbwByAHQAaAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAATwB1AHQAYgBhAGMAawAgACgAUwBvAHUAdABoACkAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAdwBlAHQAIABhAG4AZAAgAGQAcgB5ACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAyADoAIABUAHIAYQBuAHMAbABhAHQAaQBuAGcAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBzACAAdABvACAAdwBlAHQAIABhAG4AZAAgAGQAcgB5ACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAdwBhAHIAbQAgAC8AIABjAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAvACAAZAByAHkAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAIABhAG4AZAAgAGgAaQBnAGgAIAB0AGUAbQBwACAAYwBsAGEAcwBzAGUAcwAgAHQAbwAgAGEAYwBjAG8AbQBtAG8AZABhAHQAZQAgAGMAbABpAG0AYQB0AGUAIABzAGMAZQBuAGEAcgBpAG8AcwAgAGUAeABjAGwAdQBkAGUAZAAgAGIAeQAgAFYARQBFAFIARwAgAGMAcgBpAHQAZQByAGkAYQAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAGkAeABlAGQAIAB0AHkAcABvACAALQAgAEMAaABhAG4AZwBlAGQAIABcAHUAMAAwADIANwBGAHIAeQBcAHUAMAAwADIANwAgAHQAbwAgAFwAdQAwADAAMgA3AEQAcgB5AFwAdQAwADAAMgA3AC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADUALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAFcAZQB0ACAAbwByACAARAByAHkAIABaAG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABtAG8AbgB0AGEAbgBlAFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAHcAZQB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABkAHIAeQBcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdABcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAtACAAaABpAGcAaAAgAHQAZQBtAHAAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAaABpAGcAaAAgAHQAZQBtAHAAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA1ACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAB3AGEAcgBtACAALwAgAGMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC8AIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdAAgAGEAbgBkACAAaABpAGcAaAAgAHQAZQBtAHAAIABjAGwAYQBzAHMAZQBzACAAdABvACAAYQBjAGMAbwBtAG0AbwBkAGEAdABlACAAYwBsAGkAbQBhAHQAZQAgAHMAYwBlAG4AYQByAGkAbwBzACAAZQB4AGMAbAB1AGQAZQBkACAAYgB5ACAAVgBFAEUAUgBHACAAYwByAGkAdABlAHIAaQBhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAaQB4AGUAZAAgAHQAeQBwAG8AIABpAG4AIABNAEEAVAAgAHYAYQBsAHUAZQAgAGYAbwByACAAdwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAYwBoAGEAbgBnAGUAZAAgADEAMAAgAHQAbwAgADEAMQAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIABtAGkAbgAgAGEAbgBkACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAZgBvAHIAIABNAEEAVAAsACAATQBBAFAALAAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAIABwAGUAcgAgAHkAZQBhAHIALAAgAGUAbABlAHYAYQB0AGkAbwBuACwAIABNAEEAUAA6AFAARQBUACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlAHMAIABmAHIAbwBtACAAcgBlAGEAbAAgAGMAbABpAG0AYQB0AGUAIABkAGEAdABhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAQQBGACAAYQBjAGMAZQBwAHQAcwAgAHIAYQBpAG4AZgBhAGwAbAAgAGEAcwAgAGEAIABwAHIAbwB4AHkAIABmAG8AcgAgAHAAcgBlAGMAaQBwAGkAdABhAHQAaQBvAG4ALgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOQAsACAAMQA2ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAGwAaQBtAGEAdABlACAAWgBvAG4AZQBcACIALAAgAFwAIgBNAEEAVABcACIALAAgAFwAIgBNAEEAUABcACIALAAgAFwAIgBGAHIAbwBzAHQAIABkAGEAeQBzACAAcABlAHIAIAB5AGUAYQByAFwAIgAsACAAXAAiAEUAbABlAHYAYQB0AGkAbwBuAFwAIgAsACAAXAAiAE0AQQBQADoAUABFAFQAXAAiACwAIABcACIATQBpAG4AIAB0AGUAbQBwAFwAIgAsACAAXAAiAE0AYQB4ACAAdABlAG0AcABcACIALAAgAFwAIgBNAGkAbgAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBNAGEAeAAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBNAGkAbgAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAXAAiACwAIABcACIATQBhAHgAIABmAHIAbwBzAHQAIABkAGEAeQBzAFwAIgAsACAAXAAiAE0AaQBuACAAZQBsAGUAdgBhAHQAaQBvAG4AXAAiACwAIABcACIATQBhAHgAIABlAGwAZQB2AGEAdABpAG8AbgBcACIALAAgAFwAIgBNAGkAbgAgAE0AQQBQADoAUABFAFQAXAAiACwAIABcACIATQBpAG4AIABNAEEAUAA6AFAARQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABtAG8AbgB0AGEAbgBlAFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQA4ACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAwADAAIABtAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAMQA4AC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAANwAsACAAMQAwADAAMAAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAHcAZQB0AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQA4ACAAQwBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADIAMAAwADAAIABtAG0AXAAiACwAIABcACIAZCIgADcAXAAiACwAIABcACIAZCIgADEAMAAwADAAIABtAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAMQA4AC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAyADAAMAAwAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQAuADkAOQA5ACwAIAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAOAAgAEMAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADAAMAAwACAAbQBtACAALQAgAGQiIAAyADAAMAAwACAAbQBtAFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgADEAOAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAAMQAwADAAMAAuADAAMAAxACwAIAAyADAAMAAwACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQAuADkAOQA5ACwAIAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAGQAcgB5AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQA4ACAAQwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAwADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAXAAiACwAIAAxADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgADEALgAwADAAMQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAGQiIAAxAFwAIgAsACAAMQAwAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAgAC0AOQA5ADkAOQA5ADkALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMAAgAEMAIAAtACAAZCIgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxAFwAIgAsACAALQA5ADkAOQA5ADkAOQAsACAAMQAwACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAxAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMAAgAEMAIAAtACAAZCIgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAZCIgADEAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAMQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBBAHAAcABlAG4AZABpAGMAZQBzAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdABlADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AQQBUACAAPQAgAG0AZQBhAG4AIABhAG4AbgB1AGEAbAAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBBAFAAIAA9ACAAbQBlAGEAbgAgAGEAbgBuAHUAYQBsACAAcAByAGUAYwBpAHAAaQB0AGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABFAFQAIAA9ACAAcABvAHQAZQBuAHQAaQBhAGwAIABlAHYAYQBwAG8AdAByAGEAbgBzAHAAaQByAGEAdABpAG8AbgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABBAGQAZABlAGQAIABlAHgAdAByAGEAIABNAEEAVAAgAG0AaQBuACAAYQBuAGQAIABNAEEAVAAgAG0AYQB4ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGMAYQBsAGMAdQBsAGEAdABlACAAegBvAG4AZQAgAGYAcgBvAG0AIAByAGUAYQBsACAAdABlAG0AcABlAHIAYQB0AHUAcgBlACAAZABhAHQAYQAuAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANAAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AHUAcgBlACAAWgBvAG4AZQBcACIALAAgAFwAIgBNAGUAZABpAGEAbgAgAEEAbgBuAHUAYQBsACAAVABlAG0AcABlAHIAYQB0AHUAcgBlACAAKABNAEEAVAApAFwAIgAsACAAXAAiAE0AaQBuACAATQBBAFQAXAAiACwAIABcACIATQBhAHgAIABNAEEAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgAFwAIgBlIiAAMgA2ACAAQwBcACIALAAgADIANgAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIABcACIAMQA1ACAALQAgADIANQAgAEMAXAAiACwAIAAxADUALAAgADIANQAuADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIABcACIAZCIgADEANAAgAEMAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADQALgA5ADkAOQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAAQQBkAGQAZQBkACAAZQB4AHQAcgBhACAAUgBhAGkAbgBmAGEAbABsACAAbQBpAG4AIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAG0AYQB4ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGMAYQBsAGMAdQBsAGEAdABlACAAegBvAG4AZQAgAGYAcgBvAG0AIAByAGUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAZABhAHQAYQAuAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBhAGkAbgBmAGEAbABsACAAWgBvAG4AZQBcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABtAGkAbgBcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABtAGEAeABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbAAgAFwAdQAwADAAMwBlACAANgAwADAAbQBtAFwAIgAsACAANgAwADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATABvAHcAIAByAGEAaQBuAGYAYQBsAGwAXAAiACwAIABcACIAQQBuAG4AdQBhAGwAIAByAGEAaQBuAGYAYQBsAGwAIABkIiAANgAwADAAbQBtAFwAIgAsACAALQA5ADkAOQA5ADkAOQAsACAANgAwADAAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABaAG8AbgBlAFwAIgAsACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAGMAcgBpAHQAZQByAGkAYQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATABlAGEAYwBoAGkAbgBnACAAbwBjAGMAdQByAHMAXAAiACwAIABcACIAowMoADXYX9w12E7cNdhW3DXYW9wpAFwAdQAwADAAMwBlAKMDKAA12DjcNdhH3DAAKQArADXYYNw12FzcNdhW3DXYWdwgADXYZNw12E7cNdhh3DXYUtw12F/cIAAOITXYXNw12FncNdhR3DXYVtw12FvcNdhU3CAANdhQ3DXYTtw12F3cNdhO3DXYUNw12FbcNdhh3DXYZtxcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATABlAGEAYwBoAGkAbgBnACAAZABvAGUAcwAgAG4AbwB0ACAAbwBjAGMAdQByAFwAIgAsACAAXAAiAKMDKAA12F/cNdhO3DXYVtw12FvcKQBkIqMDKAA12DjcNdhH3DAAKQArADXYYNw12FzcNdhW3DXYWdwgADXYZNw12E7cNdhh3DXYUtw12F/cIAAOITXYXNw12FncNdhR3DXYVtw12FvcNdhU3CAANdhQ3DXYTtw12F3cNdhO3DXYUNw12FbcNdhh3DXYZtxcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXABuADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAbgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAEQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcwAgAGkAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAXAAiACwAXAAiAEYAcgBhAGMAVwBFAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFkAZQBzACAALQAgAGkAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwAgAC0AIABuAG8AdAAgAGkAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAXAAiACwAIAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoACgAXAAiAFwAIgApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAGQAYQB0AGEAIABzAGMAbwByAGUAcwAgAGYAbwByACAAcwBjAG8AcABlACAAMwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABYAFgAWABYAFgAWABYAFgAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABhAHQAYQAgAHMAbwB1AHIAYwBlAFwAIgAsACAAXAAiAEQAYQB0AGEAIABzAGMAbwByAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAbgB0AGUAcgBuAGEAdABpAG8AbgBhAGwAIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAcwBjAG8AcABlACAAMwAgAGQAYQB0AGEAYgBhAHMAZQBcACIALAAgADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB0AGEAdABlACAAbwByACAAcgBlAGcAaQBvAG4AYQBsACAAcwBjAG8AcABlACAAMwAgAGQAYQB0AGEAYgBhAHMAZQBcACIALAAgADMAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBtAGkAcwBzAGkAbwBuAHMAIABpAG4AdABlAG4AcwBpAHQAeQAgAGMAYQBsAGMAdQBsAGEAdABlAGQAIABmAHIAbwBtACAAYQBwAHAAcgBvAHYAZQBkACAAbQBlAHQAaABvAGQAXAAiACwAIAA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAZQByAGkAZgBpAGUAZAAgAGMAcgBlAGQAZQBuAHQAaQBhAGwAIABtAGEAdABjAGgAaQBuAGcAIABJAFMATwAxADQAMAA2ADcAXAAiACwAIAA1AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXABuADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAbgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgARABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAVgBvAGwAdQBtAGUAIAAxADoAIABMAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmACAAKAAzAC4ARAAuAGIALgAyACkAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAcgBhAGMATABFAEEAQwBIAFwAIgAsADAALgAyADQAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoACgAXAAiAFwAIgApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABuAGkAdAByAG8AZwBlAG4AIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABuAGkAdAByAG8AZwBlAG4AIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABrAGcAIABOADIATwAtAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgAFYAbwBsAHUAbQBlACAAMQA6ACAARQBxAHUAYQB0AGkAbwBuACAAMwAuAEQALgBCAF8AMQAwAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARgBsAGUAYQBjAGgAXAAiACwAMAAuADAAMQAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoACgAXAAiAFwAIgApACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXABuAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADEAXABuAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAZgBvAHIAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AIAAoAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AKQAgACgARQBGAE4AMgBPACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAGYAbwByACAAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAGsAZwAgAE4AMgBPAC0ATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADIALgAyAC4AMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQA1ACwAIAA1ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABqAFwAIgAsAFwAIgBFAEYATgAyAE8AXAAiACwAIABcACIAUAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAbwBuAGwAeQBcACIALAAgAFwAIgBJAHIAcgBpAGcAYQB0AGkAbwBuACAAbQBlAHQAaABvAGQAXAAiACwAIABcACIAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsADAALgAwADAANQA5ACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwAFwAIgAsADAALgAwADAANwAsACAAXAAiAEMAcgBvAHAAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsADAALgAwADAAMQA4ACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEwAbwB3ACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQBcACIALAAwAC4AMAAwADEAOAAsACAAXAAiAFAAYQBzAHQAdQByAGUAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcAAgACgAbABvAHcAIAByAGEAaQBuAGYAYQBsAGwAKQBcACIALAAwAC4AMAAwADIAOQAsACAAXAAiAEMAcgBvAHAAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAGMAcgBvAHAAIAAoAGgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAKQBcACIALAAwAC4AMAAwADgALAAgAFwAIgBDAHIAbwBwAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIASABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB1AGcAYQByAFwAIgAsADAALgAwADEAOQA5ACwAIABcACIAUwB1AGcAYQByAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AdAB0AG8AbgBcACIALAAwAC4AMAAwADUAMwAsACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAG8AcgB0AGkAYwB1AGwAdAB1AHIAYQBsACAAYwByAG8AcABzAFwAIgAsADAALgAwADAANgA0ACwAIABcACIASABvAHIAdABpAGMAdQBsAHQAdQByAGEAbAAgAGMAcgBvAHAAcwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBpAGMAZQAgACgAYwBvAG4AdABpAG4AdQBvAHUAcwAgAGYAbABvAG8AZABpAG4AZwApAFwAIgAsADAALgAwADAAMwAsACAAXAAiAFIAaQBjAGUAXAAiACwAIABcACIAQwBvAG4AdABpAG4AdQBvAHUAcwAgAGYAbABvAG8AZABpAG4AZwBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBpAGMAZQAgACgAcwBpAG4AZwBsAGUAIABhAG4AZAAgAG0AdQBsAHQAaQBwAGwAZQAgAGQAcgBhAGkAbgBhAGcAZQAsACAAbwByACAAYQBsAHQAZQByAG4AYQB0AGUAIAB3AGUAdAB0AGkAbgBnACAAYQBuAGQAIABkAHIAeQBpAG4AZwApAFwAIgAsADAALgAwADAANQAsACAAXAAiAFIAaQBjAGUAXAAiACwAIABcACIAUwBpAG4AZwBsAGUAIABhAG4AZAAgAG0AdQBsAHQAaQBwAGwAZQAgAGQAcgBhAGkAbgBhAGcAZQAsACAAbwByACAAYQBsAHQAZQByAG4AYQB0AGUAIAB3AGUAdAB0AGkAbgBnACAAYQBuAGQAIABkAHIAeQBpAG4AZwBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBxAHUAYQBjAHUAbAB0AHUAcgBlAFwAIgAsADAALgAwADAAMgA2ACwAIABcACIAQQBxAHUAYQBjAHUAbAB0AHUAcgBlAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAG8AcgBlAHMAdAByAHkAXAAiACwAMAAuADAAMAAxADgALAAgAFwAIgBGAG8AcgBlAHMAdAByAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA1ACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGUAbQBvAHYAZQBkACAAZAB1AHAAbABpAGMAYQB0AGUAIABcAHUAMAAwADIANwBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAB1ADAAMAAyADcAIAByAG8AdwAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGUAbQBvAHYAZQBkACAAYQBzAHQAZQByAGkAcwBrAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAFwAdQAwADAAMgA3AHAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAG8AbgBsAHkAXAB1ADAAMAAyADcALAAgAFwAdQAwADAAMgA3AHIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAXAB1ADAAMAAyADcAIABhAG4AZAAgAFwAdQAwADAAMgA3AGkAcgByAGkAZwBhAHQAaQBvAG4AIABtAGUAdABoAG8AZABcAHUAMAAwADIANwAgAGMAbwBsAHUAbQBuAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAdQBwAGwAaQBjAGEAdABlAGQAIABcAHUAMAAwADIANwBuAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQBcAHUAMAAwADIANwAgAHIAbwB3ACAAdwBpAHQAaAAgAHMAYQBtAGUAIABFAEYAIABmAG8AcgAgAGwAbwB3ACAAYQBuAGQAIABoAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAFwAbgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABDAGgAYQBwAHQAZQByACAAMQAsACAAcwBlAGMAdABpAG8AbgAgADEALgA4AC4AMgAgAEwAZQBhAGMAaABpAG4AZwAsACAAYwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBzAFwAbgBJAFAAQwBDADoAIABOADIATwAgAEUATQBJAFMAUwBJAE8ATgBTACAARgBSAE8ATQAgAE0AQQBOAEEARwBFAEQAIABTAE8ASQBMAFMALAAgAEEATgBEACAAQwBPADIAIABFAE0ASQBTAFMASQBPAE4AUwAgAEYAUgBPAE0AIABMAEkATQBFACAAQQBOAEQAIABVAFIARQBBACAAQQBQAFAATABJAEMAQQBUAEkATwBOAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwBXAEUAVAAgAGYAbwByACAAaQByAHIAaQBnAGEAdABpAG8AbgAgAHQAeQBwAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAEMAaABhAHAAdABlAHIAIAAxACwAIABzAGUAYwB0AGkAbwBuACAAMQAuADgALgAyACAATABlAGEAYwBoAGkAbgBnACwAIABjAGwAaQBtAGEAdABlACAAYQBuAGQAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBJAFAAQwBDACAAMgAwADEAOQAgAFIAZQBmAGkAbgBlAG0AZQBuAHQAIABWAG8AbAB1AG0AZQAgADQAOgAgAEMAaABhAHAAdABlAHIAIAAxADEAOgAgAE4AMgBPACAARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAATQBhAG4AYQBnAGUAZAAgAFMAbwBpAGwAcwAsACAAYQBuAGQAIABDAE8AMgAgAEUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAEwAaQBtAGUAIABhAG4AZAAgAFUAcgBlAGEAIABBAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGkAbwBuACAAdAB5AHAAZQAgAGkAcgBcACIALABcACIARgByAGEAYwBXAEUAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAByAGkAcAAgAGkAcgByAGkAZwBhAHQAaQBvAG4AXAAiACwAIAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAcAByAGkAbgBrAGwAZQByACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB1AHIAZgBhAGMAZQAgAGkAcgByAGkAZwBhAHQAaQBvAG4AXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AdABoAGUAcgAgAGkAcgByAGkAZwBhAHQAaQBvAG4AXAAiACwAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAARgBSAE8ATQAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAAVABhAGIAbABlACAAYwByAGUAYQB0AGUAZAAgAGIAYQBzAGUAZAAgAG8AbgAgAFYARQBFAFIARwAgAHQAZQB4AHQAIABcAHUAMAAwADIANwBBAHIAZQBhAHMAIABhAHIAZQAgAHMAdQBiAGoAZQBjAHQAIAB0AG8AIABsAGUAYQBjAGgAaQBuAGcAIAAoAGkALgBlAC4ALAAgAGkAbgAgAHQAaABlACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQApACAAdwBoAGUAbgAuAC4ALgAgAHQAaABlACAAbABhAG4AZAAgAGkAcwAgAGkAcgByAGkAZwBhAHQAZQBkACAAKABlAHgAYwBlAHAAdAAgAGQAcgBpAHAAIABpAHIAcgBpAGcAYQB0AGkAbwBuACkALgBcAHUAMAAwADIANwBcACIAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAFwAbgBUAGEAYgBsAGUAIABBAC4AMgAuADIALgAyADoAIABFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAdQByAGkAbgBlACAAYQBuAGQAIABkAHUAbgBnACAAZABlAHAAbwBzAGkAdABlAGQAIABvAG4AIABwAGEAcwB0AHUAcgBlACwAIAByAGEAbgBnAGUAIABvAHIAIABwAGEAZABkAG8AYwBrACAAKABrAGcAIABOADIATwAtAE4ALwBrAGcAIABOACkAIAAoAEUARgBQAFIAUAApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAdQByAGkAbgBlACAAYQBuAGQAIABkAHUAbgBnACAAZABlAHAAbwBzAGkAdABlAGQAIABvAG4AIABwAGEAcwB0AHUAcgBlACwAIAByAGEAbgBnAGUAIABvAHIAIABwAGEAZABkAG8AYwBrAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AMgBPACAALQAgAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADIALgAyAC4AMgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAEUARgBQAFIAUABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAAyAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABDAGgAYQBuAGcAZQBkACAAXAB1ADAAMAAyADcARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBzAFwAdQAwADAAMgA3ACAAdABvACAAcwBpAG4AZwB1AGwAYQByACAAXAB1ADAAMAAyADcARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcAHUAMAAwADIANwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAG8AbgB0AGgAcwAgAHQAbwAgAFMAZQBhAHMAbwBuAHMAIABNAGEAcABwAGkAbgBnAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBvAG4AdABoAFwAIgAsACAAXAAiAFMAZQBhAHMAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAGEAbgB1AGEAcgB5AFwAIgAsACAAXAAiAFMAdQBtAG0AZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAGUAYgByAHUAYQByAHkAXAAiACwAIABcACIAUwB1AG0AbQBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQByAGMAaABcACIALAAgAFwAIgBBAHUAdAB1AG0AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBwAHIAaQBsAFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAGEAeQBcACIALAAgAFwAIgBBAHUAdAB1AG0AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASgB1AG4AZQBcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASgB1AGwAeQBcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQB1AGcAdQBzAHQAXAAiACwAIABcACIAVwBpAG4AdABlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAZQBwAHQAZQBtAGIAZQByAFwAIgAsACAAXAAiAFMAcAByAGkAbgBnAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBPAGMAdABvAGIAZQByAFwAIgAsACAAXAAiAFMAcAByAGkAbgBnAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdgBlAG0AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAZQBjAGUAbQBiAGUAcgBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBhAG4AdQByAGUAIABNAGEAbgBhAGcAZQBtAGUAbgB0ACAAEyAgAE0AZQB0AGgAYQBuAGUAIABjAG8AbgB2AGUAcgBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABwAGUAcgAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAIAAoAGYAcgBhAGMAdABpAG8AbgApACAAKABNAEMARgBpAG0AKQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAxAC4AOAAuADEAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIAMgAsACAAMQA2ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAE0AQQBUACAAKAC6AEMAKQBcACIALAAgAFwAIgBVAG4AYwBvAHYAZQByAGUAZAAgAGEAbgBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuAFwAIgAsACAAXAAiAEMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBcACIALAAgAFwAIgBMAGkAcQB1AGkAZAAgAFMAbAB1AHIAcgB5ACAAKAB3AGkAdABoAG8AdQB0ACAAbgBhAHQAdQByAGEAbAAgAGMAcgB1AHMAdAApAFwAIgAsACAAXAAiAEQAYQBpAGwAeQAgAHMAcAByAGUAYQBkACAAKABiACkAXAAiACwAIABcACIAQwBvAG0AcABvAHMAdABpAG4AZwAgACgAcABhAHMAcwBpAHYAZQAgAHcAaQBuAGQAcgBvAHcAKQBcACIALAAgAFwAIgBTAG8AbABpAGQAIABTAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAFAAaQB0ACAAUwB0AG8AcgBhAGcAZQAgAFwAdQAwADAAMwBjADEAIABtAG8AbgB0AGgAXAAiACwAIABcACIARABlAGUAcAAgAEwAaQB0AHQAZQByAFwAIgAsACAAXAAiAFAAbwB1AGwAdAByAHkAIABNAGEAbgB1AHIAZQAgACgAdwBpAHQAaAAvAHcAaQB0AGgAbwB1AHQAIABsAGkAdAB0AGUAcgApAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAcAByAG8AYwBlAHMAcwBpAG4AZwAgAGkAbgB0AG8AIABwAGUAbABsAGUAdABpAHoAZQBkACAAZgBlAHIAdABpAGwAaQBzAGUAcgBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgAgAHQAbwAgAHMAbwBpAGwAXAAiACwAIABcACIAUABhAHMAdAB1AHIAZQAsACAAUgBhAG4AZwBlACAAYQBuAGQAIABQAGEAZABkAG8AYwBrACAAKABjACkAKABkACkAXAAiACwAIABcACIATQBBAFQAIAByAGEAdwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgAFwAIgBkIjEAMABcACIALAAgADAALgA2ADYALAAgADAALgAxACwAIAAwAC4AMQAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIAAxADEALAAgADAALgA2ADgALAAgADAALgAxACwAIAAwAC4AMQAxACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgADEAMgAsACAAMAAuADcALAAgADAALgAxACwAIAAwAC4AMQAzACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgADEAMwAsACAAMAAuADcAMQAsACAAMAAuADEALAAgADAALgAxADQALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQA0ACwAIAAwAC4ANwAzACwAIAAwAC4AMQAsACAAMAAuADEANQAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA1ACwAIAAwAC4ANwA0ACwAIAAwAC4AMQAsACAAMAAuADEANwAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEANQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEANgAsACAAMAAuADcANQAsACAAMAAuADEALAAgADAALgAxADgALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADcALAAgADAALgA3ADYALAAgADAALgAxACwAIAAwAC4AMgAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEANwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEAOAAsACAAMAAuADcANwAsACAAMAAuADEALAAgADAALgAyADIALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADkALAAgADAALgA3ADcALAAgADAALgAxACwAIAAwAC4AMgA0ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgAwACwAIAAwAC4ANwA4ACwAIAAwAC4AMQAsACAAMAAuADIANgAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIAMQAsACAAMAAuADcAOAAsACAAMAAuADEALAAgADAALgAyADkALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADIALAAgADAALgA3ADgALAAgADAALgAxACwAIAAwAC4AMwAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgAzACwAIAAwAC4ANwA5ACwAIAAwAC4AMQAsACAAMAAuADMANAAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIANAAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgAzADcALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADUALAAgADAALgA3ADkALAAgADAALgAxACwAIAAwAC4ANAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AXAAiACwAIAAyADYALAAgADAALgA3ADkALAAgADAALgAxACwAIAAwAC4ANAA0ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AXAAiACwAIAAyADcALAAgADAALgA4ACwAIAAwAC4AMQAsACAAMAAuADQAOAAsACAAMAAuADAAMQAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIANwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtAFwAIgAsACAAXAAiAGUiMgA4AFwAIgAsACAAMAAuADgALAAgADAALgAxACwAIAAwAC4ANQAsACAAMAAuADAAMQAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBBAG4AYQBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuAFwAIgAsACAAXAAiAEQAaQBnAGUAcwB0AGUAcgAgAC8AIABjAG8AdgBlAHIAZQBkACAAbABhAGcAbwBvAG4AcwBcACIALAAgAFwAIgBMAGkAcQB1AGkAZAAgAHMAeQBzAHQAZQBtAHMAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAXAAiACwAIABcACIAQwBvAG0AcABvAHMAdABpAG4AZwAgACgAcABhAHMAcwBpAHYAZQAgAHcAaQBuAGQAcgBvAHcAKQBcACIALAAgAFwAIgBTAG8AbABpAGQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAFAAaQB0ACAAcwB0AG8AcgBhAGcAZQBcACIALAAgAFwAIgBEAGUAZQBwACAAbABpAHQAdABlAHIAXAAiACwAIABcACIAUABvAHUAbAB0AHIAeQAgAG0AYQBuAHUAcgBlACAAdwBpAHQAaAAgAGIAZQBkAGQAaQBuAGcAXAAiACwAIABcACIAUABvAHUAbAB0AHIAeQAgAG0AYQBuAHUAcgBlACAAdwBpAHQAaABvAHUAdAAgAGIAZQBkAGQAaQBuAGcAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABwAHIAbwBjAGUAcwBzAGkAbgBnAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuAFwAIgAsACAAXAAiAFAAYQBzAHQAdQByAGUAIAByAGEAbgBnAGUAIABhAG4AZAAgAHAAYQBkAGQAbwBjAGsAXAAiACwAIABcACIATQBBAFQAIAByAGEAdwBcACIAIABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAOgAgAEEAZABkAGUAZAAgAHIAbwB3ACAAbwBmACAATgBJAFIAIABNAE0AQQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgAgAEQAdQBwAGwAaQBjAGEAdABlAGQAIABcAHUAMAAwADIANwBQAG8AdQBsAHQAcgB5ACAAdwBpAHQAaAAgAGEAbgBkACAAdwBpAHQAaABvAHUAdAAgAGwAaQB0AHQAZQByAFwAdQAwADAAMgA3ACAAYwBvAGwAdQBtAG4AIAB3AGkAdABoACAAcwBlAHAAYQByAGEAdABlACAATgBJAFIAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AIABBAGQAZABlAGQAIABcAHUAMAAwADIANwBNAEEAVAAgAHIAYQB3AFwAdQAwADAAMgA3ACAAYwBvAGwAdQBtAG4AIAB0AG8AIABhAGwAbABvAHcAIABsAG8AbwBrAHUAcAAgAG8AZgAgAG4AdQBtAGIAZQByAHMALgBcACIAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAbgBkACAAYwByAG8AcAAgAHIAZQBzAGkAZAB1AGUAcwAgAHIAZQB0AHUAcgBuAGUAZAAgAHQAbwAgAHQAaABlACAAcwBvAGkAbABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBGAE4AaQAgAFwAdQAwADAAMgA2ACAARQBGAE4AMgBPAGkAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABOADIATwAgAC0AIABOACAALwAgAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADIALgAxAC4ANABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgAFwAIgBFAEYATgBpACAAXAB1ADAAMAAyADYAIABFAEYATgAyAE8AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIAAwAC4AMAAwADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAANQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIAXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBcAG4AQwBvAG4AdgBlAHIAdAAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcAG4ARQBOADIATwAgAEMATwAyAGUAXABuAHQAIABDAE8AMgBlAFwAbgBFAE4AMgBPADoAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAAoAHQAIABOADIATwApAFwAbgBHAFcAUABOADIATwA6ACAAZwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIAAoAHQAIABDAE8AMgAtAGUAIAAvACAAdAAgAE4AMgBPACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABFAF8ATgAyAE8ALAAgAEcAVwBQAF8ATgAyAE8ALABcAG4AIAAgACAAIABFAF8ATgAyAE8AIAAqACAARwBXAFAAXwBOADIATwBcAG4AIAAgACkAXABuADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAbwBuAHYAZQByAHQAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAB0AG8AIABjAGEAcgBiAG8AbgAgAGQAaQBvAHgAaQBkAGUAIABlAHEAdQBpAHYAYQBsAGUAbgB0ACAAZQBtAGkAcwBzAGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBOADIATwAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAE8AMgBlAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMATwAyAF8AZQAgAD0AIABFAF8AewBOADIATwB9ACAAXABcAHQAaQBtAGUAcwAgAEcAVwBQAF8AewBOADIATwB9AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUATgAyAE8AXAAiACwAXAAiAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAE4AMgBPACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAVwBQAE4AMgBPAFwAIgAsAFwAIgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAATgAyAE8AKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBcAG4AQwBvAG4AdgBlAHIAdAAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcAG4ARQBDAEgANAAgAEMATwAyAGUAXABuAHQAIABDAE8AMgBlAFwAbgBFAEMASAA0ADoAIABtAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAAoAHQAIABDAEgANAApAFwAbgBHAFcAUABDAEgANAA6ACAAZwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAG0AZQB0AGgAYQBuAGUAIAAoAHQAIABDAE8AMgAtAGUAIAAvACAAdAAgAEMASAA0ACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABFAF8AQwBIADQALAAgAEcAVwBQAF8AQwBIADQALABcAG4AIAAgACAAIABFAF8AQwBIADQAIAAqACAARwBXAFAAXwBDAEgANABcAG4AIAAgACkAXABuADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAbwBuAHYAZQByAHQAIABtAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAB0AG8AIABjAGEAcgBiAG8AbgAgAGQAaQBvAHgAaQBkAGUAIABlAHEAdQBpAHYAYQBsAGUAbgB0ACAAZQBtAGkAcwBzAGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBDAEgANAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAE8AMgBlAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMATwAyAF8AZQAgAD0AIABFAF8AewBDAEgANAB9ACAAXABcAHQAaQBtAGUAcwAgAEcAVwBQAF8AewBDAEgANAB9AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUAQwBIADQAXAAiACwAXAAiAE0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAEMASAA0ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAVwBQAEMASAA0AFwAIgAsAFwAIgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbQBlAHQAaABhAG4AZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAAQwBIADQAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIAVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAUgBvAHcAUwB0AGEAcgB0AE4AdQBtAGIAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwALABSAG8AdwBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAYQBuAGQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAUgBPAFcAKABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAApACAAKwAgAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkAIAAtACAAMQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABUAGEAYgBsAGUASABlAGEAZABlAHIAQwBlAGwAbAAsAFwAbgAgACAAQwBPAEwAVQBNAE4AKABUAGEAYgBsAGUASABlAGEAZABlAHIAQwBlAGwAbAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBBAHIAcgBhAHkASQBuAFQAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgAEEAcgByAGEAeQBEAGEAdABhACwAIABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQAsACAAWwBDAG8AbAB1AG0AbgBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAQQBuAGQAQQByAHIAYQB5AF0ALABcAG4AIABJAEYARQBSAFIATwBSACgAXABuACAAIAAgACAAIABJAE4ARABFAFgAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAVQBOAEkAUQBVAEUAKABBAHIAcgBhAHkARABhAHQAYQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBPAFcAKAApAC0AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAUgBvAHcAUwB0AGEAcgB0AE4AdQBtAGIAZQByACgAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwALAAgAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEMATwBMAFUATQBOACgAKQAtAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAEMAbwBsAHUAbQBuAFMAdABhAHIAdABOAHUAbQBiAGUAcgAoAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACkAIAArAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAEMAbwBsAHUAbQBuAHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBBAG4AZABBAHIAcgBhAHkAKQAsACAAMQAsACAAQwBvAGwAdQBtAG4AcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAEEAbgBkAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACAAIAAgACAAKQAsACAAXAAiAFwAIgBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFwAIgBcACIAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEkARgAoAEkAUwBOAFUATQBCAEUAUgAoAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFwAIgBcACIAKQBcAG4AIAAgACAAIAApACwAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApACwAIAAwACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBUAHcAbwBDAG8AbAB1AG0AbgBzAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlADEALAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADIALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAWwBWAGEAbAB1AGUASQBGAEYAYQBsAHMAZQBdACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoADEALAAgACgATABvAG8AawB1AHAAQQByAHIAYQB5ADEAPQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQApACoAKABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABWAGEAbAB1AGUASQBGAEYAYQBsAHMAZQApACwAIABcACIAXAAiACwAIABWAGEAbAB1AGUASQBGAEYAYQBsAHMAZQApACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBPAG4AZQBDAG8AbAB1AG0AbgBBAG4AZABIAGUAYQBkAGUAcgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACwAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMgAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADEALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFsAVgBhAGwAdQBlAEkAZgBGAGEAbABzAGUAXQAsAFwAbgAgACAAIAAgAEkARgBFAFIAUgBPAFIAKABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADEALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACkAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAFYAYQBsAHUAZQBJAGYARgBhAGwAcwBlACkALAAgAFwAIgBcACIALAAgAFYAYQBsAHUAZQBJAGYARgBhAGwAcwBlACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAcABsAGkAdABTAHQAcgBpAG4AZwBJAG4AdABvAEEAcgByAGEAeQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEMAZQBsAGwALAAgAEQAZQBsAGkAbQBpAHQAZQByACwAIABbAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAxAF0ALAAgAFsAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADIAXQAsAFwAbgAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAWABNAEwAKABcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBcAHUAMAAwADMAYwB0AFwAdQAwADAAMwBlAFwAdQAwADAAMwBjAHMAXAB1ADAAMAAzAGUAXAAiACAAXAB1ADAAMAAyADYAXABuACAAIAAgACAAIAAgACAAIABTAFUAQgBTAFQASQBUAFUAVABFACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFMAVQBCAFMAVABJAFQAVQBUAEUAKABTAFUAQgBTAFQASQBUAFUAVABFACgAQwBlAGwAbAAsAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAxACwAXAAiAFwAIgApACwAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADIALABcACIAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAARABlAGwAaQBtAGkAdABlAHIALABcACIAXAB1ADAAMAAzAGMALwBzAFwAdQAwADAAMwBlAFwAdQAwADAAMwBjAHMAXAB1ADAAMAAzAGUAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAKQAgAFwAdQAwADAAMgA2AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFwAdQAwADAAMwBjAC8AcwBcAHUAMAAwADMAZQBcAHUAMAAwADMAYwAvAHQAXAB1ADAAMAAzAGUAXAAiACwAXABuACAAIAAgACAAIAAgACAAIABcACIALwAvAHMAXAAiAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABDAGwAaQBtAGEAdABlAFoAbwBuAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABhAHYAZwBUAGUAbQBwACwAYQB2AGcAUgBhAGkAbgAsAGYAcgBvAHMAdABEAGEAeQBzACwAZQBsAGUAdgAsAG0AYQBwAF8AcABlAHQALABcAG4AIAAgACAAIABtAGkAbgBUAGUAbQBwAEEAcgByAGEAeQAsAG0AYQB4AFQAZQBtAHAAQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4AUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQAsAG0AYQB4AFIAYQBpAG4AZgBhAGwAbABBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBGAHIAbwBzAHQAQQByAHIAYQB5ACwAbQBhAHgARgByAG8AcwB0AEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAEUAbABlAHYAYQB0AGkAbwBuAEEAcgByAGEAeQAsAG0AYQB4AEUAbABlAHYAYQB0AGkAbwBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAFAARQBUAEEAcgByAGEAeQAsAG0AYQB4AFAARQBUAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAGMAbABpAG0AYQB0AGUAWgBvAG4AZQBBAHIAcgBhAHkALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAbQBhAHMAawAsAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBUAGUAbQBwAEEAcgByAGEAeQApAFwAdQAwADAAMwBjAD0AYQB2AGcAVABlAG0AcAApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AFQAZQBtAHAAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBhAHYAZwBUAGUAbQBwACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4AUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQApAFwAdQAwADAAMwBjAD0AYQB2AGcAUgBhAGkAbgApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AFIAYQBpAG4AZgBhAGwAbABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGEAdgBnAFIAYQBpAG4AKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBGAHIAbwBzAHQAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBmAHIAbwBzAHQARABhAHkAcwApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AEYAcgBvAHMAdABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGYAcgBvAHMAdABEAGEAeQBzACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4ARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBlAGwAZQB2ACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBlAGwAZQB2ACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4AUABFAFQAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBtAGEAcABfAHAAZQB0ACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgAUABFAFQAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBtAGEAcABfAHAAZQB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAFQAQQBLAEUAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAKABjAGwAaQBtAGEAdABlAFoAbwBuAGUAQQByAHIAYQB5ACwAbQBhAHMAawAsACAAXAAiAE4AbwAgAG0AYQB0AGMAaABcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAASQB0AGUAbQBGAHIAbwBtAE0AaQBuAE0AYQB4AFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABNAGkAbgBBAHIAcgBhAHkALAAgAE0AYQB4AEEAcgByAGEAeQAsACAASQB0AGUAbQBBAHIAcgBhAHkALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAbQBhAHMAawAsAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABNAGkAbgBBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAE0AYQB4AEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0ATABvAG8AawB1AHAAVgBhAGwAdQBlACkALABcAG4AIAAgACAAIAAgACAAIAAgAEYASQBMAFQARQBSACgASQB0AGUAbQBBAHIAcgBhAHkALAAgAG0AYQBzAGsALAAgAFwAIgBOAG8AIABtAGEAdABjAGgAXAAiACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBTAHUAbQBRAHUAYQBuAHQAaQB0AHkARgByAG8AbQBDAHIAaQB0AGUAcgBpAGEAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAEMAcgBpAHQAZQByAGkAYQAxACwAIABDAHIAaQB0AGUAcgBpAGEAMQBUAHkAcABlAEEAcgByAGEAeQAsACAAUQB1AGEAbgB0AGkAdAB5ACwAIABbAE0AdQBsAHQAaQBwAGwAaQBlAHIAXQAsACAAWwBDAHIAaQB0AGUAcgBpAGEAMgBdACwAWwBDAHIAaQB0AGUAcgBpAGEAMgBBAHIAcgBhAHkAXQAsAFwAbgAgACAATABFAFQAKABcAG4AIAAgACAAIABtAHUAbAB0AGkAcABsAGkAZQByACwAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAE0AdQBsAHQAaQBwAGwAaQBlAHIAKQAsADEALABNAHUAbAB0AGkAcABsAGkAZQByACkALABcAG4AIAAgACAAIABxAHUAYQBuAHQAaQB0AHkALAAgAFEAdQBhAG4AdABpAHQAeQAqAE0AdQBsAHQAaQBwAGwAaQBlAHIALABcAG4AIAAgACAAIABjAHIAaQB0AGUAcgBpAGEAMQAsAC0ALQAoAEMAcgBpAHQAZQByAGkAYQAxAFQAeQBwAGUAQQByAHIAYQB5AD0AQwByAGkAdABlAHIAaQBhADEAKQAsAFwAbgAgACAAIAAgAGMAcgBpAHQAZQByAGkAYQAyACwASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABDAHIAaQB0AGUAcgBpAGEAMgApACwAMQAsAC0ALQAoAEMAcgBpAHQAZQByAGkAYQAyAEEAcgByAGEAeQA9AEMAcgBpAHQAZQByAGkAYQAyACkAKQAsAFwAbgAgACAAIAAgAFMAVQBNAFAAUgBPAEQAVQBDAFQAKABjAHIAaQB0AGUAcgBpAGEAMQAqAGMAcgBpAHQAZQByAGkAYQAyACoAcQB1AGEAbgB0AGkAdAB5ACkAXABuACAAIAApAFwAbgApADsAXABuAFwAbgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAHMAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBTAHQAYQByAHQALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBFAG4AZAAsAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAUwAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgACAAIAAgACAARQAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAXABuACAAIAAgACAAIAAgACAAIABtACwATQBPAE4AVABIACgAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAApACwAXABuACAAIAAgACAAIAAgACAAIABkACwARABBAFkAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAFAAZQByAGkAbwBkAEUAbgBkACwATABBAE0AQgBEAEEAKABzAHQALABFAEQAQQBUAEUAKABzAHQALAAxADIAKQAtADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAQQAsAFMALQAzADYANQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBhACwAWQBFAEEAUgAoAEEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBiACwAWQBFAEEAUgAoAEUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZgBpAHIAcwB0AFkAZQBhAHIALAB5AGEAKwAoAFAAZQByAGkAbwBkAEUAbgBkACgARABBAFQARQAoAHkAYQAsAG0ALABkACkAKQBcAHUAMAAwADMAYwAgAFMAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAbABhAHMAdABZAGUAYQByACwAeQBiAC0AKABEAEEAVABFACgAeQBiACwAbQAsAGQAKQBcAHUAMAAwADMAZQAgAEUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAATQBBAFgAKAAwACwAbABhAHMAdABZAGUAYQByAC0AZgBpAHIAcwB0AFkAZQBhAHIAKwAxACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAFAAZQByAGkAbwBkAHMAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBTAHQAYQByAHQALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBFAG4AZAAsAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAUwAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgACAAIAAgACAARQAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAXABuACAAIAAgACAAIAAgACAAIABtACwATQBPAE4AVABIACgAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAApACwAXABuACAAIAAgACAAIAAgACAAIABkACwARABBAFkAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALAAgAC8AKgBoAGUAbABwAGUAcgA6ACAAZQBuAGQAIABkAGEAdABlACAAZgBvAHIAIABhACAAcgBlAHAAbwByAHQAaQBuAGcAIABwAGUAcgBpAG8AZAAgAHMAdABhAHIAdABpAG4AZwAgAGEAdAAgAGEAIABnAGkAdgBlAG4AIABkAGEAdABlACoALwBcAG4AIAAgACAAIAAgACAAIAAgAFAAZQByAGkAbwBkAEUAbgBkACwATABBAE0AQgBEAEEAKABzAHQALABFAEQAQQBUAEUAKABzAHQALAAxADIAKQAtADEAKQAsACAALwAqAG8AbgBsAHkAIABuAGUAZQBkACAAdABvACAAbABvAG8AawAgAGIAYQBjAGsAIAAzADYANQAgAGQAYQB5AHMAKABtAGEAeAAgAG8AdgBlAHIAbABhAHAAIAB3AGkAbgBkAG8AdwApACoALwBcAG4AIAAgACAAIAAgACAAIAAgAEEALABTAC0AMwA2ADUALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYQAsAFkARQBBAFIAKABBACkALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYgAsAFkARQBBAFIAKABFACkALAAgAC8AKgBpAGYAIAB0AGgAZQAgAGEAbgBjAGgAbwByACAAZgBvAHIAIAB5AGEAIABlAG4AZABzACAAYgBlAGYAbwByAGUAIABTACwAaQB0ACAAYwBhAG4AXAB1ADAAMAAyADcAdAAgAG8AdgBlAHIAbABhAHAAOwAgAG0AbwB2AGUAIAB0AG8AIABuAGUAeAB0ACAAeQBlAGEAcgAqAC8AXABuACAAIAAgACAAIAAgACAAIABmAGkAcgBzAHQAWQBlAGEAcgAsAHkAYQArACgAUABlAHIAaQBvAGQARQBuAGQAKABEAEEAVABFACgAeQBhACwAbQAsAGQAKQApAFwAdQAwADAAMwBjAFMAKQAsACAALwAqAGkAZgAgAHQAaABlACAAYQBuAGMAaABvAHIAIABmAG8AcgAgAHkAYgAgAHMAdABhAHIAdABzACAAYQBmAHQAZQByACAARQAsAGkAdAAgAGMAYQBuAFwAdQAwADAAMgA3AHQAIABvAHYAZQByAGwAYQBwADsAIABtAG8AdgBlACAAdABvACAAcAByAGUAdgBpAG8AdQBzACAAeQBlAGEAcgAqAC8AXABuACAAIAAgACAAIAAgACAAIABsAGEAcwB0AFkAZQBhAHIALAB5AGIALQAoAEQAQQBUAEUAKAB5AGIALABtACwAZAApAFwAdQAwADAAMwBlAEUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAbgAsAE0AQQBYACgAMAAsAGwAYQBzAHQAWQBlAGEAcgAtAGYAaQByAHMAdABZAGUAYQByACsAMQApACwAXABuACAAIAAgACAAIAAgACAAIAB5AHIAcwAsAFMARQBRAFUARQBOAEMARQAoAG4ALAAxACwAZgBpAHIAcwB0AFkAZQBhAHIALAAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAHMAdABhAHIAdABzACwARABBAFQARQAoAHkAcgBzACwAbQAsAGQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZQBuAGQAcwAsAE0AQQBQACgAcwB0AGEAcgB0AHMALABQAGUAcgBpAG8AZABFAG4AZAApACwAXABuACAAIAAgACAAIAAgACAAIAB0AGEAZwAsAEkARgAoAHMAdABhAHIAdABzAD0AUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAIgAgACgAVABoAGkAcwAgAHIAZQBwAG8AcgB0AGkAbgBnACAAYwB5AGMAbABlACkAXAAiACwAXAAiAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABzAHQAYQByAHQAcwBUAGUAeAB0ACwAVABFAFgAVAAoAHMAdABhAHIAdABzACwAXAAiAGQAZAAgAG0AbQBtACAAeQB5AHkAeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZQBuAGQAcwBUAGUAeAB0ACwAVABFAFgAVAAoAGUAbgBkAHMALABcACIAZABkACAAbQBtAG0AIAB5AHkAeQB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABuAD0AMAAsAFwAIgBcACIALABIAFMAVABBAEMASwAoAHMAdABhAHIAdABzAFQAZQB4AHQAIABcAHUAMAAwADIANgAgAFwAIgAgAHQAbwAgAFwAIgAgAFwAdQAwADAAMgA2ACAAZQBuAGQAcwBUAGUAeAB0ACAAXAB1ADAAMAAyADYAIAB0AGEAZwApACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkARgB1AG4AYwB0AGkAbwBuAE4AYQBtAGUAXABuAD0ATABBAE0AQgBEAEEAKABGAHUAbgBjAHQAaQBvAG4ALAAgAFQARQBYAFQAQgBFAEYATwBSAEUAKABGAE8AUgBNAFUATABBAFQARQBYAFQAKABGAHUAbgBjAHQAaQBvAG4AKQAsACAAXAAiACgAXAAiACkAKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAE4AMgBPAEUARgBGAHIAbwBtAFAAcgBvAGQASQByAHIAaQBnAGEAdABpAG8AbgBSAGEAaQBuAGYAYQBsAGwAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAIABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACwAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AQQByAHIAYQB5ACwAIABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkAEEAcgByAGEAeQAsACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAQQByAHIAYQB5ACwAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQALAAgAEkARgAoAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAPQBcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEEAbgB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQAsACAASQBGACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAAgAD0AIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAIABcACIAQQBuAHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKAAxACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEEAcgByAGEAeQA9AFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AKQAqAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAoAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAQQByAHIAYQB5AD0ASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAApACoAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACgAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAQQByAHIAYQB5AD0AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEcAZQB0AEYAcgBhAGMAVwBFAFQAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ALABcAG4AIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQALAAgAFwAbgAgACAAIAAgACAAIAAgACAAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUALABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBMAG8AbwBrAHUAcAAsAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQALAAgAFwAbgAgACAAIAAgACAAIAAgACAAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ATABvAG8AawB1AHAALABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBGAHIAYQBjAFcARQBUACAAKwAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVABcAHUAMAAwADMAZQAwACwAIAAxACwAIAAwACkAXABuACAAIAAgACAAKQApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEMAbwBuAHYAZQByAHQAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAVABvAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUALABcAG4AIAAgACAAIABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBBAHIAcgBhAHkALAAgAFMAdABhAHQAZQBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUALAAgAFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAEEAcgByAGEAeQAsACAAUwB0AGEAdABlAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwBvAHUAcgBjAGUASAB5AHAAZQByAGwAaQBuAGsAXABuAD0ATABBAE0AQgBEAEEAKABUAGEAcgBnAGUAdABDAGUAbABsACwAXABuACAAIABMAEUAVAAoAFwAbgAgACAAIAAgAHMAaAAsACAAVABFAFgAVABBAEYAVABFAFIAKABDAEUATABMACgAXAAiAGYAaQBsAGUAbgBhAG0AZQBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsACAAXAAiAF0AXAAiACkALABcAG4AIAAgACAAIABhAGQAZAByACwAIABDAEUATABMACgAXAAiAGEAZABkAHIAZQBzAHMAXAAiACwAIABUAGEAcgBnAGUAdABDAGUAbABsACkALABcAG4AIAAgACAAIABcACIAIwBcAHUAMAAwADIANwBcACIAIABcAHUAMAAwADIANgAgAHMAaAAgAFwAdQAwADAAMgA2ACAAXAAiAFwAdQAwADAAMgA3ACEAXAAiACAAXAB1ADAAMAAyADYAIABhAGQAZAByAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAbwB1AHIAYwBlAEgAeQBwAGUAcgBsAGkAbgBrAEQAaQBmAGYAZQByAGUAbgB0AFMAaABlAGUAdABcAG4APQBMAEEATQBCAEQAQQAoAFQAYQByAGcAZQB0AEMAZQBsAGwALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAcwBoACwAIABUAEUAWABUAEEARgBUAEUAUgAoAEMARQBMAEwAKABcACIAZgBpAGwAZQBuAGEAbQBlAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAIABcACIAXQBcACIAKQAsAFwAbgAgACAAIAAgAGEAZABkAHIALAAgAEMARQBMAEwAKABcACIAYQBkAGQAcgBlAHMAcwBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsAFwAbgAgACAAIAAgAFwAIgAjAFwAIgAgAFwAdQAwADAAMgA2ACAAYQBkAGQAcgBcAG4AIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgBnAHUAbQBlAG4AdABzAF8AMQBfADIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALABcAG4AIAAgACAAIABDAEgATwBPAFMARQBDAE8ATABTACgAQQByAGcAdQBtAGUAbgB0AHMAQQByAHIAYQB5ACwAIAAxACwAIAAyACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgBnAHUAbQBlAG4AdABzAF8AMwBfADQAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALABcAG4AIAAgACAAIABDAEgATwBPAFMARQBDAE8ATABTACgAQQByAGcAdQBtAGUAbgB0AHMAQQByAHIAYQB5ACwAIAAzACwAIAA0ACkAXABuACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8ARwBlAHQATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUALAAgAE0ATQBTACwAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUAQQByAHIAYQB5ACwAIABNAE0AUwBBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKABcAG4AIAAgACAAIAAgACAAIAAgAE0ARQBEAEkAQQBOACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFIATwBVAE4ARAAoAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAsACAAMAApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATQBJAE4AKABUAGUAbQBwAGUAcgBhAHQAdQByAGUAQQByAHIAYQB5ACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABNAEEAWAAoAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkALABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKABNAE0AUwAsACAATQBNAFMAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFIAZQBzAHUAbAB0AHMASQB0AGUAbQBGAHIAbwBtAEUAcQB1AGEAdABpAG8AbgBUAGkAdABsAGUAQQBuAGQAUwBvAHUAcgBjAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGkAdABsAGUAQwBlAGwAbAAsACAAUwBvAHUAcgBjAGUAQwBlAGwAbAAsAFwAbgAgACAAIAAgAFMAVQBCAFMAVABJAFQAVQBUAEUAKABMAEUARgBUACgAUwBvAHUAcgBjAGUAQwBlAGwAbAAsACAARgBJAE4ARAAoAFwAIgAsAFwAIgAsACAAUwBvAHUAcgBjAGUAQwBlAGwAbAApACAALQAxACkALAAgAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABcACIALAAgAFwAIgBcACIAKQAgAFwAdQAwADAAMgA2ACAAXAAiACAAXAAiACAAXAB1ADAAMAAyADYAIABUAGkAdABsAGUAQwBlAGwAbABcAG4AKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AVwBhAHMAdABlAHcAYQB0AGUAcgBfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAiACwAIgB0AGUAeAB0ACIAOgAiAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AMQAxAC4AMQA6ACAAVwBhAHMAdABlAHcAYQB0AGUAcgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AMQAxAC4AMQAuADEALgAxACAATQBlAHQAaABvAGQAIAAxACAALQAgAE0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABvAG4AcwBpAHQAZQAgAFcAYQBzAHQAZQB3AGEAdABlAHIAIABNAGEAbgBhAGcAZQBtAGUAbgB0AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8AMQAxAF8AMQBfADEAXwAxAF8AXwAxAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFcAYQBzAHQAZQB3AGEAdABlAHIAVAByAGUAYQB0AG0AZQBuAHQAXABuAE0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIAB3AGEAcwB0AGUAdwBhAHQAZQByACAAdAByAGUAYQB0AG0AZQBuAHQAXABuAEUAXwBDAEgANABcAG4AdAAgAEMASAA0AFwAbgBFAF8AewBDAEgANAB9AD0AXABcAGYAcgBhAGMAewAxAH0AewAxADAAMAAwAH0AXABcAHQAaQBtAGUAcwBcAFwAbABlAGYAdABbAFwAXABsAGUAZgB0ACgAVwBfAHQAXABcAHQAaQBtAGUAcwBcAFwAbABlAGYAdAAoAEMATwBEAF8AewBpAG4AfQBcAFwAdABpAG0AZQBzACgAMQAtAEYAXwB7AHMAbAB1AGQAZwBlAH0AKQAtAEMATwBEAF8AewBvAHUAdAB9AFwAXAByAGkAZwBoAHQAKQBcAFwAdABpAG0AZQBzACAAQwBGAF8AewB3AHcALAB0AH0AXABcAHQAaQBtAGUAcwAgAEUARgBfAHsAdwB3AH0AXABcAHIAaQBnAGgAdAApACsAXABcAGwAZQBmAHQAKABXAF8AdABcAFwAdABpAG0AZQBzAFwAXABsAGUAZgB0ACgAQwBPAEQAXwB7AGkAbgB9AFwAXAB0AGkAbQBlAHMAKABGAF8AewBzAGwAdQBkAGcAZQB9AC0ARgBfAHsAcgBlAG0AbwB2AGUAZAB9ACkAXABcAHIAaQBnAGgAdAApAFwAXAB0AGkAbQBlAHMAIABDAEYAXwB7AHMAbAB1AGQAZwBlACwAdAB9AFwAXAB0AGkAbQBlAHMAIABFAEYAXwB7AHMAbAB1AGQAZwBlAH0AXABcAHIAaQBnAGgAdAApAC0AXABcAGwAZQBmAHQAKAA2AC4ANwA4ADQAXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQA0AH0AXABcAHQAaQBtAGUAcwAoAFEAXwB7AGMAYQBwAH0AKwBRAF8AewBmAGwAYQByAGUAZAB9ACsAUQBfAHsAbwB1AHQAfQApAFwAXAByAGkAZwBoAHQAKQArAFwAXABsAGUAZgB0ACgAUQBfAHsAZgBsAGEAcgBlAGQAfQBcAFwAdABpAG0AZQBzACAARQBDAF8AewBmAGwAYQByAGUAZAB9AFwAXAB0AGkAbQBlAHMAIABFAEYAXwB7AGYAbABhAHIAZQBkACwAQwBIADQAfQBcAFwAcgBpAGcAaAB0ACkAXABcAHIAaQBnAGgAdABdAFwAbgBXAF8AdAAgAD0AIABxAHUAYQBuAHQAaQB0AHkAIABvAGYAIAB3AGEAcwB0AGUAdwBhAHQAZQByACAAdAByAGUAYQB0AGUAZAAgAGEAdAAgAGYAYQBjAGkAbABpAHQAeQAgAHQAeQBwAGUAIAB0ACAAKABtADMAKQBcAG4AQwBPAEQAXwBpAG4AIAA9ACAAYQB2AGUAcgBhAGcAZQAgAGkAbgBsAGUAdAAgAEMAaABlAG0AaQBjAGEAbAAgAE8AeAB5AGcAZQBuACAARABlAG0AYQBuAGQAIABjAG8AbgBjAGUAbgB0AHIAYQB0AGkAbwBuACAAbwBmACAAdwBhAHMAdABlAHcAYQB0AGUAcgAgACgAawBnACAAQwBPAEQALwBtADMAKQBcAG4ARgBfAHMAbAB1AGQAZwBlACAAPQAgAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAEMATwBEACAAcgBlAG0AbwB2AGUAZAAgAGYAcgBvAG0AIAB3AGEAcwB0AGUAdwBhAHQAZQByACAAYQBzACAAcwBsAHUAZABnAGUAXABuAEMATwBEAF8AbwB1AHQAIAA9ACAAYQB2AGUAcgBhAGcAZQAgAG8AdQB0AGwAZQB0ACAAQwBPAEQAIABjAG8AbgBjAGUAbgB0AHIAYQB0AGkAbwBuACAAbwBmACAAdwBhAHMAdABlAHcAYQB0AGUAcgAgACgAawBnACAAQwBPAEQALwBtADMAKQBcAG4AQwBGAF8AdwB3AF8AdAAgAD0AIABtAGUAdABoAGEAbgBlACAAYwBvAHIAcgBlAGMAdABpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABmAGEAYwBpAGwAaQB0AHkAIAB0AHkAcABlACAAdAAgAHUAcwBlAGQAIAB0AG8AIAB0AHIAZQBhAHQAIAB3AGEAcwB0AGUAdwBhAHQAZQByAFwAbgBFAEYAXwB3AHcAIAA9ACAAbQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB3AGEAcwB0AGUAdwBhAHQAZQByACAAKABrAGcAIABDAE8AMgBlAC8AawBnACAAQwBPAEQAKQBcAG4ARgBfAHIAZQBtAG8AdgBlAGQAIAA9ACAAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAQwBPAEQAIAByAGUAbQBvAHYAZQBkACAAZgByAG8AbQAgAHQAaABlACAAdwBhAHMAdABlAHcAYQB0AGUAcgAgAHQAcgBlAGEAdABtAGUAbgB0ACAAZgBhAGMAaQBsAGkAdAB5ACAAYQBuAGQAIAB0AHIAYQBuAHMAZgBlAHIAcgBlAGQAIABlAGwAcwBlAHcAaABlAHIAZQBcAG4AQwBGAF8AcwBsAHUAZABnAGUAXwB0ACAAPQAgAG0AZQB0AGgAYQBuAGUAIABjAG8AcgByAGUAYwB0AGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAGYAYQBjAGkAbABpAHQAeQAgAHQAeQBwAGUAIAB0ACAAdQBzAGUAZAAgAHQAbwAgAHQAcgBlAGEAdAAgAHMAbAB1AGQAZwBlAFwAbgBFAEYAXwBzAGwAdQBkAGcAZQAgAD0AIABtAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHMAbAB1AGQAZwBlACAAKABrAGcAIABDAE8AMgBlAC8AawBnACAAQwBPAEQAKQBcAG4AUQBfAGMAYQBwACAAPQAgAHEAdQBhAG4AdABpAHQAeQAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAIABpAG4AIABzAGwAdQBkAGcAZQAgAGIAaQBvAGcAYQBzACAAYwBhAHAAdAB1AHIAZQBkACAAZgBvAHIAIABjAG8AbQBiAHUAcwB0AGkAbwBuACAAKABtADMAIABDAEgANAApAFwAbgBRAF8AZgBsAGEAcgBlAGQAIAA9ACAAcQB1AGEAbgB0AGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQAgAGkAbgAgAHMAbAB1AGQAZwBlACAAYgBpAG8AZwBhAHMAIABmAGwAYQByAGUAZAAgACgAbQAzACAAQwBIADQAKQBcAG4AUQBfAG8AdQB0ACAAPQAgAHEAdQBhAG4AdABpAHQAeQAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAIABpAG4AIABzAGwAdQBkAGcAZQAgAGIAaQBvAGcAYQBzACAAdAByAGEAbgBzAGYAZQByAHIAZQBkACAAbwB1AHQAIABvAGYAIAB0AGgAZQAgAHQAcgBlAGEAdABtAGUAbgB0ACAAZgBhAGMAaQBsAGkAdAB5ACAAKABtADMAIABDAEgANAApAFwAbgBFAEMAXwBmAGwAYQByAGUAZAAgAD0AIABlAG4AZQByAGcAeQAgAGMAbwBuAHQAZQBuAHQAIABmAGEAYwB0AG8AcgAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAIABpAG4AIABzAGwAdQBkAGcAZQAgAGIAaQBvAGcAYQBzACAAZgBsAGEAcgBlAGQAIAAoAEcASgAvAG0AMwApAFwAbgBFAEYAXwBmAGwAYQByAGUAZABfAEMASAA0ACAAPQAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAcwBsAHUAZABnAGUAIABiAGkAbwBnAGEAcwAgAGYAbABhAHIAZQBkACAAKABrAGcAIABDAE8AMgBlAC8ARwBKACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8AMQAxAF8AMQBfADEAXwAxAF8AXwAxAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFcAYQBzAHQAZQB3AGEAdABlAHIAVAByAGUAYQB0AG0AZQBuAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAVwBfAHQALAAgAEMATwBEAF8AaQBuACwAIABGAF8AcwBsAHUAZABnAGUALAAgAEMATwBEAF8AbwB1AHQALAAgAEMARgBfAHcAdwBfAHQALAAgAEUARgBfAHcAdwAsACAARgBfAHIAZQBtAG8AdgBlAGQALAAgAEMARgBfAHMAbAB1AGQAZwBlAF8AdAAsACAARQBGAF8AcwBsAHUAZABnAGUALAAgAFEAXwBjAGEAcAAsACAAUQBfAGYAbABhAHIAZQBkACwAIABRAF8AbwB1AHQALAAgAEUAQwBfAGYAbABhAHIAZQBkACwAIABFAEYAXwBmAGwAYQByAGUAZABDAEgANAAsAFwAbgAgACAAIAAgACgAMQAvADEAMAAwADAAKQAgACoAIAAoACgAVwBfAHQAIAAqACAAKABDAE8ARABfAGkAbgAgACoAIAAoADEAIAAtACAARgBfAHMAbAB1AGQAZwBlACkAIAAtACAAQwBPAEQAXwBvAHUAdAApACAAKgAgAEMARgBfAHcAdwBfAHQAIAAqACAARQBGAF8AdwB3ACkAIAArACAAKABXAF8AdAAgACoAIAAoAEMATwBEAF8AaQBuACAAKgAgACgARgBfAHMAbAB1AGQAZwBlACAALQAgAEYAXwByAGUAbQBvAHYAZQBkACkAKQAgACoAIABDAEYAXwBzAGwAdQBkAGcAZQBfAHQAIAAqACAARQBGAF8AcwBsAHUAZABnAGUAKQAgAC0AIAAoADYALgA3ADgANAAgACoAIAAxADAAXgAtADQAIAAqACAAKABRAF8AYwBhAHAAIAArACAAUQBfAGYAbABhAHIAZQBkACAAKwAgAFEAXwBvAHUAdAApACkAIAArACAAKABRAF8AZgBsAGEAcgBlAGQAIAAqACAAKABFAEMAXwBmAGwAYQByAGUAZAAgACoAIABFAEYAXwBmAGwAYQByAGUAZABDAEgANAApACkAKQBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEAMQBfADEAXwAxAF8AMQBfAF8AMQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBXAGEAcwB0AGUAdwBhAHQAZQByAFQAcgBlAGEAdABtAGUAbgB0AF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAdwBhAHMAdABlAHcAYQB0AGUAcgAgAHQAcgBlAGEAdABtAGUAbgB0AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADEAXwAxAF8AMQBfADEAXwBfADEAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AVwBhAHMAdABlAHcAYQB0AGUAcgBUAHIAZQBhAHQAbQBlAG4AdABfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBfAEMASAA0AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADEAXwAxAF8AMQBfADEAXwBfADEAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AVwBhAHMAdABlAHcAYQB0AGUAcgBUAHIAZQBhAHQAbQBlAG4AdABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAEgANABcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQAxAF8AMQBfADEAXwAxAF8AXwAxAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFcAYQBzAHQAZQB3AGEAdABlAHIAVAByAGUAYQB0AG0AZQBuAHQAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAMQAxAC4AMQAuADEALgAxACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADEAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQAxAF8AMQBfADEAXwAxAF8AXwAxAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFcAYQBzAHQAZQB3AGEAdABlAHIAVAByAGUAYQB0AG0AZQBuAHQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAARwByAGUAZQBuAGgAbwB1AHMAZQAgAGEAbgBkACAARQBuAGUAcgBnAHkAIABSAGUAcABvAHIAdABpAG4AZwAgAE0AZQBhAHMAdQByAGUAbQBlAG4AdAAgAEQAZQB0AGUAcgBtAGkAbgBhAHQAaQBvAG4AIAAyADAAMAA4AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADEAXwAxAF8AMQBfADEAXwBfADEAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AVwBhAHMAdABlAHcAYQB0AGUAcgBUAHIAZQBhAHQAbQBlAG4AdABfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwB7AEMASAA0AH0APQBcAFwAZgByAGEAYwB7ADEAfQB7ADEAMAAwADAAfQBcAFwAdABpAG0AZQBzAFwAXABsAGUAZgB0AHsAXABcAGwAZQBmAHQAewBXAF8AdABcAFwAdABpAG0AZQBzAFwAXABsAGUAZgB0AFsAQwBPAEQAXwB7AGkAbgB9AFwAXAB0AGkAbQBlAHMAKAAxAC0ARgBfAHsAcwBsAHUAZABnAGUAfQApAC0AQwBPAEQAXwB7AG8AdQB0AH0AXABcAHIAaQBnAGgAdABdAFwAXAB0AGkAbQBlAHMAIABDAEYAXwB7AHcAdwAsAHQAfQBcAFwAdABpAG0AZQBzACAARQBGAF8AewB3AHcAfQBcAFwAcgBpAGcAaAB0AH0AKwBcAFwAbABlAGYAdAB7AFcAXwB0AFwAXAB0AGkAbQBlAHMAXABcAGwAZQBmAHQAWwBDAE8ARABfAHsAaQBuAH0AXABcAHQAaQBtAGUAcwAoAEYAXwB7AHMAbAB1AGQAZwBlAH0ALQBGAF8AewByAGUAbQBvAHYAZQBkAH0AKQBcAFwAcgBpAGcAaAB0AF0AXABcAHQAaQBtAGUAcwAgAEMARgBfAHsAcwBsAHUAZABnAGUALAB0AH0AXABcAHQAaQBtAGUAcwAgAEUARgBfAHsAcwBsAHUAZABnAGUAfQBcAFwAcgBpAGcAaAB0AH0ALQBcAFwAbABlAGYAdAB7ADYALgA3ADgANABcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADQAfQBcAFwAdABpAG0AZQBzACAAXABcAGwAZQBmAHQAWwAgAFEAXwB7AGMAYQBwAH0AKwBRAF8AewBmAGwAYQByAGUAZAB9ACsAUQBfAHsAbwB1AHQAfQBcAFwAcgBpAGcAaAB0AF0AXABcAHIAaQBnAGgAdAB9ACsAXABcAGwAZQBmAHQAewBRAF8AewBmAGwAYQByAGUAZAB9AFwAXAB0AGkAbQBlAHMAIABcAFwAbABlAGYAdABbACAARQBDAF8AewBmAGwAYQByAGUAZAB9AFwAXAB0AGkAbQBlAHMAIABFAEYAXwB7AGYAbABhAHIAZQBkACwAQwBIADQAfQBcAFwAcgBpAGcAaAB0AF0AXABcAHIAaQBnAGgAdAB9AFwAXAByAGkAZwBoAHQAfQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQAxAF8AMQBfADEAXwAxAF8AXwAxAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFcAYQBzAHQAZQB3AGEAdABlAHIAVAByAGUAYQB0AG0AZQBuAHQAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEANQAsACAANAAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAF8AdABcACIALAAgAFwAIgBxAHUAYQBuAHQAaQB0AHkAIABvAGYAIAB3AGEAcwB0AGUAdwBhAHQAZQByACAAdAByAGUAYQB0AGUAZAAgAGEAdAAgAGYAYQBjAGkAbABpAHQAeQAgAHQAeQBwAGUAIAB0AFwAIgAsACAAXAAiAG0AMwBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwBEAF8AaQBuAFwAIgAsACAAXAAiAGEAdgBlAHIAYQBnAGUAIABpAG4AbABlAHQAIABDAGgAZQBtAGkAYwBhAGwAIABPAHgAeQBnAGUAbgAgAEQAZQBtAGEAbgBkACAAYwBvAG4AYwBlAG4AdAByAGEAdABpAG8AbgAgAG8AZgAgAHcAYQBzAHQAZQB3AGEAdABlAHIAXAAiACwAIABcACIAawBnACAAQwBPAEQALwBtADMAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAF8AcwBsAHUAZABnAGUAXAAiACwAIABcACIAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAQwBPAEQAIAByAGUAbQBvAHYAZQBkACAAZgByAG8AbQAgAHcAYQBzAHQAZQB3AGEAdABlAHIAIABhAHMAIABzAGwAdQBkAGcAZQBcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAE8ARABfAG8AdQB0AFwAIgAsACAAXAAiAGEAdgBlAHIAYQBnAGUAIABvAHUAdABsAGUAdAAgAEMATwBEACAAYwBvAG4AYwBlAG4AdAByAGEAdABpAG8AbgAgAG8AZgAgAHcAYQBzAHQAZQB3AGEAdABlAHIAXAAiACwAIABcACIAawBnACAAQwBPAEQALwBtADMAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAEYAXwB3AHcAXwB0AFwAIgAsACAAXAAiAG0AZQB0AGgAYQBuAGUAIABjAG8AcgByAGUAYwB0AGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAGYAYQBjAGkAbABpAHQAeQAgAHQAeQBwAGUAIAB0ACAAdQBzAGUAZAAgAHQAbwAgAHQAcgBlAGEAdAAgAHcAYQBzAHQAZQB3AGEAdABlAHIAXAAiACwAIABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAF8AdwB3AFwAIgAsACAAXAAiAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAdwBhAHMAdABlAHcAYQB0AGUAcgBcACIALAAgAFwAIgBrAGcAIABDAEgANAAvAGsAZwAgAEMATwBEAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBfAHIAZQBtAG8AdgBlAGQAXAAiACwAIABcACIAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAQwBPAEQAIAByAGUAbQBvAHYAZQBkACAAZgByAG8AbQAgAHQAaABlACAAdwBhAHMAdABlAHcAYQB0AGUAcgAgAHQAcgBlAGEAdABtAGUAbgB0ACAAZgBhAGMAaQBsAGkAdAB5ACAAYQBuAGQAIAB0AHIAYQBuAHMAZgBlAHIAcgBlAGQAIABlAGwAcwBlAHcAaABlAHIAZQBcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAEYAXwBzAGwAdQBkAGcAZQBfAHQAXAAiACwAIABcACIAbQBlAHQAaABhAG4AZQAgAGMAbwByAHIAZQBjAHQAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAZgBhAGMAaQBsAGkAdAB5ACAAdAB5AHAAZQAgAHQAIAB1AHMAZQBkACAAdABvACAAdAByAGUAYQB0ACAAcwBsAHUAZABnAGUAXAAiACwAIABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAF8AcwBsAHUAZABnAGUAXAAiACwAIABcACIAbQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABzAGwAdQBkAGcAZQBcACIALAAgAFwAIgBrAGcAIABDAEgANAAvAGsAZwAgAEMATwBEAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUQBfAGMAYQBwAFwAIgAsACAAXAAiAHEAdQBhAG4AdABpAHQAeQAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAIABpAG4AIABzAGwAdQBkAGcAZQAgAGIAaQBvAGcAYQBzACAAYwBhAHAAdAB1AHIAZQBkACAAZgBvAHIAIABjAG8AbQBiAHUAcwB0AGkAbwBuAFwAIgAsACAAXAAiAG0AMwAgAEMASAA0AFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUQBfAGYAbABhAHIAZQBkAFwAIgAsACAAXAAiAHEAdQBhAG4AdABpAHQAeQAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAIABpAG4AIABzAGwAdQBkAGcAZQAgAGIAaQBvAGcAYQBzACAAZgBsAGEAcgBlAGQAIABiAHkAIAB0AGgAZQAgAHQAcgBlAGEAdABtAGUAbgB0ACAAZgBhAGMAaQBsAGkAdAB5AFwAIgAsACAAXAAiAG0AMwAgAEMASAA0AFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUQBfAG8AdQB0AFwAIgAsACAAXAAiAHEAdQBhAG4AdABpAHQAeQAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAIABpAG4AIABzAGwAdQBkAGcAZQAgAGIAaQBvAGcAYQBzACAAdAByAGEAbgBzAGYAZQByAHIAZQBkACAAbwB1AHQAIABvAGYAIAB0AGgAZQAgAHQAcgBlAGEAdABtAGUAbgB0ACAAZgBhAGMAaQBsAGkAdAB5AFwAIgAsACAAXAAiAG0AMwAgAEMASAA0AFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBDAF8AZgBsAGEAcgBlAGQAXAAiACwAIABcACIAZQBuAGUAcgBnAHkAIABjAG8AbgB0AGUAbgB0ACAAZgBhAGMAdABvAHIAIABvAGYAIABtAGUAdABoAGEAbgBlACAAaQBuACAAcwBsAHUAZABnAGUAIABiAGkAbwBnAGEAcwAgAGYAbABhAHIAZQBkAFwAIgAsACAAXAAiAEcASgAvAG0AMwBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARgBfAGYAbABhAHIAZQBkAEMASAA0AFwAIgAsACAAXAAiAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAcwBsAHUAZABnAGUAIABiAGkAbwBnAGEAcwAgAGYAbABhAHIAZQBkAFwAIgAsACAAXAAiAGsAZwAgAEMASAA0AC8ARwBKAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAdABcACIALAAgAFwAIgB0AHIAZQBhAHQAbQBlAG4AdAAgAGYAYQBjAGkAbABpAHQAeQAgAHQAeQBwAGUAXAAiACwAIABcACIAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAFYARQBFAFIARwBfADEAMQBfADEAXwAxAF8AMQBfAF8AMQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBXAGEAcwB0AGUAdwBhAHQAZQByAFQAcgBlAGEAdABtAGUAbgB0AF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBOACAAUwBPAFUAUgBDAEUAOgAgAEMAaABhAG4AZwBlAGQAIAB1AG4AaQB0AHMAIABvAGYAIABFAEYAXwB3AHcALAAgAEUARgBfAFMAbAB1AGQAZwBlACAAYQBuAGQAIABFAEYAXwBmAGwAYQByAGUAZAAgAGYAcgBvAG0AIABDAE8AMgBlACAAdABvACAAQwBIADQAIAB0AG8AIABtAGEAdABjAGgAIABkAGEAdABhACAAaQBuACAAVABhAGIAbABlACAAXAAiACkAOwAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBTAG8AdQByAGMAZQBEAGEAdABhACIALAAiAHQAZQB4AHQAIgA6ACIALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgBUAGEAYgBsAGUAIABBAC4ANAAuADEALgAzADoAIABNAGUAdABoAGEAbgBlACAAYwBvAHIAcgBlAGMAdABpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB0AHIAZQBhAHQAbQBlAG4AdAAgAGYAYQBjAGkAbABpAHQAeQAgAHQAeQBwAGUAIAB0ACAAdQBzAGUAZAAgAHQAbwAgAHQAcgBlAGEAdAAgAHcAYQBzAHQAZQB3AGEAdABlAHIAIAAoAGYAcgBhAGMAdABpAG8AbgApACAAKABDAEYAdwB3ACwAdAApAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEMAbwByAHIAZQBjAHQAaQBvAG4ARgBhAGMAdABvAHIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFQAaQB0AGwAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAE0AZQB0AGgAYQBuAGUAIABjAG8AcgByAGUAYwB0AGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHQAcgBlAGEAdABtAGUAbgB0ACAAZgBhAGMAaQBsAGkAdAB5ACAAdAB5AHAAZQAgAHQAIAB1AHMAZQBkACAAdABvACAAdAByAGUAYQB0ACAAdwBhAHMAdABlAHcAYQB0AGUAcgBcACIAKQApADsAXABuAFwAbgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEMAbwByAHIAZQBjAHQAaQBvAG4ARgBhAGMAdABvAHIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFYAYQByAGkAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEMARgB3AHcALAB0AFwAIgApACkAOwBcAG4AXABuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUAQwBvAHIAcgBlAGMAdABpAG8AbgBGAGEAYwB0AG8AcgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AVQBuAGkAdABcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIAKQApADsAXABuAFwAbgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEMAbwByAHIAZQBjAHQAaQBvAG4ARgBhAGMAdABvAHIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADQALgAxAC4AMwBcACIAKQApADsAXABuAFwAbgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEMAbwByAHIAZQBjAHQAaQBvAG4ARgBhAGMAdABvAHIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAEQAYQB0AGEAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANgAsACAAMgAsAFwAbgAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBGAGEAYwBpAGwAaQB0AHkAIAB0AHkAcABlACAAdABcACIALAAgAFwAIgBDAEYAdwB3ACwAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBNAGEAbgBhAGcAZQBkACAAYQBlAHIAbwBiAGkAYwAgAHQAcgBlAGEAdABtAGUAbgB0AFwAIgAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFUAbgBtAGEAbgBhAGcAZQBkACAAYQBlAHIAbwBiAGkAYwAgAHQAcgBlAGEAdABtAGUAbgB0AFwAIgAsACAAMAAuADMAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBBAG4AYQBlAHIAbwBiAGkAYwAgAGQAaQBnAGUAcwB0AG8AcgAvAHIAZQBhAGMAdABvAHIAXAAiACwAIAAwAC4AOAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFMAaABhAGwAbABvAHcAIABhAG4AYQBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuACAAKABkIiAAMgAgAG0AKQBcACIALAAgADAALgAyADsAXABuACAAIAAgACAAIAAgACAAIABcACIARABlAGUAcAAgAGEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AIAAoAFwAdQAwADAAMwBlACAAMgBtACkAXAAiACwAIAAwAC4AOABcAG4AIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgApACkAKQA7AFwAbgBcAG4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBDAG8AcgByAGUAYwB0AGkAbwBuAEYAYQBjAHQAbwByAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAFwAIgApACkAOwBcAG4AXABuAFwAbgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFQAYQBiAGwAZQAgAEEALgA0AC4AMQAuADQAOgAgAE0AZQB0AGgAYQBuAGUAIABjAG8AcgByAGUAYwB0AGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHQAcgBlAGEAdABtAGUAbgB0ACAAZgBhAGMAaQBsAGkAdAB5ACAAdAB5AHAAZQAgAHQAIAB1AHMAZQBkACAAdABvACAAdAByAGUAYQB0ACAAcwBsAHUAZABnAGUAIAAoAGYAcgBhAGMAdABpAG8AbgApACAAKABDAEYAcwBsAHUAZABnAGUALAB0ACkAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUAQwBvAHIAcgBlAGMAdABpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBfAFQAaQB0AGwAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAE0AZQB0AGgAYQBuAGUAIABjAG8AcgByAGUAYwB0AGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHQAcgBlAGEAdABtAGUAbgB0ACAAZgBhAGMAaQBsAGkAdAB5ACAAdAB5AHAAZQAgAHQAIAB1AHMAZQBkACAAdABvACAAdAByAGUAYQB0ACAAcwBsAHUAZABnAGUAXAAiACkAKQA7AFwAbgBcAG4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBDAG8AcgByAGUAYwB0AGkAbwBuAEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAQwBGAHMAbAB1AGQAZwBlACwAdABcACIAKQApADsAXABuAFwAbgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEMAbwByAHIAZQBjAHQAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAXwBVAG4AaQB0AFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgApACkAOwBcAG4AXABuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUAQwBvAHIAcgBlAGMAdABpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBfAFMAbwB1AHIAYwBlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADQALgAxAC4ANABcACIAKQApADsAXABuAFwAbgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEMAbwByAHIAZQBjAHQAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAXwBEAGEAdABhAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADIALABcAG4AIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIABcACIARgBhAGMAaQBsAGkAdAB5ACAAdAB5AHAAZQAgAHQAXAAiACwAIABcACIAQwBGAHMAbAB1AGQAZwBlACwAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBNAGEAbgBhAGcAZQBkACAAYQBlAHIAbwBiAGkAYwAgAHQAcgBlAGEAdABtAGUAbgB0AFwAIgAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFUAbgBtAGEAbgBhAGcAZQBkACAAYQBlAHIAbwBiAGkAYwAgAHQAcgBlAGEAdABtAGUAbgB0AFwAIgAsACAAMAAuADMAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBBAG4AYQBlAHIAbwBiAGkAYwAgAGQAaQBnAGUAcwB0AG8AcgAvAHIAZQBhAGMAdABvAHIAXAAiACwAIAAwAC4AOAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFMAaABhAGwAbABvAHcAIABhAG4AYQBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuACAAKABkIiAAMgAgAG0AKQBcACIALAAgADAALgAyADsAXABuACAAIAAgACAAIAAgACAAIABcACIARABlAGUAcAAgAGEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AIAAoAFwAdQAwADAAMwBlACAAMgBtACkAXAAiACwAIAAwAC4AOABcAG4AIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgApACkAKQA7AFwAbgBcAG4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBDAG8AcgByAGUAYwB0AGkAbwBuAEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBcACIAKQApADsAXABuAFwAbgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBUAGkAdABsAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBNAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHcAYQBzAHQAZQB3AGEAdABlAHIAXAAiACkAKQA7AFwAbgBcAG4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFYAYQByAGkAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEUARgB3AHcAXAAiACkAKQA7AFwAbgBcAG4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFUAbgBpAHQAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBrAGcAIABDAEgANAAgAC8AIABrAGcAIABDAE8ARABcACIAKQApADsAXABuAFwAbgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AUwBvAHUAcgBjAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAAxADEALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdABzAFwAIgApACkAOwBcAG4AXABuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBEAGEAdABhAFwAbgA9AEwAQQBNAEIARABBACgAIAAwAC4AMgA1ACkAOwBcAG4AXABuAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAXwBUAGkAdABsAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBNAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHMAbAB1AGQAZwBlAFwAIgApACkAOwBcAG4AXABuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIARQBGAHMAbAB1AGQAZwBlAFwAIgApACkAOwBcAG4AXABuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAF8AVQBuAGkAdABcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAGsAZwAgAEMASAA0ACAALwAgAGsAZwAgAEMATwBEAFwAIgApACkAOwBcAG4AXABuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAF8AUwBvAHUAcgBjAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAAxADEALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdABzAFwAIgApACkAOwBcAG4AXABuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAF8ARABhAHQAYQBcAG4APQBMAEEATQBCAEQAQQAoADAALgAyADUAKQA7AFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgBXAGEAcwB0AGUAXwBFAG4AZQByAGcAeQBDAG8AbgB0AGUAbgB0AEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAEIAaQBvAGcAYQBzAEYAbABhAHIAZQBkAF8AVABpAHQAbABlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIARQBuAGUAcgBnAHkAIABjAG8AbgB0AGUAbgB0ACAAZgBhAGMAdABvAHIAIABvAGYAIABzAGwAdQBkAGcAZQAgAGIAaQBvAGcAYQBzACAAZgBsAGEAcgBlAGQAXAAiACkAKQA7AFwAbgBcAG4AVwBhAHMAdABlAF8ARQBuAGUAcgBnAHkAQwBvAG4AdABlAG4AdABGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBCAGkAbwBnAGEAcwBGAGwAYQByAGUAZABfAFYAYQByAGkAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEUAQwBmAGwAYQByAGUAZABcACIAKQApADsAXABuAFwAbgBXAGEAcwB0AGUAXwBFAG4AZQByAGcAeQBDAG8AbgB0AGUAbgB0AEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAEIAaQBvAGcAYQBzAEYAbABhAHIAZQBkAF8AVQBuAGkAdABcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEcASgAgAC8AIABtADMAXAAiACkAKQA7AFwAbgBcAG4AVwBhAHMAdABlAF8ARQBuAGUAcgBnAHkAQwBvAG4AdABlAG4AdABGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBCAGkAbwBnAGEAcwBGAGwAYQByAGUAZABfAFMAbwB1AHIAYwBlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAMQAxAC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAcwBcACIAKQApADsAXABuAFwAbgBXAGEAcwB0AGUAXwBFAG4AZQByAGcAeQBDAG8AbgB0AGUAbgB0AEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAEIAaQBvAGcAYQBzAEYAbABhAHIAZQBkAF8ARABhAHQAYQBcAG4APQBMAEEATQBCAEQAQQAoADAALgAwADMANwA3ACkAOwBcAG4AXABuAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAQgBpAG8AZwBhAHMARgBsAGEAcgBlAGQAXwBUAGkAdABsAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBNAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHMAbAB1AGQAZwBlACAAYgBpAG8AZwBhAHMAIABmAGwAYQByAGUAZABcACIAKQApADsAXABuAFwAbgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBCAGkAbwBnAGEAcwBGAGwAYQByAGUAZABfAFYAYQByAGkAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEUARgBmAGwAYQByAGUAZAAsAEMASAA0AFwAIgApACkAOwBcAG4AXABuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAEIAaQBvAGcAYQBzAEYAbABhAHIAZQBkAF8AVQBuAGkAdABcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAGsAZwAgAEMASAA0ACAALwAgAEcASgBcACIAKQApADsAXABuAFwAbgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBCAGkAbwBnAGEAcwBGAGwAYQByAGUAZABfAFMAbwB1AHIAYwBlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAMQAxAC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAcwBcACIAKQApADsAXABuAFwAbgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBCAGkAbwBnAGEAcwBGAGwAYQByAGUAZABfAEQAYQB0AGEAXABuAD0ATABBAE0AQgBEAEEAKAAwAC4AMgAyADgAOQApADsAXABuAFwAbgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAFcAYQBzAHQAZQBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBCAGkAbwBnAGEAcwBGAGwAYQByAGUAZABfAFQAaQB0AGwAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAcwBsAHUAZABnAGUAIABiAGkAbwBnAGEAcwAgAGYAbABhAHIAZQBkAFwAIgApACkAOwBcAG4AXABuAFcAYQBzAHQAZQBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBCAGkAbwBnAGEAcwBGAGwAYQByAGUAZABfAFYAYQByAGkAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEUARgBmAGwAYQByAGUAZAAsAE4AMgBPAFwAIgApACkAOwBcAG4AXABuAFcAYQBzAHQAZQBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBCAGkAbwBnAGEAcwBGAGwAYQByAGUAZABfAFUAbgBpAHQAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBrAGcAIABOADIATwAgAC8AIABHAEoAXAAiACkAKQA7AFwAbgBcAG4AVwBhAHMAdABlAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAEIAaQBvAGcAYQBzAEYAbABhAHIAZQBkAF8AUwBvAHUAcgBjAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAAxADEALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdABzAFwAIgApACkAOwBcAG4AXABuAFcAYQBzAHQAZQBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBCAGkAbwBnAGEAcwBGAGwAYQByAGUAZABfAEQAYQB0AGEAXABuAD0ATABBAE0AQgBEAEEAKAAxAC4AMQAzADIAZQAtADQAKQA7AFwAbgAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBOADIATwBfAEUAcQB1AGEAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAxADEALgAxADoAIABXAGEAcwB0AGUAdwBhAHQAZQByAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAxADEALgAxAC4AMwAuADEAIABNAGUAdABoAG8AZAAgADEAIAAtACAATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAG8AbgBzAGkAdABlACAAVwBhAHMAdABlAHcAYQB0AGUAcgAgAE0AYQBuAGEAZwBlAG0AZQBuAHQAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwAxADEAXwAxAF8AMwBfADEAXwBfADEAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEYAbABhAHIAZQBkAEIAaQBvAGcAYQBzAFwAbgBOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAZgBsAGEAcgBlAGQAIABiAGkAbwBnAGEAcwBcAG4ARQBfAE4AMgBPAFwAbgB0ACAATgAyAE8AXABuAEUAXwB7AE4AMgBPAH0APQBcAFwAZgByAGEAYwB7AFEAXwB7AGYAbABhAHIAZQBkAH0AfQB7ADEAMAAwADAAfQBcAFwAdABpAG0AZQBzACAARQBGAF8AewBmAGwAYQByAGUAZAAsAE4AMgBPAH0AXABuAFEAXwBmAGwAYQByAGUAZAAgAD0AIAB2AG8AbAB1AG0AZQAgAG8AZgAgAGIAaQBvAGcAYQBzACAAZgBsAGEAcgBlAGQAIAAoAG0AMwAgAG8AcgAgAEcASgApAFwAbgBFAEYAXwBmAGwAYQByAGUAZABfAE4AMgBPACAAPQAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAZgBsAGEAcgBlAGQAIABiAGkAbwBnAGEAcwAgACgAawBnACAATgAyAE8ALwBHAEoAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwAxADEAXwAxAF8AMwBfADEAXwBfADEAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEYAbABhAHIAZQBkAEIAaQBvAGcAYQBzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFEAXwBmAGwAYQByAGUAZAAsACAARQBDAF8AZgBsAGEAcgBlAGQALAAgAEUARgBfAGYAbABhAHIAZQBkAE4AMgBPACwAXABuACAAIAAgACAAKABRAF8AZgBsAGEAcgBlAGQAIAAvACAAMQAwADAAMAApACAAKgAgACgARQBDAF8AZgBsAGEAcgBlAGQAIAAqACAARQBGAF8AZgBsAGEAcgBlAGQATgAyAE8AKQBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEAMQBfADEAXwAzAF8AMQBfAF8AMQBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ARgBsAGEAcgBlAGQAQgBpAG8AZwBhAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABmAGwAYQByAGUAZAAgAGIAaQBvAGcAYQBzAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADEAXwAxAF8AMwBfADEAXwBfADEAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEYAbABhAHIAZQBkAEIAaQBvAGcAYQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAF8ATgAyAE8AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEAMQBfADEAXwAzAF8AMQBfAF8AMQBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ARgBsAGEAcgBlAGQAQgBpAG8AZwBhAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgB0ACAATgAyAE8AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEAMQBfADEAXwAzAF8AMQBfAF8AMQBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ARgBsAGEAcgBlAGQAQgBpAG8AZwBhAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAMQAxAC4AMQAuADMALgAxACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADEAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQAxAF8AMQBfADMAXwAxAF8AXwAxAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBGAGwAYQByAGUAZABCAGkAbwBnAGEAcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQAxAF8AMQBfADMAXwAxAF8AXwAxAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBGAGwAYQByAGUAZABCAGkAbwBnAGEAcwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwB7AE4AMgBPAH0APQBcAFwAZgByAGEAYwB7AFEAXwB7AGYAbABhAHIAZQBkAH0AfQB7ADEAMAAwADAAfQBcAFwAdABpAG0AZQBzACAAXABcAGwAZQBmAHQAWwBFAEMAXwB7AGYAbABhAHIAZQBkAH0AIABcAFwAdABpAG0AZQBzACAARQBGAF8AewBmAGwAYQByAGUAZAAsAE4AMgBPAH0AXABcAHIAaQBnAGgAdABdAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADEAXwAxAF8AMwBfADEAXwBfADEAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEYAbABhAHIAZQBkAEIAaQBvAGcAYQBzAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAA0ACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEAXwBmAGwAYQByAGUAZABcACIALAAgAFwAIgB2AG8AbAB1AG0AZQAgAG8AZgAgAGIAaQBvAGcAYQBzACAAZgBsAGEAcgBlAGQAXAAiACwAIABcACIAbQAzAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBDAF8AZgBsAGEAcgBlAGQAXAAiACwAIABcACIAZQBuAGUAcgBnAHkAIABjAG8AbgB0AGUAbgB0ACAAZgBhAGMAdABvAHIAIABvAGYAIABzAGwAdQBkAGcAZQAgAGIAaQBvAGcAYQBzACAAZgBsAGEAcgBlAGQAXAAiACwAIABcACIARwBKAC8AbQAzAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAF8AZgBsAGEAcgBlAGQATgAyAE8AXAAiACwAIABcACIAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABmAGwAYQByAGUAZAAgAGIAaQBvAGcAYQBzAFwAIgAsACAAXAAiAGsAZwAgAE4AMgBPAC8ARwBKAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AIgB9AF0ALAAiAHAAcgBvAGoAZQBjAHQATgBhAG0AZQBzACIAOgBbACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEEAcABwAGUAbgBkAGkAYwBlAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAUgBvAHcAUwB0AGEAcgB0AE4AdQBtAGIAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAHIAYQB5AEkAbgBUAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUAVAB3AG8AQwBvAGwAdQBtAG4AcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBPAG4AZQBDAG8AbAB1AG0AbgBBAG4AZABIAGUAYQBkAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBTAHAAbABpAHQAUwB0AHIAaQBuAGcASQBuAHQAbwBBAHIAcgBhAHkAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQwBsAGkAbQBhAHQAZQBaAG8AbgBlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAEkAdABlAG0ARgByAG8AbQBNAGkAbgBNAGEAeAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBTAHUAbQBRAHUAYQBuAHQAaQB0AHkARgByAG8AbQBDAHIAaQB0AGUAcgBpAGEAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAUABlAHIAaQBvAGQAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEYAdQBuAGMAdABpAG8AbgBOAGEAbQBlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAE4AMgBPAEUARgBGAHIAbwBtAFAAcgBvAGQASQByAHIAaQBnAGEAdABpAG8AbgBSAGEAaQBuAGYAYQBsAGwAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBHAGUAdABGAHIAYQBjAFcARQBUACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEMAbwBuAHYAZQByAHQAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAVABvAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADEAXwAxAF8AMQBfADEAXwBfADEAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AVwBhAHMAdABlAHcAYQB0AGUAcgBUAHIAZQBhAHQAbQBlAG4AdAAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQAxAF8AMQBfADEAXwAxAF8AXwAxAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFcAYQBzAHQAZQB3AGEAdABlAHIAVAByAGUAYQB0AG0AZQBuAHQAXwBUAGkAdABsAGUAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEAMQBfADEAXwAxAF8AMQBfAF8AMQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBXAGEAcwB0AGUAdwBhAHQAZQByAFQAcgBlAGEAdABtAGUAbgB0AF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADEAXwAxAF8AMQBfADEAXwBfADEAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AVwBhAHMAdABlAHcAYQB0AGUAcgBUAHIAZQBhAHQAbQBlAG4AdABfAFUAbgBpAHQAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEAMQBfADEAXwAxAF8AMQBfAF8AMQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBXAGEAcwB0AGUAdwBhAHQAZQByAFQAcgBlAGEAdABtAGUAbgB0AF8AUwBvAHUAcgBjAGUAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEAMQBfADEAXwAxAF8AMQBfAF8AMQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBXAGEAcwB0AGUAdwBhAHQAZQByAFQAcgBlAGEAdABtAGUAbgB0AF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEAMQBfADEAXwAxAF8AMQBfAF8AMQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBXAGEAcwB0AGUAdwBhAHQAZQByAFQAcgBlAGEAdABtAGUAbgB0AF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQAxAF8AMQBfADEAXwAxAF8AXwAxAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFcAYQBzAHQAZQB3AGEAdABlAHIAVAByAGUAYQB0AG0AZQBuAHQAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQAxAF8AMQBfADEAXwAxAF8AXwAxAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFcAYQBzAHQAZQB3AGEAdABlAHIAVAByAGUAYQB0AG0AZQBuAHQAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUAQwBvAHIAcgBlAGMAdABpAG8AbgBGAGEAYwB0AG8AcgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AVABpAHQAbABlACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBDAG8AcgByAGUAYwB0AGkAbwBuAEYAYQBjAHQAbwByAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEMAbwByAHIAZQBjAHQAaQBvAG4ARgBhAGMAdABvAHIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFUAbgBpAHQAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEMAbwByAHIAZQBjAHQAaQBvAG4ARgBhAGMAdABvAHIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBDAG8AcgByAGUAYwB0AGkAbwBuAEYAYQBjAHQAbwByAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBEAGEAdABhACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBDAG8AcgByAGUAYwB0AGkAbwBuAEYAYQBjAHQAbwByAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUAQwBvAHIAcgBlAGMAdABpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBfAFQAaQB0AGwAZQAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUAQwBvAHIAcgBlAGMAdABpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUAQwBvAHIAcgBlAGMAdABpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBfAFUAbgBpAHQAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEMAbwByAHIAZQBjAHQAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAXwBTAG8AdQByAGMAZQAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUAQwBvAHIAcgBlAGMAdABpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBfAEQAYQB0AGEAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEMAbwByAHIAZQBjAHQAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBUAGkAdABsAGUAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFUAbgBpAHQAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AUwBvAHUAcgBjAGUAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBXAGEAcwB0AGUAdwBhAHQAZQByAF8ARABhAHQAYQAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAF8AVABpAHQAbABlACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBfAFUAbgBpAHQAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBfAFMAbwB1AHIAYwBlACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAXwBEAGEAdABhACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AVwBhAHMAdABlAF8ARQBuAGUAcgBnAHkAQwBvAG4AdABlAG4AdABGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBCAGkAbwBnAGEAcwBGAGwAYQByAGUAZABfAFQAaQB0AGwAZQAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFcAYQBzAHQAZQBfAEUAbgBlAHIAZwB5AEMAbwBuAHQAZQBuAHQARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAQgBpAG8AZwBhAHMARgBsAGEAcgBlAGQAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBXAGEAcwB0AGUAXwBFAG4AZQByAGcAeQBDAG8AbgB0AGUAbgB0AEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAEIAaQBvAGcAYQBzAEYAbABhAHIAZQBkAF8AVQBuAGkAdAAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFcAYQBzAHQAZQBfAEUAbgBlAHIAZwB5AEMAbwBuAHQAZQBuAHQARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAQgBpAG8AZwBhAHMARgBsAGEAcgBlAGQAXwBTAG8AdQByAGMAZQAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFcAYQBzAHQAZQBfAEUAbgBlAHIAZwB5AEMAbwBuAHQAZQBuAHQARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAQgBpAG8AZwBhAHMARgBsAGEAcgBlAGQAXwBEAGEAdABhACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAQgBpAG8AZwBhAHMARgBsAGEAcgBlAGQAXwBUAGkAdABsAGUAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBCAGkAbwBnAGEAcwBGAGwAYQByAGUAZABfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAEIAaQBvAGcAYQBzAEYAbABhAHIAZQBkAF8AVQBuAGkAdAAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAEIAaQBvAGcAYQBzAEYAbABhAHIAZQBkAF8AUwBvAHUAcgBjAGUAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBCAGkAbwBnAGEAcwBGAGwAYQByAGUAZABfAEQAYQB0AGEAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBXAGEAcwB0AGUAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAQgBpAG8AZwBhAHMARgBsAGEAcgBlAGQAXwBUAGkAdABsAGUAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBXAGEAcwB0AGUAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAQgBpAG8AZwBhAHMARgBsAGEAcgBlAGQAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBXAGEAcwB0AGUAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAQgBpAG8AZwBhAHMARgBsAGEAcgBlAGQAXwBVAG4AaQB0ACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AVwBhAHMAdABlAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAEIAaQBvAGcAYQBzAEYAbABhAHIAZQBkAF8AUwBvAHUAcgBjAGUAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBXAGEAcwB0AGUAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAQgBpAG8AZwBhAHMARgBsAGEAcgBlAGQAXwBEAGEAdABhACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBOADIATwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQAxAF8AMQBfADMAXwAxAF8AXwAxAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBGAGwAYQByAGUAZABCAGkAbwBnAGEAcwAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8ATgAyAE8AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEAMQBfADEAXwAzAF8AMQBfAF8AMQBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ARgBsAGEAcgBlAGQAQgBpAG8AZwBhAHMAXwBUAGkAdABsAGUAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAE4AMgBPAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADEAXwAxAF8AMwBfADEAXwBfADEAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEYAbABhAHIAZQBkAEIAaQBvAGcAYQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBOADIATwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQAxAF8AMQBfADMAXwAxAF8AXwAxAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBGAGwAYQByAGUAZABCAGkAbwBnAGEAcwBfAFUAbgBpAHQAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAE4AMgBPAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADEAXwAxAF8AMwBfADEAXwBfADEAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEYAbABhAHIAZQBkAEIAaQBvAGcAYQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAE4AMgBPAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADEAXwAxAF8AMwBfADEAXwBfADEAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEYAbABhAHIAZQBkAEIAaQBvAGcAYQBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAE4AMgBPAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADEAXwAxAF8AMwBfADEAXwBfADEAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEYAbABhAHIAZQBkAEIAaQBvAGcAYQBzAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8ATgAyAE8AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEAMQBfADEAXwAzAF8AMQBfAF8AMQBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ARgBsAGEAcgBlAGQAQgBpAG8AZwBhAHMAXwBBAHIAZwB1AG0AZQBuAHQAcwAiAF0ALAAiAGwAbwBjAGEAbABlACIAOgB7ACIAbABpAHMAdABTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAsACIALAAiAHIAbwB3AFMAZQBwAGEAcgBhAHQAbwByACIAOgAiADsAIgAsACIAYwBvAGwAdQBtAG4AUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgB0AGgAbwB1AHMAYQBuAGQAcwBTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAsACIALAAiAHQAaABvAHUAcwBhAG4AZABzAFAAbwBzAGkAdABpAG8AbgBzACIAOgBbADMAXQAsACIAZABlAGMAaQBtAGEAbABTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAuACIALAAiAGQAYQB0AGUATwByAGQAZQByACIAOgAiAEQATQBZACIALAAiAGMAdQByAHIAZQBuAGMAeQBTAHkAbQBiAG8AbAAiADoAIgAkACIALAAiAGkAcwBDAHUAcgByAGUAbgBjAHkAUwB5AG0AYgBvAGwATABlAGEAZAAiADoAdAByAHUAZQAsACIAaQBzAEMAdQByAHIAZQBuAGMAeQBTAGUAcABCAHkAUwBwAGEAYwBlACIAOgBmAGEAbABzAGUALAAiAHIAbwB3AEwAZQB0AHQAZQByACIAOgAiAFIAIgAsACIAYwBvAGwAdQBtAG4ATABlAHQAdABlAHIAIgA6ACIAQwAiACwAIgByAGMATABlAGYAdABCAHIAYQBjAGsAZQB0ACIAOgAiAFsAIgAsACIAcgBjAFIAaQBnAGgAdABCAHIAYQBjAGsAZQB0ACIAOgAiAF0AIgAsACIAcwB0AGEAdABlAG0AZQBuAHQAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIAOwAiACwAIgBsAG8AYwBhAGwAZQBOAGEAbQBlACIAOgAiAGUAbgAtAHUAcwAiAH0AfQA=</AFEJSONBlob>
+<AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgAvAC8AIAAtAC0ALQAgAFcAbwByAGsAYgBvAG8AawAgAG0AbwBkAHUAbABlACAALQAtAC0AXABuAC8ALwAgAEEAIABmAGkAbABlACAAbwBmACAAbgBhAG0AZQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAG8AZgAgAHQAaABlACAAZgBvAHIAbQA6AFwAbgAvAC8AIAAgACAAIABuAGEAbQBlACAAPQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AOwBcAG4AXABuACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhACIALAAiAHQAZQB4AHQAIgA6ACIALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgBTAG8AdQByAGMAZQAgAGQAYQB0AGEAIAB0AGgAYQB0ACAAaQBzACAAYwBvAG0AbQBvAG4AIABhAGMAcgBvAHMAcwAgAGEAbABsACAAZQBuAHQAZQByAHAAcgBpAHMAZQAgAHQAeQBwAGUAcwBcAG4ARQB4AGMAZQBsACAAbQBvAGQAdQBsAGUAIABuAGEAbQBlADoAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFMAbwB1AHIAYwBlADoAIABOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQBcAG4ATgBJAFIAXwAyADAAMgAzAF8AVgBvAGwAMQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXABuAHAAIAA9ACAAZABlAG4AcwBpAHQAeQAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAIAAoADAALgA2ADcAOAA0ACAAawBnAC8AbQAzACkAXABuAFQAYQBrAGUAbgAgAGYAcgBvAG0AIAB0AGgAZQAgAE4AYQB0AGkAbwBuAGEAbAAgAEcAcgBlAGUAbgBoAG8AdQBzAGUAIABhAG4AZAAgAEUAbgBlAHIAZwB5ACAAUgBlAHAAbwByAHQAaQBuAGcAIABcAG4AKABNAGUAYQBzAHUAcgBlAG0AZQBuAHQAKQAgAEQAZQB0AGUAcgBtAGkAbgBhAHQAaQBvAG4AIAAyADAAMAA4AFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHAAIAA9ACAAZABlAG4AcwBpAHQAeQAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcALwBtADMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgADIAMAAyADMAIABWAG8AbAB1AG0AZQAgADEAOgAgAEUAcQB1AGEAdABpAG8AbgBzACAAMwAuAEIALgAxAGEAXwAyACwAIAAzAC4AQgAuADEAYwBfADIALAAgADMALgBCAC4AMwBfADEALAAgADMALgBCAC4ANABnAF8AMgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAMAAuADYANwA4ADQAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAFwAbgBDAGcAIAA9ACAANAA0AC8AMgA4ACAAZgBhAGMAdABvAHIAIAB0AG8AIABjAG8AbgB2AGUAcgB0ACAAZQBsAGUAbQBlAG4AdABhAGwAIABtAGEAcwBzACAAbwBmACAATgAyAE8AIAB0AG8AIABtAG8AbABlAGMAdQBsAGEAcgAgAG0AYQBzAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABOADIATwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBDAGcATgAyAE8AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAYQBjAHQAbwByAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgADIAMAAyADMAIABWAG8AbAB1AG0AZQAgADEAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgANAA0AC8AMgA4ACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAFwAbgBGAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABnAGEAcwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgBhAGMAdABvAHIAIAB0AG8AIABjAG8AbgB2AGUAcgB0ACAAZQBsAGUAbQBlAG4AdABhAGwAIABtAGEAcwBzACAAbwBmACAAZwBhAHMAIAB0AG8AIABtAG8AbABlAGMAdQBsAGEAcgAgAG0AYQBzAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBDAGcAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgBhAGMAdABvAHIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFgAWABYAFgAWABYAFgAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADgALAAgADQALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAYQBzAFwAIgAsACAAXAAiAEMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBcACIALAAgAFwAIgBDAG8AbgB2AGUAcgBzAGkAbwBuACAAZgBhAGMAdABvAHIAIAAxAFwAIgAsACAAXAAiAEMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgADIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyAFwAIgAsACAAXAAiADQANAAvADEAMgBcACIALAAgADQANAAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMASAA0AFwAIgAsACAAXAAiADEANgAvADEAMgBcACIALAAgADEANgAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AMgBPAFwAIgAsACAAXAAiADQANAAvADIAOABcACIALAAgADQANAAsACAAMgA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB4AFwAIgAsACAAXAAiADQANgAvADEANABcACIALAAgADQANgAsACAAMQA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwBcACIALAAgAFwAIgAyADgALwAxADIAXAAiACwAIAAyADgALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAE8AMgAgAEwAaQBtAGUAXAAiACwAIABcACIANAA0AC8AMQAyAFwAIgAsACAANAA0ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBNAFYATwBDAFwAIgAsACAAXAAiADEANAAvADEAMgBcACIALAAgADEANAAsACAAMQAyAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABOADIATwBcAG4ARwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAGcAcgBlAGUAbgBoAG8AdQBzAGUAIABnAGEAcwBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABnAHIAZQBlAG4AaABvAHUAcwBlACAAZwBhAHMAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARwBXAFAATgAyAE8AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgBhAGMAdABvAHIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFgAWABYAFgAWABYAFgAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADgALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAYQBzAFwAIgAsACAAXAAiAEMATwAyAC0AZQAgAGYAYQBjAHQAbwByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAE8AMgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBIADQAXAAiACwAIAAyADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgAyAE8AXAAiACwAIAAyADYANQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAEYANABcACIALAAgADYANgAzADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwAyAEYANgBcACIALAAgADEAMgAyADAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAEYANgBcACIALAAgADIAMgA4ADAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAEYAMwBcACIALAAgADEANwAyADAAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAcwB0AGEAdABlAHMAIABhAG4AZAAgAHQAZQByAHIAaQB0AG8AcgBpAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA5ACwAIAAzACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHQAYQB0AGUALwBUAGUAcgByAGkAdABvAHIAeQBcACIALAAgAFwAIgBDAG8AbQBtAG8AbgAgAE4AYQBtAGUAXAAiACwAIABcACIAQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AZQB3ACAAUwBvAHUAdABoACAAVwBhAGwAZQBzAFwAIgAsACAAXAAiAE4AZQB3ACAAUwBvAHUAdABoACAAVwBhAGwAZQBzAFwAIgAsACAAXAAiAE4AUwBXAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAQwBhAHAAaQB0AGEAbAAgAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAEEAQwBUAFwAIgAsACAAXAAiAEEAQwBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAGkAYwB0AG8AcgBpAGEAXAAiACwAIABcACIAVgBpAGMAdABvAHIAaQBhAFwAIgAsACAAXAAiAFYASQBDAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBRAHUAZQBlAG4AcwBsAGEAbgBkAFwAIgAsACAAXAAiAFEAdQBlAGUAbgBzAGwAYQBuAGQAXAAiACwAIABcACIAUQBMAEQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAbwB1AHQAaAAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFMAbwB1AHQAaAAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFMAQQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQBcACIALAAgAFwAIgBXAEEAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAYQBzAG0AYQBuAGkAYQBcACIALAAgAFwAIgBUAGEAcwBtAGEAbgBpAGEAXAAiACwAIABcACIAVABBAFMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwByAHQAaABlAHIAbgAgAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAE4AbwByAHQAaABlAHIAbgAgAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAE4AVABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQBCAFMAIABTAHQAYQB0AGkAcwB0AGMAYQBsACAAQQByAGUAYQBzACAATABlAHYAZQBsACAANAAgAC0AIABXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAEIAdQByAGUAYQB1ACAAbwBmACAAUwB0AGEAdABpAHMAdABpAGMAcwAgACgAQQBCAFMAKQAgAC0AIABTAHQAYQB0AGkAcwB0AGkAYwBhAGwAIABBAHIAZQBhAHMAIABMAGUAdgBlAGwAIAAyACAALQAgADIAMAAyADEAIAAtACAAUwBoAGEAcABlAGYAaQBsAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADEALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAQQAgADQAIABOAGEAbQBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBCAHUAbgBiAHUAcgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAGEAbgBkAHUAcgBhAGgAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABJAG4AbgBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABOAG8AcgB0AGgAIABFAGEAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAATgBvAHIAdABoACAAVwBlAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAFMAbwB1AHQAaAAgAEUAYQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABTAG8AdQB0AGgAIABXAGUAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAAVwBoAGUAYQB0ACAAQgBlAGwAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhACAALQAgAE8AdQB0AGIAYQBjAGsAIAAoAE4AbwByAHQAaAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAATwB1AHQAYgBhAGMAawAgACgAUwBvAHUAdABoACkAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAdwBlAHQAIABhAG4AZAAgAGQAcgB5ACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAyADoAIABUAHIAYQBuAHMAbABhAHQAaQBuAGcAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBzACAAdABvACAAdwBlAHQAIABhAG4AZAAgAGQAcgB5ACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAdwBhAHIAbQAgAC8AIABjAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAvACAAZAByAHkAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAIABhAG4AZAAgAGgAaQBnAGgAIAB0AGUAbQBwACAAYwBsAGEAcwBzAGUAcwAgAHQAbwAgAGEAYwBjAG8AbQBtAG8AZABhAHQAZQAgAGMAbABpAG0AYQB0AGUAIABzAGMAZQBuAGEAcgBpAG8AcwAgAGUAeABjAGwAdQBkAGUAZAAgAGIAeQAgAFYARQBFAFIARwAgAGMAcgBpAHQAZQByAGkAYQAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAGkAeABlAGQAIAB0AHkAcABvACAALQAgAEMAaABhAG4AZwBlAGQAIABcAHUAMAAwADIANwBGAHIAeQBcAHUAMAAwADIANwAgAHQAbwAgAFwAdQAwADAAMgA3AEQAcgB5AFwAdQAwADAAMgA3AC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADUALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAFcAZQB0ACAAbwByACAARAByAHkAIABaAG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABtAG8AbgB0AGEAbgBlAFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAHcAZQB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABkAHIAeQBcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdABcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAtACAAaABpAGcAaAAgAHQAZQBtAHAAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAaABpAGcAaAAgAHQAZQBtAHAAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA1ACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAB3AGEAcgBtACAALwAgAGMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC8AIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdAAgAGEAbgBkACAAaABpAGcAaAAgAHQAZQBtAHAAIABjAGwAYQBzAHMAZQBzACAAdABvACAAYQBjAGMAbwBtAG0AbwBkAGEAdABlACAAYwBsAGkAbQBhAHQAZQAgAHMAYwBlAG4AYQByAGkAbwBzACAAZQB4AGMAbAB1AGQAZQBkACAAYgB5ACAAVgBFAEUAUgBHACAAYwByAGkAdABlAHIAaQBhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAaQB4AGUAZAAgAHQAeQBwAG8AIABpAG4AIABNAEEAVAAgAHYAYQBsAHUAZQAgAGYAbwByACAAdwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAYwBoAGEAbgBnAGUAZAAgADEAMAAgAHQAbwAgADEAMQAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIABtAGkAbgAgAGEAbgBkACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAZgBvAHIAIABNAEEAVAAsACAATQBBAFAALAAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAIABwAGUAcgAgAHkAZQBhAHIALAAgAGUAbABlAHYAYQB0AGkAbwBuACwAIABNAEEAUAA6AFAARQBUACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlAHMAIABmAHIAbwBtACAAcgBlAGEAbAAgAGMAbABpAG0AYQB0AGUAIABkAGEAdABhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAQQBGACAAYQBjAGMAZQBwAHQAcwAgAHIAYQBpAG4AZgBhAGwAbAAgAGEAcwAgAGEAIABwAHIAbwB4AHkAIABmAG8AcgAgAHAAcgBlAGMAaQBwAGkAdABhAHQAaQBvAG4ALgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOQAsACAAMQA2ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAGwAaQBtAGEAdABlACAAWgBvAG4AZQBcACIALAAgAFwAIgBNAEEAVABcACIALAAgAFwAIgBNAEEAUABcACIALAAgAFwAIgBGAHIAbwBzAHQAIABkAGEAeQBzACAAcABlAHIAIAB5AGUAYQByAFwAIgAsACAAXAAiAEUAbABlAHYAYQB0AGkAbwBuAFwAIgAsACAAXAAiAE0AQQBQADoAUABFAFQAXAAiACwAIABcACIATQBpAG4AIAB0AGUAbQBwAFwAIgAsACAAXAAiAE0AYQB4ACAAdABlAG0AcABcACIALAAgAFwAIgBNAGkAbgAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBNAGEAeAAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBNAGkAbgAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAXAAiACwAIABcACIATQBhAHgAIABmAHIAbwBzAHQAIABkAGEAeQBzAFwAIgAsACAAXAAiAE0AaQBuACAAZQBsAGUAdgBhAHQAaQBvAG4AXAAiACwAIABcACIATQBhAHgAIABlAGwAZQB2AGEAdABpAG8AbgBcACIALAAgAFwAIgBNAGkAbgAgAE0AQQBQADoAUABFAFQAXAAiACwAIABcACIATQBpAG4AIABNAEEAUAA6AFAARQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABtAG8AbgB0AGEAbgBlAFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQA4ACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAwADAAIABtAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAMQA4AC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAANwAsACAAMQAwADAAMAAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAHcAZQB0AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQA4ACAAQwBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADIAMAAwADAAIABtAG0AXAAiACwAIABcACIAZCIgADcAXAAiACwAIABcACIAZCIgADEAMAAwADAAIABtAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAMQA4AC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAyADAAMAAwAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQAuADkAOQA5ACwAIAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAOAAgAEMAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADAAMAAwACAAbQBtACAALQAgAGQiIAAyADAAMAAwACAAbQBtAFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgADEAOAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAAMQAwADAAMAAuADAAMAAxACwAIAAyADAAMAAwACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQAuADkAOQA5ACwAIAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAGQAcgB5AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQA4ACAAQwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAwADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAXAAiACwAIAAxADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgADEALgAwADAAMQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAGQiIAAxAFwAIgAsACAAMQAwAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAgAC0AOQA5ADkAOQA5ADkALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMAAgAEMAIAAtACAAZCIgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxAFwAIgAsACAALQA5ADkAOQA5ADkAOQAsACAAMQAwACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAxAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMAAgAEMAIAAtACAAZCIgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAZCIgADEAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAMQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBBAHAAcABlAG4AZABpAGMAZQBzAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdABlADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AQQBUACAAPQAgAG0AZQBhAG4AIABhAG4AbgB1AGEAbAAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBBAFAAIAA9ACAAbQBlAGEAbgAgAGEAbgBuAHUAYQBsACAAcAByAGUAYwBpAHAAaQB0AGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABFAFQAIAA9ACAAcABvAHQAZQBuAHQAaQBhAGwAIABlAHYAYQBwAG8AdAByAGEAbgBzAHAAaQByAGEAdABpAG8AbgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABBAGQAZABlAGQAIABlAHgAdAByAGEAIABNAEEAVAAgAG0AaQBuACAAYQBuAGQAIABNAEEAVAAgAG0AYQB4ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGMAYQBsAGMAdQBsAGEAdABlACAAegBvAG4AZQAgAGYAcgBvAG0AIAByAGUAYQBsACAAdABlAG0AcABlAHIAYQB0AHUAcgBlACAAZABhAHQAYQAuAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANAAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AHUAcgBlACAAWgBvAG4AZQBcACIALAAgAFwAIgBNAGUAZABpAGEAbgAgAEEAbgBuAHUAYQBsACAAVABlAG0AcABlAHIAYQB0AHUAcgBlACAAKABNAEEAVAApAFwAIgAsACAAXAAiAE0AaQBuACAATQBBAFQAXAAiACwAIABcACIATQBhAHgAIABNAEEAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgAFwAIgBlIiAAMgA2ACAAQwBcACIALAAgADIANgAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIABcACIAMQA1ACAALQAgADIANQAgAEMAXAAiACwAIAAxADUALAAgADIANQAuADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIABcACIAZCIgADEANAAgAEMAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADQALgA5ADkAOQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAAQQBkAGQAZQBkACAAZQB4AHQAcgBhACAAUgBhAGkAbgBmAGEAbABsACAAbQBpAG4AIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAG0AYQB4ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGMAYQBsAGMAdQBsAGEAdABlACAAegBvAG4AZQAgAGYAcgBvAG0AIAByAGUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAZABhAHQAYQAuAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBhAGkAbgBmAGEAbABsACAAWgBvAG4AZQBcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABtAGkAbgBcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABtAGEAeABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbAAgAFwAdQAwADAAMwBlACAANgAwADAAbQBtAFwAIgAsACAANgAwADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATABvAHcAIAByAGEAaQBuAGYAYQBsAGwAXAAiACwAIABcACIAQQBuAG4AdQBhAGwAIAByAGEAaQBuAGYAYQBsAGwAIABkIiAANgAwADAAbQBtAFwAIgAsACAALQA5ADkAOQA5ADkAOQAsACAANgAwADAAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABaAG8AbgBlAFwAIgAsACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAGMAcgBpAHQAZQByAGkAYQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATABlAGEAYwBoAGkAbgBnACAAbwBjAGMAdQByAHMAXAAiACwAIABcACIAowMoADXYX9w12E7cNdhW3DXYW9wpAFwAdQAwADAAMwBlAKMDKAA12DjcNdhH3DAAKQArADXYYNw12FzcNdhW3DXYWdwgADXYZNw12E7cNdhh3DXYUtw12F/cIAAOITXYXNw12FncNdhR3DXYVtw12FvcNdhU3CAANdhQ3DXYTtw12F3cNdhO3DXYUNw12FbcNdhh3DXYZtxcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATABlAGEAYwBoAGkAbgBnACAAZABvAGUAcwAgAG4AbwB0ACAAbwBjAGMAdQByAFwAIgAsACAAXAAiAKMDKAA12F/cNdhO3DXYVtw12FvcKQBkIqMDKAA12DjcNdhH3DAAKQArADXYYNw12FzcNdhW3DXYWdwgADXYZNw12E7cNdhh3DXYUtw12F/cIAAOITXYXNw12FncNdhR3DXYVtw12FvcNdhU3CAANdhQ3DXYTtw12F3cNdhO3DXYUNw12FbcNdhh3DXYZtxcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXABuADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAbgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAEQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcwAgAGkAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAXAAiACwAXAAiAEYAcgBhAGMAVwBFAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFkAZQBzACAALQAgAGkAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwAgAC0AIABuAG8AdAAgAGkAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAXAAiACwAIAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoACgAXAAiAFwAIgApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAGQAYQB0AGEAIABzAGMAbwByAGUAcwAgAGYAbwByACAAcwBjAG8AcABlACAAMwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABYAFgAWABYAFgAWABYAFgAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABhAHQAYQAgAHMAbwB1AHIAYwBlAFwAIgAsACAAXAAiAEQAYQB0AGEAIABzAGMAbwByAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAbgB0AGUAcgBuAGEAdABpAG8AbgBhAGwAIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAcwBjAG8AcABlACAAMwAgAGQAYQB0AGEAYgBhAHMAZQBcACIALAAgADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB0AGEAdABlACAAbwByACAAcgBlAGcAaQBvAG4AYQBsACAAcwBjAG8AcABlACAAMwAgAGQAYQB0AGEAYgBhAHMAZQBcACIALAAgADMAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBtAGkAcwBzAGkAbwBuAHMAIABpAG4AdABlAG4AcwBpAHQAeQAgAGMAYQBsAGMAdQBsAGEAdABlAGQAIABmAHIAbwBtACAAYQBwAHAAcgBvAHYAZQBkACAAbQBlAHQAaABvAGQAXAAiACwAIAA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAZQByAGkAZgBpAGUAZAAgAGMAcgBlAGQAZQBuAHQAaQBhAGwAIABtAGEAdABjAGgAaQBuAGcAIABJAFMATwAxADQAMAA2ADcAXAAiACwAIAA1AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXABuADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAbgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgARABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAVgBvAGwAdQBtAGUAIAAxADoAIABMAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmACAAKAAzAC4ARAAuAGIALgAyACkAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAcgBhAGMATABFAEEAQwBIAFwAIgAsADAALgAyADQAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoACgAXAAiAFwAIgApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABuAGkAdAByAG8AZwBlAG4AIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABuAGkAdAByAG8AZwBlAG4AIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABrAGcAIABOADIATwAtAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgAFYAbwBsAHUAbQBlACAAMQA6ACAARQBxAHUAYQB0AGkAbwBuACAAMwAuAEQALgBCAF8AMQAwAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARgBsAGUAYQBjAGgAXAAiACwAMAAuADAAMQAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoACgAXAAiAFwAIgApACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXABuAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADEAXABuAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAZgBvAHIAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AIAAoAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AKQAgACgARQBGAE4AMgBPACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAGYAbwByACAAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAGsAZwAgAE4AMgBPAC0ATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADIALgAyAC4AMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQA0ACwAIAA1ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABqAFwAIgAsAFwAIgBFAEYATgAyAE8AXAAiACwAIABcACIAUAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAbwBuAGwAeQBcACIALAAgAFwAIgBJAHIAcgBpAGcAYQB0AGkAbwBuACAAbQBlAHQAaABvAGQAXAAiACwAIABcACIAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsADAALgAwADAANQA5ACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwAFwAIgAsADAALgAwADAANwAsACAAXAAiAEMAcgBvAHAAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsADAALgAwADAAMQA4ACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEwAbwB3ACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQBcACIALAAwAC4AMAAwADEAOAAsACAAXAAiAFAAYQBzAHQAdQByAGUAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcAAgACgAbABvAHcAIAByAGEAaQBuAGYAYQBsAGwAKQBcACIALAAwAC4AMAAwADIAOQAsACAAXAAiAEMAcgBvAHAAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAGMAcgBvAHAAIAAoAGgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAKQBcACIALAAwAC4AMAAwADgALAAgAFwAIgBDAHIAbwBwAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIASABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB1AGcAYQByAFwAIgAsADAALgAwADEAOQA5ACwAIABcACIAUwB1AGcAYQByAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AdAB0AG8AbgBcACIALAAwAC4AMAAwADUAMwAsACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAG8AcgB0AGkAYwB1AGwAdAB1AHIAYQBsACAAYwByAG8AcABzAFwAIgAsADAALgAwADAANgA0ACwAIABcACIASABvAHIAdABpAGMAdQBsAHQAdQByAGEAbAAgAGMAcgBvAHAAcwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBpAGMAZQAgACgAYwBvAG4AdABpAG4AdQBvAHUAcwAgAGYAbABvAG8AZABpAG4AZwApAFwAIgAsADAALgAwADAAMwAsACAAXAAiAFIAaQBjAGUAXAAiACwAIABcACIAQwBvAG4AdABpAG4AdQBvAHUAcwAgAGYAbABvAG8AZABpAG4AZwBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBpAGMAZQAgACgAcwBpAG4AZwBsAGUAIABhAG4AZAAgAG0AdQBsAHQAaQBwAGwAZQAgAGQAcgBhAGkAbgBhAGcAZQAsACAAbwByACAAYQBsAHQAZQByAG4AYQB0AGUAIAB3AGUAdAB0AGkAbgBnACAAYQBuAGQAIABkAHIAeQBpAG4AZwApAFwAIgAsADAALgAwADAANQAsACAAXAAiAFIAaQBjAGUAXAAiACwAIABcACIAUwBpAG4AZwBsAGUAIABhAG4AZAAgAG0AdQBsAHQAaQBwAGwAZQAgAGQAcgBhAGkAbgBhAGcAZQAsACAAbwByACAAYQBsAHQAZQByAG4AYQB0AGUAIAB3AGUAdAB0AGkAbgBnACAAYQBuAGQAIABkAHIAeQBpAG4AZwBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBxAHUAYQBjAHUAbAB0AHUAcgBlAFwAIgAsADAALgAwADAAMgA2ACwAIABcACIAQQBxAHUAYQBjAHUAbAB0AHUAcgBlAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAG8AcgBlAHMAdAByAHkAXAAiACwAMAAuADAAMAAxADgALAAgAFwAIgBGAG8AcgBlAHMAdAByAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA1ACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGUAbQBvAHYAZQBkACAAZAB1AHAAbABpAGMAYQB0AGUAIABcAHUAMAAwADIANwBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAB1ADAAMAAyADcAIAByAG8AdwAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGUAbQBvAHYAZQBkACAAYQBzAHQAZQByAGkAcwBrAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAFwAdQAwADAAMgA3AHAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAG8AbgBsAHkAXAB1ADAAMAAyADcALAAgAFwAdQAwADAAMgA3AHIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAXAB1ADAAMAAyADcAIABhAG4AZAAgAFwAdQAwADAAMgA3AGkAcgByAGkAZwBhAHQAaQBvAG4AIABtAGUAdABoAG8AZABcAHUAMAAwADIANwAgAGMAbwBsAHUAbQBuAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAdQBwAGwAaQBjAGEAdABlAGQAIABcAHUAMAAwADIANwBuAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQBcAHUAMAAwADIANwAgAHIAbwB3ACAAdwBpAHQAaAAgAHMAYQBtAGUAIABFAEYAIABmAG8AcgAgAGwAbwB3ACAAYQBuAGQAIABoAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAFwAbgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABDAGgAYQBwAHQAZQByACAAMQAsACAAcwBlAGMAdABpAG8AbgAgADEALgA4AC4AMgAgAEwAZQBhAGMAaABpAG4AZwAsACAAYwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBzAFwAbgBJAFAAQwBDADoAIABOADIATwAgAEUATQBJAFMAUwBJAE8ATgBTACAARgBSAE8ATQAgAE0AQQBOAEEARwBFAEQAIABTAE8ASQBMAFMALAAgAEEATgBEACAAQwBPADIAIABFAE0ASQBTAFMASQBPAE4AUwAgAEYAUgBPAE0AIABMAEkATQBFACAAQQBOAEQAIABVAFIARQBBACAAQQBQAFAATABJAEMAQQBUAEkATwBOAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwBXAEUAVAAgAGYAbwByACAAaQByAHIAaQBnAGEAdABpAG8AbgAgAHQAeQBwAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAEMAaABhAHAAdABlAHIAIAAxACwAIABzAGUAYwB0AGkAbwBuACAAMQAuADgALgAyACAATABlAGEAYwBoAGkAbgBnACwAIABjAGwAaQBtAGEAdABlACAAYQBuAGQAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBJAFAAQwBDACAAMgAwADEAOQAgAFIAZQBmAGkAbgBlAG0AZQBuAHQAIABWAG8AbAB1AG0AZQAgADQAOgAgAEMAaABhAHAAdABlAHIAIAAxADEAOgAgAE4AMgBPACAARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAATQBhAG4AYQBnAGUAZAAgAFMAbwBpAGwAcwAsACAAYQBuAGQAIABDAE8AMgAgAEUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAEwAaQBtAGUAIABhAG4AZAAgAFUAcgBlAGEAIABBAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGkAbwBuACAAdAB5AHAAZQAgAGkAcgBcACIALABcACIARgByAGEAYwBXAEUAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAByAGkAcAAgAGkAcgByAGkAZwBhAHQAaQBvAG4AXAAiACwAIAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAcAByAGkAbgBrAGwAZQByACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB1AHIAZgBhAGMAZQAgAGkAcgByAGkAZwBhAHQAaQBvAG4AXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AdABoAGUAcgAgAGkAcgByAGkAZwBhAHQAaQBvAG4AXAAiACwAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAARgBSAE8ATQAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAAVABhAGIAbABlACAAYwByAGUAYQB0AGUAZAAgAGIAYQBzAGUAZAAgAG8AbgAgAFYARQBFAFIARwAgAHQAZQB4AHQAIABcAHUAMAAwADIANwBBAHIAZQBhAHMAIABhAHIAZQAgAHMAdQBiAGoAZQBjAHQAIAB0AG8AIABsAGUAYQBjAGgAaQBuAGcAIAAoAGkALgBlAC4ALAAgAGkAbgAgAHQAaABlACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQApACAAdwBoAGUAbgAuAC4ALgAgAHQAaABlACAAbABhAG4AZAAgAGkAcwAgAGkAcgByAGkAZwBhAHQAZQBkACAAKABlAHgAYwBlAHAAdAAgAGQAcgBpAHAAIABpAHIAcgBpAGcAYQB0AGkAbwBuACkALgBcAHUAMAAwADIANwBcACIAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAFwAbgBUAGEAYgBsAGUAIABBAC4AMgAuADIALgAyADoAIABFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAdQByAGkAbgBlACAAYQBuAGQAIABkAHUAbgBnACAAZABlAHAAbwBzAGkAdABlAGQAIABvAG4AIABwAGEAcwB0AHUAcgBlACwAIAByAGEAbgBnAGUAIABvAHIAIABwAGEAZABkAG8AYwBrACAAKABrAGcAIABOADIATwAtAE4ALwBrAGcAIABOACkAIAAoAEUARgBQAFIAUAApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAdQByAGkAbgBlACAAYQBuAGQAIABkAHUAbgBnACAAZABlAHAAbwBzAGkAdABlAGQAIABvAG4AIABwAGEAcwB0AHUAcgBlACwAIAByAGEAbgBnAGUAIABvAHIAIABwAGEAZABkAG8AYwBrAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AMgBPACAALQAgAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADIALgAyAC4AMgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAEUARgBQAFIAUABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAAyAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABDAGgAYQBuAGcAZQBkACAAXAB1ADAAMAAyADcARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBzAFwAdQAwADAAMgA3ACAAdABvACAAcwBpAG4AZwB1AGwAYQByACAAXAB1ADAAMAAyADcARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcAHUAMAAwADIANwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAG8AbgB0AGgAcwAgAHQAbwAgAFMAZQBhAHMAbwBuAHMAIABNAGEAcABwAGkAbgBnAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBvAG4AdABoAFwAIgAsACAAXAAiAFMAZQBhAHMAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAGEAbgB1AGEAcgB5AFwAIgAsACAAXAAiAFMAdQBtAG0AZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAGUAYgByAHUAYQByAHkAXAAiACwAIABcACIAUwB1AG0AbQBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQByAGMAaABcACIALAAgAFwAIgBBAHUAdAB1AG0AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBwAHIAaQBsAFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAGEAeQBcACIALAAgAFwAIgBBAHUAdAB1AG0AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASgB1AG4AZQBcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASgB1AGwAeQBcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQB1AGcAdQBzAHQAXAAiACwAIABcACIAVwBpAG4AdABlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAZQBwAHQAZQBtAGIAZQByAFwAIgAsACAAXAAiAFMAcAByAGkAbgBnAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBPAGMAdABvAGIAZQByAFwAIgAsACAAXAAiAFMAcAByAGkAbgBnAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdgBlAG0AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAZQBjAGUAbQBiAGUAcgBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBhAG4AdQByAGUAIABNAGEAbgBhAGcAZQBtAGUAbgB0ACAAEyAgAE0AZQB0AGgAYQBuAGUAIABjAG8AbgB2AGUAcgBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABwAGUAcgAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAIAAoAGYAcgBhAGMAdABpAG8AbgApACAAKABNAEMARgBpAG0AKQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAxAC4AOAAuADEAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIAMQAsACAAMQA2ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAE0AQQBUACAAKAC6AEMAKQBcACIALAAgAFwAIgBVAG4AYwBvAHYAZQByAGUAZAAgAGEAbgBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuAFwAIgAsACAAXAAiAEMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBcACIALAAgAFwAIgBMAGkAcQB1AGkAZAAgAFMAbAB1AHIAcgB5ACAAKAB3AGkAdABoAG8AdQB0ACAAbgBhAHQAdQByAGEAbAAgAGMAcgB1AHMAdAApAFwAIgAsACAAXAAiAEQAYQBpAGwAeQAgAHMAcAByAGUAYQBkACAAKABiACkAXAAiACwAIABcACIAQwBvAG0AcABvAHMAdABpAG4AZwAgACgAcABhAHMAcwBpAHYAZQAgAHcAaQBuAGQAcgBvAHcAKQBcACIALAAgAFwAIgBTAG8AbABpAGQAIABTAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAFAAaQB0ACAAUwB0AG8AcgBhAGcAZQAgAFwAdQAwADAAMwBjADEAIABtAG8AbgB0AGgAXAAiACwAIABcACIARABlAGUAcAAgAEwAaQB0AHQAZQByAFwAIgAsACAAXAAiAFAAbwB1AGwAdAByAHkAIABNAGEAbgB1AHIAZQAgACgAdwBpAHQAaAAvAHcAaQB0AGgAbwB1AHQAIABsAGkAdAB0AGUAcgApAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAcAByAG8AYwBlAHMAcwBpAG4AZwAgAGkAbgB0AG8AIABwAGUAbABsAGUAdABpAHoAZQBkACAAZgBlAHIAdABpAGwAaQBzAGUAcgBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgAgAHQAbwAgAHMAbwBpAGwAXAAiACwAIABcACIAUABhAHMAdAB1AHIAZQAsACAAUgBhAG4AZwBlACAAYQBuAGQAIABQAGEAZABkAG8AYwBrACAAKABjACkAKABkACkAXAAiACwAIABcACIATQBBAFQAIAByAGEAdwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgAFwAIgBkIjEAMABcACIALAAgADAALgA2ADYALAAgADAALgAxACwAIAAwAC4AMQAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIAAxADEALAAgADAALgA2ADgALAAgADAALgAxACwAIAAwAC4AMQAxACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgADEAMgAsACAAMAAuADcALAAgADAALgAxACwAIAAwAC4AMQAzACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgADEAMwAsACAAMAAuADcAMQAsACAAMAAuADEALAAgADAALgAxADQALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQA0ACwAIAAwAC4ANwAzACwAIAAwAC4AMQAsACAAMAAuADEANQAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA1ACwAIAAwAC4ANwA0ACwAIAAwAC4AMQAsACAAMAAuADEANwAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEANQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEANgAsACAAMAAuADcANQAsACAAMAAuADEALAAgADAALgAxADgALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADcALAAgADAALgA3ADYALAAgADAALgAxACwAIAAwAC4AMgAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEANwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEAOAAsACAAMAAuADcANwAsACAAMAAuADEALAAgADAALgAyADIALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADkALAAgADAALgA3ADcALAAgADAALgAxACwAIAAwAC4AMgA0ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgAwACwAIAAwAC4ANwA4ACwAIAAwAC4AMQAsACAAMAAuADIANgAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIAMQAsACAAMAAuADcAOAAsACAAMAAuADEALAAgADAALgAyADkALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADIALAAgADAALgA3ADgALAAgADAALgAxACwAIAAwAC4AMwAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgAzACwAIAAwAC4ANwA5ACwAIAAwAC4AMQAsACAAMAAuADMANAAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIANAAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgAzADcALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADUALAAgADAALgA3ADkALAAgADAALgAxACwAIAAwAC4ANAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AXAAiACwAIAAyADYALAAgADAALgA3ADkALAAgADAALgAxACwAIAAwAC4ANAA0ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AXAAiACwAIAAyADcALAAgADAALgA4ACwAIAAwAC4AMQAsACAAMAAuADQAOAAsACAAMAAuADAAMQAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIANwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtAFwAIgAsACAAXAAiAGUiMgA4AFwAIgAsACAAMAAuADgALAAgADAALgAxACwAIAAwAC4ANQAsACAAMAAuADAAMQAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBBAG4AYQBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuAFwAIgAsACAAXAAiAEQAaQBnAGUAcwB0AGUAcgAgAC8AIABjAG8AdgBlAHIAZQBkACAAbABhAGcAbwBvAG4AcwBcACIALAAgAFwAIgBMAGkAcQB1AGkAZAAgAHMAeQBzAHQAZQBtAHMAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAXAAiACwAIABcACIAQwBvAG0AcABvAHMAdABpAG4AZwAgACgAcABhAHMAcwBpAHYAZQAgAHcAaQBuAGQAcgBvAHcAKQBcACIALAAgAFwAIgBTAG8AbABpAGQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAFAAaQB0ACAAcwB0AG8AcgBhAGcAZQBcACIALAAgAFwAIgBEAGUAZQBwACAAbABpAHQAdABlAHIAXAAiACwAIABcACIAUABvAHUAbAB0AHIAeQAgAG0AYQBuAHUAcgBlACAAdwBpAHQAaAAgAGIAZQBkAGQAaQBuAGcAXAAiACwAIABcACIAUABvAHUAbAB0AHIAeQAgAG0AYQBuAHUAcgBlACAAdwBpAHQAaABvAHUAdAAgAGIAZQBkAGQAaQBuAGcAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABwAHIAbwBjAGUAcwBzAGkAbgBnAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuAFwAIgAsACAAXAAiAFAAYQBzAHQAdQByAGUAIAByAGEAbgBnAGUAIABhAG4AZAAgAHAAYQBkAGQAbwBjAGsAXAAiACwAIABcACIATQBBAFQAIAByAGEAdwBcACIAIABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIA